--- a/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DACE3759-A541-4D21-861B-546D86A2BC61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{757F3D22-E3BB-4D27-8561-4D05F0B5F506}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -796,7 +796,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>14,25,46,73</t>
+    <t>14,25,46,68,87</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>

--- a/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{085285D3-0F29-425B-AF55-08523884D48B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DACE3759-A541-4D21-861B-546D86A2BC61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="721" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="721" uniqueCount="238">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -792,15 +792,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>10,53</t>
+    <t>12,30,55,80,133,155,175,205,238</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>40,72,144,175,205,238</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>55,80,144,175,205,238</t>
+    <t>14,25,46,73</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1344,7 +1340,7 @@
         <v>43400002</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I5" s="1">
         <v>1</v>
@@ -1397,7 +1393,7 @@
         <v>43400002</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="I6" s="1">
         <v>1</v>
@@ -1450,7 +1446,7 @@
         <v>43400002</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="I7" s="1">
         <v>1</v>
@@ -1503,7 +1499,7 @@
         <v>43400002</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="I8" s="1">
         <v>1</v>

--- a/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{757F3D22-E3BB-4D27-8561-4D05F0B5F506}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DACE3759-A541-4D21-861B-546D86A2BC61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -796,7 +796,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>14,25,46,68,87</t>
+    <t>14,25,46,73</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>

--- a/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DACE3759-A541-4D21-861B-546D86A2BC61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06A7C9E9-F33B-46CF-AD6D-A562578AAA2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -796,7 +796,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>14,25,46,73</t>
+    <t>11,38,59</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>

--- a/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06A7C9E9-F33B-46CF-AD6D-A562578AAA2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DACE3759-A541-4D21-861B-546D86A2BC61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -796,7 +796,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>11,38,59</t>
+    <t>14,25,46,73</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>

--- a/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DACE3759-A541-4D21-861B-546D86A2BC61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB740E99-425B-4B61-8EB8-467DE074732C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -796,7 +796,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>14,25,46,73</t>
+    <t>11,38,56</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>

--- a/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB740E99-425B-4B61-8EB8-467DE074732C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A07C176B-2884-4CD9-8D24-6A97D03D8DDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_barries_v8" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="721" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="882" uniqueCount="240">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -788,15 +788,23 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>18,78,150,210,320,440,580,740,920</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>12,30,55,80,133,155,175,205,238</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>11,38,56</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>drop_id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>掉落id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,2,3</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1133,7 +1141,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:Q164"/>
+  <dimension ref="A1:R164"/>
   <sheetFormatPr defaultColWidth="7.125" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.5" style="1" bestFit="1" customWidth="1"/>
@@ -1150,15 +1158,16 @@
     <col min="14" max="14" width="19.375" style="1" bestFit="1" customWidth="1"/>
     <col min="15" max="16" width="21.5" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="19.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="7.125" style="1"/>
+    <col min="18" max="18" width="21.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="7.125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -1210,8 +1219,11 @@
       <c r="Q2" s="1" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R2" s="1" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -1263,8 +1275,11 @@
       <c r="Q3" s="1" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R3" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -1316,8 +1331,11 @@
       <c r="Q4" s="1" t="s">
         <v>226</v>
       </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R4" s="1" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -1340,7 +1358,7 @@
         <v>43400002</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="I5" s="1">
         <v>1</v>
@@ -1369,8 +1387,11 @@
       <c r="Q5" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R5" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A6" s="1">
         <v>2</v>
       </c>
@@ -1393,7 +1414,7 @@
         <v>43400002</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="I6" s="1">
         <v>1</v>
@@ -1422,8 +1443,11 @@
       <c r="Q6" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R6" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A7" s="1">
         <v>3</v>
       </c>
@@ -1446,7 +1470,7 @@
         <v>43400002</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="I7" s="1">
         <v>1</v>
@@ -1475,8 +1499,11 @@
       <c r="Q7" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R7" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A8" s="1">
         <v>4</v>
       </c>
@@ -1499,7 +1526,7 @@
         <v>43400002</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="I8" s="1">
         <v>1</v>
@@ -1528,8 +1555,11 @@
       <c r="Q8" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R8" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A9" s="1">
         <v>5</v>
       </c>
@@ -1581,8 +1611,11 @@
       <c r="Q9" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R9" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A10" s="1">
         <v>6</v>
       </c>
@@ -1634,8 +1667,11 @@
       <c r="Q10" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R10" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A11" s="1">
         <v>7</v>
       </c>
@@ -1657,8 +1693,8 @@
       <c r="G11" s="1">
         <v>43400002</v>
       </c>
-      <c r="H11" s="1" t="s">
-        <v>235</v>
+      <c r="H11" s="1">
+        <v>0</v>
       </c>
       <c r="I11" s="1">
         <v>1</v>
@@ -1679,7 +1715,7 @@
         <v>700</v>
       </c>
       <c r="O11" s="1">
-        <v>4</v>
+        <v>99</v>
       </c>
       <c r="P11" s="1">
         <v>1003</v>
@@ -1687,8 +1723,11 @@
       <c r="Q11" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R11" s="1">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A12" s="1">
         <v>8</v>
       </c>
@@ -1740,8 +1779,11 @@
       <c r="Q12" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R12" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A13" s="1">
         <v>9</v>
       </c>
@@ -1793,8 +1835,11 @@
       <c r="Q13" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="R13" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="1">
         <v>10</v>
       </c>
@@ -1846,8 +1891,11 @@
       <c r="Q14" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R14" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A15" s="1">
         <v>11</v>
       </c>
@@ -1899,8 +1947,11 @@
       <c r="Q15" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R15" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A16" s="1">
         <v>12</v>
       </c>
@@ -1952,8 +2003,11 @@
       <c r="Q16" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R16" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A17" s="1">
         <v>13</v>
       </c>
@@ -2005,8 +2059,11 @@
       <c r="Q17" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R17" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A18" s="1">
         <v>14</v>
       </c>
@@ -2058,8 +2115,11 @@
       <c r="Q18" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R18" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A19" s="1">
         <v>15</v>
       </c>
@@ -2111,8 +2171,11 @@
       <c r="Q19" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R19" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A20" s="1">
         <v>16</v>
       </c>
@@ -2164,8 +2227,11 @@
       <c r="Q20" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R20" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A21" s="1">
         <v>17</v>
       </c>
@@ -2217,8 +2283,11 @@
       <c r="Q21" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R21" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A22" s="1">
         <v>18</v>
       </c>
@@ -2270,8 +2339,11 @@
       <c r="Q22" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R22" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A23" s="1">
         <v>19</v>
       </c>
@@ -2323,8 +2395,11 @@
       <c r="Q23" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R23" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A24" s="1">
         <v>20</v>
       </c>
@@ -2376,8 +2451,11 @@
       <c r="Q24" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R24" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A25" s="1">
         <v>21</v>
       </c>
@@ -2429,8 +2507,11 @@
       <c r="Q25" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R25" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A26" s="1">
         <v>22</v>
       </c>
@@ -2482,8 +2563,11 @@
       <c r="Q26" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R26" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A27" s="1">
         <v>23</v>
       </c>
@@ -2535,8 +2619,11 @@
       <c r="Q27" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R27" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A28" s="1">
         <v>24</v>
       </c>
@@ -2588,8 +2675,11 @@
       <c r="Q28" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R28" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A29" s="1">
         <v>25</v>
       </c>
@@ -2641,8 +2731,11 @@
       <c r="Q29" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R29" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A30" s="1">
         <v>26</v>
       </c>
@@ -2694,8 +2787,11 @@
       <c r="Q30" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R30" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A31" s="1">
         <v>27</v>
       </c>
@@ -2747,8 +2843,11 @@
       <c r="Q31" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R31" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A32" s="1">
         <v>28</v>
       </c>
@@ -2800,8 +2899,11 @@
       <c r="Q32" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R32" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A33" s="1">
         <v>29</v>
       </c>
@@ -2853,8 +2955,11 @@
       <c r="Q33" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R33" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A34" s="1">
         <v>30</v>
       </c>
@@ -2906,8 +3011,11 @@
       <c r="Q34" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R34" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A35" s="1">
         <v>31</v>
       </c>
@@ -2959,8 +3067,11 @@
       <c r="Q35" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R35" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A36" s="1">
         <v>32</v>
       </c>
@@ -3012,8 +3123,11 @@
       <c r="Q36" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R36" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A37" s="1">
         <v>33</v>
       </c>
@@ -3065,8 +3179,11 @@
       <c r="Q37" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R37" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A38" s="1">
         <v>34</v>
       </c>
@@ -3118,8 +3235,11 @@
       <c r="Q38" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R38" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A39" s="1">
         <v>35</v>
       </c>
@@ -3171,8 +3291,11 @@
       <c r="Q39" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R39" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A40" s="1">
         <v>36</v>
       </c>
@@ -3224,8 +3347,11 @@
       <c r="Q40" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R40" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A41" s="1">
         <v>37</v>
       </c>
@@ -3277,8 +3403,11 @@
       <c r="Q41" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R41" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A42" s="1">
         <v>38</v>
       </c>
@@ -3330,8 +3459,11 @@
       <c r="Q42" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R42" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A43" s="1">
         <v>39</v>
       </c>
@@ -3383,8 +3515,11 @@
       <c r="Q43" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R43" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A44" s="1">
         <v>40</v>
       </c>
@@ -3436,8 +3571,11 @@
       <c r="Q44" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R44" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A45" s="1">
         <v>41</v>
       </c>
@@ -3489,8 +3627,11 @@
       <c r="Q45" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R45" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A46" s="1">
         <v>42</v>
       </c>
@@ -3542,8 +3683,11 @@
       <c r="Q46" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R46" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A47" s="1">
         <v>43</v>
       </c>
@@ -3595,8 +3739,11 @@
       <c r="Q47" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R47" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A48" s="1">
         <v>44</v>
       </c>
@@ -3648,8 +3795,11 @@
       <c r="Q48" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R48" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A49" s="1">
         <v>45</v>
       </c>
@@ -3701,8 +3851,11 @@
       <c r="Q49" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R49" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A50" s="1">
         <v>46</v>
       </c>
@@ -3754,8 +3907,11 @@
       <c r="Q50" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R50" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A51" s="1">
         <v>47</v>
       </c>
@@ -3807,8 +3963,11 @@
       <c r="Q51" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R51" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A52" s="1">
         <v>48</v>
       </c>
@@ -3860,8 +4019,11 @@
       <c r="Q52" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R52" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A53" s="1">
         <v>49</v>
       </c>
@@ -3913,8 +4075,11 @@
       <c r="Q53" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R53" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A54" s="1">
         <v>50</v>
       </c>
@@ -3966,8 +4131,11 @@
       <c r="Q54" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R54" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A55" s="1">
         <v>51</v>
       </c>
@@ -4019,8 +4187,11 @@
       <c r="Q55" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R55" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A56" s="1">
         <v>52</v>
       </c>
@@ -4072,8 +4243,11 @@
       <c r="Q56" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R56" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="57" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A57" s="1">
         <v>53</v>
       </c>
@@ -4125,8 +4299,11 @@
       <c r="Q57" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R57" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A58" s="1">
         <v>54</v>
       </c>
@@ -4178,8 +4355,11 @@
       <c r="Q58" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R58" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="59" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A59" s="1">
         <v>55</v>
       </c>
@@ -4231,8 +4411,11 @@
       <c r="Q59" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R59" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A60" s="1">
         <v>56</v>
       </c>
@@ -4284,8 +4467,11 @@
       <c r="Q60" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R60" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A61" s="1">
         <v>57</v>
       </c>
@@ -4337,8 +4523,11 @@
       <c r="Q61" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R61" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A62" s="1">
         <v>58</v>
       </c>
@@ -4390,8 +4579,11 @@
       <c r="Q62" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R62" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A63" s="1">
         <v>59</v>
       </c>
@@ -4443,8 +4635,11 @@
       <c r="Q63" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R63" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="64" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A64" s="1">
         <v>60</v>
       </c>
@@ -4496,8 +4691,11 @@
       <c r="Q64" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R64" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="65" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A65" s="1">
         <v>61</v>
       </c>
@@ -4549,8 +4747,11 @@
       <c r="Q65" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R65" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="66" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A66" s="1">
         <v>62</v>
       </c>
@@ -4602,8 +4803,11 @@
       <c r="Q66" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R66" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="67" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A67" s="1">
         <v>63</v>
       </c>
@@ -4655,8 +4859,11 @@
       <c r="Q67" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R67" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="68" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A68" s="1">
         <v>64</v>
       </c>
@@ -4708,8 +4915,11 @@
       <c r="Q68" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R68" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="69" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A69" s="1">
         <v>65</v>
       </c>
@@ -4761,8 +4971,11 @@
       <c r="Q69" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R69" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="70" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A70" s="1">
         <v>66</v>
       </c>
@@ -4814,8 +5027,11 @@
       <c r="Q70" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R70" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="71" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A71" s="1">
         <v>67</v>
       </c>
@@ -4867,8 +5083,11 @@
       <c r="Q71" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R71" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="72" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A72" s="1">
         <v>68</v>
       </c>
@@ -4920,8 +5139,11 @@
       <c r="Q72" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R72" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="73" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A73" s="1">
         <v>69</v>
       </c>
@@ -4973,8 +5195,11 @@
       <c r="Q73" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R73" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="74" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A74" s="1">
         <v>70</v>
       </c>
@@ -5026,8 +5251,11 @@
       <c r="Q74" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R74" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="75" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A75" s="1">
         <v>71</v>
       </c>
@@ -5079,8 +5307,11 @@
       <c r="Q75" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R75" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="76" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A76" s="1">
         <v>72</v>
       </c>
@@ -5132,8 +5363,11 @@
       <c r="Q76" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R76" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="77" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A77" s="1">
         <v>73</v>
       </c>
@@ -5185,8 +5419,11 @@
       <c r="Q77" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R77" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="78" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A78" s="1">
         <v>74</v>
       </c>
@@ -5238,8 +5475,11 @@
       <c r="Q78" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R78" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="79" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A79" s="1">
         <v>75</v>
       </c>
@@ -5291,8 +5531,11 @@
       <c r="Q79" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R79" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="80" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A80" s="1">
         <v>76</v>
       </c>
@@ -5344,8 +5587,11 @@
       <c r="Q80" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R80" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="81" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A81" s="1">
         <v>77</v>
       </c>
@@ -5397,8 +5643,11 @@
       <c r="Q81" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R81" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="82" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A82" s="1">
         <v>78</v>
       </c>
@@ -5450,8 +5699,11 @@
       <c r="Q82" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R82" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="83" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A83" s="1">
         <v>79</v>
       </c>
@@ -5503,8 +5755,11 @@
       <c r="Q83" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R83" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="84" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A84" s="1">
         <v>80</v>
       </c>
@@ -5556,8 +5811,11 @@
       <c r="Q84" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R84" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="85" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A85" s="1">
         <v>81</v>
       </c>
@@ -5609,8 +5867,11 @@
       <c r="Q85" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R85" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="86" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A86" s="1">
         <v>82</v>
       </c>
@@ -5662,8 +5923,11 @@
       <c r="Q86" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R86" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="87" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A87" s="1">
         <v>83</v>
       </c>
@@ -5715,8 +5979,11 @@
       <c r="Q87" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R87" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="88" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A88" s="1">
         <v>84</v>
       </c>
@@ -5768,8 +6035,11 @@
       <c r="Q88" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R88" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="89" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A89" s="1">
         <v>85</v>
       </c>
@@ -5821,8 +6091,11 @@
       <c r="Q89" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R89" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="90" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A90" s="1">
         <v>86</v>
       </c>
@@ -5874,8 +6147,11 @@
       <c r="Q90" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R90" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="91" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A91" s="1">
         <v>87</v>
       </c>
@@ -5927,8 +6203,11 @@
       <c r="Q91" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R91" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="92" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A92" s="1">
         <v>88</v>
       </c>
@@ -5980,8 +6259,11 @@
       <c r="Q92" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R92" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="93" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A93" s="1">
         <v>89</v>
       </c>
@@ -6033,8 +6315,11 @@
       <c r="Q93" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R93" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="94" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A94" s="1">
         <v>90</v>
       </c>
@@ -6086,8 +6371,11 @@
       <c r="Q94" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R94" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="95" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A95" s="1">
         <v>91</v>
       </c>
@@ -6139,8 +6427,11 @@
       <c r="Q95" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R95" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="96" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A96" s="1">
         <v>92</v>
       </c>
@@ -6192,8 +6483,11 @@
       <c r="Q96" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R96" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="97" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A97" s="1">
         <v>93</v>
       </c>
@@ -6245,8 +6539,11 @@
       <c r="Q97" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R97" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="98" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A98" s="1">
         <v>94</v>
       </c>
@@ -6298,8 +6595,11 @@
       <c r="Q98" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R98" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="99" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A99" s="1">
         <v>95</v>
       </c>
@@ -6351,8 +6651,11 @@
       <c r="Q99" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R99" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="100" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A100" s="1">
         <v>96</v>
       </c>
@@ -6404,8 +6707,11 @@
       <c r="Q100" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R100" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="101" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A101" s="1">
         <v>97</v>
       </c>
@@ -6457,8 +6763,11 @@
       <c r="Q101" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R101" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="102" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A102" s="1">
         <v>98</v>
       </c>
@@ -6510,8 +6819,11 @@
       <c r="Q102" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R102" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="103" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A103" s="1">
         <v>99</v>
       </c>
@@ -6563,8 +6875,11 @@
       <c r="Q103" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R103" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="104" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A104" s="1">
         <v>100</v>
       </c>
@@ -6616,8 +6931,11 @@
       <c r="Q104" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R104" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="105" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A105" s="1">
         <v>101</v>
       </c>
@@ -6669,8 +6987,11 @@
       <c r="Q105" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R105" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="106" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A106" s="1">
         <v>102</v>
       </c>
@@ -6722,8 +7043,11 @@
       <c r="Q106" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R106" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="107" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A107" s="1">
         <v>103</v>
       </c>
@@ -6775,8 +7099,11 @@
       <c r="Q107" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R107" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="108" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A108" s="1">
         <v>104</v>
       </c>
@@ -6828,8 +7155,11 @@
       <c r="Q108" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R108" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="109" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A109" s="1">
         <v>105</v>
       </c>
@@ -6881,8 +7211,11 @@
       <c r="Q109" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R109" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="110" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A110" s="1">
         <v>106</v>
       </c>
@@ -6934,8 +7267,11 @@
       <c r="Q110" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R110" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="111" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A111" s="1">
         <v>107</v>
       </c>
@@ -6987,8 +7323,11 @@
       <c r="Q111" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R111" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="112" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A112" s="1">
         <v>108</v>
       </c>
@@ -7040,8 +7379,11 @@
       <c r="Q112" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R112" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="113" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A113" s="1">
         <v>109</v>
       </c>
@@ -7093,8 +7435,11 @@
       <c r="Q113" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R113" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="114" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A114" s="1">
         <v>110</v>
       </c>
@@ -7146,8 +7491,11 @@
       <c r="Q114" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R114" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="115" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A115" s="1">
         <v>111</v>
       </c>
@@ -7199,8 +7547,11 @@
       <c r="Q115" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R115" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="116" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A116" s="1">
         <v>112</v>
       </c>
@@ -7252,8 +7603,11 @@
       <c r="Q116" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R116" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="117" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A117" s="1">
         <v>113</v>
       </c>
@@ -7305,8 +7659,11 @@
       <c r="Q117" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R117" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="118" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A118" s="1">
         <v>114</v>
       </c>
@@ -7358,8 +7715,11 @@
       <c r="Q118" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R118" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="119" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A119" s="1">
         <v>115</v>
       </c>
@@ -7411,8 +7771,11 @@
       <c r="Q119" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R119" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="120" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A120" s="1">
         <v>116</v>
       </c>
@@ -7464,8 +7827,11 @@
       <c r="Q120" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R120" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="121" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A121" s="1">
         <v>117</v>
       </c>
@@ -7517,8 +7883,11 @@
       <c r="Q121" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R121" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="122" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A122" s="1">
         <v>118</v>
       </c>
@@ -7570,8 +7939,11 @@
       <c r="Q122" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R122" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="123" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A123" s="1">
         <v>119</v>
       </c>
@@ -7623,8 +7995,11 @@
       <c r="Q123" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R123" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="124" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A124" s="1">
         <v>120</v>
       </c>
@@ -7676,8 +8051,11 @@
       <c r="Q124" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R124" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="125" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A125" s="1">
         <v>121</v>
       </c>
@@ -7729,8 +8107,11 @@
       <c r="Q125" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R125" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="126" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A126" s="1">
         <v>122</v>
       </c>
@@ -7782,8 +8163,11 @@
       <c r="Q126" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R126" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="127" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A127" s="1">
         <v>123</v>
       </c>
@@ -7835,8 +8219,11 @@
       <c r="Q127" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R127" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="128" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A128" s="1">
         <v>124</v>
       </c>
@@ -7888,8 +8275,11 @@
       <c r="Q128" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R128" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="129" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A129" s="1">
         <v>125</v>
       </c>
@@ -7941,8 +8331,11 @@
       <c r="Q129" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R129" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="130" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A130" s="1">
         <v>126</v>
       </c>
@@ -7994,8 +8387,11 @@
       <c r="Q130" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R130" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="131" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A131" s="1">
         <v>127</v>
       </c>
@@ -8047,8 +8443,11 @@
       <c r="Q131" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R131" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="132" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A132" s="1">
         <v>128</v>
       </c>
@@ -8100,8 +8499,11 @@
       <c r="Q132" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R132" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="133" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A133" s="1">
         <v>129</v>
       </c>
@@ -8153,8 +8555,11 @@
       <c r="Q133" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R133" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="134" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A134" s="1">
         <v>130</v>
       </c>
@@ -8206,8 +8611,11 @@
       <c r="Q134" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R134" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="135" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A135" s="1">
         <v>131</v>
       </c>
@@ -8259,8 +8667,11 @@
       <c r="Q135" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R135" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="136" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A136" s="1">
         <v>132</v>
       </c>
@@ -8312,8 +8723,11 @@
       <c r="Q136" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R136" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="137" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A137" s="1">
         <v>133</v>
       </c>
@@ -8365,8 +8779,11 @@
       <c r="Q137" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R137" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="138" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A138" s="1">
         <v>134</v>
       </c>
@@ -8418,8 +8835,11 @@
       <c r="Q138" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R138" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="139" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A139" s="1">
         <v>135</v>
       </c>
@@ -8471,8 +8891,11 @@
       <c r="Q139" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R139" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="140" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A140" s="1">
         <v>136</v>
       </c>
@@ -8524,8 +8947,11 @@
       <c r="Q140" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R140" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="141" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A141" s="1">
         <v>137</v>
       </c>
@@ -8577,8 +9003,11 @@
       <c r="Q141" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R141" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="142" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A142" s="1">
         <v>138</v>
       </c>
@@ -8630,8 +9059,11 @@
       <c r="Q142" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R142" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="143" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A143" s="1">
         <v>139</v>
       </c>
@@ -8683,8 +9115,11 @@
       <c r="Q143" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R143" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="144" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A144" s="1">
         <v>140</v>
       </c>
@@ -8736,8 +9171,11 @@
       <c r="Q144" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="145" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R144" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="145" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A145" s="1">
         <v>141</v>
       </c>
@@ -8789,8 +9227,11 @@
       <c r="Q145" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="146" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R145" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="146" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A146" s="1">
         <v>142</v>
       </c>
@@ -8842,8 +9283,11 @@
       <c r="Q146" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="147" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R146" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="147" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A147" s="1">
         <v>143</v>
       </c>
@@ -8895,8 +9339,11 @@
       <c r="Q147" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="148" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R147" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="148" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A148" s="1">
         <v>144</v>
       </c>
@@ -8948,8 +9395,11 @@
       <c r="Q148" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="149" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R148" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="149" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A149" s="1">
         <v>145</v>
       </c>
@@ -9001,8 +9451,11 @@
       <c r="Q149" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="150" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R149" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="150" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A150" s="1">
         <v>146</v>
       </c>
@@ -9054,8 +9507,11 @@
       <c r="Q150" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="151" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R150" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="151" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A151" s="1">
         <v>147</v>
       </c>
@@ -9107,8 +9563,11 @@
       <c r="Q151" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="152" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R151" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="152" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A152" s="1">
         <v>148</v>
       </c>
@@ -9160,8 +9619,11 @@
       <c r="Q152" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="153" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R152" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="153" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A153" s="1">
         <v>149</v>
       </c>
@@ -9213,8 +9675,11 @@
       <c r="Q153" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="154" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R153" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="154" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A154" s="1">
         <v>150</v>
       </c>
@@ -9266,8 +9731,11 @@
       <c r="Q154" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="155" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R154" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="155" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A155" s="1">
         <v>151</v>
       </c>
@@ -9319,8 +9787,11 @@
       <c r="Q155" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="156" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R155" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="156" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A156" s="1">
         <v>152</v>
       </c>
@@ -9372,8 +9843,11 @@
       <c r="Q156" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="157" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R156" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="157" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A157" s="1">
         <v>153</v>
       </c>
@@ -9425,8 +9899,11 @@
       <c r="Q157" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="158" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R157" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="158" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A158" s="1">
         <v>154</v>
       </c>
@@ -9478,8 +9955,11 @@
       <c r="Q158" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="159" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R158" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="159" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A159" s="1">
         <v>155</v>
       </c>
@@ -9531,8 +10011,11 @@
       <c r="Q159" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="160" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R159" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="160" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A160" s="1">
         <v>156</v>
       </c>
@@ -9584,8 +10067,11 @@
       <c r="Q160" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="161" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R160" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="161" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A161" s="1">
         <v>157</v>
       </c>
@@ -9637,8 +10123,11 @@
       <c r="Q161" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="162" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R161" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="162" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A162" s="1">
         <v>158</v>
       </c>
@@ -9690,8 +10179,11 @@
       <c r="Q162" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="163" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R162" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="163" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A163" s="1">
         <v>159</v>
       </c>
@@ -9743,8 +10235,11 @@
       <c r="Q163" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="164" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R163" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="164" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A164" s="1">
         <v>160</v>
       </c>
@@ -9795,6 +10290,9 @@
       </c>
       <c r="Q164" s="3" t="s">
         <v>231</v>
+      </c>
+      <c r="R164" s="1" t="s">
+        <v>239</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A07C176B-2884-4CD9-8D24-6A97D03D8DDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75C60FF9-31F7-4045-9E6E-2FB504DBE2C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1712,7 +1712,7 @@
         <v>215</v>
       </c>
       <c r="N11" s="1">
-        <v>700</v>
+        <v>100</v>
       </c>
       <c r="O11" s="1">
         <v>99</v>
@@ -1768,7 +1768,7 @@
         <v>215</v>
       </c>
       <c r="N12" s="1">
-        <v>800</v>
+        <v>100</v>
       </c>
       <c r="O12" s="1">
         <v>4</v>
@@ -1824,7 +1824,7 @@
         <v>215</v>
       </c>
       <c r="N13" s="1">
-        <v>900</v>
+        <v>100</v>
       </c>
       <c r="O13" s="1">
         <v>4</v>
@@ -1880,7 +1880,7 @@
         <v>215</v>
       </c>
       <c r="N14" s="1">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="O14" s="1">
         <v>4</v>
@@ -1936,7 +1936,7 @@
         <v>215</v>
       </c>
       <c r="N15" s="1">
-        <v>1100</v>
+        <v>100</v>
       </c>
       <c r="O15" s="1">
         <v>4</v>
@@ -1992,7 +1992,7 @@
         <v>215</v>
       </c>
       <c r="N16" s="1">
-        <v>1200</v>
+        <v>100</v>
       </c>
       <c r="O16" s="1">
         <v>4</v>
@@ -2048,7 +2048,7 @@
         <v>215</v>
       </c>
       <c r="N17" s="1">
-        <v>1300</v>
+        <v>100</v>
       </c>
       <c r="O17" s="1">
         <v>4</v>
@@ -2104,7 +2104,7 @@
         <v>215</v>
       </c>
       <c r="N18" s="1">
-        <v>1400</v>
+        <v>100</v>
       </c>
       <c r="O18" s="1">
         <v>4</v>
@@ -2160,7 +2160,7 @@
         <v>215</v>
       </c>
       <c r="N19" s="1">
-        <v>1500</v>
+        <v>100</v>
       </c>
       <c r="O19" s="1">
         <v>4</v>
@@ -2216,7 +2216,7 @@
         <v>215</v>
       </c>
       <c r="N20" s="1">
-        <v>1600</v>
+        <v>100</v>
       </c>
       <c r="O20" s="1">
         <v>4</v>
@@ -2272,7 +2272,7 @@
         <v>215</v>
       </c>
       <c r="N21" s="1">
-        <v>1700</v>
+        <v>100</v>
       </c>
       <c r="O21" s="1">
         <v>4</v>
@@ -2328,7 +2328,7 @@
         <v>215</v>
       </c>
       <c r="N22" s="1">
-        <v>1800</v>
+        <v>100</v>
       </c>
       <c r="O22" s="1">
         <v>4</v>
@@ -2384,7 +2384,7 @@
         <v>215</v>
       </c>
       <c r="N23" s="1">
-        <v>1900</v>
+        <v>100</v>
       </c>
       <c r="O23" s="1">
         <v>4</v>
@@ -2440,7 +2440,7 @@
         <v>215</v>
       </c>
       <c r="N24" s="1">
-        <v>2000</v>
+        <v>100</v>
       </c>
       <c r="O24" s="1">
         <v>4</v>
@@ -2496,7 +2496,7 @@
         <v>215</v>
       </c>
       <c r="N25" s="1">
-        <v>2100</v>
+        <v>100</v>
       </c>
       <c r="O25" s="1">
         <v>4</v>
@@ -2552,7 +2552,7 @@
         <v>215</v>
       </c>
       <c r="N26" s="1">
-        <v>2200</v>
+        <v>100</v>
       </c>
       <c r="O26" s="1">
         <v>4</v>
@@ -2608,7 +2608,7 @@
         <v>215</v>
       </c>
       <c r="N27" s="1">
-        <v>2300</v>
+        <v>100</v>
       </c>
       <c r="O27" s="1">
         <v>4</v>
@@ -2664,7 +2664,7 @@
         <v>215</v>
       </c>
       <c r="N28" s="1">
-        <v>2400</v>
+        <v>100</v>
       </c>
       <c r="O28" s="1">
         <v>4</v>
@@ -2720,7 +2720,7 @@
         <v>215</v>
       </c>
       <c r="N29" s="1">
-        <v>2500</v>
+        <v>100</v>
       </c>
       <c r="O29" s="1">
         <v>4</v>
@@ -2776,7 +2776,7 @@
         <v>215</v>
       </c>
       <c r="N30" s="1">
-        <v>2600</v>
+        <v>100</v>
       </c>
       <c r="O30" s="1">
         <v>4</v>
@@ -2832,7 +2832,7 @@
         <v>215</v>
       </c>
       <c r="N31" s="1">
-        <v>2700</v>
+        <v>100</v>
       </c>
       <c r="O31" s="1">
         <v>4</v>
@@ -2888,7 +2888,7 @@
         <v>215</v>
       </c>
       <c r="N32" s="1">
-        <v>2800</v>
+        <v>100</v>
       </c>
       <c r="O32" s="1">
         <v>4</v>
@@ -2944,7 +2944,7 @@
         <v>215</v>
       </c>
       <c r="N33" s="1">
-        <v>2900</v>
+        <v>100</v>
       </c>
       <c r="O33" s="1">
         <v>4</v>
@@ -3000,7 +3000,7 @@
         <v>215</v>
       </c>
       <c r="N34" s="1">
-        <v>3000</v>
+        <v>100</v>
       </c>
       <c r="O34" s="1">
         <v>4</v>
@@ -3056,7 +3056,7 @@
         <v>215</v>
       </c>
       <c r="N35" s="1">
-        <v>3100</v>
+        <v>100</v>
       </c>
       <c r="O35" s="1">
         <v>4</v>
@@ -3112,7 +3112,7 @@
         <v>215</v>
       </c>
       <c r="N36" s="1">
-        <v>3200</v>
+        <v>100</v>
       </c>
       <c r="O36" s="1">
         <v>4</v>
@@ -3168,7 +3168,7 @@
         <v>215</v>
       </c>
       <c r="N37" s="1">
-        <v>3300</v>
+        <v>100</v>
       </c>
       <c r="O37" s="1">
         <v>4</v>
@@ -3224,7 +3224,7 @@
         <v>215</v>
       </c>
       <c r="N38" s="1">
-        <v>3400</v>
+        <v>100</v>
       </c>
       <c r="O38" s="1">
         <v>4</v>
@@ -3280,7 +3280,7 @@
         <v>215</v>
       </c>
       <c r="N39" s="1">
-        <v>3500</v>
+        <v>100</v>
       </c>
       <c r="O39" s="1">
         <v>4</v>
@@ -3336,7 +3336,7 @@
         <v>215</v>
       </c>
       <c r="N40" s="1">
-        <v>3600</v>
+        <v>100</v>
       </c>
       <c r="O40" s="1">
         <v>4</v>
@@ -3392,7 +3392,7 @@
         <v>215</v>
       </c>
       <c r="N41" s="1">
-        <v>3700</v>
+        <v>100</v>
       </c>
       <c r="O41" s="1">
         <v>4</v>
@@ -3448,7 +3448,7 @@
         <v>215</v>
       </c>
       <c r="N42" s="1">
-        <v>3800</v>
+        <v>100</v>
       </c>
       <c r="O42" s="1">
         <v>4</v>
@@ -3504,7 +3504,7 @@
         <v>215</v>
       </c>
       <c r="N43" s="1">
-        <v>3900</v>
+        <v>100</v>
       </c>
       <c r="O43" s="1">
         <v>4</v>
@@ -3560,7 +3560,7 @@
         <v>215</v>
       </c>
       <c r="N44" s="1">
-        <v>4000</v>
+        <v>100</v>
       </c>
       <c r="O44" s="1">
         <v>4</v>
@@ -3616,7 +3616,7 @@
         <v>215</v>
       </c>
       <c r="N45" s="1">
-        <v>4100</v>
+        <v>100</v>
       </c>
       <c r="O45" s="1">
         <v>4</v>
@@ -3672,7 +3672,7 @@
         <v>215</v>
       </c>
       <c r="N46" s="1">
-        <v>4200</v>
+        <v>100</v>
       </c>
       <c r="O46" s="1">
         <v>4</v>
@@ -3728,7 +3728,7 @@
         <v>215</v>
       </c>
       <c r="N47" s="1">
-        <v>4300</v>
+        <v>100</v>
       </c>
       <c r="O47" s="1">
         <v>4</v>
@@ -3784,7 +3784,7 @@
         <v>215</v>
       </c>
       <c r="N48" s="1">
-        <v>4400</v>
+        <v>100</v>
       </c>
       <c r="O48" s="1">
         <v>4</v>
@@ -3840,7 +3840,7 @@
         <v>215</v>
       </c>
       <c r="N49" s="1">
-        <v>4500</v>
+        <v>100</v>
       </c>
       <c r="O49" s="1">
         <v>4</v>
@@ -3896,7 +3896,7 @@
         <v>215</v>
       </c>
       <c r="N50" s="1">
-        <v>4600</v>
+        <v>100</v>
       </c>
       <c r="O50" s="1">
         <v>4</v>
@@ -3952,7 +3952,7 @@
         <v>215</v>
       </c>
       <c r="N51" s="1">
-        <v>4700</v>
+        <v>100</v>
       </c>
       <c r="O51" s="1">
         <v>4</v>
@@ -4008,7 +4008,7 @@
         <v>215</v>
       </c>
       <c r="N52" s="1">
-        <v>4800</v>
+        <v>100</v>
       </c>
       <c r="O52" s="1">
         <v>4</v>
@@ -4064,7 +4064,7 @@
         <v>215</v>
       </c>
       <c r="N53" s="1">
-        <v>4900</v>
+        <v>100</v>
       </c>
       <c r="O53" s="1">
         <v>4</v>
@@ -4120,7 +4120,7 @@
         <v>215</v>
       </c>
       <c r="N54" s="1">
-        <v>5000</v>
+        <v>100</v>
       </c>
       <c r="O54" s="1">
         <v>4</v>
@@ -4176,7 +4176,7 @@
         <v>215</v>
       </c>
       <c r="N55" s="1">
-        <v>5100</v>
+        <v>100</v>
       </c>
       <c r="O55" s="1">
         <v>4</v>
@@ -4232,7 +4232,7 @@
         <v>215</v>
       </c>
       <c r="N56" s="1">
-        <v>5200</v>
+        <v>100</v>
       </c>
       <c r="O56" s="1">
         <v>4</v>
@@ -4288,7 +4288,7 @@
         <v>215</v>
       </c>
       <c r="N57" s="1">
-        <v>5300</v>
+        <v>100</v>
       </c>
       <c r="O57" s="1">
         <v>4</v>
@@ -4344,7 +4344,7 @@
         <v>215</v>
       </c>
       <c r="N58" s="1">
-        <v>5400</v>
+        <v>100</v>
       </c>
       <c r="O58" s="1">
         <v>4</v>
@@ -4400,7 +4400,7 @@
         <v>215</v>
       </c>
       <c r="N59" s="1">
-        <v>5500</v>
+        <v>100</v>
       </c>
       <c r="O59" s="1">
         <v>4</v>
@@ -4456,7 +4456,7 @@
         <v>215</v>
       </c>
       <c r="N60" s="1">
-        <v>5600</v>
+        <v>100</v>
       </c>
       <c r="O60" s="1">
         <v>4</v>
@@ -4512,7 +4512,7 @@
         <v>215</v>
       </c>
       <c r="N61" s="1">
-        <v>5700</v>
+        <v>100</v>
       </c>
       <c r="O61" s="1">
         <v>4</v>
@@ -4568,7 +4568,7 @@
         <v>215</v>
       </c>
       <c r="N62" s="1">
-        <v>5800</v>
+        <v>100</v>
       </c>
       <c r="O62" s="1">
         <v>4</v>
@@ -4624,7 +4624,7 @@
         <v>215</v>
       </c>
       <c r="N63" s="1">
-        <v>5900</v>
+        <v>100</v>
       </c>
       <c r="O63" s="1">
         <v>4</v>
@@ -4680,7 +4680,7 @@
         <v>215</v>
       </c>
       <c r="N64" s="1">
-        <v>6000</v>
+        <v>100</v>
       </c>
       <c r="O64" s="1">
         <v>4</v>
@@ -4736,7 +4736,7 @@
         <v>215</v>
       </c>
       <c r="N65" s="1">
-        <v>6100</v>
+        <v>100</v>
       </c>
       <c r="O65" s="1">
         <v>4</v>
@@ -4792,7 +4792,7 @@
         <v>215</v>
       </c>
       <c r="N66" s="1">
-        <v>6200</v>
+        <v>100</v>
       </c>
       <c r="O66" s="1">
         <v>4</v>
@@ -4848,7 +4848,7 @@
         <v>215</v>
       </c>
       <c r="N67" s="1">
-        <v>6300</v>
+        <v>100</v>
       </c>
       <c r="O67" s="1">
         <v>4</v>
@@ -4904,7 +4904,7 @@
         <v>215</v>
       </c>
       <c r="N68" s="1">
-        <v>6400</v>
+        <v>100</v>
       </c>
       <c r="O68" s="1">
         <v>4</v>
@@ -4960,7 +4960,7 @@
         <v>215</v>
       </c>
       <c r="N69" s="1">
-        <v>6500</v>
+        <v>100</v>
       </c>
       <c r="O69" s="1">
         <v>4</v>
@@ -5016,7 +5016,7 @@
         <v>215</v>
       </c>
       <c r="N70" s="1">
-        <v>6600</v>
+        <v>100</v>
       </c>
       <c r="O70" s="1">
         <v>4</v>
@@ -5072,7 +5072,7 @@
         <v>215</v>
       </c>
       <c r="N71" s="1">
-        <v>6700</v>
+        <v>100</v>
       </c>
       <c r="O71" s="1">
         <v>4</v>
@@ -5128,7 +5128,7 @@
         <v>215</v>
       </c>
       <c r="N72" s="1">
-        <v>6800</v>
+        <v>100</v>
       </c>
       <c r="O72" s="1">
         <v>4</v>
@@ -5184,7 +5184,7 @@
         <v>215</v>
       </c>
       <c r="N73" s="1">
-        <v>6900</v>
+        <v>100</v>
       </c>
       <c r="O73" s="1">
         <v>4</v>
@@ -5240,7 +5240,7 @@
         <v>215</v>
       </c>
       <c r="N74" s="1">
-        <v>7000</v>
+        <v>100</v>
       </c>
       <c r="O74" s="1">
         <v>4</v>
@@ -5296,7 +5296,7 @@
         <v>215</v>
       </c>
       <c r="N75" s="1">
-        <v>7100</v>
+        <v>100</v>
       </c>
       <c r="O75" s="1">
         <v>4</v>
@@ -5352,7 +5352,7 @@
         <v>215</v>
       </c>
       <c r="N76" s="1">
-        <v>7200</v>
+        <v>100</v>
       </c>
       <c r="O76" s="1">
         <v>4</v>
@@ -5408,7 +5408,7 @@
         <v>215</v>
       </c>
       <c r="N77" s="1">
-        <v>7300</v>
+        <v>100</v>
       </c>
       <c r="O77" s="1">
         <v>4</v>
@@ -5464,7 +5464,7 @@
         <v>215</v>
       </c>
       <c r="N78" s="1">
-        <v>7400</v>
+        <v>100</v>
       </c>
       <c r="O78" s="1">
         <v>4</v>
@@ -5520,7 +5520,7 @@
         <v>215</v>
       </c>
       <c r="N79" s="1">
-        <v>7500</v>
+        <v>100</v>
       </c>
       <c r="O79" s="1">
         <v>4</v>
@@ -5576,7 +5576,7 @@
         <v>215</v>
       </c>
       <c r="N80" s="1">
-        <v>7600</v>
+        <v>100</v>
       </c>
       <c r="O80" s="1">
         <v>4</v>
@@ -5632,7 +5632,7 @@
         <v>215</v>
       </c>
       <c r="N81" s="1">
-        <v>7700</v>
+        <v>100</v>
       </c>
       <c r="O81" s="1">
         <v>4</v>
@@ -5688,7 +5688,7 @@
         <v>215</v>
       </c>
       <c r="N82" s="1">
-        <v>7800</v>
+        <v>100</v>
       </c>
       <c r="O82" s="1">
         <v>4</v>
@@ -5744,7 +5744,7 @@
         <v>215</v>
       </c>
       <c r="N83" s="1">
-        <v>7900</v>
+        <v>100</v>
       </c>
       <c r="O83" s="1">
         <v>4</v>
@@ -5800,7 +5800,7 @@
         <v>215</v>
       </c>
       <c r="N84" s="1">
-        <v>8000</v>
+        <v>100</v>
       </c>
       <c r="O84" s="1">
         <v>4</v>
@@ -5856,7 +5856,7 @@
         <v>215</v>
       </c>
       <c r="N85" s="1">
-        <v>8100</v>
+        <v>100</v>
       </c>
       <c r="O85" s="1">
         <v>4</v>
@@ -5912,7 +5912,7 @@
         <v>215</v>
       </c>
       <c r="N86" s="1">
-        <v>8200</v>
+        <v>100</v>
       </c>
       <c r="O86" s="1">
         <v>4</v>
@@ -5968,7 +5968,7 @@
         <v>215</v>
       </c>
       <c r="N87" s="1">
-        <v>8300</v>
+        <v>100</v>
       </c>
       <c r="O87" s="1">
         <v>4</v>
@@ -6024,7 +6024,7 @@
         <v>215</v>
       </c>
       <c r="N88" s="1">
-        <v>8400</v>
+        <v>100</v>
       </c>
       <c r="O88" s="1">
         <v>4</v>
@@ -6080,7 +6080,7 @@
         <v>215</v>
       </c>
       <c r="N89" s="1">
-        <v>8500</v>
+        <v>100</v>
       </c>
       <c r="O89" s="1">
         <v>4</v>
@@ -6136,7 +6136,7 @@
         <v>215</v>
       </c>
       <c r="N90" s="1">
-        <v>8600</v>
+        <v>100</v>
       </c>
       <c r="O90" s="1">
         <v>4</v>
@@ -6192,7 +6192,7 @@
         <v>215</v>
       </c>
       <c r="N91" s="1">
-        <v>8700</v>
+        <v>100</v>
       </c>
       <c r="O91" s="1">
         <v>4</v>
@@ -6248,7 +6248,7 @@
         <v>215</v>
       </c>
       <c r="N92" s="1">
-        <v>8800</v>
+        <v>100</v>
       </c>
       <c r="O92" s="1">
         <v>4</v>
@@ -6304,7 +6304,7 @@
         <v>215</v>
       </c>
       <c r="N93" s="1">
-        <v>8900</v>
+        <v>100</v>
       </c>
       <c r="O93" s="1">
         <v>4</v>
@@ -6360,7 +6360,7 @@
         <v>215</v>
       </c>
       <c r="N94" s="1">
-        <v>9000</v>
+        <v>100</v>
       </c>
       <c r="O94" s="1">
         <v>4</v>
@@ -6416,7 +6416,7 @@
         <v>215</v>
       </c>
       <c r="N95" s="1">
-        <v>9100</v>
+        <v>100</v>
       </c>
       <c r="O95" s="1">
         <v>4</v>
@@ -6472,7 +6472,7 @@
         <v>215</v>
       </c>
       <c r="N96" s="1">
-        <v>9200</v>
+        <v>100</v>
       </c>
       <c r="O96" s="1">
         <v>4</v>
@@ -6528,7 +6528,7 @@
         <v>215</v>
       </c>
       <c r="N97" s="1">
-        <v>9300</v>
+        <v>100</v>
       </c>
       <c r="O97" s="1">
         <v>4</v>
@@ -6584,7 +6584,7 @@
         <v>215</v>
       </c>
       <c r="N98" s="1">
-        <v>9400</v>
+        <v>100</v>
       </c>
       <c r="O98" s="1">
         <v>4</v>
@@ -6640,7 +6640,7 @@
         <v>215</v>
       </c>
       <c r="N99" s="1">
-        <v>9500</v>
+        <v>100</v>
       </c>
       <c r="O99" s="1">
         <v>4</v>
@@ -6696,7 +6696,7 @@
         <v>215</v>
       </c>
       <c r="N100" s="1">
-        <v>9600</v>
+        <v>100</v>
       </c>
       <c r="O100" s="1">
         <v>4</v>
@@ -6752,7 +6752,7 @@
         <v>215</v>
       </c>
       <c r="N101" s="1">
-        <v>9700</v>
+        <v>100</v>
       </c>
       <c r="O101" s="1">
         <v>4</v>
@@ -6808,7 +6808,7 @@
         <v>215</v>
       </c>
       <c r="N102" s="1">
-        <v>9800</v>
+        <v>100</v>
       </c>
       <c r="O102" s="1">
         <v>4</v>
@@ -6864,7 +6864,7 @@
         <v>215</v>
       </c>
       <c r="N103" s="1">
-        <v>9900</v>
+        <v>100</v>
       </c>
       <c r="O103" s="1">
         <v>4</v>
@@ -6920,7 +6920,7 @@
         <v>215</v>
       </c>
       <c r="N104" s="1">
-        <v>10000</v>
+        <v>100</v>
       </c>
       <c r="O104" s="1">
         <v>4</v>
@@ -6976,7 +6976,7 @@
         <v>215</v>
       </c>
       <c r="N105" s="1">
-        <v>10100</v>
+        <v>100</v>
       </c>
       <c r="O105" s="1">
         <v>4</v>
@@ -7032,7 +7032,7 @@
         <v>215</v>
       </c>
       <c r="N106" s="1">
-        <v>10200</v>
+        <v>100</v>
       </c>
       <c r="O106" s="1">
         <v>4</v>
@@ -7088,7 +7088,7 @@
         <v>215</v>
       </c>
       <c r="N107" s="1">
-        <v>10300</v>
+        <v>100</v>
       </c>
       <c r="O107" s="1">
         <v>4</v>
@@ -7144,7 +7144,7 @@
         <v>215</v>
       </c>
       <c r="N108" s="1">
-        <v>10400</v>
+        <v>100</v>
       </c>
       <c r="O108" s="1">
         <v>4</v>
@@ -7200,7 +7200,7 @@
         <v>215</v>
       </c>
       <c r="N109" s="1">
-        <v>10500</v>
+        <v>100</v>
       </c>
       <c r="O109" s="1">
         <v>4</v>
@@ -7256,7 +7256,7 @@
         <v>215</v>
       </c>
       <c r="N110" s="1">
-        <v>10600</v>
+        <v>100</v>
       </c>
       <c r="O110" s="1">
         <v>4</v>
@@ -7312,7 +7312,7 @@
         <v>215</v>
       </c>
       <c r="N111" s="1">
-        <v>10700</v>
+        <v>100</v>
       </c>
       <c r="O111" s="1">
         <v>4</v>
@@ -7368,7 +7368,7 @@
         <v>215</v>
       </c>
       <c r="N112" s="1">
-        <v>10800</v>
+        <v>100</v>
       </c>
       <c r="O112" s="1">
         <v>4</v>
@@ -7424,7 +7424,7 @@
         <v>215</v>
       </c>
       <c r="N113" s="1">
-        <v>10900</v>
+        <v>100</v>
       </c>
       <c r="O113" s="1">
         <v>4</v>
@@ -7480,7 +7480,7 @@
         <v>215</v>
       </c>
       <c r="N114" s="1">
-        <v>11000</v>
+        <v>100</v>
       </c>
       <c r="O114" s="1">
         <v>4</v>
@@ -7536,7 +7536,7 @@
         <v>215</v>
       </c>
       <c r="N115" s="1">
-        <v>11100</v>
+        <v>100</v>
       </c>
       <c r="O115" s="1">
         <v>4</v>
@@ -7592,7 +7592,7 @@
         <v>215</v>
       </c>
       <c r="N116" s="1">
-        <v>11200</v>
+        <v>100</v>
       </c>
       <c r="O116" s="1">
         <v>4</v>
@@ -7648,7 +7648,7 @@
         <v>215</v>
       </c>
       <c r="N117" s="1">
-        <v>11300</v>
+        <v>100</v>
       </c>
       <c r="O117" s="1">
         <v>4</v>
@@ -7704,7 +7704,7 @@
         <v>215</v>
       </c>
       <c r="N118" s="1">
-        <v>11400</v>
+        <v>100</v>
       </c>
       <c r="O118" s="1">
         <v>4</v>
@@ -7760,7 +7760,7 @@
         <v>215</v>
       </c>
       <c r="N119" s="1">
-        <v>11500</v>
+        <v>100</v>
       </c>
       <c r="O119" s="1">
         <v>4</v>
@@ -7816,7 +7816,7 @@
         <v>215</v>
       </c>
       <c r="N120" s="1">
-        <v>11600</v>
+        <v>100</v>
       </c>
       <c r="O120" s="1">
         <v>4</v>
@@ -7872,7 +7872,7 @@
         <v>215</v>
       </c>
       <c r="N121" s="1">
-        <v>11700</v>
+        <v>100</v>
       </c>
       <c r="O121" s="1">
         <v>4</v>
@@ -7928,7 +7928,7 @@
         <v>215</v>
       </c>
       <c r="N122" s="1">
-        <v>11800</v>
+        <v>100</v>
       </c>
       <c r="O122" s="1">
         <v>4</v>
@@ -7984,7 +7984,7 @@
         <v>215</v>
       </c>
       <c r="N123" s="1">
-        <v>11900</v>
+        <v>100</v>
       </c>
       <c r="O123" s="1">
         <v>4</v>
@@ -8040,7 +8040,7 @@
         <v>215</v>
       </c>
       <c r="N124" s="1">
-        <v>12000</v>
+        <v>100</v>
       </c>
       <c r="O124" s="1">
         <v>4</v>
@@ -8096,7 +8096,7 @@
         <v>215</v>
       </c>
       <c r="N125" s="1">
-        <v>12100</v>
+        <v>100</v>
       </c>
       <c r="O125" s="1">
         <v>4</v>
@@ -8152,7 +8152,7 @@
         <v>215</v>
       </c>
       <c r="N126" s="1">
-        <v>12200</v>
+        <v>100</v>
       </c>
       <c r="O126" s="1">
         <v>4</v>
@@ -8208,7 +8208,7 @@
         <v>215</v>
       </c>
       <c r="N127" s="1">
-        <v>12300</v>
+        <v>100</v>
       </c>
       <c r="O127" s="1">
         <v>4</v>
@@ -8264,7 +8264,7 @@
         <v>215</v>
       </c>
       <c r="N128" s="1">
-        <v>12400</v>
+        <v>100</v>
       </c>
       <c r="O128" s="1">
         <v>4</v>
@@ -8320,7 +8320,7 @@
         <v>215</v>
       </c>
       <c r="N129" s="1">
-        <v>12500</v>
+        <v>100</v>
       </c>
       <c r="O129" s="1">
         <v>4</v>
@@ -8376,7 +8376,7 @@
         <v>215</v>
       </c>
       <c r="N130" s="1">
-        <v>12600</v>
+        <v>100</v>
       </c>
       <c r="O130" s="1">
         <v>4</v>
@@ -8432,7 +8432,7 @@
         <v>215</v>
       </c>
       <c r="N131" s="1">
-        <v>12700</v>
+        <v>100</v>
       </c>
       <c r="O131" s="1">
         <v>4</v>
@@ -8488,7 +8488,7 @@
         <v>215</v>
       </c>
       <c r="N132" s="1">
-        <v>12800</v>
+        <v>100</v>
       </c>
       <c r="O132" s="1">
         <v>4</v>
@@ -8544,7 +8544,7 @@
         <v>215</v>
       </c>
       <c r="N133" s="1">
-        <v>12900</v>
+        <v>100</v>
       </c>
       <c r="O133" s="1">
         <v>4</v>
@@ -8600,7 +8600,7 @@
         <v>215</v>
       </c>
       <c r="N134" s="1">
-        <v>13000</v>
+        <v>100</v>
       </c>
       <c r="O134" s="1">
         <v>4</v>
@@ -8656,7 +8656,7 @@
         <v>215</v>
       </c>
       <c r="N135" s="1">
-        <v>13100</v>
+        <v>100</v>
       </c>
       <c r="O135" s="1">
         <v>4</v>
@@ -8712,7 +8712,7 @@
         <v>215</v>
       </c>
       <c r="N136" s="1">
-        <v>13200</v>
+        <v>100</v>
       </c>
       <c r="O136" s="1">
         <v>4</v>
@@ -8768,7 +8768,7 @@
         <v>215</v>
       </c>
       <c r="N137" s="1">
-        <v>13300</v>
+        <v>100</v>
       </c>
       <c r="O137" s="1">
         <v>4</v>
@@ -8824,7 +8824,7 @@
         <v>215</v>
       </c>
       <c r="N138" s="1">
-        <v>13400</v>
+        <v>100</v>
       </c>
       <c r="O138" s="1">
         <v>4</v>
@@ -8880,7 +8880,7 @@
         <v>215</v>
       </c>
       <c r="N139" s="1">
-        <v>13500</v>
+        <v>100</v>
       </c>
       <c r="O139" s="1">
         <v>4</v>
@@ -8936,7 +8936,7 @@
         <v>215</v>
       </c>
       <c r="N140" s="1">
-        <v>13600</v>
+        <v>100</v>
       </c>
       <c r="O140" s="1">
         <v>4</v>
@@ -8992,7 +8992,7 @@
         <v>215</v>
       </c>
       <c r="N141" s="1">
-        <v>13700</v>
+        <v>100</v>
       </c>
       <c r="O141" s="1">
         <v>4</v>
@@ -9048,7 +9048,7 @@
         <v>215</v>
       </c>
       <c r="N142" s="1">
-        <v>13800</v>
+        <v>100</v>
       </c>
       <c r="O142" s="1">
         <v>4</v>
@@ -9104,7 +9104,7 @@
         <v>215</v>
       </c>
       <c r="N143" s="1">
-        <v>13900</v>
+        <v>100</v>
       </c>
       <c r="O143" s="1">
         <v>4</v>
@@ -9160,7 +9160,7 @@
         <v>215</v>
       </c>
       <c r="N144" s="1">
-        <v>14000</v>
+        <v>100</v>
       </c>
       <c r="O144" s="1">
         <v>4</v>
@@ -9216,7 +9216,7 @@
         <v>215</v>
       </c>
       <c r="N145" s="1">
-        <v>14100</v>
+        <v>100</v>
       </c>
       <c r="O145" s="1">
         <v>4</v>
@@ -9272,7 +9272,7 @@
         <v>215</v>
       </c>
       <c r="N146" s="1">
-        <v>14200</v>
+        <v>100</v>
       </c>
       <c r="O146" s="1">
         <v>4</v>
@@ -9328,7 +9328,7 @@
         <v>215</v>
       </c>
       <c r="N147" s="1">
-        <v>14300</v>
+        <v>100</v>
       </c>
       <c r="O147" s="1">
         <v>4</v>
@@ -9384,7 +9384,7 @@
         <v>215</v>
       </c>
       <c r="N148" s="1">
-        <v>14400</v>
+        <v>100</v>
       </c>
       <c r="O148" s="1">
         <v>4</v>
@@ -9440,7 +9440,7 @@
         <v>215</v>
       </c>
       <c r="N149" s="1">
-        <v>14500</v>
+        <v>100</v>
       </c>
       <c r="O149" s="1">
         <v>4</v>
@@ -9496,7 +9496,7 @@
         <v>215</v>
       </c>
       <c r="N150" s="1">
-        <v>14600</v>
+        <v>100</v>
       </c>
       <c r="O150" s="1">
         <v>4</v>
@@ -9552,7 +9552,7 @@
         <v>215</v>
       </c>
       <c r="N151" s="1">
-        <v>14700</v>
+        <v>100</v>
       </c>
       <c r="O151" s="1">
         <v>4</v>
@@ -9608,7 +9608,7 @@
         <v>215</v>
       </c>
       <c r="N152" s="1">
-        <v>14800</v>
+        <v>100</v>
       </c>
       <c r="O152" s="1">
         <v>4</v>
@@ -9664,7 +9664,7 @@
         <v>215</v>
       </c>
       <c r="N153" s="1">
-        <v>14900</v>
+        <v>100</v>
       </c>
       <c r="O153" s="1">
         <v>4</v>
@@ -9720,7 +9720,7 @@
         <v>215</v>
       </c>
       <c r="N154" s="1">
-        <v>15000</v>
+        <v>100</v>
       </c>
       <c r="O154" s="1">
         <v>4</v>
@@ -9776,7 +9776,7 @@
         <v>215</v>
       </c>
       <c r="N155" s="1">
-        <v>15100</v>
+        <v>100</v>
       </c>
       <c r="O155" s="1">
         <v>4</v>
@@ -9832,7 +9832,7 @@
         <v>215</v>
       </c>
       <c r="N156" s="1">
-        <v>15200</v>
+        <v>100</v>
       </c>
       <c r="O156" s="1">
         <v>4</v>
@@ -9888,7 +9888,7 @@
         <v>215</v>
       </c>
       <c r="N157" s="1">
-        <v>15300</v>
+        <v>100</v>
       </c>
       <c r="O157" s="1">
         <v>4</v>
@@ -9944,7 +9944,7 @@
         <v>215</v>
       </c>
       <c r="N158" s="1">
-        <v>15400</v>
+        <v>100</v>
       </c>
       <c r="O158" s="1">
         <v>4</v>
@@ -10000,7 +10000,7 @@
         <v>215</v>
       </c>
       <c r="N159" s="1">
-        <v>15500</v>
+        <v>100</v>
       </c>
       <c r="O159" s="1">
         <v>4</v>
@@ -10056,7 +10056,7 @@
         <v>215</v>
       </c>
       <c r="N160" s="1">
-        <v>15600</v>
+        <v>100</v>
       </c>
       <c r="O160" s="1">
         <v>4</v>
@@ -10112,7 +10112,7 @@
         <v>215</v>
       </c>
       <c r="N161" s="1">
-        <v>15700</v>
+        <v>100</v>
       </c>
       <c r="O161" s="1">
         <v>4</v>
@@ -10168,7 +10168,7 @@
         <v>215</v>
       </c>
       <c r="N162" s="1">
-        <v>15800</v>
+        <v>100</v>
       </c>
       <c r="O162" s="1">
         <v>4</v>
@@ -10224,7 +10224,7 @@
         <v>215</v>
       </c>
       <c r="N163" s="1">
-        <v>15900</v>
+        <v>100</v>
       </c>
       <c r="O163" s="1">
         <v>4</v>
@@ -10280,7 +10280,7 @@
         <v>215</v>
       </c>
       <c r="N164" s="1">
-        <v>16000</v>
+        <v>100</v>
       </c>
       <c r="O164" s="1">
         <v>4</v>

--- a/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75C60FF9-31F7-4045-9E6E-2FB504DBE2C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowHeight="15580"/>
   </bookViews>
   <sheets>
     <sheet name="maze_barries_v8" sheetId="1" r:id="rId1"/>
@@ -18,9 +12,6 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -28,6 +19,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -35,47 +28,155 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="882" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="880" uniqueCount="238">
   <si>
     <t>paipaiworld_config</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>INT_K</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>INT_S</t>
+  </si>
+  <si>
+    <t>STRING_S</t>
+  </si>
+  <si>
+    <t>INT_S_C</t>
+  </si>
+  <si>
+    <t>LIST&lt;INT&gt;_S_C</t>
+  </si>
+  <si>
+    <t>LIST&lt;INT&gt;_S</t>
   </si>
   <si>
     <t>order</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>last_id</t>
+  </si>
+  <si>
+    <t>next_id</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>box_id</t>
+  </si>
+  <si>
+    <t>box_id_first</t>
+  </si>
+  <si>
+    <t>hp_vial</t>
+  </si>
+  <si>
+    <t>drop_vial_foe</t>
+  </si>
+  <si>
+    <t>challenge_cost</t>
+  </si>
+  <si>
+    <t>mop_cost</t>
+  </si>
+  <si>
+    <t>drop_equip_lv_min</t>
+  </si>
+  <si>
+    <t>drop_equip_lv_max</t>
+  </si>
+  <si>
+    <t>energy_list</t>
+  </si>
+  <si>
+    <t>initial_kongfu</t>
+  </si>
+  <si>
+    <t>energy_id</t>
+  </si>
+  <si>
+    <t>energy_affix_rand_rule</t>
+  </si>
+  <si>
+    <t>rare_items_show</t>
+  </si>
+  <si>
+    <t>drop_id</t>
   </si>
   <si>
     <t>关卡id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>next_id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>上一关id</t>
   </si>
   <si>
     <t>下一关id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>name</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>名称</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>通关奖励（每次通关都有）</t>
+  </si>
+  <si>
+    <t>首次通关奖励</t>
+  </si>
+  <si>
+    <t>血瓶id</t>
+  </si>
+  <si>
+    <t>掉落血瓶的怪物数</t>
+  </si>
+  <si>
+    <t>挑战消耗次数</t>
+  </si>
+  <si>
+    <t>扫荡消耗体力</t>
+  </si>
+  <si>
+    <t>掉落装备等级，小</t>
+  </si>
+  <si>
+    <t>掉落装备等级,大</t>
+  </si>
+  <si>
+    <t>能力等级队列（随机）</t>
+  </si>
+  <si>
+    <t>玩家初始武力值</t>
+  </si>
+  <si>
+    <t>当前关卡使用的能力id</t>
+  </si>
+  <si>
+    <t>能力词条随机规则</t>
+  </si>
+  <si>
+    <t>展示为稀有的物品id</t>
+  </si>
+  <si>
+    <t>掉落id</t>
   </si>
   <si>
     <t>第1关</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>101,102,103,104</t>
+  </si>
+  <si>
+    <t>46200001,46800001,46900001,42761001,42761002,42761003,42761004,42761005,42761006,42761007,42761008,42761009,42761010,42761011,42761012,42761013,42761014,42761015,42761016,42761017,42761018,42761019,42761020,42761021,42761022,42761023,42761024,42761025,42761026,42761027,42761028,42761029,42761030,42761031,42761032,42761033,42761034,42761035,42761036,42761037,42761038,42761039,42761040,42761041,42761042,42761043,42761044,42761045,42761046,42761047,42761048,42761049,42761050,42761051,42761052,42761053,42761054,42761055,42761056,42761057,42761058,42761059,42761060,42761061,42761062,42761063,42761064,42761065,42761066,42761067,42761068,42761069,42761070,42761071,42761072,42761073,42761074,42761075,42761076,42761077,42761078,42761079,42761080,42761081,42761082,42761083,42761084,42761085,42761086,42761087,42761088,42761089,42761090,42761091,42761092,42761093,42761094,42761095,42761096,42761097,42761098,42761099,42761100,42761101,42761102,42761103,42761104,42761105,42761106,42761107,42761108,42761109,42761110,42761111,42761112,42761113,42761114,42761115,42761116,42761117,42761118,42761119,42761120,42761121,42761122,42761123,42761124,42761125,42761126,42761127,42761128,42761129,42761130,42761131,42761132,42761133,42761134,42761135,42761136,42761137,42761138,42761139,42761140,42761141,42761142,42761143,42761144,42761145,42761146,42761147,42761148,42761149,42761150,42761151,42761152,42761153,42761154,42761155,42761156,42761157,42761158,42761159,42761160,42662001,42662002,42662003,42662004,42662005,42662006,42662007,42662008,42662009,42662010,42662011,42662012,42662013,42662014,42662015,42662016,42662017,42662018,42662019,42662020,42662021,42662022,42662023,42662024,42662025,42662026,42662027,42662028,42662029,42662030,42662031,42662032,42662033,42662034,42662035,42662036,42662037,42662038,42662039,42662040,42662041,42662042,42662043,42662044,42662045,42662046,42662047,42662048,42662049,42662050,42662051,42662052,42662053,42662054,42662055,42662056,42662057,42662058,42662059,42662060,42662061,42662062,42662063,42662064,42662065,42662066,42662067,42662068,42662069,42662070,42662071,42662072,42662073,42662074,42662075,42662076,42662077,42662078,42662079,42662080,42662081,42662082,42662083,42662084,42662085,42662086,42662087,42662088,42662089,42662090,42662091,42662092,42662093,42662094,42662095,42662096,42662097,42662098,42662099,42662100,42662101,42662102,42662103,42662104,42662105,42662106,42662107,42662108,42662109,42662110,42662111,42662112,42662113,42662114,42662115,42662116,42662117,42662118,42662119,42662120,42662121,42662122,42662123,42662124,42662125,42662126,42662127,42662128,42662129,42662130,42662131,42662132,42662133,42662134,42662135,42662136,42662137,42662138,42662139,42662140,42662141,42662142,42662143,42662144,42662145,42662146,42662147,42662148,42662149,42662150,42662151,42662152,42662153,42662154,42662155,42662156,42662157,42662158,42662159,42662160,42663001,42663002,42663003,42663004,42663005,42663006,42663007,42663008,42663009,42663010,42663011,42663012,42663013,42663014,42663015,42663016,42663017,42663018,42663019,42663020,42663021,42663022,42663023,42663024,42663025,42663026,42663027,42663028,42663029,42663030,42663031,42663032,42663033,42663034,42663035,42663036,42663037,42663038,42663039,42663040,42663041,42663042,42663043,42663044,42663045,42663046,42663047,42663048,42663049,42663050,42663051,42663052,42663053,42663054,42663055,42663056,42663057,42663058,42663059,42663060,42663061,42663062,42663063,42663064,42663065,42663066,42663067,42663068,42663069,42663070,42663071,42663072,42663073,42663074,42663075,42663076,42663077,42663078,42663079,42663080,42663081,42663082,42663083,42663084,42663085,42663086,42663087,42663088,42663089,42663090,42663091,42663092,42663093,42663094,42663095,42663096,42663097,42663098,42663099,42663100,42663101,42663102,42663103,42663104,42663105,42663106,42663107,42663108,42663109,42663110,42663111,42663112,42663113,42663114,42663115,42663116,42663117,42663118,42663119,42663120,42663121,42663122,42663123,42663124,42663125,42663126,42663127,42663128,42663129,42663130,42663131,42663132,42663133,42663134,42663135,42663136,42663137,42663138,42663139,42663140,42663141,42663142,42663143,42663144,42663145,42663146,42663147,42663148,42663149,42663150,42663151,42663152,42663153,42663154,42663155,42663156,42663157,42663158,42663159,42663160,42666001,42666002,42666003,42666004,42666005,42666006,42666007,42666008,42666009,42666010,42666011,42666012,42666013,42666014,42666015,42666016,42666017,42666018,42666019,42666020,42666021,42666022,42666023,42666024,42666025,42666026,42666027,42666028,42666029,42666030,42666031,42666032,42666033,42666034,42666035,42666036,42666037,42666038,42666039,42666040,42666041,42666042,42666043,42666044,42666045,42666046,42666047,42666048,42666049,42666050,42666051,42666052,42666053,42666054,42666055,42666056,42666057,42666058,42666059,42666060,42666061,42666062,42666063,42666064,42666065,42666066,42666067,42666068,42666069,42666070,42666071,42666072,42666073,42666074,42666075,42666076,42666077,42666078,42666079,42666080,42666081,42666082,42666083,42666084,42666085,42666086,42666087,42666088,42666089,42666090,42666091,42666092,42666093,42666094,42666095,42666096,42666097,42666098,42666099,42666100,42666101,42666102,42666103,42666104,42666105,42666106,42666107,42666108,42666109,42666110,42666111,42666112,42666113,42666114,42666115,42666116,42666117,42666118,42666119,42666120,42666121,42666122,42666123,42666124,42666125,42666126,42666127,42666128,42666129,42666130,42666131,42666132,42666133,42666134,42666135,42666136,42666137,42666138,42666139,42666140,42666141,42666142,42666143,42666144,42666145,42666146,42666147,42666148,42666149,42666150,42666151,42666152,42666153,42666154,42666155,42666156,42666157,42666158,42666159,42666160,42664001,42664002,42664003,42664004,42664005,42664006,42664007,42664008,42664009,42664010,42664011,42664012,42664013,42664014,42664015,42664016,42664017,42664018,42664019,42664020,42664021,42664022,42664023,42664024,42664025,42664026,42664027,42664028,42664029,42664030,42664031,42664032,42664033,42664034,42664035,42664036,42664037,42664038,42664039,42664040,42664041,42664042,42664043,42664044,42664045,42664046,42664047,42664048,42664049,42664050,42664051,42664052,42664053,42664054,42664055,42664056,42664057,42664058,42664059,42664060,42664061,42664062,42664063,42664064,42664065,42664066,42664067,42664068,42664069,42664070,42664071,42664072,42664073,42664074,42664075,42664076,42664077,42664078,42664079,42664080,42664081,42664082,42664083,42664084,42664085,42664086,42664087,42664088,42664089,42664090,42664091,42664092,42664093,42664094,42664095,42664096,42664097,42664098,42664099,42664100,42664101,42664102,42664103,42664104,42664105,42664106,42664107,42664108,42664109,42664110,42664111,42664112,42664113,42664114,42664115,42664116,42664117,42664118,42664119,42664120,42664121,42664122,42664123,42664124,42664125,42664126,42664127,42664128,42664129,42664130,42664131,42664132,42664133,42664134,42664135,42664136,42664137,42664138,42664139,42664140,42664141,42664142,42664143,42664144,42664145,42664146,42664147,42664148,42664149,42664150,42664151,42664152,42664153,42664154,42664155,42664156,42664157,42664158,42664159,42664160,42665001,42665002,42665003,42665004,42665005,42665006,42665007,42665008,42665009,42665010,42665011,42665012,42665013,42665014,42665015,42665016,42665017,42665018,42665019,42665020,42665021,42665022,42665023,42665024,42665025,42665026,42665027,42665028,42665029,42665030,42665031,42665032,42665033,42665034,42665035,42665036,42665037,42665038,42665039,42665040,42665041,42665042,42665043,42665044,42665045,42665046,42665047,42665048,42665049,42665050,42665051,42665052,42665053,42665054,42665055,42665056,42665057,42665058,42665059,42665060,42665061,42665062,42665063,42665064,42665065,42665066,42665067,42665068,42665069,42665070,42665071,42665072,42665073,42665074,42665075,42665076,42665077,42665078,42665079,42665080,42665081,42665082,42665083,42665084,42665085,42665086,42665087,42665088,42665089,42665090,42665091,42665092,42665093,42665094,42665095,42665096,42665097,42665098,42665099,42665100,42665101,42665102,42665103,42665104,42665105,42665106,42665107,42665108,42665109,42665110,42665111,42665112,42665113,42665114,42665115,42665116,42665117,42665118,42665119,42665120,42665121,42665122,42665123,42665124,42665125,42665126,42665127,42665128,42665129,42665130,42665131,42665132,42665133,42665134,42665135,42665136,42665137,42665138,42665139,42665140,42665141,42665142,42665143,42665144,42665145,42665146,42665147,42665148,42665149,42665150,42665151,42665152,42665153,42665154,42665155,42665156,42665157,42665158,42665159,42665160,42667001,42667002,42667003,42667004,42667005,42667006,42667007,42667008,42667009,42667010,42667011,42667012,42667013,42667014,42667015,42667016,42667017,42667018,42667019,42667020,42667021,42667022,42667023,42667024,42667025,42667026,42667027,42667028,42667029,42667030,42667031,42667032,42667033,42667034,42667035,42667036,42667037,42667038,42667039,42667040,42667041,42667042,42667043,42667044,42667045,42667046,42667047,42667048,42667049,42667050,42667051,42667052,42667053,42667054,42667055,42667056,42667057,42667058,42667059,42667060,42667061,42667062,42667063,42667064,42667065,42667066,42667067,42667068,42667069,42667070,42667071,42667072,42667073,42667074,42667075,42667076,42667077,42667078,42667079,42667080,42667081,42667082,42667083,42667084,42667085,42667086,42667087,42667088,42667089,42667090,42667091,42667092,42667093,42667094,42667095,42667096,42667097,42667098,42667099,42667100,42667101,42667102,42667103,42667104,42667105,42667106,42667107,42667108,42667109,42667110,42667111,42667112,42667113,42667114,42667115,42667116,42667117,42667118,42667119,42667120,42667121,42667122,42667123,42667124,42667125,42667126,42667127,42667128,42667129,42667130,42667131,42667132,42667133,42667134,42667135,42667136,42667137,42667138,42667139,42667140,42667141,42667142,42667143,42667144,42667145,42667146,42667147,42667148,42667149,42667150,42667151,42667152,42667153,42667154,42667155,42667156,42667157,42667158,42667159,42667160,42668001,42668002,42668003,42668004,42668005,42668006,42668007,42668008,42668009,42668010,42668011,42668012,42668013,42668014,42668015,42668016,42668017,42668018,42668019,42668020,42668021,42668022,42668023,42668024,42668025,42668026,42668027,42668028,42668029,42668030,42668031,42668032,42668033,42668034,42668035,42668036,42668037,42668038,42668039,42668040,42668041,42668042,42668043,42668044,42668045,42668046,42668047,42668048,42668049,42668050,42668051,42668052,42668053,42668054,42668055,42668056,42668057,42668058,42668059,42668060,42668061,42668062,42668063,42668064,42668065,42668066,42668067,42668068,42668069,42668070,42668071,42668072,42668073,42668074,42668075,42668076,42668077,42668078,42668079,42668080,42668081,42668082,42668083,42668084,42668085,42668086,42668087,42668088,42668089,42668090,42668091,42668092,42668093,42668094,42668095,42668096,42668097,42668098,42668099,42668100,42668101,42668102,42668103,42668104,42668105,42668106,42668107,42668108,42668109,42668110,42668111,42668112,42668113,42668114,42668115,42668116,42668117,42668118,42668119,42668120,42668121,42668122,42668123,42668124,42668125,42668126,42668127,42668128,42668129,42668130,42668131,42668132,42668133,42668134,42668135,42668136,42668137,42668138,42668139,42668140,42668141,42668142,42668143,42668144,42668145,42668146,42668147,42668148,42668149,42668150,42668151,42668152,42668153,42668154,42668155,42668156,42668157,42668158,42668159,42668160,42781001,42781002,42781003,42781004,42781005,42781006,42781007,42781008,42781009,42781010,42781011,42781012,42781013,42781014,42781015,42781016,42781017,42781018,42781019,42781020,42781021,42781022,42781023,42781024,42781025,42781026,42781027,42781028,42781029,42781030,42781031,42781032,42781033,42781034,42781035,42781036,42781037,42781038,42781039,42781040,42781041,42781042,42781043,42781044,42781045,42781046,42781047,42781048,42781049,42781050,42781051,42781052,42781053,42781054,42781055,42781056,42781057,42781058,42781059,42781060,42781061,42781062,42781063,42781064,42781065,42781066,42781067,42781068,42781069,42781070,42781071,42781072,42781073,42781074,42781075,42781076,42781077,42781078,42781079,42781080,42781081,42781082,42781083,42781084,42781085,42781086,42781087,42781088,42781089,42781090,42781091,42781092,42781093,42781094,42781095,42781096,42781097,42781098,42781099,42781100,42781101,42781102,42781103,42781104,42781105,42781106,42781107,42781108,42781109,42781110,42781111,42781112,42781113,42781114,42781115,42781116,42781117,42781118,42781119,42781120,42781121,42781122,42781123,42781124,42781125,42781126,42781127,42781128,42781129,42781130,42781131,42781132,42781133,42781134,42781135,42781136,42781137,42781138,42781139,42781140,42781141,42781142,42781143,42781144,42781145,42781146,42781147,42781148,42781149,42781150,42781151,42781152,42781153,42781154,42781155,42781156,42781157,42781158,42781159,42781160,42682001,42682002,42682003,42682004,42682005,42682006,42682007,42682008,42682009,42682010,42682011,42682012,42682013,42682014,42682015,42682016,42682017,42682018,42682019,42682020,42682021,42682022,42682023,42682024,42682025,42682026,42682027,42682028,42682029,42682030,42682031,42682032,42682033,42682034,42682035,42682036,42682037,42682038,42682039,42682040,42682041,42682042,42682043,42682044,42682045,42682046,42682047,42682048,42682049,42682050,42682051,42682052,42682053,42682054,42682055,42682056,42682057,42682058,42682059,42682060,42682061,42682062,42682063,42682064,42682065,42682066,42682067,42682068,42682069,42682070,42682071,42682072,42682073,42682074,42682075,42682076,42682077,42682078,42682079,42682080,42682081,42682082,42682083,42682084,42682085,42682086,42682087,42682088,42682089,42682090,42682091,42682092,42682093,42682094,42682095,42682096,42682097,42682098,42682099,42682100,42682101,42682102,42682103,42682104,42682105,42682106,42682107,42682108,42682109,42682110,42682111,42682112,42682113,42682114,42682115,42682116,42682117,42682118,42682119,42682120,42682121,42682122,42682123,42682124,42682125,42682126,42682127,42682128,42682129,42682130,42682131,42682132,42682133,42682134,42682135,42682136,42682137,42682138,42682139,42682140,42682141,42682142,42682143,42682144,42682145,42682146,42682147,42682148,42682149,42682150,42682151,42682152,42682153,42682154,42682155,42682156,42682157,42682158,42682159,42682160,42683001,42683002,42683003,42683004,42683005,42683006,42683007,42683008,42683009,42683010,42683011,42683012,42683013,42683014,42683015,42683016,42683017,42683018,42683019,42683020,42683021,42683022,42683023,42683024,42683025,42683026,42683027,42683028,42683029,42683030,42683031,42683032,42683033,42683034,42683035,42683036,42683037,42683038,42683039,42683040,42683041,42683042,42683043,42683044,42683045,42683046,42683047,42683048,42683049,42683050,42683051,42683052,42683053,42683054,42683055,42683056,42683057,42683058,42683059,42683060,42683061,42683062,42683063,42683064,42683065,42683066,42683067,42683068,42683069,42683070,42683071,42683072,42683073,42683074,42683075,42683076,42683077,42683078,42683079,42683080,42683081,42683082,42683083,42683084,42683085,42683086,42683087,42683088,42683089,42683090,42683091,42683092,42683093,42683094,42683095,42683096,42683097,42683098,42683099,42683100,42683101,42683102,42683103,42683104,42683105,42683106,42683107,42683108,42683109,42683110,42683111,42683112,42683113,42683114,42683115,42683116,42683117,42683118,42683119,42683120,42683121,42683122,42683123,42683124,42683125,42683126,42683127,42683128,42683129,42683130,42683131,42683132,42683133,42683134,42683135,42683136,42683137,42683138,42683139,42683140,42683141,42683142,42683143,42683144,42683145,42683146,42683147,42683148,42683149,42683150,42683151,42683152,42683153,42683154,42683155,42683156,42683157,42683158,42683159,42683160,42686001,42686002,42686003,42686004,42686005,42686006,42686007,42686008,42686009,42686010,42686011,42686012,42686013,42686014,42686015,42686016,42686017,42686018,42686019,42686020,42686021,42686022,42686023,42686024,42686025,42686026,42686027,42686028,42686029,42686030,42686031,42686032,42686033,42686034,42686035,42686036,42686037,42686038,42686039,42686040,42686041,42686042,42686043,42686044,42686045,42686046,42686047,42686048,42686049,42686050,42686051,42686052,42686053,42686054,42686055,42686056,42686057,42686058,42686059,42686060,42686061,42686062,42686063,42686064,42686065,42686066,42686067,42686068,42686069,42686070,42686071,42686072,42686073,42686074,42686075,42686076,42686077,42686078,42686079,42686080,42686081,42686082,42686083,42686084,42686085,42686086,42686087,42686088,42686089,42686090,42686091,42686092,42686093,42686094,42686095,42686096,42686097,42686098,42686099,42686100,42686101,42686102,42686103,42686104,42686105,42686106,42686107,42686108,42686109,42686110,42686111,42686112,42686113,42686114,42686115,42686116,42686117,42686118,42686119,42686120,42686121,42686122,42686123,42686124,42686125,42686126,42686127,42686128,42686129,42686130,42686131,42686132,42686133,42686134,42686135,42686136,42686137,42686138,42686139,42686140,42686141,42686142,42686143,42686144,42686145,42686146,42686147,42686148,42686149,42686150,42686151,42686152,42686153,42686154,42686155,42686156,42686157,42686158,42686159,42686160,42684001,42684002,42684003,42684004,42684005,42684006,42684007,42684008,42684009,42684010,42684011,42684012,42684013,42684014,42684015,42684016,42684017,42684018,42684019,42684020,42684021,42684022,42684023,42684024,42684025,42684026,42684027,42684028,42684029,42684030,42684031,42684032,42684033,42684034,42684035,42684036,42684037,42684038,42684039,42684040,42684041,42684042,42684043,42684044,42684045,42684046,42684047,42684048,42684049,42684050,42684051,42684052,42684053,42684054,42684055,42684056,42684057,42684058,42684059,42684060,42684061,42684062,42684063,42684064,42684065,42684066,42684067,42684068,42684069,42684070,42684071,42684072,42684073,42684074,42684075,42684076,42684077,42684078,42684079,42684080,42684081,42684082,42684083,42684084,42684085,42684086,42684087,42684088,42684089,42684090,42684091,42684092,42684093,42684094,42684095,42684096,42684097,42684098,42684099,42684100,42684101,42684102,42684103,42684104,42684105,42684106,42684107,42684108,42684109,42684110,42684111,42684112,42684113,42684114,42684115,42684116,42684117,42684118,42684119,42684120,42684121,42684122,42684123,42684124,42684125,42684126,42684127,42684128,42684129,42684130,42684131,42684132,42684133,42684134,42684135,42684136,42684137,42684138,42684139,42684140,42684141,42684142,42684143,42684144,42684145,42684146,42684147,42684148,42684149,42684150,42684151,42684152,42684153,42684154,42684155,42684156,42684157,42684158,42684159,42684160,42685001,42685002,42685003,42685004,42685005,42685006,42685007,42685008,42685009,42685010,42685011,42685012,42685013,42685014,42685015,42685016,42685017,42685018,42685019,42685020,42685021,42685022,42685023,42685024,42685025,42685026,42685027,42685028,42685029,42685030,42685031,42685032,42685033,42685034,42685035,42685036,42685037,42685038,42685039,42685040,42685041,42685042,42685043,42685044,42685045,42685046,42685047,42685048,42685049,42685050,42685051,42685052,42685053,42685054,42685055,42685056,42685057,42685058,42685059,42685060,42685061,42685062,42685063,42685064,42685065,42685066,42685067,42685068,42685069,42685070,42685071,42685072,42685073,42685074,42685075,42685076,42685077,42685078,42685079,42685080,42685081,42685082,42685083,42685084,42685085,42685086,42685087,42685088,42685089,42685090,42685091,42685092,42685093,42685094,42685095,42685096,42685097,42685098,42685099,42685100,42685101,42685102,42685103,42685104,42685105,42685106,42685107,42685108,42685109,42685110,42685111,42685112,42685113,42685114,42685115,42685116,42685117,42685118,42685119,42685120,42685121,42685122,42685123,42685124,42685125,42685126,42685127,42685128,42685129,42685130,42685131,42685132,42685133,42685134,42685135,42685136,42685137,42685138,42685139,42685140,42685141,42685142,42685143,42685144,42685145,42685146,42685147,42685148,42685149,42685150,42685151,42685152,42685153,42685154,42685155,42685156,42685157,42685158,42685159,42685160,42687001,42687002,42687003,42687004,42687005,42687006,42687007,42687008,42687009,42687010,42687011,42687012,42687013,42687014,42687015,42687016,42687017,42687018,42687019,42687020,42687021,42687022,42687023,42687024,42687025,42687026,42687027,42687028,42687029,42687030,42687031,42687032,42687033,42687034,42687035,42687036,42687037,42687038,42687039,42687040,42687041,42687042,42687043,42687044,42687045,42687046,42687047,42687048,42687049,42687050,42687051,42687052,42687053,42687054,42687055,42687056,42687057,42687058,42687059,42687060,42687061,42687062,42687063,42687064,42687065,42687066,42687067,42687068,42687069,42687070,42687071,42687072,42687073,42687074,42687075,42687076,42687077,42687078,42687079,42687080,42687081,42687082,42687083,42687084,42687085,42687086,42687087,42687088,42687089,42687090,42687091,42687092,42687093,42687094,42687095,42687096,42687097,42687098,42687099,42687100,42687101,42687102,42687103,42687104,42687105,42687106,42687107,42687108,42687109,42687110,42687111,42687112,42687113,42687114,42687115,42687116,42687117,42687118,42687119,42687120,42687121,42687122,42687123,42687124,42687125,42687126,42687127,42687128,42687129,42687130,42687131,42687132,42687133,42687134,42687135,42687136,42687137,42687138,42687139,42687140,42687141,42687142,42687143,42687144,42687145,42687146,42687147,42687148,42687149,42687150,42687151,42687152,42687153,42687154,42687155,42687156,42687157,42687158,42687159,42687160,42688001,42688002,42688003,42688004,42688005,42688006,42688007,42688008,42688009,42688010,42688011,42688012,42688013,42688014,42688015,42688016,42688017,42688018,42688019,42688020,42688021,42688022,42688023,42688024,42688025,42688026,42688027,42688028,42688029,42688030,42688031,42688032,42688033,42688034,42688035,42688036,42688037,42688038,42688039,42688040,42688041,42688042,42688043,42688044,42688045,42688046,42688047,42688048,42688049,42688050,42688051,42688052,42688053,42688054,42688055,42688056,42688057,42688058,42688059,42688060,42688061,42688062,42688063,42688064,42688065,42688066,42688067,42688068,42688069,42688070,42688071,42688072,42688073,42688074,42688075,42688076,42688077,42688078,42688079,42688080,42688081,42688082,42688083,42688084,42688085,42688086,42688087,42688088,42688089,42688090,42688091,42688092,42688093,42688094,42688095,42688096,42688097,42688098,42688099,42688100,42688101,42688102,42688103,42688104,42688105,42688106,42688107,42688108,42688109,42688110,42688111,42688112,42688113,42688114,42688115,42688116,42688117,42688118,42688119,42688120,42688121,42688122,42688123,42688124,42688125,42688126,42688127,42688128,42688129,42688130,42688131,42688132,42688133,42688134,42688135,42688136,42688137,42688138,42688139,42688140,42688141,42688142,42688143,42688144,42688145,42688146,42688147,42688148,42688149,42688150,42688151,42688152,42688153,42688154,42688155,42688156,42688157,42688158,42688159,42688160</t>
   </si>
   <si>
     <t>第2关</t>
   </si>
   <si>
+    <t>12,30,55,80,133,155,175,205,238</t>
+  </si>
+  <si>
+    <t>1,2,3</t>
+  </si>
+  <si>
     <t>第3关</t>
   </si>
   <si>
@@ -85,6 +186,9 @@
     <t>第5关</t>
   </si>
   <si>
+    <t>18,78,150,210,320,440,580</t>
+  </si>
+  <si>
     <t>第6关</t>
   </si>
   <si>
@@ -94,6 +198,9 @@
     <t>第8关</t>
   </si>
   <si>
+    <t>5,10,20,56,91,100,150,300,500,1000</t>
+  </si>
+  <si>
     <t>第9关</t>
   </si>
   <si>
@@ -160,6 +267,396 @@
     <t>第30关</t>
   </si>
   <si>
+    <t>第31关</t>
+  </si>
+  <si>
+    <t>第32关</t>
+  </si>
+  <si>
+    <t>第33关</t>
+  </si>
+  <si>
+    <t>第34关</t>
+  </si>
+  <si>
+    <t>第35关</t>
+  </si>
+  <si>
+    <t>第36关</t>
+  </si>
+  <si>
+    <t>第37关</t>
+  </si>
+  <si>
+    <t>第38关</t>
+  </si>
+  <si>
+    <t>第39关</t>
+  </si>
+  <si>
+    <t>第40关</t>
+  </si>
+  <si>
+    <t>第41关</t>
+  </si>
+  <si>
+    <t>第42关</t>
+  </si>
+  <si>
+    <t>第43关</t>
+  </si>
+  <si>
+    <t>第44关</t>
+  </si>
+  <si>
+    <t>第45关</t>
+  </si>
+  <si>
+    <t>第46关</t>
+  </si>
+  <si>
+    <t>第47关</t>
+  </si>
+  <si>
+    <t>第48关</t>
+  </si>
+  <si>
+    <t>第49关</t>
+  </si>
+  <si>
+    <t>第50关</t>
+  </si>
+  <si>
+    <t>第51关</t>
+  </si>
+  <si>
+    <t>第52关</t>
+  </si>
+  <si>
+    <t>第53关</t>
+  </si>
+  <si>
+    <t>第54关</t>
+  </si>
+  <si>
+    <t>第55关</t>
+  </si>
+  <si>
+    <t>第56关</t>
+  </si>
+  <si>
+    <t>第57关</t>
+  </si>
+  <si>
+    <t>第58关</t>
+  </si>
+  <si>
+    <t>第59关</t>
+  </si>
+  <si>
+    <t>第60关</t>
+  </si>
+  <si>
+    <t>第61关</t>
+  </si>
+  <si>
+    <t>第62关</t>
+  </si>
+  <si>
+    <t>第63关</t>
+  </si>
+  <si>
+    <t>第64关</t>
+  </si>
+  <si>
+    <t>第65关</t>
+  </si>
+  <si>
+    <t>第66关</t>
+  </si>
+  <si>
+    <t>第67关</t>
+  </si>
+  <si>
+    <t>第68关</t>
+  </si>
+  <si>
+    <t>第69关</t>
+  </si>
+  <si>
+    <t>第70关</t>
+  </si>
+  <si>
+    <t>第71关</t>
+  </si>
+  <si>
+    <t>第72关</t>
+  </si>
+  <si>
+    <t>第73关</t>
+  </si>
+  <si>
+    <t>第74关</t>
+  </si>
+  <si>
+    <t>第75关</t>
+  </si>
+  <si>
+    <t>第76关</t>
+  </si>
+  <si>
+    <t>第77关</t>
+  </si>
+  <si>
+    <t>第78关</t>
+  </si>
+  <si>
+    <t>第79关</t>
+  </si>
+  <si>
+    <t>第80关</t>
+  </si>
+  <si>
+    <t>第81关</t>
+  </si>
+  <si>
+    <t>第82关</t>
+  </si>
+  <si>
+    <t>第83关</t>
+  </si>
+  <si>
+    <t>第84关</t>
+  </si>
+  <si>
+    <t>第85关</t>
+  </si>
+  <si>
+    <t>第86关</t>
+  </si>
+  <si>
+    <t>第87关</t>
+  </si>
+  <si>
+    <t>第88关</t>
+  </si>
+  <si>
+    <t>第89关</t>
+  </si>
+  <si>
+    <t>第90关</t>
+  </si>
+  <si>
+    <t>第91关</t>
+  </si>
+  <si>
+    <t>第92关</t>
+  </si>
+  <si>
+    <t>第93关</t>
+  </si>
+  <si>
+    <t>第94关</t>
+  </si>
+  <si>
+    <t>第95关</t>
+  </si>
+  <si>
+    <t>第96关</t>
+  </si>
+  <si>
+    <t>第97关</t>
+  </si>
+  <si>
+    <t>第98关</t>
+  </si>
+  <si>
+    <t>第99关</t>
+  </si>
+  <si>
+    <t>第100关</t>
+  </si>
+  <si>
+    <t>第101关</t>
+  </si>
+  <si>
+    <t>第102关</t>
+  </si>
+  <si>
+    <t>第103关</t>
+  </si>
+  <si>
+    <t>第104关</t>
+  </si>
+  <si>
+    <t>第105关</t>
+  </si>
+  <si>
+    <t>第106关</t>
+  </si>
+  <si>
+    <t>第107关</t>
+  </si>
+  <si>
+    <t>第108关</t>
+  </si>
+  <si>
+    <t>第109关</t>
+  </si>
+  <si>
+    <t>第110关</t>
+  </si>
+  <si>
+    <t>第111关</t>
+  </si>
+  <si>
+    <t>第112关</t>
+  </si>
+  <si>
+    <t>第113关</t>
+  </si>
+  <si>
+    <t>第114关</t>
+  </si>
+  <si>
+    <t>第115关</t>
+  </si>
+  <si>
+    <t>第116关</t>
+  </si>
+  <si>
+    <t>第117关</t>
+  </si>
+  <si>
+    <t>第118关</t>
+  </si>
+  <si>
+    <t>第119关</t>
+  </si>
+  <si>
+    <t>第120关</t>
+  </si>
+  <si>
+    <t>第121关</t>
+  </si>
+  <si>
+    <t>第122关</t>
+  </si>
+  <si>
+    <t>第123关</t>
+  </si>
+  <si>
+    <t>第124关</t>
+  </si>
+  <si>
+    <t>第125关</t>
+  </si>
+  <si>
+    <t>第126关</t>
+  </si>
+  <si>
+    <t>第127关</t>
+  </si>
+  <si>
+    <t>第128关</t>
+  </si>
+  <si>
+    <t>第129关</t>
+  </si>
+  <si>
+    <t>第130关</t>
+  </si>
+  <si>
+    <t>第131关</t>
+  </si>
+  <si>
+    <t>第132关</t>
+  </si>
+  <si>
+    <t>第133关</t>
+  </si>
+  <si>
+    <t>第134关</t>
+  </si>
+  <si>
+    <t>第135关</t>
+  </si>
+  <si>
+    <t>第136关</t>
+  </si>
+  <si>
+    <t>第137关</t>
+  </si>
+  <si>
+    <t>第138关</t>
+  </si>
+  <si>
+    <t>第139关</t>
+  </si>
+  <si>
+    <t>第140关</t>
+  </si>
+  <si>
+    <t>第141关</t>
+  </si>
+  <si>
+    <t>第142关</t>
+  </si>
+  <si>
+    <t>第143关</t>
+  </si>
+  <si>
+    <t>第144关</t>
+  </si>
+  <si>
+    <t>第145关</t>
+  </si>
+  <si>
+    <t>第146关</t>
+  </si>
+  <si>
+    <t>第147关</t>
+  </si>
+  <si>
+    <t>第148关</t>
+  </si>
+  <si>
+    <t>第149关</t>
+  </si>
+  <si>
+    <t>第150关</t>
+  </si>
+  <si>
+    <t>第151关</t>
+  </si>
+  <si>
+    <t>第152关</t>
+  </si>
+  <si>
+    <t>第153关</t>
+  </si>
+  <si>
+    <t>第154关</t>
+  </si>
+  <si>
+    <t>第155关</t>
+  </si>
+  <si>
+    <t>第156关</t>
+  </si>
+  <si>
+    <t>第157关</t>
+  </si>
+  <si>
+    <t>第158关</t>
+  </si>
+  <si>
+    <t>第159关</t>
+  </si>
+  <si>
+    <t>第160关</t>
+  </si>
+  <si>
     <t>20101:100_20201:1_20301:10_20302:10_20303:10_20304:10_20305:10_20306:10_20307:10_20308:10_20309:10_20310:10</t>
   </si>
   <si>
@@ -245,585 +742,23 @@
   </si>
   <si>
     <t>300101:100_300201:1_300301:10_300302:10_300303:10_300304:10_300305:10_300306:10_300307:10_300308:10_300309:10_300310:10</t>
-  </si>
-  <si>
-    <t>box_id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>第31关</t>
-  </si>
-  <si>
-    <t>第32关</t>
-  </si>
-  <si>
-    <t>第33关</t>
-  </si>
-  <si>
-    <t>第34关</t>
-  </si>
-  <si>
-    <t>第35关</t>
-  </si>
-  <si>
-    <t>第36关</t>
-  </si>
-  <si>
-    <t>第37关</t>
-  </si>
-  <si>
-    <t>第38关</t>
-  </si>
-  <si>
-    <t>第39关</t>
-  </si>
-  <si>
-    <t>第40关</t>
-  </si>
-  <si>
-    <t>第41关</t>
-  </si>
-  <si>
-    <t>第42关</t>
-  </si>
-  <si>
-    <t>第43关</t>
-  </si>
-  <si>
-    <t>第44关</t>
-  </si>
-  <si>
-    <t>第45关</t>
-  </si>
-  <si>
-    <t>第46关</t>
-  </si>
-  <si>
-    <t>第47关</t>
-  </si>
-  <si>
-    <t>第48关</t>
-  </si>
-  <si>
-    <t>第49关</t>
-  </si>
-  <si>
-    <t>第50关</t>
-  </si>
-  <si>
-    <t>第51关</t>
-  </si>
-  <si>
-    <t>第52关</t>
-  </si>
-  <si>
-    <t>第53关</t>
-  </si>
-  <si>
-    <t>第54关</t>
-  </si>
-  <si>
-    <t>第55关</t>
-  </si>
-  <si>
-    <t>第56关</t>
-  </si>
-  <si>
-    <t>第57关</t>
-  </si>
-  <si>
-    <t>第58关</t>
-  </si>
-  <si>
-    <t>第59关</t>
-  </si>
-  <si>
-    <t>第60关</t>
-  </si>
-  <si>
-    <t>第61关</t>
-  </si>
-  <si>
-    <t>第62关</t>
-  </si>
-  <si>
-    <t>第63关</t>
-  </si>
-  <si>
-    <t>第64关</t>
-  </si>
-  <si>
-    <t>第65关</t>
-  </si>
-  <si>
-    <t>第66关</t>
-  </si>
-  <si>
-    <t>第67关</t>
-  </si>
-  <si>
-    <t>第68关</t>
-  </si>
-  <si>
-    <t>第69关</t>
-  </si>
-  <si>
-    <t>第70关</t>
-  </si>
-  <si>
-    <t>第71关</t>
-  </si>
-  <si>
-    <t>第72关</t>
-  </si>
-  <si>
-    <t>第73关</t>
-  </si>
-  <si>
-    <t>第74关</t>
-  </si>
-  <si>
-    <t>第75关</t>
-  </si>
-  <si>
-    <t>第76关</t>
-  </si>
-  <si>
-    <t>第77关</t>
-  </si>
-  <si>
-    <t>第78关</t>
-  </si>
-  <si>
-    <t>第79关</t>
-  </si>
-  <si>
-    <t>第80关</t>
-  </si>
-  <si>
-    <t>第81关</t>
-  </si>
-  <si>
-    <t>第82关</t>
-  </si>
-  <si>
-    <t>第83关</t>
-  </si>
-  <si>
-    <t>第84关</t>
-  </si>
-  <si>
-    <t>第85关</t>
-  </si>
-  <si>
-    <t>第86关</t>
-  </si>
-  <si>
-    <t>第87关</t>
-  </si>
-  <si>
-    <t>第88关</t>
-  </si>
-  <si>
-    <t>第89关</t>
-  </si>
-  <si>
-    <t>第90关</t>
-  </si>
-  <si>
-    <t>第91关</t>
-  </si>
-  <si>
-    <t>第92关</t>
-  </si>
-  <si>
-    <t>第93关</t>
-  </si>
-  <si>
-    <t>第94关</t>
-  </si>
-  <si>
-    <t>第95关</t>
-  </si>
-  <si>
-    <t>第96关</t>
-  </si>
-  <si>
-    <t>第97关</t>
-  </si>
-  <si>
-    <t>第98关</t>
-  </si>
-  <si>
-    <t>第99关</t>
-  </si>
-  <si>
-    <t>第100关</t>
-  </si>
-  <si>
-    <t>第101关</t>
-  </si>
-  <si>
-    <t>第102关</t>
-  </si>
-  <si>
-    <t>第103关</t>
-  </si>
-  <si>
-    <t>第104关</t>
-  </si>
-  <si>
-    <t>第105关</t>
-  </si>
-  <si>
-    <t>第106关</t>
-  </si>
-  <si>
-    <t>第107关</t>
-  </si>
-  <si>
-    <t>第108关</t>
-  </si>
-  <si>
-    <t>第109关</t>
-  </si>
-  <si>
-    <t>第110关</t>
-  </si>
-  <si>
-    <t>第111关</t>
-  </si>
-  <si>
-    <t>第112关</t>
-  </si>
-  <si>
-    <t>第113关</t>
-  </si>
-  <si>
-    <t>第114关</t>
-  </si>
-  <si>
-    <t>第115关</t>
-  </si>
-  <si>
-    <t>第116关</t>
-  </si>
-  <si>
-    <t>第117关</t>
-  </si>
-  <si>
-    <t>第118关</t>
-  </si>
-  <si>
-    <t>第119关</t>
-  </si>
-  <si>
-    <t>第120关</t>
-  </si>
-  <si>
-    <t>第121关</t>
-  </si>
-  <si>
-    <t>第122关</t>
-  </si>
-  <si>
-    <t>第123关</t>
-  </si>
-  <si>
-    <t>第124关</t>
-  </si>
-  <si>
-    <t>第125关</t>
-  </si>
-  <si>
-    <t>第126关</t>
-  </si>
-  <si>
-    <t>第127关</t>
-  </si>
-  <si>
-    <t>第128关</t>
-  </si>
-  <si>
-    <t>第129关</t>
-  </si>
-  <si>
-    <t>第130关</t>
-  </si>
-  <si>
-    <t>第131关</t>
-  </si>
-  <si>
-    <t>第132关</t>
-  </si>
-  <si>
-    <t>第133关</t>
-  </si>
-  <si>
-    <t>第134关</t>
-  </si>
-  <si>
-    <t>第135关</t>
-  </si>
-  <si>
-    <t>第136关</t>
-  </si>
-  <si>
-    <t>第137关</t>
-  </si>
-  <si>
-    <t>第138关</t>
-  </si>
-  <si>
-    <t>第139关</t>
-  </si>
-  <si>
-    <t>第140关</t>
-  </si>
-  <si>
-    <t>第141关</t>
-  </si>
-  <si>
-    <t>第142关</t>
-  </si>
-  <si>
-    <t>第143关</t>
-  </si>
-  <si>
-    <t>第144关</t>
-  </si>
-  <si>
-    <t>第145关</t>
-  </si>
-  <si>
-    <t>第146关</t>
-  </si>
-  <si>
-    <t>第147关</t>
-  </si>
-  <si>
-    <t>第148关</t>
-  </si>
-  <si>
-    <t>第149关</t>
-  </si>
-  <si>
-    <t>第150关</t>
-  </si>
-  <si>
-    <t>第151关</t>
-  </si>
-  <si>
-    <t>第152关</t>
-  </si>
-  <si>
-    <t>第153关</t>
-  </si>
-  <si>
-    <t>第154关</t>
-  </si>
-  <si>
-    <t>第155关</t>
-  </si>
-  <si>
-    <t>第156关</t>
-  </si>
-  <si>
-    <t>第157关</t>
-  </si>
-  <si>
-    <t>第158关</t>
-  </si>
-  <si>
-    <t>第159关</t>
-  </si>
-  <si>
-    <t>第160关</t>
-  </si>
-  <si>
-    <t>INT_S</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>STRING_S</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>血瓶id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>掉落血瓶的怪物数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>5,10,20,56,91,100,150,300,500,1000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hp_vial</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>drop_vial_foe</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>LIST&lt;INT&gt;_S_C</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>扫荡消耗体力</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>mop_cost</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>drop_equip_lv_min</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>drop_equip_lv_max</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>掉落装备等级,大</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>掉落装备等级，小</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>LIST&lt;INT&gt;_S</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>energy_list</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>能力等级队列（随机）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>101,102,103,104</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>box_id_first</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>首次通关奖励</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>initial_kongfu</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>玩家初始武力值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>INT_S_C</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>energy_id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>当前关卡使用的能力id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>last_id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>上一关id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>rare_items_show</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>展示为稀有的物品id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>LIST&lt;INT&gt;_S</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>challenge_cost</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>挑战消耗次数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>通关奖励（每次通关都有）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>46200001,46800001,46900001,42761001,42761002,42761003,42761004,42761005,42761006,42761007,42761008,42761009,42761010,42761011,42761012,42761013,42761014,42761015,42761016,42761017,42761018,42761019,42761020,42761021,42761022,42761023,42761024,42761025,42761026,42761027,42761028,42761029,42761030,42761031,42761032,42761033,42761034,42761035,42761036,42761037,42761038,42761039,42761040,42761041,42761042,42761043,42761044,42761045,42761046,42761047,42761048,42761049,42761050,42761051,42761052,42761053,42761054,42761055,42761056,42761057,42761058,42761059,42761060,42761061,42761062,42761063,42761064,42761065,42761066,42761067,42761068,42761069,42761070,42761071,42761072,42761073,42761074,42761075,42761076,42761077,42761078,42761079,42761080,42761081,42761082,42761083,42761084,42761085,42761086,42761087,42761088,42761089,42761090,42761091,42761092,42761093,42761094,42761095,42761096,42761097,42761098,42761099,42761100,42761101,42761102,42761103,42761104,42761105,42761106,42761107,42761108,42761109,42761110,42761111,42761112,42761113,42761114,42761115,42761116,42761117,42761118,42761119,42761120,42761121,42761122,42761123,42761124,42761125,42761126,42761127,42761128,42761129,42761130,42761131,42761132,42761133,42761134,42761135,42761136,42761137,42761138,42761139,42761140,42761141,42761142,42761143,42761144,42761145,42761146,42761147,42761148,42761149,42761150,42761151,42761152,42761153,42761154,42761155,42761156,42761157,42761158,42761159,42761160,42662001,42662002,42662003,42662004,42662005,42662006,42662007,42662008,42662009,42662010,42662011,42662012,42662013,42662014,42662015,42662016,42662017,42662018,42662019,42662020,42662021,42662022,42662023,42662024,42662025,42662026,42662027,42662028,42662029,42662030,42662031,42662032,42662033,42662034,42662035,42662036,42662037,42662038,42662039,42662040,42662041,42662042,42662043,42662044,42662045,42662046,42662047,42662048,42662049,42662050,42662051,42662052,42662053,42662054,42662055,42662056,42662057,42662058,42662059,42662060,42662061,42662062,42662063,42662064,42662065,42662066,42662067,42662068,42662069,42662070,42662071,42662072,42662073,42662074,42662075,42662076,42662077,42662078,42662079,42662080,42662081,42662082,42662083,42662084,42662085,42662086,42662087,42662088,42662089,42662090,42662091,42662092,42662093,42662094,42662095,42662096,42662097,42662098,42662099,42662100,42662101,42662102,42662103,42662104,42662105,42662106,42662107,42662108,42662109,42662110,42662111,42662112,42662113,42662114,42662115,42662116,42662117,42662118,42662119,42662120,42662121,42662122,42662123,42662124,42662125,42662126,42662127,42662128,42662129,42662130,42662131,42662132,42662133,42662134,42662135,42662136,42662137,42662138,42662139,42662140,42662141,42662142,42662143,42662144,42662145,42662146,42662147,42662148,42662149,42662150,42662151,42662152,42662153,42662154,42662155,42662156,42662157,42662158,42662159,42662160,42663001,42663002,42663003,42663004,42663005,42663006,42663007,42663008,42663009,42663010,42663011,42663012,42663013,42663014,42663015,42663016,42663017,42663018,42663019,42663020,42663021,42663022,42663023,42663024,42663025,42663026,42663027,42663028,42663029,42663030,42663031,42663032,42663033,42663034,42663035,42663036,42663037,42663038,42663039,42663040,42663041,42663042,42663043,42663044,42663045,42663046,42663047,42663048,42663049,42663050,42663051,42663052,42663053,42663054,42663055,42663056,42663057,42663058,42663059,42663060,42663061,42663062,42663063,42663064,42663065,42663066,42663067,42663068,42663069,42663070,42663071,42663072,42663073,42663074,42663075,42663076,42663077,42663078,42663079,42663080,42663081,42663082,42663083,42663084,42663085,42663086,42663087,42663088,42663089,42663090,42663091,42663092,42663093,42663094,42663095,42663096,42663097,42663098,42663099,42663100,42663101,42663102,42663103,42663104,42663105,42663106,42663107,42663108,42663109,42663110,42663111,42663112,42663113,42663114,42663115,42663116,42663117,42663118,42663119,42663120,42663121,42663122,42663123,42663124,42663125,42663126,42663127,42663128,42663129,42663130,42663131,42663132,42663133,42663134,42663135,42663136,42663137,42663138,42663139,42663140,42663141,42663142,42663143,42663144,42663145,42663146,42663147,42663148,42663149,42663150,42663151,42663152,42663153,42663154,42663155,42663156,42663157,42663158,42663159,42663160,42666001,42666002,42666003,42666004,42666005,42666006,42666007,42666008,42666009,42666010,42666011,42666012,42666013,42666014,42666015,42666016,42666017,42666018,42666019,42666020,42666021,42666022,42666023,42666024,42666025,42666026,42666027,42666028,42666029,42666030,42666031,42666032,42666033,42666034,42666035,42666036,42666037,42666038,42666039,42666040,42666041,42666042,42666043,42666044,42666045,42666046,42666047,42666048,42666049,42666050,42666051,42666052,42666053,42666054,42666055,42666056,42666057,42666058,42666059,42666060,42666061,42666062,42666063,42666064,42666065,42666066,42666067,42666068,42666069,42666070,42666071,42666072,42666073,42666074,42666075,42666076,42666077,42666078,42666079,42666080,42666081,42666082,42666083,42666084,42666085,42666086,42666087,42666088,42666089,42666090,42666091,42666092,42666093,42666094,42666095,42666096,42666097,42666098,42666099,42666100,42666101,42666102,42666103,42666104,42666105,42666106,42666107,42666108,42666109,42666110,42666111,42666112,42666113,42666114,42666115,42666116,42666117,42666118,42666119,42666120,42666121,42666122,42666123,42666124,42666125,42666126,42666127,42666128,42666129,42666130,42666131,42666132,42666133,42666134,42666135,42666136,42666137,42666138,42666139,42666140,42666141,42666142,42666143,42666144,42666145,42666146,42666147,42666148,42666149,42666150,42666151,42666152,42666153,42666154,42666155,42666156,42666157,42666158,42666159,42666160,42664001,42664002,42664003,42664004,42664005,42664006,42664007,42664008,42664009,42664010,42664011,42664012,42664013,42664014,42664015,42664016,42664017,42664018,42664019,42664020,42664021,42664022,42664023,42664024,42664025,42664026,42664027,42664028,42664029,42664030,42664031,42664032,42664033,42664034,42664035,42664036,42664037,42664038,42664039,42664040,42664041,42664042,42664043,42664044,42664045,42664046,42664047,42664048,42664049,42664050,42664051,42664052,42664053,42664054,42664055,42664056,42664057,42664058,42664059,42664060,42664061,42664062,42664063,42664064,42664065,42664066,42664067,42664068,42664069,42664070,42664071,42664072,42664073,42664074,42664075,42664076,42664077,42664078,42664079,42664080,42664081,42664082,42664083,42664084,42664085,42664086,42664087,42664088,42664089,42664090,42664091,42664092,42664093,42664094,42664095,42664096,42664097,42664098,42664099,42664100,42664101,42664102,42664103,42664104,42664105,42664106,42664107,42664108,42664109,42664110,42664111,42664112,42664113,42664114,42664115,42664116,42664117,42664118,42664119,42664120,42664121,42664122,42664123,42664124,42664125,42664126,42664127,42664128,42664129,42664130,42664131,42664132,42664133,42664134,42664135,42664136,42664137,42664138,42664139,42664140,42664141,42664142,42664143,42664144,42664145,42664146,42664147,42664148,42664149,42664150,42664151,42664152,42664153,42664154,42664155,42664156,42664157,42664158,42664159,42664160,42665001,42665002,42665003,42665004,42665005,42665006,42665007,42665008,42665009,42665010,42665011,42665012,42665013,42665014,42665015,42665016,42665017,42665018,42665019,42665020,42665021,42665022,42665023,42665024,42665025,42665026,42665027,42665028,42665029,42665030,42665031,42665032,42665033,42665034,42665035,42665036,42665037,42665038,42665039,42665040,42665041,42665042,42665043,42665044,42665045,42665046,42665047,42665048,42665049,42665050,42665051,42665052,42665053,42665054,42665055,42665056,42665057,42665058,42665059,42665060,42665061,42665062,42665063,42665064,42665065,42665066,42665067,42665068,42665069,42665070,42665071,42665072,42665073,42665074,42665075,42665076,42665077,42665078,42665079,42665080,42665081,42665082,42665083,42665084,42665085,42665086,42665087,42665088,42665089,42665090,42665091,42665092,42665093,42665094,42665095,42665096,42665097,42665098,42665099,42665100,42665101,42665102,42665103,42665104,42665105,42665106,42665107,42665108,42665109,42665110,42665111,42665112,42665113,42665114,42665115,42665116,42665117,42665118,42665119,42665120,42665121,42665122,42665123,42665124,42665125,42665126,42665127,42665128,42665129,42665130,42665131,42665132,42665133,42665134,42665135,42665136,42665137,42665138,42665139,42665140,42665141,42665142,42665143,42665144,42665145,42665146,42665147,42665148,42665149,42665150,42665151,42665152,42665153,42665154,42665155,42665156,42665157,42665158,42665159,42665160,42667001,42667002,42667003,42667004,42667005,42667006,42667007,42667008,42667009,42667010,42667011,42667012,42667013,42667014,42667015,42667016,42667017,42667018,42667019,42667020,42667021,42667022,42667023,42667024,42667025,42667026,42667027,42667028,42667029,42667030,42667031,42667032,42667033,42667034,42667035,42667036,42667037,42667038,42667039,42667040,42667041,42667042,42667043,42667044,42667045,42667046,42667047,42667048,42667049,42667050,42667051,42667052,42667053,42667054,42667055,42667056,42667057,42667058,42667059,42667060,42667061,42667062,42667063,42667064,42667065,42667066,42667067,42667068,42667069,42667070,42667071,42667072,42667073,42667074,42667075,42667076,42667077,42667078,42667079,42667080,42667081,42667082,42667083,42667084,42667085,42667086,42667087,42667088,42667089,42667090,42667091,42667092,42667093,42667094,42667095,42667096,42667097,42667098,42667099,42667100,42667101,42667102,42667103,42667104,42667105,42667106,42667107,42667108,42667109,42667110,42667111,42667112,42667113,42667114,42667115,42667116,42667117,42667118,42667119,42667120,42667121,42667122,42667123,42667124,42667125,42667126,42667127,42667128,42667129,42667130,42667131,42667132,42667133,42667134,42667135,42667136,42667137,42667138,42667139,42667140,42667141,42667142,42667143,42667144,42667145,42667146,42667147,42667148,42667149,42667150,42667151,42667152,42667153,42667154,42667155,42667156,42667157,42667158,42667159,42667160,42668001,42668002,42668003,42668004,42668005,42668006,42668007,42668008,42668009,42668010,42668011,42668012,42668013,42668014,42668015,42668016,42668017,42668018,42668019,42668020,42668021,42668022,42668023,42668024,42668025,42668026,42668027,42668028,42668029,42668030,42668031,42668032,42668033,42668034,42668035,42668036,42668037,42668038,42668039,42668040,42668041,42668042,42668043,42668044,42668045,42668046,42668047,42668048,42668049,42668050,42668051,42668052,42668053,42668054,42668055,42668056,42668057,42668058,42668059,42668060,42668061,42668062,42668063,42668064,42668065,42668066,42668067,42668068,42668069,42668070,42668071,42668072,42668073,42668074,42668075,42668076,42668077,42668078,42668079,42668080,42668081,42668082,42668083,42668084,42668085,42668086,42668087,42668088,42668089,42668090,42668091,42668092,42668093,42668094,42668095,42668096,42668097,42668098,42668099,42668100,42668101,42668102,42668103,42668104,42668105,42668106,42668107,42668108,42668109,42668110,42668111,42668112,42668113,42668114,42668115,42668116,42668117,42668118,42668119,42668120,42668121,42668122,42668123,42668124,42668125,42668126,42668127,42668128,42668129,42668130,42668131,42668132,42668133,42668134,42668135,42668136,42668137,42668138,42668139,42668140,42668141,42668142,42668143,42668144,42668145,42668146,42668147,42668148,42668149,42668150,42668151,42668152,42668153,42668154,42668155,42668156,42668157,42668158,42668159,42668160,42781001,42781002,42781003,42781004,42781005,42781006,42781007,42781008,42781009,42781010,42781011,42781012,42781013,42781014,42781015,42781016,42781017,42781018,42781019,42781020,42781021,42781022,42781023,42781024,42781025,42781026,42781027,42781028,42781029,42781030,42781031,42781032,42781033,42781034,42781035,42781036,42781037,42781038,42781039,42781040,42781041,42781042,42781043,42781044,42781045,42781046,42781047,42781048,42781049,42781050,42781051,42781052,42781053,42781054,42781055,42781056,42781057,42781058,42781059,42781060,42781061,42781062,42781063,42781064,42781065,42781066,42781067,42781068,42781069,42781070,42781071,42781072,42781073,42781074,42781075,42781076,42781077,42781078,42781079,42781080,42781081,42781082,42781083,42781084,42781085,42781086,42781087,42781088,42781089,42781090,42781091,42781092,42781093,42781094,42781095,42781096,42781097,42781098,42781099,42781100,42781101,42781102,42781103,42781104,42781105,42781106,42781107,42781108,42781109,42781110,42781111,42781112,42781113,42781114,42781115,42781116,42781117,42781118,42781119,42781120,42781121,42781122,42781123,42781124,42781125,42781126,42781127,42781128,42781129,42781130,42781131,42781132,42781133,42781134,42781135,42781136,42781137,42781138,42781139,42781140,42781141,42781142,42781143,42781144,42781145,42781146,42781147,42781148,42781149,42781150,42781151,42781152,42781153,42781154,42781155,42781156,42781157,42781158,42781159,42781160,42682001,42682002,42682003,42682004,42682005,42682006,42682007,42682008,42682009,42682010,42682011,42682012,42682013,42682014,42682015,42682016,42682017,42682018,42682019,42682020,42682021,42682022,42682023,42682024,42682025,42682026,42682027,42682028,42682029,42682030,42682031,42682032,42682033,42682034,42682035,42682036,42682037,42682038,42682039,42682040,42682041,42682042,42682043,42682044,42682045,42682046,42682047,42682048,42682049,42682050,42682051,42682052,42682053,42682054,42682055,42682056,42682057,42682058,42682059,42682060,42682061,42682062,42682063,42682064,42682065,42682066,42682067,42682068,42682069,42682070,42682071,42682072,42682073,42682074,42682075,42682076,42682077,42682078,42682079,42682080,42682081,42682082,42682083,42682084,42682085,42682086,42682087,42682088,42682089,42682090,42682091,42682092,42682093,42682094,42682095,42682096,42682097,42682098,42682099,42682100,42682101,42682102,42682103,42682104,42682105,42682106,42682107,42682108,42682109,42682110,42682111,42682112,42682113,42682114,42682115,42682116,42682117,42682118,42682119,42682120,42682121,42682122,42682123,42682124,42682125,42682126,42682127,42682128,42682129,42682130,42682131,42682132,42682133,42682134,42682135,42682136,42682137,42682138,42682139,42682140,42682141,42682142,42682143,42682144,42682145,42682146,42682147,42682148,42682149,42682150,42682151,42682152,42682153,42682154,42682155,42682156,42682157,42682158,42682159,42682160,42683001,42683002,42683003,42683004,42683005,42683006,42683007,42683008,42683009,42683010,42683011,42683012,42683013,42683014,42683015,42683016,42683017,42683018,42683019,42683020,42683021,42683022,42683023,42683024,42683025,42683026,42683027,42683028,42683029,42683030,42683031,42683032,42683033,42683034,42683035,42683036,42683037,42683038,42683039,42683040,42683041,42683042,42683043,42683044,42683045,42683046,42683047,42683048,42683049,42683050,42683051,42683052,42683053,42683054,42683055,42683056,42683057,42683058,42683059,42683060,42683061,42683062,42683063,42683064,42683065,42683066,42683067,42683068,42683069,42683070,42683071,42683072,42683073,42683074,42683075,42683076,42683077,42683078,42683079,42683080,42683081,42683082,42683083,42683084,42683085,42683086,42683087,42683088,42683089,42683090,42683091,42683092,42683093,42683094,42683095,42683096,42683097,42683098,42683099,42683100,42683101,42683102,42683103,42683104,42683105,42683106,42683107,42683108,42683109,42683110,42683111,42683112,42683113,42683114,42683115,42683116,42683117,42683118,42683119,42683120,42683121,42683122,42683123,42683124,42683125,42683126,42683127,42683128,42683129,42683130,42683131,42683132,42683133,42683134,42683135,42683136,42683137,42683138,42683139,42683140,42683141,42683142,42683143,42683144,42683145,42683146,42683147,42683148,42683149,42683150,42683151,42683152,42683153,42683154,42683155,42683156,42683157,42683158,42683159,42683160,42686001,42686002,42686003,42686004,42686005,42686006,42686007,42686008,42686009,42686010,42686011,42686012,42686013,42686014,42686015,42686016,42686017,42686018,42686019,42686020,42686021,42686022,42686023,42686024,42686025,42686026,42686027,42686028,42686029,42686030,42686031,42686032,42686033,42686034,42686035,42686036,42686037,42686038,42686039,42686040,42686041,42686042,42686043,42686044,42686045,42686046,42686047,42686048,42686049,42686050,42686051,42686052,42686053,42686054,42686055,42686056,42686057,42686058,42686059,42686060,42686061,42686062,42686063,42686064,42686065,42686066,42686067,42686068,42686069,42686070,42686071,42686072,42686073,42686074,42686075,42686076,42686077,42686078,42686079,42686080,42686081,42686082,42686083,42686084,42686085,42686086,42686087,42686088,42686089,42686090,42686091,42686092,42686093,42686094,42686095,42686096,42686097,42686098,42686099,42686100,42686101,42686102,42686103,42686104,42686105,42686106,42686107,42686108,42686109,42686110,42686111,42686112,42686113,42686114,42686115,42686116,42686117,42686118,42686119,42686120,42686121,42686122,42686123,42686124,42686125,42686126,42686127,42686128,42686129,42686130,42686131,42686132,42686133,42686134,42686135,42686136,42686137,42686138,42686139,42686140,42686141,42686142,42686143,42686144,42686145,42686146,42686147,42686148,42686149,42686150,42686151,42686152,42686153,42686154,42686155,42686156,42686157,42686158,42686159,42686160,42684001,42684002,42684003,42684004,42684005,42684006,42684007,42684008,42684009,42684010,42684011,42684012,42684013,42684014,42684015,42684016,42684017,42684018,42684019,42684020,42684021,42684022,42684023,42684024,42684025,42684026,42684027,42684028,42684029,42684030,42684031,42684032,42684033,42684034,42684035,42684036,42684037,42684038,42684039,42684040,42684041,42684042,42684043,42684044,42684045,42684046,42684047,42684048,42684049,42684050,42684051,42684052,42684053,42684054,42684055,42684056,42684057,42684058,42684059,42684060,42684061,42684062,42684063,42684064,42684065,42684066,42684067,42684068,42684069,42684070,42684071,42684072,42684073,42684074,42684075,42684076,42684077,42684078,42684079,42684080,42684081,42684082,42684083,42684084,42684085,42684086,42684087,42684088,42684089,42684090,42684091,42684092,42684093,42684094,42684095,42684096,42684097,42684098,42684099,42684100,42684101,42684102,42684103,42684104,42684105,42684106,42684107,42684108,42684109,42684110,42684111,42684112,42684113,42684114,42684115,42684116,42684117,42684118,42684119,42684120,42684121,42684122,42684123,42684124,42684125,42684126,42684127,42684128,42684129,42684130,42684131,42684132,42684133,42684134,42684135,42684136,42684137,42684138,42684139,42684140,42684141,42684142,42684143,42684144,42684145,42684146,42684147,42684148,42684149,42684150,42684151,42684152,42684153,42684154,42684155,42684156,42684157,42684158,42684159,42684160,42685001,42685002,42685003,42685004,42685005,42685006,42685007,42685008,42685009,42685010,42685011,42685012,42685013,42685014,42685015,42685016,42685017,42685018,42685019,42685020,42685021,42685022,42685023,42685024,42685025,42685026,42685027,42685028,42685029,42685030,42685031,42685032,42685033,42685034,42685035,42685036,42685037,42685038,42685039,42685040,42685041,42685042,42685043,42685044,42685045,42685046,42685047,42685048,42685049,42685050,42685051,42685052,42685053,42685054,42685055,42685056,42685057,42685058,42685059,42685060,42685061,42685062,42685063,42685064,42685065,42685066,42685067,42685068,42685069,42685070,42685071,42685072,42685073,42685074,42685075,42685076,42685077,42685078,42685079,42685080,42685081,42685082,42685083,42685084,42685085,42685086,42685087,42685088,42685089,42685090,42685091,42685092,42685093,42685094,42685095,42685096,42685097,42685098,42685099,42685100,42685101,42685102,42685103,42685104,42685105,42685106,42685107,42685108,42685109,42685110,42685111,42685112,42685113,42685114,42685115,42685116,42685117,42685118,42685119,42685120,42685121,42685122,42685123,42685124,42685125,42685126,42685127,42685128,42685129,42685130,42685131,42685132,42685133,42685134,42685135,42685136,42685137,42685138,42685139,42685140,42685141,42685142,42685143,42685144,42685145,42685146,42685147,42685148,42685149,42685150,42685151,42685152,42685153,42685154,42685155,42685156,42685157,42685158,42685159,42685160,42687001,42687002,42687003,42687004,42687005,42687006,42687007,42687008,42687009,42687010,42687011,42687012,42687013,42687014,42687015,42687016,42687017,42687018,42687019,42687020,42687021,42687022,42687023,42687024,42687025,42687026,42687027,42687028,42687029,42687030,42687031,42687032,42687033,42687034,42687035,42687036,42687037,42687038,42687039,42687040,42687041,42687042,42687043,42687044,42687045,42687046,42687047,42687048,42687049,42687050,42687051,42687052,42687053,42687054,42687055,42687056,42687057,42687058,42687059,42687060,42687061,42687062,42687063,42687064,42687065,42687066,42687067,42687068,42687069,42687070,42687071,42687072,42687073,42687074,42687075,42687076,42687077,42687078,42687079,42687080,42687081,42687082,42687083,42687084,42687085,42687086,42687087,42687088,42687089,42687090,42687091,42687092,42687093,42687094,42687095,42687096,42687097,42687098,42687099,42687100,42687101,42687102,42687103,42687104,42687105,42687106,42687107,42687108,42687109,42687110,42687111,42687112,42687113,42687114,42687115,42687116,42687117,42687118,42687119,42687120,42687121,42687122,42687123,42687124,42687125,42687126,42687127,42687128,42687129,42687130,42687131,42687132,42687133,42687134,42687135,42687136,42687137,42687138,42687139,42687140,42687141,42687142,42687143,42687144,42687145,42687146,42687147,42687148,42687149,42687150,42687151,42687152,42687153,42687154,42687155,42687156,42687157,42687158,42687159,42687160,42688001,42688002,42688003,42688004,42688005,42688006,42688007,42688008,42688009,42688010,42688011,42688012,42688013,42688014,42688015,42688016,42688017,42688018,42688019,42688020,42688021,42688022,42688023,42688024,42688025,42688026,42688027,42688028,42688029,42688030,42688031,42688032,42688033,42688034,42688035,42688036,42688037,42688038,42688039,42688040,42688041,42688042,42688043,42688044,42688045,42688046,42688047,42688048,42688049,42688050,42688051,42688052,42688053,42688054,42688055,42688056,42688057,42688058,42688059,42688060,42688061,42688062,42688063,42688064,42688065,42688066,42688067,42688068,42688069,42688070,42688071,42688072,42688073,42688074,42688075,42688076,42688077,42688078,42688079,42688080,42688081,42688082,42688083,42688084,42688085,42688086,42688087,42688088,42688089,42688090,42688091,42688092,42688093,42688094,42688095,42688096,42688097,42688098,42688099,42688100,42688101,42688102,42688103,42688104,42688105,42688106,42688107,42688108,42688109,42688110,42688111,42688112,42688113,42688114,42688115,42688116,42688117,42688118,42688119,42688120,42688121,42688122,42688123,42688124,42688125,42688126,42688127,42688128,42688129,42688130,42688131,42688132,42688133,42688134,42688135,42688136,42688137,42688138,42688139,42688140,42688141,42688142,42688143,42688144,42688145,42688146,42688147,42688148,42688149,42688150,42688151,42688152,42688153,42688154,42688155,42688156,42688157,42688158,42688159,42688160</t>
-  </si>
-  <si>
-    <t>energy_affix_rand_rule</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>能力词条随机规则</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>18,78,150,210,320,440,580</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>12,30,55,80,133,155,175,205,238</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>11,38,56</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>drop_id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>掉落id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1,2,3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -831,19 +766,355 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -851,27 +1122,313 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -920,7 +1477,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic Light"/>
@@ -955,7 +1512,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic"/>
@@ -1129,213 +1686,207 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:R164"/>
-  <sheetFormatPr defaultColWidth="7.125" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="7.125" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" width="20.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="9.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="25.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="38.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="19.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="21.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="19.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="21.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="19.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="21.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.5" style="1" customWidth="1"/>
+    <col min="2" max="3" width="9.125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5" style="1" customWidth="1"/>
+    <col min="5" max="5" width="25.5" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="9.5" style="1" customWidth="1"/>
+    <col min="8" max="8" width="38.25" style="1" customWidth="1"/>
+    <col min="9" max="9" width="16.125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="13" style="1" customWidth="1"/>
+    <col min="11" max="12" width="19.375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="21.375" style="1" customWidth="1"/>
+    <col min="14" max="14" width="19.375" style="1" customWidth="1"/>
+    <col min="15" max="16" width="21.5" style="1" customWidth="1"/>
+    <col min="17" max="17" width="19.375" style="1" customWidth="1"/>
+    <col min="18" max="18" width="21.5" style="1" customWidth="1"/>
     <col min="19" max="16384" width="7.125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:18">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>198</v>
+        <v>2</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>198</v>
+        <v>2</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>199</v>
+        <v>3</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>198</v>
+        <v>2</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>198</v>
+        <v>2</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>220</v>
+        <v>4</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>205</v>
+        <v>5</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>198</v>
+        <v>2</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>198</v>
+        <v>2</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>220</v>
+        <v>4</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>220</v>
+        <v>4</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>212</v>
+        <v>6</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>220</v>
+        <v>4</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>220</v>
+        <v>4</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>220</v>
+        <v>4</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>227</v>
+        <v>6</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>223</v>
+        <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>67</v>
+        <v>11</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>216</v>
+        <v>12</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>203</v>
+        <v>13</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>204</v>
+        <v>14</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>228</v>
+        <v>15</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>207</v>
+        <v>16</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>208</v>
+        <v>17</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>209</v>
+        <v>18</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>213</v>
+        <v>19</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>218</v>
+        <v>20</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>221</v>
+        <v>21</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>232</v>
+        <v>22</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>225</v>
+        <v>23</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.15">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18">
       <c r="A4" s="1" t="s">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>224</v>
+        <v>26</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>230</v>
+        <v>29</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>217</v>
+        <v>30</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>200</v>
+        <v>31</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>201</v>
+        <v>32</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>229</v>
+        <v>33</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>206</v>
+        <v>34</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>211</v>
+        <v>35</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>210</v>
+        <v>36</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>214</v>
+        <v>37</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>219</v>
+        <v>38</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>222</v>
+        <v>39</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>233</v>
+        <v>40</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>226</v>
+        <v>41</v>
       </c>
       <c r="R4" s="1" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.15">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -1346,7 +1897,7 @@
         <v>2</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="E5" s="1">
         <v>10010</v>
@@ -1357,8 +1908,8 @@
       <c r="G5" s="1">
         <v>43400002</v>
       </c>
-      <c r="H5" s="1" t="s">
-        <v>236</v>
+      <c r="H5" s="1">
+        <v>0</v>
       </c>
       <c r="I5" s="1">
         <v>1</v>
@@ -1373,7 +1924,7 @@
         <v>1</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N5" s="1">
         <v>150</v>
@@ -1385,13 +1936,13 @@
         <v>1001</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="R5" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.15">
+        <v>45</v>
+      </c>
+      <c r="R5" s="1">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18">
       <c r="A6" s="1">
         <v>2</v>
       </c>
@@ -1402,7 +1953,7 @@
         <v>3</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="E6" s="1">
         <v>20010</v>
@@ -1414,7 +1965,7 @@
         <v>43400002</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>235</v>
+        <v>47</v>
       </c>
       <c r="I6" s="1">
         <v>1</v>
@@ -1429,7 +1980,7 @@
         <v>2</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N6" s="1">
         <v>200</v>
@@ -1441,13 +1992,13 @@
         <v>1003</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R6" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18">
       <c r="A7" s="1">
         <v>3</v>
       </c>
@@ -1458,7 +2009,7 @@
         <v>4</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="E7" s="1">
         <v>30010</v>
@@ -1470,7 +2021,7 @@
         <v>43400002</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>235</v>
+        <v>47</v>
       </c>
       <c r="I7" s="1">
         <v>1</v>
@@ -1485,7 +2036,7 @@
         <v>3</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N7" s="1">
         <v>300</v>
@@ -1497,13 +2048,13 @@
         <v>1003</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18">
       <c r="A8" s="1">
         <v>4</v>
       </c>
@@ -1514,7 +2065,7 @@
         <v>5</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="E8" s="1">
         <v>40010</v>
@@ -1526,7 +2077,7 @@
         <v>43400002</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>235</v>
+        <v>47</v>
       </c>
       <c r="I8" s="1">
         <v>1</v>
@@ -1541,7 +2092,7 @@
         <v>4</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N8" s="1">
         <v>400</v>
@@ -1553,13 +2104,13 @@
         <v>1003</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R8" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18">
       <c r="A9" s="1">
         <v>5</v>
       </c>
@@ -1570,7 +2121,7 @@
         <v>6</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="E9" s="1">
         <v>50010</v>
@@ -1582,7 +2133,7 @@
         <v>43400002</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>234</v>
+        <v>52</v>
       </c>
       <c r="I9" s="1">
         <v>1</v>
@@ -1597,7 +2148,7 @@
         <v>5</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N9" s="1">
         <v>500</v>
@@ -1609,13 +2160,13 @@
         <v>1003</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R9" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18">
       <c r="A10" s="1">
         <v>6</v>
       </c>
@@ -1626,7 +2177,7 @@
         <v>7</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="E10" s="1">
         <v>60010</v>
@@ -1638,7 +2189,7 @@
         <v>43400002</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>234</v>
+        <v>52</v>
       </c>
       <c r="I10" s="1">
         <v>1</v>
@@ -1653,7 +2204,7 @@
         <v>6</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N10" s="1">
         <v>600</v>
@@ -1665,13 +2216,13 @@
         <v>1003</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R10" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18">
       <c r="A11" s="1">
         <v>7</v>
       </c>
@@ -1682,7 +2233,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>14</v>
+        <v>54</v>
       </c>
       <c r="E11" s="1">
         <v>70010</v>
@@ -1709,7 +2260,7 @@
         <v>7</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N11" s="1">
         <v>100</v>
@@ -1721,13 +2272,13 @@
         <v>1003</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R11" s="1">
         <v>101</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:18">
       <c r="A12" s="1">
         <v>8</v>
       </c>
@@ -1738,7 +2289,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="E12" s="1">
         <v>80010</v>
@@ -1750,7 +2301,7 @@
         <v>43400002</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I12" s="1">
         <v>1</v>
@@ -1765,7 +2316,7 @@
         <v>8</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N12" s="1">
         <v>100</v>
@@ -1777,13 +2328,13 @@
         <v>1</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R12" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18">
       <c r="A13" s="1">
         <v>9</v>
       </c>
@@ -1794,7 +2345,7 @@
         <v>10</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>16</v>
+        <v>57</v>
       </c>
       <c r="E13" s="1">
         <v>90010</v>
@@ -1806,7 +2357,7 @@
         <v>43400002</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I13" s="1">
         <v>1</v>
@@ -1821,7 +2372,7 @@
         <v>9</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N13" s="1">
         <v>100</v>
@@ -1833,13 +2384,13 @@
         <v>1</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R13" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14" ht="13.5" customHeight="1" spans="1:18">
       <c r="A14" s="1">
         <v>10</v>
       </c>
@@ -1850,7 +2401,7 @@
         <v>11</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="E14" s="1">
         <v>100010</v>
@@ -1862,7 +2413,7 @@
         <v>43400002</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I14" s="1">
         <v>1</v>
@@ -1877,7 +2428,7 @@
         <v>10</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N14" s="1">
         <v>100</v>
@@ -1889,13 +2440,13 @@
         <v>1</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R14" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18">
       <c r="A15" s="1">
         <v>11</v>
       </c>
@@ -1906,7 +2457,7 @@
         <v>12</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="E15" s="1">
         <v>110010</v>
@@ -1918,7 +2469,7 @@
         <v>43400002</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I15" s="1">
         <v>1</v>
@@ -1933,7 +2484,7 @@
         <v>11</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N15" s="1">
         <v>100</v>
@@ -1945,13 +2496,13 @@
         <v>1</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R15" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18">
       <c r="A16" s="1">
         <v>12</v>
       </c>
@@ -1962,7 +2513,7 @@
         <v>13</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="E16" s="1">
         <v>120010</v>
@@ -1974,7 +2525,7 @@
         <v>43400002</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I16" s="1">
         <v>1</v>
@@ -1989,7 +2540,7 @@
         <v>12</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N16" s="1">
         <v>100</v>
@@ -2001,13 +2552,13 @@
         <v>1</v>
       </c>
       <c r="Q16" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R16" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18">
       <c r="A17" s="1">
         <v>13</v>
       </c>
@@ -2018,7 +2569,7 @@
         <v>14</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>20</v>
+        <v>61</v>
       </c>
       <c r="E17" s="1">
         <v>130010</v>
@@ -2030,7 +2581,7 @@
         <v>43400002</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I17" s="1">
         <v>1</v>
@@ -2045,7 +2596,7 @@
         <v>13</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N17" s="1">
         <v>100</v>
@@ -2057,13 +2608,13 @@
         <v>1</v>
       </c>
       <c r="Q17" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R17" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18">
       <c r="A18" s="1">
         <v>14</v>
       </c>
@@ -2074,7 +2625,7 @@
         <v>15</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="E18" s="1">
         <v>140010</v>
@@ -2086,7 +2637,7 @@
         <v>43400002</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I18" s="1">
         <v>1</v>
@@ -2101,7 +2652,7 @@
         <v>14</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N18" s="1">
         <v>100</v>
@@ -2113,13 +2664,13 @@
         <v>1</v>
       </c>
       <c r="Q18" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R18" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18">
       <c r="A19" s="1">
         <v>15</v>
       </c>
@@ -2130,7 +2681,7 @@
         <v>16</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="E19" s="1">
         <v>150010</v>
@@ -2142,7 +2693,7 @@
         <v>43400002</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I19" s="1">
         <v>1</v>
@@ -2157,7 +2708,7 @@
         <v>15</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N19" s="1">
         <v>100</v>
@@ -2169,13 +2720,13 @@
         <v>1</v>
       </c>
       <c r="Q19" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R19" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18">
       <c r="A20" s="1">
         <v>16</v>
       </c>
@@ -2186,7 +2737,7 @@
         <v>17</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>23</v>
+        <v>64</v>
       </c>
       <c r="E20" s="1">
         <v>160010</v>
@@ -2198,7 +2749,7 @@
         <v>43400002</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I20" s="1">
         <v>1</v>
@@ -2213,7 +2764,7 @@
         <v>16</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N20" s="1">
         <v>100</v>
@@ -2225,13 +2776,13 @@
         <v>1</v>
       </c>
       <c r="Q20" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R20" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18">
       <c r="A21" s="1">
         <v>17</v>
       </c>
@@ -2242,7 +2793,7 @@
         <v>18</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="E21" s="1">
         <v>170010</v>
@@ -2254,7 +2805,7 @@
         <v>43400002</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I21" s="1">
         <v>1</v>
@@ -2269,7 +2820,7 @@
         <v>17</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N21" s="1">
         <v>100</v>
@@ -2281,13 +2832,13 @@
         <v>1</v>
       </c>
       <c r="Q21" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R21" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18">
       <c r="A22" s="1">
         <v>18</v>
       </c>
@@ -2298,7 +2849,7 @@
         <v>19</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="E22" s="1">
         <v>180010</v>
@@ -2310,7 +2861,7 @@
         <v>43400002</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I22" s="1">
         <v>1</v>
@@ -2325,7 +2876,7 @@
         <v>18</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N22" s="1">
         <v>100</v>
@@ -2337,13 +2888,13 @@
         <v>1</v>
       </c>
       <c r="Q22" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R22" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18">
       <c r="A23" s="1">
         <v>19</v>
       </c>
@@ -2354,7 +2905,7 @@
         <v>20</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>26</v>
+        <v>67</v>
       </c>
       <c r="E23" s="1">
         <v>190010</v>
@@ -2366,7 +2917,7 @@
         <v>43400002</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I23" s="1">
         <v>1</v>
@@ -2381,7 +2932,7 @@
         <v>19</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N23" s="1">
         <v>100</v>
@@ -2393,13 +2944,13 @@
         <v>1</v>
       </c>
       <c r="Q23" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R23" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18">
       <c r="A24" s="1">
         <v>20</v>
       </c>
@@ -2410,7 +2961,7 @@
         <v>21</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E24" s="1">
         <v>200010</v>
@@ -2422,7 +2973,7 @@
         <v>43400002</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I24" s="1">
         <v>1</v>
@@ -2437,7 +2988,7 @@
         <v>20</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N24" s="1">
         <v>100</v>
@@ -2449,13 +3000,13 @@
         <v>1</v>
       </c>
       <c r="Q24" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R24" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18">
       <c r="A25" s="1">
         <v>21</v>
       </c>
@@ -2466,7 +3017,7 @@
         <v>22</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="E25" s="1">
         <v>210010</v>
@@ -2478,7 +3029,7 @@
         <v>43400002</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I25" s="1">
         <v>1</v>
@@ -2493,7 +3044,7 @@
         <v>21</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N25" s="1">
         <v>100</v>
@@ -2505,13 +3056,13 @@
         <v>1</v>
       </c>
       <c r="Q25" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R25" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18">
       <c r="A26" s="1">
         <v>22</v>
       </c>
@@ -2522,7 +3073,7 @@
         <v>23</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="E26" s="1">
         <v>220010</v>
@@ -2534,7 +3085,7 @@
         <v>43400002</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I26" s="1">
         <v>1</v>
@@ -2549,7 +3100,7 @@
         <v>22</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N26" s="1">
         <v>100</v>
@@ -2561,13 +3112,13 @@
         <v>1</v>
       </c>
       <c r="Q26" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R26" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18">
       <c r="A27" s="1">
         <v>23</v>
       </c>
@@ -2578,7 +3129,7 @@
         <v>24</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="E27" s="1">
         <v>230010</v>
@@ -2590,7 +3141,7 @@
         <v>43400002</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I27" s="1">
         <v>1</v>
@@ -2605,7 +3156,7 @@
         <v>23</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N27" s="1">
         <v>100</v>
@@ -2617,13 +3168,13 @@
         <v>1</v>
       </c>
       <c r="Q27" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R27" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18">
       <c r="A28" s="1">
         <v>24</v>
       </c>
@@ -2634,7 +3185,7 @@
         <v>25</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>31</v>
+        <v>72</v>
       </c>
       <c r="E28" s="1">
         <v>240010</v>
@@ -2646,7 +3197,7 @@
         <v>43400002</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I28" s="1">
         <v>1</v>
@@ -2661,7 +3212,7 @@
         <v>24</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N28" s="1">
         <v>100</v>
@@ -2673,13 +3224,13 @@
         <v>1</v>
       </c>
       <c r="Q28" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R28" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18">
       <c r="A29" s="1">
         <v>25</v>
       </c>
@@ -2690,7 +3241,7 @@
         <v>26</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>32</v>
+        <v>73</v>
       </c>
       <c r="E29" s="1">
         <v>250010</v>
@@ -2702,7 +3253,7 @@
         <v>43400002</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I29" s="1">
         <v>1</v>
@@ -2717,7 +3268,7 @@
         <v>25</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N29" s="1">
         <v>100</v>
@@ -2729,13 +3280,13 @@
         <v>1</v>
       </c>
       <c r="Q29" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R29" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18">
       <c r="A30" s="1">
         <v>26</v>
       </c>
@@ -2746,7 +3297,7 @@
         <v>27</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>33</v>
+        <v>74</v>
       </c>
       <c r="E30" s="1">
         <v>260010</v>
@@ -2758,7 +3309,7 @@
         <v>43400002</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I30" s="1">
         <v>1</v>
@@ -2773,7 +3324,7 @@
         <v>26</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N30" s="1">
         <v>100</v>
@@ -2785,13 +3336,13 @@
         <v>1</v>
       </c>
       <c r="Q30" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R30" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18">
       <c r="A31" s="1">
         <v>27</v>
       </c>
@@ -2802,7 +3353,7 @@
         <v>28</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="E31" s="1">
         <v>270010</v>
@@ -2814,7 +3365,7 @@
         <v>43400002</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I31" s="1">
         <v>1</v>
@@ -2829,7 +3380,7 @@
         <v>27</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N31" s="1">
         <v>100</v>
@@ -2841,13 +3392,13 @@
         <v>1</v>
       </c>
       <c r="Q31" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R31" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18">
       <c r="A32" s="1">
         <v>28</v>
       </c>
@@ -2858,7 +3409,7 @@
         <v>29</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>35</v>
+        <v>76</v>
       </c>
       <c r="E32" s="1">
         <v>280010</v>
@@ -2870,7 +3421,7 @@
         <v>43400002</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I32" s="1">
         <v>1</v>
@@ -2885,7 +3436,7 @@
         <v>28</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N32" s="1">
         <v>100</v>
@@ -2897,13 +3448,13 @@
         <v>1</v>
       </c>
       <c r="Q32" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R32" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18">
       <c r="A33" s="1">
         <v>29</v>
       </c>
@@ -2914,7 +3465,7 @@
         <v>30</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="E33" s="1">
         <v>290010</v>
@@ -2926,7 +3477,7 @@
         <v>43400002</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I33" s="1">
         <v>1</v>
@@ -2941,7 +3492,7 @@
         <v>29</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N33" s="1">
         <v>100</v>
@@ -2953,13 +3504,13 @@
         <v>1</v>
       </c>
       <c r="Q33" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R33" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18">
       <c r="A34" s="1">
         <v>30</v>
       </c>
@@ -2970,7 +3521,7 @@
         <v>31</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>37</v>
+        <v>78</v>
       </c>
       <c r="E34" s="1">
         <v>300010</v>
@@ -2982,7 +3533,7 @@
         <v>43400002</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I34" s="1">
         <v>1</v>
@@ -2997,7 +3548,7 @@
         <v>30</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N34" s="1">
         <v>100</v>
@@ -3009,13 +3560,13 @@
         <v>1</v>
       </c>
       <c r="Q34" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R34" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18">
       <c r="A35" s="1">
         <v>31</v>
       </c>
@@ -3026,7 +3577,7 @@
         <v>32</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="E35" s="1">
         <v>310010</v>
@@ -3038,7 +3589,7 @@
         <v>43400002</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I35" s="1">
         <v>1</v>
@@ -3053,7 +3604,7 @@
         <v>31</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N35" s="1">
         <v>100</v>
@@ -3065,13 +3616,13 @@
         <v>1</v>
       </c>
       <c r="Q35" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R35" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18">
       <c r="A36" s="1">
         <v>32</v>
       </c>
@@ -3082,7 +3633,7 @@
         <v>33</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="E36" s="1">
         <v>320010</v>
@@ -3094,7 +3645,7 @@
         <v>43400002</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I36" s="1">
         <v>1</v>
@@ -3109,7 +3660,7 @@
         <v>32</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N36" s="1">
         <v>100</v>
@@ -3121,13 +3672,13 @@
         <v>1</v>
       </c>
       <c r="Q36" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R36" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18">
       <c r="A37" s="1">
         <v>33</v>
       </c>
@@ -3138,7 +3689,7 @@
         <v>34</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="E37" s="1">
         <v>330010</v>
@@ -3150,7 +3701,7 @@
         <v>43400002</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I37" s="1">
         <v>1</v>
@@ -3165,7 +3716,7 @@
         <v>33</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N37" s="1">
         <v>100</v>
@@ -3177,13 +3728,13 @@
         <v>1</v>
       </c>
       <c r="Q37" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R37" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18">
       <c r="A38" s="1">
         <v>34</v>
       </c>
@@ -3194,7 +3745,7 @@
         <v>35</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="E38" s="1">
         <v>340010</v>
@@ -3206,7 +3757,7 @@
         <v>43400002</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I38" s="1">
         <v>1</v>
@@ -3221,7 +3772,7 @@
         <v>34</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N38" s="1">
         <v>100</v>
@@ -3233,13 +3784,13 @@
         <v>1</v>
       </c>
       <c r="Q38" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R38" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18">
       <c r="A39" s="1">
         <v>35</v>
       </c>
@@ -3250,7 +3801,7 @@
         <v>36</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="E39" s="1">
         <v>350010</v>
@@ -3262,7 +3813,7 @@
         <v>43400002</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I39" s="1">
         <v>1</v>
@@ -3277,7 +3828,7 @@
         <v>35</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N39" s="1">
         <v>100</v>
@@ -3289,13 +3840,13 @@
         <v>1</v>
       </c>
       <c r="Q39" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R39" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18">
       <c r="A40" s="1">
         <v>36</v>
       </c>
@@ -3306,7 +3857,7 @@
         <v>37</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="E40" s="1">
         <v>360010</v>
@@ -3318,7 +3869,7 @@
         <v>43400002</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I40" s="1">
         <v>1</v>
@@ -3333,7 +3884,7 @@
         <v>36</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N40" s="1">
         <v>100</v>
@@ -3345,13 +3896,13 @@
         <v>1</v>
       </c>
       <c r="Q40" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R40" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18">
       <c r="A41" s="1">
         <v>37</v>
       </c>
@@ -3362,7 +3913,7 @@
         <v>38</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="E41" s="1">
         <v>370010</v>
@@ -3374,7 +3925,7 @@
         <v>43400002</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I41" s="1">
         <v>1</v>
@@ -3389,7 +3940,7 @@
         <v>37</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N41" s="1">
         <v>100</v>
@@ -3401,13 +3952,13 @@
         <v>1</v>
       </c>
       <c r="Q41" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R41" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18">
       <c r="A42" s="1">
         <v>38</v>
       </c>
@@ -3418,7 +3969,7 @@
         <v>39</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="E42" s="1">
         <v>380010</v>
@@ -3430,7 +3981,7 @@
         <v>43400002</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I42" s="1">
         <v>1</v>
@@ -3445,7 +3996,7 @@
         <v>38</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N42" s="1">
         <v>100</v>
@@ -3457,13 +4008,13 @@
         <v>1</v>
       </c>
       <c r="Q42" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R42" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18">
       <c r="A43" s="1">
         <v>39</v>
       </c>
@@ -3474,7 +4025,7 @@
         <v>40</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="E43" s="1">
         <v>390010</v>
@@ -3486,7 +4037,7 @@
         <v>43400002</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I43" s="1">
         <v>1</v>
@@ -3501,7 +4052,7 @@
         <v>39</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N43" s="1">
         <v>100</v>
@@ -3513,13 +4064,13 @@
         <v>1</v>
       </c>
       <c r="Q43" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R43" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18">
       <c r="A44" s="1">
         <v>40</v>
       </c>
@@ -3530,7 +4081,7 @@
         <v>41</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="E44" s="1">
         <v>400010</v>
@@ -3542,7 +4093,7 @@
         <v>43400002</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I44" s="1">
         <v>1</v>
@@ -3557,7 +4108,7 @@
         <v>40</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N44" s="1">
         <v>100</v>
@@ -3569,13 +4120,13 @@
         <v>1</v>
       </c>
       <c r="Q44" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R44" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18">
       <c r="A45" s="1">
         <v>41</v>
       </c>
@@ -3586,7 +4137,7 @@
         <v>42</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="E45" s="1">
         <v>410010</v>
@@ -3598,7 +4149,7 @@
         <v>43400002</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I45" s="1">
         <v>1</v>
@@ -3613,7 +4164,7 @@
         <v>41</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N45" s="1">
         <v>100</v>
@@ -3625,13 +4176,13 @@
         <v>1</v>
       </c>
       <c r="Q45" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R45" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18">
       <c r="A46" s="1">
         <v>42</v>
       </c>
@@ -3642,7 +4193,7 @@
         <v>43</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="E46" s="1">
         <v>420010</v>
@@ -3654,7 +4205,7 @@
         <v>43400002</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I46" s="1">
         <v>1</v>
@@ -3669,7 +4220,7 @@
         <v>42</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N46" s="1">
         <v>100</v>
@@ -3681,13 +4232,13 @@
         <v>1</v>
       </c>
       <c r="Q46" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R46" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18">
       <c r="A47" s="1">
         <v>43</v>
       </c>
@@ -3698,7 +4249,7 @@
         <v>44</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="E47" s="1">
         <v>430010</v>
@@ -3710,7 +4261,7 @@
         <v>43400002</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I47" s="1">
         <v>1</v>
@@ -3725,7 +4276,7 @@
         <v>43</v>
       </c>
       <c r="M47" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N47" s="1">
         <v>100</v>
@@ -3737,13 +4288,13 @@
         <v>1</v>
       </c>
       <c r="Q47" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R47" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18">
       <c r="A48" s="1">
         <v>44</v>
       </c>
@@ -3754,7 +4305,7 @@
         <v>45</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="E48" s="1">
         <v>440010</v>
@@ -3766,7 +4317,7 @@
         <v>43400002</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I48" s="1">
         <v>1</v>
@@ -3781,7 +4332,7 @@
         <v>44</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N48" s="1">
         <v>100</v>
@@ -3793,13 +4344,13 @@
         <v>1</v>
       </c>
       <c r="Q48" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R48" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18">
       <c r="A49" s="1">
         <v>45</v>
       </c>
@@ -3810,7 +4361,7 @@
         <v>46</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="E49" s="1">
         <v>450010</v>
@@ -3822,7 +4373,7 @@
         <v>43400002</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I49" s="1">
         <v>1</v>
@@ -3837,7 +4388,7 @@
         <v>45</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N49" s="1">
         <v>100</v>
@@ -3849,13 +4400,13 @@
         <v>1</v>
       </c>
       <c r="Q49" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R49" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18">
       <c r="A50" s="1">
         <v>46</v>
       </c>
@@ -3866,7 +4417,7 @@
         <v>47</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="E50" s="1">
         <v>460010</v>
@@ -3878,7 +4429,7 @@
         <v>43400002</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I50" s="1">
         <v>1</v>
@@ -3893,7 +4444,7 @@
         <v>46</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N50" s="1">
         <v>100</v>
@@ -3905,13 +4456,13 @@
         <v>1</v>
       </c>
       <c r="Q50" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R50" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18">
       <c r="A51" s="1">
         <v>47</v>
       </c>
@@ -3922,7 +4473,7 @@
         <v>48</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="E51" s="1">
         <v>470010</v>
@@ -3934,7 +4485,7 @@
         <v>43400002</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I51" s="1">
         <v>1</v>
@@ -3949,7 +4500,7 @@
         <v>47</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N51" s="1">
         <v>100</v>
@@ -3961,13 +4512,13 @@
         <v>1</v>
       </c>
       <c r="Q51" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R51" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18">
       <c r="A52" s="1">
         <v>48</v>
       </c>
@@ -3978,7 +4529,7 @@
         <v>49</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="E52" s="1">
         <v>480010</v>
@@ -3990,7 +4541,7 @@
         <v>43400002</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I52" s="1">
         <v>1</v>
@@ -4005,7 +4556,7 @@
         <v>48</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N52" s="1">
         <v>100</v>
@@ -4017,13 +4568,13 @@
         <v>1</v>
       </c>
       <c r="Q52" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R52" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18">
       <c r="A53" s="1">
         <v>49</v>
       </c>
@@ -4034,7 +4585,7 @@
         <v>50</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="E53" s="1">
         <v>490010</v>
@@ -4046,7 +4597,7 @@
         <v>43400002</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I53" s="1">
         <v>1</v>
@@ -4061,7 +4612,7 @@
         <v>49</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N53" s="1">
         <v>100</v>
@@ -4073,13 +4624,13 @@
         <v>1</v>
       </c>
       <c r="Q53" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R53" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18">
       <c r="A54" s="1">
         <v>50</v>
       </c>
@@ -4090,7 +4641,7 @@
         <v>51</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="E54" s="1">
         <v>500010</v>
@@ -4102,7 +4653,7 @@
         <v>43400002</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I54" s="1">
         <v>1</v>
@@ -4117,7 +4668,7 @@
         <v>50</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N54" s="1">
         <v>100</v>
@@ -4129,13 +4680,13 @@
         <v>1</v>
       </c>
       <c r="Q54" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R54" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18">
       <c r="A55" s="1">
         <v>51</v>
       </c>
@@ -4146,7 +4697,7 @@
         <v>52</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="E55" s="1">
         <v>510010</v>
@@ -4158,7 +4709,7 @@
         <v>43400002</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I55" s="1">
         <v>1</v>
@@ -4173,7 +4724,7 @@
         <v>51</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N55" s="1">
         <v>100</v>
@@ -4185,13 +4736,13 @@
         <v>1</v>
       </c>
       <c r="Q55" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R55" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18">
       <c r="A56" s="1">
         <v>52</v>
       </c>
@@ -4202,7 +4753,7 @@
         <v>53</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="E56" s="1">
         <v>520010</v>
@@ -4214,7 +4765,7 @@
         <v>43400002</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I56" s="1">
         <v>1</v>
@@ -4229,7 +4780,7 @@
         <v>52</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N56" s="1">
         <v>100</v>
@@ -4241,13 +4792,13 @@
         <v>1</v>
       </c>
       <c r="Q56" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R56" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="57" spans="1:18">
       <c r="A57" s="1">
         <v>53</v>
       </c>
@@ -4258,7 +4809,7 @@
         <v>54</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="E57" s="1">
         <v>530010</v>
@@ -4270,7 +4821,7 @@
         <v>43400002</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I57" s="1">
         <v>1</v>
@@ -4285,7 +4836,7 @@
         <v>53</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N57" s="1">
         <v>100</v>
@@ -4297,13 +4848,13 @@
         <v>1</v>
       </c>
       <c r="Q57" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R57" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18">
       <c r="A58" s="1">
         <v>54</v>
       </c>
@@ -4314,7 +4865,7 @@
         <v>55</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="E58" s="1">
         <v>540010</v>
@@ -4326,7 +4877,7 @@
         <v>43400002</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I58" s="1">
         <v>1</v>
@@ -4341,7 +4892,7 @@
         <v>54</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N58" s="1">
         <v>100</v>
@@ -4353,13 +4904,13 @@
         <v>1</v>
       </c>
       <c r="Q58" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R58" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="59" spans="1:18">
       <c r="A59" s="1">
         <v>55</v>
       </c>
@@ -4370,7 +4921,7 @@
         <v>56</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="E59" s="1">
         <v>550010</v>
@@ -4382,7 +4933,7 @@
         <v>43400002</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I59" s="1">
         <v>1</v>
@@ -4397,7 +4948,7 @@
         <v>55</v>
       </c>
       <c r="M59" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N59" s="1">
         <v>100</v>
@@ -4409,13 +4960,13 @@
         <v>1</v>
       </c>
       <c r="Q59" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R59" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18">
       <c r="A60" s="1">
         <v>56</v>
       </c>
@@ -4426,7 +4977,7 @@
         <v>57</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="E60" s="1">
         <v>560010</v>
@@ -4438,7 +4989,7 @@
         <v>43400002</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I60" s="1">
         <v>1</v>
@@ -4453,7 +5004,7 @@
         <v>56</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N60" s="1">
         <v>100</v>
@@ -4465,13 +5016,13 @@
         <v>1</v>
       </c>
       <c r="Q60" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R60" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18">
       <c r="A61" s="1">
         <v>57</v>
       </c>
@@ -4482,7 +5033,7 @@
         <v>58</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="E61" s="1">
         <v>570010</v>
@@ -4494,7 +5045,7 @@
         <v>43400002</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I61" s="1">
         <v>1</v>
@@ -4509,7 +5060,7 @@
         <v>57</v>
       </c>
       <c r="M61" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N61" s="1">
         <v>100</v>
@@ -4521,13 +5072,13 @@
         <v>1</v>
       </c>
       <c r="Q61" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R61" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18">
       <c r="A62" s="1">
         <v>58</v>
       </c>
@@ -4538,7 +5089,7 @@
         <v>59</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="E62" s="1">
         <v>580010</v>
@@ -4550,7 +5101,7 @@
         <v>43400002</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I62" s="1">
         <v>1</v>
@@ -4565,7 +5116,7 @@
         <v>58</v>
       </c>
       <c r="M62" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N62" s="1">
         <v>100</v>
@@ -4577,13 +5128,13 @@
         <v>1</v>
       </c>
       <c r="Q62" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R62" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18">
       <c r="A63" s="1">
         <v>59</v>
       </c>
@@ -4594,7 +5145,7 @@
         <v>60</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="E63" s="1">
         <v>590010</v>
@@ -4606,7 +5157,7 @@
         <v>43400002</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I63" s="1">
         <v>1</v>
@@ -4621,7 +5172,7 @@
         <v>59</v>
       </c>
       <c r="M63" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N63" s="1">
         <v>100</v>
@@ -4633,13 +5184,13 @@
         <v>1</v>
       </c>
       <c r="Q63" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R63" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="64" spans="1:18">
       <c r="A64" s="1">
         <v>60</v>
       </c>
@@ -4650,7 +5201,7 @@
         <v>61</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="E64" s="1">
         <v>600010</v>
@@ -4662,7 +5213,7 @@
         <v>43400002</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I64" s="1">
         <v>1</v>
@@ -4677,7 +5228,7 @@
         <v>60</v>
       </c>
       <c r="M64" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N64" s="1">
         <v>100</v>
@@ -4689,13 +5240,13 @@
         <v>1</v>
       </c>
       <c r="Q64" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R64" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="65" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="65" spans="1:18">
       <c r="A65" s="1">
         <v>61</v>
       </c>
@@ -4706,7 +5257,7 @@
         <v>62</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="E65" s="1">
         <v>610010</v>
@@ -4718,7 +5269,7 @@
         <v>43400002</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I65" s="1">
         <v>1</v>
@@ -4733,7 +5284,7 @@
         <v>61</v>
       </c>
       <c r="M65" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N65" s="1">
         <v>100</v>
@@ -4745,13 +5296,13 @@
         <v>1</v>
       </c>
       <c r="Q65" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R65" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="66" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="66" spans="1:18">
       <c r="A66" s="1">
         <v>62</v>
       </c>
@@ -4762,7 +5313,7 @@
         <v>63</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="E66" s="1">
         <v>620010</v>
@@ -4774,7 +5325,7 @@
         <v>43400002</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I66" s="1">
         <v>1</v>
@@ -4789,7 +5340,7 @@
         <v>62</v>
       </c>
       <c r="M66" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N66" s="1">
         <v>100</v>
@@ -4801,13 +5352,13 @@
         <v>1</v>
       </c>
       <c r="Q66" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R66" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="67" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="67" spans="1:18">
       <c r="A67" s="1">
         <v>63</v>
       </c>
@@ -4818,7 +5369,7 @@
         <v>64</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="E67" s="1">
         <v>630010</v>
@@ -4830,7 +5381,7 @@
         <v>43400002</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I67" s="1">
         <v>1</v>
@@ -4845,7 +5396,7 @@
         <v>63</v>
       </c>
       <c r="M67" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N67" s="1">
         <v>100</v>
@@ -4857,13 +5408,13 @@
         <v>1</v>
       </c>
       <c r="Q67" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R67" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="68" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="68" spans="1:18">
       <c r="A68" s="1">
         <v>64</v>
       </c>
@@ -4874,7 +5425,7 @@
         <v>65</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="E68" s="1">
         <v>640010</v>
@@ -4886,7 +5437,7 @@
         <v>43400002</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I68" s="1">
         <v>1</v>
@@ -4901,7 +5452,7 @@
         <v>64</v>
       </c>
       <c r="M68" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N68" s="1">
         <v>100</v>
@@ -4913,13 +5464,13 @@
         <v>1</v>
       </c>
       <c r="Q68" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R68" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="69" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="69" spans="1:18">
       <c r="A69" s="1">
         <v>65</v>
       </c>
@@ -4930,7 +5481,7 @@
         <v>66</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="E69" s="1">
         <v>650010</v>
@@ -4942,7 +5493,7 @@
         <v>43400002</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I69" s="1">
         <v>1</v>
@@ -4957,7 +5508,7 @@
         <v>65</v>
       </c>
       <c r="M69" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N69" s="1">
         <v>100</v>
@@ -4969,13 +5520,13 @@
         <v>1</v>
       </c>
       <c r="Q69" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R69" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="70" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="70" spans="1:18">
       <c r="A70" s="1">
         <v>66</v>
       </c>
@@ -4986,7 +5537,7 @@
         <v>67</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="E70" s="1">
         <v>660010</v>
@@ -4998,7 +5549,7 @@
         <v>43400002</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I70" s="1">
         <v>1</v>
@@ -5013,7 +5564,7 @@
         <v>66</v>
       </c>
       <c r="M70" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N70" s="1">
         <v>100</v>
@@ -5025,13 +5576,13 @@
         <v>1</v>
       </c>
       <c r="Q70" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R70" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="71" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="71" spans="1:18">
       <c r="A71" s="1">
         <v>67</v>
       </c>
@@ -5042,7 +5593,7 @@
         <v>68</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="E71" s="1">
         <v>670010</v>
@@ -5054,7 +5605,7 @@
         <v>43400002</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I71" s="1">
         <v>1</v>
@@ -5069,7 +5620,7 @@
         <v>67</v>
       </c>
       <c r="M71" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N71" s="1">
         <v>100</v>
@@ -5081,13 +5632,13 @@
         <v>1</v>
       </c>
       <c r="Q71" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R71" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="72" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="72" spans="1:18">
       <c r="A72" s="1">
         <v>68</v>
       </c>
@@ -5098,7 +5649,7 @@
         <v>69</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="E72" s="1">
         <v>680010</v>
@@ -5110,7 +5661,7 @@
         <v>43400002</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I72" s="1">
         <v>1</v>
@@ -5125,7 +5676,7 @@
         <v>68</v>
       </c>
       <c r="M72" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N72" s="1">
         <v>100</v>
@@ -5137,13 +5688,13 @@
         <v>1</v>
       </c>
       <c r="Q72" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R72" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="73" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="73" spans="1:18">
       <c r="A73" s="1">
         <v>69</v>
       </c>
@@ -5154,7 +5705,7 @@
         <v>70</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="E73" s="1">
         <v>690010</v>
@@ -5166,7 +5717,7 @@
         <v>43400002</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I73" s="1">
         <v>1</v>
@@ -5181,7 +5732,7 @@
         <v>69</v>
       </c>
       <c r="M73" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N73" s="1">
         <v>100</v>
@@ -5193,13 +5744,13 @@
         <v>1</v>
       </c>
       <c r="Q73" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R73" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="74" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="74" spans="1:18">
       <c r="A74" s="1">
         <v>70</v>
       </c>
@@ -5210,7 +5761,7 @@
         <v>71</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="E74" s="1">
         <v>700010</v>
@@ -5222,7 +5773,7 @@
         <v>43400002</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I74" s="1">
         <v>1</v>
@@ -5237,7 +5788,7 @@
         <v>70</v>
       </c>
       <c r="M74" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N74" s="1">
         <v>100</v>
@@ -5249,13 +5800,13 @@
         <v>1</v>
       </c>
       <c r="Q74" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R74" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="75" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="75" spans="1:18">
       <c r="A75" s="1">
         <v>71</v>
       </c>
@@ -5266,7 +5817,7 @@
         <v>72</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="E75" s="1">
         <v>710010</v>
@@ -5278,7 +5829,7 @@
         <v>43400002</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I75" s="1">
         <v>1</v>
@@ -5293,7 +5844,7 @@
         <v>71</v>
       </c>
       <c r="M75" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N75" s="1">
         <v>100</v>
@@ -5305,13 +5856,13 @@
         <v>1</v>
       </c>
       <c r="Q75" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R75" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="76" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="76" spans="1:18">
       <c r="A76" s="1">
         <v>72</v>
       </c>
@@ -5322,7 +5873,7 @@
         <v>73</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="E76" s="1">
         <v>720010</v>
@@ -5334,7 +5885,7 @@
         <v>43400002</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I76" s="1">
         <v>1</v>
@@ -5349,7 +5900,7 @@
         <v>72</v>
       </c>
       <c r="M76" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N76" s="1">
         <v>100</v>
@@ -5361,13 +5912,13 @@
         <v>1</v>
       </c>
       <c r="Q76" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R76" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="77" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="77" spans="1:18">
       <c r="A77" s="1">
         <v>73</v>
       </c>
@@ -5378,7 +5929,7 @@
         <v>74</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="E77" s="1">
         <v>730010</v>
@@ -5390,7 +5941,7 @@
         <v>43400002</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I77" s="1">
         <v>1</v>
@@ -5405,7 +5956,7 @@
         <v>73</v>
       </c>
       <c r="M77" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N77" s="1">
         <v>100</v>
@@ -5417,13 +5968,13 @@
         <v>1</v>
       </c>
       <c r="Q77" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R77" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="78" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="78" spans="1:18">
       <c r="A78" s="1">
         <v>74</v>
       </c>
@@ -5434,7 +5985,7 @@
         <v>75</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="E78" s="1">
         <v>740010</v>
@@ -5446,7 +5997,7 @@
         <v>43400002</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I78" s="1">
         <v>1</v>
@@ -5461,7 +6012,7 @@
         <v>74</v>
       </c>
       <c r="M78" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N78" s="1">
         <v>100</v>
@@ -5473,13 +6024,13 @@
         <v>1</v>
       </c>
       <c r="Q78" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R78" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="79" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="79" spans="1:18">
       <c r="A79" s="1">
         <v>75</v>
       </c>
@@ -5490,7 +6041,7 @@
         <v>76</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="E79" s="1">
         <v>750010</v>
@@ -5502,7 +6053,7 @@
         <v>43400002</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I79" s="1">
         <v>1</v>
@@ -5517,7 +6068,7 @@
         <v>75</v>
       </c>
       <c r="M79" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N79" s="1">
         <v>100</v>
@@ -5529,13 +6080,13 @@
         <v>1</v>
       </c>
       <c r="Q79" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R79" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="80" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="80" spans="1:18">
       <c r="A80" s="1">
         <v>76</v>
       </c>
@@ -5546,7 +6097,7 @@
         <v>77</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="E80" s="1">
         <v>760010</v>
@@ -5558,7 +6109,7 @@
         <v>43400002</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I80" s="1">
         <v>1</v>
@@ -5573,7 +6124,7 @@
         <v>76</v>
       </c>
       <c r="M80" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N80" s="1">
         <v>100</v>
@@ -5585,13 +6136,13 @@
         <v>1</v>
       </c>
       <c r="Q80" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R80" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="81" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="81" spans="1:18">
       <c r="A81" s="1">
         <v>77</v>
       </c>
@@ -5602,7 +6153,7 @@
         <v>78</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="E81" s="1">
         <v>770010</v>
@@ -5614,7 +6165,7 @@
         <v>43400002</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I81" s="1">
         <v>1</v>
@@ -5629,7 +6180,7 @@
         <v>77</v>
       </c>
       <c r="M81" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N81" s="1">
         <v>100</v>
@@ -5641,13 +6192,13 @@
         <v>1</v>
       </c>
       <c r="Q81" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R81" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="82" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="82" spans="1:18">
       <c r="A82" s="1">
         <v>78</v>
       </c>
@@ -5658,7 +6209,7 @@
         <v>79</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="E82" s="1">
         <v>780010</v>
@@ -5670,7 +6221,7 @@
         <v>43400002</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I82" s="1">
         <v>1</v>
@@ -5685,7 +6236,7 @@
         <v>78</v>
       </c>
       <c r="M82" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N82" s="1">
         <v>100</v>
@@ -5697,13 +6248,13 @@
         <v>1</v>
       </c>
       <c r="Q82" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R82" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="83" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="83" spans="1:18">
       <c r="A83" s="1">
         <v>79</v>
       </c>
@@ -5714,7 +6265,7 @@
         <v>80</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="E83" s="1">
         <v>790010</v>
@@ -5726,7 +6277,7 @@
         <v>43400002</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I83" s="1">
         <v>1</v>
@@ -5741,7 +6292,7 @@
         <v>79</v>
       </c>
       <c r="M83" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N83" s="1">
         <v>100</v>
@@ -5753,13 +6304,13 @@
         <v>1</v>
       </c>
       <c r="Q83" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R83" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="84" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="84" spans="1:18">
       <c r="A84" s="1">
         <v>80</v>
       </c>
@@ -5770,7 +6321,7 @@
         <v>81</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="E84" s="1">
         <v>800010</v>
@@ -5782,7 +6333,7 @@
         <v>43400002</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I84" s="1">
         <v>1</v>
@@ -5797,7 +6348,7 @@
         <v>80</v>
       </c>
       <c r="M84" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N84" s="1">
         <v>100</v>
@@ -5809,13 +6360,13 @@
         <v>1</v>
       </c>
       <c r="Q84" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R84" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="85" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="85" spans="1:18">
       <c r="A85" s="1">
         <v>81</v>
       </c>
@@ -5826,7 +6377,7 @@
         <v>82</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="E85" s="1">
         <v>810010</v>
@@ -5838,7 +6389,7 @@
         <v>43400002</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I85" s="1">
         <v>1</v>
@@ -5853,7 +6404,7 @@
         <v>81</v>
       </c>
       <c r="M85" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N85" s="1">
         <v>100</v>
@@ -5865,13 +6416,13 @@
         <v>1</v>
       </c>
       <c r="Q85" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R85" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="86" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="86" spans="1:18">
       <c r="A86" s="1">
         <v>82</v>
       </c>
@@ -5882,7 +6433,7 @@
         <v>83</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="E86" s="1">
         <v>820010</v>
@@ -5894,7 +6445,7 @@
         <v>43400002</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I86" s="1">
         <v>1</v>
@@ -5909,7 +6460,7 @@
         <v>82</v>
       </c>
       <c r="M86" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N86" s="1">
         <v>100</v>
@@ -5921,13 +6472,13 @@
         <v>1</v>
       </c>
       <c r="Q86" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R86" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="87" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="87" spans="1:18">
       <c r="A87" s="1">
         <v>83</v>
       </c>
@@ -5938,7 +6489,7 @@
         <v>84</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="E87" s="1">
         <v>830010</v>
@@ -5950,7 +6501,7 @@
         <v>43400002</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I87" s="1">
         <v>1</v>
@@ -5965,7 +6516,7 @@
         <v>83</v>
       </c>
       <c r="M87" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N87" s="1">
         <v>100</v>
@@ -5977,13 +6528,13 @@
         <v>1</v>
       </c>
       <c r="Q87" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R87" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="88" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="88" spans="1:18">
       <c r="A88" s="1">
         <v>84</v>
       </c>
@@ -5994,7 +6545,7 @@
         <v>85</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="E88" s="1">
         <v>840010</v>
@@ -6006,7 +6557,7 @@
         <v>43400002</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I88" s="1">
         <v>1</v>
@@ -6021,7 +6572,7 @@
         <v>84</v>
       </c>
       <c r="M88" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N88" s="1">
         <v>100</v>
@@ -6033,13 +6584,13 @@
         <v>1</v>
       </c>
       <c r="Q88" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R88" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="89" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="89" spans="1:18">
       <c r="A89" s="1">
         <v>85</v>
       </c>
@@ -6050,7 +6601,7 @@
         <v>86</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="E89" s="1">
         <v>850010</v>
@@ -6062,7 +6613,7 @@
         <v>43400002</v>
       </c>
       <c r="H89" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I89" s="1">
         <v>1</v>
@@ -6077,7 +6628,7 @@
         <v>85</v>
       </c>
       <c r="M89" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N89" s="1">
         <v>100</v>
@@ -6089,13 +6640,13 @@
         <v>1</v>
       </c>
       <c r="Q89" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R89" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="90" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="90" spans="1:18">
       <c r="A90" s="1">
         <v>86</v>
       </c>
@@ -6106,7 +6657,7 @@
         <v>87</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="E90" s="1">
         <v>860010</v>
@@ -6118,7 +6669,7 @@
         <v>43400002</v>
       </c>
       <c r="H90" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I90" s="1">
         <v>1</v>
@@ -6133,7 +6684,7 @@
         <v>86</v>
       </c>
       <c r="M90" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N90" s="1">
         <v>100</v>
@@ -6145,13 +6696,13 @@
         <v>1</v>
       </c>
       <c r="Q90" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R90" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="91" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="91" spans="1:18">
       <c r="A91" s="1">
         <v>87</v>
       </c>
@@ -6162,7 +6713,7 @@
         <v>88</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="E91" s="1">
         <v>870010</v>
@@ -6174,7 +6725,7 @@
         <v>43400002</v>
       </c>
       <c r="H91" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I91" s="1">
         <v>1</v>
@@ -6189,7 +6740,7 @@
         <v>87</v>
       </c>
       <c r="M91" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N91" s="1">
         <v>100</v>
@@ -6201,13 +6752,13 @@
         <v>1</v>
       </c>
       <c r="Q91" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R91" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="92" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="92" spans="1:18">
       <c r="A92" s="1">
         <v>88</v>
       </c>
@@ -6218,7 +6769,7 @@
         <v>89</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="E92" s="1">
         <v>880010</v>
@@ -6230,7 +6781,7 @@
         <v>43400002</v>
       </c>
       <c r="H92" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I92" s="1">
         <v>1</v>
@@ -6245,7 +6796,7 @@
         <v>88</v>
       </c>
       <c r="M92" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N92" s="1">
         <v>100</v>
@@ -6257,13 +6808,13 @@
         <v>1</v>
       </c>
       <c r="Q92" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R92" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="93" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="93" spans="1:18">
       <c r="A93" s="1">
         <v>89</v>
       </c>
@@ -6274,7 +6825,7 @@
         <v>90</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="E93" s="1">
         <v>890010</v>
@@ -6286,7 +6837,7 @@
         <v>43400002</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I93" s="1">
         <v>1</v>
@@ -6301,7 +6852,7 @@
         <v>89</v>
       </c>
       <c r="M93" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N93" s="1">
         <v>100</v>
@@ -6313,13 +6864,13 @@
         <v>1</v>
       </c>
       <c r="Q93" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R93" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="94" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="94" spans="1:18">
       <c r="A94" s="1">
         <v>90</v>
       </c>
@@ -6330,7 +6881,7 @@
         <v>91</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="E94" s="1">
         <v>900010</v>
@@ -6342,7 +6893,7 @@
         <v>43400002</v>
       </c>
       <c r="H94" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I94" s="1">
         <v>1</v>
@@ -6357,7 +6908,7 @@
         <v>90</v>
       </c>
       <c r="M94" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N94" s="1">
         <v>100</v>
@@ -6369,13 +6920,13 @@
         <v>1</v>
       </c>
       <c r="Q94" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R94" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="95" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="95" spans="1:18">
       <c r="A95" s="1">
         <v>91</v>
       </c>
@@ -6386,7 +6937,7 @@
         <v>92</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="E95" s="1">
         <v>910010</v>
@@ -6398,7 +6949,7 @@
         <v>43400002</v>
       </c>
       <c r="H95" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I95" s="1">
         <v>1</v>
@@ -6413,7 +6964,7 @@
         <v>91</v>
       </c>
       <c r="M95" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N95" s="1">
         <v>100</v>
@@ -6425,13 +6976,13 @@
         <v>1</v>
       </c>
       <c r="Q95" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R95" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="96" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="96" spans="1:18">
       <c r="A96" s="1">
         <v>92</v>
       </c>
@@ -6442,7 +6993,7 @@
         <v>93</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="E96" s="1">
         <v>920010</v>
@@ -6454,7 +7005,7 @@
         <v>43400002</v>
       </c>
       <c r="H96" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I96" s="1">
         <v>1</v>
@@ -6469,7 +7020,7 @@
         <v>92</v>
       </c>
       <c r="M96" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N96" s="1">
         <v>100</v>
@@ -6481,13 +7032,13 @@
         <v>1</v>
       </c>
       <c r="Q96" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R96" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="97" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="97" spans="1:18">
       <c r="A97" s="1">
         <v>93</v>
       </c>
@@ -6498,7 +7049,7 @@
         <v>94</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="E97" s="1">
         <v>930010</v>
@@ -6510,7 +7061,7 @@
         <v>43400002</v>
       </c>
       <c r="H97" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I97" s="1">
         <v>1</v>
@@ -6525,7 +7076,7 @@
         <v>93</v>
       </c>
       <c r="M97" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N97" s="1">
         <v>100</v>
@@ -6537,13 +7088,13 @@
         <v>1</v>
       </c>
       <c r="Q97" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R97" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="98" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="98" spans="1:18">
       <c r="A98" s="1">
         <v>94</v>
       </c>
@@ -6554,7 +7105,7 @@
         <v>95</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="E98" s="1">
         <v>940010</v>
@@ -6566,7 +7117,7 @@
         <v>43400002</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I98" s="1">
         <v>1</v>
@@ -6581,7 +7132,7 @@
         <v>94</v>
       </c>
       <c r="M98" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N98" s="1">
         <v>100</v>
@@ -6593,13 +7144,13 @@
         <v>1</v>
       </c>
       <c r="Q98" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R98" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="99" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="99" spans="1:18">
       <c r="A99" s="1">
         <v>95</v>
       </c>
@@ -6610,7 +7161,7 @@
         <v>96</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="E99" s="1">
         <v>950010</v>
@@ -6622,7 +7173,7 @@
         <v>43400002</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I99" s="1">
         <v>1</v>
@@ -6637,7 +7188,7 @@
         <v>95</v>
       </c>
       <c r="M99" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N99" s="1">
         <v>100</v>
@@ -6649,13 +7200,13 @@
         <v>1</v>
       </c>
       <c r="Q99" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R99" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="100" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="100" spans="1:18">
       <c r="A100" s="1">
         <v>96</v>
       </c>
@@ -6666,7 +7217,7 @@
         <v>97</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="E100" s="1">
         <v>960010</v>
@@ -6678,7 +7229,7 @@
         <v>43400002</v>
       </c>
       <c r="H100" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I100" s="1">
         <v>1</v>
@@ -6693,7 +7244,7 @@
         <v>96</v>
       </c>
       <c r="M100" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N100" s="1">
         <v>100</v>
@@ -6705,13 +7256,13 @@
         <v>1</v>
       </c>
       <c r="Q100" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R100" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="101" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="101" spans="1:18">
       <c r="A101" s="1">
         <v>97</v>
       </c>
@@ -6722,7 +7273,7 @@
         <v>98</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="E101" s="1">
         <v>970010</v>
@@ -6734,7 +7285,7 @@
         <v>43400002</v>
       </c>
       <c r="H101" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I101" s="1">
         <v>1</v>
@@ -6749,7 +7300,7 @@
         <v>97</v>
       </c>
       <c r="M101" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N101" s="1">
         <v>100</v>
@@ -6761,13 +7312,13 @@
         <v>1</v>
       </c>
       <c r="Q101" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R101" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="102" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="102" spans="1:18">
       <c r="A102" s="1">
         <v>98</v>
       </c>
@@ -6778,7 +7329,7 @@
         <v>99</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="E102" s="1">
         <v>980010</v>
@@ -6790,7 +7341,7 @@
         <v>43400002</v>
       </c>
       <c r="H102" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I102" s="1">
         <v>1</v>
@@ -6805,7 +7356,7 @@
         <v>98</v>
       </c>
       <c r="M102" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N102" s="1">
         <v>100</v>
@@ -6817,13 +7368,13 @@
         <v>1</v>
       </c>
       <c r="Q102" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R102" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="103" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="103" spans="1:18">
       <c r="A103" s="1">
         <v>99</v>
       </c>
@@ -6834,7 +7385,7 @@
         <v>100</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="E103" s="1">
         <v>990010</v>
@@ -6846,7 +7397,7 @@
         <v>43400002</v>
       </c>
       <c r="H103" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I103" s="1">
         <v>1</v>
@@ -6861,7 +7412,7 @@
         <v>99</v>
       </c>
       <c r="M103" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N103" s="1">
         <v>100</v>
@@ -6873,13 +7424,13 @@
         <v>1</v>
       </c>
       <c r="Q103" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R103" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="104" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="104" spans="1:18">
       <c r="A104" s="1">
         <v>100</v>
       </c>
@@ -6890,7 +7441,7 @@
         <v>101</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="E104" s="1">
         <v>1000010</v>
@@ -6902,7 +7453,7 @@
         <v>43400002</v>
       </c>
       <c r="H104" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I104" s="1">
         <v>1</v>
@@ -6917,7 +7468,7 @@
         <v>100</v>
       </c>
       <c r="M104" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N104" s="1">
         <v>100</v>
@@ -6929,13 +7480,13 @@
         <v>1</v>
       </c>
       <c r="Q104" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R104" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="105" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="105" spans="1:18">
       <c r="A105" s="1">
         <v>101</v>
       </c>
@@ -6946,7 +7497,7 @@
         <v>102</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="E105" s="1">
         <v>1010010</v>
@@ -6958,7 +7509,7 @@
         <v>43400002</v>
       </c>
       <c r="H105" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I105" s="1">
         <v>1</v>
@@ -6973,7 +7524,7 @@
         <v>101</v>
       </c>
       <c r="M105" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N105" s="1">
         <v>100</v>
@@ -6985,13 +7536,13 @@
         <v>1</v>
       </c>
       <c r="Q105" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R105" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="106" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="106" spans="1:18">
       <c r="A106" s="1">
         <v>102</v>
       </c>
@@ -7002,7 +7553,7 @@
         <v>103</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="E106" s="1">
         <v>1020010</v>
@@ -7014,7 +7565,7 @@
         <v>43400002</v>
       </c>
       <c r="H106" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I106" s="1">
         <v>1</v>
@@ -7029,7 +7580,7 @@
         <v>102</v>
       </c>
       <c r="M106" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N106" s="1">
         <v>100</v>
@@ -7041,13 +7592,13 @@
         <v>1</v>
       </c>
       <c r="Q106" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R106" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="107" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="107" spans="1:18">
       <c r="A107" s="1">
         <v>103</v>
       </c>
@@ -7058,7 +7609,7 @@
         <v>104</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="E107" s="1">
         <v>1030010</v>
@@ -7070,7 +7621,7 @@
         <v>43400002</v>
       </c>
       <c r="H107" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I107" s="1">
         <v>1</v>
@@ -7085,7 +7636,7 @@
         <v>103</v>
       </c>
       <c r="M107" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N107" s="1">
         <v>100</v>
@@ -7097,13 +7648,13 @@
         <v>1</v>
       </c>
       <c r="Q107" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R107" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="108" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="108" spans="1:18">
       <c r="A108" s="1">
         <v>104</v>
       </c>
@@ -7114,7 +7665,7 @@
         <v>105</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="E108" s="1">
         <v>1040010</v>
@@ -7126,7 +7677,7 @@
         <v>43400002</v>
       </c>
       <c r="H108" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I108" s="1">
         <v>1</v>
@@ -7141,7 +7692,7 @@
         <v>104</v>
       </c>
       <c r="M108" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N108" s="1">
         <v>100</v>
@@ -7153,13 +7704,13 @@
         <v>1</v>
       </c>
       <c r="Q108" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R108" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="109" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="109" spans="1:18">
       <c r="A109" s="1">
         <v>105</v>
       </c>
@@ -7170,7 +7721,7 @@
         <v>106</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="E109" s="1">
         <v>1050010</v>
@@ -7182,7 +7733,7 @@
         <v>43400002</v>
       </c>
       <c r="H109" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I109" s="1">
         <v>1</v>
@@ -7197,7 +7748,7 @@
         <v>105</v>
       </c>
       <c r="M109" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N109" s="1">
         <v>100</v>
@@ -7209,13 +7760,13 @@
         <v>1</v>
       </c>
       <c r="Q109" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R109" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="110" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="110" spans="1:18">
       <c r="A110" s="1">
         <v>106</v>
       </c>
@@ -7226,7 +7777,7 @@
         <v>107</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="E110" s="1">
         <v>1060010</v>
@@ -7238,7 +7789,7 @@
         <v>43400002</v>
       </c>
       <c r="H110" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I110" s="1">
         <v>1</v>
@@ -7253,7 +7804,7 @@
         <v>106</v>
       </c>
       <c r="M110" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N110" s="1">
         <v>100</v>
@@ -7265,13 +7816,13 @@
         <v>1</v>
       </c>
       <c r="Q110" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R110" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="111" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="111" spans="1:18">
       <c r="A111" s="1">
         <v>107</v>
       </c>
@@ -7282,7 +7833,7 @@
         <v>108</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="E111" s="1">
         <v>1070010</v>
@@ -7294,7 +7845,7 @@
         <v>43400002</v>
       </c>
       <c r="H111" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I111" s="1">
         <v>1</v>
@@ -7309,7 +7860,7 @@
         <v>107</v>
       </c>
       <c r="M111" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N111" s="1">
         <v>100</v>
@@ -7321,13 +7872,13 @@
         <v>1</v>
       </c>
       <c r="Q111" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R111" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="112" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="112" spans="1:18">
       <c r="A112" s="1">
         <v>108</v>
       </c>
@@ -7338,7 +7889,7 @@
         <v>109</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="E112" s="1">
         <v>1080010</v>
@@ -7350,7 +7901,7 @@
         <v>43400002</v>
       </c>
       <c r="H112" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I112" s="1">
         <v>1</v>
@@ -7365,7 +7916,7 @@
         <v>108</v>
       </c>
       <c r="M112" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N112" s="1">
         <v>100</v>
@@ -7377,13 +7928,13 @@
         <v>1</v>
       </c>
       <c r="Q112" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R112" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="113" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="113" spans="1:18">
       <c r="A113" s="1">
         <v>109</v>
       </c>
@@ -7394,7 +7945,7 @@
         <v>110</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="E113" s="1">
         <v>1090010</v>
@@ -7406,7 +7957,7 @@
         <v>43400002</v>
       </c>
       <c r="H113" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I113" s="1">
         <v>1</v>
@@ -7421,7 +7972,7 @@
         <v>109</v>
       </c>
       <c r="M113" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N113" s="1">
         <v>100</v>
@@ -7433,13 +7984,13 @@
         <v>1</v>
       </c>
       <c r="Q113" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R113" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="114" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="114" spans="1:18">
       <c r="A114" s="1">
         <v>110</v>
       </c>
@@ -7450,7 +8001,7 @@
         <v>111</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="E114" s="1">
         <v>1100010</v>
@@ -7462,7 +8013,7 @@
         <v>43400002</v>
       </c>
       <c r="H114" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I114" s="1">
         <v>1</v>
@@ -7477,7 +8028,7 @@
         <v>110</v>
       </c>
       <c r="M114" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N114" s="1">
         <v>100</v>
@@ -7489,13 +8040,13 @@
         <v>1</v>
       </c>
       <c r="Q114" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R114" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="115" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="115" spans="1:18">
       <c r="A115" s="1">
         <v>111</v>
       </c>
@@ -7506,7 +8057,7 @@
         <v>112</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="E115" s="1">
         <v>1110010</v>
@@ -7518,7 +8069,7 @@
         <v>43400002</v>
       </c>
       <c r="H115" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I115" s="1">
         <v>1</v>
@@ -7533,7 +8084,7 @@
         <v>111</v>
       </c>
       <c r="M115" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N115" s="1">
         <v>100</v>
@@ -7545,13 +8096,13 @@
         <v>1</v>
       </c>
       <c r="Q115" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R115" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="116" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="116" spans="1:18">
       <c r="A116" s="1">
         <v>112</v>
       </c>
@@ -7562,7 +8113,7 @@
         <v>113</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="E116" s="1">
         <v>1120010</v>
@@ -7574,7 +8125,7 @@
         <v>43400002</v>
       </c>
       <c r="H116" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I116" s="1">
         <v>1</v>
@@ -7589,7 +8140,7 @@
         <v>112</v>
       </c>
       <c r="M116" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N116" s="1">
         <v>100</v>
@@ -7601,13 +8152,13 @@
         <v>1</v>
       </c>
       <c r="Q116" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R116" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="117" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="117" spans="1:18">
       <c r="A117" s="1">
         <v>113</v>
       </c>
@@ -7618,7 +8169,7 @@
         <v>114</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="E117" s="1">
         <v>1130010</v>
@@ -7630,7 +8181,7 @@
         <v>43400002</v>
       </c>
       <c r="H117" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I117" s="1">
         <v>1</v>
@@ -7645,7 +8196,7 @@
         <v>113</v>
       </c>
       <c r="M117" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N117" s="1">
         <v>100</v>
@@ -7657,13 +8208,13 @@
         <v>1</v>
       </c>
       <c r="Q117" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R117" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="118" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="118" spans="1:18">
       <c r="A118" s="1">
         <v>114</v>
       </c>
@@ -7674,7 +8225,7 @@
         <v>115</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="E118" s="1">
         <v>1140010</v>
@@ -7686,7 +8237,7 @@
         <v>43400002</v>
       </c>
       <c r="H118" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I118" s="1">
         <v>1</v>
@@ -7701,7 +8252,7 @@
         <v>114</v>
       </c>
       <c r="M118" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N118" s="1">
         <v>100</v>
@@ -7713,13 +8264,13 @@
         <v>1</v>
       </c>
       <c r="Q118" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R118" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="119" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="119" spans="1:18">
       <c r="A119" s="1">
         <v>115</v>
       </c>
@@ -7730,7 +8281,7 @@
         <v>116</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="E119" s="1">
         <v>1150010</v>
@@ -7742,7 +8293,7 @@
         <v>43400002</v>
       </c>
       <c r="H119" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I119" s="1">
         <v>1</v>
@@ -7757,7 +8308,7 @@
         <v>115</v>
       </c>
       <c r="M119" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N119" s="1">
         <v>100</v>
@@ -7769,13 +8320,13 @@
         <v>1</v>
       </c>
       <c r="Q119" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R119" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="120" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="120" spans="1:18">
       <c r="A120" s="1">
         <v>116</v>
       </c>
@@ -7786,7 +8337,7 @@
         <v>117</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="E120" s="1">
         <v>1160010</v>
@@ -7798,7 +8349,7 @@
         <v>43400002</v>
       </c>
       <c r="H120" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I120" s="1">
         <v>1</v>
@@ -7813,7 +8364,7 @@
         <v>116</v>
       </c>
       <c r="M120" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N120" s="1">
         <v>100</v>
@@ -7825,13 +8376,13 @@
         <v>1</v>
       </c>
       <c r="Q120" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R120" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="121" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="121" spans="1:18">
       <c r="A121" s="1">
         <v>117</v>
       </c>
@@ -7842,7 +8393,7 @@
         <v>118</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="E121" s="1">
         <v>1170010</v>
@@ -7854,7 +8405,7 @@
         <v>43400002</v>
       </c>
       <c r="H121" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I121" s="1">
         <v>1</v>
@@ -7869,7 +8420,7 @@
         <v>117</v>
       </c>
       <c r="M121" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N121" s="1">
         <v>100</v>
@@ -7881,13 +8432,13 @@
         <v>1</v>
       </c>
       <c r="Q121" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R121" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="122" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="122" spans="1:18">
       <c r="A122" s="1">
         <v>118</v>
       </c>
@@ -7898,7 +8449,7 @@
         <v>119</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="E122" s="1">
         <v>1180010</v>
@@ -7910,7 +8461,7 @@
         <v>43400002</v>
       </c>
       <c r="H122" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I122" s="1">
         <v>1</v>
@@ -7925,7 +8476,7 @@
         <v>118</v>
       </c>
       <c r="M122" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N122" s="1">
         <v>100</v>
@@ -7937,13 +8488,13 @@
         <v>1</v>
       </c>
       <c r="Q122" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R122" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="123" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="123" spans="1:18">
       <c r="A123" s="1">
         <v>119</v>
       </c>
@@ -7954,7 +8505,7 @@
         <v>120</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="E123" s="1">
         <v>1190010</v>
@@ -7966,7 +8517,7 @@
         <v>43400002</v>
       </c>
       <c r="H123" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I123" s="1">
         <v>1</v>
@@ -7981,7 +8532,7 @@
         <v>119</v>
       </c>
       <c r="M123" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N123" s="1">
         <v>100</v>
@@ -7993,13 +8544,13 @@
         <v>1</v>
       </c>
       <c r="Q123" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R123" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="124" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="124" spans="1:18">
       <c r="A124" s="1">
         <v>120</v>
       </c>
@@ -8010,7 +8561,7 @@
         <v>121</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="E124" s="1">
         <v>1200010</v>
@@ -8022,7 +8573,7 @@
         <v>43400002</v>
       </c>
       <c r="H124" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I124" s="1">
         <v>1</v>
@@ -8037,7 +8588,7 @@
         <v>120</v>
       </c>
       <c r="M124" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N124" s="1">
         <v>100</v>
@@ -8049,13 +8600,13 @@
         <v>1</v>
       </c>
       <c r="Q124" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R124" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="125" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="125" spans="1:18">
       <c r="A125" s="1">
         <v>121</v>
       </c>
@@ -8066,7 +8617,7 @@
         <v>122</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="E125" s="1">
         <v>1210010</v>
@@ -8078,7 +8629,7 @@
         <v>43400002</v>
       </c>
       <c r="H125" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I125" s="1">
         <v>1</v>
@@ -8093,7 +8644,7 @@
         <v>121</v>
       </c>
       <c r="M125" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N125" s="1">
         <v>100</v>
@@ -8105,13 +8656,13 @@
         <v>1</v>
       </c>
       <c r="Q125" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R125" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="126" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="126" spans="1:18">
       <c r="A126" s="1">
         <v>122</v>
       </c>
@@ -8122,7 +8673,7 @@
         <v>123</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="E126" s="1">
         <v>1220010</v>
@@ -8134,7 +8685,7 @@
         <v>43400002</v>
       </c>
       <c r="H126" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I126" s="1">
         <v>1</v>
@@ -8149,7 +8700,7 @@
         <v>122</v>
       </c>
       <c r="M126" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N126" s="1">
         <v>100</v>
@@ -8161,13 +8712,13 @@
         <v>1</v>
       </c>
       <c r="Q126" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R126" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="127" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="127" spans="1:18">
       <c r="A127" s="1">
         <v>123</v>
       </c>
@@ -8178,7 +8729,7 @@
         <v>124</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="E127" s="1">
         <v>1230010</v>
@@ -8190,7 +8741,7 @@
         <v>43400002</v>
       </c>
       <c r="H127" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I127" s="1">
         <v>1</v>
@@ -8205,7 +8756,7 @@
         <v>123</v>
       </c>
       <c r="M127" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N127" s="1">
         <v>100</v>
@@ -8217,13 +8768,13 @@
         <v>1</v>
       </c>
       <c r="Q127" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R127" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="128" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="128" spans="1:18">
       <c r="A128" s="1">
         <v>124</v>
       </c>
@@ -8234,7 +8785,7 @@
         <v>125</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="E128" s="1">
         <v>1240010</v>
@@ -8246,7 +8797,7 @@
         <v>43400002</v>
       </c>
       <c r="H128" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I128" s="1">
         <v>1</v>
@@ -8261,7 +8812,7 @@
         <v>124</v>
       </c>
       <c r="M128" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N128" s="1">
         <v>100</v>
@@ -8273,13 +8824,13 @@
         <v>1</v>
       </c>
       <c r="Q128" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R128" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="129" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="129" spans="1:18">
       <c r="A129" s="1">
         <v>125</v>
       </c>
@@ -8290,7 +8841,7 @@
         <v>126</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="E129" s="1">
         <v>1250010</v>
@@ -8302,7 +8853,7 @@
         <v>43400002</v>
       </c>
       <c r="H129" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I129" s="1">
         <v>1</v>
@@ -8317,7 +8868,7 @@
         <v>125</v>
       </c>
       <c r="M129" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N129" s="1">
         <v>100</v>
@@ -8329,13 +8880,13 @@
         <v>1</v>
       </c>
       <c r="Q129" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R129" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="130" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="130" spans="1:18">
       <c r="A130" s="1">
         <v>126</v>
       </c>
@@ -8346,7 +8897,7 @@
         <v>127</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="E130" s="1">
         <v>1260010</v>
@@ -8358,7 +8909,7 @@
         <v>43400002</v>
       </c>
       <c r="H130" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I130" s="1">
         <v>1</v>
@@ -8373,7 +8924,7 @@
         <v>126</v>
       </c>
       <c r="M130" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N130" s="1">
         <v>100</v>
@@ -8385,13 +8936,13 @@
         <v>1</v>
       </c>
       <c r="Q130" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R130" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="131" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="131" spans="1:18">
       <c r="A131" s="1">
         <v>127</v>
       </c>
@@ -8402,7 +8953,7 @@
         <v>128</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="E131" s="1">
         <v>1270010</v>
@@ -8414,7 +8965,7 @@
         <v>43400002</v>
       </c>
       <c r="H131" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I131" s="1">
         <v>1</v>
@@ -8429,7 +8980,7 @@
         <v>127</v>
       </c>
       <c r="M131" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N131" s="1">
         <v>100</v>
@@ -8441,13 +8992,13 @@
         <v>1</v>
       </c>
       <c r="Q131" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R131" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="132" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="132" spans="1:18">
       <c r="A132" s="1">
         <v>128</v>
       </c>
@@ -8458,7 +9009,7 @@
         <v>129</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="E132" s="1">
         <v>1280010</v>
@@ -8470,7 +9021,7 @@
         <v>43400002</v>
       </c>
       <c r="H132" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I132" s="1">
         <v>1</v>
@@ -8485,7 +9036,7 @@
         <v>128</v>
       </c>
       <c r="M132" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N132" s="1">
         <v>100</v>
@@ -8497,13 +9048,13 @@
         <v>1</v>
       </c>
       <c r="Q132" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R132" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="133" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="133" spans="1:18">
       <c r="A133" s="1">
         <v>129</v>
       </c>
@@ -8514,7 +9065,7 @@
         <v>130</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="E133" s="1">
         <v>1290010</v>
@@ -8526,7 +9077,7 @@
         <v>43400002</v>
       </c>
       <c r="H133" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I133" s="1">
         <v>1</v>
@@ -8541,7 +9092,7 @@
         <v>129</v>
       </c>
       <c r="M133" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N133" s="1">
         <v>100</v>
@@ -8553,13 +9104,13 @@
         <v>1</v>
       </c>
       <c r="Q133" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R133" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="134" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="134" spans="1:18">
       <c r="A134" s="1">
         <v>130</v>
       </c>
@@ -8570,7 +9121,7 @@
         <v>131</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="E134" s="1">
         <v>1300010</v>
@@ -8582,7 +9133,7 @@
         <v>43400002</v>
       </c>
       <c r="H134" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I134" s="1">
         <v>1</v>
@@ -8597,7 +9148,7 @@
         <v>130</v>
       </c>
       <c r="M134" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N134" s="1">
         <v>100</v>
@@ -8609,13 +9160,13 @@
         <v>1</v>
       </c>
       <c r="Q134" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R134" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="135" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="135" spans="1:18">
       <c r="A135" s="1">
         <v>131</v>
       </c>
@@ -8626,7 +9177,7 @@
         <v>132</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="E135" s="1">
         <v>1310010</v>
@@ -8638,7 +9189,7 @@
         <v>43400002</v>
       </c>
       <c r="H135" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I135" s="1">
         <v>1</v>
@@ -8653,7 +9204,7 @@
         <v>131</v>
       </c>
       <c r="M135" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N135" s="1">
         <v>100</v>
@@ -8665,13 +9216,13 @@
         <v>1</v>
       </c>
       <c r="Q135" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R135" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="136" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="136" spans="1:18">
       <c r="A136" s="1">
         <v>132</v>
       </c>
@@ -8682,7 +9233,7 @@
         <v>133</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="E136" s="1">
         <v>1320010</v>
@@ -8694,7 +9245,7 @@
         <v>43400002</v>
       </c>
       <c r="H136" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I136" s="1">
         <v>1</v>
@@ -8709,7 +9260,7 @@
         <v>132</v>
       </c>
       <c r="M136" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N136" s="1">
         <v>100</v>
@@ -8721,13 +9272,13 @@
         <v>1</v>
       </c>
       <c r="Q136" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R136" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="137" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="137" spans="1:18">
       <c r="A137" s="1">
         <v>133</v>
       </c>
@@ -8738,7 +9289,7 @@
         <v>134</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="E137" s="1">
         <v>1330010</v>
@@ -8750,7 +9301,7 @@
         <v>43400002</v>
       </c>
       <c r="H137" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I137" s="1">
         <v>1</v>
@@ -8765,7 +9316,7 @@
         <v>133</v>
       </c>
       <c r="M137" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N137" s="1">
         <v>100</v>
@@ -8777,13 +9328,13 @@
         <v>1</v>
       </c>
       <c r="Q137" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R137" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="138" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="138" spans="1:18">
       <c r="A138" s="1">
         <v>134</v>
       </c>
@@ -8794,7 +9345,7 @@
         <v>135</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="E138" s="1">
         <v>1340010</v>
@@ -8806,7 +9357,7 @@
         <v>43400002</v>
       </c>
       <c r="H138" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I138" s="1">
         <v>1</v>
@@ -8821,7 +9372,7 @@
         <v>134</v>
       </c>
       <c r="M138" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N138" s="1">
         <v>100</v>
@@ -8833,13 +9384,13 @@
         <v>1</v>
       </c>
       <c r="Q138" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R138" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="139" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="139" spans="1:18">
       <c r="A139" s="1">
         <v>135</v>
       </c>
@@ -8850,7 +9401,7 @@
         <v>136</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="E139" s="1">
         <v>1350010</v>
@@ -8862,7 +9413,7 @@
         <v>43400002</v>
       </c>
       <c r="H139" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I139" s="1">
         <v>1</v>
@@ -8877,7 +9428,7 @@
         <v>135</v>
       </c>
       <c r="M139" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N139" s="1">
         <v>100</v>
@@ -8889,13 +9440,13 @@
         <v>1</v>
       </c>
       <c r="Q139" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R139" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="140" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="140" spans="1:18">
       <c r="A140" s="1">
         <v>136</v>
       </c>
@@ -8906,7 +9457,7 @@
         <v>137</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="E140" s="1">
         <v>1360010</v>
@@ -8918,7 +9469,7 @@
         <v>43400002</v>
       </c>
       <c r="H140" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I140" s="1">
         <v>1</v>
@@ -8933,7 +9484,7 @@
         <v>136</v>
       </c>
       <c r="M140" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N140" s="1">
         <v>100</v>
@@ -8945,13 +9496,13 @@
         <v>1</v>
       </c>
       <c r="Q140" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R140" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="141" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="141" spans="1:18">
       <c r="A141" s="1">
         <v>137</v>
       </c>
@@ -8962,7 +9513,7 @@
         <v>138</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="E141" s="1">
         <v>1370010</v>
@@ -8974,7 +9525,7 @@
         <v>43400002</v>
       </c>
       <c r="H141" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I141" s="1">
         <v>1</v>
@@ -8989,7 +9540,7 @@
         <v>137</v>
       </c>
       <c r="M141" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N141" s="1">
         <v>100</v>
@@ -9001,13 +9552,13 @@
         <v>1</v>
       </c>
       <c r="Q141" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R141" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="142" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="142" spans="1:18">
       <c r="A142" s="1">
         <v>138</v>
       </c>
@@ -9018,7 +9569,7 @@
         <v>139</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="E142" s="1">
         <v>1380010</v>
@@ -9030,7 +9581,7 @@
         <v>43400002</v>
       </c>
       <c r="H142" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I142" s="1">
         <v>1</v>
@@ -9045,7 +9596,7 @@
         <v>138</v>
       </c>
       <c r="M142" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N142" s="1">
         <v>100</v>
@@ -9057,13 +9608,13 @@
         <v>1</v>
       </c>
       <c r="Q142" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R142" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="143" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="143" spans="1:18">
       <c r="A143" s="1">
         <v>139</v>
       </c>
@@ -9074,7 +9625,7 @@
         <v>140</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="E143" s="1">
         <v>1390010</v>
@@ -9086,7 +9637,7 @@
         <v>43400002</v>
       </c>
       <c r="H143" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I143" s="1">
         <v>1</v>
@@ -9101,7 +9652,7 @@
         <v>139</v>
       </c>
       <c r="M143" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N143" s="1">
         <v>100</v>
@@ -9113,13 +9664,13 @@
         <v>1</v>
       </c>
       <c r="Q143" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R143" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="144" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="144" spans="1:18">
       <c r="A144" s="1">
         <v>140</v>
       </c>
@@ -9130,7 +9681,7 @@
         <v>141</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="E144" s="1">
         <v>1400010</v>
@@ -9142,7 +9693,7 @@
         <v>43400002</v>
       </c>
       <c r="H144" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I144" s="1">
         <v>1</v>
@@ -9157,7 +9708,7 @@
         <v>140</v>
       </c>
       <c r="M144" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N144" s="1">
         <v>100</v>
@@ -9169,13 +9720,13 @@
         <v>1</v>
       </c>
       <c r="Q144" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R144" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="145" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="145" spans="1:18">
       <c r="A145" s="1">
         <v>141</v>
       </c>
@@ -9186,7 +9737,7 @@
         <v>142</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="E145" s="1">
         <v>1410010</v>
@@ -9198,7 +9749,7 @@
         <v>43400002</v>
       </c>
       <c r="H145" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I145" s="1">
         <v>1</v>
@@ -9213,7 +9764,7 @@
         <v>141</v>
       </c>
       <c r="M145" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N145" s="1">
         <v>100</v>
@@ -9225,13 +9776,13 @@
         <v>1</v>
       </c>
       <c r="Q145" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R145" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="146" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="146" spans="1:18">
       <c r="A146" s="1">
         <v>142</v>
       </c>
@@ -9242,7 +9793,7 @@
         <v>143</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="E146" s="1">
         <v>1420010</v>
@@ -9254,7 +9805,7 @@
         <v>43400002</v>
       </c>
       <c r="H146" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I146" s="1">
         <v>1</v>
@@ -9269,7 +9820,7 @@
         <v>142</v>
       </c>
       <c r="M146" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N146" s="1">
         <v>100</v>
@@ -9281,13 +9832,13 @@
         <v>1</v>
       </c>
       <c r="Q146" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R146" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="147" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="147" spans="1:18">
       <c r="A147" s="1">
         <v>143</v>
       </c>
@@ -9298,7 +9849,7 @@
         <v>144</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="E147" s="1">
         <v>1430010</v>
@@ -9310,7 +9861,7 @@
         <v>43400002</v>
       </c>
       <c r="H147" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I147" s="1">
         <v>1</v>
@@ -9325,7 +9876,7 @@
         <v>143</v>
       </c>
       <c r="M147" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N147" s="1">
         <v>100</v>
@@ -9337,13 +9888,13 @@
         <v>1</v>
       </c>
       <c r="Q147" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R147" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="148" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="148" spans="1:18">
       <c r="A148" s="1">
         <v>144</v>
       </c>
@@ -9354,7 +9905,7 @@
         <v>145</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="E148" s="1">
         <v>1440010</v>
@@ -9366,7 +9917,7 @@
         <v>43400002</v>
       </c>
       <c r="H148" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I148" s="1">
         <v>1</v>
@@ -9381,7 +9932,7 @@
         <v>144</v>
       </c>
       <c r="M148" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N148" s="1">
         <v>100</v>
@@ -9393,13 +9944,13 @@
         <v>1</v>
       </c>
       <c r="Q148" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R148" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="149" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="149" spans="1:18">
       <c r="A149" s="1">
         <v>145</v>
       </c>
@@ -9410,7 +9961,7 @@
         <v>146</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="E149" s="1">
         <v>1450010</v>
@@ -9422,7 +9973,7 @@
         <v>43400002</v>
       </c>
       <c r="H149" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I149" s="1">
         <v>1</v>
@@ -9437,7 +9988,7 @@
         <v>145</v>
       </c>
       <c r="M149" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N149" s="1">
         <v>100</v>
@@ -9449,13 +10000,13 @@
         <v>1</v>
       </c>
       <c r="Q149" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R149" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="150" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="150" spans="1:18">
       <c r="A150" s="1">
         <v>146</v>
       </c>
@@ -9466,7 +10017,7 @@
         <v>147</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="E150" s="1">
         <v>1460010</v>
@@ -9478,7 +10029,7 @@
         <v>43400002</v>
       </c>
       <c r="H150" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I150" s="1">
         <v>1</v>
@@ -9493,7 +10044,7 @@
         <v>146</v>
       </c>
       <c r="M150" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N150" s="1">
         <v>100</v>
@@ -9505,13 +10056,13 @@
         <v>1</v>
       </c>
       <c r="Q150" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R150" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="151" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="151" spans="1:18">
       <c r="A151" s="1">
         <v>147</v>
       </c>
@@ -9522,7 +10073,7 @@
         <v>148</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="E151" s="1">
         <v>1470010</v>
@@ -9534,7 +10085,7 @@
         <v>43400002</v>
       </c>
       <c r="H151" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I151" s="1">
         <v>1</v>
@@ -9549,7 +10100,7 @@
         <v>147</v>
       </c>
       <c r="M151" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N151" s="1">
         <v>100</v>
@@ -9561,13 +10112,13 @@
         <v>1</v>
       </c>
       <c r="Q151" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R151" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="152" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="152" spans="1:18">
       <c r="A152" s="1">
         <v>148</v>
       </c>
@@ -9578,7 +10129,7 @@
         <v>149</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="E152" s="1">
         <v>1480010</v>
@@ -9590,7 +10141,7 @@
         <v>43400002</v>
       </c>
       <c r="H152" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I152" s="1">
         <v>1</v>
@@ -9605,7 +10156,7 @@
         <v>148</v>
       </c>
       <c r="M152" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N152" s="1">
         <v>100</v>
@@ -9617,13 +10168,13 @@
         <v>1</v>
       </c>
       <c r="Q152" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R152" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="153" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="153" spans="1:18">
       <c r="A153" s="1">
         <v>149</v>
       </c>
@@ -9634,7 +10185,7 @@
         <v>150</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="E153" s="1">
         <v>1490010</v>
@@ -9646,7 +10197,7 @@
         <v>43400002</v>
       </c>
       <c r="H153" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I153" s="1">
         <v>1</v>
@@ -9661,7 +10212,7 @@
         <v>149</v>
       </c>
       <c r="M153" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N153" s="1">
         <v>100</v>
@@ -9673,13 +10224,13 @@
         <v>1</v>
       </c>
       <c r="Q153" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R153" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="154" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="154" spans="1:18">
       <c r="A154" s="1">
         <v>150</v>
       </c>
@@ -9690,7 +10241,7 @@
         <v>151</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="E154" s="1">
         <v>1500010</v>
@@ -9702,7 +10253,7 @@
         <v>43400002</v>
       </c>
       <c r="H154" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I154" s="1">
         <v>1</v>
@@ -9717,7 +10268,7 @@
         <v>150</v>
       </c>
       <c r="M154" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N154" s="1">
         <v>100</v>
@@ -9729,13 +10280,13 @@
         <v>1</v>
       </c>
       <c r="Q154" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R154" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="155" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="155" spans="1:18">
       <c r="A155" s="1">
         <v>151</v>
       </c>
@@ -9746,7 +10297,7 @@
         <v>152</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="E155" s="1">
         <v>1510010</v>
@@ -9758,7 +10309,7 @@
         <v>43400002</v>
       </c>
       <c r="H155" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I155" s="1">
         <v>1</v>
@@ -9773,7 +10324,7 @@
         <v>151</v>
       </c>
       <c r="M155" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N155" s="1">
         <v>100</v>
@@ -9785,13 +10336,13 @@
         <v>1</v>
       </c>
       <c r="Q155" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R155" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="156" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="156" spans="1:18">
       <c r="A156" s="1">
         <v>152</v>
       </c>
@@ -9802,7 +10353,7 @@
         <v>153</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="E156" s="1">
         <v>1520010</v>
@@ -9814,7 +10365,7 @@
         <v>43400002</v>
       </c>
       <c r="H156" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I156" s="1">
         <v>1</v>
@@ -9829,7 +10380,7 @@
         <v>152</v>
       </c>
       <c r="M156" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N156" s="1">
         <v>100</v>
@@ -9841,13 +10392,13 @@
         <v>1</v>
       </c>
       <c r="Q156" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R156" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="157" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="157" spans="1:18">
       <c r="A157" s="1">
         <v>153</v>
       </c>
@@ -9858,7 +10409,7 @@
         <v>154</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="E157" s="1">
         <v>1530010</v>
@@ -9870,7 +10421,7 @@
         <v>43400002</v>
       </c>
       <c r="H157" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I157" s="1">
         <v>1</v>
@@ -9885,7 +10436,7 @@
         <v>153</v>
       </c>
       <c r="M157" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N157" s="1">
         <v>100</v>
@@ -9897,13 +10448,13 @@
         <v>1</v>
       </c>
       <c r="Q157" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R157" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="158" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="158" spans="1:18">
       <c r="A158" s="1">
         <v>154</v>
       </c>
@@ -9914,7 +10465,7 @@
         <v>155</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="E158" s="1">
         <v>1540010</v>
@@ -9926,7 +10477,7 @@
         <v>43400002</v>
       </c>
       <c r="H158" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I158" s="1">
         <v>1</v>
@@ -9941,7 +10492,7 @@
         <v>154</v>
       </c>
       <c r="M158" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N158" s="1">
         <v>100</v>
@@ -9953,13 +10504,13 @@
         <v>1</v>
       </c>
       <c r="Q158" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R158" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="159" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="159" spans="1:18">
       <c r="A159" s="1">
         <v>155</v>
       </c>
@@ -9970,7 +10521,7 @@
         <v>156</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="E159" s="1">
         <v>1550010</v>
@@ -9982,7 +10533,7 @@
         <v>43400002</v>
       </c>
       <c r="H159" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I159" s="1">
         <v>1</v>
@@ -9997,7 +10548,7 @@
         <v>155</v>
       </c>
       <c r="M159" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N159" s="1">
         <v>100</v>
@@ -10009,13 +10560,13 @@
         <v>1</v>
       </c>
       <c r="Q159" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R159" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="160" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="160" spans="1:18">
       <c r="A160" s="1">
         <v>156</v>
       </c>
@@ -10026,7 +10577,7 @@
         <v>157</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="E160" s="1">
         <v>1560010</v>
@@ -10038,7 +10589,7 @@
         <v>43400002</v>
       </c>
       <c r="H160" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I160" s="1">
         <v>1</v>
@@ -10053,7 +10604,7 @@
         <v>156</v>
       </c>
       <c r="M160" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N160" s="1">
         <v>100</v>
@@ -10065,13 +10616,13 @@
         <v>1</v>
       </c>
       <c r="Q160" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R160" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="161" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="161" spans="1:18">
       <c r="A161" s="1">
         <v>157</v>
       </c>
@@ -10082,7 +10633,7 @@
         <v>158</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="E161" s="1">
         <v>1570010</v>
@@ -10094,7 +10645,7 @@
         <v>43400002</v>
       </c>
       <c r="H161" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I161" s="1">
         <v>1</v>
@@ -10109,7 +10660,7 @@
         <v>157</v>
       </c>
       <c r="M161" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N161" s="1">
         <v>100</v>
@@ -10121,13 +10672,13 @@
         <v>1</v>
       </c>
       <c r="Q161" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R161" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="162" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="162" spans="1:18">
       <c r="A162" s="1">
         <v>158</v>
       </c>
@@ -10138,7 +10689,7 @@
         <v>159</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="E162" s="1">
         <v>1580010</v>
@@ -10150,7 +10701,7 @@
         <v>43400002</v>
       </c>
       <c r="H162" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I162" s="1">
         <v>1</v>
@@ -10165,7 +10716,7 @@
         <v>158</v>
       </c>
       <c r="M162" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N162" s="1">
         <v>100</v>
@@ -10177,13 +10728,13 @@
         <v>1</v>
       </c>
       <c r="Q162" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R162" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="163" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="163" spans="1:18">
       <c r="A163" s="1">
         <v>159</v>
       </c>
@@ -10194,7 +10745,7 @@
         <v>160</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="E163" s="1">
         <v>1590010</v>
@@ -10206,7 +10757,7 @@
         <v>43400002</v>
       </c>
       <c r="H163" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I163" s="1">
         <v>1</v>
@@ -10221,7 +10772,7 @@
         <v>159</v>
       </c>
       <c r="M163" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N163" s="1">
         <v>100</v>
@@ -10233,13 +10784,13 @@
         <v>1</v>
       </c>
       <c r="Q163" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R163" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="164" spans="1:18" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="164" spans="1:18">
       <c r="A164" s="1">
         <v>160</v>
       </c>
@@ -10250,7 +10801,7 @@
         <v>-1</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="E164" s="1">
         <v>1600010</v>
@@ -10262,7 +10813,7 @@
         <v>43400002</v>
       </c>
       <c r="H164" s="1" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="I164" s="1">
         <v>1</v>
@@ -10277,7 +10828,7 @@
         <v>160</v>
       </c>
       <c r="M164" s="2" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="N164" s="1">
         <v>100</v>
@@ -10289,32 +10840,32 @@
         <v>1</v>
       </c>
       <c r="Q164" s="3" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="R164" s="1" t="s">
-        <v>239</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33853DBC-0067-4AC2-B260-DDF526E77673}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="B4:AH34"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col min="2" max="2" width="121.25" bestFit="1" customWidth="1"/>
-    <col min="3" max="14" width="7.5" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.875" bestFit="1" customWidth="1"/>
-    <col min="17" max="26" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="121.25" customWidth="1"/>
+    <col min="3" max="14" width="7.5" customWidth="1"/>
+    <col min="15" max="15" width="11" customWidth="1"/>
+    <col min="16" max="16" width="8.875" customWidth="1"/>
+    <col min="17" max="26" width="9.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="4" spans="3:14">
       <c r="C4">
         <v>100</v>
       </c>
@@ -10352,7 +10903,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:34">
       <c r="B5" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,O5:Z5)</f>
         <v>10101:100_10201:1_10301:10_10302:10_10303:10_10304:10_10305:10_10306:10_10307:10_10308:10_10309:10_10310:10</v>
@@ -10450,9 +11001,9 @@
       <c r="AG5" s="1"/>
       <c r="AH5" s="1"/>
     </row>
-    <row r="6" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:34">
       <c r="B6" t="s">
-        <v>38</v>
+        <v>209</v>
       </c>
       <c r="C6">
         <v>20101</v>
@@ -10547,9 +11098,9 @@
       <c r="AG6" s="1"/>
       <c r="AH6" s="1"/>
     </row>
-    <row r="7" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:34">
       <c r="B7" t="s">
-        <v>39</v>
+        <v>210</v>
       </c>
       <c r="C7">
         <v>30101</v>
@@ -10644,9 +11195,9 @@
       <c r="AG7" s="1"/>
       <c r="AH7" s="1"/>
     </row>
-    <row r="8" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:34">
       <c r="B8" t="s">
-        <v>40</v>
+        <v>211</v>
       </c>
       <c r="C8">
         <v>40101</v>
@@ -10741,9 +11292,9 @@
       <c r="AG8" s="1"/>
       <c r="AH8" s="1"/>
     </row>
-    <row r="9" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:34">
       <c r="B9" t="s">
-        <v>41</v>
+        <v>212</v>
       </c>
       <c r="C9">
         <v>50101</v>
@@ -10838,9 +11389,9 @@
       <c r="AG9" s="1"/>
       <c r="AH9" s="1"/>
     </row>
-    <row r="10" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:34">
       <c r="B10" t="s">
-        <v>42</v>
+        <v>213</v>
       </c>
       <c r="C10">
         <v>60101</v>
@@ -10935,9 +11486,9 @@
       <c r="AG10" s="1"/>
       <c r="AH10" s="1"/>
     </row>
-    <row r="11" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:34">
       <c r="B11" t="s">
-        <v>43</v>
+        <v>214</v>
       </c>
       <c r="C11">
         <v>70101</v>
@@ -11032,9 +11583,9 @@
       <c r="AG11" s="1"/>
       <c r="AH11" s="1"/>
     </row>
-    <row r="12" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:34">
       <c r="B12" t="s">
-        <v>44</v>
+        <v>215</v>
       </c>
       <c r="C12">
         <v>80101</v>
@@ -11129,9 +11680,9 @@
       <c r="AG12" s="1"/>
       <c r="AH12" s="1"/>
     </row>
-    <row r="13" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:34">
       <c r="B13" t="s">
-        <v>45</v>
+        <v>216</v>
       </c>
       <c r="C13">
         <v>90101</v>
@@ -11226,9 +11777,9 @@
       <c r="AG13" s="1"/>
       <c r="AH13" s="1"/>
     </row>
-    <row r="14" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:34">
       <c r="B14" t="s">
-        <v>46</v>
+        <v>217</v>
       </c>
       <c r="C14">
         <v>100101</v>
@@ -11323,9 +11874,9 @@
       <c r="AG14" s="1"/>
       <c r="AH14" s="1"/>
     </row>
-    <row r="15" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:34">
       <c r="B15" t="s">
-        <v>47</v>
+        <v>218</v>
       </c>
       <c r="C15">
         <v>110101</v>
@@ -11420,9 +11971,9 @@
       <c r="AG15" s="1"/>
       <c r="AH15" s="1"/>
     </row>
-    <row r="16" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:34">
       <c r="B16" t="s">
-        <v>48</v>
+        <v>219</v>
       </c>
       <c r="C16">
         <v>120101</v>
@@ -11517,9 +12068,9 @@
       <c r="AG16" s="1"/>
       <c r="AH16" s="1"/>
     </row>
-    <row r="17" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:34">
       <c r="B17" t="s">
-        <v>49</v>
+        <v>220</v>
       </c>
       <c r="C17">
         <v>130101</v>
@@ -11614,9 +12165,9 @@
       <c r="AG17" s="1"/>
       <c r="AH17" s="1"/>
     </row>
-    <row r="18" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:34">
       <c r="B18" t="s">
-        <v>50</v>
+        <v>221</v>
       </c>
       <c r="C18">
         <v>140101</v>
@@ -11711,9 +12262,9 @@
       <c r="AG18" s="1"/>
       <c r="AH18" s="1"/>
     </row>
-    <row r="19" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:34">
       <c r="B19" t="s">
-        <v>51</v>
+        <v>222</v>
       </c>
       <c r="C19">
         <v>150101</v>
@@ -11808,9 +12359,9 @@
       <c r="AG19" s="1"/>
       <c r="AH19" s="1"/>
     </row>
-    <row r="20" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:34">
       <c r="B20" t="s">
-        <v>52</v>
+        <v>223</v>
       </c>
       <c r="C20">
         <v>160101</v>
@@ -11905,9 +12456,9 @@
       <c r="AG20" s="1"/>
       <c r="AH20" s="1"/>
     </row>
-    <row r="21" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:34">
       <c r="B21" t="s">
-        <v>53</v>
+        <v>224</v>
       </c>
       <c r="C21">
         <v>170101</v>
@@ -12002,9 +12553,9 @@
       <c r="AG21" s="1"/>
       <c r="AH21" s="1"/>
     </row>
-    <row r="22" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:34">
       <c r="B22" t="s">
-        <v>54</v>
+        <v>225</v>
       </c>
       <c r="C22">
         <v>180101</v>
@@ -12099,9 +12650,9 @@
       <c r="AG22" s="1"/>
       <c r="AH22" s="1"/>
     </row>
-    <row r="23" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:34">
       <c r="B23" t="s">
-        <v>55</v>
+        <v>226</v>
       </c>
       <c r="C23">
         <v>190101</v>
@@ -12196,9 +12747,9 @@
       <c r="AG23" s="1"/>
       <c r="AH23" s="1"/>
     </row>
-    <row r="24" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:34">
       <c r="B24" t="s">
-        <v>56</v>
+        <v>227</v>
       </c>
       <c r="C24">
         <v>200101</v>
@@ -12293,9 +12844,9 @@
       <c r="AG24" s="1"/>
       <c r="AH24" s="1"/>
     </row>
-    <row r="25" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:34">
       <c r="B25" t="s">
-        <v>57</v>
+        <v>228</v>
       </c>
       <c r="C25">
         <v>210101</v>
@@ -12390,9 +12941,9 @@
       <c r="AG25" s="1"/>
       <c r="AH25" s="1"/>
     </row>
-    <row r="26" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:34">
       <c r="B26" t="s">
-        <v>58</v>
+        <v>229</v>
       </c>
       <c r="C26">
         <v>220101</v>
@@ -12487,9 +13038,9 @@
       <c r="AG26" s="1"/>
       <c r="AH26" s="1"/>
     </row>
-    <row r="27" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:34">
       <c r="B27" t="s">
-        <v>59</v>
+        <v>230</v>
       </c>
       <c r="C27">
         <v>230101</v>
@@ -12584,9 +13135,9 @@
       <c r="AG27" s="1"/>
       <c r="AH27" s="1"/>
     </row>
-    <row r="28" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:34">
       <c r="B28" t="s">
-        <v>60</v>
+        <v>231</v>
       </c>
       <c r="C28">
         <v>240101</v>
@@ -12681,9 +13232,9 @@
       <c r="AG28" s="1"/>
       <c r="AH28" s="1"/>
     </row>
-    <row r="29" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:34">
       <c r="B29" t="s">
-        <v>61</v>
+        <v>232</v>
       </c>
       <c r="C29">
         <v>250101</v>
@@ -12778,9 +13329,9 @@
       <c r="AG29" s="1"/>
       <c r="AH29" s="1"/>
     </row>
-    <row r="30" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:26">
       <c r="B30" t="s">
-        <v>62</v>
+        <v>233</v>
       </c>
       <c r="C30">
         <v>260101</v>
@@ -12867,9 +13418,9 @@
         <v>260310:10</v>
       </c>
     </row>
-    <row r="31" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:26">
       <c r="B31" t="s">
-        <v>63</v>
+        <v>234</v>
       </c>
       <c r="C31">
         <v>270101</v>
@@ -12956,9 +13507,9 @@
         <v>270310:10</v>
       </c>
     </row>
-    <row r="32" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:26">
       <c r="B32" t="s">
-        <v>64</v>
+        <v>235</v>
       </c>
       <c r="C32">
         <v>280101</v>
@@ -13045,9 +13596,9 @@
         <v>280310:10</v>
       </c>
     </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:26">
       <c r="B33" t="s">
-        <v>65</v>
+        <v>236</v>
       </c>
       <c r="C33">
         <v>290101</v>
@@ -13134,9 +13685,9 @@
         <v>290310:10</v>
       </c>
     </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:26">
       <c r="B34" t="s">
-        <v>66</v>
+        <v>237</v>
       </c>
       <c r="C34">
         <v>300101</v>
@@ -13224,7 +13775,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8C49A9F-15D5-49F9-996D-DD812962EE0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F8FE8AA-F3F4-4994-AC88-BD1A09CA5D4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_barries_v8" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="880" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="876" uniqueCount="240">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1861,8 +1861,8 @@
       <c r="G14" s="1">
         <v>43400002</v>
       </c>
-      <c r="H14" s="1" t="s">
-        <v>202</v>
+      <c r="H14" s="1">
+        <v>0</v>
       </c>
       <c r="I14" s="1">
         <v>1</v>
@@ -1883,16 +1883,16 @@
         <v>100</v>
       </c>
       <c r="O14" s="1">
-        <v>4</v>
+        <v>99</v>
       </c>
       <c r="P14" s="1">
-        <v>1</v>
+        <v>1003</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="R14" s="1" t="s">
-        <v>239</v>
+      <c r="R14" s="1">
+        <v>101</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.15">
@@ -1917,8 +1917,8 @@
       <c r="G15" s="1">
         <v>43400002</v>
       </c>
-      <c r="H15" s="1" t="s">
-        <v>202</v>
+      <c r="H15" s="1">
+        <v>0</v>
       </c>
       <c r="I15" s="1">
         <v>1</v>
@@ -1939,16 +1939,16 @@
         <v>100</v>
       </c>
       <c r="O15" s="1">
-        <v>4</v>
+        <v>99</v>
       </c>
       <c r="P15" s="1">
-        <v>1</v>
+        <v>1003</v>
       </c>
       <c r="Q15" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="R15" s="1" t="s">
-        <v>239</v>
+      <c r="R15" s="1">
+        <v>101</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.15">

--- a/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F8FE8AA-F3F4-4994-AC88-BD1A09CA5D4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C015577-D50D-408F-9BC5-72414A2ABE5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_barries_v8" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="876" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="888" uniqueCount="250">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -805,6 +805,46 @@
   </si>
   <si>
     <t>1,2,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>普攻档位1刷怪区域：所需武力值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>普攻档位2刷怪区域：所需武力值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>普攻档位3刷怪区域：所需武力值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>attack_action1_need_kongfu</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>attack_action2_need_kongfu</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>attack_action3_need_kongfu</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>110001:0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>110001:160</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>110001:240</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MAP&lt;INT:INT&gt;_S_C</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1141,7 +1181,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:R164"/>
+  <dimension ref="A1:U164"/>
   <sheetFormatPr defaultColWidth="7.125" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.5" style="1" bestFit="1" customWidth="1"/>
@@ -1159,15 +1199,16 @@
     <col min="15" max="16" width="21.5" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="19.375" style="1" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="21.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="7.125" style="1"/>
+    <col min="19" max="21" width="30.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="7.125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -1222,8 +1263,17 @@
       <c r="R2" s="1" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="S2" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -1278,8 +1328,17 @@
       <c r="R3" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="S3" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="U3" s="1" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -1334,8 +1393,17 @@
       <c r="R4" s="1" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="S4" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="T4" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="U4" s="1" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -1391,7 +1459,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A6" s="1">
         <v>2</v>
       </c>
@@ -1447,7 +1515,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A7" s="1">
         <v>3</v>
       </c>
@@ -1503,7 +1571,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A8" s="1">
         <v>4</v>
       </c>
@@ -1559,7 +1627,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A9" s="1">
         <v>5</v>
       </c>
@@ -1615,7 +1683,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A10" s="1">
         <v>6</v>
       </c>
@@ -1671,7 +1739,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A11" s="1">
         <v>7</v>
       </c>
@@ -1727,7 +1795,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A12" s="1">
         <v>8</v>
       </c>
@@ -1783,7 +1851,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A13" s="1">
         <v>9</v>
       </c>
@@ -1839,7 +1907,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:21" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="1">
         <v>10</v>
       </c>
@@ -1895,7 +1963,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A15" s="1">
         <v>11</v>
       </c>
@@ -1950,8 +2018,17 @@
       <c r="R15" s="1">
         <v>101</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="S15" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="T15" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="U15" s="1" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A16" s="1">
         <v>12</v>
       </c>

--- a/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C015577-D50D-408F-9BC5-72414A2ABE5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E35151C-5A3A-4824-A7DA-B35F5C7C6CE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -844,7 +844,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>MAP&lt;INT:INT&gt;_S_C</t>
+    <t>MAP&lt;INT:LONG&gt;_S_C</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>

--- a/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E35151C-5A3A-4824-A7DA-B35F5C7C6CE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5DD4C0B-D343-42BA-9875-47925733655D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="888" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="891" uniqueCount="253">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -845,6 +845,18 @@
   </si>
   <si>
     <t>MAP&lt;INT:LONG&gt;_S_C</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10001:0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10001:160</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10001:240</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1458,6 +1470,15 @@
       <c r="R5" s="1" t="s">
         <v>239</v>
       </c>
+      <c r="S5" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="T5" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="U5" s="1" t="s">
+        <v>252</v>
+      </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A6" s="1">

--- a/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5DD4C0B-D343-42BA-9875-47925733655D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB4AB2B0-435D-44B4-8CFC-805165479620}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -836,14 +836,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>110001:160</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>110001:240</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>MAP&lt;INT:LONG&gt;_S_C</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -857,6 +849,14 @@
   </si>
   <si>
     <t>10001:240</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>110001:140</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>110001:200</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1276,13 +1276,13 @@
         <v>205</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.15">
@@ -1471,13 +1471,13 @@
         <v>239</v>
       </c>
       <c r="S5" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="T5" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="U5" s="1" t="s">
         <v>250</v>
-      </c>
-      <c r="T5" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="U5" s="1" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.15">
@@ -2037,16 +2037,16 @@
         <v>231</v>
       </c>
       <c r="R15" s="1">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="S15" s="1" t="s">
         <v>246</v>
       </c>
       <c r="T15" s="1" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="U15" s="1" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.15">

--- a/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB4AB2B0-435D-44B4-8CFC-805165479620}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46A4A3FF-A5A2-4AD2-B54D-0F197C9C16ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -832,10 +832,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>110001:0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>MAP&lt;INT:LONG&gt;_S_C</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -852,11 +848,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>110001:140</t>
+    <t>110001:0_110002:0</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>110001:200</t>
+    <t>110001:140_110002:550</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>110001:200_110002:675</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1276,13 +1276,13 @@
         <v>205</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.15">
@@ -1471,13 +1471,13 @@
         <v>239</v>
       </c>
       <c r="S5" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="T5" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="T5" s="1" t="s">
+      <c r="U5" s="1" t="s">
         <v>249</v>
-      </c>
-      <c r="U5" s="1" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.15">
@@ -2040,7 +2040,7 @@
         <v>0</v>
       </c>
       <c r="S15" s="1" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="T15" s="1" t="s">
         <v>251</v>

--- a/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46A4A3FF-A5A2-4AD2-B54D-0F197C9C16ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE49DD62-E8A9-41F3-95F7-0ADE5470733F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -852,11 +852,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>110001:140_110002:550</t>
+    <t>110001:175_110002:550</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>110001:200_110002:675</t>
+    <t>110001:250_110002:700</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>

--- a/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE49DD62-E8A9-41F3-95F7-0ADE5470733F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D48BD56-D917-4852-9B85-99EB8E8C7FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -852,11 +852,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>110001:175_110002:550</t>
+    <t>110001:180_110002:600</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>110001:250_110002:700</t>
+    <t>110001:300_110002:800</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>

--- a/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D48BD56-D917-4852-9B85-99EB8E8C7FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BCB557D-1CBA-4E0C-8858-FA6450437536}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -852,11 +852,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>110001:180_110002:600</t>
+    <t>110001:180_110002:550</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>110001:300_110002:800</t>
+    <t>110001:300_110002:750</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>

--- a/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BCB557D-1CBA-4E0C-8858-FA6450437536}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF751AE0-4E28-4FCF-9ADB-5704F156EA39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1459,10 +1459,10 @@
         <v>150</v>
       </c>
       <c r="O5" s="1">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="P5" s="1">
-        <v>1001</v>
+        <v>101</v>
       </c>
       <c r="Q5" s="3" t="s">
         <v>231</v>

--- a/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF751AE0-4E28-4FCF-9ADB-5704F156EA39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E106B453-4B87-4F6F-A5C7-753922848C44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_barries_v8" sheetId="1" r:id="rId1"/>
@@ -848,15 +848,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>110001:0_110002:0</t>
+    <t>110001:0_110002:0_110003:0</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>110001:180_110002:550</t>
+    <t>110001:180_110002:550_110003:200</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>110001:300_110002:750</t>
+    <t>110001:300_110002:750_110003:550</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2031,7 +2031,7 @@
         <v>99</v>
       </c>
       <c r="P15" s="1">
-        <v>1003</v>
+        <v>101</v>
       </c>
       <c r="Q15" s="3" t="s">
         <v>231</v>

--- a/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E106B453-4B87-4F6F-A5C7-753922848C44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C085DEED-8373-4197-8911-5D7376DBF8C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_barries_v8" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="891" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1211" uniqueCount="259">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -857,6 +857,29 @@
   </si>
   <si>
     <t>110001:300_110002:750_110003:550</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MAP&lt;INT:INT&gt;_S_C</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10001:100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10001:101</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>110001:99_110002:99_110003:99_110004:99</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>110001:101_110002:101_110003:101_110004:101</t>
+  </si>
+  <si>
+    <t>0:0</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -907,11 +930,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="20" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1208,7 +1232,7 @@
     <col min="11" max="12" width="19.375" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="21.375" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="19.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="21.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="43.875" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="19.375" style="1" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="21.5" style="1" bestFit="1" customWidth="1"/>
     <col min="19" max="21" width="30.75" style="1" bestFit="1" customWidth="1"/>
@@ -1264,10 +1288,10 @@
         <v>220</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>220</v>
+        <v>253</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>220</v>
+        <v>253</v>
       </c>
       <c r="Q2" s="1" t="s">
         <v>227</v>
@@ -1458,11 +1482,11 @@
       <c r="N5" s="1">
         <v>150</v>
       </c>
-      <c r="O5" s="1">
-        <v>100</v>
-      </c>
-      <c r="P5" s="1">
-        <v>101</v>
+      <c r="O5" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>255</v>
       </c>
       <c r="Q5" s="3" t="s">
         <v>231</v>
@@ -1523,11 +1547,11 @@
       <c r="N6" s="1">
         <v>200</v>
       </c>
-      <c r="O6" s="1">
-        <v>2</v>
-      </c>
-      <c r="P6" s="1">
-        <v>1003</v>
+      <c r="O6" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P6" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q6" s="3" t="s">
         <v>231</v>
@@ -1579,11 +1603,11 @@
       <c r="N7" s="1">
         <v>300</v>
       </c>
-      <c r="O7" s="1">
-        <v>2</v>
-      </c>
-      <c r="P7" s="1">
-        <v>1003</v>
+      <c r="O7" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P7" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q7" s="3" t="s">
         <v>231</v>
@@ -1635,11 +1659,11 @@
       <c r="N8" s="1">
         <v>400</v>
       </c>
-      <c r="O8" s="1">
-        <v>2</v>
-      </c>
-      <c r="P8" s="1">
-        <v>1003</v>
+      <c r="O8" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P8" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q8" s="3" t="s">
         <v>231</v>
@@ -1691,11 +1715,11 @@
       <c r="N9" s="1">
         <v>500</v>
       </c>
-      <c r="O9" s="1">
-        <v>3</v>
-      </c>
-      <c r="P9" s="1">
-        <v>1003</v>
+      <c r="O9" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P9" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q9" s="3" t="s">
         <v>231</v>
@@ -1747,11 +1771,11 @@
       <c r="N10" s="1">
         <v>600</v>
       </c>
-      <c r="O10" s="1">
-        <v>3</v>
-      </c>
-      <c r="P10" s="1">
-        <v>1003</v>
+      <c r="O10" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P10" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q10" s="3" t="s">
         <v>231</v>
@@ -1803,11 +1827,11 @@
       <c r="N11" s="1">
         <v>100</v>
       </c>
-      <c r="O11" s="1">
-        <v>99</v>
-      </c>
-      <c r="P11" s="1">
-        <v>1003</v>
+      <c r="O11" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P11" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q11" s="3" t="s">
         <v>231</v>
@@ -1859,11 +1883,11 @@
       <c r="N12" s="1">
         <v>100</v>
       </c>
-      <c r="O12" s="1">
-        <v>4</v>
-      </c>
-      <c r="P12" s="1">
-        <v>1003</v>
+      <c r="O12" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P12" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q12" s="3" t="s">
         <v>231</v>
@@ -1915,11 +1939,11 @@
       <c r="N13" s="1">
         <v>100</v>
       </c>
-      <c r="O13" s="1">
-        <v>99</v>
-      </c>
-      <c r="P13" s="1">
-        <v>1003</v>
+      <c r="O13" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P13" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q13" s="3" t="s">
         <v>231</v>
@@ -1971,11 +1995,11 @@
       <c r="N14" s="1">
         <v>100</v>
       </c>
-      <c r="O14" s="1">
-        <v>99</v>
-      </c>
-      <c r="P14" s="1">
-        <v>1003</v>
+      <c r="O14" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P14" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>231</v>
@@ -2027,11 +2051,11 @@
       <c r="N15" s="1">
         <v>100</v>
       </c>
-      <c r="O15" s="1">
-        <v>99</v>
-      </c>
-      <c r="P15" s="1">
-        <v>101</v>
+      <c r="O15" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="P15" s="1" t="s">
+        <v>257</v>
       </c>
       <c r="Q15" s="3" t="s">
         <v>231</v>
@@ -2092,11 +2116,11 @@
       <c r="N16" s="1">
         <v>100</v>
       </c>
-      <c r="O16" s="1">
-        <v>4</v>
-      </c>
-      <c r="P16" s="1">
-        <v>1</v>
+      <c r="O16" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P16" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q16" s="3" t="s">
         <v>231</v>
@@ -2148,11 +2172,11 @@
       <c r="N17" s="1">
         <v>100</v>
       </c>
-      <c r="O17" s="1">
-        <v>4</v>
-      </c>
-      <c r="P17" s="1">
-        <v>1</v>
+      <c r="O17" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P17" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q17" s="3" t="s">
         <v>231</v>
@@ -2204,11 +2228,11 @@
       <c r="N18" s="1">
         <v>100</v>
       </c>
-      <c r="O18" s="1">
-        <v>4</v>
-      </c>
-      <c r="P18" s="1">
-        <v>1</v>
+      <c r="O18" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P18" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q18" s="3" t="s">
         <v>231</v>
@@ -2260,11 +2284,11 @@
       <c r="N19" s="1">
         <v>100</v>
       </c>
-      <c r="O19" s="1">
-        <v>4</v>
-      </c>
-      <c r="P19" s="1">
-        <v>1</v>
+      <c r="O19" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P19" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q19" s="3" t="s">
         <v>231</v>
@@ -2316,11 +2340,11 @@
       <c r="N20" s="1">
         <v>100</v>
       </c>
-      <c r="O20" s="1">
-        <v>4</v>
-      </c>
-      <c r="P20" s="1">
-        <v>1</v>
+      <c r="O20" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P20" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q20" s="3" t="s">
         <v>231</v>
@@ -2372,11 +2396,11 @@
       <c r="N21" s="1">
         <v>100</v>
       </c>
-      <c r="O21" s="1">
-        <v>4</v>
-      </c>
-      <c r="P21" s="1">
-        <v>1</v>
+      <c r="O21" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P21" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q21" s="3" t="s">
         <v>231</v>
@@ -2428,11 +2452,11 @@
       <c r="N22" s="1">
         <v>100</v>
       </c>
-      <c r="O22" s="1">
-        <v>4</v>
-      </c>
-      <c r="P22" s="1">
-        <v>1</v>
+      <c r="O22" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P22" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q22" s="3" t="s">
         <v>231</v>
@@ -2484,11 +2508,11 @@
       <c r="N23" s="1">
         <v>100</v>
       </c>
-      <c r="O23" s="1">
-        <v>4</v>
-      </c>
-      <c r="P23" s="1">
-        <v>1</v>
+      <c r="O23" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P23" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q23" s="3" t="s">
         <v>231</v>
@@ -2540,11 +2564,11 @@
       <c r="N24" s="1">
         <v>100</v>
       </c>
-      <c r="O24" s="1">
-        <v>4</v>
-      </c>
-      <c r="P24" s="1">
-        <v>1</v>
+      <c r="O24" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P24" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q24" s="3" t="s">
         <v>231</v>
@@ -2596,11 +2620,11 @@
       <c r="N25" s="1">
         <v>100</v>
       </c>
-      <c r="O25" s="1">
-        <v>4</v>
-      </c>
-      <c r="P25" s="1">
-        <v>1</v>
+      <c r="O25" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P25" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q25" s="3" t="s">
         <v>231</v>
@@ -2652,11 +2676,11 @@
       <c r="N26" s="1">
         <v>100</v>
       </c>
-      <c r="O26" s="1">
-        <v>4</v>
-      </c>
-      <c r="P26" s="1">
-        <v>1</v>
+      <c r="O26" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P26" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q26" s="3" t="s">
         <v>231</v>
@@ -2708,11 +2732,11 @@
       <c r="N27" s="1">
         <v>100</v>
       </c>
-      <c r="O27" s="1">
-        <v>4</v>
-      </c>
-      <c r="P27" s="1">
-        <v>1</v>
+      <c r="O27" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P27" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q27" s="3" t="s">
         <v>231</v>
@@ -2764,11 +2788,11 @@
       <c r="N28" s="1">
         <v>100</v>
       </c>
-      <c r="O28" s="1">
-        <v>4</v>
-      </c>
-      <c r="P28" s="1">
-        <v>1</v>
+      <c r="O28" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P28" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q28" s="3" t="s">
         <v>231</v>
@@ -2820,11 +2844,11 @@
       <c r="N29" s="1">
         <v>100</v>
       </c>
-      <c r="O29" s="1">
-        <v>4</v>
-      </c>
-      <c r="P29" s="1">
-        <v>1</v>
+      <c r="O29" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P29" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q29" s="3" t="s">
         <v>231</v>
@@ -2876,11 +2900,11 @@
       <c r="N30" s="1">
         <v>100</v>
       </c>
-      <c r="O30" s="1">
-        <v>4</v>
-      </c>
-      <c r="P30" s="1">
-        <v>1</v>
+      <c r="O30" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P30" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q30" s="3" t="s">
         <v>231</v>
@@ -2932,11 +2956,11 @@
       <c r="N31" s="1">
         <v>100</v>
       </c>
-      <c r="O31" s="1">
-        <v>4</v>
-      </c>
-      <c r="P31" s="1">
-        <v>1</v>
+      <c r="O31" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P31" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q31" s="3" t="s">
         <v>231</v>
@@ -2988,11 +3012,11 @@
       <c r="N32" s="1">
         <v>100</v>
       </c>
-      <c r="O32" s="1">
-        <v>4</v>
-      </c>
-      <c r="P32" s="1">
-        <v>1</v>
+      <c r="O32" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P32" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q32" s="3" t="s">
         <v>231</v>
@@ -3044,11 +3068,11 @@
       <c r="N33" s="1">
         <v>100</v>
       </c>
-      <c r="O33" s="1">
-        <v>4</v>
-      </c>
-      <c r="P33" s="1">
-        <v>1</v>
+      <c r="O33" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P33" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q33" s="3" t="s">
         <v>231</v>
@@ -3100,11 +3124,11 @@
       <c r="N34" s="1">
         <v>100</v>
       </c>
-      <c r="O34" s="1">
-        <v>4</v>
-      </c>
-      <c r="P34" s="1">
-        <v>1</v>
+      <c r="O34" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P34" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q34" s="3" t="s">
         <v>231</v>
@@ -3156,11 +3180,11 @@
       <c r="N35" s="1">
         <v>100</v>
       </c>
-      <c r="O35" s="1">
-        <v>4</v>
-      </c>
-      <c r="P35" s="1">
-        <v>1</v>
+      <c r="O35" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P35" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q35" s="3" t="s">
         <v>231</v>
@@ -3212,11 +3236,11 @@
       <c r="N36" s="1">
         <v>100</v>
       </c>
-      <c r="O36" s="1">
-        <v>4</v>
-      </c>
-      <c r="P36" s="1">
-        <v>1</v>
+      <c r="O36" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P36" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q36" s="3" t="s">
         <v>231</v>
@@ -3268,11 +3292,11 @@
       <c r="N37" s="1">
         <v>100</v>
       </c>
-      <c r="O37" s="1">
-        <v>4</v>
-      </c>
-      <c r="P37" s="1">
-        <v>1</v>
+      <c r="O37" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P37" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q37" s="3" t="s">
         <v>231</v>
@@ -3324,11 +3348,11 @@
       <c r="N38" s="1">
         <v>100</v>
       </c>
-      <c r="O38" s="1">
-        <v>4</v>
-      </c>
-      <c r="P38" s="1">
-        <v>1</v>
+      <c r="O38" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P38" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q38" s="3" t="s">
         <v>231</v>
@@ -3380,11 +3404,11 @@
       <c r="N39" s="1">
         <v>100</v>
       </c>
-      <c r="O39" s="1">
-        <v>4</v>
-      </c>
-      <c r="P39" s="1">
-        <v>1</v>
+      <c r="O39" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P39" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q39" s="3" t="s">
         <v>231</v>
@@ -3436,11 +3460,11 @@
       <c r="N40" s="1">
         <v>100</v>
       </c>
-      <c r="O40" s="1">
-        <v>4</v>
-      </c>
-      <c r="P40" s="1">
-        <v>1</v>
+      <c r="O40" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P40" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q40" s="3" t="s">
         <v>231</v>
@@ -3492,11 +3516,11 @@
       <c r="N41" s="1">
         <v>100</v>
       </c>
-      <c r="O41" s="1">
-        <v>4</v>
-      </c>
-      <c r="P41" s="1">
-        <v>1</v>
+      <c r="O41" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P41" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q41" s="3" t="s">
         <v>231</v>
@@ -3548,11 +3572,11 @@
       <c r="N42" s="1">
         <v>100</v>
       </c>
-      <c r="O42" s="1">
-        <v>4</v>
-      </c>
-      <c r="P42" s="1">
-        <v>1</v>
+      <c r="O42" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P42" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q42" s="3" t="s">
         <v>231</v>
@@ -3604,11 +3628,11 @@
       <c r="N43" s="1">
         <v>100</v>
       </c>
-      <c r="O43" s="1">
-        <v>4</v>
-      </c>
-      <c r="P43" s="1">
-        <v>1</v>
+      <c r="O43" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P43" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q43" s="3" t="s">
         <v>231</v>
@@ -3660,11 +3684,11 @@
       <c r="N44" s="1">
         <v>100</v>
       </c>
-      <c r="O44" s="1">
-        <v>4</v>
-      </c>
-      <c r="P44" s="1">
-        <v>1</v>
+      <c r="O44" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P44" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q44" s="3" t="s">
         <v>231</v>
@@ -3716,11 +3740,11 @@
       <c r="N45" s="1">
         <v>100</v>
       </c>
-      <c r="O45" s="1">
-        <v>4</v>
-      </c>
-      <c r="P45" s="1">
-        <v>1</v>
+      <c r="O45" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P45" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q45" s="3" t="s">
         <v>231</v>
@@ -3772,11 +3796,11 @@
       <c r="N46" s="1">
         <v>100</v>
       </c>
-      <c r="O46" s="1">
-        <v>4</v>
-      </c>
-      <c r="P46" s="1">
-        <v>1</v>
+      <c r="O46" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P46" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q46" s="3" t="s">
         <v>231</v>
@@ -3828,11 +3852,11 @@
       <c r="N47" s="1">
         <v>100</v>
       </c>
-      <c r="O47" s="1">
-        <v>4</v>
-      </c>
-      <c r="P47" s="1">
-        <v>1</v>
+      <c r="O47" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P47" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q47" s="3" t="s">
         <v>231</v>
@@ -3884,11 +3908,11 @@
       <c r="N48" s="1">
         <v>100</v>
       </c>
-      <c r="O48" s="1">
-        <v>4</v>
-      </c>
-      <c r="P48" s="1">
-        <v>1</v>
+      <c r="O48" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P48" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q48" s="3" t="s">
         <v>231</v>
@@ -3940,11 +3964,11 @@
       <c r="N49" s="1">
         <v>100</v>
       </c>
-      <c r="O49" s="1">
-        <v>4</v>
-      </c>
-      <c r="P49" s="1">
-        <v>1</v>
+      <c r="O49" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P49" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q49" s="3" t="s">
         <v>231</v>
@@ -3996,11 +4020,11 @@
       <c r="N50" s="1">
         <v>100</v>
       </c>
-      <c r="O50" s="1">
-        <v>4</v>
-      </c>
-      <c r="P50" s="1">
-        <v>1</v>
+      <c r="O50" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P50" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q50" s="3" t="s">
         <v>231</v>
@@ -4052,11 +4076,11 @@
       <c r="N51" s="1">
         <v>100</v>
       </c>
-      <c r="O51" s="1">
-        <v>4</v>
-      </c>
-      <c r="P51" s="1">
-        <v>1</v>
+      <c r="O51" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P51" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q51" s="3" t="s">
         <v>231</v>
@@ -4108,11 +4132,11 @@
       <c r="N52" s="1">
         <v>100</v>
       </c>
-      <c r="O52" s="1">
-        <v>4</v>
-      </c>
-      <c r="P52" s="1">
-        <v>1</v>
+      <c r="O52" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P52" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q52" s="3" t="s">
         <v>231</v>
@@ -4164,11 +4188,11 @@
       <c r="N53" s="1">
         <v>100</v>
       </c>
-      <c r="O53" s="1">
-        <v>4</v>
-      </c>
-      <c r="P53" s="1">
-        <v>1</v>
+      <c r="O53" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P53" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q53" s="3" t="s">
         <v>231</v>
@@ -4220,11 +4244,11 @@
       <c r="N54" s="1">
         <v>100</v>
       </c>
-      <c r="O54" s="1">
-        <v>4</v>
-      </c>
-      <c r="P54" s="1">
-        <v>1</v>
+      <c r="O54" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P54" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q54" s="3" t="s">
         <v>231</v>
@@ -4276,11 +4300,11 @@
       <c r="N55" s="1">
         <v>100</v>
       </c>
-      <c r="O55" s="1">
-        <v>4</v>
-      </c>
-      <c r="P55" s="1">
-        <v>1</v>
+      <c r="O55" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P55" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q55" s="3" t="s">
         <v>231</v>
@@ -4332,11 +4356,11 @@
       <c r="N56" s="1">
         <v>100</v>
       </c>
-      <c r="O56" s="1">
-        <v>4</v>
-      </c>
-      <c r="P56" s="1">
-        <v>1</v>
+      <c r="O56" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P56" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q56" s="3" t="s">
         <v>231</v>
@@ -4388,11 +4412,11 @@
       <c r="N57" s="1">
         <v>100</v>
       </c>
-      <c r="O57" s="1">
-        <v>4</v>
-      </c>
-      <c r="P57" s="1">
-        <v>1</v>
+      <c r="O57" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P57" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q57" s="3" t="s">
         <v>231</v>
@@ -4444,11 +4468,11 @@
       <c r="N58" s="1">
         <v>100</v>
       </c>
-      <c r="O58" s="1">
-        <v>4</v>
-      </c>
-      <c r="P58" s="1">
-        <v>1</v>
+      <c r="O58" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P58" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q58" s="3" t="s">
         <v>231</v>
@@ -4500,11 +4524,11 @@
       <c r="N59" s="1">
         <v>100</v>
       </c>
-      <c r="O59" s="1">
-        <v>4</v>
-      </c>
-      <c r="P59" s="1">
-        <v>1</v>
+      <c r="O59" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P59" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q59" s="3" t="s">
         <v>231</v>
@@ -4556,11 +4580,11 @@
       <c r="N60" s="1">
         <v>100</v>
       </c>
-      <c r="O60" s="1">
-        <v>4</v>
-      </c>
-      <c r="P60" s="1">
-        <v>1</v>
+      <c r="O60" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P60" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q60" s="3" t="s">
         <v>231</v>
@@ -4612,11 +4636,11 @@
       <c r="N61" s="1">
         <v>100</v>
       </c>
-      <c r="O61" s="1">
-        <v>4</v>
-      </c>
-      <c r="P61" s="1">
-        <v>1</v>
+      <c r="O61" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P61" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q61" s="3" t="s">
         <v>231</v>
@@ -4668,11 +4692,11 @@
       <c r="N62" s="1">
         <v>100</v>
       </c>
-      <c r="O62" s="1">
-        <v>4</v>
-      </c>
-      <c r="P62" s="1">
-        <v>1</v>
+      <c r="O62" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P62" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q62" s="3" t="s">
         <v>231</v>
@@ -4724,11 +4748,11 @@
       <c r="N63" s="1">
         <v>100</v>
       </c>
-      <c r="O63" s="1">
-        <v>4</v>
-      </c>
-      <c r="P63" s="1">
-        <v>1</v>
+      <c r="O63" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P63" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q63" s="3" t="s">
         <v>231</v>
@@ -4780,11 +4804,11 @@
       <c r="N64" s="1">
         <v>100</v>
       </c>
-      <c r="O64" s="1">
-        <v>4</v>
-      </c>
-      <c r="P64" s="1">
-        <v>1</v>
+      <c r="O64" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P64" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q64" s="3" t="s">
         <v>231</v>
@@ -4836,11 +4860,11 @@
       <c r="N65" s="1">
         <v>100</v>
       </c>
-      <c r="O65" s="1">
-        <v>4</v>
-      </c>
-      <c r="P65" s="1">
-        <v>1</v>
+      <c r="O65" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P65" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q65" s="3" t="s">
         <v>231</v>
@@ -4892,11 +4916,11 @@
       <c r="N66" s="1">
         <v>100</v>
       </c>
-      <c r="O66" s="1">
-        <v>4</v>
-      </c>
-      <c r="P66" s="1">
-        <v>1</v>
+      <c r="O66" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P66" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q66" s="3" t="s">
         <v>231</v>
@@ -4948,11 +4972,11 @@
       <c r="N67" s="1">
         <v>100</v>
       </c>
-      <c r="O67" s="1">
-        <v>4</v>
-      </c>
-      <c r="P67" s="1">
-        <v>1</v>
+      <c r="O67" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P67" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q67" s="3" t="s">
         <v>231</v>
@@ -5004,11 +5028,11 @@
       <c r="N68" s="1">
         <v>100</v>
       </c>
-      <c r="O68" s="1">
-        <v>4</v>
-      </c>
-      <c r="P68" s="1">
-        <v>1</v>
+      <c r="O68" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P68" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q68" s="3" t="s">
         <v>231</v>
@@ -5060,11 +5084,11 @@
       <c r="N69" s="1">
         <v>100</v>
       </c>
-      <c r="O69" s="1">
-        <v>4</v>
-      </c>
-      <c r="P69" s="1">
-        <v>1</v>
+      <c r="O69" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P69" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q69" s="3" t="s">
         <v>231</v>
@@ -5116,11 +5140,11 @@
       <c r="N70" s="1">
         <v>100</v>
       </c>
-      <c r="O70" s="1">
-        <v>4</v>
-      </c>
-      <c r="P70" s="1">
-        <v>1</v>
+      <c r="O70" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P70" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q70" s="3" t="s">
         <v>231</v>
@@ -5172,11 +5196,11 @@
       <c r="N71" s="1">
         <v>100</v>
       </c>
-      <c r="O71" s="1">
-        <v>4</v>
-      </c>
-      <c r="P71" s="1">
-        <v>1</v>
+      <c r="O71" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P71" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q71" s="3" t="s">
         <v>231</v>
@@ -5228,11 +5252,11 @@
       <c r="N72" s="1">
         <v>100</v>
       </c>
-      <c r="O72" s="1">
-        <v>4</v>
-      </c>
-      <c r="P72" s="1">
-        <v>1</v>
+      <c r="O72" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P72" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q72" s="3" t="s">
         <v>231</v>
@@ -5284,11 +5308,11 @@
       <c r="N73" s="1">
         <v>100</v>
       </c>
-      <c r="O73" s="1">
-        <v>4</v>
-      </c>
-      <c r="P73" s="1">
-        <v>1</v>
+      <c r="O73" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P73" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q73" s="3" t="s">
         <v>231</v>
@@ -5340,11 +5364,11 @@
       <c r="N74" s="1">
         <v>100</v>
       </c>
-      <c r="O74" s="1">
-        <v>4</v>
-      </c>
-      <c r="P74" s="1">
-        <v>1</v>
+      <c r="O74" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P74" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q74" s="3" t="s">
         <v>231</v>
@@ -5396,11 +5420,11 @@
       <c r="N75" s="1">
         <v>100</v>
       </c>
-      <c r="O75" s="1">
-        <v>4</v>
-      </c>
-      <c r="P75" s="1">
-        <v>1</v>
+      <c r="O75" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P75" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q75" s="3" t="s">
         <v>231</v>
@@ -5452,11 +5476,11 @@
       <c r="N76" s="1">
         <v>100</v>
       </c>
-      <c r="O76" s="1">
-        <v>4</v>
-      </c>
-      <c r="P76" s="1">
-        <v>1</v>
+      <c r="O76" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P76" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q76" s="3" t="s">
         <v>231</v>
@@ -5508,11 +5532,11 @@
       <c r="N77" s="1">
         <v>100</v>
       </c>
-      <c r="O77" s="1">
-        <v>4</v>
-      </c>
-      <c r="P77" s="1">
-        <v>1</v>
+      <c r="O77" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P77" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q77" s="3" t="s">
         <v>231</v>
@@ -5564,11 +5588,11 @@
       <c r="N78" s="1">
         <v>100</v>
       </c>
-      <c r="O78" s="1">
-        <v>4</v>
-      </c>
-      <c r="P78" s="1">
-        <v>1</v>
+      <c r="O78" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P78" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q78" s="3" t="s">
         <v>231</v>
@@ -5620,11 +5644,11 @@
       <c r="N79" s="1">
         <v>100</v>
       </c>
-      <c r="O79" s="1">
-        <v>4</v>
-      </c>
-      <c r="P79" s="1">
-        <v>1</v>
+      <c r="O79" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P79" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q79" s="3" t="s">
         <v>231</v>
@@ -5676,11 +5700,11 @@
       <c r="N80" s="1">
         <v>100</v>
       </c>
-      <c r="O80" s="1">
-        <v>4</v>
-      </c>
-      <c r="P80" s="1">
-        <v>1</v>
+      <c r="O80" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P80" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q80" s="3" t="s">
         <v>231</v>
@@ -5732,11 +5756,11 @@
       <c r="N81" s="1">
         <v>100</v>
       </c>
-      <c r="O81" s="1">
-        <v>4</v>
-      </c>
-      <c r="P81" s="1">
-        <v>1</v>
+      <c r="O81" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P81" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q81" s="3" t="s">
         <v>231</v>
@@ -5788,11 +5812,11 @@
       <c r="N82" s="1">
         <v>100</v>
       </c>
-      <c r="O82" s="1">
-        <v>4</v>
-      </c>
-      <c r="P82" s="1">
-        <v>1</v>
+      <c r="O82" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P82" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q82" s="3" t="s">
         <v>231</v>
@@ -5844,11 +5868,11 @@
       <c r="N83" s="1">
         <v>100</v>
       </c>
-      <c r="O83" s="1">
-        <v>4</v>
-      </c>
-      <c r="P83" s="1">
-        <v>1</v>
+      <c r="O83" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P83" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q83" s="3" t="s">
         <v>231</v>
@@ -5900,11 +5924,11 @@
       <c r="N84" s="1">
         <v>100</v>
       </c>
-      <c r="O84" s="1">
-        <v>4</v>
-      </c>
-      <c r="P84" s="1">
-        <v>1</v>
+      <c r="O84" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P84" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q84" s="3" t="s">
         <v>231</v>
@@ -5956,11 +5980,11 @@
       <c r="N85" s="1">
         <v>100</v>
       </c>
-      <c r="O85" s="1">
-        <v>4</v>
-      </c>
-      <c r="P85" s="1">
-        <v>1</v>
+      <c r="O85" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P85" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q85" s="3" t="s">
         <v>231</v>
@@ -6012,11 +6036,11 @@
       <c r="N86" s="1">
         <v>100</v>
       </c>
-      <c r="O86" s="1">
-        <v>4</v>
-      </c>
-      <c r="P86" s="1">
-        <v>1</v>
+      <c r="O86" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P86" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q86" s="3" t="s">
         <v>231</v>
@@ -6068,11 +6092,11 @@
       <c r="N87" s="1">
         <v>100</v>
       </c>
-      <c r="O87" s="1">
-        <v>4</v>
-      </c>
-      <c r="P87" s="1">
-        <v>1</v>
+      <c r="O87" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P87" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q87" s="3" t="s">
         <v>231</v>
@@ -6124,11 +6148,11 @@
       <c r="N88" s="1">
         <v>100</v>
       </c>
-      <c r="O88" s="1">
-        <v>4</v>
-      </c>
-      <c r="P88" s="1">
-        <v>1</v>
+      <c r="O88" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P88" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q88" s="3" t="s">
         <v>231</v>
@@ -6180,11 +6204,11 @@
       <c r="N89" s="1">
         <v>100</v>
       </c>
-      <c r="O89" s="1">
-        <v>4</v>
-      </c>
-      <c r="P89" s="1">
-        <v>1</v>
+      <c r="O89" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P89" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q89" s="3" t="s">
         <v>231</v>
@@ -6236,11 +6260,11 @@
       <c r="N90" s="1">
         <v>100</v>
       </c>
-      <c r="O90" s="1">
-        <v>4</v>
-      </c>
-      <c r="P90" s="1">
-        <v>1</v>
+      <c r="O90" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P90" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q90" s="3" t="s">
         <v>231</v>
@@ -6292,11 +6316,11 @@
       <c r="N91" s="1">
         <v>100</v>
       </c>
-      <c r="O91" s="1">
-        <v>4</v>
-      </c>
-      <c r="P91" s="1">
-        <v>1</v>
+      <c r="O91" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P91" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q91" s="3" t="s">
         <v>231</v>
@@ -6348,11 +6372,11 @@
       <c r="N92" s="1">
         <v>100</v>
       </c>
-      <c r="O92" s="1">
-        <v>4</v>
-      </c>
-      <c r="P92" s="1">
-        <v>1</v>
+      <c r="O92" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P92" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q92" s="3" t="s">
         <v>231</v>
@@ -6404,11 +6428,11 @@
       <c r="N93" s="1">
         <v>100</v>
       </c>
-      <c r="O93" s="1">
-        <v>4</v>
-      </c>
-      <c r="P93" s="1">
-        <v>1</v>
+      <c r="O93" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P93" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q93" s="3" t="s">
         <v>231</v>
@@ -6460,11 +6484,11 @@
       <c r="N94" s="1">
         <v>100</v>
       </c>
-      <c r="O94" s="1">
-        <v>4</v>
-      </c>
-      <c r="P94" s="1">
-        <v>1</v>
+      <c r="O94" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P94" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q94" s="3" t="s">
         <v>231</v>
@@ -6516,11 +6540,11 @@
       <c r="N95" s="1">
         <v>100</v>
       </c>
-      <c r="O95" s="1">
-        <v>4</v>
-      </c>
-      <c r="P95" s="1">
-        <v>1</v>
+      <c r="O95" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P95" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q95" s="3" t="s">
         <v>231</v>
@@ -6572,11 +6596,11 @@
       <c r="N96" s="1">
         <v>100</v>
       </c>
-      <c r="O96" s="1">
-        <v>4</v>
-      </c>
-      <c r="P96" s="1">
-        <v>1</v>
+      <c r="O96" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P96" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q96" s="3" t="s">
         <v>231</v>
@@ -6628,11 +6652,11 @@
       <c r="N97" s="1">
         <v>100</v>
       </c>
-      <c r="O97" s="1">
-        <v>4</v>
-      </c>
-      <c r="P97" s="1">
-        <v>1</v>
+      <c r="O97" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P97" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q97" s="3" t="s">
         <v>231</v>
@@ -6684,11 +6708,11 @@
       <c r="N98" s="1">
         <v>100</v>
       </c>
-      <c r="O98" s="1">
-        <v>4</v>
-      </c>
-      <c r="P98" s="1">
-        <v>1</v>
+      <c r="O98" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P98" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q98" s="3" t="s">
         <v>231</v>
@@ -6740,11 +6764,11 @@
       <c r="N99" s="1">
         <v>100</v>
       </c>
-      <c r="O99" s="1">
-        <v>4</v>
-      </c>
-      <c r="P99" s="1">
-        <v>1</v>
+      <c r="O99" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P99" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q99" s="3" t="s">
         <v>231</v>
@@ -6796,11 +6820,11 @@
       <c r="N100" s="1">
         <v>100</v>
       </c>
-      <c r="O100" s="1">
-        <v>4</v>
-      </c>
-      <c r="P100" s="1">
-        <v>1</v>
+      <c r="O100" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P100" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q100" s="3" t="s">
         <v>231</v>
@@ -6852,11 +6876,11 @@
       <c r="N101" s="1">
         <v>100</v>
       </c>
-      <c r="O101" s="1">
-        <v>4</v>
-      </c>
-      <c r="P101" s="1">
-        <v>1</v>
+      <c r="O101" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P101" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q101" s="3" t="s">
         <v>231</v>
@@ -6908,11 +6932,11 @@
       <c r="N102" s="1">
         <v>100</v>
       </c>
-      <c r="O102" s="1">
-        <v>4</v>
-      </c>
-      <c r="P102" s="1">
-        <v>1</v>
+      <c r="O102" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P102" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q102" s="3" t="s">
         <v>231</v>
@@ -6964,11 +6988,11 @@
       <c r="N103" s="1">
         <v>100</v>
       </c>
-      <c r="O103" s="1">
-        <v>4</v>
-      </c>
-      <c r="P103" s="1">
-        <v>1</v>
+      <c r="O103" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P103" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q103" s="3" t="s">
         <v>231</v>
@@ -7020,11 +7044,11 @@
       <c r="N104" s="1">
         <v>100</v>
       </c>
-      <c r="O104" s="1">
-        <v>4</v>
-      </c>
-      <c r="P104" s="1">
-        <v>1</v>
+      <c r="O104" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P104" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q104" s="3" t="s">
         <v>231</v>
@@ -7076,11 +7100,11 @@
       <c r="N105" s="1">
         <v>100</v>
       </c>
-      <c r="O105" s="1">
-        <v>4</v>
-      </c>
-      <c r="P105" s="1">
-        <v>1</v>
+      <c r="O105" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P105" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q105" s="3" t="s">
         <v>231</v>
@@ -7132,11 +7156,11 @@
       <c r="N106" s="1">
         <v>100</v>
       </c>
-      <c r="O106" s="1">
-        <v>4</v>
-      </c>
-      <c r="P106" s="1">
-        <v>1</v>
+      <c r="O106" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P106" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q106" s="3" t="s">
         <v>231</v>
@@ -7188,11 +7212,11 @@
       <c r="N107" s="1">
         <v>100</v>
       </c>
-      <c r="O107" s="1">
-        <v>4</v>
-      </c>
-      <c r="P107" s="1">
-        <v>1</v>
+      <c r="O107" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P107" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q107" s="3" t="s">
         <v>231</v>
@@ -7244,11 +7268,11 @@
       <c r="N108" s="1">
         <v>100</v>
       </c>
-      <c r="O108" s="1">
-        <v>4</v>
-      </c>
-      <c r="P108" s="1">
-        <v>1</v>
+      <c r="O108" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P108" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q108" s="3" t="s">
         <v>231</v>
@@ -7300,11 +7324,11 @@
       <c r="N109" s="1">
         <v>100</v>
       </c>
-      <c r="O109" s="1">
-        <v>4</v>
-      </c>
-      <c r="P109" s="1">
-        <v>1</v>
+      <c r="O109" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P109" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q109" s="3" t="s">
         <v>231</v>
@@ -7356,11 +7380,11 @@
       <c r="N110" s="1">
         <v>100</v>
       </c>
-      <c r="O110" s="1">
-        <v>4</v>
-      </c>
-      <c r="P110" s="1">
-        <v>1</v>
+      <c r="O110" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P110" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q110" s="3" t="s">
         <v>231</v>
@@ -7412,11 +7436,11 @@
       <c r="N111" s="1">
         <v>100</v>
       </c>
-      <c r="O111" s="1">
-        <v>4</v>
-      </c>
-      <c r="P111" s="1">
-        <v>1</v>
+      <c r="O111" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P111" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q111" s="3" t="s">
         <v>231</v>
@@ -7468,11 +7492,11 @@
       <c r="N112" s="1">
         <v>100</v>
       </c>
-      <c r="O112" s="1">
-        <v>4</v>
-      </c>
-      <c r="P112" s="1">
-        <v>1</v>
+      <c r="O112" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P112" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q112" s="3" t="s">
         <v>231</v>
@@ -7524,11 +7548,11 @@
       <c r="N113" s="1">
         <v>100</v>
       </c>
-      <c r="O113" s="1">
-        <v>4</v>
-      </c>
-      <c r="P113" s="1">
-        <v>1</v>
+      <c r="O113" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P113" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q113" s="3" t="s">
         <v>231</v>
@@ -7580,11 +7604,11 @@
       <c r="N114" s="1">
         <v>100</v>
       </c>
-      <c r="O114" s="1">
-        <v>4</v>
-      </c>
-      <c r="P114" s="1">
-        <v>1</v>
+      <c r="O114" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P114" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q114" s="3" t="s">
         <v>231</v>
@@ -7636,11 +7660,11 @@
       <c r="N115" s="1">
         <v>100</v>
       </c>
-      <c r="O115" s="1">
-        <v>4</v>
-      </c>
-      <c r="P115" s="1">
-        <v>1</v>
+      <c r="O115" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P115" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q115" s="3" t="s">
         <v>231</v>
@@ -7692,11 +7716,11 @@
       <c r="N116" s="1">
         <v>100</v>
       </c>
-      <c r="O116" s="1">
-        <v>4</v>
-      </c>
-      <c r="P116" s="1">
-        <v>1</v>
+      <c r="O116" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P116" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q116" s="3" t="s">
         <v>231</v>
@@ -7748,11 +7772,11 @@
       <c r="N117" s="1">
         <v>100</v>
       </c>
-      <c r="O117" s="1">
-        <v>4</v>
-      </c>
-      <c r="P117" s="1">
-        <v>1</v>
+      <c r="O117" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P117" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q117" s="3" t="s">
         <v>231</v>
@@ -7804,11 +7828,11 @@
       <c r="N118" s="1">
         <v>100</v>
       </c>
-      <c r="O118" s="1">
-        <v>4</v>
-      </c>
-      <c r="P118" s="1">
-        <v>1</v>
+      <c r="O118" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P118" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q118" s="3" t="s">
         <v>231</v>
@@ -7860,11 +7884,11 @@
       <c r="N119" s="1">
         <v>100</v>
       </c>
-      <c r="O119" s="1">
-        <v>4</v>
-      </c>
-      <c r="P119" s="1">
-        <v>1</v>
+      <c r="O119" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P119" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q119" s="3" t="s">
         <v>231</v>
@@ -7916,11 +7940,11 @@
       <c r="N120" s="1">
         <v>100</v>
       </c>
-      <c r="O120" s="1">
-        <v>4</v>
-      </c>
-      <c r="P120" s="1">
-        <v>1</v>
+      <c r="O120" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P120" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q120" s="3" t="s">
         <v>231</v>
@@ -7972,11 +7996,11 @@
       <c r="N121" s="1">
         <v>100</v>
       </c>
-      <c r="O121" s="1">
-        <v>4</v>
-      </c>
-      <c r="P121" s="1">
-        <v>1</v>
+      <c r="O121" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P121" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q121" s="3" t="s">
         <v>231</v>
@@ -8028,11 +8052,11 @@
       <c r="N122" s="1">
         <v>100</v>
       </c>
-      <c r="O122" s="1">
-        <v>4</v>
-      </c>
-      <c r="P122" s="1">
-        <v>1</v>
+      <c r="O122" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P122" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q122" s="3" t="s">
         <v>231</v>
@@ -8084,11 +8108,11 @@
       <c r="N123" s="1">
         <v>100</v>
       </c>
-      <c r="O123" s="1">
-        <v>4</v>
-      </c>
-      <c r="P123" s="1">
-        <v>1</v>
+      <c r="O123" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P123" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q123" s="3" t="s">
         <v>231</v>
@@ -8140,11 +8164,11 @@
       <c r="N124" s="1">
         <v>100</v>
       </c>
-      <c r="O124" s="1">
-        <v>4</v>
-      </c>
-      <c r="P124" s="1">
-        <v>1</v>
+      <c r="O124" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P124" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q124" s="3" t="s">
         <v>231</v>
@@ -8196,11 +8220,11 @@
       <c r="N125" s="1">
         <v>100</v>
       </c>
-      <c r="O125" s="1">
-        <v>4</v>
-      </c>
-      <c r="P125" s="1">
-        <v>1</v>
+      <c r="O125" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P125" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q125" s="3" t="s">
         <v>231</v>
@@ -8252,11 +8276,11 @@
       <c r="N126" s="1">
         <v>100</v>
       </c>
-      <c r="O126" s="1">
-        <v>4</v>
-      </c>
-      <c r="P126" s="1">
-        <v>1</v>
+      <c r="O126" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P126" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q126" s="3" t="s">
         <v>231</v>
@@ -8308,11 +8332,11 @@
       <c r="N127" s="1">
         <v>100</v>
       </c>
-      <c r="O127" s="1">
-        <v>4</v>
-      </c>
-      <c r="P127" s="1">
-        <v>1</v>
+      <c r="O127" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P127" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q127" s="3" t="s">
         <v>231</v>
@@ -8364,11 +8388,11 @@
       <c r="N128" s="1">
         <v>100</v>
       </c>
-      <c r="O128" s="1">
-        <v>4</v>
-      </c>
-      <c r="P128" s="1">
-        <v>1</v>
+      <c r="O128" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P128" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q128" s="3" t="s">
         <v>231</v>
@@ -8420,11 +8444,11 @@
       <c r="N129" s="1">
         <v>100</v>
       </c>
-      <c r="O129" s="1">
-        <v>4</v>
-      </c>
-      <c r="P129" s="1">
-        <v>1</v>
+      <c r="O129" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P129" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q129" s="3" t="s">
         <v>231</v>
@@ -8476,11 +8500,11 @@
       <c r="N130" s="1">
         <v>100</v>
       </c>
-      <c r="O130" s="1">
-        <v>4</v>
-      </c>
-      <c r="P130" s="1">
-        <v>1</v>
+      <c r="O130" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P130" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q130" s="3" t="s">
         <v>231</v>
@@ -8532,11 +8556,11 @@
       <c r="N131" s="1">
         <v>100</v>
       </c>
-      <c r="O131" s="1">
-        <v>4</v>
-      </c>
-      <c r="P131" s="1">
-        <v>1</v>
+      <c r="O131" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P131" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q131" s="3" t="s">
         <v>231</v>
@@ -8588,11 +8612,11 @@
       <c r="N132" s="1">
         <v>100</v>
       </c>
-      <c r="O132" s="1">
-        <v>4</v>
-      </c>
-      <c r="P132" s="1">
-        <v>1</v>
+      <c r="O132" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P132" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q132" s="3" t="s">
         <v>231</v>
@@ -8644,11 +8668,11 @@
       <c r="N133" s="1">
         <v>100</v>
       </c>
-      <c r="O133" s="1">
-        <v>4</v>
-      </c>
-      <c r="P133" s="1">
-        <v>1</v>
+      <c r="O133" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P133" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q133" s="3" t="s">
         <v>231</v>
@@ -8700,11 +8724,11 @@
       <c r="N134" s="1">
         <v>100</v>
       </c>
-      <c r="O134" s="1">
-        <v>4</v>
-      </c>
-      <c r="P134" s="1">
-        <v>1</v>
+      <c r="O134" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P134" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q134" s="3" t="s">
         <v>231</v>
@@ -8756,11 +8780,11 @@
       <c r="N135" s="1">
         <v>100</v>
       </c>
-      <c r="O135" s="1">
-        <v>4</v>
-      </c>
-      <c r="P135" s="1">
-        <v>1</v>
+      <c r="O135" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P135" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q135" s="3" t="s">
         <v>231</v>
@@ -8812,11 +8836,11 @@
       <c r="N136" s="1">
         <v>100</v>
       </c>
-      <c r="O136" s="1">
-        <v>4</v>
-      </c>
-      <c r="P136" s="1">
-        <v>1</v>
+      <c r="O136" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P136" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q136" s="3" t="s">
         <v>231</v>
@@ -8868,11 +8892,11 @@
       <c r="N137" s="1">
         <v>100</v>
       </c>
-      <c r="O137" s="1">
-        <v>4</v>
-      </c>
-      <c r="P137" s="1">
-        <v>1</v>
+      <c r="O137" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P137" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q137" s="3" t="s">
         <v>231</v>
@@ -8924,11 +8948,11 @@
       <c r="N138" s="1">
         <v>100</v>
       </c>
-      <c r="O138" s="1">
-        <v>4</v>
-      </c>
-      <c r="P138" s="1">
-        <v>1</v>
+      <c r="O138" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P138" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q138" s="3" t="s">
         <v>231</v>
@@ -8980,11 +9004,11 @@
       <c r="N139" s="1">
         <v>100</v>
       </c>
-      <c r="O139" s="1">
-        <v>4</v>
-      </c>
-      <c r="P139" s="1">
-        <v>1</v>
+      <c r="O139" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P139" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q139" s="3" t="s">
         <v>231</v>
@@ -9036,11 +9060,11 @@
       <c r="N140" s="1">
         <v>100</v>
       </c>
-      <c r="O140" s="1">
-        <v>4</v>
-      </c>
-      <c r="P140" s="1">
-        <v>1</v>
+      <c r="O140" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P140" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q140" s="3" t="s">
         <v>231</v>
@@ -9092,11 +9116,11 @@
       <c r="N141" s="1">
         <v>100</v>
       </c>
-      <c r="O141" s="1">
-        <v>4</v>
-      </c>
-      <c r="P141" s="1">
-        <v>1</v>
+      <c r="O141" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P141" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q141" s="3" t="s">
         <v>231</v>
@@ -9148,11 +9172,11 @@
       <c r="N142" s="1">
         <v>100</v>
       </c>
-      <c r="O142" s="1">
-        <v>4</v>
-      </c>
-      <c r="P142" s="1">
-        <v>1</v>
+      <c r="O142" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P142" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q142" s="3" t="s">
         <v>231</v>
@@ -9204,11 +9228,11 @@
       <c r="N143" s="1">
         <v>100</v>
       </c>
-      <c r="O143" s="1">
-        <v>4</v>
-      </c>
-      <c r="P143" s="1">
-        <v>1</v>
+      <c r="O143" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P143" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q143" s="3" t="s">
         <v>231</v>
@@ -9260,11 +9284,11 @@
       <c r="N144" s="1">
         <v>100</v>
       </c>
-      <c r="O144" s="1">
-        <v>4</v>
-      </c>
-      <c r="P144" s="1">
-        <v>1</v>
+      <c r="O144" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P144" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q144" s="3" t="s">
         <v>231</v>
@@ -9316,11 +9340,11 @@
       <c r="N145" s="1">
         <v>100</v>
       </c>
-      <c r="O145" s="1">
-        <v>4</v>
-      </c>
-      <c r="P145" s="1">
-        <v>1</v>
+      <c r="O145" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P145" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q145" s="3" t="s">
         <v>231</v>
@@ -9372,11 +9396,11 @@
       <c r="N146" s="1">
         <v>100</v>
       </c>
-      <c r="O146" s="1">
-        <v>4</v>
-      </c>
-      <c r="P146" s="1">
-        <v>1</v>
+      <c r="O146" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P146" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q146" s="3" t="s">
         <v>231</v>
@@ -9428,11 +9452,11 @@
       <c r="N147" s="1">
         <v>100</v>
       </c>
-      <c r="O147" s="1">
-        <v>4</v>
-      </c>
-      <c r="P147" s="1">
-        <v>1</v>
+      <c r="O147" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P147" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q147" s="3" t="s">
         <v>231</v>
@@ -9484,11 +9508,11 @@
       <c r="N148" s="1">
         <v>100</v>
       </c>
-      <c r="O148" s="1">
-        <v>4</v>
-      </c>
-      <c r="P148" s="1">
-        <v>1</v>
+      <c r="O148" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P148" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q148" s="3" t="s">
         <v>231</v>
@@ -9540,11 +9564,11 @@
       <c r="N149" s="1">
         <v>100</v>
       </c>
-      <c r="O149" s="1">
-        <v>4</v>
-      </c>
-      <c r="P149" s="1">
-        <v>1</v>
+      <c r="O149" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P149" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q149" s="3" t="s">
         <v>231</v>
@@ -9596,11 +9620,11 @@
       <c r="N150" s="1">
         <v>100</v>
       </c>
-      <c r="O150" s="1">
-        <v>4</v>
-      </c>
-      <c r="P150" s="1">
-        <v>1</v>
+      <c r="O150" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P150" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q150" s="3" t="s">
         <v>231</v>
@@ -9652,11 +9676,11 @@
       <c r="N151" s="1">
         <v>100</v>
       </c>
-      <c r="O151" s="1">
-        <v>4</v>
-      </c>
-      <c r="P151" s="1">
-        <v>1</v>
+      <c r="O151" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P151" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q151" s="3" t="s">
         <v>231</v>
@@ -9708,11 +9732,11 @@
       <c r="N152" s="1">
         <v>100</v>
       </c>
-      <c r="O152" s="1">
-        <v>4</v>
-      </c>
-      <c r="P152" s="1">
-        <v>1</v>
+      <c r="O152" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P152" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q152" s="3" t="s">
         <v>231</v>
@@ -9764,11 +9788,11 @@
       <c r="N153" s="1">
         <v>100</v>
       </c>
-      <c r="O153" s="1">
-        <v>4</v>
-      </c>
-      <c r="P153" s="1">
-        <v>1</v>
+      <c r="O153" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P153" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q153" s="3" t="s">
         <v>231</v>
@@ -9820,11 +9844,11 @@
       <c r="N154" s="1">
         <v>100</v>
       </c>
-      <c r="O154" s="1">
-        <v>4</v>
-      </c>
-      <c r="P154" s="1">
-        <v>1</v>
+      <c r="O154" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P154" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q154" s="3" t="s">
         <v>231</v>
@@ -9876,11 +9900,11 @@
       <c r="N155" s="1">
         <v>100</v>
       </c>
-      <c r="O155" s="1">
-        <v>4</v>
-      </c>
-      <c r="P155" s="1">
-        <v>1</v>
+      <c r="O155" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P155" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q155" s="3" t="s">
         <v>231</v>
@@ -9932,11 +9956,11 @@
       <c r="N156" s="1">
         <v>100</v>
       </c>
-      <c r="O156" s="1">
-        <v>4</v>
-      </c>
-      <c r="P156" s="1">
-        <v>1</v>
+      <c r="O156" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P156" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q156" s="3" t="s">
         <v>231</v>
@@ -9988,11 +10012,11 @@
       <c r="N157" s="1">
         <v>100</v>
       </c>
-      <c r="O157" s="1">
-        <v>4</v>
-      </c>
-      <c r="P157" s="1">
-        <v>1</v>
+      <c r="O157" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P157" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q157" s="3" t="s">
         <v>231</v>
@@ -10044,11 +10068,11 @@
       <c r="N158" s="1">
         <v>100</v>
       </c>
-      <c r="O158" s="1">
-        <v>4</v>
-      </c>
-      <c r="P158" s="1">
-        <v>1</v>
+      <c r="O158" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P158" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q158" s="3" t="s">
         <v>231</v>
@@ -10100,11 +10124,11 @@
       <c r="N159" s="1">
         <v>100</v>
       </c>
-      <c r="O159" s="1">
-        <v>4</v>
-      </c>
-      <c r="P159" s="1">
-        <v>1</v>
+      <c r="O159" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P159" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q159" s="3" t="s">
         <v>231</v>
@@ -10156,11 +10180,11 @@
       <c r="N160" s="1">
         <v>100</v>
       </c>
-      <c r="O160" s="1">
-        <v>4</v>
-      </c>
-      <c r="P160" s="1">
-        <v>1</v>
+      <c r="O160" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P160" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q160" s="3" t="s">
         <v>231</v>
@@ -10212,11 +10236,11 @@
       <c r="N161" s="1">
         <v>100</v>
       </c>
-      <c r="O161" s="1">
-        <v>4</v>
-      </c>
-      <c r="P161" s="1">
-        <v>1</v>
+      <c r="O161" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P161" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q161" s="3" t="s">
         <v>231</v>
@@ -10268,11 +10292,11 @@
       <c r="N162" s="1">
         <v>100</v>
       </c>
-      <c r="O162" s="1">
-        <v>4</v>
-      </c>
-      <c r="P162" s="1">
-        <v>1</v>
+      <c r="O162" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P162" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q162" s="3" t="s">
         <v>231</v>
@@ -10324,11 +10348,11 @@
       <c r="N163" s="1">
         <v>100</v>
       </c>
-      <c r="O163" s="1">
-        <v>4</v>
-      </c>
-      <c r="P163" s="1">
-        <v>1</v>
+      <c r="O163" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P163" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q163" s="3" t="s">
         <v>231</v>
@@ -10380,11 +10404,11 @@
       <c r="N164" s="1">
         <v>100</v>
       </c>
-      <c r="O164" s="1">
-        <v>4</v>
-      </c>
-      <c r="P164" s="1">
-        <v>1</v>
+      <c r="O164" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P164" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="Q164" s="3" t="s">
         <v>231</v>

--- a/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C085DEED-8373-4197-8911-5D7376DBF8C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8B99D75-F2AD-42C0-B437-ED262E5E8304}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -852,14 +852,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>110001:180_110002:550_110003:200</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>110001:300_110002:750_110003:550</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>MAP&lt;INT:INT&gt;_S_C</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -872,14 +864,22 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>110001:99_110002:99_110003:99_110004:99</t>
+    <t>110001:101_110002:101_110003:101_110004:101</t>
+  </si>
+  <si>
+    <t>0:0</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>110001:101_110002:101_110003:101_110004:101</t>
-  </si>
-  <si>
-    <t>0:0</t>
+    <t>110001:1101_110002:1102_110003:1103_110004:1104</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>110001:300_110002:550_110003:200</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>110001:550_110002:750_110003:550</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1288,10 +1288,10 @@
         <v>220</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="Q2" s="1" t="s">
         <v>227</v>
@@ -1483,10 +1483,10 @@
         <v>150</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="Q5" s="3" t="s">
         <v>231</v>
@@ -1548,10 +1548,10 @@
         <v>200</v>
       </c>
       <c r="O6" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P6" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q6" s="3" t="s">
         <v>231</v>
@@ -1604,10 +1604,10 @@
         <v>300</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P7" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q7" s="3" t="s">
         <v>231</v>
@@ -1660,10 +1660,10 @@
         <v>400</v>
       </c>
       <c r="O8" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P8" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q8" s="3" t="s">
         <v>231</v>
@@ -1716,10 +1716,10 @@
         <v>500</v>
       </c>
       <c r="O9" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P9" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q9" s="3" t="s">
         <v>231</v>
@@ -1772,10 +1772,10 @@
         <v>600</v>
       </c>
       <c r="O10" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P10" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q10" s="3" t="s">
         <v>231</v>
@@ -1828,10 +1828,10 @@
         <v>100</v>
       </c>
       <c r="O11" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P11" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q11" s="3" t="s">
         <v>231</v>
@@ -1884,10 +1884,10 @@
         <v>100</v>
       </c>
       <c r="O12" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P12" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q12" s="3" t="s">
         <v>231</v>
@@ -1940,10 +1940,10 @@
         <v>100</v>
       </c>
       <c r="O13" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P13" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q13" s="3" t="s">
         <v>231</v>
@@ -1996,10 +1996,10 @@
         <v>100</v>
       </c>
       <c r="O14" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P14" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>231</v>
@@ -2055,7 +2055,7 @@
         <v>256</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="Q15" s="3" t="s">
         <v>231</v>
@@ -2067,10 +2067,10 @@
         <v>250</v>
       </c>
       <c r="T15" s="1" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="U15" s="1" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.15">
@@ -2117,10 +2117,10 @@
         <v>100</v>
       </c>
       <c r="O16" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P16" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q16" s="3" t="s">
         <v>231</v>
@@ -2173,10 +2173,10 @@
         <v>100</v>
       </c>
       <c r="O17" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P17" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q17" s="3" t="s">
         <v>231</v>
@@ -2229,10 +2229,10 @@
         <v>100</v>
       </c>
       <c r="O18" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P18" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q18" s="3" t="s">
         <v>231</v>
@@ -2285,10 +2285,10 @@
         <v>100</v>
       </c>
       <c r="O19" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P19" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q19" s="3" t="s">
         <v>231</v>
@@ -2341,10 +2341,10 @@
         <v>100</v>
       </c>
       <c r="O20" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P20" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q20" s="3" t="s">
         <v>231</v>
@@ -2397,10 +2397,10 @@
         <v>100</v>
       </c>
       <c r="O21" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P21" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q21" s="3" t="s">
         <v>231</v>
@@ -2453,10 +2453,10 @@
         <v>100</v>
       </c>
       <c r="O22" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P22" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q22" s="3" t="s">
         <v>231</v>
@@ -2509,10 +2509,10 @@
         <v>100</v>
       </c>
       <c r="O23" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P23" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q23" s="3" t="s">
         <v>231</v>
@@ -2565,10 +2565,10 @@
         <v>100</v>
       </c>
       <c r="O24" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P24" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q24" s="3" t="s">
         <v>231</v>
@@ -2621,10 +2621,10 @@
         <v>100</v>
       </c>
       <c r="O25" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P25" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q25" s="3" t="s">
         <v>231</v>
@@ -2677,10 +2677,10 @@
         <v>100</v>
       </c>
       <c r="O26" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P26" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q26" s="3" t="s">
         <v>231</v>
@@ -2733,10 +2733,10 @@
         <v>100</v>
       </c>
       <c r="O27" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P27" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q27" s="3" t="s">
         <v>231</v>
@@ -2789,10 +2789,10 @@
         <v>100</v>
       </c>
       <c r="O28" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P28" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q28" s="3" t="s">
         <v>231</v>
@@ -2845,10 +2845,10 @@
         <v>100</v>
       </c>
       <c r="O29" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P29" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q29" s="3" t="s">
         <v>231</v>
@@ -2901,10 +2901,10 @@
         <v>100</v>
       </c>
       <c r="O30" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P30" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q30" s="3" t="s">
         <v>231</v>
@@ -2957,10 +2957,10 @@
         <v>100</v>
       </c>
       <c r="O31" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P31" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q31" s="3" t="s">
         <v>231</v>
@@ -3013,10 +3013,10 @@
         <v>100</v>
       </c>
       <c r="O32" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P32" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q32" s="3" t="s">
         <v>231</v>
@@ -3069,10 +3069,10 @@
         <v>100</v>
       </c>
       <c r="O33" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P33" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q33" s="3" t="s">
         <v>231</v>
@@ -3125,10 +3125,10 @@
         <v>100</v>
       </c>
       <c r="O34" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P34" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q34" s="3" t="s">
         <v>231</v>
@@ -3181,10 +3181,10 @@
         <v>100</v>
       </c>
       <c r="O35" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P35" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q35" s="3" t="s">
         <v>231</v>
@@ -3237,10 +3237,10 @@
         <v>100</v>
       </c>
       <c r="O36" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P36" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q36" s="3" t="s">
         <v>231</v>
@@ -3293,10 +3293,10 @@
         <v>100</v>
       </c>
       <c r="O37" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P37" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q37" s="3" t="s">
         <v>231</v>
@@ -3349,10 +3349,10 @@
         <v>100</v>
       </c>
       <c r="O38" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P38" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q38" s="3" t="s">
         <v>231</v>
@@ -3405,10 +3405,10 @@
         <v>100</v>
       </c>
       <c r="O39" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P39" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q39" s="3" t="s">
         <v>231</v>
@@ -3461,10 +3461,10 @@
         <v>100</v>
       </c>
       <c r="O40" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P40" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q40" s="3" t="s">
         <v>231</v>
@@ -3517,10 +3517,10 @@
         <v>100</v>
       </c>
       <c r="O41" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P41" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q41" s="3" t="s">
         <v>231</v>
@@ -3573,10 +3573,10 @@
         <v>100</v>
       </c>
       <c r="O42" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P42" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q42" s="3" t="s">
         <v>231</v>
@@ -3629,10 +3629,10 @@
         <v>100</v>
       </c>
       <c r="O43" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P43" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q43" s="3" t="s">
         <v>231</v>
@@ -3685,10 +3685,10 @@
         <v>100</v>
       </c>
       <c r="O44" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P44" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q44" s="3" t="s">
         <v>231</v>
@@ -3741,10 +3741,10 @@
         <v>100</v>
       </c>
       <c r="O45" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P45" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q45" s="3" t="s">
         <v>231</v>
@@ -3797,10 +3797,10 @@
         <v>100</v>
       </c>
       <c r="O46" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P46" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q46" s="3" t="s">
         <v>231</v>
@@ -3853,10 +3853,10 @@
         <v>100</v>
       </c>
       <c r="O47" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P47" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q47" s="3" t="s">
         <v>231</v>
@@ -3909,10 +3909,10 @@
         <v>100</v>
       </c>
       <c r="O48" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P48" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q48" s="3" t="s">
         <v>231</v>
@@ -3965,10 +3965,10 @@
         <v>100</v>
       </c>
       <c r="O49" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P49" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q49" s="3" t="s">
         <v>231</v>
@@ -4021,10 +4021,10 @@
         <v>100</v>
       </c>
       <c r="O50" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P50" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q50" s="3" t="s">
         <v>231</v>
@@ -4077,10 +4077,10 @@
         <v>100</v>
       </c>
       <c r="O51" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P51" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q51" s="3" t="s">
         <v>231</v>
@@ -4133,10 +4133,10 @@
         <v>100</v>
       </c>
       <c r="O52" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P52" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q52" s="3" t="s">
         <v>231</v>
@@ -4189,10 +4189,10 @@
         <v>100</v>
       </c>
       <c r="O53" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P53" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q53" s="3" t="s">
         <v>231</v>
@@ -4245,10 +4245,10 @@
         <v>100</v>
       </c>
       <c r="O54" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P54" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q54" s="3" t="s">
         <v>231</v>
@@ -4301,10 +4301,10 @@
         <v>100</v>
       </c>
       <c r="O55" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P55" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q55" s="3" t="s">
         <v>231</v>
@@ -4357,10 +4357,10 @@
         <v>100</v>
       </c>
       <c r="O56" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P56" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q56" s="3" t="s">
         <v>231</v>
@@ -4413,10 +4413,10 @@
         <v>100</v>
       </c>
       <c r="O57" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P57" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q57" s="3" t="s">
         <v>231</v>
@@ -4469,10 +4469,10 @@
         <v>100</v>
       </c>
       <c r="O58" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P58" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q58" s="3" t="s">
         <v>231</v>
@@ -4525,10 +4525,10 @@
         <v>100</v>
       </c>
       <c r="O59" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P59" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q59" s="3" t="s">
         <v>231</v>
@@ -4581,10 +4581,10 @@
         <v>100</v>
       </c>
       <c r="O60" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P60" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q60" s="3" t="s">
         <v>231</v>
@@ -4637,10 +4637,10 @@
         <v>100</v>
       </c>
       <c r="O61" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P61" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q61" s="3" t="s">
         <v>231</v>
@@ -4693,10 +4693,10 @@
         <v>100</v>
       </c>
       <c r="O62" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P62" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q62" s="3" t="s">
         <v>231</v>
@@ -4749,10 +4749,10 @@
         <v>100</v>
       </c>
       <c r="O63" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P63" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q63" s="3" t="s">
         <v>231</v>
@@ -4805,10 +4805,10 @@
         <v>100</v>
       </c>
       <c r="O64" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P64" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q64" s="3" t="s">
         <v>231</v>
@@ -4861,10 +4861,10 @@
         <v>100</v>
       </c>
       <c r="O65" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P65" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q65" s="3" t="s">
         <v>231</v>
@@ -4917,10 +4917,10 @@
         <v>100</v>
       </c>
       <c r="O66" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P66" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q66" s="3" t="s">
         <v>231</v>
@@ -4973,10 +4973,10 @@
         <v>100</v>
       </c>
       <c r="O67" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P67" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q67" s="3" t="s">
         <v>231</v>
@@ -5029,10 +5029,10 @@
         <v>100</v>
       </c>
       <c r="O68" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P68" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q68" s="3" t="s">
         <v>231</v>
@@ -5085,10 +5085,10 @@
         <v>100</v>
       </c>
       <c r="O69" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P69" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q69" s="3" t="s">
         <v>231</v>
@@ -5141,10 +5141,10 @@
         <v>100</v>
       </c>
       <c r="O70" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P70" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q70" s="3" t="s">
         <v>231</v>
@@ -5197,10 +5197,10 @@
         <v>100</v>
       </c>
       <c r="O71" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P71" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q71" s="3" t="s">
         <v>231</v>
@@ -5253,10 +5253,10 @@
         <v>100</v>
       </c>
       <c r="O72" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P72" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q72" s="3" t="s">
         <v>231</v>
@@ -5309,10 +5309,10 @@
         <v>100</v>
       </c>
       <c r="O73" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P73" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q73" s="3" t="s">
         <v>231</v>
@@ -5365,10 +5365,10 @@
         <v>100</v>
       </c>
       <c r="O74" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P74" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q74" s="3" t="s">
         <v>231</v>
@@ -5421,10 +5421,10 @@
         <v>100</v>
       </c>
       <c r="O75" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P75" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q75" s="3" t="s">
         <v>231</v>
@@ -5477,10 +5477,10 @@
         <v>100</v>
       </c>
       <c r="O76" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P76" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q76" s="3" t="s">
         <v>231</v>
@@ -5533,10 +5533,10 @@
         <v>100</v>
       </c>
       <c r="O77" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P77" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q77" s="3" t="s">
         <v>231</v>
@@ -5589,10 +5589,10 @@
         <v>100</v>
       </c>
       <c r="O78" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P78" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q78" s="3" t="s">
         <v>231</v>
@@ -5645,10 +5645,10 @@
         <v>100</v>
       </c>
       <c r="O79" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P79" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q79" s="3" t="s">
         <v>231</v>
@@ -5701,10 +5701,10 @@
         <v>100</v>
       </c>
       <c r="O80" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P80" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q80" s="3" t="s">
         <v>231</v>
@@ -5757,10 +5757,10 @@
         <v>100</v>
       </c>
       <c r="O81" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P81" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q81" s="3" t="s">
         <v>231</v>
@@ -5813,10 +5813,10 @@
         <v>100</v>
       </c>
       <c r="O82" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P82" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q82" s="3" t="s">
         <v>231</v>
@@ -5869,10 +5869,10 @@
         <v>100</v>
       </c>
       <c r="O83" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P83" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q83" s="3" t="s">
         <v>231</v>
@@ -5925,10 +5925,10 @@
         <v>100</v>
       </c>
       <c r="O84" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P84" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q84" s="3" t="s">
         <v>231</v>
@@ -5981,10 +5981,10 @@
         <v>100</v>
       </c>
       <c r="O85" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P85" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q85" s="3" t="s">
         <v>231</v>
@@ -6037,10 +6037,10 @@
         <v>100</v>
       </c>
       <c r="O86" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P86" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q86" s="3" t="s">
         <v>231</v>
@@ -6093,10 +6093,10 @@
         <v>100</v>
       </c>
       <c r="O87" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P87" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q87" s="3" t="s">
         <v>231</v>
@@ -6149,10 +6149,10 @@
         <v>100</v>
       </c>
       <c r="O88" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P88" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q88" s="3" t="s">
         <v>231</v>
@@ -6205,10 +6205,10 @@
         <v>100</v>
       </c>
       <c r="O89" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P89" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q89" s="3" t="s">
         <v>231</v>
@@ -6261,10 +6261,10 @@
         <v>100</v>
       </c>
       <c r="O90" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P90" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q90" s="3" t="s">
         <v>231</v>
@@ -6317,10 +6317,10 @@
         <v>100</v>
       </c>
       <c r="O91" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P91" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q91" s="3" t="s">
         <v>231</v>
@@ -6373,10 +6373,10 @@
         <v>100</v>
       </c>
       <c r="O92" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P92" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q92" s="3" t="s">
         <v>231</v>
@@ -6429,10 +6429,10 @@
         <v>100</v>
       </c>
       <c r="O93" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P93" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q93" s="3" t="s">
         <v>231</v>
@@ -6485,10 +6485,10 @@
         <v>100</v>
       </c>
       <c r="O94" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P94" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q94" s="3" t="s">
         <v>231</v>
@@ -6541,10 +6541,10 @@
         <v>100</v>
       </c>
       <c r="O95" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P95" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q95" s="3" t="s">
         <v>231</v>
@@ -6597,10 +6597,10 @@
         <v>100</v>
       </c>
       <c r="O96" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P96" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q96" s="3" t="s">
         <v>231</v>
@@ -6653,10 +6653,10 @@
         <v>100</v>
       </c>
       <c r="O97" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P97" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q97" s="3" t="s">
         <v>231</v>
@@ -6709,10 +6709,10 @@
         <v>100</v>
       </c>
       <c r="O98" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P98" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q98" s="3" t="s">
         <v>231</v>
@@ -6765,10 +6765,10 @@
         <v>100</v>
       </c>
       <c r="O99" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P99" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q99" s="3" t="s">
         <v>231</v>
@@ -6821,10 +6821,10 @@
         <v>100</v>
       </c>
       <c r="O100" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P100" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q100" s="3" t="s">
         <v>231</v>
@@ -6877,10 +6877,10 @@
         <v>100</v>
       </c>
       <c r="O101" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P101" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q101" s="3" t="s">
         <v>231</v>
@@ -6933,10 +6933,10 @@
         <v>100</v>
       </c>
       <c r="O102" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P102" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q102" s="3" t="s">
         <v>231</v>
@@ -6989,10 +6989,10 @@
         <v>100</v>
       </c>
       <c r="O103" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P103" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q103" s="3" t="s">
         <v>231</v>
@@ -7045,10 +7045,10 @@
         <v>100</v>
       </c>
       <c r="O104" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P104" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q104" s="3" t="s">
         <v>231</v>
@@ -7101,10 +7101,10 @@
         <v>100</v>
       </c>
       <c r="O105" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P105" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q105" s="3" t="s">
         <v>231</v>
@@ -7157,10 +7157,10 @@
         <v>100</v>
       </c>
       <c r="O106" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P106" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q106" s="3" t="s">
         <v>231</v>
@@ -7213,10 +7213,10 @@
         <v>100</v>
       </c>
       <c r="O107" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P107" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q107" s="3" t="s">
         <v>231</v>
@@ -7269,10 +7269,10 @@
         <v>100</v>
       </c>
       <c r="O108" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P108" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q108" s="3" t="s">
         <v>231</v>
@@ -7325,10 +7325,10 @@
         <v>100</v>
       </c>
       <c r="O109" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P109" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q109" s="3" t="s">
         <v>231</v>
@@ -7381,10 +7381,10 @@
         <v>100</v>
       </c>
       <c r="O110" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P110" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q110" s="3" t="s">
         <v>231</v>
@@ -7437,10 +7437,10 @@
         <v>100</v>
       </c>
       <c r="O111" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P111" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q111" s="3" t="s">
         <v>231</v>
@@ -7493,10 +7493,10 @@
         <v>100</v>
       </c>
       <c r="O112" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P112" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q112" s="3" t="s">
         <v>231</v>
@@ -7549,10 +7549,10 @@
         <v>100</v>
       </c>
       <c r="O113" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P113" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q113" s="3" t="s">
         <v>231</v>
@@ -7605,10 +7605,10 @@
         <v>100</v>
       </c>
       <c r="O114" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P114" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q114" s="3" t="s">
         <v>231</v>
@@ -7661,10 +7661,10 @@
         <v>100</v>
       </c>
       <c r="O115" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P115" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q115" s="3" t="s">
         <v>231</v>
@@ -7717,10 +7717,10 @@
         <v>100</v>
       </c>
       <c r="O116" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P116" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q116" s="3" t="s">
         <v>231</v>
@@ -7773,10 +7773,10 @@
         <v>100</v>
       </c>
       <c r="O117" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P117" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q117" s="3" t="s">
         <v>231</v>
@@ -7829,10 +7829,10 @@
         <v>100</v>
       </c>
       <c r="O118" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P118" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q118" s="3" t="s">
         <v>231</v>
@@ -7885,10 +7885,10 @@
         <v>100</v>
       </c>
       <c r="O119" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P119" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q119" s="3" t="s">
         <v>231</v>
@@ -7941,10 +7941,10 @@
         <v>100</v>
       </c>
       <c r="O120" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P120" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q120" s="3" t="s">
         <v>231</v>
@@ -7997,10 +7997,10 @@
         <v>100</v>
       </c>
       <c r="O121" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P121" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q121" s="3" t="s">
         <v>231</v>
@@ -8053,10 +8053,10 @@
         <v>100</v>
       </c>
       <c r="O122" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P122" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q122" s="3" t="s">
         <v>231</v>
@@ -8109,10 +8109,10 @@
         <v>100</v>
       </c>
       <c r="O123" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P123" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q123" s="3" t="s">
         <v>231</v>
@@ -8165,10 +8165,10 @@
         <v>100</v>
       </c>
       <c r="O124" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P124" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q124" s="3" t="s">
         <v>231</v>
@@ -8221,10 +8221,10 @@
         <v>100</v>
       </c>
       <c r="O125" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P125" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q125" s="3" t="s">
         <v>231</v>
@@ -8277,10 +8277,10 @@
         <v>100</v>
       </c>
       <c r="O126" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P126" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q126" s="3" t="s">
         <v>231</v>
@@ -8333,10 +8333,10 @@
         <v>100</v>
       </c>
       <c r="O127" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P127" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q127" s="3" t="s">
         <v>231</v>
@@ -8389,10 +8389,10 @@
         <v>100</v>
       </c>
       <c r="O128" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P128" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q128" s="3" t="s">
         <v>231</v>
@@ -8445,10 +8445,10 @@
         <v>100</v>
       </c>
       <c r="O129" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P129" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q129" s="3" t="s">
         <v>231</v>
@@ -8501,10 +8501,10 @@
         <v>100</v>
       </c>
       <c r="O130" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P130" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q130" s="3" t="s">
         <v>231</v>
@@ -8557,10 +8557,10 @@
         <v>100</v>
       </c>
       <c r="O131" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P131" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q131" s="3" t="s">
         <v>231</v>
@@ -8613,10 +8613,10 @@
         <v>100</v>
       </c>
       <c r="O132" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P132" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q132" s="3" t="s">
         <v>231</v>
@@ -8669,10 +8669,10 @@
         <v>100</v>
       </c>
       <c r="O133" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P133" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q133" s="3" t="s">
         <v>231</v>
@@ -8725,10 +8725,10 @@
         <v>100</v>
       </c>
       <c r="O134" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P134" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q134" s="3" t="s">
         <v>231</v>
@@ -8781,10 +8781,10 @@
         <v>100</v>
       </c>
       <c r="O135" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P135" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q135" s="3" t="s">
         <v>231</v>
@@ -8837,10 +8837,10 @@
         <v>100</v>
       </c>
       <c r="O136" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P136" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q136" s="3" t="s">
         <v>231</v>
@@ -8893,10 +8893,10 @@
         <v>100</v>
       </c>
       <c r="O137" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P137" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q137" s="3" t="s">
         <v>231</v>
@@ -8949,10 +8949,10 @@
         <v>100</v>
       </c>
       <c r="O138" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P138" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q138" s="3" t="s">
         <v>231</v>
@@ -9005,10 +9005,10 @@
         <v>100</v>
       </c>
       <c r="O139" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P139" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q139" s="3" t="s">
         <v>231</v>
@@ -9061,10 +9061,10 @@
         <v>100</v>
       </c>
       <c r="O140" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P140" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q140" s="3" t="s">
         <v>231</v>
@@ -9117,10 +9117,10 @@
         <v>100</v>
       </c>
       <c r="O141" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P141" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q141" s="3" t="s">
         <v>231</v>
@@ -9173,10 +9173,10 @@
         <v>100</v>
       </c>
       <c r="O142" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P142" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q142" s="3" t="s">
         <v>231</v>
@@ -9229,10 +9229,10 @@
         <v>100</v>
       </c>
       <c r="O143" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P143" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q143" s="3" t="s">
         <v>231</v>
@@ -9285,10 +9285,10 @@
         <v>100</v>
       </c>
       <c r="O144" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P144" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q144" s="3" t="s">
         <v>231</v>
@@ -9341,10 +9341,10 @@
         <v>100</v>
       </c>
       <c r="O145" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P145" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q145" s="3" t="s">
         <v>231</v>
@@ -9397,10 +9397,10 @@
         <v>100</v>
       </c>
       <c r="O146" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P146" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q146" s="3" t="s">
         <v>231</v>
@@ -9453,10 +9453,10 @@
         <v>100</v>
       </c>
       <c r="O147" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P147" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q147" s="3" t="s">
         <v>231</v>
@@ -9509,10 +9509,10 @@
         <v>100</v>
       </c>
       <c r="O148" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P148" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q148" s="3" t="s">
         <v>231</v>
@@ -9565,10 +9565,10 @@
         <v>100</v>
       </c>
       <c r="O149" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P149" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q149" s="3" t="s">
         <v>231</v>
@@ -9621,10 +9621,10 @@
         <v>100</v>
       </c>
       <c r="O150" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P150" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q150" s="3" t="s">
         <v>231</v>
@@ -9677,10 +9677,10 @@
         <v>100</v>
       </c>
       <c r="O151" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P151" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q151" s="3" t="s">
         <v>231</v>
@@ -9733,10 +9733,10 @@
         <v>100</v>
       </c>
       <c r="O152" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P152" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q152" s="3" t="s">
         <v>231</v>
@@ -9789,10 +9789,10 @@
         <v>100</v>
       </c>
       <c r="O153" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P153" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q153" s="3" t="s">
         <v>231</v>
@@ -9845,10 +9845,10 @@
         <v>100</v>
       </c>
       <c r="O154" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P154" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q154" s="3" t="s">
         <v>231</v>
@@ -9901,10 +9901,10 @@
         <v>100</v>
       </c>
       <c r="O155" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P155" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q155" s="3" t="s">
         <v>231</v>
@@ -9957,10 +9957,10 @@
         <v>100</v>
       </c>
       <c r="O156" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P156" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q156" s="3" t="s">
         <v>231</v>
@@ -10013,10 +10013,10 @@
         <v>100</v>
       </c>
       <c r="O157" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P157" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q157" s="3" t="s">
         <v>231</v>
@@ -10069,10 +10069,10 @@
         <v>100</v>
       </c>
       <c r="O158" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P158" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q158" s="3" t="s">
         <v>231</v>
@@ -10125,10 +10125,10 @@
         <v>100</v>
       </c>
       <c r="O159" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P159" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q159" s="3" t="s">
         <v>231</v>
@@ -10181,10 +10181,10 @@
         <v>100</v>
       </c>
       <c r="O160" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P160" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q160" s="3" t="s">
         <v>231</v>
@@ -10237,10 +10237,10 @@
         <v>100</v>
       </c>
       <c r="O161" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P161" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q161" s="3" t="s">
         <v>231</v>
@@ -10293,10 +10293,10 @@
         <v>100</v>
       </c>
       <c r="O162" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P162" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q162" s="3" t="s">
         <v>231</v>
@@ -10349,10 +10349,10 @@
         <v>100</v>
       </c>
       <c r="O163" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P163" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q163" s="3" t="s">
         <v>231</v>
@@ -10405,10 +10405,10 @@
         <v>100</v>
       </c>
       <c r="O164" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P164" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q164" s="3" t="s">
         <v>231</v>

--- a/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8B99D75-F2AD-42C0-B437-ED262E5E8304}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5934785D-31C5-4712-AB96-E2A5AB6B9351}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_barries_v8" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1211" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1211" uniqueCount="416">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -867,10 +867,6 @@
     <t>110001:101_110002:101_110003:101_110004:101</t>
   </si>
   <si>
-    <t>0:0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>110001:1101_110002:1102_110003:1103_110004:1104</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -881,6 +877,480 @@
   <si>
     <t>110001:550_110002:750_110003:550</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20001:101</t>
+  </si>
+  <si>
+    <t>30001:101</t>
+  </si>
+  <si>
+    <t>40001:101</t>
+  </si>
+  <si>
+    <t>50001:101</t>
+  </si>
+  <si>
+    <t>60001:101</t>
+  </si>
+  <si>
+    <t>70001:101</t>
+  </si>
+  <si>
+    <t>80001:101</t>
+  </si>
+  <si>
+    <t>90001:101</t>
+  </si>
+  <si>
+    <t>100001:101</t>
+  </si>
+  <si>
+    <t>120001:101</t>
+  </si>
+  <si>
+    <t>130001:101</t>
+  </si>
+  <si>
+    <t>140001:101</t>
+  </si>
+  <si>
+    <t>150001:101</t>
+  </si>
+  <si>
+    <t>160001:101</t>
+  </si>
+  <si>
+    <t>170001:101</t>
+  </si>
+  <si>
+    <t>180001:101</t>
+  </si>
+  <si>
+    <t>190001:101</t>
+  </si>
+  <si>
+    <t>200001:101</t>
+  </si>
+  <si>
+    <t>210001:101</t>
+  </si>
+  <si>
+    <t>220001:101</t>
+  </si>
+  <si>
+    <t>230001:101</t>
+  </si>
+  <si>
+    <t>240001:101</t>
+  </si>
+  <si>
+    <t>250001:101</t>
+  </si>
+  <si>
+    <t>260001:101</t>
+  </si>
+  <si>
+    <t>270001:101</t>
+  </si>
+  <si>
+    <t>280001:101</t>
+  </si>
+  <si>
+    <t>290001:101</t>
+  </si>
+  <si>
+    <t>300001:101</t>
+  </si>
+  <si>
+    <t>310001:101</t>
+  </si>
+  <si>
+    <t>320001:101</t>
+  </si>
+  <si>
+    <t>330001:101</t>
+  </si>
+  <si>
+    <t>340001:101</t>
+  </si>
+  <si>
+    <t>350001:101</t>
+  </si>
+  <si>
+    <t>360001:101</t>
+  </si>
+  <si>
+    <t>370001:101</t>
+  </si>
+  <si>
+    <t>380001:101</t>
+  </si>
+  <si>
+    <t>390001:101</t>
+  </si>
+  <si>
+    <t>400001:101</t>
+  </si>
+  <si>
+    <t>410001:101</t>
+  </si>
+  <si>
+    <t>420001:101</t>
+  </si>
+  <si>
+    <t>430001:101</t>
+  </si>
+  <si>
+    <t>440001:101</t>
+  </si>
+  <si>
+    <t>450001:101</t>
+  </si>
+  <si>
+    <t>460001:101</t>
+  </si>
+  <si>
+    <t>470001:101</t>
+  </si>
+  <si>
+    <t>480001:101</t>
+  </si>
+  <si>
+    <t>490001:101</t>
+  </si>
+  <si>
+    <t>500001:101</t>
+  </si>
+  <si>
+    <t>510001:101</t>
+  </si>
+  <si>
+    <t>520001:101</t>
+  </si>
+  <si>
+    <t>530001:101</t>
+  </si>
+  <si>
+    <t>540001:101</t>
+  </si>
+  <si>
+    <t>550001:101</t>
+  </si>
+  <si>
+    <t>560001:101</t>
+  </si>
+  <si>
+    <t>570001:101</t>
+  </si>
+  <si>
+    <t>580001:101</t>
+  </si>
+  <si>
+    <t>590001:101</t>
+  </si>
+  <si>
+    <t>600001:101</t>
+  </si>
+  <si>
+    <t>610001:101</t>
+  </si>
+  <si>
+    <t>620001:101</t>
+  </si>
+  <si>
+    <t>630001:101</t>
+  </si>
+  <si>
+    <t>640001:101</t>
+  </si>
+  <si>
+    <t>650001:101</t>
+  </si>
+  <si>
+    <t>660001:101</t>
+  </si>
+  <si>
+    <t>670001:101</t>
+  </si>
+  <si>
+    <t>680001:101</t>
+  </si>
+  <si>
+    <t>690001:101</t>
+  </si>
+  <si>
+    <t>700001:101</t>
+  </si>
+  <si>
+    <t>710001:101</t>
+  </si>
+  <si>
+    <t>720001:101</t>
+  </si>
+  <si>
+    <t>730001:101</t>
+  </si>
+  <si>
+    <t>740001:101</t>
+  </si>
+  <si>
+    <t>750001:101</t>
+  </si>
+  <si>
+    <t>760001:101</t>
+  </si>
+  <si>
+    <t>770001:101</t>
+  </si>
+  <si>
+    <t>780001:101</t>
+  </si>
+  <si>
+    <t>790001:101</t>
+  </si>
+  <si>
+    <t>800001:101</t>
+  </si>
+  <si>
+    <t>810001:101</t>
+  </si>
+  <si>
+    <t>820001:101</t>
+  </si>
+  <si>
+    <t>830001:101</t>
+  </si>
+  <si>
+    <t>840001:101</t>
+  </si>
+  <si>
+    <t>850001:101</t>
+  </si>
+  <si>
+    <t>860001:101</t>
+  </si>
+  <si>
+    <t>870001:101</t>
+  </si>
+  <si>
+    <t>880001:101</t>
+  </si>
+  <si>
+    <t>890001:101</t>
+  </si>
+  <si>
+    <t>900001:101</t>
+  </si>
+  <si>
+    <t>910001:101</t>
+  </si>
+  <si>
+    <t>920001:101</t>
+  </si>
+  <si>
+    <t>930001:101</t>
+  </si>
+  <si>
+    <t>940001:101</t>
+  </si>
+  <si>
+    <t>950001:101</t>
+  </si>
+  <si>
+    <t>960001:101</t>
+  </si>
+  <si>
+    <t>970001:101</t>
+  </si>
+  <si>
+    <t>980001:101</t>
+  </si>
+  <si>
+    <t>990001:101</t>
+  </si>
+  <si>
+    <t>1000001:101</t>
+  </si>
+  <si>
+    <t>1010001:101</t>
+  </si>
+  <si>
+    <t>1020001:101</t>
+  </si>
+  <si>
+    <t>1030001:101</t>
+  </si>
+  <si>
+    <t>1040001:101</t>
+  </si>
+  <si>
+    <t>1050001:101</t>
+  </si>
+  <si>
+    <t>1060001:101</t>
+  </si>
+  <si>
+    <t>1070001:101</t>
+  </si>
+  <si>
+    <t>1080001:101</t>
+  </si>
+  <si>
+    <t>1090001:101</t>
+  </si>
+  <si>
+    <t>1100001:101</t>
+  </si>
+  <si>
+    <t>1110001:101</t>
+  </si>
+  <si>
+    <t>1120001:101</t>
+  </si>
+  <si>
+    <t>1130001:101</t>
+  </si>
+  <si>
+    <t>1140001:101</t>
+  </si>
+  <si>
+    <t>1150001:101</t>
+  </si>
+  <si>
+    <t>1160001:101</t>
+  </si>
+  <si>
+    <t>1170001:101</t>
+  </si>
+  <si>
+    <t>1180001:101</t>
+  </si>
+  <si>
+    <t>1190001:101</t>
+  </si>
+  <si>
+    <t>1200001:101</t>
+  </si>
+  <si>
+    <t>1210001:101</t>
+  </si>
+  <si>
+    <t>1220001:101</t>
+  </si>
+  <si>
+    <t>1230001:101</t>
+  </si>
+  <si>
+    <t>1240001:101</t>
+  </si>
+  <si>
+    <t>1250001:101</t>
+  </si>
+  <si>
+    <t>1260001:101</t>
+  </si>
+  <si>
+    <t>1270001:101</t>
+  </si>
+  <si>
+    <t>1280001:101</t>
+  </si>
+  <si>
+    <t>1290001:101</t>
+  </si>
+  <si>
+    <t>1300001:101</t>
+  </si>
+  <si>
+    <t>1310001:101</t>
+  </si>
+  <si>
+    <t>1320001:101</t>
+  </si>
+  <si>
+    <t>1330001:101</t>
+  </si>
+  <si>
+    <t>1340001:101</t>
+  </si>
+  <si>
+    <t>1350001:101</t>
+  </si>
+  <si>
+    <t>1360001:101</t>
+  </si>
+  <si>
+    <t>1370001:101</t>
+  </si>
+  <si>
+    <t>1380001:101</t>
+  </si>
+  <si>
+    <t>1390001:101</t>
+  </si>
+  <si>
+    <t>1400001:101</t>
+  </si>
+  <si>
+    <t>1410001:101</t>
+  </si>
+  <si>
+    <t>1420001:101</t>
+  </si>
+  <si>
+    <t>1430001:101</t>
+  </si>
+  <si>
+    <t>1440001:101</t>
+  </si>
+  <si>
+    <t>1450001:101</t>
+  </si>
+  <si>
+    <t>1460001:101</t>
+  </si>
+  <si>
+    <t>1470001:101</t>
+  </si>
+  <si>
+    <t>1480001:101</t>
+  </si>
+  <si>
+    <t>1490001:101</t>
+  </si>
+  <si>
+    <t>1500001:101</t>
+  </si>
+  <si>
+    <t>1510001:101</t>
+  </si>
+  <si>
+    <t>1520001:101</t>
+  </si>
+  <si>
+    <t>1530001:101</t>
+  </si>
+  <si>
+    <t>1540001:101</t>
+  </si>
+  <si>
+    <t>1550001:101</t>
+  </si>
+  <si>
+    <t>1560001:101</t>
+  </si>
+  <si>
+    <t>1570001:101</t>
+  </si>
+  <si>
+    <t>1580001:101</t>
+  </si>
+  <si>
+    <t>1590001:101</t>
+  </si>
+  <si>
+    <t>1600001:101</t>
   </si>
 </sst>
 </file>
@@ -1548,10 +2018,10 @@
         <v>200</v>
       </c>
       <c r="O6" s="4" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="P6" s="4" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="Q6" s="3" t="s">
         <v>231</v>
@@ -1604,10 +2074,10 @@
         <v>300</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="P7" s="4" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="Q7" s="3" t="s">
         <v>231</v>
@@ -1660,10 +2130,10 @@
         <v>400</v>
       </c>
       <c r="O8" s="4" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="P8" s="4" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="Q8" s="3" t="s">
         <v>231</v>
@@ -1716,10 +2186,10 @@
         <v>500</v>
       </c>
       <c r="O9" s="4" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="P9" s="4" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="Q9" s="3" t="s">
         <v>231</v>
@@ -1772,10 +2242,10 @@
         <v>600</v>
       </c>
       <c r="O10" s="4" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="P10" s="4" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="Q10" s="3" t="s">
         <v>231</v>
@@ -1828,10 +2298,10 @@
         <v>100</v>
       </c>
       <c r="O11" s="4" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="P11" s="4" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="Q11" s="3" t="s">
         <v>231</v>
@@ -1884,10 +2354,10 @@
         <v>100</v>
       </c>
       <c r="O12" s="4" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="P12" s="4" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="Q12" s="3" t="s">
         <v>231</v>
@@ -1940,10 +2410,10 @@
         <v>100</v>
       </c>
       <c r="O13" s="4" t="s">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="P13" s="4" t="s">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="Q13" s="3" t="s">
         <v>231</v>
@@ -1996,10 +2466,10 @@
         <v>100</v>
       </c>
       <c r="O14" s="4" t="s">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="P14" s="4" t="s">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>231</v>
@@ -2052,7 +2522,7 @@
         <v>100</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="P15" s="1" t="s">
         <v>254</v>
@@ -2067,10 +2537,10 @@
         <v>250</v>
       </c>
       <c r="T15" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="U15" s="1" t="s">
         <v>257</v>
-      </c>
-      <c r="U15" s="1" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.15">
@@ -2117,10 +2587,10 @@
         <v>100</v>
       </c>
       <c r="O16" s="4" t="s">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="P16" s="4" t="s">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="Q16" s="3" t="s">
         <v>231</v>
@@ -2173,10 +2643,10 @@
         <v>100</v>
       </c>
       <c r="O17" s="4" t="s">
-        <v>255</v>
+        <v>268</v>
       </c>
       <c r="P17" s="4" t="s">
-        <v>255</v>
+        <v>268</v>
       </c>
       <c r="Q17" s="3" t="s">
         <v>231</v>
@@ -2229,10 +2699,10 @@
         <v>100</v>
       </c>
       <c r="O18" s="4" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
       <c r="P18" s="4" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
       <c r="Q18" s="3" t="s">
         <v>231</v>
@@ -2285,10 +2755,10 @@
         <v>100</v>
       </c>
       <c r="O19" s="4" t="s">
-        <v>255</v>
+        <v>270</v>
       </c>
       <c r="P19" s="4" t="s">
-        <v>255</v>
+        <v>270</v>
       </c>
       <c r="Q19" s="3" t="s">
         <v>231</v>
@@ -2341,10 +2811,10 @@
         <v>100</v>
       </c>
       <c r="O20" s="4" t="s">
-        <v>255</v>
+        <v>271</v>
       </c>
       <c r="P20" s="4" t="s">
-        <v>255</v>
+        <v>271</v>
       </c>
       <c r="Q20" s="3" t="s">
         <v>231</v>
@@ -2397,10 +2867,10 @@
         <v>100</v>
       </c>
       <c r="O21" s="4" t="s">
-        <v>255</v>
+        <v>272</v>
       </c>
       <c r="P21" s="4" t="s">
-        <v>255</v>
+        <v>272</v>
       </c>
       <c r="Q21" s="3" t="s">
         <v>231</v>
@@ -2453,10 +2923,10 @@
         <v>100</v>
       </c>
       <c r="O22" s="4" t="s">
-        <v>255</v>
+        <v>273</v>
       </c>
       <c r="P22" s="4" t="s">
-        <v>255</v>
+        <v>273</v>
       </c>
       <c r="Q22" s="3" t="s">
         <v>231</v>
@@ -2509,10 +2979,10 @@
         <v>100</v>
       </c>
       <c r="O23" s="4" t="s">
-        <v>255</v>
+        <v>274</v>
       </c>
       <c r="P23" s="4" t="s">
-        <v>255</v>
+        <v>274</v>
       </c>
       <c r="Q23" s="3" t="s">
         <v>231</v>
@@ -2565,10 +3035,10 @@
         <v>100</v>
       </c>
       <c r="O24" s="4" t="s">
-        <v>255</v>
+        <v>275</v>
       </c>
       <c r="P24" s="4" t="s">
-        <v>255</v>
+        <v>275</v>
       </c>
       <c r="Q24" s="3" t="s">
         <v>231</v>
@@ -2621,10 +3091,10 @@
         <v>100</v>
       </c>
       <c r="O25" s="4" t="s">
-        <v>255</v>
+        <v>276</v>
       </c>
       <c r="P25" s="4" t="s">
-        <v>255</v>
+        <v>276</v>
       </c>
       <c r="Q25" s="3" t="s">
         <v>231</v>
@@ -2677,10 +3147,10 @@
         <v>100</v>
       </c>
       <c r="O26" s="4" t="s">
-        <v>255</v>
+        <v>277</v>
       </c>
       <c r="P26" s="4" t="s">
-        <v>255</v>
+        <v>277</v>
       </c>
       <c r="Q26" s="3" t="s">
         <v>231</v>
@@ -2733,10 +3203,10 @@
         <v>100</v>
       </c>
       <c r="O27" s="4" t="s">
-        <v>255</v>
+        <v>278</v>
       </c>
       <c r="P27" s="4" t="s">
-        <v>255</v>
+        <v>278</v>
       </c>
       <c r="Q27" s="3" t="s">
         <v>231</v>
@@ -2789,10 +3259,10 @@
         <v>100</v>
       </c>
       <c r="O28" s="4" t="s">
-        <v>255</v>
+        <v>279</v>
       </c>
       <c r="P28" s="4" t="s">
-        <v>255</v>
+        <v>279</v>
       </c>
       <c r="Q28" s="3" t="s">
         <v>231</v>
@@ -2845,10 +3315,10 @@
         <v>100</v>
       </c>
       <c r="O29" s="4" t="s">
-        <v>255</v>
+        <v>280</v>
       </c>
       <c r="P29" s="4" t="s">
-        <v>255</v>
+        <v>280</v>
       </c>
       <c r="Q29" s="3" t="s">
         <v>231</v>
@@ -2901,10 +3371,10 @@
         <v>100</v>
       </c>
       <c r="O30" s="4" t="s">
-        <v>255</v>
+        <v>281</v>
       </c>
       <c r="P30" s="4" t="s">
-        <v>255</v>
+        <v>281</v>
       </c>
       <c r="Q30" s="3" t="s">
         <v>231</v>
@@ -2957,10 +3427,10 @@
         <v>100</v>
       </c>
       <c r="O31" s="4" t="s">
-        <v>255</v>
+        <v>282</v>
       </c>
       <c r="P31" s="4" t="s">
-        <v>255</v>
+        <v>282</v>
       </c>
       <c r="Q31" s="3" t="s">
         <v>231</v>
@@ -3013,10 +3483,10 @@
         <v>100</v>
       </c>
       <c r="O32" s="4" t="s">
-        <v>255</v>
+        <v>283</v>
       </c>
       <c r="P32" s="4" t="s">
-        <v>255</v>
+        <v>283</v>
       </c>
       <c r="Q32" s="3" t="s">
         <v>231</v>
@@ -3069,10 +3539,10 @@
         <v>100</v>
       </c>
       <c r="O33" s="4" t="s">
-        <v>255</v>
+        <v>284</v>
       </c>
       <c r="P33" s="4" t="s">
-        <v>255</v>
+        <v>284</v>
       </c>
       <c r="Q33" s="3" t="s">
         <v>231</v>
@@ -3125,10 +3595,10 @@
         <v>100</v>
       </c>
       <c r="O34" s="4" t="s">
-        <v>255</v>
+        <v>285</v>
       </c>
       <c r="P34" s="4" t="s">
-        <v>255</v>
+        <v>285</v>
       </c>
       <c r="Q34" s="3" t="s">
         <v>231</v>
@@ -3181,10 +3651,10 @@
         <v>100</v>
       </c>
       <c r="O35" s="4" t="s">
-        <v>255</v>
+        <v>286</v>
       </c>
       <c r="P35" s="4" t="s">
-        <v>255</v>
+        <v>286</v>
       </c>
       <c r="Q35" s="3" t="s">
         <v>231</v>
@@ -3237,10 +3707,10 @@
         <v>100</v>
       </c>
       <c r="O36" s="4" t="s">
-        <v>255</v>
+        <v>287</v>
       </c>
       <c r="P36" s="4" t="s">
-        <v>255</v>
+        <v>287</v>
       </c>
       <c r="Q36" s="3" t="s">
         <v>231</v>
@@ -3293,10 +3763,10 @@
         <v>100</v>
       </c>
       <c r="O37" s="4" t="s">
-        <v>255</v>
+        <v>288</v>
       </c>
       <c r="P37" s="4" t="s">
-        <v>255</v>
+        <v>288</v>
       </c>
       <c r="Q37" s="3" t="s">
         <v>231</v>
@@ -3349,10 +3819,10 @@
         <v>100</v>
       </c>
       <c r="O38" s="4" t="s">
-        <v>255</v>
+        <v>289</v>
       </c>
       <c r="P38" s="4" t="s">
-        <v>255</v>
+        <v>289</v>
       </c>
       <c r="Q38" s="3" t="s">
         <v>231</v>
@@ -3405,10 +3875,10 @@
         <v>100</v>
       </c>
       <c r="O39" s="4" t="s">
-        <v>255</v>
+        <v>290</v>
       </c>
       <c r="P39" s="4" t="s">
-        <v>255</v>
+        <v>290</v>
       </c>
       <c r="Q39" s="3" t="s">
         <v>231</v>
@@ -3461,10 +3931,10 @@
         <v>100</v>
       </c>
       <c r="O40" s="4" t="s">
-        <v>255</v>
+        <v>291</v>
       </c>
       <c r="P40" s="4" t="s">
-        <v>255</v>
+        <v>291</v>
       </c>
       <c r="Q40" s="3" t="s">
         <v>231</v>
@@ -3517,10 +3987,10 @@
         <v>100</v>
       </c>
       <c r="O41" s="4" t="s">
-        <v>255</v>
+        <v>292</v>
       </c>
       <c r="P41" s="4" t="s">
-        <v>255</v>
+        <v>292</v>
       </c>
       <c r="Q41" s="3" t="s">
         <v>231</v>
@@ -3573,10 +4043,10 @@
         <v>100</v>
       </c>
       <c r="O42" s="4" t="s">
-        <v>255</v>
+        <v>293</v>
       </c>
       <c r="P42" s="4" t="s">
-        <v>255</v>
+        <v>293</v>
       </c>
       <c r="Q42" s="3" t="s">
         <v>231</v>
@@ -3629,10 +4099,10 @@
         <v>100</v>
       </c>
       <c r="O43" s="4" t="s">
-        <v>255</v>
+        <v>294</v>
       </c>
       <c r="P43" s="4" t="s">
-        <v>255</v>
+        <v>294</v>
       </c>
       <c r="Q43" s="3" t="s">
         <v>231</v>
@@ -3685,10 +4155,10 @@
         <v>100</v>
       </c>
       <c r="O44" s="4" t="s">
-        <v>255</v>
+        <v>295</v>
       </c>
       <c r="P44" s="4" t="s">
-        <v>255</v>
+        <v>295</v>
       </c>
       <c r="Q44" s="3" t="s">
         <v>231</v>
@@ -3741,10 +4211,10 @@
         <v>100</v>
       </c>
       <c r="O45" s="4" t="s">
-        <v>255</v>
+        <v>296</v>
       </c>
       <c r="P45" s="4" t="s">
-        <v>255</v>
+        <v>296</v>
       </c>
       <c r="Q45" s="3" t="s">
         <v>231</v>
@@ -3797,10 +4267,10 @@
         <v>100</v>
       </c>
       <c r="O46" s="4" t="s">
-        <v>255</v>
+        <v>297</v>
       </c>
       <c r="P46" s="4" t="s">
-        <v>255</v>
+        <v>297</v>
       </c>
       <c r="Q46" s="3" t="s">
         <v>231</v>
@@ -3853,10 +4323,10 @@
         <v>100</v>
       </c>
       <c r="O47" s="4" t="s">
-        <v>255</v>
+        <v>298</v>
       </c>
       <c r="P47" s="4" t="s">
-        <v>255</v>
+        <v>298</v>
       </c>
       <c r="Q47" s="3" t="s">
         <v>231</v>
@@ -3909,10 +4379,10 @@
         <v>100</v>
       </c>
       <c r="O48" s="4" t="s">
-        <v>255</v>
+        <v>299</v>
       </c>
       <c r="P48" s="4" t="s">
-        <v>255</v>
+        <v>299</v>
       </c>
       <c r="Q48" s="3" t="s">
         <v>231</v>
@@ -3965,10 +4435,10 @@
         <v>100</v>
       </c>
       <c r="O49" s="4" t="s">
-        <v>255</v>
+        <v>300</v>
       </c>
       <c r="P49" s="4" t="s">
-        <v>255</v>
+        <v>300</v>
       </c>
       <c r="Q49" s="3" t="s">
         <v>231</v>
@@ -4021,10 +4491,10 @@
         <v>100</v>
       </c>
       <c r="O50" s="4" t="s">
-        <v>255</v>
+        <v>301</v>
       </c>
       <c r="P50" s="4" t="s">
-        <v>255</v>
+        <v>301</v>
       </c>
       <c r="Q50" s="3" t="s">
         <v>231</v>
@@ -4077,10 +4547,10 @@
         <v>100</v>
       </c>
       <c r="O51" s="4" t="s">
-        <v>255</v>
+        <v>302</v>
       </c>
       <c r="P51" s="4" t="s">
-        <v>255</v>
+        <v>302</v>
       </c>
       <c r="Q51" s="3" t="s">
         <v>231</v>
@@ -4133,10 +4603,10 @@
         <v>100</v>
       </c>
       <c r="O52" s="4" t="s">
-        <v>255</v>
+        <v>303</v>
       </c>
       <c r="P52" s="4" t="s">
-        <v>255</v>
+        <v>303</v>
       </c>
       <c r="Q52" s="3" t="s">
         <v>231</v>
@@ -4189,10 +4659,10 @@
         <v>100</v>
       </c>
       <c r="O53" s="4" t="s">
-        <v>255</v>
+        <v>304</v>
       </c>
       <c r="P53" s="4" t="s">
-        <v>255</v>
+        <v>304</v>
       </c>
       <c r="Q53" s="3" t="s">
         <v>231</v>
@@ -4245,10 +4715,10 @@
         <v>100</v>
       </c>
       <c r="O54" s="4" t="s">
-        <v>255</v>
+        <v>305</v>
       </c>
       <c r="P54" s="4" t="s">
-        <v>255</v>
+        <v>305</v>
       </c>
       <c r="Q54" s="3" t="s">
         <v>231</v>
@@ -4301,10 +4771,10 @@
         <v>100</v>
       </c>
       <c r="O55" s="4" t="s">
-        <v>255</v>
+        <v>306</v>
       </c>
       <c r="P55" s="4" t="s">
-        <v>255</v>
+        <v>306</v>
       </c>
       <c r="Q55" s="3" t="s">
         <v>231</v>
@@ -4357,10 +4827,10 @@
         <v>100</v>
       </c>
       <c r="O56" s="4" t="s">
-        <v>255</v>
+        <v>307</v>
       </c>
       <c r="P56" s="4" t="s">
-        <v>255</v>
+        <v>307</v>
       </c>
       <c r="Q56" s="3" t="s">
         <v>231</v>
@@ -4413,10 +4883,10 @@
         <v>100</v>
       </c>
       <c r="O57" s="4" t="s">
-        <v>255</v>
+        <v>308</v>
       </c>
       <c r="P57" s="4" t="s">
-        <v>255</v>
+        <v>308</v>
       </c>
       <c r="Q57" s="3" t="s">
         <v>231</v>
@@ -4469,10 +4939,10 @@
         <v>100</v>
       </c>
       <c r="O58" s="4" t="s">
-        <v>255</v>
+        <v>309</v>
       </c>
       <c r="P58" s="4" t="s">
-        <v>255</v>
+        <v>309</v>
       </c>
       <c r="Q58" s="3" t="s">
         <v>231</v>
@@ -4525,10 +4995,10 @@
         <v>100</v>
       </c>
       <c r="O59" s="4" t="s">
-        <v>255</v>
+        <v>310</v>
       </c>
       <c r="P59" s="4" t="s">
-        <v>255</v>
+        <v>310</v>
       </c>
       <c r="Q59" s="3" t="s">
         <v>231</v>
@@ -4581,10 +5051,10 @@
         <v>100</v>
       </c>
       <c r="O60" s="4" t="s">
-        <v>255</v>
+        <v>311</v>
       </c>
       <c r="P60" s="4" t="s">
-        <v>255</v>
+        <v>311</v>
       </c>
       <c r="Q60" s="3" t="s">
         <v>231</v>
@@ -4637,10 +5107,10 @@
         <v>100</v>
       </c>
       <c r="O61" s="4" t="s">
-        <v>255</v>
+        <v>312</v>
       </c>
       <c r="P61" s="4" t="s">
-        <v>255</v>
+        <v>312</v>
       </c>
       <c r="Q61" s="3" t="s">
         <v>231</v>
@@ -4693,10 +5163,10 @@
         <v>100</v>
       </c>
       <c r="O62" s="4" t="s">
-        <v>255</v>
+        <v>313</v>
       </c>
       <c r="P62" s="4" t="s">
-        <v>255</v>
+        <v>313</v>
       </c>
       <c r="Q62" s="3" t="s">
         <v>231</v>
@@ -4749,10 +5219,10 @@
         <v>100</v>
       </c>
       <c r="O63" s="4" t="s">
-        <v>255</v>
+        <v>314</v>
       </c>
       <c r="P63" s="4" t="s">
-        <v>255</v>
+        <v>314</v>
       </c>
       <c r="Q63" s="3" t="s">
         <v>231</v>
@@ -4805,10 +5275,10 @@
         <v>100</v>
       </c>
       <c r="O64" s="4" t="s">
-        <v>255</v>
+        <v>315</v>
       </c>
       <c r="P64" s="4" t="s">
-        <v>255</v>
+        <v>315</v>
       </c>
       <c r="Q64" s="3" t="s">
         <v>231</v>
@@ -4861,10 +5331,10 @@
         <v>100</v>
       </c>
       <c r="O65" s="4" t="s">
-        <v>255</v>
+        <v>316</v>
       </c>
       <c r="P65" s="4" t="s">
-        <v>255</v>
+        <v>316</v>
       </c>
       <c r="Q65" s="3" t="s">
         <v>231</v>
@@ -4917,10 +5387,10 @@
         <v>100</v>
       </c>
       <c r="O66" s="4" t="s">
-        <v>255</v>
+        <v>317</v>
       </c>
       <c r="P66" s="4" t="s">
-        <v>255</v>
+        <v>317</v>
       </c>
       <c r="Q66" s="3" t="s">
         <v>231</v>
@@ -4973,10 +5443,10 @@
         <v>100</v>
       </c>
       <c r="O67" s="4" t="s">
-        <v>255</v>
+        <v>318</v>
       </c>
       <c r="P67" s="4" t="s">
-        <v>255</v>
+        <v>318</v>
       </c>
       <c r="Q67" s="3" t="s">
         <v>231</v>
@@ -5029,10 +5499,10 @@
         <v>100</v>
       </c>
       <c r="O68" s="4" t="s">
-        <v>255</v>
+        <v>319</v>
       </c>
       <c r="P68" s="4" t="s">
-        <v>255</v>
+        <v>319</v>
       </c>
       <c r="Q68" s="3" t="s">
         <v>231</v>
@@ -5085,10 +5555,10 @@
         <v>100</v>
       </c>
       <c r="O69" s="4" t="s">
-        <v>255</v>
+        <v>320</v>
       </c>
       <c r="P69" s="4" t="s">
-        <v>255</v>
+        <v>320</v>
       </c>
       <c r="Q69" s="3" t="s">
         <v>231</v>
@@ -5141,10 +5611,10 @@
         <v>100</v>
       </c>
       <c r="O70" s="4" t="s">
-        <v>255</v>
+        <v>321</v>
       </c>
       <c r="P70" s="4" t="s">
-        <v>255</v>
+        <v>321</v>
       </c>
       <c r="Q70" s="3" t="s">
         <v>231</v>
@@ -5197,10 +5667,10 @@
         <v>100</v>
       </c>
       <c r="O71" s="4" t="s">
-        <v>255</v>
+        <v>322</v>
       </c>
       <c r="P71" s="4" t="s">
-        <v>255</v>
+        <v>322</v>
       </c>
       <c r="Q71" s="3" t="s">
         <v>231</v>
@@ -5253,10 +5723,10 @@
         <v>100</v>
       </c>
       <c r="O72" s="4" t="s">
-        <v>255</v>
+        <v>323</v>
       </c>
       <c r="P72" s="4" t="s">
-        <v>255</v>
+        <v>323</v>
       </c>
       <c r="Q72" s="3" t="s">
         <v>231</v>
@@ -5309,10 +5779,10 @@
         <v>100</v>
       </c>
       <c r="O73" s="4" t="s">
-        <v>255</v>
+        <v>324</v>
       </c>
       <c r="P73" s="4" t="s">
-        <v>255</v>
+        <v>324</v>
       </c>
       <c r="Q73" s="3" t="s">
         <v>231</v>
@@ -5365,10 +5835,10 @@
         <v>100</v>
       </c>
       <c r="O74" s="4" t="s">
-        <v>255</v>
+        <v>325</v>
       </c>
       <c r="P74" s="4" t="s">
-        <v>255</v>
+        <v>325</v>
       </c>
       <c r="Q74" s="3" t="s">
         <v>231</v>
@@ -5421,10 +5891,10 @@
         <v>100</v>
       </c>
       <c r="O75" s="4" t="s">
-        <v>255</v>
+        <v>326</v>
       </c>
       <c r="P75" s="4" t="s">
-        <v>255</v>
+        <v>326</v>
       </c>
       <c r="Q75" s="3" t="s">
         <v>231</v>
@@ -5477,10 +5947,10 @@
         <v>100</v>
       </c>
       <c r="O76" s="4" t="s">
-        <v>255</v>
+        <v>327</v>
       </c>
       <c r="P76" s="4" t="s">
-        <v>255</v>
+        <v>327</v>
       </c>
       <c r="Q76" s="3" t="s">
         <v>231</v>
@@ -5533,10 +6003,10 @@
         <v>100</v>
       </c>
       <c r="O77" s="4" t="s">
-        <v>255</v>
+        <v>328</v>
       </c>
       <c r="P77" s="4" t="s">
-        <v>255</v>
+        <v>328</v>
       </c>
       <c r="Q77" s="3" t="s">
         <v>231</v>
@@ -5589,10 +6059,10 @@
         <v>100</v>
       </c>
       <c r="O78" s="4" t="s">
-        <v>255</v>
+        <v>329</v>
       </c>
       <c r="P78" s="4" t="s">
-        <v>255</v>
+        <v>329</v>
       </c>
       <c r="Q78" s="3" t="s">
         <v>231</v>
@@ -5645,10 +6115,10 @@
         <v>100</v>
       </c>
       <c r="O79" s="4" t="s">
-        <v>255</v>
+        <v>330</v>
       </c>
       <c r="P79" s="4" t="s">
-        <v>255</v>
+        <v>330</v>
       </c>
       <c r="Q79" s="3" t="s">
         <v>231</v>
@@ -5701,10 +6171,10 @@
         <v>100</v>
       </c>
       <c r="O80" s="4" t="s">
-        <v>255</v>
+        <v>331</v>
       </c>
       <c r="P80" s="4" t="s">
-        <v>255</v>
+        <v>331</v>
       </c>
       <c r="Q80" s="3" t="s">
         <v>231</v>
@@ -5757,10 +6227,10 @@
         <v>100</v>
       </c>
       <c r="O81" s="4" t="s">
-        <v>255</v>
+        <v>332</v>
       </c>
       <c r="P81" s="4" t="s">
-        <v>255</v>
+        <v>332</v>
       </c>
       <c r="Q81" s="3" t="s">
         <v>231</v>
@@ -5813,10 +6283,10 @@
         <v>100</v>
       </c>
       <c r="O82" s="4" t="s">
-        <v>255</v>
+        <v>333</v>
       </c>
       <c r="P82" s="4" t="s">
-        <v>255</v>
+        <v>333</v>
       </c>
       <c r="Q82" s="3" t="s">
         <v>231</v>
@@ -5869,10 +6339,10 @@
         <v>100</v>
       </c>
       <c r="O83" s="4" t="s">
-        <v>255</v>
+        <v>334</v>
       </c>
       <c r="P83" s="4" t="s">
-        <v>255</v>
+        <v>334</v>
       </c>
       <c r="Q83" s="3" t="s">
         <v>231</v>
@@ -5925,10 +6395,10 @@
         <v>100</v>
       </c>
       <c r="O84" s="4" t="s">
-        <v>255</v>
+        <v>335</v>
       </c>
       <c r="P84" s="4" t="s">
-        <v>255</v>
+        <v>335</v>
       </c>
       <c r="Q84" s="3" t="s">
         <v>231</v>
@@ -5981,10 +6451,10 @@
         <v>100</v>
       </c>
       <c r="O85" s="4" t="s">
-        <v>255</v>
+        <v>336</v>
       </c>
       <c r="P85" s="4" t="s">
-        <v>255</v>
+        <v>336</v>
       </c>
       <c r="Q85" s="3" t="s">
         <v>231</v>
@@ -6037,10 +6507,10 @@
         <v>100</v>
       </c>
       <c r="O86" s="4" t="s">
-        <v>255</v>
+        <v>337</v>
       </c>
       <c r="P86" s="4" t="s">
-        <v>255</v>
+        <v>337</v>
       </c>
       <c r="Q86" s="3" t="s">
         <v>231</v>
@@ -6093,10 +6563,10 @@
         <v>100</v>
       </c>
       <c r="O87" s="4" t="s">
-        <v>255</v>
+        <v>338</v>
       </c>
       <c r="P87" s="4" t="s">
-        <v>255</v>
+        <v>338</v>
       </c>
       <c r="Q87" s="3" t="s">
         <v>231</v>
@@ -6149,10 +6619,10 @@
         <v>100</v>
       </c>
       <c r="O88" s="4" t="s">
-        <v>255</v>
+        <v>339</v>
       </c>
       <c r="P88" s="4" t="s">
-        <v>255</v>
+        <v>339</v>
       </c>
       <c r="Q88" s="3" t="s">
         <v>231</v>
@@ -6205,10 +6675,10 @@
         <v>100</v>
       </c>
       <c r="O89" s="4" t="s">
-        <v>255</v>
+        <v>340</v>
       </c>
       <c r="P89" s="4" t="s">
-        <v>255</v>
+        <v>340</v>
       </c>
       <c r="Q89" s="3" t="s">
         <v>231</v>
@@ -6261,10 +6731,10 @@
         <v>100</v>
       </c>
       <c r="O90" s="4" t="s">
-        <v>255</v>
+        <v>341</v>
       </c>
       <c r="P90" s="4" t="s">
-        <v>255</v>
+        <v>341</v>
       </c>
       <c r="Q90" s="3" t="s">
         <v>231</v>
@@ -6317,10 +6787,10 @@
         <v>100</v>
       </c>
       <c r="O91" s="4" t="s">
-        <v>255</v>
+        <v>342</v>
       </c>
       <c r="P91" s="4" t="s">
-        <v>255</v>
+        <v>342</v>
       </c>
       <c r="Q91" s="3" t="s">
         <v>231</v>
@@ -6373,10 +6843,10 @@
         <v>100</v>
       </c>
       <c r="O92" s="4" t="s">
-        <v>255</v>
+        <v>343</v>
       </c>
       <c r="P92" s="4" t="s">
-        <v>255</v>
+        <v>343</v>
       </c>
       <c r="Q92" s="3" t="s">
         <v>231</v>
@@ -6429,10 +6899,10 @@
         <v>100</v>
       </c>
       <c r="O93" s="4" t="s">
-        <v>255</v>
+        <v>344</v>
       </c>
       <c r="P93" s="4" t="s">
-        <v>255</v>
+        <v>344</v>
       </c>
       <c r="Q93" s="3" t="s">
         <v>231</v>
@@ -6485,10 +6955,10 @@
         <v>100</v>
       </c>
       <c r="O94" s="4" t="s">
-        <v>255</v>
+        <v>345</v>
       </c>
       <c r="P94" s="4" t="s">
-        <v>255</v>
+        <v>345</v>
       </c>
       <c r="Q94" s="3" t="s">
         <v>231</v>
@@ -6541,10 +7011,10 @@
         <v>100</v>
       </c>
       <c r="O95" s="4" t="s">
-        <v>255</v>
+        <v>346</v>
       </c>
       <c r="P95" s="4" t="s">
-        <v>255</v>
+        <v>346</v>
       </c>
       <c r="Q95" s="3" t="s">
         <v>231</v>
@@ -6597,10 +7067,10 @@
         <v>100</v>
       </c>
       <c r="O96" s="4" t="s">
-        <v>255</v>
+        <v>347</v>
       </c>
       <c r="P96" s="4" t="s">
-        <v>255</v>
+        <v>347</v>
       </c>
       <c r="Q96" s="3" t="s">
         <v>231</v>
@@ -6653,10 +7123,10 @@
         <v>100</v>
       </c>
       <c r="O97" s="4" t="s">
-        <v>255</v>
+        <v>348</v>
       </c>
       <c r="P97" s="4" t="s">
-        <v>255</v>
+        <v>348</v>
       </c>
       <c r="Q97" s="3" t="s">
         <v>231</v>
@@ -6709,10 +7179,10 @@
         <v>100</v>
       </c>
       <c r="O98" s="4" t="s">
-        <v>255</v>
+        <v>349</v>
       </c>
       <c r="P98" s="4" t="s">
-        <v>255</v>
+        <v>349</v>
       </c>
       <c r="Q98" s="3" t="s">
         <v>231</v>
@@ -6765,10 +7235,10 @@
         <v>100</v>
       </c>
       <c r="O99" s="4" t="s">
-        <v>255</v>
+        <v>350</v>
       </c>
       <c r="P99" s="4" t="s">
-        <v>255</v>
+        <v>350</v>
       </c>
       <c r="Q99" s="3" t="s">
         <v>231</v>
@@ -6821,10 +7291,10 @@
         <v>100</v>
       </c>
       <c r="O100" s="4" t="s">
-        <v>255</v>
+        <v>351</v>
       </c>
       <c r="P100" s="4" t="s">
-        <v>255</v>
+        <v>351</v>
       </c>
       <c r="Q100" s="3" t="s">
         <v>231</v>
@@ -6877,10 +7347,10 @@
         <v>100</v>
       </c>
       <c r="O101" s="4" t="s">
-        <v>255</v>
+        <v>352</v>
       </c>
       <c r="P101" s="4" t="s">
-        <v>255</v>
+        <v>352</v>
       </c>
       <c r="Q101" s="3" t="s">
         <v>231</v>
@@ -6933,10 +7403,10 @@
         <v>100</v>
       </c>
       <c r="O102" s="4" t="s">
-        <v>255</v>
+        <v>353</v>
       </c>
       <c r="P102" s="4" t="s">
-        <v>255</v>
+        <v>353</v>
       </c>
       <c r="Q102" s="3" t="s">
         <v>231</v>
@@ -6989,10 +7459,10 @@
         <v>100</v>
       </c>
       <c r="O103" s="4" t="s">
-        <v>255</v>
+        <v>354</v>
       </c>
       <c r="P103" s="4" t="s">
-        <v>255</v>
+        <v>354</v>
       </c>
       <c r="Q103" s="3" t="s">
         <v>231</v>
@@ -7045,10 +7515,10 @@
         <v>100</v>
       </c>
       <c r="O104" s="4" t="s">
-        <v>255</v>
+        <v>355</v>
       </c>
       <c r="P104" s="4" t="s">
-        <v>255</v>
+        <v>355</v>
       </c>
       <c r="Q104" s="3" t="s">
         <v>231</v>
@@ -7101,10 +7571,10 @@
         <v>100</v>
       </c>
       <c r="O105" s="4" t="s">
-        <v>255</v>
+        <v>356</v>
       </c>
       <c r="P105" s="4" t="s">
-        <v>255</v>
+        <v>356</v>
       </c>
       <c r="Q105" s="3" t="s">
         <v>231</v>
@@ -7157,10 +7627,10 @@
         <v>100</v>
       </c>
       <c r="O106" s="4" t="s">
-        <v>255</v>
+        <v>357</v>
       </c>
       <c r="P106" s="4" t="s">
-        <v>255</v>
+        <v>357</v>
       </c>
       <c r="Q106" s="3" t="s">
         <v>231</v>
@@ -7213,10 +7683,10 @@
         <v>100</v>
       </c>
       <c r="O107" s="4" t="s">
-        <v>255</v>
+        <v>358</v>
       </c>
       <c r="P107" s="4" t="s">
-        <v>255</v>
+        <v>358</v>
       </c>
       <c r="Q107" s="3" t="s">
         <v>231</v>
@@ -7269,10 +7739,10 @@
         <v>100</v>
       </c>
       <c r="O108" s="4" t="s">
-        <v>255</v>
+        <v>359</v>
       </c>
       <c r="P108" s="4" t="s">
-        <v>255</v>
+        <v>359</v>
       </c>
       <c r="Q108" s="3" t="s">
         <v>231</v>
@@ -7325,10 +7795,10 @@
         <v>100</v>
       </c>
       <c r="O109" s="4" t="s">
-        <v>255</v>
+        <v>360</v>
       </c>
       <c r="P109" s="4" t="s">
-        <v>255</v>
+        <v>360</v>
       </c>
       <c r="Q109" s="3" t="s">
         <v>231</v>
@@ -7381,10 +7851,10 @@
         <v>100</v>
       </c>
       <c r="O110" s="4" t="s">
-        <v>255</v>
+        <v>361</v>
       </c>
       <c r="P110" s="4" t="s">
-        <v>255</v>
+        <v>361</v>
       </c>
       <c r="Q110" s="3" t="s">
         <v>231</v>
@@ -7437,10 +7907,10 @@
         <v>100</v>
       </c>
       <c r="O111" s="4" t="s">
-        <v>255</v>
+        <v>362</v>
       </c>
       <c r="P111" s="4" t="s">
-        <v>255</v>
+        <v>362</v>
       </c>
       <c r="Q111" s="3" t="s">
         <v>231</v>
@@ -7493,10 +7963,10 @@
         <v>100</v>
       </c>
       <c r="O112" s="4" t="s">
-        <v>255</v>
+        <v>363</v>
       </c>
       <c r="P112" s="4" t="s">
-        <v>255</v>
+        <v>363</v>
       </c>
       <c r="Q112" s="3" t="s">
         <v>231</v>
@@ -7549,10 +8019,10 @@
         <v>100</v>
       </c>
       <c r="O113" s="4" t="s">
-        <v>255</v>
+        <v>364</v>
       </c>
       <c r="P113" s="4" t="s">
-        <v>255</v>
+        <v>364</v>
       </c>
       <c r="Q113" s="3" t="s">
         <v>231</v>
@@ -7605,10 +8075,10 @@
         <v>100</v>
       </c>
       <c r="O114" s="4" t="s">
-        <v>255</v>
+        <v>365</v>
       </c>
       <c r="P114" s="4" t="s">
-        <v>255</v>
+        <v>365</v>
       </c>
       <c r="Q114" s="3" t="s">
         <v>231</v>
@@ -7661,10 +8131,10 @@
         <v>100</v>
       </c>
       <c r="O115" s="4" t="s">
-        <v>255</v>
+        <v>366</v>
       </c>
       <c r="P115" s="4" t="s">
-        <v>255</v>
+        <v>366</v>
       </c>
       <c r="Q115" s="3" t="s">
         <v>231</v>
@@ -7717,10 +8187,10 @@
         <v>100</v>
       </c>
       <c r="O116" s="4" t="s">
-        <v>255</v>
+        <v>367</v>
       </c>
       <c r="P116" s="4" t="s">
-        <v>255</v>
+        <v>367</v>
       </c>
       <c r="Q116" s="3" t="s">
         <v>231</v>
@@ -7773,10 +8243,10 @@
         <v>100</v>
       </c>
       <c r="O117" s="4" t="s">
-        <v>255</v>
+        <v>368</v>
       </c>
       <c r="P117" s="4" t="s">
-        <v>255</v>
+        <v>368</v>
       </c>
       <c r="Q117" s="3" t="s">
         <v>231</v>
@@ -7829,10 +8299,10 @@
         <v>100</v>
       </c>
       <c r="O118" s="4" t="s">
-        <v>255</v>
+        <v>369</v>
       </c>
       <c r="P118" s="4" t="s">
-        <v>255</v>
+        <v>369</v>
       </c>
       <c r="Q118" s="3" t="s">
         <v>231</v>
@@ -7885,10 +8355,10 @@
         <v>100</v>
       </c>
       <c r="O119" s="4" t="s">
-        <v>255</v>
+        <v>370</v>
       </c>
       <c r="P119" s="4" t="s">
-        <v>255</v>
+        <v>370</v>
       </c>
       <c r="Q119" s="3" t="s">
         <v>231</v>
@@ -7941,10 +8411,10 @@
         <v>100</v>
       </c>
       <c r="O120" s="4" t="s">
-        <v>255</v>
+        <v>371</v>
       </c>
       <c r="P120" s="4" t="s">
-        <v>255</v>
+        <v>371</v>
       </c>
       <c r="Q120" s="3" t="s">
         <v>231</v>
@@ -7997,10 +8467,10 @@
         <v>100</v>
       </c>
       <c r="O121" s="4" t="s">
-        <v>255</v>
+        <v>372</v>
       </c>
       <c r="P121" s="4" t="s">
-        <v>255</v>
+        <v>372</v>
       </c>
       <c r="Q121" s="3" t="s">
         <v>231</v>
@@ -8053,10 +8523,10 @@
         <v>100</v>
       </c>
       <c r="O122" s="4" t="s">
-        <v>255</v>
+        <v>373</v>
       </c>
       <c r="P122" s="4" t="s">
-        <v>255</v>
+        <v>373</v>
       </c>
       <c r="Q122" s="3" t="s">
         <v>231</v>
@@ -8109,10 +8579,10 @@
         <v>100</v>
       </c>
       <c r="O123" s="4" t="s">
-        <v>255</v>
+        <v>374</v>
       </c>
       <c r="P123" s="4" t="s">
-        <v>255</v>
+        <v>374</v>
       </c>
       <c r="Q123" s="3" t="s">
         <v>231</v>
@@ -8165,10 +8635,10 @@
         <v>100</v>
       </c>
       <c r="O124" s="4" t="s">
-        <v>255</v>
+        <v>375</v>
       </c>
       <c r="P124" s="4" t="s">
-        <v>255</v>
+        <v>375</v>
       </c>
       <c r="Q124" s="3" t="s">
         <v>231</v>
@@ -8221,10 +8691,10 @@
         <v>100</v>
       </c>
       <c r="O125" s="4" t="s">
-        <v>255</v>
+        <v>376</v>
       </c>
       <c r="P125" s="4" t="s">
-        <v>255</v>
+        <v>376</v>
       </c>
       <c r="Q125" s="3" t="s">
         <v>231</v>
@@ -8277,10 +8747,10 @@
         <v>100</v>
       </c>
       <c r="O126" s="4" t="s">
-        <v>255</v>
+        <v>377</v>
       </c>
       <c r="P126" s="4" t="s">
-        <v>255</v>
+        <v>377</v>
       </c>
       <c r="Q126" s="3" t="s">
         <v>231</v>
@@ -8333,10 +8803,10 @@
         <v>100</v>
       </c>
       <c r="O127" s="4" t="s">
-        <v>255</v>
+        <v>378</v>
       </c>
       <c r="P127" s="4" t="s">
-        <v>255</v>
+        <v>378</v>
       </c>
       <c r="Q127" s="3" t="s">
         <v>231</v>
@@ -8389,10 +8859,10 @@
         <v>100</v>
       </c>
       <c r="O128" s="4" t="s">
-        <v>255</v>
+        <v>379</v>
       </c>
       <c r="P128" s="4" t="s">
-        <v>255</v>
+        <v>379</v>
       </c>
       <c r="Q128" s="3" t="s">
         <v>231</v>
@@ -8445,10 +8915,10 @@
         <v>100</v>
       </c>
       <c r="O129" s="4" t="s">
-        <v>255</v>
+        <v>380</v>
       </c>
       <c r="P129" s="4" t="s">
-        <v>255</v>
+        <v>380</v>
       </c>
       <c r="Q129" s="3" t="s">
         <v>231</v>
@@ -8501,10 +8971,10 @@
         <v>100</v>
       </c>
       <c r="O130" s="4" t="s">
-        <v>255</v>
+        <v>381</v>
       </c>
       <c r="P130" s="4" t="s">
-        <v>255</v>
+        <v>381</v>
       </c>
       <c r="Q130" s="3" t="s">
         <v>231</v>
@@ -8557,10 +9027,10 @@
         <v>100</v>
       </c>
       <c r="O131" s="4" t="s">
-        <v>255</v>
+        <v>382</v>
       </c>
       <c r="P131" s="4" t="s">
-        <v>255</v>
+        <v>382</v>
       </c>
       <c r="Q131" s="3" t="s">
         <v>231</v>
@@ -8613,10 +9083,10 @@
         <v>100</v>
       </c>
       <c r="O132" s="4" t="s">
-        <v>255</v>
+        <v>383</v>
       </c>
       <c r="P132" s="4" t="s">
-        <v>255</v>
+        <v>383</v>
       </c>
       <c r="Q132" s="3" t="s">
         <v>231</v>
@@ -8669,10 +9139,10 @@
         <v>100</v>
       </c>
       <c r="O133" s="4" t="s">
-        <v>255</v>
+        <v>384</v>
       </c>
       <c r="P133" s="4" t="s">
-        <v>255</v>
+        <v>384</v>
       </c>
       <c r="Q133" s="3" t="s">
         <v>231</v>
@@ -8725,10 +9195,10 @@
         <v>100</v>
       </c>
       <c r="O134" s="4" t="s">
-        <v>255</v>
+        <v>385</v>
       </c>
       <c r="P134" s="4" t="s">
-        <v>255</v>
+        <v>385</v>
       </c>
       <c r="Q134" s="3" t="s">
         <v>231</v>
@@ -8781,10 +9251,10 @@
         <v>100</v>
       </c>
       <c r="O135" s="4" t="s">
-        <v>255</v>
+        <v>386</v>
       </c>
       <c r="P135" s="4" t="s">
-        <v>255</v>
+        <v>386</v>
       </c>
       <c r="Q135" s="3" t="s">
         <v>231</v>
@@ -8837,10 +9307,10 @@
         <v>100</v>
       </c>
       <c r="O136" s="4" t="s">
-        <v>255</v>
+        <v>387</v>
       </c>
       <c r="P136" s="4" t="s">
-        <v>255</v>
+        <v>387</v>
       </c>
       <c r="Q136" s="3" t="s">
         <v>231</v>
@@ -8893,10 +9363,10 @@
         <v>100</v>
       </c>
       <c r="O137" s="4" t="s">
-        <v>255</v>
+        <v>388</v>
       </c>
       <c r="P137" s="4" t="s">
-        <v>255</v>
+        <v>388</v>
       </c>
       <c r="Q137" s="3" t="s">
         <v>231</v>
@@ -8949,10 +9419,10 @@
         <v>100</v>
       </c>
       <c r="O138" s="4" t="s">
-        <v>255</v>
+        <v>389</v>
       </c>
       <c r="P138" s="4" t="s">
-        <v>255</v>
+        <v>389</v>
       </c>
       <c r="Q138" s="3" t="s">
         <v>231</v>
@@ -9005,10 +9475,10 @@
         <v>100</v>
       </c>
       <c r="O139" s="4" t="s">
-        <v>255</v>
+        <v>390</v>
       </c>
       <c r="P139" s="4" t="s">
-        <v>255</v>
+        <v>390</v>
       </c>
       <c r="Q139" s="3" t="s">
         <v>231</v>
@@ -9061,10 +9531,10 @@
         <v>100</v>
       </c>
       <c r="O140" s="4" t="s">
-        <v>255</v>
+        <v>391</v>
       </c>
       <c r="P140" s="4" t="s">
-        <v>255</v>
+        <v>391</v>
       </c>
       <c r="Q140" s="3" t="s">
         <v>231</v>
@@ -9117,10 +9587,10 @@
         <v>100</v>
       </c>
       <c r="O141" s="4" t="s">
-        <v>255</v>
+        <v>392</v>
       </c>
       <c r="P141" s="4" t="s">
-        <v>255</v>
+        <v>392</v>
       </c>
       <c r="Q141" s="3" t="s">
         <v>231</v>
@@ -9173,10 +9643,10 @@
         <v>100</v>
       </c>
       <c r="O142" s="4" t="s">
-        <v>255</v>
+        <v>393</v>
       </c>
       <c r="P142" s="4" t="s">
-        <v>255</v>
+        <v>393</v>
       </c>
       <c r="Q142" s="3" t="s">
         <v>231</v>
@@ -9229,10 +9699,10 @@
         <v>100</v>
       </c>
       <c r="O143" s="4" t="s">
-        <v>255</v>
+        <v>394</v>
       </c>
       <c r="P143" s="4" t="s">
-        <v>255</v>
+        <v>394</v>
       </c>
       <c r="Q143" s="3" t="s">
         <v>231</v>
@@ -9285,10 +9755,10 @@
         <v>100</v>
       </c>
       <c r="O144" s="4" t="s">
-        <v>255</v>
+        <v>395</v>
       </c>
       <c r="P144" s="4" t="s">
-        <v>255</v>
+        <v>395</v>
       </c>
       <c r="Q144" s="3" t="s">
         <v>231</v>
@@ -9341,10 +9811,10 @@
         <v>100</v>
       </c>
       <c r="O145" s="4" t="s">
-        <v>255</v>
+        <v>396</v>
       </c>
       <c r="P145" s="4" t="s">
-        <v>255</v>
+        <v>396</v>
       </c>
       <c r="Q145" s="3" t="s">
         <v>231</v>
@@ -9397,10 +9867,10 @@
         <v>100</v>
       </c>
       <c r="O146" s="4" t="s">
-        <v>255</v>
+        <v>397</v>
       </c>
       <c r="P146" s="4" t="s">
-        <v>255</v>
+        <v>397</v>
       </c>
       <c r="Q146" s="3" t="s">
         <v>231</v>
@@ -9453,10 +9923,10 @@
         <v>100</v>
       </c>
       <c r="O147" s="4" t="s">
-        <v>255</v>
+        <v>398</v>
       </c>
       <c r="P147" s="4" t="s">
-        <v>255</v>
+        <v>398</v>
       </c>
       <c r="Q147" s="3" t="s">
         <v>231</v>
@@ -9509,10 +9979,10 @@
         <v>100</v>
       </c>
       <c r="O148" s="4" t="s">
-        <v>255</v>
+        <v>399</v>
       </c>
       <c r="P148" s="4" t="s">
-        <v>255</v>
+        <v>399</v>
       </c>
       <c r="Q148" s="3" t="s">
         <v>231</v>
@@ -9565,10 +10035,10 @@
         <v>100</v>
       </c>
       <c r="O149" s="4" t="s">
-        <v>255</v>
+        <v>400</v>
       </c>
       <c r="P149" s="4" t="s">
-        <v>255</v>
+        <v>400</v>
       </c>
       <c r="Q149" s="3" t="s">
         <v>231</v>
@@ -9621,10 +10091,10 @@
         <v>100</v>
       </c>
       <c r="O150" s="4" t="s">
-        <v>255</v>
+        <v>401</v>
       </c>
       <c r="P150" s="4" t="s">
-        <v>255</v>
+        <v>401</v>
       </c>
       <c r="Q150" s="3" t="s">
         <v>231</v>
@@ -9677,10 +10147,10 @@
         <v>100</v>
       </c>
       <c r="O151" s="4" t="s">
-        <v>255</v>
+        <v>402</v>
       </c>
       <c r="P151" s="4" t="s">
-        <v>255</v>
+        <v>402</v>
       </c>
       <c r="Q151" s="3" t="s">
         <v>231</v>
@@ -9733,10 +10203,10 @@
         <v>100</v>
       </c>
       <c r="O152" s="4" t="s">
-        <v>255</v>
+        <v>403</v>
       </c>
       <c r="P152" s="4" t="s">
-        <v>255</v>
+        <v>403</v>
       </c>
       <c r="Q152" s="3" t="s">
         <v>231</v>
@@ -9789,10 +10259,10 @@
         <v>100</v>
       </c>
       <c r="O153" s="4" t="s">
-        <v>255</v>
+        <v>404</v>
       </c>
       <c r="P153" s="4" t="s">
-        <v>255</v>
+        <v>404</v>
       </c>
       <c r="Q153" s="3" t="s">
         <v>231</v>
@@ -9845,10 +10315,10 @@
         <v>100</v>
       </c>
       <c r="O154" s="4" t="s">
-        <v>255</v>
+        <v>405</v>
       </c>
       <c r="P154" s="4" t="s">
-        <v>255</v>
+        <v>405</v>
       </c>
       <c r="Q154" s="3" t="s">
         <v>231</v>
@@ -9901,10 +10371,10 @@
         <v>100</v>
       </c>
       <c r="O155" s="4" t="s">
-        <v>255</v>
+        <v>406</v>
       </c>
       <c r="P155" s="4" t="s">
-        <v>255</v>
+        <v>406</v>
       </c>
       <c r="Q155" s="3" t="s">
         <v>231</v>
@@ -9957,10 +10427,10 @@
         <v>100</v>
       </c>
       <c r="O156" s="4" t="s">
-        <v>255</v>
+        <v>407</v>
       </c>
       <c r="P156" s="4" t="s">
-        <v>255</v>
+        <v>407</v>
       </c>
       <c r="Q156" s="3" t="s">
         <v>231</v>
@@ -10013,10 +10483,10 @@
         <v>100</v>
       </c>
       <c r="O157" s="4" t="s">
-        <v>255</v>
+        <v>408</v>
       </c>
       <c r="P157" s="4" t="s">
-        <v>255</v>
+        <v>408</v>
       </c>
       <c r="Q157" s="3" t="s">
         <v>231</v>
@@ -10069,10 +10539,10 @@
         <v>100</v>
       </c>
       <c r="O158" s="4" t="s">
-        <v>255</v>
+        <v>409</v>
       </c>
       <c r="P158" s="4" t="s">
-        <v>255</v>
+        <v>409</v>
       </c>
       <c r="Q158" s="3" t="s">
         <v>231</v>
@@ -10125,10 +10595,10 @@
         <v>100</v>
       </c>
       <c r="O159" s="4" t="s">
-        <v>255</v>
+        <v>410</v>
       </c>
       <c r="P159" s="4" t="s">
-        <v>255</v>
+        <v>410</v>
       </c>
       <c r="Q159" s="3" t="s">
         <v>231</v>
@@ -10181,10 +10651,10 @@
         <v>100</v>
       </c>
       <c r="O160" s="4" t="s">
-        <v>255</v>
+        <v>411</v>
       </c>
       <c r="P160" s="4" t="s">
-        <v>255</v>
+        <v>411</v>
       </c>
       <c r="Q160" s="3" t="s">
         <v>231</v>
@@ -10237,10 +10707,10 @@
         <v>100</v>
       </c>
       <c r="O161" s="4" t="s">
-        <v>255</v>
+        <v>412</v>
       </c>
       <c r="P161" s="4" t="s">
-        <v>255</v>
+        <v>412</v>
       </c>
       <c r="Q161" s="3" t="s">
         <v>231</v>
@@ -10293,10 +10763,10 @@
         <v>100</v>
       </c>
       <c r="O162" s="4" t="s">
-        <v>255</v>
+        <v>413</v>
       </c>
       <c r="P162" s="4" t="s">
-        <v>255</v>
+        <v>413</v>
       </c>
       <c r="Q162" s="3" t="s">
         <v>231</v>
@@ -10349,10 +10819,10 @@
         <v>100</v>
       </c>
       <c r="O163" s="4" t="s">
-        <v>255</v>
+        <v>414</v>
       </c>
       <c r="P163" s="4" t="s">
-        <v>255</v>
+        <v>414</v>
       </c>
       <c r="Q163" s="3" t="s">
         <v>231</v>
@@ -10405,10 +10875,10 @@
         <v>100</v>
       </c>
       <c r="O164" s="4" t="s">
-        <v>255</v>
+        <v>415</v>
       </c>
       <c r="P164" s="4" t="s">
-        <v>255</v>
+        <v>415</v>
       </c>
       <c r="Q164" s="3" t="s">
         <v>231</v>

--- a/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5934785D-31C5-4712-AB96-E2A5AB6B9351}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{977FEFDA-0F99-420F-8269-FC341F7B6387}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_barries_v8" sheetId="1" r:id="rId1"/>
@@ -871,486 +871,486 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>110001:300_110002:550_110003:200</t>
+    <t>20001:101</t>
+  </si>
+  <si>
+    <t>30001:101</t>
+  </si>
+  <si>
+    <t>40001:101</t>
+  </si>
+  <si>
+    <t>50001:101</t>
+  </si>
+  <si>
+    <t>60001:101</t>
+  </si>
+  <si>
+    <t>70001:101</t>
+  </si>
+  <si>
+    <t>80001:101</t>
+  </si>
+  <si>
+    <t>90001:101</t>
+  </si>
+  <si>
+    <t>100001:101</t>
+  </si>
+  <si>
+    <t>120001:101</t>
+  </si>
+  <si>
+    <t>130001:101</t>
+  </si>
+  <si>
+    <t>140001:101</t>
+  </si>
+  <si>
+    <t>150001:101</t>
+  </si>
+  <si>
+    <t>160001:101</t>
+  </si>
+  <si>
+    <t>170001:101</t>
+  </si>
+  <si>
+    <t>180001:101</t>
+  </si>
+  <si>
+    <t>190001:101</t>
+  </si>
+  <si>
+    <t>200001:101</t>
+  </si>
+  <si>
+    <t>210001:101</t>
+  </si>
+  <si>
+    <t>220001:101</t>
+  </si>
+  <si>
+    <t>230001:101</t>
+  </si>
+  <si>
+    <t>240001:101</t>
+  </si>
+  <si>
+    <t>250001:101</t>
+  </si>
+  <si>
+    <t>260001:101</t>
+  </si>
+  <si>
+    <t>270001:101</t>
+  </si>
+  <si>
+    <t>280001:101</t>
+  </si>
+  <si>
+    <t>290001:101</t>
+  </si>
+  <si>
+    <t>300001:101</t>
+  </si>
+  <si>
+    <t>310001:101</t>
+  </si>
+  <si>
+    <t>320001:101</t>
+  </si>
+  <si>
+    <t>330001:101</t>
+  </si>
+  <si>
+    <t>340001:101</t>
+  </si>
+  <si>
+    <t>350001:101</t>
+  </si>
+  <si>
+    <t>360001:101</t>
+  </si>
+  <si>
+    <t>370001:101</t>
+  </si>
+  <si>
+    <t>380001:101</t>
+  </si>
+  <si>
+    <t>390001:101</t>
+  </si>
+  <si>
+    <t>400001:101</t>
+  </si>
+  <si>
+    <t>410001:101</t>
+  </si>
+  <si>
+    <t>420001:101</t>
+  </si>
+  <si>
+    <t>430001:101</t>
+  </si>
+  <si>
+    <t>440001:101</t>
+  </si>
+  <si>
+    <t>450001:101</t>
+  </si>
+  <si>
+    <t>460001:101</t>
+  </si>
+  <si>
+    <t>470001:101</t>
+  </si>
+  <si>
+    <t>480001:101</t>
+  </si>
+  <si>
+    <t>490001:101</t>
+  </si>
+  <si>
+    <t>500001:101</t>
+  </si>
+  <si>
+    <t>510001:101</t>
+  </si>
+  <si>
+    <t>520001:101</t>
+  </si>
+  <si>
+    <t>530001:101</t>
+  </si>
+  <si>
+    <t>540001:101</t>
+  </si>
+  <si>
+    <t>550001:101</t>
+  </si>
+  <si>
+    <t>560001:101</t>
+  </si>
+  <si>
+    <t>570001:101</t>
+  </si>
+  <si>
+    <t>580001:101</t>
+  </si>
+  <si>
+    <t>590001:101</t>
+  </si>
+  <si>
+    <t>600001:101</t>
+  </si>
+  <si>
+    <t>610001:101</t>
+  </si>
+  <si>
+    <t>620001:101</t>
+  </si>
+  <si>
+    <t>630001:101</t>
+  </si>
+  <si>
+    <t>640001:101</t>
+  </si>
+  <si>
+    <t>650001:101</t>
+  </si>
+  <si>
+    <t>660001:101</t>
+  </si>
+  <si>
+    <t>670001:101</t>
+  </si>
+  <si>
+    <t>680001:101</t>
+  </si>
+  <si>
+    <t>690001:101</t>
+  </si>
+  <si>
+    <t>700001:101</t>
+  </si>
+  <si>
+    <t>710001:101</t>
+  </si>
+  <si>
+    <t>720001:101</t>
+  </si>
+  <si>
+    <t>730001:101</t>
+  </si>
+  <si>
+    <t>740001:101</t>
+  </si>
+  <si>
+    <t>750001:101</t>
+  </si>
+  <si>
+    <t>760001:101</t>
+  </si>
+  <si>
+    <t>770001:101</t>
+  </si>
+  <si>
+    <t>780001:101</t>
+  </si>
+  <si>
+    <t>790001:101</t>
+  </si>
+  <si>
+    <t>800001:101</t>
+  </si>
+  <si>
+    <t>810001:101</t>
+  </si>
+  <si>
+    <t>820001:101</t>
+  </si>
+  <si>
+    <t>830001:101</t>
+  </si>
+  <si>
+    <t>840001:101</t>
+  </si>
+  <si>
+    <t>850001:101</t>
+  </si>
+  <si>
+    <t>860001:101</t>
+  </si>
+  <si>
+    <t>870001:101</t>
+  </si>
+  <si>
+    <t>880001:101</t>
+  </si>
+  <si>
+    <t>890001:101</t>
+  </si>
+  <si>
+    <t>900001:101</t>
+  </si>
+  <si>
+    <t>910001:101</t>
+  </si>
+  <si>
+    <t>920001:101</t>
+  </si>
+  <si>
+    <t>930001:101</t>
+  </si>
+  <si>
+    <t>940001:101</t>
+  </si>
+  <si>
+    <t>950001:101</t>
+  </si>
+  <si>
+    <t>960001:101</t>
+  </si>
+  <si>
+    <t>970001:101</t>
+  </si>
+  <si>
+    <t>980001:101</t>
+  </si>
+  <si>
+    <t>990001:101</t>
+  </si>
+  <si>
+    <t>1000001:101</t>
+  </si>
+  <si>
+    <t>1010001:101</t>
+  </si>
+  <si>
+    <t>1020001:101</t>
+  </si>
+  <si>
+    <t>1030001:101</t>
+  </si>
+  <si>
+    <t>1040001:101</t>
+  </si>
+  <si>
+    <t>1050001:101</t>
+  </si>
+  <si>
+    <t>1060001:101</t>
+  </si>
+  <si>
+    <t>1070001:101</t>
+  </si>
+  <si>
+    <t>1080001:101</t>
+  </si>
+  <si>
+    <t>1090001:101</t>
+  </si>
+  <si>
+    <t>1100001:101</t>
+  </si>
+  <si>
+    <t>1110001:101</t>
+  </si>
+  <si>
+    <t>1120001:101</t>
+  </si>
+  <si>
+    <t>1130001:101</t>
+  </si>
+  <si>
+    <t>1140001:101</t>
+  </si>
+  <si>
+    <t>1150001:101</t>
+  </si>
+  <si>
+    <t>1160001:101</t>
+  </si>
+  <si>
+    <t>1170001:101</t>
+  </si>
+  <si>
+    <t>1180001:101</t>
+  </si>
+  <si>
+    <t>1190001:101</t>
+  </si>
+  <si>
+    <t>1200001:101</t>
+  </si>
+  <si>
+    <t>1210001:101</t>
+  </si>
+  <si>
+    <t>1220001:101</t>
+  </si>
+  <si>
+    <t>1230001:101</t>
+  </si>
+  <si>
+    <t>1240001:101</t>
+  </si>
+  <si>
+    <t>1250001:101</t>
+  </si>
+  <si>
+    <t>1260001:101</t>
+  </si>
+  <si>
+    <t>1270001:101</t>
+  </si>
+  <si>
+    <t>1280001:101</t>
+  </si>
+  <si>
+    <t>1290001:101</t>
+  </si>
+  <si>
+    <t>1300001:101</t>
+  </si>
+  <si>
+    <t>1310001:101</t>
+  </si>
+  <si>
+    <t>1320001:101</t>
+  </si>
+  <si>
+    <t>1330001:101</t>
+  </si>
+  <si>
+    <t>1340001:101</t>
+  </si>
+  <si>
+    <t>1350001:101</t>
+  </si>
+  <si>
+    <t>1360001:101</t>
+  </si>
+  <si>
+    <t>1370001:101</t>
+  </si>
+  <si>
+    <t>1380001:101</t>
+  </si>
+  <si>
+    <t>1390001:101</t>
+  </si>
+  <si>
+    <t>1400001:101</t>
+  </si>
+  <si>
+    <t>1410001:101</t>
+  </si>
+  <si>
+    <t>1420001:101</t>
+  </si>
+  <si>
+    <t>1430001:101</t>
+  </si>
+  <si>
+    <t>1440001:101</t>
+  </si>
+  <si>
+    <t>1450001:101</t>
+  </si>
+  <si>
+    <t>1460001:101</t>
+  </si>
+  <si>
+    <t>1470001:101</t>
+  </si>
+  <si>
+    <t>1480001:101</t>
+  </si>
+  <si>
+    <t>1490001:101</t>
+  </si>
+  <si>
+    <t>1500001:101</t>
+  </si>
+  <si>
+    <t>1510001:101</t>
+  </si>
+  <si>
+    <t>1520001:101</t>
+  </si>
+  <si>
+    <t>1530001:101</t>
+  </si>
+  <si>
+    <t>1540001:101</t>
+  </si>
+  <si>
+    <t>1550001:101</t>
+  </si>
+  <si>
+    <t>1560001:101</t>
+  </si>
+  <si>
+    <t>1570001:101</t>
+  </si>
+  <si>
+    <t>1580001:101</t>
+  </si>
+  <si>
+    <t>1590001:101</t>
+  </si>
+  <si>
+    <t>1600001:101</t>
+  </si>
+  <si>
+    <t>110001:300_110002:550_110003:700</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>110001:550_110002:750_110003:550</t>
+    <t>110001:550_110002:850_1100031150</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>20001:101</t>
-  </si>
-  <si>
-    <t>30001:101</t>
-  </si>
-  <si>
-    <t>40001:101</t>
-  </si>
-  <si>
-    <t>50001:101</t>
-  </si>
-  <si>
-    <t>60001:101</t>
-  </si>
-  <si>
-    <t>70001:101</t>
-  </si>
-  <si>
-    <t>80001:101</t>
-  </si>
-  <si>
-    <t>90001:101</t>
-  </si>
-  <si>
-    <t>100001:101</t>
-  </si>
-  <si>
-    <t>120001:101</t>
-  </si>
-  <si>
-    <t>130001:101</t>
-  </si>
-  <si>
-    <t>140001:101</t>
-  </si>
-  <si>
-    <t>150001:101</t>
-  </si>
-  <si>
-    <t>160001:101</t>
-  </si>
-  <si>
-    <t>170001:101</t>
-  </si>
-  <si>
-    <t>180001:101</t>
-  </si>
-  <si>
-    <t>190001:101</t>
-  </si>
-  <si>
-    <t>200001:101</t>
-  </si>
-  <si>
-    <t>210001:101</t>
-  </si>
-  <si>
-    <t>220001:101</t>
-  </si>
-  <si>
-    <t>230001:101</t>
-  </si>
-  <si>
-    <t>240001:101</t>
-  </si>
-  <si>
-    <t>250001:101</t>
-  </si>
-  <si>
-    <t>260001:101</t>
-  </si>
-  <si>
-    <t>270001:101</t>
-  </si>
-  <si>
-    <t>280001:101</t>
-  </si>
-  <si>
-    <t>290001:101</t>
-  </si>
-  <si>
-    <t>300001:101</t>
-  </si>
-  <si>
-    <t>310001:101</t>
-  </si>
-  <si>
-    <t>320001:101</t>
-  </si>
-  <si>
-    <t>330001:101</t>
-  </si>
-  <si>
-    <t>340001:101</t>
-  </si>
-  <si>
-    <t>350001:101</t>
-  </si>
-  <si>
-    <t>360001:101</t>
-  </si>
-  <si>
-    <t>370001:101</t>
-  </si>
-  <si>
-    <t>380001:101</t>
-  </si>
-  <si>
-    <t>390001:101</t>
-  </si>
-  <si>
-    <t>400001:101</t>
-  </si>
-  <si>
-    <t>410001:101</t>
-  </si>
-  <si>
-    <t>420001:101</t>
-  </si>
-  <si>
-    <t>430001:101</t>
-  </si>
-  <si>
-    <t>440001:101</t>
-  </si>
-  <si>
-    <t>450001:101</t>
-  </si>
-  <si>
-    <t>460001:101</t>
-  </si>
-  <si>
-    <t>470001:101</t>
-  </si>
-  <si>
-    <t>480001:101</t>
-  </si>
-  <si>
-    <t>490001:101</t>
-  </si>
-  <si>
-    <t>500001:101</t>
-  </si>
-  <si>
-    <t>510001:101</t>
-  </si>
-  <si>
-    <t>520001:101</t>
-  </si>
-  <si>
-    <t>530001:101</t>
-  </si>
-  <si>
-    <t>540001:101</t>
-  </si>
-  <si>
-    <t>550001:101</t>
-  </si>
-  <si>
-    <t>560001:101</t>
-  </si>
-  <si>
-    <t>570001:101</t>
-  </si>
-  <si>
-    <t>580001:101</t>
-  </si>
-  <si>
-    <t>590001:101</t>
-  </si>
-  <si>
-    <t>600001:101</t>
-  </si>
-  <si>
-    <t>610001:101</t>
-  </si>
-  <si>
-    <t>620001:101</t>
-  </si>
-  <si>
-    <t>630001:101</t>
-  </si>
-  <si>
-    <t>640001:101</t>
-  </si>
-  <si>
-    <t>650001:101</t>
-  </si>
-  <si>
-    <t>660001:101</t>
-  </si>
-  <si>
-    <t>670001:101</t>
-  </si>
-  <si>
-    <t>680001:101</t>
-  </si>
-  <si>
-    <t>690001:101</t>
-  </si>
-  <si>
-    <t>700001:101</t>
-  </si>
-  <si>
-    <t>710001:101</t>
-  </si>
-  <si>
-    <t>720001:101</t>
-  </si>
-  <si>
-    <t>730001:101</t>
-  </si>
-  <si>
-    <t>740001:101</t>
-  </si>
-  <si>
-    <t>750001:101</t>
-  </si>
-  <si>
-    <t>760001:101</t>
-  </si>
-  <si>
-    <t>770001:101</t>
-  </si>
-  <si>
-    <t>780001:101</t>
-  </si>
-  <si>
-    <t>790001:101</t>
-  </si>
-  <si>
-    <t>800001:101</t>
-  </si>
-  <si>
-    <t>810001:101</t>
-  </si>
-  <si>
-    <t>820001:101</t>
-  </si>
-  <si>
-    <t>830001:101</t>
-  </si>
-  <si>
-    <t>840001:101</t>
-  </si>
-  <si>
-    <t>850001:101</t>
-  </si>
-  <si>
-    <t>860001:101</t>
-  </si>
-  <si>
-    <t>870001:101</t>
-  </si>
-  <si>
-    <t>880001:101</t>
-  </si>
-  <si>
-    <t>890001:101</t>
-  </si>
-  <si>
-    <t>900001:101</t>
-  </si>
-  <si>
-    <t>910001:101</t>
-  </si>
-  <si>
-    <t>920001:101</t>
-  </si>
-  <si>
-    <t>930001:101</t>
-  </si>
-  <si>
-    <t>940001:101</t>
-  </si>
-  <si>
-    <t>950001:101</t>
-  </si>
-  <si>
-    <t>960001:101</t>
-  </si>
-  <si>
-    <t>970001:101</t>
-  </si>
-  <si>
-    <t>980001:101</t>
-  </si>
-  <si>
-    <t>990001:101</t>
-  </si>
-  <si>
-    <t>1000001:101</t>
-  </si>
-  <si>
-    <t>1010001:101</t>
-  </si>
-  <si>
-    <t>1020001:101</t>
-  </si>
-  <si>
-    <t>1030001:101</t>
-  </si>
-  <si>
-    <t>1040001:101</t>
-  </si>
-  <si>
-    <t>1050001:101</t>
-  </si>
-  <si>
-    <t>1060001:101</t>
-  </si>
-  <si>
-    <t>1070001:101</t>
-  </si>
-  <si>
-    <t>1080001:101</t>
-  </si>
-  <si>
-    <t>1090001:101</t>
-  </si>
-  <si>
-    <t>1100001:101</t>
-  </si>
-  <si>
-    <t>1110001:101</t>
-  </si>
-  <si>
-    <t>1120001:101</t>
-  </si>
-  <si>
-    <t>1130001:101</t>
-  </si>
-  <si>
-    <t>1140001:101</t>
-  </si>
-  <si>
-    <t>1150001:101</t>
-  </si>
-  <si>
-    <t>1160001:101</t>
-  </si>
-  <si>
-    <t>1170001:101</t>
-  </si>
-  <si>
-    <t>1180001:101</t>
-  </si>
-  <si>
-    <t>1190001:101</t>
-  </si>
-  <si>
-    <t>1200001:101</t>
-  </si>
-  <si>
-    <t>1210001:101</t>
-  </si>
-  <si>
-    <t>1220001:101</t>
-  </si>
-  <si>
-    <t>1230001:101</t>
-  </si>
-  <si>
-    <t>1240001:101</t>
-  </si>
-  <si>
-    <t>1250001:101</t>
-  </si>
-  <si>
-    <t>1260001:101</t>
-  </si>
-  <si>
-    <t>1270001:101</t>
-  </si>
-  <si>
-    <t>1280001:101</t>
-  </si>
-  <si>
-    <t>1290001:101</t>
-  </si>
-  <si>
-    <t>1300001:101</t>
-  </si>
-  <si>
-    <t>1310001:101</t>
-  </si>
-  <si>
-    <t>1320001:101</t>
-  </si>
-  <si>
-    <t>1330001:101</t>
-  </si>
-  <si>
-    <t>1340001:101</t>
-  </si>
-  <si>
-    <t>1350001:101</t>
-  </si>
-  <si>
-    <t>1360001:101</t>
-  </si>
-  <si>
-    <t>1370001:101</t>
-  </si>
-  <si>
-    <t>1380001:101</t>
-  </si>
-  <si>
-    <t>1390001:101</t>
-  </si>
-  <si>
-    <t>1400001:101</t>
-  </si>
-  <si>
-    <t>1410001:101</t>
-  </si>
-  <si>
-    <t>1420001:101</t>
-  </si>
-  <si>
-    <t>1430001:101</t>
-  </si>
-  <si>
-    <t>1440001:101</t>
-  </si>
-  <si>
-    <t>1450001:101</t>
-  </si>
-  <si>
-    <t>1460001:101</t>
-  </si>
-  <si>
-    <t>1470001:101</t>
-  </si>
-  <si>
-    <t>1480001:101</t>
-  </si>
-  <si>
-    <t>1490001:101</t>
-  </si>
-  <si>
-    <t>1500001:101</t>
-  </si>
-  <si>
-    <t>1510001:101</t>
-  </si>
-  <si>
-    <t>1520001:101</t>
-  </si>
-  <si>
-    <t>1530001:101</t>
-  </si>
-  <si>
-    <t>1540001:101</t>
-  </si>
-  <si>
-    <t>1550001:101</t>
-  </si>
-  <si>
-    <t>1560001:101</t>
-  </si>
-  <si>
-    <t>1570001:101</t>
-  </si>
-  <si>
-    <t>1580001:101</t>
-  </si>
-  <si>
-    <t>1590001:101</t>
-  </si>
-  <si>
-    <t>1600001:101</t>
   </si>
 </sst>
 </file>
@@ -2018,10 +2018,10 @@
         <v>200</v>
       </c>
       <c r="O6" s="4" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="P6" s="4" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="Q6" s="3" t="s">
         <v>231</v>
@@ -2074,10 +2074,10 @@
         <v>300</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="P7" s="4" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="Q7" s="3" t="s">
         <v>231</v>
@@ -2130,10 +2130,10 @@
         <v>400</v>
       </c>
       <c r="O8" s="4" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="P8" s="4" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="Q8" s="3" t="s">
         <v>231</v>
@@ -2186,10 +2186,10 @@
         <v>500</v>
       </c>
       <c r="O9" s="4" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="P9" s="4" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="Q9" s="3" t="s">
         <v>231</v>
@@ -2242,10 +2242,10 @@
         <v>600</v>
       </c>
       <c r="O10" s="4" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="P10" s="4" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="Q10" s="3" t="s">
         <v>231</v>
@@ -2298,10 +2298,10 @@
         <v>100</v>
       </c>
       <c r="O11" s="4" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="P11" s="4" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="Q11" s="3" t="s">
         <v>231</v>
@@ -2354,10 +2354,10 @@
         <v>100</v>
       </c>
       <c r="O12" s="4" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="P12" s="4" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="Q12" s="3" t="s">
         <v>231</v>
@@ -2410,10 +2410,10 @@
         <v>100</v>
       </c>
       <c r="O13" s="4" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="P13" s="4" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="Q13" s="3" t="s">
         <v>231</v>
@@ -2466,10 +2466,10 @@
         <v>100</v>
       </c>
       <c r="O14" s="4" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="P14" s="4" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>231</v>
@@ -2537,10 +2537,10 @@
         <v>250</v>
       </c>
       <c r="T15" s="1" t="s">
-        <v>256</v>
+        <v>414</v>
       </c>
       <c r="U15" s="1" t="s">
-        <v>257</v>
+        <v>415</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.15">
@@ -2587,10 +2587,10 @@
         <v>100</v>
       </c>
       <c r="O16" s="4" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="P16" s="4" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="Q16" s="3" t="s">
         <v>231</v>
@@ -2643,10 +2643,10 @@
         <v>100</v>
       </c>
       <c r="O17" s="4" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="P17" s="4" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="Q17" s="3" t="s">
         <v>231</v>
@@ -2699,10 +2699,10 @@
         <v>100</v>
       </c>
       <c r="O18" s="4" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="P18" s="4" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="Q18" s="3" t="s">
         <v>231</v>
@@ -2755,10 +2755,10 @@
         <v>100</v>
       </c>
       <c r="O19" s="4" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="P19" s="4" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="Q19" s="3" t="s">
         <v>231</v>
@@ -2811,10 +2811,10 @@
         <v>100</v>
       </c>
       <c r="O20" s="4" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="P20" s="4" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="Q20" s="3" t="s">
         <v>231</v>
@@ -2867,10 +2867,10 @@
         <v>100</v>
       </c>
       <c r="O21" s="4" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="P21" s="4" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="Q21" s="3" t="s">
         <v>231</v>
@@ -2923,10 +2923,10 @@
         <v>100</v>
       </c>
       <c r="O22" s="4" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="P22" s="4" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="Q22" s="3" t="s">
         <v>231</v>
@@ -2979,10 +2979,10 @@
         <v>100</v>
       </c>
       <c r="O23" s="4" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="P23" s="4" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="Q23" s="3" t="s">
         <v>231</v>
@@ -3035,10 +3035,10 @@
         <v>100</v>
       </c>
       <c r="O24" s="4" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="P24" s="4" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="Q24" s="3" t="s">
         <v>231</v>
@@ -3091,10 +3091,10 @@
         <v>100</v>
       </c>
       <c r="O25" s="4" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="P25" s="4" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="Q25" s="3" t="s">
         <v>231</v>
@@ -3147,10 +3147,10 @@
         <v>100</v>
       </c>
       <c r="O26" s="4" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="P26" s="4" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="Q26" s="3" t="s">
         <v>231</v>
@@ -3203,10 +3203,10 @@
         <v>100</v>
       </c>
       <c r="O27" s="4" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="P27" s="4" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="Q27" s="3" t="s">
         <v>231</v>
@@ -3259,10 +3259,10 @@
         <v>100</v>
       </c>
       <c r="O28" s="4" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="P28" s="4" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="Q28" s="3" t="s">
         <v>231</v>
@@ -3315,10 +3315,10 @@
         <v>100</v>
       </c>
       <c r="O29" s="4" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="P29" s="4" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="Q29" s="3" t="s">
         <v>231</v>
@@ -3371,10 +3371,10 @@
         <v>100</v>
       </c>
       <c r="O30" s="4" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="P30" s="4" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="Q30" s="3" t="s">
         <v>231</v>
@@ -3427,10 +3427,10 @@
         <v>100</v>
       </c>
       <c r="O31" s="4" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="P31" s="4" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="Q31" s="3" t="s">
         <v>231</v>
@@ -3483,10 +3483,10 @@
         <v>100</v>
       </c>
       <c r="O32" s="4" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="P32" s="4" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="Q32" s="3" t="s">
         <v>231</v>
@@ -3539,10 +3539,10 @@
         <v>100</v>
       </c>
       <c r="O33" s="4" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="P33" s="4" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="Q33" s="3" t="s">
         <v>231</v>
@@ -3595,10 +3595,10 @@
         <v>100</v>
       </c>
       <c r="O34" s="4" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="P34" s="4" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="Q34" s="3" t="s">
         <v>231</v>
@@ -3651,10 +3651,10 @@
         <v>100</v>
       </c>
       <c r="O35" s="4" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="P35" s="4" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="Q35" s="3" t="s">
         <v>231</v>
@@ -3707,10 +3707,10 @@
         <v>100</v>
       </c>
       <c r="O36" s="4" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="P36" s="4" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="Q36" s="3" t="s">
         <v>231</v>
@@ -3763,10 +3763,10 @@
         <v>100</v>
       </c>
       <c r="O37" s="4" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="P37" s="4" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="Q37" s="3" t="s">
         <v>231</v>
@@ -3819,10 +3819,10 @@
         <v>100</v>
       </c>
       <c r="O38" s="4" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="P38" s="4" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="Q38" s="3" t="s">
         <v>231</v>
@@ -3875,10 +3875,10 @@
         <v>100</v>
       </c>
       <c r="O39" s="4" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="P39" s="4" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="Q39" s="3" t="s">
         <v>231</v>
@@ -3931,10 +3931,10 @@
         <v>100</v>
       </c>
       <c r="O40" s="4" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="P40" s="4" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="Q40" s="3" t="s">
         <v>231</v>
@@ -3987,10 +3987,10 @@
         <v>100</v>
       </c>
       <c r="O41" s="4" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="P41" s="4" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="Q41" s="3" t="s">
         <v>231</v>
@@ -4043,10 +4043,10 @@
         <v>100</v>
       </c>
       <c r="O42" s="4" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="P42" s="4" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="Q42" s="3" t="s">
         <v>231</v>
@@ -4099,10 +4099,10 @@
         <v>100</v>
       </c>
       <c r="O43" s="4" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="P43" s="4" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="Q43" s="3" t="s">
         <v>231</v>
@@ -4155,10 +4155,10 @@
         <v>100</v>
       </c>
       <c r="O44" s="4" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="P44" s="4" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="Q44" s="3" t="s">
         <v>231</v>
@@ -4211,10 +4211,10 @@
         <v>100</v>
       </c>
       <c r="O45" s="4" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="P45" s="4" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="Q45" s="3" t="s">
         <v>231</v>
@@ -4267,10 +4267,10 @@
         <v>100</v>
       </c>
       <c r="O46" s="4" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="P46" s="4" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="Q46" s="3" t="s">
         <v>231</v>
@@ -4323,10 +4323,10 @@
         <v>100</v>
       </c>
       <c r="O47" s="4" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="P47" s="4" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="Q47" s="3" t="s">
         <v>231</v>
@@ -4379,10 +4379,10 @@
         <v>100</v>
       </c>
       <c r="O48" s="4" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="P48" s="4" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="Q48" s="3" t="s">
         <v>231</v>
@@ -4435,10 +4435,10 @@
         <v>100</v>
       </c>
       <c r="O49" s="4" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="P49" s="4" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="Q49" s="3" t="s">
         <v>231</v>
@@ -4491,10 +4491,10 @@
         <v>100</v>
       </c>
       <c r="O50" s="4" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="P50" s="4" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="Q50" s="3" t="s">
         <v>231</v>
@@ -4547,10 +4547,10 @@
         <v>100</v>
       </c>
       <c r="O51" s="4" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="P51" s="4" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="Q51" s="3" t="s">
         <v>231</v>
@@ -4603,10 +4603,10 @@
         <v>100</v>
       </c>
       <c r="O52" s="4" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="P52" s="4" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="Q52" s="3" t="s">
         <v>231</v>
@@ -4659,10 +4659,10 @@
         <v>100</v>
       </c>
       <c r="O53" s="4" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="P53" s="4" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="Q53" s="3" t="s">
         <v>231</v>
@@ -4715,10 +4715,10 @@
         <v>100</v>
       </c>
       <c r="O54" s="4" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="P54" s="4" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="Q54" s="3" t="s">
         <v>231</v>
@@ -4771,10 +4771,10 @@
         <v>100</v>
       </c>
       <c r="O55" s="4" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="P55" s="4" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="Q55" s="3" t="s">
         <v>231</v>
@@ -4827,10 +4827,10 @@
         <v>100</v>
       </c>
       <c r="O56" s="4" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="P56" s="4" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="Q56" s="3" t="s">
         <v>231</v>
@@ -4883,10 +4883,10 @@
         <v>100</v>
       </c>
       <c r="O57" s="4" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="P57" s="4" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="Q57" s="3" t="s">
         <v>231</v>
@@ -4939,10 +4939,10 @@
         <v>100</v>
       </c>
       <c r="O58" s="4" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="P58" s="4" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="Q58" s="3" t="s">
         <v>231</v>
@@ -4995,10 +4995,10 @@
         <v>100</v>
       </c>
       <c r="O59" s="4" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="P59" s="4" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="Q59" s="3" t="s">
         <v>231</v>
@@ -5051,10 +5051,10 @@
         <v>100</v>
       </c>
       <c r="O60" s="4" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="P60" s="4" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="Q60" s="3" t="s">
         <v>231</v>
@@ -5107,10 +5107,10 @@
         <v>100</v>
       </c>
       <c r="O61" s="4" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="P61" s="4" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="Q61" s="3" t="s">
         <v>231</v>
@@ -5163,10 +5163,10 @@
         <v>100</v>
       </c>
       <c r="O62" s="4" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="P62" s="4" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="Q62" s="3" t="s">
         <v>231</v>
@@ -5219,10 +5219,10 @@
         <v>100</v>
       </c>
       <c r="O63" s="4" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="P63" s="4" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="Q63" s="3" t="s">
         <v>231</v>
@@ -5275,10 +5275,10 @@
         <v>100</v>
       </c>
       <c r="O64" s="4" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="P64" s="4" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="Q64" s="3" t="s">
         <v>231</v>
@@ -5331,10 +5331,10 @@
         <v>100</v>
       </c>
       <c r="O65" s="4" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="P65" s="4" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="Q65" s="3" t="s">
         <v>231</v>
@@ -5387,10 +5387,10 @@
         <v>100</v>
       </c>
       <c r="O66" s="4" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="P66" s="4" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="Q66" s="3" t="s">
         <v>231</v>
@@ -5443,10 +5443,10 @@
         <v>100</v>
       </c>
       <c r="O67" s="4" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="P67" s="4" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="Q67" s="3" t="s">
         <v>231</v>
@@ -5499,10 +5499,10 @@
         <v>100</v>
       </c>
       <c r="O68" s="4" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="P68" s="4" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="Q68" s="3" t="s">
         <v>231</v>
@@ -5555,10 +5555,10 @@
         <v>100</v>
       </c>
       <c r="O69" s="4" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="P69" s="4" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="Q69" s="3" t="s">
         <v>231</v>
@@ -5611,10 +5611,10 @@
         <v>100</v>
       </c>
       <c r="O70" s="4" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="P70" s="4" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="Q70" s="3" t="s">
         <v>231</v>
@@ -5667,10 +5667,10 @@
         <v>100</v>
       </c>
       <c r="O71" s="4" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="P71" s="4" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="Q71" s="3" t="s">
         <v>231</v>
@@ -5723,10 +5723,10 @@
         <v>100</v>
       </c>
       <c r="O72" s="4" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="P72" s="4" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="Q72" s="3" t="s">
         <v>231</v>
@@ -5779,10 +5779,10 @@
         <v>100</v>
       </c>
       <c r="O73" s="4" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="P73" s="4" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="Q73" s="3" t="s">
         <v>231</v>
@@ -5835,10 +5835,10 @@
         <v>100</v>
       </c>
       <c r="O74" s="4" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="P74" s="4" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="Q74" s="3" t="s">
         <v>231</v>
@@ -5891,10 +5891,10 @@
         <v>100</v>
       </c>
       <c r="O75" s="4" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="P75" s="4" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="Q75" s="3" t="s">
         <v>231</v>
@@ -5947,10 +5947,10 @@
         <v>100</v>
       </c>
       <c r="O76" s="4" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="P76" s="4" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="Q76" s="3" t="s">
         <v>231</v>
@@ -6003,10 +6003,10 @@
         <v>100</v>
       </c>
       <c r="O77" s="4" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="P77" s="4" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="Q77" s="3" t="s">
         <v>231</v>
@@ -6059,10 +6059,10 @@
         <v>100</v>
       </c>
       <c r="O78" s="4" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="P78" s="4" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="Q78" s="3" t="s">
         <v>231</v>
@@ -6115,10 +6115,10 @@
         <v>100</v>
       </c>
       <c r="O79" s="4" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="P79" s="4" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="Q79" s="3" t="s">
         <v>231</v>
@@ -6171,10 +6171,10 @@
         <v>100</v>
       </c>
       <c r="O80" s="4" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="P80" s="4" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="Q80" s="3" t="s">
         <v>231</v>
@@ -6227,10 +6227,10 @@
         <v>100</v>
       </c>
       <c r="O81" s="4" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="P81" s="4" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="Q81" s="3" t="s">
         <v>231</v>
@@ -6283,10 +6283,10 @@
         <v>100</v>
       </c>
       <c r="O82" s="4" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="P82" s="4" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="Q82" s="3" t="s">
         <v>231</v>
@@ -6339,10 +6339,10 @@
         <v>100</v>
       </c>
       <c r="O83" s="4" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="P83" s="4" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="Q83" s="3" t="s">
         <v>231</v>
@@ -6395,10 +6395,10 @@
         <v>100</v>
       </c>
       <c r="O84" s="4" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="P84" s="4" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="Q84" s="3" t="s">
         <v>231</v>
@@ -6451,10 +6451,10 @@
         <v>100</v>
       </c>
       <c r="O85" s="4" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="P85" s="4" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="Q85" s="3" t="s">
         <v>231</v>
@@ -6507,10 +6507,10 @@
         <v>100</v>
       </c>
       <c r="O86" s="4" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="P86" s="4" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="Q86" s="3" t="s">
         <v>231</v>
@@ -6563,10 +6563,10 @@
         <v>100</v>
       </c>
       <c r="O87" s="4" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="P87" s="4" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="Q87" s="3" t="s">
         <v>231</v>
@@ -6619,10 +6619,10 @@
         <v>100</v>
       </c>
       <c r="O88" s="4" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="P88" s="4" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="Q88" s="3" t="s">
         <v>231</v>
@@ -6675,10 +6675,10 @@
         <v>100</v>
       </c>
       <c r="O89" s="4" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="P89" s="4" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="Q89" s="3" t="s">
         <v>231</v>
@@ -6731,10 +6731,10 @@
         <v>100</v>
       </c>
       <c r="O90" s="4" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="P90" s="4" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="Q90" s="3" t="s">
         <v>231</v>
@@ -6787,10 +6787,10 @@
         <v>100</v>
       </c>
       <c r="O91" s="4" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="P91" s="4" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="Q91" s="3" t="s">
         <v>231</v>
@@ -6843,10 +6843,10 @@
         <v>100</v>
       </c>
       <c r="O92" s="4" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="P92" s="4" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="Q92" s="3" t="s">
         <v>231</v>
@@ -6899,10 +6899,10 @@
         <v>100</v>
       </c>
       <c r="O93" s="4" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="P93" s="4" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="Q93" s="3" t="s">
         <v>231</v>
@@ -6955,10 +6955,10 @@
         <v>100</v>
       </c>
       <c r="O94" s="4" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="P94" s="4" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="Q94" s="3" t="s">
         <v>231</v>
@@ -7011,10 +7011,10 @@
         <v>100</v>
       </c>
       <c r="O95" s="4" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="P95" s="4" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="Q95" s="3" t="s">
         <v>231</v>
@@ -7067,10 +7067,10 @@
         <v>100</v>
       </c>
       <c r="O96" s="4" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="P96" s="4" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="Q96" s="3" t="s">
         <v>231</v>
@@ -7123,10 +7123,10 @@
         <v>100</v>
       </c>
       <c r="O97" s="4" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="P97" s="4" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="Q97" s="3" t="s">
         <v>231</v>
@@ -7179,10 +7179,10 @@
         <v>100</v>
       </c>
       <c r="O98" s="4" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="P98" s="4" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="Q98" s="3" t="s">
         <v>231</v>
@@ -7235,10 +7235,10 @@
         <v>100</v>
       </c>
       <c r="O99" s="4" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="P99" s="4" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="Q99" s="3" t="s">
         <v>231</v>
@@ -7291,10 +7291,10 @@
         <v>100</v>
       </c>
       <c r="O100" s="4" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="P100" s="4" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="Q100" s="3" t="s">
         <v>231</v>
@@ -7347,10 +7347,10 @@
         <v>100</v>
       </c>
       <c r="O101" s="4" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="P101" s="4" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="Q101" s="3" t="s">
         <v>231</v>
@@ -7403,10 +7403,10 @@
         <v>100</v>
       </c>
       <c r="O102" s="4" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="P102" s="4" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="Q102" s="3" t="s">
         <v>231</v>
@@ -7459,10 +7459,10 @@
         <v>100</v>
       </c>
       <c r="O103" s="4" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="P103" s="4" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="Q103" s="3" t="s">
         <v>231</v>
@@ -7515,10 +7515,10 @@
         <v>100</v>
       </c>
       <c r="O104" s="4" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="P104" s="4" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="Q104" s="3" t="s">
         <v>231</v>
@@ -7571,10 +7571,10 @@
         <v>100</v>
       </c>
       <c r="O105" s="4" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="P105" s="4" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="Q105" s="3" t="s">
         <v>231</v>
@@ -7627,10 +7627,10 @@
         <v>100</v>
       </c>
       <c r="O106" s="4" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="P106" s="4" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="Q106" s="3" t="s">
         <v>231</v>
@@ -7683,10 +7683,10 @@
         <v>100</v>
       </c>
       <c r="O107" s="4" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="P107" s="4" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="Q107" s="3" t="s">
         <v>231</v>
@@ -7739,10 +7739,10 @@
         <v>100</v>
       </c>
       <c r="O108" s="4" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="P108" s="4" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="Q108" s="3" t="s">
         <v>231</v>
@@ -7795,10 +7795,10 @@
         <v>100</v>
       </c>
       <c r="O109" s="4" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="P109" s="4" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="Q109" s="3" t="s">
         <v>231</v>
@@ -7851,10 +7851,10 @@
         <v>100</v>
       </c>
       <c r="O110" s="4" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="P110" s="4" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="Q110" s="3" t="s">
         <v>231</v>
@@ -7907,10 +7907,10 @@
         <v>100</v>
       </c>
       <c r="O111" s="4" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="P111" s="4" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="Q111" s="3" t="s">
         <v>231</v>
@@ -7963,10 +7963,10 @@
         <v>100</v>
       </c>
       <c r="O112" s="4" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="P112" s="4" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="Q112" s="3" t="s">
         <v>231</v>
@@ -8019,10 +8019,10 @@
         <v>100</v>
       </c>
       <c r="O113" s="4" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="P113" s="4" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="Q113" s="3" t="s">
         <v>231</v>
@@ -8075,10 +8075,10 @@
         <v>100</v>
       </c>
       <c r="O114" s="4" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="P114" s="4" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="Q114" s="3" t="s">
         <v>231</v>
@@ -8131,10 +8131,10 @@
         <v>100</v>
       </c>
       <c r="O115" s="4" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="P115" s="4" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="Q115" s="3" t="s">
         <v>231</v>
@@ -8187,10 +8187,10 @@
         <v>100</v>
       </c>
       <c r="O116" s="4" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="P116" s="4" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="Q116" s="3" t="s">
         <v>231</v>
@@ -8243,10 +8243,10 @@
         <v>100</v>
       </c>
       <c r="O117" s="4" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="P117" s="4" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="Q117" s="3" t="s">
         <v>231</v>
@@ -8299,10 +8299,10 @@
         <v>100</v>
       </c>
       <c r="O118" s="4" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="P118" s="4" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="Q118" s="3" t="s">
         <v>231</v>
@@ -8355,10 +8355,10 @@
         <v>100</v>
       </c>
       <c r="O119" s="4" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="P119" s="4" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="Q119" s="3" t="s">
         <v>231</v>
@@ -8411,10 +8411,10 @@
         <v>100</v>
       </c>
       <c r="O120" s="4" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="P120" s="4" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="Q120" s="3" t="s">
         <v>231</v>
@@ -8467,10 +8467,10 @@
         <v>100</v>
       </c>
       <c r="O121" s="4" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="P121" s="4" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="Q121" s="3" t="s">
         <v>231</v>
@@ -8523,10 +8523,10 @@
         <v>100</v>
       </c>
       <c r="O122" s="4" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="P122" s="4" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="Q122" s="3" t="s">
         <v>231</v>
@@ -8579,10 +8579,10 @@
         <v>100</v>
       </c>
       <c r="O123" s="4" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="P123" s="4" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="Q123" s="3" t="s">
         <v>231</v>
@@ -8635,10 +8635,10 @@
         <v>100</v>
       </c>
       <c r="O124" s="4" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="P124" s="4" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="Q124" s="3" t="s">
         <v>231</v>
@@ -8691,10 +8691,10 @@
         <v>100</v>
       </c>
       <c r="O125" s="4" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="P125" s="4" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="Q125" s="3" t="s">
         <v>231</v>
@@ -8747,10 +8747,10 @@
         <v>100</v>
       </c>
       <c r="O126" s="4" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="P126" s="4" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="Q126" s="3" t="s">
         <v>231</v>
@@ -8803,10 +8803,10 @@
         <v>100</v>
       </c>
       <c r="O127" s="4" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="P127" s="4" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="Q127" s="3" t="s">
         <v>231</v>
@@ -8859,10 +8859,10 @@
         <v>100</v>
       </c>
       <c r="O128" s="4" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="P128" s="4" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="Q128" s="3" t="s">
         <v>231</v>
@@ -8915,10 +8915,10 @@
         <v>100</v>
       </c>
       <c r="O129" s="4" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="P129" s="4" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="Q129" s="3" t="s">
         <v>231</v>
@@ -8971,10 +8971,10 @@
         <v>100</v>
       </c>
       <c r="O130" s="4" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="P130" s="4" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="Q130" s="3" t="s">
         <v>231</v>
@@ -9027,10 +9027,10 @@
         <v>100</v>
       </c>
       <c r="O131" s="4" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="P131" s="4" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="Q131" s="3" t="s">
         <v>231</v>
@@ -9083,10 +9083,10 @@
         <v>100</v>
       </c>
       <c r="O132" s="4" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="P132" s="4" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="Q132" s="3" t="s">
         <v>231</v>
@@ -9139,10 +9139,10 @@
         <v>100</v>
       </c>
       <c r="O133" s="4" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="P133" s="4" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="Q133" s="3" t="s">
         <v>231</v>
@@ -9195,10 +9195,10 @@
         <v>100</v>
       </c>
       <c r="O134" s="4" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="P134" s="4" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="Q134" s="3" t="s">
         <v>231</v>
@@ -9251,10 +9251,10 @@
         <v>100</v>
       </c>
       <c r="O135" s="4" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="P135" s="4" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="Q135" s="3" t="s">
         <v>231</v>
@@ -9307,10 +9307,10 @@
         <v>100</v>
       </c>
       <c r="O136" s="4" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="P136" s="4" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="Q136" s="3" t="s">
         <v>231</v>
@@ -9363,10 +9363,10 @@
         <v>100</v>
       </c>
       <c r="O137" s="4" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="P137" s="4" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="Q137" s="3" t="s">
         <v>231</v>
@@ -9419,10 +9419,10 @@
         <v>100</v>
       </c>
       <c r="O138" s="4" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="P138" s="4" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="Q138" s="3" t="s">
         <v>231</v>
@@ -9475,10 +9475,10 @@
         <v>100</v>
       </c>
       <c r="O139" s="4" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="P139" s="4" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="Q139" s="3" t="s">
         <v>231</v>
@@ -9531,10 +9531,10 @@
         <v>100</v>
       </c>
       <c r="O140" s="4" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="P140" s="4" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="Q140" s="3" t="s">
         <v>231</v>
@@ -9587,10 +9587,10 @@
         <v>100</v>
       </c>
       <c r="O141" s="4" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="P141" s="4" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="Q141" s="3" t="s">
         <v>231</v>
@@ -9643,10 +9643,10 @@
         <v>100</v>
       </c>
       <c r="O142" s="4" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="P142" s="4" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="Q142" s="3" t="s">
         <v>231</v>
@@ -9699,10 +9699,10 @@
         <v>100</v>
       </c>
       <c r="O143" s="4" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="P143" s="4" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="Q143" s="3" t="s">
         <v>231</v>
@@ -9755,10 +9755,10 @@
         <v>100</v>
       </c>
       <c r="O144" s="4" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="P144" s="4" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="Q144" s="3" t="s">
         <v>231</v>
@@ -9811,10 +9811,10 @@
         <v>100</v>
       </c>
       <c r="O145" s="4" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="P145" s="4" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="Q145" s="3" t="s">
         <v>231</v>
@@ -9867,10 +9867,10 @@
         <v>100</v>
       </c>
       <c r="O146" s="4" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="P146" s="4" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="Q146" s="3" t="s">
         <v>231</v>
@@ -9923,10 +9923,10 @@
         <v>100</v>
       </c>
       <c r="O147" s="4" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="P147" s="4" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="Q147" s="3" t="s">
         <v>231</v>
@@ -9979,10 +9979,10 @@
         <v>100</v>
       </c>
       <c r="O148" s="4" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="P148" s="4" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="Q148" s="3" t="s">
         <v>231</v>
@@ -10035,10 +10035,10 @@
         <v>100</v>
       </c>
       <c r="O149" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="P149" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="Q149" s="3" t="s">
         <v>231</v>
@@ -10091,10 +10091,10 @@
         <v>100</v>
       </c>
       <c r="O150" s="4" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="P150" s="4" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="Q150" s="3" t="s">
         <v>231</v>
@@ -10147,10 +10147,10 @@
         <v>100</v>
       </c>
       <c r="O151" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="P151" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="Q151" s="3" t="s">
         <v>231</v>
@@ -10203,10 +10203,10 @@
         <v>100</v>
       </c>
       <c r="O152" s="4" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="P152" s="4" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="Q152" s="3" t="s">
         <v>231</v>
@@ -10259,10 +10259,10 @@
         <v>100</v>
       </c>
       <c r="O153" s="4" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="P153" s="4" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="Q153" s="3" t="s">
         <v>231</v>
@@ -10315,10 +10315,10 @@
         <v>100</v>
       </c>
       <c r="O154" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="P154" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="Q154" s="3" t="s">
         <v>231</v>
@@ -10371,10 +10371,10 @@
         <v>100</v>
       </c>
       <c r="O155" s="4" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="P155" s="4" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="Q155" s="3" t="s">
         <v>231</v>
@@ -10427,10 +10427,10 @@
         <v>100</v>
       </c>
       <c r="O156" s="4" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="P156" s="4" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="Q156" s="3" t="s">
         <v>231</v>
@@ -10483,10 +10483,10 @@
         <v>100</v>
       </c>
       <c r="O157" s="4" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="P157" s="4" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="Q157" s="3" t="s">
         <v>231</v>
@@ -10539,10 +10539,10 @@
         <v>100</v>
       </c>
       <c r="O158" s="4" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="P158" s="4" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="Q158" s="3" t="s">
         <v>231</v>
@@ -10595,10 +10595,10 @@
         <v>100</v>
       </c>
       <c r="O159" s="4" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="P159" s="4" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="Q159" s="3" t="s">
         <v>231</v>
@@ -10651,10 +10651,10 @@
         <v>100</v>
       </c>
       <c r="O160" s="4" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="P160" s="4" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="Q160" s="3" t="s">
         <v>231</v>
@@ -10707,10 +10707,10 @@
         <v>100</v>
       </c>
       <c r="O161" s="4" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="P161" s="4" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="Q161" s="3" t="s">
         <v>231</v>
@@ -10763,10 +10763,10 @@
         <v>100</v>
       </c>
       <c r="O162" s="4" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="P162" s="4" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="Q162" s="3" t="s">
         <v>231</v>
@@ -10819,10 +10819,10 @@
         <v>100</v>
       </c>
       <c r="O163" s="4" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="P163" s="4" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="Q163" s="3" t="s">
         <v>231</v>
@@ -10875,10 +10875,10 @@
         <v>100</v>
       </c>
       <c r="O164" s="4" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="P164" s="4" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="Q164" s="3" t="s">
         <v>231</v>

--- a/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{977FEFDA-0F99-420F-8269-FC341F7B6387}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{282BB161-68A8-4356-8C1F-F4245FC3B681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1211" uniqueCount="416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2393" uniqueCount="416">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1349,7 +1349,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>110001:550_110002:850_1100031150</t>
+    <t>110001:550_110002:850_110003:1150</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>

--- a/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{282BB161-68A8-4356-8C1F-F4245FC3B681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3C83C10-8470-43A5-A4F7-4086E5DDFBCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2393" uniqueCount="416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1211" uniqueCount="416">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -848,10 +848,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>110001:0_110002:0_110003:0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>MAP&lt;INT:INT&gt;_S_C</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1345,11 +1341,15 @@
     <t>1600001:101</t>
   </si>
   <si>
-    <t>110001:300_110002:550_110003:700</t>
+    <t>110001:0_110002:0_110003:0_110004:0</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>110001:550_110002:850_110003:1150</t>
+    <t>110001:300_110002:550_110003:700_110004:750</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>110001:550_110002:850_110003:1150_110004:1250</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1758,10 +1758,10 @@
         <v>220</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="Q2" s="1" t="s">
         <v>227</v>
@@ -1953,10 +1953,10 @@
         <v>150</v>
       </c>
       <c r="O5" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="P5" s="1" t="s">
         <v>252</v>
-      </c>
-      <c r="P5" s="1" t="s">
-        <v>253</v>
       </c>
       <c r="Q5" s="3" t="s">
         <v>231</v>
@@ -2018,10 +2018,10 @@
         <v>200</v>
       </c>
       <c r="O6" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="P6" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="Q6" s="3" t="s">
         <v>231</v>
@@ -2074,10 +2074,10 @@
         <v>300</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="P7" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="Q7" s="3" t="s">
         <v>231</v>
@@ -2130,10 +2130,10 @@
         <v>400</v>
       </c>
       <c r="O8" s="4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="P8" s="4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="Q8" s="3" t="s">
         <v>231</v>
@@ -2186,10 +2186,10 @@
         <v>500</v>
       </c>
       <c r="O9" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="P9" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="Q9" s="3" t="s">
         <v>231</v>
@@ -2242,10 +2242,10 @@
         <v>600</v>
       </c>
       <c r="O10" s="4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="P10" s="4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="Q10" s="3" t="s">
         <v>231</v>
@@ -2298,10 +2298,10 @@
         <v>100</v>
       </c>
       <c r="O11" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="P11" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="Q11" s="3" t="s">
         <v>231</v>
@@ -2354,10 +2354,10 @@
         <v>100</v>
       </c>
       <c r="O12" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="P12" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q12" s="3" t="s">
         <v>231</v>
@@ -2410,10 +2410,10 @@
         <v>100</v>
       </c>
       <c r="O13" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P13" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q13" s="3" t="s">
         <v>231</v>
@@ -2466,10 +2466,10 @@
         <v>100</v>
       </c>
       <c r="O14" s="4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="P14" s="4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>231</v>
@@ -2522,10 +2522,10 @@
         <v>100</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="Q15" s="3" t="s">
         <v>231</v>
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="S15" s="1" t="s">
-        <v>250</v>
+        <v>413</v>
       </c>
       <c r="T15" s="1" t="s">
         <v>414</v>
@@ -2587,10 +2587,10 @@
         <v>100</v>
       </c>
       <c r="O16" s="4" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="P16" s="4" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="Q16" s="3" t="s">
         <v>231</v>
@@ -2643,10 +2643,10 @@
         <v>100</v>
       </c>
       <c r="O17" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P17" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="Q17" s="3" t="s">
         <v>231</v>
@@ -2699,10 +2699,10 @@
         <v>100</v>
       </c>
       <c r="O18" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P18" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="Q18" s="3" t="s">
         <v>231</v>
@@ -2755,10 +2755,10 @@
         <v>100</v>
       </c>
       <c r="O19" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="P19" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q19" s="3" t="s">
         <v>231</v>
@@ -2811,10 +2811,10 @@
         <v>100</v>
       </c>
       <c r="O20" s="4" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="P20" s="4" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q20" s="3" t="s">
         <v>231</v>
@@ -2867,10 +2867,10 @@
         <v>100</v>
       </c>
       <c r="O21" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="P21" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="Q21" s="3" t="s">
         <v>231</v>
@@ -2923,10 +2923,10 @@
         <v>100</v>
       </c>
       <c r="O22" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="P22" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="Q22" s="3" t="s">
         <v>231</v>
@@ -2979,10 +2979,10 @@
         <v>100</v>
       </c>
       <c r="O23" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="P23" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="Q23" s="3" t="s">
         <v>231</v>
@@ -3035,10 +3035,10 @@
         <v>100</v>
       </c>
       <c r="O24" s="4" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P24" s="4" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="Q24" s="3" t="s">
         <v>231</v>
@@ -3091,10 +3091,10 @@
         <v>100</v>
       </c>
       <c r="O25" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="P25" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="Q25" s="3" t="s">
         <v>231</v>
@@ -3147,10 +3147,10 @@
         <v>100</v>
       </c>
       <c r="O26" s="4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="P26" s="4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="Q26" s="3" t="s">
         <v>231</v>
@@ -3203,10 +3203,10 @@
         <v>100</v>
       </c>
       <c r="O27" s="4" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="P27" s="4" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="Q27" s="3" t="s">
         <v>231</v>
@@ -3259,10 +3259,10 @@
         <v>100</v>
       </c>
       <c r="O28" s="4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="P28" s="4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="Q28" s="3" t="s">
         <v>231</v>
@@ -3315,10 +3315,10 @@
         <v>100</v>
       </c>
       <c r="O29" s="4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="P29" s="4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="Q29" s="3" t="s">
         <v>231</v>
@@ -3371,10 +3371,10 @@
         <v>100</v>
       </c>
       <c r="O30" s="4" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P30" s="4" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="Q30" s="3" t="s">
         <v>231</v>
@@ -3427,10 +3427,10 @@
         <v>100</v>
       </c>
       <c r="O31" s="4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="P31" s="4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="Q31" s="3" t="s">
         <v>231</v>
@@ -3483,10 +3483,10 @@
         <v>100</v>
       </c>
       <c r="O32" s="4" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="P32" s="4" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="Q32" s="3" t="s">
         <v>231</v>
@@ -3539,10 +3539,10 @@
         <v>100</v>
       </c>
       <c r="O33" s="4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="P33" s="4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="Q33" s="3" t="s">
         <v>231</v>
@@ -3595,10 +3595,10 @@
         <v>100</v>
       </c>
       <c r="O34" s="4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="P34" s="4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="Q34" s="3" t="s">
         <v>231</v>
@@ -3651,10 +3651,10 @@
         <v>100</v>
       </c>
       <c r="O35" s="4" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="P35" s="4" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="Q35" s="3" t="s">
         <v>231</v>
@@ -3707,10 +3707,10 @@
         <v>100</v>
       </c>
       <c r="O36" s="4" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="P36" s="4" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="Q36" s="3" t="s">
         <v>231</v>
@@ -3763,10 +3763,10 @@
         <v>100</v>
       </c>
       <c r="O37" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="P37" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="Q37" s="3" t="s">
         <v>231</v>
@@ -3819,10 +3819,10 @@
         <v>100</v>
       </c>
       <c r="O38" s="4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="P38" s="4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="Q38" s="3" t="s">
         <v>231</v>
@@ -3875,10 +3875,10 @@
         <v>100</v>
       </c>
       <c r="O39" s="4" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="P39" s="4" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="Q39" s="3" t="s">
         <v>231</v>
@@ -3931,10 +3931,10 @@
         <v>100</v>
       </c>
       <c r="O40" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="P40" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="Q40" s="3" t="s">
         <v>231</v>
@@ -3987,10 +3987,10 @@
         <v>100</v>
       </c>
       <c r="O41" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="P41" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="Q41" s="3" t="s">
         <v>231</v>
@@ -4043,10 +4043,10 @@
         <v>100</v>
       </c>
       <c r="O42" s="4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="P42" s="4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="Q42" s="3" t="s">
         <v>231</v>
@@ -4099,10 +4099,10 @@
         <v>100</v>
       </c>
       <c r="O43" s="4" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="P43" s="4" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="Q43" s="3" t="s">
         <v>231</v>
@@ -4155,10 +4155,10 @@
         <v>100</v>
       </c>
       <c r="O44" s="4" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="P44" s="4" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="Q44" s="3" t="s">
         <v>231</v>
@@ -4211,10 +4211,10 @@
         <v>100</v>
       </c>
       <c r="O45" s="4" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="P45" s="4" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="Q45" s="3" t="s">
         <v>231</v>
@@ -4267,10 +4267,10 @@
         <v>100</v>
       </c>
       <c r="O46" s="4" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="P46" s="4" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="Q46" s="3" t="s">
         <v>231</v>
@@ -4323,10 +4323,10 @@
         <v>100</v>
       </c>
       <c r="O47" s="4" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="P47" s="4" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="Q47" s="3" t="s">
         <v>231</v>
@@ -4379,10 +4379,10 @@
         <v>100</v>
       </c>
       <c r="O48" s="4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="P48" s="4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="Q48" s="3" t="s">
         <v>231</v>
@@ -4435,10 +4435,10 @@
         <v>100</v>
       </c>
       <c r="O49" s="4" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="P49" s="4" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="Q49" s="3" t="s">
         <v>231</v>
@@ -4491,10 +4491,10 @@
         <v>100</v>
       </c>
       <c r="O50" s="4" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="P50" s="4" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="Q50" s="3" t="s">
         <v>231</v>
@@ -4547,10 +4547,10 @@
         <v>100</v>
       </c>
       <c r="O51" s="4" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="P51" s="4" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="Q51" s="3" t="s">
         <v>231</v>
@@ -4603,10 +4603,10 @@
         <v>100</v>
       </c>
       <c r="O52" s="4" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="P52" s="4" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="Q52" s="3" t="s">
         <v>231</v>
@@ -4659,10 +4659,10 @@
         <v>100</v>
       </c>
       <c r="O53" s="4" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="P53" s="4" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="Q53" s="3" t="s">
         <v>231</v>
@@ -4715,10 +4715,10 @@
         <v>100</v>
       </c>
       <c r="O54" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P54" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="Q54" s="3" t="s">
         <v>231</v>
@@ -4771,10 +4771,10 @@
         <v>100</v>
       </c>
       <c r="O55" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="P55" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="Q55" s="3" t="s">
         <v>231</v>
@@ -4827,10 +4827,10 @@
         <v>100</v>
       </c>
       <c r="O56" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="P56" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="Q56" s="3" t="s">
         <v>231</v>
@@ -4883,10 +4883,10 @@
         <v>100</v>
       </c>
       <c r="O57" s="4" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="P57" s="4" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="Q57" s="3" t="s">
         <v>231</v>
@@ -4939,10 +4939,10 @@
         <v>100</v>
       </c>
       <c r="O58" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="P58" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="Q58" s="3" t="s">
         <v>231</v>
@@ -4995,10 +4995,10 @@
         <v>100</v>
       </c>
       <c r="O59" s="4" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P59" s="4" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="Q59" s="3" t="s">
         <v>231</v>
@@ -5051,10 +5051,10 @@
         <v>100</v>
       </c>
       <c r="O60" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="P60" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="Q60" s="3" t="s">
         <v>231</v>
@@ -5107,10 +5107,10 @@
         <v>100</v>
       </c>
       <c r="O61" s="4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="P61" s="4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="Q61" s="3" t="s">
         <v>231</v>
@@ -5163,10 +5163,10 @@
         <v>100</v>
       </c>
       <c r="O62" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="P62" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="Q62" s="3" t="s">
         <v>231</v>
@@ -5219,10 +5219,10 @@
         <v>100</v>
       </c>
       <c r="O63" s="4" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="P63" s="4" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="Q63" s="3" t="s">
         <v>231</v>
@@ -5275,10 +5275,10 @@
         <v>100</v>
       </c>
       <c r="O64" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="P64" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="Q64" s="3" t="s">
         <v>231</v>
@@ -5331,10 +5331,10 @@
         <v>100</v>
       </c>
       <c r="O65" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="P65" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="Q65" s="3" t="s">
         <v>231</v>
@@ -5387,10 +5387,10 @@
         <v>100</v>
       </c>
       <c r="O66" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="P66" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="Q66" s="3" t="s">
         <v>231</v>
@@ -5443,10 +5443,10 @@
         <v>100</v>
       </c>
       <c r="O67" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="P67" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="Q67" s="3" t="s">
         <v>231</v>
@@ -5499,10 +5499,10 @@
         <v>100</v>
       </c>
       <c r="O68" s="4" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P68" s="4" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="Q68" s="3" t="s">
         <v>231</v>
@@ -5555,10 +5555,10 @@
         <v>100</v>
       </c>
       <c r="O69" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="P69" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="Q69" s="3" t="s">
         <v>231</v>
@@ -5611,10 +5611,10 @@
         <v>100</v>
       </c>
       <c r="O70" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="P70" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="Q70" s="3" t="s">
         <v>231</v>
@@ -5667,10 +5667,10 @@
         <v>100</v>
       </c>
       <c r="O71" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="P71" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="Q71" s="3" t="s">
         <v>231</v>
@@ -5723,10 +5723,10 @@
         <v>100</v>
       </c>
       <c r="O72" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="P72" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="Q72" s="3" t="s">
         <v>231</v>
@@ -5779,10 +5779,10 @@
         <v>100</v>
       </c>
       <c r="O73" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="P73" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="Q73" s="3" t="s">
         <v>231</v>
@@ -5835,10 +5835,10 @@
         <v>100</v>
       </c>
       <c r="O74" s="4" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="P74" s="4" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="Q74" s="3" t="s">
         <v>231</v>
@@ -5891,10 +5891,10 @@
         <v>100</v>
       </c>
       <c r="O75" s="4" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="P75" s="4" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="Q75" s="3" t="s">
         <v>231</v>
@@ -5947,10 +5947,10 @@
         <v>100</v>
       </c>
       <c r="O76" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="P76" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="Q76" s="3" t="s">
         <v>231</v>
@@ -6003,10 +6003,10 @@
         <v>100</v>
       </c>
       <c r="O77" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="P77" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="Q77" s="3" t="s">
         <v>231</v>
@@ -6059,10 +6059,10 @@
         <v>100</v>
       </c>
       <c r="O78" s="4" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="P78" s="4" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Q78" s="3" t="s">
         <v>231</v>
@@ -6115,10 +6115,10 @@
         <v>100</v>
       </c>
       <c r="O79" s="4" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="P79" s="4" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="Q79" s="3" t="s">
         <v>231</v>
@@ -6171,10 +6171,10 @@
         <v>100</v>
       </c>
       <c r="O80" s="4" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="P80" s="4" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="Q80" s="3" t="s">
         <v>231</v>
@@ -6227,10 +6227,10 @@
         <v>100</v>
       </c>
       <c r="O81" s="4" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="P81" s="4" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="Q81" s="3" t="s">
         <v>231</v>
@@ -6283,10 +6283,10 @@
         <v>100</v>
       </c>
       <c r="O82" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="P82" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="Q82" s="3" t="s">
         <v>231</v>
@@ -6339,10 +6339,10 @@
         <v>100</v>
       </c>
       <c r="O83" s="4" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="P83" s="4" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="Q83" s="3" t="s">
         <v>231</v>
@@ -6395,10 +6395,10 @@
         <v>100</v>
       </c>
       <c r="O84" s="4" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="P84" s="4" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="Q84" s="3" t="s">
         <v>231</v>
@@ -6451,10 +6451,10 @@
         <v>100</v>
       </c>
       <c r="O85" s="4" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="P85" s="4" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="Q85" s="3" t="s">
         <v>231</v>
@@ -6507,10 +6507,10 @@
         <v>100</v>
       </c>
       <c r="O86" s="4" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="P86" s="4" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="Q86" s="3" t="s">
         <v>231</v>
@@ -6563,10 +6563,10 @@
         <v>100</v>
       </c>
       <c r="O87" s="4" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="P87" s="4" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="Q87" s="3" t="s">
         <v>231</v>
@@ -6619,10 +6619,10 @@
         <v>100</v>
       </c>
       <c r="O88" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="P88" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="Q88" s="3" t="s">
         <v>231</v>
@@ -6675,10 +6675,10 @@
         <v>100</v>
       </c>
       <c r="O89" s="4" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="P89" s="4" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="Q89" s="3" t="s">
         <v>231</v>
@@ -6731,10 +6731,10 @@
         <v>100</v>
       </c>
       <c r="O90" s="4" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="P90" s="4" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="Q90" s="3" t="s">
         <v>231</v>
@@ -6787,10 +6787,10 @@
         <v>100</v>
       </c>
       <c r="O91" s="4" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="P91" s="4" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="Q91" s="3" t="s">
         <v>231</v>
@@ -6843,10 +6843,10 @@
         <v>100</v>
       </c>
       <c r="O92" s="4" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="P92" s="4" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="Q92" s="3" t="s">
         <v>231</v>
@@ -6899,10 +6899,10 @@
         <v>100</v>
       </c>
       <c r="O93" s="4" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="P93" s="4" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="Q93" s="3" t="s">
         <v>231</v>
@@ -6955,10 +6955,10 @@
         <v>100</v>
       </c>
       <c r="O94" s="4" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="P94" s="4" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="Q94" s="3" t="s">
         <v>231</v>
@@ -7011,10 +7011,10 @@
         <v>100</v>
       </c>
       <c r="O95" s="4" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P95" s="4" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="Q95" s="3" t="s">
         <v>231</v>
@@ -7067,10 +7067,10 @@
         <v>100</v>
       </c>
       <c r="O96" s="4" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="P96" s="4" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="Q96" s="3" t="s">
         <v>231</v>
@@ -7123,10 +7123,10 @@
         <v>100</v>
       </c>
       <c r="O97" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="P97" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="Q97" s="3" t="s">
         <v>231</v>
@@ -7179,10 +7179,10 @@
         <v>100</v>
       </c>
       <c r="O98" s="4" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="P98" s="4" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="Q98" s="3" t="s">
         <v>231</v>
@@ -7235,10 +7235,10 @@
         <v>100</v>
       </c>
       <c r="O99" s="4" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="P99" s="4" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="Q99" s="3" t="s">
         <v>231</v>
@@ -7291,10 +7291,10 @@
         <v>100</v>
       </c>
       <c r="O100" s="4" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="P100" s="4" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="Q100" s="3" t="s">
         <v>231</v>
@@ -7347,10 +7347,10 @@
         <v>100</v>
       </c>
       <c r="O101" s="4" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="P101" s="4" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="Q101" s="3" t="s">
         <v>231</v>
@@ -7403,10 +7403,10 @@
         <v>100</v>
       </c>
       <c r="O102" s="4" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="P102" s="4" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="Q102" s="3" t="s">
         <v>231</v>
@@ -7459,10 +7459,10 @@
         <v>100</v>
       </c>
       <c r="O103" s="4" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="P103" s="4" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="Q103" s="3" t="s">
         <v>231</v>
@@ -7515,10 +7515,10 @@
         <v>100</v>
       </c>
       <c r="O104" s="4" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="P104" s="4" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="Q104" s="3" t="s">
         <v>231</v>
@@ -7571,10 +7571,10 @@
         <v>100</v>
       </c>
       <c r="O105" s="4" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="P105" s="4" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="Q105" s="3" t="s">
         <v>231</v>
@@ -7627,10 +7627,10 @@
         <v>100</v>
       </c>
       <c r="O106" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="P106" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="Q106" s="3" t="s">
         <v>231</v>
@@ -7683,10 +7683,10 @@
         <v>100</v>
       </c>
       <c r="O107" s="4" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="P107" s="4" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="Q107" s="3" t="s">
         <v>231</v>
@@ -7739,10 +7739,10 @@
         <v>100</v>
       </c>
       <c r="O108" s="4" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="P108" s="4" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="Q108" s="3" t="s">
         <v>231</v>
@@ -7795,10 +7795,10 @@
         <v>100</v>
       </c>
       <c r="O109" s="4" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="P109" s="4" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="Q109" s="3" t="s">
         <v>231</v>
@@ -7851,10 +7851,10 @@
         <v>100</v>
       </c>
       <c r="O110" s="4" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="P110" s="4" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="Q110" s="3" t="s">
         <v>231</v>
@@ -7907,10 +7907,10 @@
         <v>100</v>
       </c>
       <c r="O111" s="4" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="P111" s="4" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="Q111" s="3" t="s">
         <v>231</v>
@@ -7963,10 +7963,10 @@
         <v>100</v>
       </c>
       <c r="O112" s="4" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="P112" s="4" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="Q112" s="3" t="s">
         <v>231</v>
@@ -8019,10 +8019,10 @@
         <v>100</v>
       </c>
       <c r="O113" s="4" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="P113" s="4" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="Q113" s="3" t="s">
         <v>231</v>
@@ -8075,10 +8075,10 @@
         <v>100</v>
       </c>
       <c r="O114" s="4" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="P114" s="4" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="Q114" s="3" t="s">
         <v>231</v>
@@ -8131,10 +8131,10 @@
         <v>100</v>
       </c>
       <c r="O115" s="4" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="P115" s="4" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="Q115" s="3" t="s">
         <v>231</v>
@@ -8187,10 +8187,10 @@
         <v>100</v>
       </c>
       <c r="O116" s="4" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="P116" s="4" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="Q116" s="3" t="s">
         <v>231</v>
@@ -8243,10 +8243,10 @@
         <v>100</v>
       </c>
       <c r="O117" s="4" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="P117" s="4" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="Q117" s="3" t="s">
         <v>231</v>
@@ -8299,10 +8299,10 @@
         <v>100</v>
       </c>
       <c r="O118" s="4" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="P118" s="4" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="Q118" s="3" t="s">
         <v>231</v>
@@ -8355,10 +8355,10 @@
         <v>100</v>
       </c>
       <c r="O119" s="4" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="P119" s="4" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="Q119" s="3" t="s">
         <v>231</v>
@@ -8411,10 +8411,10 @@
         <v>100</v>
       </c>
       <c r="O120" s="4" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="P120" s="4" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="Q120" s="3" t="s">
         <v>231</v>
@@ -8467,10 +8467,10 @@
         <v>100</v>
       </c>
       <c r="O121" s="4" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="P121" s="4" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="Q121" s="3" t="s">
         <v>231</v>
@@ -8523,10 +8523,10 @@
         <v>100</v>
       </c>
       <c r="O122" s="4" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="P122" s="4" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="Q122" s="3" t="s">
         <v>231</v>
@@ -8579,10 +8579,10 @@
         <v>100</v>
       </c>
       <c r="O123" s="4" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="P123" s="4" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="Q123" s="3" t="s">
         <v>231</v>
@@ -8635,10 +8635,10 @@
         <v>100</v>
       </c>
       <c r="O124" s="4" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="P124" s="4" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="Q124" s="3" t="s">
         <v>231</v>
@@ -8691,10 +8691,10 @@
         <v>100</v>
       </c>
       <c r="O125" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="P125" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="Q125" s="3" t="s">
         <v>231</v>
@@ -8747,10 +8747,10 @@
         <v>100</v>
       </c>
       <c r="O126" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="P126" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="Q126" s="3" t="s">
         <v>231</v>
@@ -8803,10 +8803,10 @@
         <v>100</v>
       </c>
       <c r="O127" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="P127" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="Q127" s="3" t="s">
         <v>231</v>
@@ -8859,10 +8859,10 @@
         <v>100</v>
       </c>
       <c r="O128" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="P128" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="Q128" s="3" t="s">
         <v>231</v>
@@ -8915,10 +8915,10 @@
         <v>100</v>
       </c>
       <c r="O129" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="P129" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="Q129" s="3" t="s">
         <v>231</v>
@@ -8971,10 +8971,10 @@
         <v>100</v>
       </c>
       <c r="O130" s="4" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="P130" s="4" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="Q130" s="3" t="s">
         <v>231</v>
@@ -9027,10 +9027,10 @@
         <v>100</v>
       </c>
       <c r="O131" s="4" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="P131" s="4" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="Q131" s="3" t="s">
         <v>231</v>
@@ -9083,10 +9083,10 @@
         <v>100</v>
       </c>
       <c r="O132" s="4" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="P132" s="4" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="Q132" s="3" t="s">
         <v>231</v>
@@ -9139,10 +9139,10 @@
         <v>100</v>
       </c>
       <c r="O133" s="4" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="P133" s="4" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="Q133" s="3" t="s">
         <v>231</v>
@@ -9195,10 +9195,10 @@
         <v>100</v>
       </c>
       <c r="O134" s="4" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="P134" s="4" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="Q134" s="3" t="s">
         <v>231</v>
@@ -9251,10 +9251,10 @@
         <v>100</v>
       </c>
       <c r="O135" s="4" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="P135" s="4" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="Q135" s="3" t="s">
         <v>231</v>
@@ -9307,10 +9307,10 @@
         <v>100</v>
       </c>
       <c r="O136" s="4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="P136" s="4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="Q136" s="3" t="s">
         <v>231</v>
@@ -9363,10 +9363,10 @@
         <v>100</v>
       </c>
       <c r="O137" s="4" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="P137" s="4" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="Q137" s="3" t="s">
         <v>231</v>
@@ -9419,10 +9419,10 @@
         <v>100</v>
       </c>
       <c r="O138" s="4" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="P138" s="4" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="Q138" s="3" t="s">
         <v>231</v>
@@ -9475,10 +9475,10 @@
         <v>100</v>
       </c>
       <c r="O139" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="P139" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="Q139" s="3" t="s">
         <v>231</v>
@@ -9531,10 +9531,10 @@
         <v>100</v>
       </c>
       <c r="O140" s="4" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="P140" s="4" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="Q140" s="3" t="s">
         <v>231</v>
@@ -9587,10 +9587,10 @@
         <v>100</v>
       </c>
       <c r="O141" s="4" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="P141" s="4" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="Q141" s="3" t="s">
         <v>231</v>
@@ -9643,10 +9643,10 @@
         <v>100</v>
       </c>
       <c r="O142" s="4" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="P142" s="4" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="Q142" s="3" t="s">
         <v>231</v>
@@ -9699,10 +9699,10 @@
         <v>100</v>
       </c>
       <c r="O143" s="4" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="P143" s="4" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="Q143" s="3" t="s">
         <v>231</v>
@@ -9755,10 +9755,10 @@
         <v>100</v>
       </c>
       <c r="O144" s="4" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="P144" s="4" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="Q144" s="3" t="s">
         <v>231</v>
@@ -9811,10 +9811,10 @@
         <v>100</v>
       </c>
       <c r="O145" s="4" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="P145" s="4" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="Q145" s="3" t="s">
         <v>231</v>
@@ -9867,10 +9867,10 @@
         <v>100</v>
       </c>
       <c r="O146" s="4" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="P146" s="4" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="Q146" s="3" t="s">
         <v>231</v>
@@ -9923,10 +9923,10 @@
         <v>100</v>
       </c>
       <c r="O147" s="4" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="P147" s="4" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="Q147" s="3" t="s">
         <v>231</v>
@@ -9979,10 +9979,10 @@
         <v>100</v>
       </c>
       <c r="O148" s="4" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P148" s="4" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q148" s="3" t="s">
         <v>231</v>
@@ -10035,10 +10035,10 @@
         <v>100</v>
       </c>
       <c r="O149" s="4" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="P149" s="4" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="Q149" s="3" t="s">
         <v>231</v>
@@ -10091,10 +10091,10 @@
         <v>100</v>
       </c>
       <c r="O150" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="P150" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="Q150" s="3" t="s">
         <v>231</v>
@@ -10147,10 +10147,10 @@
         <v>100</v>
       </c>
       <c r="O151" s="4" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="P151" s="4" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="Q151" s="3" t="s">
         <v>231</v>
@@ -10203,10 +10203,10 @@
         <v>100</v>
       </c>
       <c r="O152" s="4" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="P152" s="4" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="Q152" s="3" t="s">
         <v>231</v>
@@ -10259,10 +10259,10 @@
         <v>100</v>
       </c>
       <c r="O153" s="4" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="P153" s="4" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="Q153" s="3" t="s">
         <v>231</v>
@@ -10315,10 +10315,10 @@
         <v>100</v>
       </c>
       <c r="O154" s="4" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="P154" s="4" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="Q154" s="3" t="s">
         <v>231</v>
@@ -10371,10 +10371,10 @@
         <v>100</v>
       </c>
       <c r="O155" s="4" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="P155" s="4" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="Q155" s="3" t="s">
         <v>231</v>
@@ -10427,10 +10427,10 @@
         <v>100</v>
       </c>
       <c r="O156" s="4" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="P156" s="4" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="Q156" s="3" t="s">
         <v>231</v>
@@ -10483,10 +10483,10 @@
         <v>100</v>
       </c>
       <c r="O157" s="4" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="P157" s="4" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="Q157" s="3" t="s">
         <v>231</v>
@@ -10539,10 +10539,10 @@
         <v>100</v>
       </c>
       <c r="O158" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="P158" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="Q158" s="3" t="s">
         <v>231</v>
@@ -10595,10 +10595,10 @@
         <v>100</v>
       </c>
       <c r="O159" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="P159" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="Q159" s="3" t="s">
         <v>231</v>
@@ -10651,10 +10651,10 @@
         <v>100</v>
       </c>
       <c r="O160" s="4" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="P160" s="4" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="Q160" s="3" t="s">
         <v>231</v>
@@ -10707,10 +10707,10 @@
         <v>100</v>
       </c>
       <c r="O161" s="4" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="P161" s="4" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="Q161" s="3" t="s">
         <v>231</v>
@@ -10763,10 +10763,10 @@
         <v>100</v>
       </c>
       <c r="O162" s="4" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="P162" s="4" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="Q162" s="3" t="s">
         <v>231</v>
@@ -10819,10 +10819,10 @@
         <v>100</v>
       </c>
       <c r="O163" s="4" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="P163" s="4" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="Q163" s="3" t="s">
         <v>231</v>
@@ -10875,10 +10875,10 @@
         <v>100</v>
       </c>
       <c r="O164" s="4" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="P164" s="4" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="Q164" s="3" t="s">
         <v>231</v>

--- a/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3C83C10-8470-43A5-A4F7-4086E5DDFBCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F855F3C8-3F23-44B3-AE67-090D86EFBE78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_barries_v8" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1211" uniqueCount="416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1211" uniqueCount="574">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -863,10 +863,6 @@
     <t>110001:101_110002:101_110003:101_110004:101</t>
   </si>
   <si>
-    <t>110001:1101_110002:1102_110003:1103_110004:1104</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>20001:101</t>
   </si>
   <si>
@@ -1350,6 +1346,484 @@
   </si>
   <si>
     <t>110001:550_110002:850_110003:1150_110004:1250</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20001:100</t>
+  </si>
+  <si>
+    <t>30001:100</t>
+  </si>
+  <si>
+    <t>40001:100</t>
+  </si>
+  <si>
+    <t>50001:100</t>
+  </si>
+  <si>
+    <t>60001:100</t>
+  </si>
+  <si>
+    <t>70001:100</t>
+  </si>
+  <si>
+    <t>80001:100</t>
+  </si>
+  <si>
+    <t>90001:100</t>
+  </si>
+  <si>
+    <t>100001:100</t>
+  </si>
+  <si>
+    <t>120001:100</t>
+  </si>
+  <si>
+    <t>130001:100</t>
+  </si>
+  <si>
+    <t>140001:100</t>
+  </si>
+  <si>
+    <t>150001:100</t>
+  </si>
+  <si>
+    <t>160001:100</t>
+  </si>
+  <si>
+    <t>170001:100</t>
+  </si>
+  <si>
+    <t>180001:100</t>
+  </si>
+  <si>
+    <t>190001:100</t>
+  </si>
+  <si>
+    <t>200001:100</t>
+  </si>
+  <si>
+    <t>210001:100</t>
+  </si>
+  <si>
+    <t>220001:100</t>
+  </si>
+  <si>
+    <t>230001:100</t>
+  </si>
+  <si>
+    <t>240001:100</t>
+  </si>
+  <si>
+    <t>250001:100</t>
+  </si>
+  <si>
+    <t>260001:100</t>
+  </si>
+  <si>
+    <t>270001:100</t>
+  </si>
+  <si>
+    <t>280001:100</t>
+  </si>
+  <si>
+    <t>290001:100</t>
+  </si>
+  <si>
+    <t>300001:100</t>
+  </si>
+  <si>
+    <t>310001:100</t>
+  </si>
+  <si>
+    <t>320001:100</t>
+  </si>
+  <si>
+    <t>330001:100</t>
+  </si>
+  <si>
+    <t>340001:100</t>
+  </si>
+  <si>
+    <t>350001:100</t>
+  </si>
+  <si>
+    <t>360001:100</t>
+  </si>
+  <si>
+    <t>370001:100</t>
+  </si>
+  <si>
+    <t>380001:100</t>
+  </si>
+  <si>
+    <t>390001:100</t>
+  </si>
+  <si>
+    <t>400001:100</t>
+  </si>
+  <si>
+    <t>410001:100</t>
+  </si>
+  <si>
+    <t>420001:100</t>
+  </si>
+  <si>
+    <t>430001:100</t>
+  </si>
+  <si>
+    <t>440001:100</t>
+  </si>
+  <si>
+    <t>450001:100</t>
+  </si>
+  <si>
+    <t>460001:100</t>
+  </si>
+  <si>
+    <t>470001:100</t>
+  </si>
+  <si>
+    <t>480001:100</t>
+  </si>
+  <si>
+    <t>490001:100</t>
+  </si>
+  <si>
+    <t>500001:100</t>
+  </si>
+  <si>
+    <t>510001:100</t>
+  </si>
+  <si>
+    <t>520001:100</t>
+  </si>
+  <si>
+    <t>530001:100</t>
+  </si>
+  <si>
+    <t>540001:100</t>
+  </si>
+  <si>
+    <t>550001:100</t>
+  </si>
+  <si>
+    <t>560001:100</t>
+  </si>
+  <si>
+    <t>570001:100</t>
+  </si>
+  <si>
+    <t>580001:100</t>
+  </si>
+  <si>
+    <t>590001:100</t>
+  </si>
+  <si>
+    <t>600001:100</t>
+  </si>
+  <si>
+    <t>610001:100</t>
+  </si>
+  <si>
+    <t>620001:100</t>
+  </si>
+  <si>
+    <t>630001:100</t>
+  </si>
+  <si>
+    <t>640001:100</t>
+  </si>
+  <si>
+    <t>650001:100</t>
+  </si>
+  <si>
+    <t>660001:100</t>
+  </si>
+  <si>
+    <t>670001:100</t>
+  </si>
+  <si>
+    <t>680001:100</t>
+  </si>
+  <si>
+    <t>690001:100</t>
+  </si>
+  <si>
+    <t>700001:100</t>
+  </si>
+  <si>
+    <t>710001:100</t>
+  </si>
+  <si>
+    <t>720001:100</t>
+  </si>
+  <si>
+    <t>730001:100</t>
+  </si>
+  <si>
+    <t>740001:100</t>
+  </si>
+  <si>
+    <t>750001:100</t>
+  </si>
+  <si>
+    <t>760001:100</t>
+  </si>
+  <si>
+    <t>770001:100</t>
+  </si>
+  <si>
+    <t>780001:100</t>
+  </si>
+  <si>
+    <t>790001:100</t>
+  </si>
+  <si>
+    <t>800001:100</t>
+  </si>
+  <si>
+    <t>810001:100</t>
+  </si>
+  <si>
+    <t>820001:100</t>
+  </si>
+  <si>
+    <t>830001:100</t>
+  </si>
+  <si>
+    <t>840001:100</t>
+  </si>
+  <si>
+    <t>850001:100</t>
+  </si>
+  <si>
+    <t>860001:100</t>
+  </si>
+  <si>
+    <t>870001:100</t>
+  </si>
+  <si>
+    <t>880001:100</t>
+  </si>
+  <si>
+    <t>890001:100</t>
+  </si>
+  <si>
+    <t>900001:100</t>
+  </si>
+  <si>
+    <t>910001:100</t>
+  </si>
+  <si>
+    <t>920001:100</t>
+  </si>
+  <si>
+    <t>930001:100</t>
+  </si>
+  <si>
+    <t>940001:100</t>
+  </si>
+  <si>
+    <t>950001:100</t>
+  </si>
+  <si>
+    <t>960001:100</t>
+  </si>
+  <si>
+    <t>970001:100</t>
+  </si>
+  <si>
+    <t>980001:100</t>
+  </si>
+  <si>
+    <t>990001:100</t>
+  </si>
+  <si>
+    <t>1000001:100</t>
+  </si>
+  <si>
+    <t>1010001:100</t>
+  </si>
+  <si>
+    <t>1020001:100</t>
+  </si>
+  <si>
+    <t>1030001:100</t>
+  </si>
+  <si>
+    <t>1040001:100</t>
+  </si>
+  <si>
+    <t>1050001:100</t>
+  </si>
+  <si>
+    <t>1060001:100</t>
+  </si>
+  <si>
+    <t>1070001:100</t>
+  </si>
+  <si>
+    <t>1080001:100</t>
+  </si>
+  <si>
+    <t>1090001:100</t>
+  </si>
+  <si>
+    <t>1100001:100</t>
+  </si>
+  <si>
+    <t>1110001:100</t>
+  </si>
+  <si>
+    <t>1120001:100</t>
+  </si>
+  <si>
+    <t>1130001:100</t>
+  </si>
+  <si>
+    <t>1140001:100</t>
+  </si>
+  <si>
+    <t>1150001:100</t>
+  </si>
+  <si>
+    <t>1160001:100</t>
+  </si>
+  <si>
+    <t>1170001:100</t>
+  </si>
+  <si>
+    <t>1180001:100</t>
+  </si>
+  <si>
+    <t>1190001:100</t>
+  </si>
+  <si>
+    <t>1200001:100</t>
+  </si>
+  <si>
+    <t>1210001:100</t>
+  </si>
+  <si>
+    <t>1220001:100</t>
+  </si>
+  <si>
+    <t>1230001:100</t>
+  </si>
+  <si>
+    <t>1240001:100</t>
+  </si>
+  <si>
+    <t>1250001:100</t>
+  </si>
+  <si>
+    <t>1260001:100</t>
+  </si>
+  <si>
+    <t>1270001:100</t>
+  </si>
+  <si>
+    <t>1280001:100</t>
+  </si>
+  <si>
+    <t>1290001:100</t>
+  </si>
+  <si>
+    <t>1300001:100</t>
+  </si>
+  <si>
+    <t>1310001:100</t>
+  </si>
+  <si>
+    <t>1320001:100</t>
+  </si>
+  <si>
+    <t>1330001:100</t>
+  </si>
+  <si>
+    <t>1340001:100</t>
+  </si>
+  <si>
+    <t>1350001:100</t>
+  </si>
+  <si>
+    <t>1360001:100</t>
+  </si>
+  <si>
+    <t>1370001:100</t>
+  </si>
+  <si>
+    <t>1380001:100</t>
+  </si>
+  <si>
+    <t>1390001:100</t>
+  </si>
+  <si>
+    <t>1400001:100</t>
+  </si>
+  <si>
+    <t>1410001:100</t>
+  </si>
+  <si>
+    <t>1420001:100</t>
+  </si>
+  <si>
+    <t>1430001:100</t>
+  </si>
+  <si>
+    <t>1440001:100</t>
+  </si>
+  <si>
+    <t>1450001:100</t>
+  </si>
+  <si>
+    <t>1460001:100</t>
+  </si>
+  <si>
+    <t>1470001:100</t>
+  </si>
+  <si>
+    <t>1480001:100</t>
+  </si>
+  <si>
+    <t>1490001:100</t>
+  </si>
+  <si>
+    <t>1500001:100</t>
+  </si>
+  <si>
+    <t>1510001:100</t>
+  </si>
+  <si>
+    <t>1520001:100</t>
+  </si>
+  <si>
+    <t>1530001:100</t>
+  </si>
+  <si>
+    <t>1540001:100</t>
+  </si>
+  <si>
+    <t>1550001:100</t>
+  </si>
+  <si>
+    <t>1560001:100</t>
+  </si>
+  <si>
+    <t>1570001:100</t>
+  </si>
+  <si>
+    <t>1580001:100</t>
+  </si>
+  <si>
+    <t>1590001:100</t>
+  </si>
+  <si>
+    <t>1600001:100</t>
+  </si>
+  <si>
+    <t>110001:1101_110002:1101_110003:1101_110004:1101</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2018,10 +2492,10 @@
         <v>200</v>
       </c>
       <c r="O6" s="4" t="s">
-        <v>255</v>
+        <v>415</v>
       </c>
       <c r="P6" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="Q6" s="3" t="s">
         <v>231</v>
@@ -2074,10 +2548,10 @@
         <v>300</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>256</v>
+        <v>416</v>
       </c>
       <c r="P7" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="Q7" s="3" t="s">
         <v>231</v>
@@ -2130,10 +2604,10 @@
         <v>400</v>
       </c>
       <c r="O8" s="4" t="s">
-        <v>257</v>
+        <v>417</v>
       </c>
       <c r="P8" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="Q8" s="3" t="s">
         <v>231</v>
@@ -2186,10 +2660,10 @@
         <v>500</v>
       </c>
       <c r="O9" s="4" t="s">
-        <v>258</v>
+        <v>418</v>
       </c>
       <c r="P9" s="4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="Q9" s="3" t="s">
         <v>231</v>
@@ -2242,10 +2716,10 @@
         <v>600</v>
       </c>
       <c r="O10" s="4" t="s">
-        <v>259</v>
+        <v>419</v>
       </c>
       <c r="P10" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="Q10" s="3" t="s">
         <v>231</v>
@@ -2298,10 +2772,10 @@
         <v>100</v>
       </c>
       <c r="O11" s="4" t="s">
-        <v>260</v>
+        <v>420</v>
       </c>
       <c r="P11" s="4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="Q11" s="3" t="s">
         <v>231</v>
@@ -2354,10 +2828,10 @@
         <v>100</v>
       </c>
       <c r="O12" s="4" t="s">
-        <v>261</v>
+        <v>421</v>
       </c>
       <c r="P12" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="Q12" s="3" t="s">
         <v>231</v>
@@ -2410,10 +2884,10 @@
         <v>100</v>
       </c>
       <c r="O13" s="4" t="s">
-        <v>262</v>
+        <v>422</v>
       </c>
       <c r="P13" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q13" s="3" t="s">
         <v>231</v>
@@ -2466,10 +2940,10 @@
         <v>100</v>
       </c>
       <c r="O14" s="4" t="s">
-        <v>263</v>
+        <v>423</v>
       </c>
       <c r="P14" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>231</v>
@@ -2522,7 +2996,7 @@
         <v>100</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>254</v>
+        <v>573</v>
       </c>
       <c r="P15" s="1" t="s">
         <v>253</v>
@@ -2534,13 +3008,13 @@
         <v>0</v>
       </c>
       <c r="S15" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="T15" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="T15" s="1" t="s">
+      <c r="U15" s="1" t="s">
         <v>414</v>
-      </c>
-      <c r="U15" s="1" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.15">
@@ -2587,10 +3061,10 @@
         <v>100</v>
       </c>
       <c r="O16" s="4" t="s">
-        <v>264</v>
+        <v>424</v>
       </c>
       <c r="P16" s="4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="Q16" s="3" t="s">
         <v>231</v>
@@ -2643,10 +3117,10 @@
         <v>100</v>
       </c>
       <c r="O17" s="4" t="s">
-        <v>265</v>
+        <v>425</v>
       </c>
       <c r="P17" s="4" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="Q17" s="3" t="s">
         <v>231</v>
@@ -2699,10 +3173,10 @@
         <v>100</v>
       </c>
       <c r="O18" s="4" t="s">
-        <v>266</v>
+        <v>426</v>
       </c>
       <c r="P18" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="Q18" s="3" t="s">
         <v>231</v>
@@ -2755,10 +3229,10 @@
         <v>100</v>
       </c>
       <c r="O19" s="4" t="s">
-        <v>267</v>
+        <v>427</v>
       </c>
       <c r="P19" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="Q19" s="3" t="s">
         <v>231</v>
@@ -2811,10 +3285,10 @@
         <v>100</v>
       </c>
       <c r="O20" s="4" t="s">
-        <v>268</v>
+        <v>428</v>
       </c>
       <c r="P20" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q20" s="3" t="s">
         <v>231</v>
@@ -2867,10 +3341,10 @@
         <v>100</v>
       </c>
       <c r="O21" s="4" t="s">
-        <v>269</v>
+        <v>429</v>
       </c>
       <c r="P21" s="4" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q21" s="3" t="s">
         <v>231</v>
@@ -2923,10 +3397,10 @@
         <v>100</v>
       </c>
       <c r="O22" s="4" t="s">
-        <v>270</v>
+        <v>430</v>
       </c>
       <c r="P22" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="Q22" s="3" t="s">
         <v>231</v>
@@ -2979,10 +3453,10 @@
         <v>100</v>
       </c>
       <c r="O23" s="4" t="s">
-        <v>271</v>
+        <v>431</v>
       </c>
       <c r="P23" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="Q23" s="3" t="s">
         <v>231</v>
@@ -3035,10 +3509,10 @@
         <v>100</v>
       </c>
       <c r="O24" s="4" t="s">
-        <v>272</v>
+        <v>432</v>
       </c>
       <c r="P24" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="Q24" s="3" t="s">
         <v>231</v>
@@ -3091,10 +3565,10 @@
         <v>100</v>
       </c>
       <c r="O25" s="4" t="s">
-        <v>273</v>
+        <v>433</v>
       </c>
       <c r="P25" s="4" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="Q25" s="3" t="s">
         <v>231</v>
@@ -3147,10 +3621,10 @@
         <v>100</v>
       </c>
       <c r="O26" s="4" t="s">
-        <v>274</v>
+        <v>434</v>
       </c>
       <c r="P26" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="Q26" s="3" t="s">
         <v>231</v>
@@ -3203,10 +3677,10 @@
         <v>100</v>
       </c>
       <c r="O27" s="4" t="s">
-        <v>275</v>
+        <v>435</v>
       </c>
       <c r="P27" s="4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="Q27" s="3" t="s">
         <v>231</v>
@@ -3259,10 +3733,10 @@
         <v>100</v>
       </c>
       <c r="O28" s="4" t="s">
-        <v>276</v>
+        <v>436</v>
       </c>
       <c r="P28" s="4" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="Q28" s="3" t="s">
         <v>231</v>
@@ -3315,10 +3789,10 @@
         <v>100</v>
       </c>
       <c r="O29" s="4" t="s">
-        <v>277</v>
+        <v>437</v>
       </c>
       <c r="P29" s="4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="Q29" s="3" t="s">
         <v>231</v>
@@ -3371,10 +3845,10 @@
         <v>100</v>
       </c>
       <c r="O30" s="4" t="s">
-        <v>278</v>
+        <v>438</v>
       </c>
       <c r="P30" s="4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="Q30" s="3" t="s">
         <v>231</v>
@@ -3427,10 +3901,10 @@
         <v>100</v>
       </c>
       <c r="O31" s="4" t="s">
-        <v>279</v>
+        <v>439</v>
       </c>
       <c r="P31" s="4" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="Q31" s="3" t="s">
         <v>231</v>
@@ -3483,10 +3957,10 @@
         <v>100</v>
       </c>
       <c r="O32" s="4" t="s">
-        <v>280</v>
+        <v>440</v>
       </c>
       <c r="P32" s="4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="Q32" s="3" t="s">
         <v>231</v>
@@ -3539,10 +4013,10 @@
         <v>100</v>
       </c>
       <c r="O33" s="4" t="s">
-        <v>281</v>
+        <v>441</v>
       </c>
       <c r="P33" s="4" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="Q33" s="3" t="s">
         <v>231</v>
@@ -3595,10 +4069,10 @@
         <v>100</v>
       </c>
       <c r="O34" s="4" t="s">
-        <v>282</v>
+        <v>442</v>
       </c>
       <c r="P34" s="4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="Q34" s="3" t="s">
         <v>231</v>
@@ -3651,10 +4125,10 @@
         <v>100</v>
       </c>
       <c r="O35" s="4" t="s">
-        <v>283</v>
+        <v>443</v>
       </c>
       <c r="P35" s="4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="Q35" s="3" t="s">
         <v>231</v>
@@ -3707,10 +4181,10 @@
         <v>100</v>
       </c>
       <c r="O36" s="4" t="s">
-        <v>284</v>
+        <v>444</v>
       </c>
       <c r="P36" s="4" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="Q36" s="3" t="s">
         <v>231</v>
@@ -3763,10 +4237,10 @@
         <v>100</v>
       </c>
       <c r="O37" s="4" t="s">
-        <v>285</v>
+        <v>445</v>
       </c>
       <c r="P37" s="4" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="Q37" s="3" t="s">
         <v>231</v>
@@ -3819,10 +4293,10 @@
         <v>100</v>
       </c>
       <c r="O38" s="4" t="s">
-        <v>286</v>
+        <v>446</v>
       </c>
       <c r="P38" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="Q38" s="3" t="s">
         <v>231</v>
@@ -3875,10 +4349,10 @@
         <v>100</v>
       </c>
       <c r="O39" s="4" t="s">
-        <v>287</v>
+        <v>447</v>
       </c>
       <c r="P39" s="4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="Q39" s="3" t="s">
         <v>231</v>
@@ -3931,10 +4405,10 @@
         <v>100</v>
       </c>
       <c r="O40" s="4" t="s">
-        <v>288</v>
+        <v>448</v>
       </c>
       <c r="P40" s="4" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="Q40" s="3" t="s">
         <v>231</v>
@@ -3987,10 +4461,10 @@
         <v>100</v>
       </c>
       <c r="O41" s="4" t="s">
-        <v>289</v>
+        <v>449</v>
       </c>
       <c r="P41" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="Q41" s="3" t="s">
         <v>231</v>
@@ -4043,10 +4517,10 @@
         <v>100</v>
       </c>
       <c r="O42" s="4" t="s">
-        <v>290</v>
+        <v>450</v>
       </c>
       <c r="P42" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="Q42" s="3" t="s">
         <v>231</v>
@@ -4099,10 +4573,10 @@
         <v>100</v>
       </c>
       <c r="O43" s="4" t="s">
-        <v>291</v>
+        <v>451</v>
       </c>
       <c r="P43" s="4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="Q43" s="3" t="s">
         <v>231</v>
@@ -4155,10 +4629,10 @@
         <v>100</v>
       </c>
       <c r="O44" s="4" t="s">
-        <v>292</v>
+        <v>452</v>
       </c>
       <c r="P44" s="4" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="Q44" s="3" t="s">
         <v>231</v>
@@ -4211,10 +4685,10 @@
         <v>100</v>
       </c>
       <c r="O45" s="4" t="s">
-        <v>293</v>
+        <v>453</v>
       </c>
       <c r="P45" s="4" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="Q45" s="3" t="s">
         <v>231</v>
@@ -4267,10 +4741,10 @@
         <v>100</v>
       </c>
       <c r="O46" s="4" t="s">
-        <v>294</v>
+        <v>454</v>
       </c>
       <c r="P46" s="4" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="Q46" s="3" t="s">
         <v>231</v>
@@ -4323,10 +4797,10 @@
         <v>100</v>
       </c>
       <c r="O47" s="4" t="s">
-        <v>295</v>
+        <v>455</v>
       </c>
       <c r="P47" s="4" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="Q47" s="3" t="s">
         <v>231</v>
@@ -4379,10 +4853,10 @@
         <v>100</v>
       </c>
       <c r="O48" s="4" t="s">
-        <v>296</v>
+        <v>456</v>
       </c>
       <c r="P48" s="4" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="Q48" s="3" t="s">
         <v>231</v>
@@ -4435,10 +4909,10 @@
         <v>100</v>
       </c>
       <c r="O49" s="4" t="s">
-        <v>297</v>
+        <v>457</v>
       </c>
       <c r="P49" s="4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="Q49" s="3" t="s">
         <v>231</v>
@@ -4491,10 +4965,10 @@
         <v>100</v>
       </c>
       <c r="O50" s="4" t="s">
-        <v>298</v>
+        <v>458</v>
       </c>
       <c r="P50" s="4" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="Q50" s="3" t="s">
         <v>231</v>
@@ -4547,10 +5021,10 @@
         <v>100</v>
       </c>
       <c r="O51" s="4" t="s">
-        <v>299</v>
+        <v>459</v>
       </c>
       <c r="P51" s="4" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="Q51" s="3" t="s">
         <v>231</v>
@@ -4603,10 +5077,10 @@
         <v>100</v>
       </c>
       <c r="O52" s="4" t="s">
-        <v>300</v>
+        <v>460</v>
       </c>
       <c r="P52" s="4" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="Q52" s="3" t="s">
         <v>231</v>
@@ -4659,10 +5133,10 @@
         <v>100</v>
       </c>
       <c r="O53" s="4" t="s">
-        <v>301</v>
+        <v>461</v>
       </c>
       <c r="P53" s="4" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="Q53" s="3" t="s">
         <v>231</v>
@@ -4715,10 +5189,10 @@
         <v>100</v>
       </c>
       <c r="O54" s="4" t="s">
-        <v>302</v>
+        <v>462</v>
       </c>
       <c r="P54" s="4" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="Q54" s="3" t="s">
         <v>231</v>
@@ -4771,10 +5245,10 @@
         <v>100</v>
       </c>
       <c r="O55" s="4" t="s">
-        <v>303</v>
+        <v>463</v>
       </c>
       <c r="P55" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="Q55" s="3" t="s">
         <v>231</v>
@@ -4827,10 +5301,10 @@
         <v>100</v>
       </c>
       <c r="O56" s="4" t="s">
-        <v>304</v>
+        <v>464</v>
       </c>
       <c r="P56" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="Q56" s="3" t="s">
         <v>231</v>
@@ -4883,10 +5357,10 @@
         <v>100</v>
       </c>
       <c r="O57" s="4" t="s">
-        <v>305</v>
+        <v>465</v>
       </c>
       <c r="P57" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="Q57" s="3" t="s">
         <v>231</v>
@@ -4939,10 +5413,10 @@
         <v>100</v>
       </c>
       <c r="O58" s="4" t="s">
-        <v>306</v>
+        <v>466</v>
       </c>
       <c r="P58" s="4" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="Q58" s="3" t="s">
         <v>231</v>
@@ -4995,10 +5469,10 @@
         <v>100</v>
       </c>
       <c r="O59" s="4" t="s">
-        <v>307</v>
+        <v>467</v>
       </c>
       <c r="P59" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="Q59" s="3" t="s">
         <v>231</v>
@@ -5051,10 +5525,10 @@
         <v>100</v>
       </c>
       <c r="O60" s="4" t="s">
-        <v>308</v>
+        <v>468</v>
       </c>
       <c r="P60" s="4" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="Q60" s="3" t="s">
         <v>231</v>
@@ -5107,10 +5581,10 @@
         <v>100</v>
       </c>
       <c r="O61" s="4" t="s">
-        <v>309</v>
+        <v>469</v>
       </c>
       <c r="P61" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="Q61" s="3" t="s">
         <v>231</v>
@@ -5163,10 +5637,10 @@
         <v>100</v>
       </c>
       <c r="O62" s="4" t="s">
-        <v>310</v>
+        <v>470</v>
       </c>
       <c r="P62" s="4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="Q62" s="3" t="s">
         <v>231</v>
@@ -5219,10 +5693,10 @@
         <v>100</v>
       </c>
       <c r="O63" s="4" t="s">
-        <v>311</v>
+        <v>471</v>
       </c>
       <c r="P63" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="Q63" s="3" t="s">
         <v>231</v>
@@ -5275,10 +5749,10 @@
         <v>100</v>
       </c>
       <c r="O64" s="4" t="s">
-        <v>312</v>
+        <v>472</v>
       </c>
       <c r="P64" s="4" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="Q64" s="3" t="s">
         <v>231</v>
@@ -5331,10 +5805,10 @@
         <v>100</v>
       </c>
       <c r="O65" s="4" t="s">
-        <v>313</v>
+        <v>473</v>
       </c>
       <c r="P65" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="Q65" s="3" t="s">
         <v>231</v>
@@ -5387,10 +5861,10 @@
         <v>100</v>
       </c>
       <c r="O66" s="4" t="s">
-        <v>314</v>
+        <v>474</v>
       </c>
       <c r="P66" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="Q66" s="3" t="s">
         <v>231</v>
@@ -5443,10 +5917,10 @@
         <v>100</v>
       </c>
       <c r="O67" s="4" t="s">
-        <v>315</v>
+        <v>475</v>
       </c>
       <c r="P67" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="Q67" s="3" t="s">
         <v>231</v>
@@ -5499,10 +5973,10 @@
         <v>100</v>
       </c>
       <c r="O68" s="4" t="s">
-        <v>316</v>
+        <v>476</v>
       </c>
       <c r="P68" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="Q68" s="3" t="s">
         <v>231</v>
@@ -5555,10 +6029,10 @@
         <v>100</v>
       </c>
       <c r="O69" s="4" t="s">
-        <v>317</v>
+        <v>477</v>
       </c>
       <c r="P69" s="4" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="Q69" s="3" t="s">
         <v>231</v>
@@ -5611,10 +6085,10 @@
         <v>100</v>
       </c>
       <c r="O70" s="4" t="s">
-        <v>318</v>
+        <v>478</v>
       </c>
       <c r="P70" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="Q70" s="3" t="s">
         <v>231</v>
@@ -5667,10 +6141,10 @@
         <v>100</v>
       </c>
       <c r="O71" s="4" t="s">
-        <v>319</v>
+        <v>479</v>
       </c>
       <c r="P71" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="Q71" s="3" t="s">
         <v>231</v>
@@ -5723,10 +6197,10 @@
         <v>100</v>
       </c>
       <c r="O72" s="4" t="s">
-        <v>320</v>
+        <v>480</v>
       </c>
       <c r="P72" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="Q72" s="3" t="s">
         <v>231</v>
@@ -5779,10 +6253,10 @@
         <v>100</v>
       </c>
       <c r="O73" s="4" t="s">
-        <v>321</v>
+        <v>481</v>
       </c>
       <c r="P73" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="Q73" s="3" t="s">
         <v>231</v>
@@ -5835,10 +6309,10 @@
         <v>100</v>
       </c>
       <c r="O74" s="4" t="s">
-        <v>322</v>
+        <v>482</v>
       </c>
       <c r="P74" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="Q74" s="3" t="s">
         <v>231</v>
@@ -5891,10 +6365,10 @@
         <v>100</v>
       </c>
       <c r="O75" s="4" t="s">
-        <v>323</v>
+        <v>483</v>
       </c>
       <c r="P75" s="4" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="Q75" s="3" t="s">
         <v>231</v>
@@ -5947,10 +6421,10 @@
         <v>100</v>
       </c>
       <c r="O76" s="4" t="s">
-        <v>324</v>
+        <v>484</v>
       </c>
       <c r="P76" s="4" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="Q76" s="3" t="s">
         <v>231</v>
@@ -6003,10 +6477,10 @@
         <v>100</v>
       </c>
       <c r="O77" s="4" t="s">
-        <v>325</v>
+        <v>485</v>
       </c>
       <c r="P77" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="Q77" s="3" t="s">
         <v>231</v>
@@ -6059,10 +6533,10 @@
         <v>100</v>
       </c>
       <c r="O78" s="4" t="s">
-        <v>326</v>
+        <v>486</v>
       </c>
       <c r="P78" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="Q78" s="3" t="s">
         <v>231</v>
@@ -6115,10 +6589,10 @@
         <v>100</v>
       </c>
       <c r="O79" s="4" t="s">
-        <v>327</v>
+        <v>487</v>
       </c>
       <c r="P79" s="4" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Q79" s="3" t="s">
         <v>231</v>
@@ -6171,10 +6645,10 @@
         <v>100</v>
       </c>
       <c r="O80" s="4" t="s">
-        <v>328</v>
+        <v>488</v>
       </c>
       <c r="P80" s="4" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="Q80" s="3" t="s">
         <v>231</v>
@@ -6227,10 +6701,10 @@
         <v>100</v>
       </c>
       <c r="O81" s="4" t="s">
-        <v>329</v>
+        <v>489</v>
       </c>
       <c r="P81" s="4" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="Q81" s="3" t="s">
         <v>231</v>
@@ -6283,10 +6757,10 @@
         <v>100</v>
       </c>
       <c r="O82" s="4" t="s">
-        <v>330</v>
+        <v>490</v>
       </c>
       <c r="P82" s="4" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="Q82" s="3" t="s">
         <v>231</v>
@@ -6339,10 +6813,10 @@
         <v>100</v>
       </c>
       <c r="O83" s="4" t="s">
-        <v>331</v>
+        <v>491</v>
       </c>
       <c r="P83" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="Q83" s="3" t="s">
         <v>231</v>
@@ -6395,10 +6869,10 @@
         <v>100</v>
       </c>
       <c r="O84" s="4" t="s">
-        <v>332</v>
+        <v>492</v>
       </c>
       <c r="P84" s="4" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="Q84" s="3" t="s">
         <v>231</v>
@@ -6451,10 +6925,10 @@
         <v>100</v>
       </c>
       <c r="O85" s="4" t="s">
-        <v>333</v>
+        <v>493</v>
       </c>
       <c r="P85" s="4" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="Q85" s="3" t="s">
         <v>231</v>
@@ -6507,10 +6981,10 @@
         <v>100</v>
       </c>
       <c r="O86" s="4" t="s">
-        <v>334</v>
+        <v>494</v>
       </c>
       <c r="P86" s="4" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="Q86" s="3" t="s">
         <v>231</v>
@@ -6563,10 +7037,10 @@
         <v>100</v>
       </c>
       <c r="O87" s="4" t="s">
-        <v>335</v>
+        <v>495</v>
       </c>
       <c r="P87" s="4" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="Q87" s="3" t="s">
         <v>231</v>
@@ -6619,10 +7093,10 @@
         <v>100</v>
       </c>
       <c r="O88" s="4" t="s">
-        <v>336</v>
+        <v>496</v>
       </c>
       <c r="P88" s="4" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="Q88" s="3" t="s">
         <v>231</v>
@@ -6675,10 +7149,10 @@
         <v>100</v>
       </c>
       <c r="O89" s="4" t="s">
-        <v>337</v>
+        <v>497</v>
       </c>
       <c r="P89" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="Q89" s="3" t="s">
         <v>231</v>
@@ -6731,10 +7205,10 @@
         <v>100</v>
       </c>
       <c r="O90" s="4" t="s">
-        <v>338</v>
+        <v>498</v>
       </c>
       <c r="P90" s="4" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="Q90" s="3" t="s">
         <v>231</v>
@@ -6787,10 +7261,10 @@
         <v>100</v>
       </c>
       <c r="O91" s="4" t="s">
-        <v>339</v>
+        <v>499</v>
       </c>
       <c r="P91" s="4" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="Q91" s="3" t="s">
         <v>231</v>
@@ -6843,10 +7317,10 @@
         <v>100</v>
       </c>
       <c r="O92" s="4" t="s">
-        <v>340</v>
+        <v>500</v>
       </c>
       <c r="P92" s="4" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="Q92" s="3" t="s">
         <v>231</v>
@@ -6899,10 +7373,10 @@
         <v>100</v>
       </c>
       <c r="O93" s="4" t="s">
-        <v>341</v>
+        <v>501</v>
       </c>
       <c r="P93" s="4" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="Q93" s="3" t="s">
         <v>231</v>
@@ -6955,10 +7429,10 @@
         <v>100</v>
       </c>
       <c r="O94" s="4" t="s">
-        <v>342</v>
+        <v>502</v>
       </c>
       <c r="P94" s="4" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="Q94" s="3" t="s">
         <v>231</v>
@@ -7011,10 +7485,10 @@
         <v>100</v>
       </c>
       <c r="O95" s="4" t="s">
-        <v>343</v>
+        <v>503</v>
       </c>
       <c r="P95" s="4" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="Q95" s="3" t="s">
         <v>231</v>
@@ -7067,10 +7541,10 @@
         <v>100</v>
       </c>
       <c r="O96" s="4" t="s">
-        <v>344</v>
+        <v>504</v>
       </c>
       <c r="P96" s="4" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="Q96" s="3" t="s">
         <v>231</v>
@@ -7123,10 +7597,10 @@
         <v>100</v>
       </c>
       <c r="O97" s="4" t="s">
-        <v>345</v>
+        <v>505</v>
       </c>
       <c r="P97" s="4" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="Q97" s="3" t="s">
         <v>231</v>
@@ -7179,10 +7653,10 @@
         <v>100</v>
       </c>
       <c r="O98" s="4" t="s">
-        <v>346</v>
+        <v>506</v>
       </c>
       <c r="P98" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="Q98" s="3" t="s">
         <v>231</v>
@@ -7235,10 +7709,10 @@
         <v>100</v>
       </c>
       <c r="O99" s="4" t="s">
-        <v>347</v>
+        <v>507</v>
       </c>
       <c r="P99" s="4" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="Q99" s="3" t="s">
         <v>231</v>
@@ -7291,10 +7765,10 @@
         <v>100</v>
       </c>
       <c r="O100" s="4" t="s">
-        <v>348</v>
+        <v>508</v>
       </c>
       <c r="P100" s="4" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="Q100" s="3" t="s">
         <v>231</v>
@@ -7347,10 +7821,10 @@
         <v>100</v>
       </c>
       <c r="O101" s="4" t="s">
-        <v>349</v>
+        <v>509</v>
       </c>
       <c r="P101" s="4" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="Q101" s="3" t="s">
         <v>231</v>
@@ -7403,10 +7877,10 @@
         <v>100</v>
       </c>
       <c r="O102" s="4" t="s">
-        <v>350</v>
+        <v>510</v>
       </c>
       <c r="P102" s="4" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="Q102" s="3" t="s">
         <v>231</v>
@@ -7459,10 +7933,10 @@
         <v>100</v>
       </c>
       <c r="O103" s="4" t="s">
-        <v>351</v>
+        <v>511</v>
       </c>
       <c r="P103" s="4" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="Q103" s="3" t="s">
         <v>231</v>
@@ -7515,10 +7989,10 @@
         <v>100</v>
       </c>
       <c r="O104" s="4" t="s">
-        <v>352</v>
+        <v>512</v>
       </c>
       <c r="P104" s="4" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="Q104" s="3" t="s">
         <v>231</v>
@@ -7571,10 +8045,10 @@
         <v>100</v>
       </c>
       <c r="O105" s="4" t="s">
-        <v>353</v>
+        <v>513</v>
       </c>
       <c r="P105" s="4" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="Q105" s="3" t="s">
         <v>231</v>
@@ -7627,10 +8101,10 @@
         <v>100</v>
       </c>
       <c r="O106" s="4" t="s">
-        <v>354</v>
+        <v>514</v>
       </c>
       <c r="P106" s="4" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="Q106" s="3" t="s">
         <v>231</v>
@@ -7683,10 +8157,10 @@
         <v>100</v>
       </c>
       <c r="O107" s="4" t="s">
-        <v>355</v>
+        <v>515</v>
       </c>
       <c r="P107" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="Q107" s="3" t="s">
         <v>231</v>
@@ -7739,10 +8213,10 @@
         <v>100</v>
       </c>
       <c r="O108" s="4" t="s">
-        <v>356</v>
+        <v>516</v>
       </c>
       <c r="P108" s="4" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="Q108" s="3" t="s">
         <v>231</v>
@@ -7795,10 +8269,10 @@
         <v>100</v>
       </c>
       <c r="O109" s="4" t="s">
-        <v>357</v>
+        <v>517</v>
       </c>
       <c r="P109" s="4" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="Q109" s="3" t="s">
         <v>231</v>
@@ -7851,10 +8325,10 @@
         <v>100</v>
       </c>
       <c r="O110" s="4" t="s">
-        <v>358</v>
+        <v>518</v>
       </c>
       <c r="P110" s="4" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="Q110" s="3" t="s">
         <v>231</v>
@@ -7907,10 +8381,10 @@
         <v>100</v>
       </c>
       <c r="O111" s="4" t="s">
-        <v>359</v>
+        <v>519</v>
       </c>
       <c r="P111" s="4" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="Q111" s="3" t="s">
         <v>231</v>
@@ -7963,10 +8437,10 @@
         <v>100</v>
       </c>
       <c r="O112" s="4" t="s">
-        <v>360</v>
+        <v>520</v>
       </c>
       <c r="P112" s="4" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="Q112" s="3" t="s">
         <v>231</v>
@@ -8019,10 +8493,10 @@
         <v>100</v>
       </c>
       <c r="O113" s="4" t="s">
-        <v>361</v>
+        <v>521</v>
       </c>
       <c r="P113" s="4" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="Q113" s="3" t="s">
         <v>231</v>
@@ -8075,10 +8549,10 @@
         <v>100</v>
       </c>
       <c r="O114" s="4" t="s">
-        <v>362</v>
+        <v>522</v>
       </c>
       <c r="P114" s="4" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="Q114" s="3" t="s">
         <v>231</v>
@@ -8131,10 +8605,10 @@
         <v>100</v>
       </c>
       <c r="O115" s="4" t="s">
-        <v>363</v>
+        <v>523</v>
       </c>
       <c r="P115" s="4" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="Q115" s="3" t="s">
         <v>231</v>
@@ -8187,10 +8661,10 @@
         <v>100</v>
       </c>
       <c r="O116" s="4" t="s">
-        <v>364</v>
+        <v>524</v>
       </c>
       <c r="P116" s="4" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="Q116" s="3" t="s">
         <v>231</v>
@@ -8243,10 +8717,10 @@
         <v>100</v>
       </c>
       <c r="O117" s="4" t="s">
-        <v>365</v>
+        <v>525</v>
       </c>
       <c r="P117" s="4" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="Q117" s="3" t="s">
         <v>231</v>
@@ -8299,10 +8773,10 @@
         <v>100</v>
       </c>
       <c r="O118" s="4" t="s">
-        <v>366</v>
+        <v>526</v>
       </c>
       <c r="P118" s="4" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="Q118" s="3" t="s">
         <v>231</v>
@@ -8355,10 +8829,10 @@
         <v>100</v>
       </c>
       <c r="O119" s="4" t="s">
-        <v>367</v>
+        <v>527</v>
       </c>
       <c r="P119" s="4" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="Q119" s="3" t="s">
         <v>231</v>
@@ -8411,10 +8885,10 @@
         <v>100</v>
       </c>
       <c r="O120" s="4" t="s">
-        <v>368</v>
+        <v>528</v>
       </c>
       <c r="P120" s="4" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="Q120" s="3" t="s">
         <v>231</v>
@@ -8467,10 +8941,10 @@
         <v>100</v>
       </c>
       <c r="O121" s="4" t="s">
-        <v>369</v>
+        <v>529</v>
       </c>
       <c r="P121" s="4" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="Q121" s="3" t="s">
         <v>231</v>
@@ -8523,10 +8997,10 @@
         <v>100</v>
       </c>
       <c r="O122" s="4" t="s">
-        <v>370</v>
+        <v>530</v>
       </c>
       <c r="P122" s="4" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="Q122" s="3" t="s">
         <v>231</v>
@@ -8579,10 +9053,10 @@
         <v>100</v>
       </c>
       <c r="O123" s="4" t="s">
-        <v>371</v>
+        <v>531</v>
       </c>
       <c r="P123" s="4" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="Q123" s="3" t="s">
         <v>231</v>
@@ -8635,10 +9109,10 @@
         <v>100</v>
       </c>
       <c r="O124" s="4" t="s">
-        <v>372</v>
+        <v>532</v>
       </c>
       <c r="P124" s="4" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="Q124" s="3" t="s">
         <v>231</v>
@@ -8691,10 +9165,10 @@
         <v>100</v>
       </c>
       <c r="O125" s="4" t="s">
-        <v>373</v>
+        <v>533</v>
       </c>
       <c r="P125" s="4" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="Q125" s="3" t="s">
         <v>231</v>
@@ -8747,10 +9221,10 @@
         <v>100</v>
       </c>
       <c r="O126" s="4" t="s">
-        <v>374</v>
+        <v>534</v>
       </c>
       <c r="P126" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="Q126" s="3" t="s">
         <v>231</v>
@@ -8803,10 +9277,10 @@
         <v>100</v>
       </c>
       <c r="O127" s="4" t="s">
-        <v>375</v>
+        <v>535</v>
       </c>
       <c r="P127" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="Q127" s="3" t="s">
         <v>231</v>
@@ -8859,10 +9333,10 @@
         <v>100</v>
       </c>
       <c r="O128" s="4" t="s">
-        <v>376</v>
+        <v>536</v>
       </c>
       <c r="P128" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="Q128" s="3" t="s">
         <v>231</v>
@@ -8915,10 +9389,10 @@
         <v>100</v>
       </c>
       <c r="O129" s="4" t="s">
-        <v>377</v>
+        <v>537</v>
       </c>
       <c r="P129" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="Q129" s="3" t="s">
         <v>231</v>
@@ -8971,10 +9445,10 @@
         <v>100</v>
       </c>
       <c r="O130" s="4" t="s">
-        <v>378</v>
+        <v>538</v>
       </c>
       <c r="P130" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="Q130" s="3" t="s">
         <v>231</v>
@@ -9027,10 +9501,10 @@
         <v>100</v>
       </c>
       <c r="O131" s="4" t="s">
-        <v>379</v>
+        <v>539</v>
       </c>
       <c r="P131" s="4" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="Q131" s="3" t="s">
         <v>231</v>
@@ -9083,10 +9557,10 @@
         <v>100</v>
       </c>
       <c r="O132" s="4" t="s">
-        <v>380</v>
+        <v>540</v>
       </c>
       <c r="P132" s="4" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="Q132" s="3" t="s">
         <v>231</v>
@@ -9139,10 +9613,10 @@
         <v>100</v>
       </c>
       <c r="O133" s="4" t="s">
-        <v>381</v>
+        <v>541</v>
       </c>
       <c r="P133" s="4" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="Q133" s="3" t="s">
         <v>231</v>
@@ -9195,10 +9669,10 @@
         <v>100</v>
       </c>
       <c r="O134" s="4" t="s">
-        <v>382</v>
+        <v>542</v>
       </c>
       <c r="P134" s="4" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="Q134" s="3" t="s">
         <v>231</v>
@@ -9251,10 +9725,10 @@
         <v>100</v>
       </c>
       <c r="O135" s="4" t="s">
-        <v>383</v>
+        <v>543</v>
       </c>
       <c r="P135" s="4" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="Q135" s="3" t="s">
         <v>231</v>
@@ -9307,10 +9781,10 @@
         <v>100</v>
       </c>
       <c r="O136" s="4" t="s">
-        <v>384</v>
+        <v>544</v>
       </c>
       <c r="P136" s="4" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="Q136" s="3" t="s">
         <v>231</v>
@@ -9363,10 +9837,10 @@
         <v>100</v>
       </c>
       <c r="O137" s="4" t="s">
-        <v>385</v>
+        <v>545</v>
       </c>
       <c r="P137" s="4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="Q137" s="3" t="s">
         <v>231</v>
@@ -9419,10 +9893,10 @@
         <v>100</v>
       </c>
       <c r="O138" s="4" t="s">
-        <v>386</v>
+        <v>546</v>
       </c>
       <c r="P138" s="4" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="Q138" s="3" t="s">
         <v>231</v>
@@ -9475,10 +9949,10 @@
         <v>100</v>
       </c>
       <c r="O139" s="4" t="s">
-        <v>387</v>
+        <v>547</v>
       </c>
       <c r="P139" s="4" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="Q139" s="3" t="s">
         <v>231</v>
@@ -9531,10 +10005,10 @@
         <v>100</v>
       </c>
       <c r="O140" s="4" t="s">
-        <v>388</v>
+        <v>548</v>
       </c>
       <c r="P140" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="Q140" s="3" t="s">
         <v>231</v>
@@ -9587,10 +10061,10 @@
         <v>100</v>
       </c>
       <c r="O141" s="4" t="s">
-        <v>389</v>
+        <v>549</v>
       </c>
       <c r="P141" s="4" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="Q141" s="3" t="s">
         <v>231</v>
@@ -9643,10 +10117,10 @@
         <v>100</v>
       </c>
       <c r="O142" s="4" t="s">
-        <v>390</v>
+        <v>550</v>
       </c>
       <c r="P142" s="4" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="Q142" s="3" t="s">
         <v>231</v>
@@ -9699,10 +10173,10 @@
         <v>100</v>
       </c>
       <c r="O143" s="4" t="s">
-        <v>391</v>
+        <v>551</v>
       </c>
       <c r="P143" s="4" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="Q143" s="3" t="s">
         <v>231</v>
@@ -9755,10 +10229,10 @@
         <v>100</v>
       </c>
       <c r="O144" s="4" t="s">
-        <v>392</v>
+        <v>552</v>
       </c>
       <c r="P144" s="4" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="Q144" s="3" t="s">
         <v>231</v>
@@ -9811,10 +10285,10 @@
         <v>100</v>
       </c>
       <c r="O145" s="4" t="s">
-        <v>393</v>
+        <v>553</v>
       </c>
       <c r="P145" s="4" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="Q145" s="3" t="s">
         <v>231</v>
@@ -9867,10 +10341,10 @@
         <v>100</v>
       </c>
       <c r="O146" s="4" t="s">
-        <v>394</v>
+        <v>554</v>
       </c>
       <c r="P146" s="4" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="Q146" s="3" t="s">
         <v>231</v>
@@ -9923,10 +10397,10 @@
         <v>100</v>
       </c>
       <c r="O147" s="4" t="s">
-        <v>395</v>
+        <v>555</v>
       </c>
       <c r="P147" s="4" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="Q147" s="3" t="s">
         <v>231</v>
@@ -9979,10 +10453,10 @@
         <v>100</v>
       </c>
       <c r="O148" s="4" t="s">
-        <v>396</v>
+        <v>556</v>
       </c>
       <c r="P148" s="4" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="Q148" s="3" t="s">
         <v>231</v>
@@ -10035,10 +10509,10 @@
         <v>100</v>
       </c>
       <c r="O149" s="4" t="s">
-        <v>397</v>
+        <v>557</v>
       </c>
       <c r="P149" s="4" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q149" s="3" t="s">
         <v>231</v>
@@ -10091,10 +10565,10 @@
         <v>100</v>
       </c>
       <c r="O150" s="4" t="s">
-        <v>398</v>
+        <v>558</v>
       </c>
       <c r="P150" s="4" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="Q150" s="3" t="s">
         <v>231</v>
@@ -10147,10 +10621,10 @@
         <v>100</v>
       </c>
       <c r="O151" s="4" t="s">
-        <v>399</v>
+        <v>559</v>
       </c>
       <c r="P151" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="Q151" s="3" t="s">
         <v>231</v>
@@ -10203,10 +10677,10 @@
         <v>100</v>
       </c>
       <c r="O152" s="4" t="s">
-        <v>400</v>
+        <v>560</v>
       </c>
       <c r="P152" s="4" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="Q152" s="3" t="s">
         <v>231</v>
@@ -10259,10 +10733,10 @@
         <v>100</v>
       </c>
       <c r="O153" s="4" t="s">
-        <v>401</v>
+        <v>561</v>
       </c>
       <c r="P153" s="4" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="Q153" s="3" t="s">
         <v>231</v>
@@ -10315,10 +10789,10 @@
         <v>100</v>
       </c>
       <c r="O154" s="4" t="s">
-        <v>402</v>
+        <v>562</v>
       </c>
       <c r="P154" s="4" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="Q154" s="3" t="s">
         <v>231</v>
@@ -10371,10 +10845,10 @@
         <v>100</v>
       </c>
       <c r="O155" s="4" t="s">
-        <v>403</v>
+        <v>563</v>
       </c>
       <c r="P155" s="4" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="Q155" s="3" t="s">
         <v>231</v>
@@ -10427,10 +10901,10 @@
         <v>100</v>
       </c>
       <c r="O156" s="4" t="s">
-        <v>404</v>
+        <v>564</v>
       </c>
       <c r="P156" s="4" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="Q156" s="3" t="s">
         <v>231</v>
@@ -10483,10 +10957,10 @@
         <v>100</v>
       </c>
       <c r="O157" s="4" t="s">
-        <v>405</v>
+        <v>565</v>
       </c>
       <c r="P157" s="4" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="Q157" s="3" t="s">
         <v>231</v>
@@ -10539,10 +11013,10 @@
         <v>100</v>
       </c>
       <c r="O158" s="4" t="s">
-        <v>406</v>
+        <v>566</v>
       </c>
       <c r="P158" s="4" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="Q158" s="3" t="s">
         <v>231</v>
@@ -10595,10 +11069,10 @@
         <v>100</v>
       </c>
       <c r="O159" s="4" t="s">
-        <v>407</v>
+        <v>567</v>
       </c>
       <c r="P159" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="Q159" s="3" t="s">
         <v>231</v>
@@ -10651,10 +11125,10 @@
         <v>100</v>
       </c>
       <c r="O160" s="4" t="s">
-        <v>408</v>
+        <v>568</v>
       </c>
       <c r="P160" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="Q160" s="3" t="s">
         <v>231</v>
@@ -10707,10 +11181,10 @@
         <v>100</v>
       </c>
       <c r="O161" s="4" t="s">
-        <v>409</v>
+        <v>569</v>
       </c>
       <c r="P161" s="4" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="Q161" s="3" t="s">
         <v>231</v>
@@ -10763,10 +11237,10 @@
         <v>100</v>
       </c>
       <c r="O162" s="4" t="s">
-        <v>410</v>
+        <v>570</v>
       </c>
       <c r="P162" s="4" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="Q162" s="3" t="s">
         <v>231</v>
@@ -10819,10 +11293,10 @@
         <v>100</v>
       </c>
       <c r="O163" s="4" t="s">
-        <v>411</v>
+        <v>571</v>
       </c>
       <c r="P163" s="4" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="Q163" s="3" t="s">
         <v>231</v>
@@ -10875,10 +11349,10 @@
         <v>100</v>
       </c>
       <c r="O164" s="4" t="s">
-        <v>412</v>
+        <v>572</v>
       </c>
       <c r="P164" s="4" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="Q164" s="3" t="s">
         <v>231</v>

--- a/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F855F3C8-3F23-44B3-AE67-090D86EFBE78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50604506-93F2-433E-86C9-3B8E885D92DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_barries_v8" sheetId="1" r:id="rId1"/>
@@ -1341,489 +1341,489 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>110001:300_110002:550_110003:700_110004:750</t>
+    <t>20001:100</t>
+  </si>
+  <si>
+    <t>30001:100</t>
+  </si>
+  <si>
+    <t>40001:100</t>
+  </si>
+  <si>
+    <t>50001:100</t>
+  </si>
+  <si>
+    <t>60001:100</t>
+  </si>
+  <si>
+    <t>70001:100</t>
+  </si>
+  <si>
+    <t>80001:100</t>
+  </si>
+  <si>
+    <t>90001:100</t>
+  </si>
+  <si>
+    <t>100001:100</t>
+  </si>
+  <si>
+    <t>120001:100</t>
+  </si>
+  <si>
+    <t>130001:100</t>
+  </si>
+  <si>
+    <t>140001:100</t>
+  </si>
+  <si>
+    <t>150001:100</t>
+  </si>
+  <si>
+    <t>160001:100</t>
+  </si>
+  <si>
+    <t>170001:100</t>
+  </si>
+  <si>
+    <t>180001:100</t>
+  </si>
+  <si>
+    <t>190001:100</t>
+  </si>
+  <si>
+    <t>200001:100</t>
+  </si>
+  <si>
+    <t>210001:100</t>
+  </si>
+  <si>
+    <t>220001:100</t>
+  </si>
+  <si>
+    <t>230001:100</t>
+  </si>
+  <si>
+    <t>240001:100</t>
+  </si>
+  <si>
+    <t>250001:100</t>
+  </si>
+  <si>
+    <t>260001:100</t>
+  </si>
+  <si>
+    <t>270001:100</t>
+  </si>
+  <si>
+    <t>280001:100</t>
+  </si>
+  <si>
+    <t>290001:100</t>
+  </si>
+  <si>
+    <t>300001:100</t>
+  </si>
+  <si>
+    <t>310001:100</t>
+  </si>
+  <si>
+    <t>320001:100</t>
+  </si>
+  <si>
+    <t>330001:100</t>
+  </si>
+  <si>
+    <t>340001:100</t>
+  </si>
+  <si>
+    <t>350001:100</t>
+  </si>
+  <si>
+    <t>360001:100</t>
+  </si>
+  <si>
+    <t>370001:100</t>
+  </si>
+  <si>
+    <t>380001:100</t>
+  </si>
+  <si>
+    <t>390001:100</t>
+  </si>
+  <si>
+    <t>400001:100</t>
+  </si>
+  <si>
+    <t>410001:100</t>
+  </si>
+  <si>
+    <t>420001:100</t>
+  </si>
+  <si>
+    <t>430001:100</t>
+  </si>
+  <si>
+    <t>440001:100</t>
+  </si>
+  <si>
+    <t>450001:100</t>
+  </si>
+  <si>
+    <t>460001:100</t>
+  </si>
+  <si>
+    <t>470001:100</t>
+  </si>
+  <si>
+    <t>480001:100</t>
+  </si>
+  <si>
+    <t>490001:100</t>
+  </si>
+  <si>
+    <t>500001:100</t>
+  </si>
+  <si>
+    <t>510001:100</t>
+  </si>
+  <si>
+    <t>520001:100</t>
+  </si>
+  <si>
+    <t>530001:100</t>
+  </si>
+  <si>
+    <t>540001:100</t>
+  </si>
+  <si>
+    <t>550001:100</t>
+  </si>
+  <si>
+    <t>560001:100</t>
+  </si>
+  <si>
+    <t>570001:100</t>
+  </si>
+  <si>
+    <t>580001:100</t>
+  </si>
+  <si>
+    <t>590001:100</t>
+  </si>
+  <si>
+    <t>600001:100</t>
+  </si>
+  <si>
+    <t>610001:100</t>
+  </si>
+  <si>
+    <t>620001:100</t>
+  </si>
+  <si>
+    <t>630001:100</t>
+  </si>
+  <si>
+    <t>640001:100</t>
+  </si>
+  <si>
+    <t>650001:100</t>
+  </si>
+  <si>
+    <t>660001:100</t>
+  </si>
+  <si>
+    <t>670001:100</t>
+  </si>
+  <si>
+    <t>680001:100</t>
+  </si>
+  <si>
+    <t>690001:100</t>
+  </si>
+  <si>
+    <t>700001:100</t>
+  </si>
+  <si>
+    <t>710001:100</t>
+  </si>
+  <si>
+    <t>720001:100</t>
+  </si>
+  <si>
+    <t>730001:100</t>
+  </si>
+  <si>
+    <t>740001:100</t>
+  </si>
+  <si>
+    <t>750001:100</t>
+  </si>
+  <si>
+    <t>760001:100</t>
+  </si>
+  <si>
+    <t>770001:100</t>
+  </si>
+  <si>
+    <t>780001:100</t>
+  </si>
+  <si>
+    <t>790001:100</t>
+  </si>
+  <si>
+    <t>800001:100</t>
+  </si>
+  <si>
+    <t>810001:100</t>
+  </si>
+  <si>
+    <t>820001:100</t>
+  </si>
+  <si>
+    <t>830001:100</t>
+  </si>
+  <si>
+    <t>840001:100</t>
+  </si>
+  <si>
+    <t>850001:100</t>
+  </si>
+  <si>
+    <t>860001:100</t>
+  </si>
+  <si>
+    <t>870001:100</t>
+  </si>
+  <si>
+    <t>880001:100</t>
+  </si>
+  <si>
+    <t>890001:100</t>
+  </si>
+  <si>
+    <t>900001:100</t>
+  </si>
+  <si>
+    <t>910001:100</t>
+  </si>
+  <si>
+    <t>920001:100</t>
+  </si>
+  <si>
+    <t>930001:100</t>
+  </si>
+  <si>
+    <t>940001:100</t>
+  </si>
+  <si>
+    <t>950001:100</t>
+  </si>
+  <si>
+    <t>960001:100</t>
+  </si>
+  <si>
+    <t>970001:100</t>
+  </si>
+  <si>
+    <t>980001:100</t>
+  </si>
+  <si>
+    <t>990001:100</t>
+  </si>
+  <si>
+    <t>1000001:100</t>
+  </si>
+  <si>
+    <t>1010001:100</t>
+  </si>
+  <si>
+    <t>1020001:100</t>
+  </si>
+  <si>
+    <t>1030001:100</t>
+  </si>
+  <si>
+    <t>1040001:100</t>
+  </si>
+  <si>
+    <t>1050001:100</t>
+  </si>
+  <si>
+    <t>1060001:100</t>
+  </si>
+  <si>
+    <t>1070001:100</t>
+  </si>
+  <si>
+    <t>1080001:100</t>
+  </si>
+  <si>
+    <t>1090001:100</t>
+  </si>
+  <si>
+    <t>1100001:100</t>
+  </si>
+  <si>
+    <t>1110001:100</t>
+  </si>
+  <si>
+    <t>1120001:100</t>
+  </si>
+  <si>
+    <t>1130001:100</t>
+  </si>
+  <si>
+    <t>1140001:100</t>
+  </si>
+  <si>
+    <t>1150001:100</t>
+  </si>
+  <si>
+    <t>1160001:100</t>
+  </si>
+  <si>
+    <t>1170001:100</t>
+  </si>
+  <si>
+    <t>1180001:100</t>
+  </si>
+  <si>
+    <t>1190001:100</t>
+  </si>
+  <si>
+    <t>1200001:100</t>
+  </si>
+  <si>
+    <t>1210001:100</t>
+  </si>
+  <si>
+    <t>1220001:100</t>
+  </si>
+  <si>
+    <t>1230001:100</t>
+  </si>
+  <si>
+    <t>1240001:100</t>
+  </si>
+  <si>
+    <t>1250001:100</t>
+  </si>
+  <si>
+    <t>1260001:100</t>
+  </si>
+  <si>
+    <t>1270001:100</t>
+  </si>
+  <si>
+    <t>1280001:100</t>
+  </si>
+  <si>
+    <t>1290001:100</t>
+  </si>
+  <si>
+    <t>1300001:100</t>
+  </si>
+  <si>
+    <t>1310001:100</t>
+  </si>
+  <si>
+    <t>1320001:100</t>
+  </si>
+  <si>
+    <t>1330001:100</t>
+  </si>
+  <si>
+    <t>1340001:100</t>
+  </si>
+  <si>
+    <t>1350001:100</t>
+  </si>
+  <si>
+    <t>1360001:100</t>
+  </si>
+  <si>
+    <t>1370001:100</t>
+  </si>
+  <si>
+    <t>1380001:100</t>
+  </si>
+  <si>
+    <t>1390001:100</t>
+  </si>
+  <si>
+    <t>1400001:100</t>
+  </si>
+  <si>
+    <t>1410001:100</t>
+  </si>
+  <si>
+    <t>1420001:100</t>
+  </si>
+  <si>
+    <t>1430001:100</t>
+  </si>
+  <si>
+    <t>1440001:100</t>
+  </si>
+  <si>
+    <t>1450001:100</t>
+  </si>
+  <si>
+    <t>1460001:100</t>
+  </si>
+  <si>
+    <t>1470001:100</t>
+  </si>
+  <si>
+    <t>1480001:100</t>
+  </si>
+  <si>
+    <t>1490001:100</t>
+  </si>
+  <si>
+    <t>1500001:100</t>
+  </si>
+  <si>
+    <t>1510001:100</t>
+  </si>
+  <si>
+    <t>1520001:100</t>
+  </si>
+  <si>
+    <t>1530001:100</t>
+  </si>
+  <si>
+    <t>1540001:100</t>
+  </si>
+  <si>
+    <t>1550001:100</t>
+  </si>
+  <si>
+    <t>1560001:100</t>
+  </si>
+  <si>
+    <t>1570001:100</t>
+  </si>
+  <si>
+    <t>1580001:100</t>
+  </si>
+  <si>
+    <t>1590001:100</t>
+  </si>
+  <si>
+    <t>1600001:100</t>
+  </si>
+  <si>
+    <t>110001:1101_110002:1101_110003:1101_110004:1101</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>110001:550_110002:850_110003:1150_110004:1250</t>
+    <t>110001:300_110002:950_110003:2100_110004:3350</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>20001:100</t>
-  </si>
-  <si>
-    <t>30001:100</t>
-  </si>
-  <si>
-    <t>40001:100</t>
-  </si>
-  <si>
-    <t>50001:100</t>
-  </si>
-  <si>
-    <t>60001:100</t>
-  </si>
-  <si>
-    <t>70001:100</t>
-  </si>
-  <si>
-    <t>80001:100</t>
-  </si>
-  <si>
-    <t>90001:100</t>
-  </si>
-  <si>
-    <t>100001:100</t>
-  </si>
-  <si>
-    <t>120001:100</t>
-  </si>
-  <si>
-    <t>130001:100</t>
-  </si>
-  <si>
-    <t>140001:100</t>
-  </si>
-  <si>
-    <t>150001:100</t>
-  </si>
-  <si>
-    <t>160001:100</t>
-  </si>
-  <si>
-    <t>170001:100</t>
-  </si>
-  <si>
-    <t>180001:100</t>
-  </si>
-  <si>
-    <t>190001:100</t>
-  </si>
-  <si>
-    <t>200001:100</t>
-  </si>
-  <si>
-    <t>210001:100</t>
-  </si>
-  <si>
-    <t>220001:100</t>
-  </si>
-  <si>
-    <t>230001:100</t>
-  </si>
-  <si>
-    <t>240001:100</t>
-  </si>
-  <si>
-    <t>250001:100</t>
-  </si>
-  <si>
-    <t>260001:100</t>
-  </si>
-  <si>
-    <t>270001:100</t>
-  </si>
-  <si>
-    <t>280001:100</t>
-  </si>
-  <si>
-    <t>290001:100</t>
-  </si>
-  <si>
-    <t>300001:100</t>
-  </si>
-  <si>
-    <t>310001:100</t>
-  </si>
-  <si>
-    <t>320001:100</t>
-  </si>
-  <si>
-    <t>330001:100</t>
-  </si>
-  <si>
-    <t>340001:100</t>
-  </si>
-  <si>
-    <t>350001:100</t>
-  </si>
-  <si>
-    <t>360001:100</t>
-  </si>
-  <si>
-    <t>370001:100</t>
-  </si>
-  <si>
-    <t>380001:100</t>
-  </si>
-  <si>
-    <t>390001:100</t>
-  </si>
-  <si>
-    <t>400001:100</t>
-  </si>
-  <si>
-    <t>410001:100</t>
-  </si>
-  <si>
-    <t>420001:100</t>
-  </si>
-  <si>
-    <t>430001:100</t>
-  </si>
-  <si>
-    <t>440001:100</t>
-  </si>
-  <si>
-    <t>450001:100</t>
-  </si>
-  <si>
-    <t>460001:100</t>
-  </si>
-  <si>
-    <t>470001:100</t>
-  </si>
-  <si>
-    <t>480001:100</t>
-  </si>
-  <si>
-    <t>490001:100</t>
-  </si>
-  <si>
-    <t>500001:100</t>
-  </si>
-  <si>
-    <t>510001:100</t>
-  </si>
-  <si>
-    <t>520001:100</t>
-  </si>
-  <si>
-    <t>530001:100</t>
-  </si>
-  <si>
-    <t>540001:100</t>
-  </si>
-  <si>
-    <t>550001:100</t>
-  </si>
-  <si>
-    <t>560001:100</t>
-  </si>
-  <si>
-    <t>570001:100</t>
-  </si>
-  <si>
-    <t>580001:100</t>
-  </si>
-  <si>
-    <t>590001:100</t>
-  </si>
-  <si>
-    <t>600001:100</t>
-  </si>
-  <si>
-    <t>610001:100</t>
-  </si>
-  <si>
-    <t>620001:100</t>
-  </si>
-  <si>
-    <t>630001:100</t>
-  </si>
-  <si>
-    <t>640001:100</t>
-  </si>
-  <si>
-    <t>650001:100</t>
-  </si>
-  <si>
-    <t>660001:100</t>
-  </si>
-  <si>
-    <t>670001:100</t>
-  </si>
-  <si>
-    <t>680001:100</t>
-  </si>
-  <si>
-    <t>690001:100</t>
-  </si>
-  <si>
-    <t>700001:100</t>
-  </si>
-  <si>
-    <t>710001:100</t>
-  </si>
-  <si>
-    <t>720001:100</t>
-  </si>
-  <si>
-    <t>730001:100</t>
-  </si>
-  <si>
-    <t>740001:100</t>
-  </si>
-  <si>
-    <t>750001:100</t>
-  </si>
-  <si>
-    <t>760001:100</t>
-  </si>
-  <si>
-    <t>770001:100</t>
-  </si>
-  <si>
-    <t>780001:100</t>
-  </si>
-  <si>
-    <t>790001:100</t>
-  </si>
-  <si>
-    <t>800001:100</t>
-  </si>
-  <si>
-    <t>810001:100</t>
-  </si>
-  <si>
-    <t>820001:100</t>
-  </si>
-  <si>
-    <t>830001:100</t>
-  </si>
-  <si>
-    <t>840001:100</t>
-  </si>
-  <si>
-    <t>850001:100</t>
-  </si>
-  <si>
-    <t>860001:100</t>
-  </si>
-  <si>
-    <t>870001:100</t>
-  </si>
-  <si>
-    <t>880001:100</t>
-  </si>
-  <si>
-    <t>890001:100</t>
-  </si>
-  <si>
-    <t>900001:100</t>
-  </si>
-  <si>
-    <t>910001:100</t>
-  </si>
-  <si>
-    <t>920001:100</t>
-  </si>
-  <si>
-    <t>930001:100</t>
-  </si>
-  <si>
-    <t>940001:100</t>
-  </si>
-  <si>
-    <t>950001:100</t>
-  </si>
-  <si>
-    <t>960001:100</t>
-  </si>
-  <si>
-    <t>970001:100</t>
-  </si>
-  <si>
-    <t>980001:100</t>
-  </si>
-  <si>
-    <t>990001:100</t>
-  </si>
-  <si>
-    <t>1000001:100</t>
-  </si>
-  <si>
-    <t>1010001:100</t>
-  </si>
-  <si>
-    <t>1020001:100</t>
-  </si>
-  <si>
-    <t>1030001:100</t>
-  </si>
-  <si>
-    <t>1040001:100</t>
-  </si>
-  <si>
-    <t>1050001:100</t>
-  </si>
-  <si>
-    <t>1060001:100</t>
-  </si>
-  <si>
-    <t>1070001:100</t>
-  </si>
-  <si>
-    <t>1080001:100</t>
-  </si>
-  <si>
-    <t>1090001:100</t>
-  </si>
-  <si>
-    <t>1100001:100</t>
-  </si>
-  <si>
-    <t>1110001:100</t>
-  </si>
-  <si>
-    <t>1120001:100</t>
-  </si>
-  <si>
-    <t>1130001:100</t>
-  </si>
-  <si>
-    <t>1140001:100</t>
-  </si>
-  <si>
-    <t>1150001:100</t>
-  </si>
-  <si>
-    <t>1160001:100</t>
-  </si>
-  <si>
-    <t>1170001:100</t>
-  </si>
-  <si>
-    <t>1180001:100</t>
-  </si>
-  <si>
-    <t>1190001:100</t>
-  </si>
-  <si>
-    <t>1200001:100</t>
-  </si>
-  <si>
-    <t>1210001:100</t>
-  </si>
-  <si>
-    <t>1220001:100</t>
-  </si>
-  <si>
-    <t>1230001:100</t>
-  </si>
-  <si>
-    <t>1240001:100</t>
-  </si>
-  <si>
-    <t>1250001:100</t>
-  </si>
-  <si>
-    <t>1260001:100</t>
-  </si>
-  <si>
-    <t>1270001:100</t>
-  </si>
-  <si>
-    <t>1280001:100</t>
-  </si>
-  <si>
-    <t>1290001:100</t>
-  </si>
-  <si>
-    <t>1300001:100</t>
-  </si>
-  <si>
-    <t>1310001:100</t>
-  </si>
-  <si>
-    <t>1320001:100</t>
-  </si>
-  <si>
-    <t>1330001:100</t>
-  </si>
-  <si>
-    <t>1340001:100</t>
-  </si>
-  <si>
-    <t>1350001:100</t>
-  </si>
-  <si>
-    <t>1360001:100</t>
-  </si>
-  <si>
-    <t>1370001:100</t>
-  </si>
-  <si>
-    <t>1380001:100</t>
-  </si>
-  <si>
-    <t>1390001:100</t>
-  </si>
-  <si>
-    <t>1400001:100</t>
-  </si>
-  <si>
-    <t>1410001:100</t>
-  </si>
-  <si>
-    <t>1420001:100</t>
-  </si>
-  <si>
-    <t>1430001:100</t>
-  </si>
-  <si>
-    <t>1440001:100</t>
-  </si>
-  <si>
-    <t>1450001:100</t>
-  </si>
-  <si>
-    <t>1460001:100</t>
-  </si>
-  <si>
-    <t>1470001:100</t>
-  </si>
-  <si>
-    <t>1480001:100</t>
-  </si>
-  <si>
-    <t>1490001:100</t>
-  </si>
-  <si>
-    <t>1500001:100</t>
-  </si>
-  <si>
-    <t>1510001:100</t>
-  </si>
-  <si>
-    <t>1520001:100</t>
-  </si>
-  <si>
-    <t>1530001:100</t>
-  </si>
-  <si>
-    <t>1540001:100</t>
-  </si>
-  <si>
-    <t>1550001:100</t>
-  </si>
-  <si>
-    <t>1560001:100</t>
-  </si>
-  <si>
-    <t>1570001:100</t>
-  </si>
-  <si>
-    <t>1580001:100</t>
-  </si>
-  <si>
-    <t>1590001:100</t>
-  </si>
-  <si>
-    <t>1600001:100</t>
-  </si>
-  <si>
-    <t>110001:1101_110002:1101_110003:1101_110004:1101</t>
+    <t>110001:550_110002:1350_110003:2400_110004:3700</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2492,7 +2492,7 @@
         <v>200</v>
       </c>
       <c r="O6" s="4" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="P6" s="4" t="s">
         <v>254</v>
@@ -2548,7 +2548,7 @@
         <v>300</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="P7" s="4" t="s">
         <v>255</v>
@@ -2604,7 +2604,7 @@
         <v>400</v>
       </c>
       <c r="O8" s="4" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="P8" s="4" t="s">
         <v>256</v>
@@ -2660,7 +2660,7 @@
         <v>500</v>
       </c>
       <c r="O9" s="4" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="P9" s="4" t="s">
         <v>257</v>
@@ -2716,7 +2716,7 @@
         <v>600</v>
       </c>
       <c r="O10" s="4" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="P10" s="4" t="s">
         <v>258</v>
@@ -2772,7 +2772,7 @@
         <v>100</v>
       </c>
       <c r="O11" s="4" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="P11" s="4" t="s">
         <v>259</v>
@@ -2828,7 +2828,7 @@
         <v>100</v>
       </c>
       <c r="O12" s="4" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="P12" s="4" t="s">
         <v>260</v>
@@ -2884,7 +2884,7 @@
         <v>100</v>
       </c>
       <c r="O13" s="4" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="P13" s="4" t="s">
         <v>261</v>
@@ -2940,7 +2940,7 @@
         <v>100</v>
       </c>
       <c r="O14" s="4" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="P14" s="4" t="s">
         <v>262</v>
@@ -2996,7 +2996,7 @@
         <v>100</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="P15" s="1" t="s">
         <v>253</v>
@@ -3011,10 +3011,10 @@
         <v>412</v>
       </c>
       <c r="T15" s="1" t="s">
-        <v>413</v>
+        <v>572</v>
       </c>
       <c r="U15" s="1" t="s">
-        <v>414</v>
+        <v>573</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.15">
@@ -3061,7 +3061,7 @@
         <v>100</v>
       </c>
       <c r="O16" s="4" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="P16" s="4" t="s">
         <v>263</v>
@@ -3117,7 +3117,7 @@
         <v>100</v>
       </c>
       <c r="O17" s="4" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="P17" s="4" t="s">
         <v>264</v>
@@ -3173,7 +3173,7 @@
         <v>100</v>
       </c>
       <c r="O18" s="4" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="P18" s="4" t="s">
         <v>265</v>
@@ -3229,7 +3229,7 @@
         <v>100</v>
       </c>
       <c r="O19" s="4" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="P19" s="4" t="s">
         <v>266</v>
@@ -3285,7 +3285,7 @@
         <v>100</v>
       </c>
       <c r="O20" s="4" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="P20" s="4" t="s">
         <v>267</v>
@@ -3341,7 +3341,7 @@
         <v>100</v>
       </c>
       <c r="O21" s="4" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="P21" s="4" t="s">
         <v>268</v>
@@ -3397,7 +3397,7 @@
         <v>100</v>
       </c>
       <c r="O22" s="4" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="P22" s="4" t="s">
         <v>269</v>
@@ -3453,7 +3453,7 @@
         <v>100</v>
       </c>
       <c r="O23" s="4" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="P23" s="4" t="s">
         <v>270</v>
@@ -3509,7 +3509,7 @@
         <v>100</v>
       </c>
       <c r="O24" s="4" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="P24" s="4" t="s">
         <v>271</v>
@@ -3565,7 +3565,7 @@
         <v>100</v>
       </c>
       <c r="O25" s="4" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="P25" s="4" t="s">
         <v>272</v>
@@ -3621,7 +3621,7 @@
         <v>100</v>
       </c>
       <c r="O26" s="4" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="P26" s="4" t="s">
         <v>273</v>
@@ -3677,7 +3677,7 @@
         <v>100</v>
       </c>
       <c r="O27" s="4" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="P27" s="4" t="s">
         <v>274</v>
@@ -3733,7 +3733,7 @@
         <v>100</v>
       </c>
       <c r="O28" s="4" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="P28" s="4" t="s">
         <v>275</v>
@@ -3789,7 +3789,7 @@
         <v>100</v>
       </c>
       <c r="O29" s="4" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="P29" s="4" t="s">
         <v>276</v>
@@ -3845,7 +3845,7 @@
         <v>100</v>
       </c>
       <c r="O30" s="4" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="P30" s="4" t="s">
         <v>277</v>
@@ -3901,7 +3901,7 @@
         <v>100</v>
       </c>
       <c r="O31" s="4" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="P31" s="4" t="s">
         <v>278</v>
@@ -3957,7 +3957,7 @@
         <v>100</v>
       </c>
       <c r="O32" s="4" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="P32" s="4" t="s">
         <v>279</v>
@@ -4013,7 +4013,7 @@
         <v>100</v>
       </c>
       <c r="O33" s="4" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="P33" s="4" t="s">
         <v>280</v>
@@ -4069,7 +4069,7 @@
         <v>100</v>
       </c>
       <c r="O34" s="4" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="P34" s="4" t="s">
         <v>281</v>
@@ -4125,7 +4125,7 @@
         <v>100</v>
       </c>
       <c r="O35" s="4" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="P35" s="4" t="s">
         <v>282</v>
@@ -4181,7 +4181,7 @@
         <v>100</v>
       </c>
       <c r="O36" s="4" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="P36" s="4" t="s">
         <v>283</v>
@@ -4237,7 +4237,7 @@
         <v>100</v>
       </c>
       <c r="O37" s="4" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="P37" s="4" t="s">
         <v>284</v>
@@ -4293,7 +4293,7 @@
         <v>100</v>
       </c>
       <c r="O38" s="4" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="P38" s="4" t="s">
         <v>285</v>
@@ -4349,7 +4349,7 @@
         <v>100</v>
       </c>
       <c r="O39" s="4" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="P39" s="4" t="s">
         <v>286</v>
@@ -4405,7 +4405,7 @@
         <v>100</v>
       </c>
       <c r="O40" s="4" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="P40" s="4" t="s">
         <v>287</v>
@@ -4461,7 +4461,7 @@
         <v>100</v>
       </c>
       <c r="O41" s="4" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="P41" s="4" t="s">
         <v>288</v>
@@ -4517,7 +4517,7 @@
         <v>100</v>
       </c>
       <c r="O42" s="4" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="P42" s="4" t="s">
         <v>289</v>
@@ -4573,7 +4573,7 @@
         <v>100</v>
       </c>
       <c r="O43" s="4" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="P43" s="4" t="s">
         <v>290</v>
@@ -4629,7 +4629,7 @@
         <v>100</v>
       </c>
       <c r="O44" s="4" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="P44" s="4" t="s">
         <v>291</v>
@@ -4685,7 +4685,7 @@
         <v>100</v>
       </c>
       <c r="O45" s="4" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="P45" s="4" t="s">
         <v>292</v>
@@ -4741,7 +4741,7 @@
         <v>100</v>
       </c>
       <c r="O46" s="4" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="P46" s="4" t="s">
         <v>293</v>
@@ -4797,7 +4797,7 @@
         <v>100</v>
       </c>
       <c r="O47" s="4" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="P47" s="4" t="s">
         <v>294</v>
@@ -4853,7 +4853,7 @@
         <v>100</v>
       </c>
       <c r="O48" s="4" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="P48" s="4" t="s">
         <v>295</v>
@@ -4909,7 +4909,7 @@
         <v>100</v>
       </c>
       <c r="O49" s="4" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="P49" s="4" t="s">
         <v>296</v>
@@ -4965,7 +4965,7 @@
         <v>100</v>
       </c>
       <c r="O50" s="4" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="P50" s="4" t="s">
         <v>297</v>
@@ -5021,7 +5021,7 @@
         <v>100</v>
       </c>
       <c r="O51" s="4" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="P51" s="4" t="s">
         <v>298</v>
@@ -5077,7 +5077,7 @@
         <v>100</v>
       </c>
       <c r="O52" s="4" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="P52" s="4" t="s">
         <v>299</v>
@@ -5133,7 +5133,7 @@
         <v>100</v>
       </c>
       <c r="O53" s="4" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="P53" s="4" t="s">
         <v>300</v>
@@ -5189,7 +5189,7 @@
         <v>100</v>
       </c>
       <c r="O54" s="4" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="P54" s="4" t="s">
         <v>301</v>
@@ -5245,7 +5245,7 @@
         <v>100</v>
       </c>
       <c r="O55" s="4" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="P55" s="4" t="s">
         <v>302</v>
@@ -5301,7 +5301,7 @@
         <v>100</v>
       </c>
       <c r="O56" s="4" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="P56" s="4" t="s">
         <v>303</v>
@@ -5357,7 +5357,7 @@
         <v>100</v>
       </c>
       <c r="O57" s="4" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="P57" s="4" t="s">
         <v>304</v>
@@ -5413,7 +5413,7 @@
         <v>100</v>
       </c>
       <c r="O58" s="4" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="P58" s="4" t="s">
         <v>305</v>
@@ -5469,7 +5469,7 @@
         <v>100</v>
       </c>
       <c r="O59" s="4" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="P59" s="4" t="s">
         <v>306</v>
@@ -5525,7 +5525,7 @@
         <v>100</v>
       </c>
       <c r="O60" s="4" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="P60" s="4" t="s">
         <v>307</v>
@@ -5581,7 +5581,7 @@
         <v>100</v>
       </c>
       <c r="O61" s="4" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="P61" s="4" t="s">
         <v>308</v>
@@ -5637,7 +5637,7 @@
         <v>100</v>
       </c>
       <c r="O62" s="4" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="P62" s="4" t="s">
         <v>309</v>
@@ -5693,7 +5693,7 @@
         <v>100</v>
       </c>
       <c r="O63" s="4" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="P63" s="4" t="s">
         <v>310</v>
@@ -5749,7 +5749,7 @@
         <v>100</v>
       </c>
       <c r="O64" s="4" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="P64" s="4" t="s">
         <v>311</v>
@@ -5805,7 +5805,7 @@
         <v>100</v>
       </c>
       <c r="O65" s="4" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="P65" s="4" t="s">
         <v>312</v>
@@ -5861,7 +5861,7 @@
         <v>100</v>
       </c>
       <c r="O66" s="4" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="P66" s="4" t="s">
         <v>313</v>
@@ -5917,7 +5917,7 @@
         <v>100</v>
       </c>
       <c r="O67" s="4" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="P67" s="4" t="s">
         <v>314</v>
@@ -5973,7 +5973,7 @@
         <v>100</v>
       </c>
       <c r="O68" s="4" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="P68" s="4" t="s">
         <v>315</v>
@@ -6029,7 +6029,7 @@
         <v>100</v>
       </c>
       <c r="O69" s="4" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="P69" s="4" t="s">
         <v>316</v>
@@ -6085,7 +6085,7 @@
         <v>100</v>
       </c>
       <c r="O70" s="4" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="P70" s="4" t="s">
         <v>317</v>
@@ -6141,7 +6141,7 @@
         <v>100</v>
       </c>
       <c r="O71" s="4" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="P71" s="4" t="s">
         <v>318</v>
@@ -6197,7 +6197,7 @@
         <v>100</v>
       </c>
       <c r="O72" s="4" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="P72" s="4" t="s">
         <v>319</v>
@@ -6253,7 +6253,7 @@
         <v>100</v>
       </c>
       <c r="O73" s="4" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="P73" s="4" t="s">
         <v>320</v>
@@ -6309,7 +6309,7 @@
         <v>100</v>
       </c>
       <c r="O74" s="4" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="P74" s="4" t="s">
         <v>321</v>
@@ -6365,7 +6365,7 @@
         <v>100</v>
       </c>
       <c r="O75" s="4" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="P75" s="4" t="s">
         <v>322</v>
@@ -6421,7 +6421,7 @@
         <v>100</v>
       </c>
       <c r="O76" s="4" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="P76" s="4" t="s">
         <v>323</v>
@@ -6477,7 +6477,7 @@
         <v>100</v>
       </c>
       <c r="O77" s="4" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="P77" s="4" t="s">
         <v>324</v>
@@ -6533,7 +6533,7 @@
         <v>100</v>
       </c>
       <c r="O78" s="4" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="P78" s="4" t="s">
         <v>325</v>
@@ -6589,7 +6589,7 @@
         <v>100</v>
       </c>
       <c r="O79" s="4" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="P79" s="4" t="s">
         <v>326</v>
@@ -6645,7 +6645,7 @@
         <v>100</v>
       </c>
       <c r="O80" s="4" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="P80" s="4" t="s">
         <v>327</v>
@@ -6701,7 +6701,7 @@
         <v>100</v>
       </c>
       <c r="O81" s="4" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="P81" s="4" t="s">
         <v>328</v>
@@ -6757,7 +6757,7 @@
         <v>100</v>
       </c>
       <c r="O82" s="4" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="P82" s="4" t="s">
         <v>329</v>
@@ -6813,7 +6813,7 @@
         <v>100</v>
       </c>
       <c r="O83" s="4" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="P83" s="4" t="s">
         <v>330</v>
@@ -6869,7 +6869,7 @@
         <v>100</v>
       </c>
       <c r="O84" s="4" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="P84" s="4" t="s">
         <v>331</v>
@@ -6925,7 +6925,7 @@
         <v>100</v>
       </c>
       <c r="O85" s="4" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="P85" s="4" t="s">
         <v>332</v>
@@ -6981,7 +6981,7 @@
         <v>100</v>
       </c>
       <c r="O86" s="4" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="P86" s="4" t="s">
         <v>333</v>
@@ -7037,7 +7037,7 @@
         <v>100</v>
       </c>
       <c r="O87" s="4" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="P87" s="4" t="s">
         <v>334</v>
@@ -7093,7 +7093,7 @@
         <v>100</v>
       </c>
       <c r="O88" s="4" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="P88" s="4" t="s">
         <v>335</v>
@@ -7149,7 +7149,7 @@
         <v>100</v>
       </c>
       <c r="O89" s="4" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="P89" s="4" t="s">
         <v>336</v>
@@ -7205,7 +7205,7 @@
         <v>100</v>
       </c>
       <c r="O90" s="4" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="P90" s="4" t="s">
         <v>337</v>
@@ -7261,7 +7261,7 @@
         <v>100</v>
       </c>
       <c r="O91" s="4" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="P91" s="4" t="s">
         <v>338</v>
@@ -7317,7 +7317,7 @@
         <v>100</v>
       </c>
       <c r="O92" s="4" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="P92" s="4" t="s">
         <v>339</v>
@@ -7373,7 +7373,7 @@
         <v>100</v>
       </c>
       <c r="O93" s="4" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="P93" s="4" t="s">
         <v>340</v>
@@ -7429,7 +7429,7 @@
         <v>100</v>
       </c>
       <c r="O94" s="4" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="P94" s="4" t="s">
         <v>341</v>
@@ -7485,7 +7485,7 @@
         <v>100</v>
       </c>
       <c r="O95" s="4" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="P95" s="4" t="s">
         <v>342</v>
@@ -7541,7 +7541,7 @@
         <v>100</v>
       </c>
       <c r="O96" s="4" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="P96" s="4" t="s">
         <v>343</v>
@@ -7597,7 +7597,7 @@
         <v>100</v>
       </c>
       <c r="O97" s="4" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="P97" s="4" t="s">
         <v>344</v>
@@ -7653,7 +7653,7 @@
         <v>100</v>
       </c>
       <c r="O98" s="4" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="P98" s="4" t="s">
         <v>345</v>
@@ -7709,7 +7709,7 @@
         <v>100</v>
       </c>
       <c r="O99" s="4" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="P99" s="4" t="s">
         <v>346</v>
@@ -7765,7 +7765,7 @@
         <v>100</v>
       </c>
       <c r="O100" s="4" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="P100" s="4" t="s">
         <v>347</v>
@@ -7821,7 +7821,7 @@
         <v>100</v>
       </c>
       <c r="O101" s="4" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="P101" s="4" t="s">
         <v>348</v>
@@ -7877,7 +7877,7 @@
         <v>100</v>
       </c>
       <c r="O102" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="P102" s="4" t="s">
         <v>349</v>
@@ -7933,7 +7933,7 @@
         <v>100</v>
       </c>
       <c r="O103" s="4" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="P103" s="4" t="s">
         <v>350</v>
@@ -7989,7 +7989,7 @@
         <v>100</v>
       </c>
       <c r="O104" s="4" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="P104" s="4" t="s">
         <v>351</v>
@@ -8045,7 +8045,7 @@
         <v>100</v>
       </c>
       <c r="O105" s="4" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="P105" s="4" t="s">
         <v>352</v>
@@ -8101,7 +8101,7 @@
         <v>100</v>
       </c>
       <c r="O106" s="4" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="P106" s="4" t="s">
         <v>353</v>
@@ -8157,7 +8157,7 @@
         <v>100</v>
       </c>
       <c r="O107" s="4" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="P107" s="4" t="s">
         <v>354</v>
@@ -8213,7 +8213,7 @@
         <v>100</v>
       </c>
       <c r="O108" s="4" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="P108" s="4" t="s">
         <v>355</v>
@@ -8269,7 +8269,7 @@
         <v>100</v>
       </c>
       <c r="O109" s="4" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="P109" s="4" t="s">
         <v>356</v>
@@ -8325,7 +8325,7 @@
         <v>100</v>
       </c>
       <c r="O110" s="4" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="P110" s="4" t="s">
         <v>357</v>
@@ -8381,7 +8381,7 @@
         <v>100</v>
       </c>
       <c r="O111" s="4" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="P111" s="4" t="s">
         <v>358</v>
@@ -8437,7 +8437,7 @@
         <v>100</v>
       </c>
       <c r="O112" s="4" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="P112" s="4" t="s">
         <v>359</v>
@@ -8493,7 +8493,7 @@
         <v>100</v>
       </c>
       <c r="O113" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="P113" s="4" t="s">
         <v>360</v>
@@ -8549,7 +8549,7 @@
         <v>100</v>
       </c>
       <c r="O114" s="4" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="P114" s="4" t="s">
         <v>361</v>
@@ -8605,7 +8605,7 @@
         <v>100</v>
       </c>
       <c r="O115" s="4" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="P115" s="4" t="s">
         <v>362</v>
@@ -8661,7 +8661,7 @@
         <v>100</v>
       </c>
       <c r="O116" s="4" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="P116" s="4" t="s">
         <v>363</v>
@@ -8717,7 +8717,7 @@
         <v>100</v>
       </c>
       <c r="O117" s="4" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="P117" s="4" t="s">
         <v>364</v>
@@ -8773,7 +8773,7 @@
         <v>100</v>
       </c>
       <c r="O118" s="4" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="P118" s="4" t="s">
         <v>365</v>
@@ -8829,7 +8829,7 @@
         <v>100</v>
       </c>
       <c r="O119" s="4" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="P119" s="4" t="s">
         <v>366</v>
@@ -8885,7 +8885,7 @@
         <v>100</v>
       </c>
       <c r="O120" s="4" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="P120" s="4" t="s">
         <v>367</v>
@@ -8941,7 +8941,7 @@
         <v>100</v>
       </c>
       <c r="O121" s="4" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="P121" s="4" t="s">
         <v>368</v>
@@ -8997,7 +8997,7 @@
         <v>100</v>
       </c>
       <c r="O122" s="4" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="P122" s="4" t="s">
         <v>369</v>
@@ -9053,7 +9053,7 @@
         <v>100</v>
       </c>
       <c r="O123" s="4" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="P123" s="4" t="s">
         <v>370</v>
@@ -9109,7 +9109,7 @@
         <v>100</v>
       </c>
       <c r="O124" s="4" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="P124" s="4" t="s">
         <v>371</v>
@@ -9165,7 +9165,7 @@
         <v>100</v>
       </c>
       <c r="O125" s="4" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="P125" s="4" t="s">
         <v>372</v>
@@ -9221,7 +9221,7 @@
         <v>100</v>
       </c>
       <c r="O126" s="4" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="P126" s="4" t="s">
         <v>373</v>
@@ -9277,7 +9277,7 @@
         <v>100</v>
       </c>
       <c r="O127" s="4" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="P127" s="4" t="s">
         <v>374</v>
@@ -9333,7 +9333,7 @@
         <v>100</v>
       </c>
       <c r="O128" s="4" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="P128" s="4" t="s">
         <v>375</v>
@@ -9389,7 +9389,7 @@
         <v>100</v>
       </c>
       <c r="O129" s="4" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="P129" s="4" t="s">
         <v>376</v>
@@ -9445,7 +9445,7 @@
         <v>100</v>
       </c>
       <c r="O130" s="4" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="P130" s="4" t="s">
         <v>377</v>
@@ -9501,7 +9501,7 @@
         <v>100</v>
       </c>
       <c r="O131" s="4" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="P131" s="4" t="s">
         <v>378</v>
@@ -9557,7 +9557,7 @@
         <v>100</v>
       </c>
       <c r="O132" s="4" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="P132" s="4" t="s">
         <v>379</v>
@@ -9613,7 +9613,7 @@
         <v>100</v>
       </c>
       <c r="O133" s="4" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="P133" s="4" t="s">
         <v>380</v>
@@ -9669,7 +9669,7 @@
         <v>100</v>
       </c>
       <c r="O134" s="4" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="P134" s="4" t="s">
         <v>381</v>
@@ -9725,7 +9725,7 @@
         <v>100</v>
       </c>
       <c r="O135" s="4" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="P135" s="4" t="s">
         <v>382</v>
@@ -9781,7 +9781,7 @@
         <v>100</v>
       </c>
       <c r="O136" s="4" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="P136" s="4" t="s">
         <v>383</v>
@@ -9837,7 +9837,7 @@
         <v>100</v>
       </c>
       <c r="O137" s="4" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="P137" s="4" t="s">
         <v>384</v>
@@ -9893,7 +9893,7 @@
         <v>100</v>
       </c>
       <c r="O138" s="4" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="P138" s="4" t="s">
         <v>385</v>
@@ -9949,7 +9949,7 @@
         <v>100</v>
       </c>
       <c r="O139" s="4" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="P139" s="4" t="s">
         <v>386</v>
@@ -10005,7 +10005,7 @@
         <v>100</v>
       </c>
       <c r="O140" s="4" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="P140" s="4" t="s">
         <v>387</v>
@@ -10061,7 +10061,7 @@
         <v>100</v>
       </c>
       <c r="O141" s="4" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="P141" s="4" t="s">
         <v>388</v>
@@ -10117,7 +10117,7 @@
         <v>100</v>
       </c>
       <c r="O142" s="4" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="P142" s="4" t="s">
         <v>389</v>
@@ -10173,7 +10173,7 @@
         <v>100</v>
       </c>
       <c r="O143" s="4" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="P143" s="4" t="s">
         <v>390</v>
@@ -10229,7 +10229,7 @@
         <v>100</v>
       </c>
       <c r="O144" s="4" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="P144" s="4" t="s">
         <v>391</v>
@@ -10285,7 +10285,7 @@
         <v>100</v>
       </c>
       <c r="O145" s="4" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="P145" s="4" t="s">
         <v>392</v>
@@ -10341,7 +10341,7 @@
         <v>100</v>
       </c>
       <c r="O146" s="4" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="P146" s="4" t="s">
         <v>393</v>
@@ -10397,7 +10397,7 @@
         <v>100</v>
       </c>
       <c r="O147" s="4" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="P147" s="4" t="s">
         <v>394</v>
@@ -10453,7 +10453,7 @@
         <v>100</v>
       </c>
       <c r="O148" s="4" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="P148" s="4" t="s">
         <v>395</v>
@@ -10509,7 +10509,7 @@
         <v>100</v>
       </c>
       <c r="O149" s="4" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="P149" s="4" t="s">
         <v>396</v>
@@ -10565,7 +10565,7 @@
         <v>100</v>
       </c>
       <c r="O150" s="4" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="P150" s="4" t="s">
         <v>397</v>
@@ -10621,7 +10621,7 @@
         <v>100</v>
       </c>
       <c r="O151" s="4" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="P151" s="4" t="s">
         <v>398</v>
@@ -10677,7 +10677,7 @@
         <v>100</v>
       </c>
       <c r="O152" s="4" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="P152" s="4" t="s">
         <v>399</v>
@@ -10733,7 +10733,7 @@
         <v>100</v>
       </c>
       <c r="O153" s="4" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="P153" s="4" t="s">
         <v>400</v>
@@ -10789,7 +10789,7 @@
         <v>100</v>
       </c>
       <c r="O154" s="4" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="P154" s="4" t="s">
         <v>401</v>
@@ -10845,7 +10845,7 @@
         <v>100</v>
       </c>
       <c r="O155" s="4" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="P155" s="4" t="s">
         <v>402</v>
@@ -10901,7 +10901,7 @@
         <v>100</v>
       </c>
       <c r="O156" s="4" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="P156" s="4" t="s">
         <v>403</v>
@@ -10957,7 +10957,7 @@
         <v>100</v>
       </c>
       <c r="O157" s="4" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="P157" s="4" t="s">
         <v>404</v>
@@ -11013,7 +11013,7 @@
         <v>100</v>
       </c>
       <c r="O158" s="4" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="P158" s="4" t="s">
         <v>405</v>
@@ -11069,7 +11069,7 @@
         <v>100</v>
       </c>
       <c r="O159" s="4" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="P159" s="4" t="s">
         <v>406</v>
@@ -11125,7 +11125,7 @@
         <v>100</v>
       </c>
       <c r="O160" s="4" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="P160" s="4" t="s">
         <v>407</v>
@@ -11181,7 +11181,7 @@
         <v>100</v>
       </c>
       <c r="O161" s="4" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="P161" s="4" t="s">
         <v>408</v>
@@ -11237,7 +11237,7 @@
         <v>100</v>
       </c>
       <c r="O162" s="4" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="P162" s="4" t="s">
         <v>409</v>
@@ -11293,7 +11293,7 @@
         <v>100</v>
       </c>
       <c r="O163" s="4" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="P163" s="4" t="s">
         <v>410</v>
@@ -11349,7 +11349,7 @@
         <v>100</v>
       </c>
       <c r="O164" s="4" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="P164" s="4" t="s">
         <v>411</v>

--- a/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50604506-93F2-433E-86C9-3B8E885D92DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{164C4A0B-0007-4BDF-A11F-7160A77D52B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -852,979 +852,978 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>10001:100</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10001:101</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>110001:101_110002:101_110003:101_110004:101</t>
-  </si>
-  <si>
-    <t>20001:101</t>
-  </si>
-  <si>
-    <t>30001:101</t>
-  </si>
-  <si>
-    <t>40001:101</t>
-  </si>
-  <si>
-    <t>50001:101</t>
-  </si>
-  <si>
-    <t>60001:101</t>
-  </si>
-  <si>
-    <t>70001:101</t>
-  </si>
-  <si>
-    <t>80001:101</t>
-  </si>
-  <si>
-    <t>90001:101</t>
-  </si>
-  <si>
-    <t>100001:101</t>
-  </si>
-  <si>
-    <t>120001:101</t>
-  </si>
-  <si>
-    <t>130001:101</t>
-  </si>
-  <si>
-    <t>140001:101</t>
-  </si>
-  <si>
-    <t>150001:101</t>
-  </si>
-  <si>
-    <t>160001:101</t>
-  </si>
-  <si>
-    <t>170001:101</t>
-  </si>
-  <si>
-    <t>180001:101</t>
-  </si>
-  <si>
-    <t>190001:101</t>
-  </si>
-  <si>
-    <t>200001:101</t>
-  </si>
-  <si>
-    <t>210001:101</t>
-  </si>
-  <si>
-    <t>220001:101</t>
-  </si>
-  <si>
-    <t>230001:101</t>
-  </si>
-  <si>
-    <t>240001:101</t>
-  </si>
-  <si>
-    <t>250001:101</t>
-  </si>
-  <si>
-    <t>260001:101</t>
-  </si>
-  <si>
-    <t>270001:101</t>
-  </si>
-  <si>
-    <t>280001:101</t>
-  </si>
-  <si>
-    <t>290001:101</t>
-  </si>
-  <si>
-    <t>300001:101</t>
-  </si>
-  <si>
-    <t>310001:101</t>
-  </si>
-  <si>
-    <t>320001:101</t>
-  </si>
-  <si>
-    <t>330001:101</t>
-  </si>
-  <si>
-    <t>340001:101</t>
-  </si>
-  <si>
-    <t>350001:101</t>
-  </si>
-  <si>
-    <t>360001:101</t>
-  </si>
-  <si>
-    <t>370001:101</t>
-  </si>
-  <si>
-    <t>380001:101</t>
-  </si>
-  <si>
-    <t>390001:101</t>
-  </si>
-  <si>
-    <t>400001:101</t>
-  </si>
-  <si>
-    <t>410001:101</t>
-  </si>
-  <si>
-    <t>420001:101</t>
-  </si>
-  <si>
-    <t>430001:101</t>
-  </si>
-  <si>
-    <t>440001:101</t>
-  </si>
-  <si>
-    <t>450001:101</t>
-  </si>
-  <si>
-    <t>460001:101</t>
-  </si>
-  <si>
-    <t>470001:101</t>
-  </si>
-  <si>
-    <t>480001:101</t>
-  </si>
-  <si>
-    <t>490001:101</t>
-  </si>
-  <si>
-    <t>500001:101</t>
-  </si>
-  <si>
-    <t>510001:101</t>
-  </si>
-  <si>
-    <t>520001:101</t>
-  </si>
-  <si>
-    <t>530001:101</t>
-  </si>
-  <si>
-    <t>540001:101</t>
-  </si>
-  <si>
-    <t>550001:101</t>
-  </si>
-  <si>
-    <t>560001:101</t>
-  </si>
-  <si>
-    <t>570001:101</t>
-  </si>
-  <si>
-    <t>580001:101</t>
-  </si>
-  <si>
-    <t>590001:101</t>
-  </si>
-  <si>
-    <t>600001:101</t>
-  </si>
-  <si>
-    <t>610001:101</t>
-  </si>
-  <si>
-    <t>620001:101</t>
-  </si>
-  <si>
-    <t>630001:101</t>
-  </si>
-  <si>
-    <t>640001:101</t>
-  </si>
-  <si>
-    <t>650001:101</t>
-  </si>
-  <si>
-    <t>660001:101</t>
-  </si>
-  <si>
-    <t>670001:101</t>
-  </si>
-  <si>
-    <t>680001:101</t>
-  </si>
-  <si>
-    <t>690001:101</t>
-  </si>
-  <si>
-    <t>700001:101</t>
-  </si>
-  <si>
-    <t>710001:101</t>
-  </si>
-  <si>
-    <t>720001:101</t>
-  </si>
-  <si>
-    <t>730001:101</t>
-  </si>
-  <si>
-    <t>740001:101</t>
-  </si>
-  <si>
-    <t>750001:101</t>
-  </si>
-  <si>
-    <t>760001:101</t>
-  </si>
-  <si>
-    <t>770001:101</t>
-  </si>
-  <si>
-    <t>780001:101</t>
-  </si>
-  <si>
-    <t>790001:101</t>
-  </si>
-  <si>
-    <t>800001:101</t>
-  </si>
-  <si>
-    <t>810001:101</t>
-  </si>
-  <si>
-    <t>820001:101</t>
-  </si>
-  <si>
-    <t>830001:101</t>
-  </si>
-  <si>
-    <t>840001:101</t>
-  </si>
-  <si>
-    <t>850001:101</t>
-  </si>
-  <si>
-    <t>860001:101</t>
-  </si>
-  <si>
-    <t>870001:101</t>
-  </si>
-  <si>
-    <t>880001:101</t>
-  </si>
-  <si>
-    <t>890001:101</t>
-  </si>
-  <si>
-    <t>900001:101</t>
-  </si>
-  <si>
-    <t>910001:101</t>
-  </si>
-  <si>
-    <t>920001:101</t>
-  </si>
-  <si>
-    <t>930001:101</t>
-  </si>
-  <si>
-    <t>940001:101</t>
-  </si>
-  <si>
-    <t>950001:101</t>
-  </si>
-  <si>
-    <t>960001:101</t>
-  </si>
-  <si>
-    <t>970001:101</t>
-  </si>
-  <si>
-    <t>980001:101</t>
-  </si>
-  <si>
-    <t>990001:101</t>
-  </si>
-  <si>
-    <t>1000001:101</t>
-  </si>
-  <si>
-    <t>1010001:101</t>
-  </si>
-  <si>
-    <t>1020001:101</t>
-  </si>
-  <si>
-    <t>1030001:101</t>
-  </si>
-  <si>
-    <t>1040001:101</t>
-  </si>
-  <si>
-    <t>1050001:101</t>
-  </si>
-  <si>
-    <t>1060001:101</t>
-  </si>
-  <si>
-    <t>1070001:101</t>
-  </si>
-  <si>
-    <t>1080001:101</t>
-  </si>
-  <si>
-    <t>1090001:101</t>
-  </si>
-  <si>
-    <t>1100001:101</t>
-  </si>
-  <si>
-    <t>1110001:101</t>
-  </si>
-  <si>
-    <t>1120001:101</t>
-  </si>
-  <si>
-    <t>1130001:101</t>
-  </si>
-  <si>
-    <t>1140001:101</t>
-  </si>
-  <si>
-    <t>1150001:101</t>
-  </si>
-  <si>
-    <t>1160001:101</t>
-  </si>
-  <si>
-    <t>1170001:101</t>
-  </si>
-  <si>
-    <t>1180001:101</t>
-  </si>
-  <si>
-    <t>1190001:101</t>
-  </si>
-  <si>
-    <t>1200001:101</t>
-  </si>
-  <si>
-    <t>1210001:101</t>
-  </si>
-  <si>
-    <t>1220001:101</t>
-  </si>
-  <si>
-    <t>1230001:101</t>
-  </si>
-  <si>
-    <t>1240001:101</t>
-  </si>
-  <si>
-    <t>1250001:101</t>
-  </si>
-  <si>
-    <t>1260001:101</t>
-  </si>
-  <si>
-    <t>1270001:101</t>
-  </si>
-  <si>
-    <t>1280001:101</t>
-  </si>
-  <si>
-    <t>1290001:101</t>
-  </si>
-  <si>
-    <t>1300001:101</t>
-  </si>
-  <si>
-    <t>1310001:101</t>
-  </si>
-  <si>
-    <t>1320001:101</t>
-  </si>
-  <si>
-    <t>1330001:101</t>
-  </si>
-  <si>
-    <t>1340001:101</t>
-  </si>
-  <si>
-    <t>1350001:101</t>
-  </si>
-  <si>
-    <t>1360001:101</t>
-  </si>
-  <si>
-    <t>1370001:101</t>
-  </si>
-  <si>
-    <t>1380001:101</t>
-  </si>
-  <si>
-    <t>1390001:101</t>
-  </si>
-  <si>
-    <t>1400001:101</t>
-  </si>
-  <si>
-    <t>1410001:101</t>
-  </si>
-  <si>
-    <t>1420001:101</t>
-  </si>
-  <si>
-    <t>1430001:101</t>
-  </si>
-  <si>
-    <t>1440001:101</t>
-  </si>
-  <si>
-    <t>1450001:101</t>
-  </si>
-  <si>
-    <t>1460001:101</t>
-  </si>
-  <si>
-    <t>1470001:101</t>
-  </si>
-  <si>
-    <t>1480001:101</t>
-  </si>
-  <si>
-    <t>1490001:101</t>
-  </si>
-  <si>
-    <t>1500001:101</t>
-  </si>
-  <si>
-    <t>1510001:101</t>
-  </si>
-  <si>
-    <t>1520001:101</t>
-  </si>
-  <si>
-    <t>1530001:101</t>
-  </si>
-  <si>
-    <t>1540001:101</t>
-  </si>
-  <si>
-    <t>1550001:101</t>
-  </si>
-  <si>
-    <t>1560001:101</t>
-  </si>
-  <si>
-    <t>1570001:101</t>
-  </si>
-  <si>
-    <t>1580001:101</t>
-  </si>
-  <si>
-    <t>1590001:101</t>
-  </si>
-  <si>
-    <t>1600001:101</t>
-  </si>
-  <si>
     <t>110001:0_110002:0_110003:0_110004:0</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>20001:100</t>
-  </si>
-  <si>
-    <t>30001:100</t>
-  </si>
-  <si>
-    <t>40001:100</t>
-  </si>
-  <si>
-    <t>50001:100</t>
-  </si>
-  <si>
-    <t>60001:100</t>
-  </si>
-  <si>
-    <t>70001:100</t>
-  </si>
-  <si>
-    <t>80001:100</t>
-  </si>
-  <si>
-    <t>90001:100</t>
-  </si>
-  <si>
-    <t>100001:100</t>
-  </si>
-  <si>
-    <t>120001:100</t>
-  </si>
-  <si>
-    <t>130001:100</t>
-  </si>
-  <si>
-    <t>140001:100</t>
-  </si>
-  <si>
-    <t>150001:100</t>
-  </si>
-  <si>
-    <t>160001:100</t>
-  </si>
-  <si>
-    <t>170001:100</t>
-  </si>
-  <si>
-    <t>180001:100</t>
-  </si>
-  <si>
-    <t>190001:100</t>
-  </si>
-  <si>
-    <t>200001:100</t>
-  </si>
-  <si>
-    <t>210001:100</t>
-  </si>
-  <si>
-    <t>220001:100</t>
-  </si>
-  <si>
-    <t>230001:100</t>
-  </si>
-  <si>
-    <t>240001:100</t>
-  </si>
-  <si>
-    <t>250001:100</t>
-  </si>
-  <si>
-    <t>260001:100</t>
-  </si>
-  <si>
-    <t>270001:100</t>
-  </si>
-  <si>
-    <t>280001:100</t>
-  </si>
-  <si>
-    <t>290001:100</t>
-  </si>
-  <si>
-    <t>300001:100</t>
-  </si>
-  <si>
-    <t>310001:100</t>
-  </si>
-  <si>
-    <t>320001:100</t>
-  </si>
-  <si>
-    <t>330001:100</t>
-  </si>
-  <si>
-    <t>340001:100</t>
-  </si>
-  <si>
-    <t>350001:100</t>
-  </si>
-  <si>
-    <t>360001:100</t>
-  </si>
-  <si>
-    <t>370001:100</t>
-  </si>
-  <si>
-    <t>380001:100</t>
-  </si>
-  <si>
-    <t>390001:100</t>
-  </si>
-  <si>
-    <t>400001:100</t>
-  </si>
-  <si>
-    <t>410001:100</t>
-  </si>
-  <si>
-    <t>420001:100</t>
-  </si>
-  <si>
-    <t>430001:100</t>
-  </si>
-  <si>
-    <t>440001:100</t>
-  </si>
-  <si>
-    <t>450001:100</t>
-  </si>
-  <si>
-    <t>460001:100</t>
-  </si>
-  <si>
-    <t>470001:100</t>
-  </si>
-  <si>
-    <t>480001:100</t>
-  </si>
-  <si>
-    <t>490001:100</t>
-  </si>
-  <si>
-    <t>500001:100</t>
-  </si>
-  <si>
-    <t>510001:100</t>
-  </si>
-  <si>
-    <t>520001:100</t>
-  </si>
-  <si>
-    <t>530001:100</t>
-  </si>
-  <si>
-    <t>540001:100</t>
-  </si>
-  <si>
-    <t>550001:100</t>
-  </si>
-  <si>
-    <t>560001:100</t>
-  </si>
-  <si>
-    <t>570001:100</t>
-  </si>
-  <si>
-    <t>580001:100</t>
-  </si>
-  <si>
-    <t>590001:100</t>
-  </si>
-  <si>
-    <t>600001:100</t>
-  </si>
-  <si>
-    <t>610001:100</t>
-  </si>
-  <si>
-    <t>620001:100</t>
-  </si>
-  <si>
-    <t>630001:100</t>
-  </si>
-  <si>
-    <t>640001:100</t>
-  </si>
-  <si>
-    <t>650001:100</t>
-  </si>
-  <si>
-    <t>660001:100</t>
-  </si>
-  <si>
-    <t>670001:100</t>
-  </si>
-  <si>
-    <t>680001:100</t>
-  </si>
-  <si>
-    <t>690001:100</t>
-  </si>
-  <si>
-    <t>700001:100</t>
-  </si>
-  <si>
-    <t>710001:100</t>
-  </si>
-  <si>
-    <t>720001:100</t>
-  </si>
-  <si>
-    <t>730001:100</t>
-  </si>
-  <si>
-    <t>740001:100</t>
-  </si>
-  <si>
-    <t>750001:100</t>
-  </si>
-  <si>
-    <t>760001:100</t>
-  </si>
-  <si>
-    <t>770001:100</t>
-  </si>
-  <si>
-    <t>780001:100</t>
-  </si>
-  <si>
-    <t>790001:100</t>
-  </si>
-  <si>
-    <t>800001:100</t>
-  </si>
-  <si>
-    <t>810001:100</t>
-  </si>
-  <si>
-    <t>820001:100</t>
-  </si>
-  <si>
-    <t>830001:100</t>
-  </si>
-  <si>
-    <t>840001:100</t>
-  </si>
-  <si>
-    <t>850001:100</t>
-  </si>
-  <si>
-    <t>860001:100</t>
-  </si>
-  <si>
-    <t>870001:100</t>
-  </si>
-  <si>
-    <t>880001:100</t>
-  </si>
-  <si>
-    <t>890001:100</t>
-  </si>
-  <si>
-    <t>900001:100</t>
-  </si>
-  <si>
-    <t>910001:100</t>
-  </si>
-  <si>
-    <t>920001:100</t>
-  </si>
-  <si>
-    <t>930001:100</t>
-  </si>
-  <si>
-    <t>940001:100</t>
-  </si>
-  <si>
-    <t>950001:100</t>
-  </si>
-  <si>
-    <t>960001:100</t>
-  </si>
-  <si>
-    <t>970001:100</t>
-  </si>
-  <si>
-    <t>980001:100</t>
-  </si>
-  <si>
-    <t>990001:100</t>
-  </si>
-  <si>
-    <t>1000001:100</t>
-  </si>
-  <si>
-    <t>1010001:100</t>
-  </si>
-  <si>
-    <t>1020001:100</t>
-  </si>
-  <si>
-    <t>1030001:100</t>
-  </si>
-  <si>
-    <t>1040001:100</t>
-  </si>
-  <si>
-    <t>1050001:100</t>
-  </si>
-  <si>
-    <t>1060001:100</t>
-  </si>
-  <si>
-    <t>1070001:100</t>
-  </si>
-  <si>
-    <t>1080001:100</t>
-  </si>
-  <si>
-    <t>1090001:100</t>
-  </si>
-  <si>
-    <t>1100001:100</t>
-  </si>
-  <si>
-    <t>1110001:100</t>
-  </si>
-  <si>
-    <t>1120001:100</t>
-  </si>
-  <si>
-    <t>1130001:100</t>
-  </si>
-  <si>
-    <t>1140001:100</t>
-  </si>
-  <si>
-    <t>1150001:100</t>
-  </si>
-  <si>
-    <t>1160001:100</t>
-  </si>
-  <si>
-    <t>1170001:100</t>
-  </si>
-  <si>
-    <t>1180001:100</t>
-  </si>
-  <si>
-    <t>1190001:100</t>
-  </si>
-  <si>
-    <t>1200001:100</t>
-  </si>
-  <si>
-    <t>1210001:100</t>
-  </si>
-  <si>
-    <t>1220001:100</t>
-  </si>
-  <si>
-    <t>1230001:100</t>
-  </si>
-  <si>
-    <t>1240001:100</t>
-  </si>
-  <si>
-    <t>1250001:100</t>
-  </si>
-  <si>
-    <t>1260001:100</t>
-  </si>
-  <si>
-    <t>1270001:100</t>
-  </si>
-  <si>
-    <t>1280001:100</t>
-  </si>
-  <si>
-    <t>1290001:100</t>
-  </si>
-  <si>
-    <t>1300001:100</t>
-  </si>
-  <si>
-    <t>1310001:100</t>
-  </si>
-  <si>
-    <t>1320001:100</t>
-  </si>
-  <si>
-    <t>1330001:100</t>
-  </si>
-  <si>
-    <t>1340001:100</t>
-  </si>
-  <si>
-    <t>1350001:100</t>
-  </si>
-  <si>
-    <t>1360001:100</t>
-  </si>
-  <si>
-    <t>1370001:100</t>
-  </si>
-  <si>
-    <t>1380001:100</t>
-  </si>
-  <si>
-    <t>1390001:100</t>
-  </si>
-  <si>
-    <t>1400001:100</t>
-  </si>
-  <si>
-    <t>1410001:100</t>
-  </si>
-  <si>
-    <t>1420001:100</t>
-  </si>
-  <si>
-    <t>1430001:100</t>
-  </si>
-  <si>
-    <t>1440001:100</t>
-  </si>
-  <si>
-    <t>1450001:100</t>
-  </si>
-  <si>
-    <t>1460001:100</t>
-  </si>
-  <si>
-    <t>1470001:100</t>
-  </si>
-  <si>
-    <t>1480001:100</t>
-  </si>
-  <si>
-    <t>1490001:100</t>
-  </si>
-  <si>
-    <t>1500001:100</t>
-  </si>
-  <si>
-    <t>1510001:100</t>
-  </si>
-  <si>
-    <t>1520001:100</t>
-  </si>
-  <si>
-    <t>1530001:100</t>
-  </si>
-  <si>
-    <t>1540001:100</t>
-  </si>
-  <si>
-    <t>1550001:100</t>
-  </si>
-  <si>
-    <t>1560001:100</t>
-  </si>
-  <si>
-    <t>1570001:100</t>
-  </si>
-  <si>
-    <t>1580001:100</t>
-  </si>
-  <si>
-    <t>1590001:100</t>
-  </si>
-  <si>
-    <t>1600001:100</t>
-  </si>
-  <si>
-    <t>110001:1101_110002:1101_110003:1101_110004:1101</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>110001:300_110002:950_110003:2100_110004:3350</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>110001:550_110002:1350_110003:2400_110004:3700</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>110001:1101_110002:1101_110003:1101_110004:1101_0:1101</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>110001:101_110002:101_110003:101_110004:101_0:101</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>120001:100_0:100</t>
+  </si>
+  <si>
+    <t>120001:101_0:101</t>
+  </si>
+  <si>
+    <t>130001:100_0:100</t>
+  </si>
+  <si>
+    <t>130001:101_0:101</t>
+  </si>
+  <si>
+    <t>140001:100_0:100</t>
+  </si>
+  <si>
+    <t>140001:101_0:101</t>
+  </si>
+  <si>
+    <t>150001:100_0:100</t>
+  </si>
+  <si>
+    <t>150001:101_0:101</t>
+  </si>
+  <si>
+    <t>160001:100_0:100</t>
+  </si>
+  <si>
+    <t>160001:101_0:101</t>
+  </si>
+  <si>
+    <t>170001:100_0:100</t>
+  </si>
+  <si>
+    <t>170001:101_0:101</t>
+  </si>
+  <si>
+    <t>180001:100_0:100</t>
+  </si>
+  <si>
+    <t>180001:101_0:101</t>
+  </si>
+  <si>
+    <t>190001:100_0:100</t>
+  </si>
+  <si>
+    <t>190001:101_0:101</t>
+  </si>
+  <si>
+    <t>200001:100_0:100</t>
+  </si>
+  <si>
+    <t>200001:101_0:101</t>
+  </si>
+  <si>
+    <t>210001:100_0:100</t>
+  </si>
+  <si>
+    <t>210001:101_0:101</t>
+  </si>
+  <si>
+    <t>220001:100_0:100</t>
+  </si>
+  <si>
+    <t>220001:101_0:101</t>
+  </si>
+  <si>
+    <t>230001:100_0:100</t>
+  </si>
+  <si>
+    <t>230001:101_0:101</t>
+  </si>
+  <si>
+    <t>240001:100_0:100</t>
+  </si>
+  <si>
+    <t>240001:101_0:101</t>
+  </si>
+  <si>
+    <t>250001:100_0:100</t>
+  </si>
+  <si>
+    <t>250001:101_0:101</t>
+  </si>
+  <si>
+    <t>260001:100_0:100</t>
+  </si>
+  <si>
+    <t>260001:101_0:101</t>
+  </si>
+  <si>
+    <t>270001:100_0:100</t>
+  </si>
+  <si>
+    <t>270001:101_0:101</t>
+  </si>
+  <si>
+    <t>280001:100_0:100</t>
+  </si>
+  <si>
+    <t>280001:101_0:101</t>
+  </si>
+  <si>
+    <t>290001:100_0:100</t>
+  </si>
+  <si>
+    <t>290001:101_0:101</t>
+  </si>
+  <si>
+    <t>300001:100_0:100</t>
+  </si>
+  <si>
+    <t>300001:101_0:101</t>
+  </si>
+  <si>
+    <t>310001:100_0:100</t>
+  </si>
+  <si>
+    <t>310001:101_0:101</t>
+  </si>
+  <si>
+    <t>320001:100_0:100</t>
+  </si>
+  <si>
+    <t>320001:101_0:101</t>
+  </si>
+  <si>
+    <t>330001:100_0:100</t>
+  </si>
+  <si>
+    <t>330001:101_0:101</t>
+  </si>
+  <si>
+    <t>340001:100_0:100</t>
+  </si>
+  <si>
+    <t>340001:101_0:101</t>
+  </si>
+  <si>
+    <t>350001:100_0:100</t>
+  </si>
+  <si>
+    <t>350001:101_0:101</t>
+  </si>
+  <si>
+    <t>360001:100_0:100</t>
+  </si>
+  <si>
+    <t>360001:101_0:101</t>
+  </si>
+  <si>
+    <t>370001:100_0:100</t>
+  </si>
+  <si>
+    <t>370001:101_0:101</t>
+  </si>
+  <si>
+    <t>380001:100_0:100</t>
+  </si>
+  <si>
+    <t>380001:101_0:101</t>
+  </si>
+  <si>
+    <t>390001:100_0:100</t>
+  </si>
+  <si>
+    <t>390001:101_0:101</t>
+  </si>
+  <si>
+    <t>400001:100_0:100</t>
+  </si>
+  <si>
+    <t>400001:101_0:101</t>
+  </si>
+  <si>
+    <t>410001:100_0:100</t>
+  </si>
+  <si>
+    <t>410001:101_0:101</t>
+  </si>
+  <si>
+    <t>420001:100_0:100</t>
+  </si>
+  <si>
+    <t>420001:101_0:101</t>
+  </si>
+  <si>
+    <t>430001:100_0:100</t>
+  </si>
+  <si>
+    <t>430001:101_0:101</t>
+  </si>
+  <si>
+    <t>440001:100_0:100</t>
+  </si>
+  <si>
+    <t>440001:101_0:101</t>
+  </si>
+  <si>
+    <t>450001:100_0:100</t>
+  </si>
+  <si>
+    <t>450001:101_0:101</t>
+  </si>
+  <si>
+    <t>460001:100_0:100</t>
+  </si>
+  <si>
+    <t>460001:101_0:101</t>
+  </si>
+  <si>
+    <t>470001:100_0:100</t>
+  </si>
+  <si>
+    <t>470001:101_0:101</t>
+  </si>
+  <si>
+    <t>480001:100_0:100</t>
+  </si>
+  <si>
+    <t>480001:101_0:101</t>
+  </si>
+  <si>
+    <t>490001:100_0:100</t>
+  </si>
+  <si>
+    <t>490001:101_0:101</t>
+  </si>
+  <si>
+    <t>500001:100_0:100</t>
+  </si>
+  <si>
+    <t>500001:101_0:101</t>
+  </si>
+  <si>
+    <t>510001:100_0:100</t>
+  </si>
+  <si>
+    <t>510001:101_0:101</t>
+  </si>
+  <si>
+    <t>520001:100_0:100</t>
+  </si>
+  <si>
+    <t>520001:101_0:101</t>
+  </si>
+  <si>
+    <t>530001:100_0:100</t>
+  </si>
+  <si>
+    <t>530001:101_0:101</t>
+  </si>
+  <si>
+    <t>540001:100_0:100</t>
+  </si>
+  <si>
+    <t>540001:101_0:101</t>
+  </si>
+  <si>
+    <t>550001:100_0:100</t>
+  </si>
+  <si>
+    <t>550001:101_0:101</t>
+  </si>
+  <si>
+    <t>560001:100_0:100</t>
+  </si>
+  <si>
+    <t>560001:101_0:101</t>
+  </si>
+  <si>
+    <t>570001:100_0:100</t>
+  </si>
+  <si>
+    <t>570001:101_0:101</t>
+  </si>
+  <si>
+    <t>580001:100_0:100</t>
+  </si>
+  <si>
+    <t>580001:101_0:101</t>
+  </si>
+  <si>
+    <t>590001:100_0:100</t>
+  </si>
+  <si>
+    <t>590001:101_0:101</t>
+  </si>
+  <si>
+    <t>600001:100_0:100</t>
+  </si>
+  <si>
+    <t>600001:101_0:101</t>
+  </si>
+  <si>
+    <t>610001:100_0:100</t>
+  </si>
+  <si>
+    <t>610001:101_0:101</t>
+  </si>
+  <si>
+    <t>620001:100_0:100</t>
+  </si>
+  <si>
+    <t>620001:101_0:101</t>
+  </si>
+  <si>
+    <t>630001:100_0:100</t>
+  </si>
+  <si>
+    <t>630001:101_0:101</t>
+  </si>
+  <si>
+    <t>640001:100_0:100</t>
+  </si>
+  <si>
+    <t>640001:101_0:101</t>
+  </si>
+  <si>
+    <t>650001:100_0:100</t>
+  </si>
+  <si>
+    <t>650001:101_0:101</t>
+  </si>
+  <si>
+    <t>660001:100_0:100</t>
+  </si>
+  <si>
+    <t>660001:101_0:101</t>
+  </si>
+  <si>
+    <t>670001:100_0:100</t>
+  </si>
+  <si>
+    <t>670001:101_0:101</t>
+  </si>
+  <si>
+    <t>680001:100_0:100</t>
+  </si>
+  <si>
+    <t>680001:101_0:101</t>
+  </si>
+  <si>
+    <t>690001:100_0:100</t>
+  </si>
+  <si>
+    <t>690001:101_0:101</t>
+  </si>
+  <si>
+    <t>700001:100_0:100</t>
+  </si>
+  <si>
+    <t>700001:101_0:101</t>
+  </si>
+  <si>
+    <t>710001:100_0:100</t>
+  </si>
+  <si>
+    <t>710001:101_0:101</t>
+  </si>
+  <si>
+    <t>720001:100_0:100</t>
+  </si>
+  <si>
+    <t>720001:101_0:101</t>
+  </si>
+  <si>
+    <t>730001:100_0:100</t>
+  </si>
+  <si>
+    <t>730001:101_0:101</t>
+  </si>
+  <si>
+    <t>740001:100_0:100</t>
+  </si>
+  <si>
+    <t>740001:101_0:101</t>
+  </si>
+  <si>
+    <t>750001:100_0:100</t>
+  </si>
+  <si>
+    <t>750001:101_0:101</t>
+  </si>
+  <si>
+    <t>760001:100_0:100</t>
+  </si>
+  <si>
+    <t>760001:101_0:101</t>
+  </si>
+  <si>
+    <t>770001:100_0:100</t>
+  </si>
+  <si>
+    <t>770001:101_0:101</t>
+  </si>
+  <si>
+    <t>780001:100_0:100</t>
+  </si>
+  <si>
+    <t>780001:101_0:101</t>
+  </si>
+  <si>
+    <t>790001:100_0:100</t>
+  </si>
+  <si>
+    <t>790001:101_0:101</t>
+  </si>
+  <si>
+    <t>800001:100_0:100</t>
+  </si>
+  <si>
+    <t>800001:101_0:101</t>
+  </si>
+  <si>
+    <t>810001:100_0:100</t>
+  </si>
+  <si>
+    <t>810001:101_0:101</t>
+  </si>
+  <si>
+    <t>820001:100_0:100</t>
+  </si>
+  <si>
+    <t>820001:101_0:101</t>
+  </si>
+  <si>
+    <t>830001:100_0:100</t>
+  </si>
+  <si>
+    <t>830001:101_0:101</t>
+  </si>
+  <si>
+    <t>840001:100_0:100</t>
+  </si>
+  <si>
+    <t>840001:101_0:101</t>
+  </si>
+  <si>
+    <t>850001:100_0:100</t>
+  </si>
+  <si>
+    <t>850001:101_0:101</t>
+  </si>
+  <si>
+    <t>860001:100_0:100</t>
+  </si>
+  <si>
+    <t>860001:101_0:101</t>
+  </si>
+  <si>
+    <t>870001:100_0:100</t>
+  </si>
+  <si>
+    <t>870001:101_0:101</t>
+  </si>
+  <si>
+    <t>880001:100_0:100</t>
+  </si>
+  <si>
+    <t>880001:101_0:101</t>
+  </si>
+  <si>
+    <t>890001:100_0:100</t>
+  </si>
+  <si>
+    <t>890001:101_0:101</t>
+  </si>
+  <si>
+    <t>900001:100_0:100</t>
+  </si>
+  <si>
+    <t>900001:101_0:101</t>
+  </si>
+  <si>
+    <t>910001:100_0:100</t>
+  </si>
+  <si>
+    <t>910001:101_0:101</t>
+  </si>
+  <si>
+    <t>920001:100_0:100</t>
+  </si>
+  <si>
+    <t>920001:101_0:101</t>
+  </si>
+  <si>
+    <t>930001:100_0:100</t>
+  </si>
+  <si>
+    <t>930001:101_0:101</t>
+  </si>
+  <si>
+    <t>940001:100_0:100</t>
+  </si>
+  <si>
+    <t>940001:101_0:101</t>
+  </si>
+  <si>
+    <t>950001:100_0:100</t>
+  </si>
+  <si>
+    <t>950001:101_0:101</t>
+  </si>
+  <si>
+    <t>960001:100_0:100</t>
+  </si>
+  <si>
+    <t>960001:101_0:101</t>
+  </si>
+  <si>
+    <t>970001:100_0:100</t>
+  </si>
+  <si>
+    <t>970001:101_0:101</t>
+  </si>
+  <si>
+    <t>980001:100_0:100</t>
+  </si>
+  <si>
+    <t>980001:101_0:101</t>
+  </si>
+  <si>
+    <t>990001:100_0:100</t>
+  </si>
+  <si>
+    <t>990001:101_0:101</t>
+  </si>
+  <si>
+    <t>1000001:100_0:100</t>
+  </si>
+  <si>
+    <t>1000001:101_0:101</t>
+  </si>
+  <si>
+    <t>1010001:100_0:100</t>
+  </si>
+  <si>
+    <t>1010001:101_0:101</t>
+  </si>
+  <si>
+    <t>1020001:100_0:100</t>
+  </si>
+  <si>
+    <t>1020001:101_0:101</t>
+  </si>
+  <si>
+    <t>1030001:100_0:100</t>
+  </si>
+  <si>
+    <t>1030001:101_0:101</t>
+  </si>
+  <si>
+    <t>1040001:100_0:100</t>
+  </si>
+  <si>
+    <t>1040001:101_0:101</t>
+  </si>
+  <si>
+    <t>1050001:100_0:100</t>
+  </si>
+  <si>
+    <t>1050001:101_0:101</t>
+  </si>
+  <si>
+    <t>1060001:100_0:100</t>
+  </si>
+  <si>
+    <t>1060001:101_0:101</t>
+  </si>
+  <si>
+    <t>1070001:100_0:100</t>
+  </si>
+  <si>
+    <t>1070001:101_0:101</t>
+  </si>
+  <si>
+    <t>1080001:100_0:100</t>
+  </si>
+  <si>
+    <t>1080001:101_0:101</t>
+  </si>
+  <si>
+    <t>1090001:100_0:100</t>
+  </si>
+  <si>
+    <t>1090001:101_0:101</t>
+  </si>
+  <si>
+    <t>1100001:100_0:100</t>
+  </si>
+  <si>
+    <t>1100001:101_0:101</t>
+  </si>
+  <si>
+    <t>1110001:100_0:100</t>
+  </si>
+  <si>
+    <t>1110001:101_0:101</t>
+  </si>
+  <si>
+    <t>1120001:100_0:100</t>
+  </si>
+  <si>
+    <t>1120001:101_0:101</t>
+  </si>
+  <si>
+    <t>1130001:100_0:100</t>
+  </si>
+  <si>
+    <t>1130001:101_0:101</t>
+  </si>
+  <si>
+    <t>1140001:100_0:100</t>
+  </si>
+  <si>
+    <t>1140001:101_0:101</t>
+  </si>
+  <si>
+    <t>1150001:100_0:100</t>
+  </si>
+  <si>
+    <t>1150001:101_0:101</t>
+  </si>
+  <si>
+    <t>1160001:100_0:100</t>
+  </si>
+  <si>
+    <t>1160001:101_0:101</t>
+  </si>
+  <si>
+    <t>1170001:100_0:100</t>
+  </si>
+  <si>
+    <t>1170001:101_0:101</t>
+  </si>
+  <si>
+    <t>1180001:100_0:100</t>
+  </si>
+  <si>
+    <t>1180001:101_0:101</t>
+  </si>
+  <si>
+    <t>1190001:100_0:100</t>
+  </si>
+  <si>
+    <t>1190001:101_0:101</t>
+  </si>
+  <si>
+    <t>1200001:100_0:100</t>
+  </si>
+  <si>
+    <t>1200001:101_0:101</t>
+  </si>
+  <si>
+    <t>1210001:100_0:100</t>
+  </si>
+  <si>
+    <t>1210001:101_0:101</t>
+  </si>
+  <si>
+    <t>1220001:100_0:100</t>
+  </si>
+  <si>
+    <t>1220001:101_0:101</t>
+  </si>
+  <si>
+    <t>1230001:100_0:100</t>
+  </si>
+  <si>
+    <t>1230001:101_0:101</t>
+  </si>
+  <si>
+    <t>1240001:100_0:100</t>
+  </si>
+  <si>
+    <t>1240001:101_0:101</t>
+  </si>
+  <si>
+    <t>1250001:100_0:100</t>
+  </si>
+  <si>
+    <t>1250001:101_0:101</t>
+  </si>
+  <si>
+    <t>1260001:100_0:100</t>
+  </si>
+  <si>
+    <t>1260001:101_0:101</t>
+  </si>
+  <si>
+    <t>1270001:100_0:100</t>
+  </si>
+  <si>
+    <t>1270001:101_0:101</t>
+  </si>
+  <si>
+    <t>1280001:100_0:100</t>
+  </si>
+  <si>
+    <t>1280001:101_0:101</t>
+  </si>
+  <si>
+    <t>1290001:100_0:100</t>
+  </si>
+  <si>
+    <t>1290001:101_0:101</t>
+  </si>
+  <si>
+    <t>1300001:100_0:100</t>
+  </si>
+  <si>
+    <t>1300001:101_0:101</t>
+  </si>
+  <si>
+    <t>1310001:100_0:100</t>
+  </si>
+  <si>
+    <t>1310001:101_0:101</t>
+  </si>
+  <si>
+    <t>1320001:100_0:100</t>
+  </si>
+  <si>
+    <t>1320001:101_0:101</t>
+  </si>
+  <si>
+    <t>1330001:100_0:100</t>
+  </si>
+  <si>
+    <t>1330001:101_0:101</t>
+  </si>
+  <si>
+    <t>1340001:100_0:100</t>
+  </si>
+  <si>
+    <t>1340001:101_0:101</t>
+  </si>
+  <si>
+    <t>1350001:100_0:100</t>
+  </si>
+  <si>
+    <t>1350001:101_0:101</t>
+  </si>
+  <si>
+    <t>1360001:100_0:100</t>
+  </si>
+  <si>
+    <t>1360001:101_0:101</t>
+  </si>
+  <si>
+    <t>1370001:100_0:100</t>
+  </si>
+  <si>
+    <t>1370001:101_0:101</t>
+  </si>
+  <si>
+    <t>1380001:100_0:100</t>
+  </si>
+  <si>
+    <t>1380001:101_0:101</t>
+  </si>
+  <si>
+    <t>1390001:100_0:100</t>
+  </si>
+  <si>
+    <t>1390001:101_0:101</t>
+  </si>
+  <si>
+    <t>1400001:100_0:100</t>
+  </si>
+  <si>
+    <t>1400001:101_0:101</t>
+  </si>
+  <si>
+    <t>1410001:100_0:100</t>
+  </si>
+  <si>
+    <t>1410001:101_0:101</t>
+  </si>
+  <si>
+    <t>1420001:100_0:100</t>
+  </si>
+  <si>
+    <t>1420001:101_0:101</t>
+  </si>
+  <si>
+    <t>1430001:100_0:100</t>
+  </si>
+  <si>
+    <t>1430001:101_0:101</t>
+  </si>
+  <si>
+    <t>1440001:100_0:100</t>
+  </si>
+  <si>
+    <t>1440001:101_0:101</t>
+  </si>
+  <si>
+    <t>1450001:100_0:100</t>
+  </si>
+  <si>
+    <t>1450001:101_0:101</t>
+  </si>
+  <si>
+    <t>1460001:100_0:100</t>
+  </si>
+  <si>
+    <t>1460001:101_0:101</t>
+  </si>
+  <si>
+    <t>1470001:100_0:100</t>
+  </si>
+  <si>
+    <t>1470001:101_0:101</t>
+  </si>
+  <si>
+    <t>1480001:100_0:100</t>
+  </si>
+  <si>
+    <t>1480001:101_0:101</t>
+  </si>
+  <si>
+    <t>1490001:100_0:100</t>
+  </si>
+  <si>
+    <t>1490001:101_0:101</t>
+  </si>
+  <si>
+    <t>1500001:100_0:100</t>
+  </si>
+  <si>
+    <t>1500001:101_0:101</t>
+  </si>
+  <si>
+    <t>1510001:100_0:100</t>
+  </si>
+  <si>
+    <t>1510001:101_0:101</t>
+  </si>
+  <si>
+    <t>1520001:100_0:100</t>
+  </si>
+  <si>
+    <t>1520001:101_0:101</t>
+  </si>
+  <si>
+    <t>1530001:100_0:100</t>
+  </si>
+  <si>
+    <t>1530001:101_0:101</t>
+  </si>
+  <si>
+    <t>1540001:100_0:100</t>
+  </si>
+  <si>
+    <t>1540001:101_0:101</t>
+  </si>
+  <si>
+    <t>1550001:100_0:100</t>
+  </si>
+  <si>
+    <t>1550001:101_0:101</t>
+  </si>
+  <si>
+    <t>1560001:100_0:100</t>
+  </si>
+  <si>
+    <t>1560001:101_0:101</t>
+  </si>
+  <si>
+    <t>1570001:100_0:100</t>
+  </si>
+  <si>
+    <t>1570001:101_0:101</t>
+  </si>
+  <si>
+    <t>1580001:100_0:100</t>
+  </si>
+  <si>
+    <t>1580001:101_0:101</t>
+  </si>
+  <si>
+    <t>1590001:100_0:100</t>
+  </si>
+  <si>
+    <t>1590001:101_0:101</t>
+  </si>
+  <si>
+    <t>1600001:100_0:100</t>
+  </si>
+  <si>
+    <t>1600001:101_0:101</t>
+  </si>
+  <si>
+    <t>10001:100_0:100</t>
+  </si>
+  <si>
+    <t>10001:101_0:101</t>
+  </si>
+  <si>
+    <t>20001:100_0:100</t>
+  </si>
+  <si>
+    <t>20001:101_0:101</t>
+  </si>
+  <si>
+    <t>30001:100_0:100</t>
+  </si>
+  <si>
+    <t>30001:101_0:101</t>
+  </si>
+  <si>
+    <t>40001:100_0:100</t>
+  </si>
+  <si>
+    <t>40001:101_0:101</t>
+  </si>
+  <si>
+    <t>50001:100_0:100</t>
+  </si>
+  <si>
+    <t>50001:101_0:101</t>
+  </si>
+  <si>
+    <t>60001:100_0:100</t>
+  </si>
+  <si>
+    <t>60001:101_0:101</t>
+  </si>
+  <si>
+    <t>70001:100_0:100</t>
+  </si>
+  <si>
+    <t>70001:101_0:101</t>
+  </si>
+  <si>
+    <t>80001:100_0:100</t>
+  </si>
+  <si>
+    <t>80001:101_0:101</t>
+  </si>
+  <si>
+    <t>90001:100_0:100</t>
+  </si>
+  <si>
+    <t>90001:101_0:101</t>
+  </si>
+  <si>
+    <t>100001:100_0:100</t>
+  </si>
+  <si>
+    <t>100001:101_0:101</t>
   </si>
 </sst>
 </file>
@@ -2176,7 +2175,8 @@
     <col min="11" max="12" width="19.375" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="21.375" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="19.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="43.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="60.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="54.875" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="19.375" style="1" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="21.5" style="1" bestFit="1" customWidth="1"/>
     <col min="19" max="21" width="30.75" style="1" bestFit="1" customWidth="1"/>
@@ -2427,10 +2427,10 @@
         <v>150</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>251</v>
+        <v>554</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>252</v>
+        <v>555</v>
       </c>
       <c r="Q5" s="3" t="s">
         <v>231</v>
@@ -2492,10 +2492,10 @@
         <v>200</v>
       </c>
       <c r="O6" s="4" t="s">
-        <v>413</v>
+        <v>556</v>
       </c>
       <c r="P6" s="4" t="s">
-        <v>254</v>
+        <v>557</v>
       </c>
       <c r="Q6" s="3" t="s">
         <v>231</v>
@@ -2548,10 +2548,10 @@
         <v>300</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>414</v>
+        <v>558</v>
       </c>
       <c r="P7" s="4" t="s">
-        <v>255</v>
+        <v>559</v>
       </c>
       <c r="Q7" s="3" t="s">
         <v>231</v>
@@ -2604,10 +2604,10 @@
         <v>400</v>
       </c>
       <c r="O8" s="4" t="s">
-        <v>415</v>
+        <v>560</v>
       </c>
       <c r="P8" s="4" t="s">
-        <v>256</v>
+        <v>561</v>
       </c>
       <c r="Q8" s="3" t="s">
         <v>231</v>
@@ -2660,10 +2660,10 @@
         <v>500</v>
       </c>
       <c r="O9" s="4" t="s">
-        <v>416</v>
+        <v>562</v>
       </c>
       <c r="P9" s="4" t="s">
-        <v>257</v>
+        <v>563</v>
       </c>
       <c r="Q9" s="3" t="s">
         <v>231</v>
@@ -2716,10 +2716,10 @@
         <v>600</v>
       </c>
       <c r="O10" s="4" t="s">
-        <v>417</v>
+        <v>564</v>
       </c>
       <c r="P10" s="4" t="s">
-        <v>258</v>
+        <v>565</v>
       </c>
       <c r="Q10" s="3" t="s">
         <v>231</v>
@@ -2772,10 +2772,10 @@
         <v>100</v>
       </c>
       <c r="O11" s="4" t="s">
-        <v>418</v>
+        <v>566</v>
       </c>
       <c r="P11" s="4" t="s">
-        <v>259</v>
+        <v>567</v>
       </c>
       <c r="Q11" s="3" t="s">
         <v>231</v>
@@ -2828,10 +2828,10 @@
         <v>100</v>
       </c>
       <c r="O12" s="4" t="s">
-        <v>419</v>
+        <v>568</v>
       </c>
       <c r="P12" s="4" t="s">
-        <v>260</v>
+        <v>569</v>
       </c>
       <c r="Q12" s="3" t="s">
         <v>231</v>
@@ -2884,10 +2884,10 @@
         <v>100</v>
       </c>
       <c r="O13" s="4" t="s">
-        <v>420</v>
+        <v>570</v>
       </c>
       <c r="P13" s="4" t="s">
-        <v>261</v>
+        <v>571</v>
       </c>
       <c r="Q13" s="3" t="s">
         <v>231</v>
@@ -2940,10 +2940,10 @@
         <v>100</v>
       </c>
       <c r="O14" s="4" t="s">
-        <v>421</v>
+        <v>572</v>
       </c>
       <c r="P14" s="4" t="s">
-        <v>262</v>
+        <v>573</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>231</v>
@@ -2996,10 +2996,10 @@
         <v>100</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>571</v>
+        <v>254</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q15" s="3" t="s">
         <v>231</v>
@@ -3008,13 +3008,13 @@
         <v>0</v>
       </c>
       <c r="S15" s="1" t="s">
-        <v>412</v>
+        <v>251</v>
       </c>
       <c r="T15" s="1" t="s">
-        <v>572</v>
+        <v>252</v>
       </c>
       <c r="U15" s="1" t="s">
-        <v>573</v>
+        <v>253</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.15">
@@ -3061,10 +3061,10 @@
         <v>100</v>
       </c>
       <c r="O16" s="4" t="s">
-        <v>422</v>
+        <v>256</v>
       </c>
       <c r="P16" s="4" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="Q16" s="3" t="s">
         <v>231</v>
@@ -3117,10 +3117,10 @@
         <v>100</v>
       </c>
       <c r="O17" s="4" t="s">
-        <v>423</v>
+        <v>258</v>
       </c>
       <c r="P17" s="4" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="Q17" s="3" t="s">
         <v>231</v>
@@ -3173,10 +3173,10 @@
         <v>100</v>
       </c>
       <c r="O18" s="4" t="s">
-        <v>424</v>
+        <v>260</v>
       </c>
       <c r="P18" s="4" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="Q18" s="3" t="s">
         <v>231</v>
@@ -3229,10 +3229,10 @@
         <v>100</v>
       </c>
       <c r="O19" s="4" t="s">
-        <v>425</v>
+        <v>262</v>
       </c>
       <c r="P19" s="4" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="Q19" s="3" t="s">
         <v>231</v>
@@ -3285,10 +3285,10 @@
         <v>100</v>
       </c>
       <c r="O20" s="4" t="s">
-        <v>426</v>
+        <v>264</v>
       </c>
       <c r="P20" s="4" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="Q20" s="3" t="s">
         <v>231</v>
@@ -3341,10 +3341,10 @@
         <v>100</v>
       </c>
       <c r="O21" s="4" t="s">
-        <v>427</v>
+        <v>266</v>
       </c>
       <c r="P21" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q21" s="3" t="s">
         <v>231</v>
@@ -3397,7 +3397,7 @@
         <v>100</v>
       </c>
       <c r="O22" s="4" t="s">
-        <v>428</v>
+        <v>268</v>
       </c>
       <c r="P22" s="4" t="s">
         <v>269</v>
@@ -3453,10 +3453,10 @@
         <v>100</v>
       </c>
       <c r="O23" s="4" t="s">
-        <v>429</v>
+        <v>270</v>
       </c>
       <c r="P23" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q23" s="3" t="s">
         <v>231</v>
@@ -3509,10 +3509,10 @@
         <v>100</v>
       </c>
       <c r="O24" s="4" t="s">
-        <v>430</v>
+        <v>272</v>
       </c>
       <c r="P24" s="4" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q24" s="3" t="s">
         <v>231</v>
@@ -3565,10 +3565,10 @@
         <v>100</v>
       </c>
       <c r="O25" s="4" t="s">
-        <v>431</v>
+        <v>274</v>
       </c>
       <c r="P25" s="4" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q25" s="3" t="s">
         <v>231</v>
@@ -3621,10 +3621,10 @@
         <v>100</v>
       </c>
       <c r="O26" s="4" t="s">
-        <v>432</v>
+        <v>276</v>
       </c>
       <c r="P26" s="4" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="Q26" s="3" t="s">
         <v>231</v>
@@ -3677,10 +3677,10 @@
         <v>100</v>
       </c>
       <c r="O27" s="4" t="s">
-        <v>433</v>
+        <v>278</v>
       </c>
       <c r="P27" s="4" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="Q27" s="3" t="s">
         <v>231</v>
@@ -3733,10 +3733,10 @@
         <v>100</v>
       </c>
       <c r="O28" s="4" t="s">
-        <v>434</v>
+        <v>280</v>
       </c>
       <c r="P28" s="4" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="Q28" s="3" t="s">
         <v>231</v>
@@ -3789,10 +3789,10 @@
         <v>100</v>
       </c>
       <c r="O29" s="4" t="s">
-        <v>435</v>
+        <v>282</v>
       </c>
       <c r="P29" s="4" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="Q29" s="3" t="s">
         <v>231</v>
@@ -3845,10 +3845,10 @@
         <v>100</v>
       </c>
       <c r="O30" s="4" t="s">
-        <v>436</v>
+        <v>284</v>
       </c>
       <c r="P30" s="4" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="Q30" s="3" t="s">
         <v>231</v>
@@ -3901,10 +3901,10 @@
         <v>100</v>
       </c>
       <c r="O31" s="4" t="s">
-        <v>437</v>
+        <v>286</v>
       </c>
       <c r="P31" s="4" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="Q31" s="3" t="s">
         <v>231</v>
@@ -3957,10 +3957,10 @@
         <v>100</v>
       </c>
       <c r="O32" s="4" t="s">
-        <v>438</v>
+        <v>288</v>
       </c>
       <c r="P32" s="4" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="Q32" s="3" t="s">
         <v>231</v>
@@ -4013,10 +4013,10 @@
         <v>100</v>
       </c>
       <c r="O33" s="4" t="s">
-        <v>439</v>
+        <v>290</v>
       </c>
       <c r="P33" s="4" t="s">
-        <v>280</v>
+        <v>291</v>
       </c>
       <c r="Q33" s="3" t="s">
         <v>231</v>
@@ -4069,10 +4069,10 @@
         <v>100</v>
       </c>
       <c r="O34" s="4" t="s">
-        <v>440</v>
+        <v>292</v>
       </c>
       <c r="P34" s="4" t="s">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="Q34" s="3" t="s">
         <v>231</v>
@@ -4125,10 +4125,10 @@
         <v>100</v>
       </c>
       <c r="O35" s="4" t="s">
-        <v>441</v>
+        <v>294</v>
       </c>
       <c r="P35" s="4" t="s">
-        <v>282</v>
+        <v>295</v>
       </c>
       <c r="Q35" s="3" t="s">
         <v>231</v>
@@ -4181,10 +4181,10 @@
         <v>100</v>
       </c>
       <c r="O36" s="4" t="s">
-        <v>442</v>
+        <v>296</v>
       </c>
       <c r="P36" s="4" t="s">
-        <v>283</v>
+        <v>297</v>
       </c>
       <c r="Q36" s="3" t="s">
         <v>231</v>
@@ -4237,10 +4237,10 @@
         <v>100</v>
       </c>
       <c r="O37" s="4" t="s">
-        <v>443</v>
+        <v>298</v>
       </c>
       <c r="P37" s="4" t="s">
-        <v>284</v>
+        <v>299</v>
       </c>
       <c r="Q37" s="3" t="s">
         <v>231</v>
@@ -4293,10 +4293,10 @@
         <v>100</v>
       </c>
       <c r="O38" s="4" t="s">
-        <v>444</v>
+        <v>300</v>
       </c>
       <c r="P38" s="4" t="s">
-        <v>285</v>
+        <v>301</v>
       </c>
       <c r="Q38" s="3" t="s">
         <v>231</v>
@@ -4349,10 +4349,10 @@
         <v>100</v>
       </c>
       <c r="O39" s="4" t="s">
-        <v>445</v>
+        <v>302</v>
       </c>
       <c r="P39" s="4" t="s">
-        <v>286</v>
+        <v>303</v>
       </c>
       <c r="Q39" s="3" t="s">
         <v>231</v>
@@ -4405,10 +4405,10 @@
         <v>100</v>
       </c>
       <c r="O40" s="4" t="s">
-        <v>446</v>
+        <v>304</v>
       </c>
       <c r="P40" s="4" t="s">
-        <v>287</v>
+        <v>305</v>
       </c>
       <c r="Q40" s="3" t="s">
         <v>231</v>
@@ -4461,10 +4461,10 @@
         <v>100</v>
       </c>
       <c r="O41" s="4" t="s">
-        <v>447</v>
+        <v>306</v>
       </c>
       <c r="P41" s="4" t="s">
-        <v>288</v>
+        <v>307</v>
       </c>
       <c r="Q41" s="3" t="s">
         <v>231</v>
@@ -4517,10 +4517,10 @@
         <v>100</v>
       </c>
       <c r="O42" s="4" t="s">
-        <v>448</v>
+        <v>308</v>
       </c>
       <c r="P42" s="4" t="s">
-        <v>289</v>
+        <v>309</v>
       </c>
       <c r="Q42" s="3" t="s">
         <v>231</v>
@@ -4573,10 +4573,10 @@
         <v>100</v>
       </c>
       <c r="O43" s="4" t="s">
-        <v>449</v>
+        <v>310</v>
       </c>
       <c r="P43" s="4" t="s">
-        <v>290</v>
+        <v>311</v>
       </c>
       <c r="Q43" s="3" t="s">
         <v>231</v>
@@ -4629,10 +4629,10 @@
         <v>100</v>
       </c>
       <c r="O44" s="4" t="s">
-        <v>450</v>
+        <v>312</v>
       </c>
       <c r="P44" s="4" t="s">
-        <v>291</v>
+        <v>313</v>
       </c>
       <c r="Q44" s="3" t="s">
         <v>231</v>
@@ -4685,10 +4685,10 @@
         <v>100</v>
       </c>
       <c r="O45" s="4" t="s">
-        <v>451</v>
+        <v>314</v>
       </c>
       <c r="P45" s="4" t="s">
-        <v>292</v>
+        <v>315</v>
       </c>
       <c r="Q45" s="3" t="s">
         <v>231</v>
@@ -4741,10 +4741,10 @@
         <v>100</v>
       </c>
       <c r="O46" s="4" t="s">
-        <v>452</v>
+        <v>316</v>
       </c>
       <c r="P46" s="4" t="s">
-        <v>293</v>
+        <v>317</v>
       </c>
       <c r="Q46" s="3" t="s">
         <v>231</v>
@@ -4797,10 +4797,10 @@
         <v>100</v>
       </c>
       <c r="O47" s="4" t="s">
-        <v>453</v>
+        <v>318</v>
       </c>
       <c r="P47" s="4" t="s">
-        <v>294</v>
+        <v>319</v>
       </c>
       <c r="Q47" s="3" t="s">
         <v>231</v>
@@ -4853,10 +4853,10 @@
         <v>100</v>
       </c>
       <c r="O48" s="4" t="s">
-        <v>454</v>
+        <v>320</v>
       </c>
       <c r="P48" s="4" t="s">
-        <v>295</v>
+        <v>321</v>
       </c>
       <c r="Q48" s="3" t="s">
         <v>231</v>
@@ -4909,10 +4909,10 @@
         <v>100</v>
       </c>
       <c r="O49" s="4" t="s">
-        <v>455</v>
+        <v>322</v>
       </c>
       <c r="P49" s="4" t="s">
-        <v>296</v>
+        <v>323</v>
       </c>
       <c r="Q49" s="3" t="s">
         <v>231</v>
@@ -4965,10 +4965,10 @@
         <v>100</v>
       </c>
       <c r="O50" s="4" t="s">
-        <v>456</v>
+        <v>324</v>
       </c>
       <c r="P50" s="4" t="s">
-        <v>297</v>
+        <v>325</v>
       </c>
       <c r="Q50" s="3" t="s">
         <v>231</v>
@@ -5021,10 +5021,10 @@
         <v>100</v>
       </c>
       <c r="O51" s="4" t="s">
-        <v>457</v>
+        <v>326</v>
       </c>
       <c r="P51" s="4" t="s">
-        <v>298</v>
+        <v>327</v>
       </c>
       <c r="Q51" s="3" t="s">
         <v>231</v>
@@ -5077,10 +5077,10 @@
         <v>100</v>
       </c>
       <c r="O52" s="4" t="s">
-        <v>458</v>
+        <v>328</v>
       </c>
       <c r="P52" s="4" t="s">
-        <v>299</v>
+        <v>329</v>
       </c>
       <c r="Q52" s="3" t="s">
         <v>231</v>
@@ -5133,10 +5133,10 @@
         <v>100</v>
       </c>
       <c r="O53" s="4" t="s">
-        <v>459</v>
+        <v>330</v>
       </c>
       <c r="P53" s="4" t="s">
-        <v>300</v>
+        <v>331</v>
       </c>
       <c r="Q53" s="3" t="s">
         <v>231</v>
@@ -5189,10 +5189,10 @@
         <v>100</v>
       </c>
       <c r="O54" s="4" t="s">
-        <v>460</v>
+        <v>332</v>
       </c>
       <c r="P54" s="4" t="s">
-        <v>301</v>
+        <v>333</v>
       </c>
       <c r="Q54" s="3" t="s">
         <v>231</v>
@@ -5245,10 +5245,10 @@
         <v>100</v>
       </c>
       <c r="O55" s="4" t="s">
-        <v>461</v>
+        <v>334</v>
       </c>
       <c r="P55" s="4" t="s">
-        <v>302</v>
+        <v>335</v>
       </c>
       <c r="Q55" s="3" t="s">
         <v>231</v>
@@ -5301,10 +5301,10 @@
         <v>100</v>
       </c>
       <c r="O56" s="4" t="s">
-        <v>462</v>
+        <v>336</v>
       </c>
       <c r="P56" s="4" t="s">
-        <v>303</v>
+        <v>337</v>
       </c>
       <c r="Q56" s="3" t="s">
         <v>231</v>
@@ -5357,10 +5357,10 @@
         <v>100</v>
       </c>
       <c r="O57" s="4" t="s">
-        <v>463</v>
+        <v>338</v>
       </c>
       <c r="P57" s="4" t="s">
-        <v>304</v>
+        <v>339</v>
       </c>
       <c r="Q57" s="3" t="s">
         <v>231</v>
@@ -5413,10 +5413,10 @@
         <v>100</v>
       </c>
       <c r="O58" s="4" t="s">
-        <v>464</v>
+        <v>340</v>
       </c>
       <c r="P58" s="4" t="s">
-        <v>305</v>
+        <v>341</v>
       </c>
       <c r="Q58" s="3" t="s">
         <v>231</v>
@@ -5469,10 +5469,10 @@
         <v>100</v>
       </c>
       <c r="O59" s="4" t="s">
-        <v>465</v>
+        <v>342</v>
       </c>
       <c r="P59" s="4" t="s">
-        <v>306</v>
+        <v>343</v>
       </c>
       <c r="Q59" s="3" t="s">
         <v>231</v>
@@ -5525,10 +5525,10 @@
         <v>100</v>
       </c>
       <c r="O60" s="4" t="s">
-        <v>466</v>
+        <v>344</v>
       </c>
       <c r="P60" s="4" t="s">
-        <v>307</v>
+        <v>345</v>
       </c>
       <c r="Q60" s="3" t="s">
         <v>231</v>
@@ -5581,10 +5581,10 @@
         <v>100</v>
       </c>
       <c r="O61" s="4" t="s">
-        <v>467</v>
+        <v>346</v>
       </c>
       <c r="P61" s="4" t="s">
-        <v>308</v>
+        <v>347</v>
       </c>
       <c r="Q61" s="3" t="s">
         <v>231</v>
@@ -5637,10 +5637,10 @@
         <v>100</v>
       </c>
       <c r="O62" s="4" t="s">
-        <v>468</v>
+        <v>348</v>
       </c>
       <c r="P62" s="4" t="s">
-        <v>309</v>
+        <v>349</v>
       </c>
       <c r="Q62" s="3" t="s">
         <v>231</v>
@@ -5693,10 +5693,10 @@
         <v>100</v>
       </c>
       <c r="O63" s="4" t="s">
-        <v>469</v>
+        <v>350</v>
       </c>
       <c r="P63" s="4" t="s">
-        <v>310</v>
+        <v>351</v>
       </c>
       <c r="Q63" s="3" t="s">
         <v>231</v>
@@ -5749,10 +5749,10 @@
         <v>100</v>
       </c>
       <c r="O64" s="4" t="s">
-        <v>470</v>
+        <v>352</v>
       </c>
       <c r="P64" s="4" t="s">
-        <v>311</v>
+        <v>353</v>
       </c>
       <c r="Q64" s="3" t="s">
         <v>231</v>
@@ -5805,10 +5805,10 @@
         <v>100</v>
       </c>
       <c r="O65" s="4" t="s">
-        <v>471</v>
+        <v>354</v>
       </c>
       <c r="P65" s="4" t="s">
-        <v>312</v>
+        <v>355</v>
       </c>
       <c r="Q65" s="3" t="s">
         <v>231</v>
@@ -5861,10 +5861,10 @@
         <v>100</v>
       </c>
       <c r="O66" s="4" t="s">
-        <v>472</v>
+        <v>356</v>
       </c>
       <c r="P66" s="4" t="s">
-        <v>313</v>
+        <v>357</v>
       </c>
       <c r="Q66" s="3" t="s">
         <v>231</v>
@@ -5917,10 +5917,10 @@
         <v>100</v>
       </c>
       <c r="O67" s="4" t="s">
-        <v>473</v>
+        <v>358</v>
       </c>
       <c r="P67" s="4" t="s">
-        <v>314</v>
+        <v>359</v>
       </c>
       <c r="Q67" s="3" t="s">
         <v>231</v>
@@ -5973,10 +5973,10 @@
         <v>100</v>
       </c>
       <c r="O68" s="4" t="s">
-        <v>474</v>
+        <v>360</v>
       </c>
       <c r="P68" s="4" t="s">
-        <v>315</v>
+        <v>361</v>
       </c>
       <c r="Q68" s="3" t="s">
         <v>231</v>
@@ -6029,10 +6029,10 @@
         <v>100</v>
       </c>
       <c r="O69" s="4" t="s">
-        <v>475</v>
+        <v>362</v>
       </c>
       <c r="P69" s="4" t="s">
-        <v>316</v>
+        <v>363</v>
       </c>
       <c r="Q69" s="3" t="s">
         <v>231</v>
@@ -6085,10 +6085,10 @@
         <v>100</v>
       </c>
       <c r="O70" s="4" t="s">
-        <v>476</v>
+        <v>364</v>
       </c>
       <c r="P70" s="4" t="s">
-        <v>317</v>
+        <v>365</v>
       </c>
       <c r="Q70" s="3" t="s">
         <v>231</v>
@@ -6141,10 +6141,10 @@
         <v>100</v>
       </c>
       <c r="O71" s="4" t="s">
-        <v>477</v>
+        <v>366</v>
       </c>
       <c r="P71" s="4" t="s">
-        <v>318</v>
+        <v>367</v>
       </c>
       <c r="Q71" s="3" t="s">
         <v>231</v>
@@ -6197,10 +6197,10 @@
         <v>100</v>
       </c>
       <c r="O72" s="4" t="s">
-        <v>478</v>
+        <v>368</v>
       </c>
       <c r="P72" s="4" t="s">
-        <v>319</v>
+        <v>369</v>
       </c>
       <c r="Q72" s="3" t="s">
         <v>231</v>
@@ -6253,10 +6253,10 @@
         <v>100</v>
       </c>
       <c r="O73" s="4" t="s">
-        <v>479</v>
+        <v>370</v>
       </c>
       <c r="P73" s="4" t="s">
-        <v>320</v>
+        <v>371</v>
       </c>
       <c r="Q73" s="3" t="s">
         <v>231</v>
@@ -6309,10 +6309,10 @@
         <v>100</v>
       </c>
       <c r="O74" s="4" t="s">
-        <v>480</v>
+        <v>372</v>
       </c>
       <c r="P74" s="4" t="s">
-        <v>321</v>
+        <v>373</v>
       </c>
       <c r="Q74" s="3" t="s">
         <v>231</v>
@@ -6365,10 +6365,10 @@
         <v>100</v>
       </c>
       <c r="O75" s="4" t="s">
-        <v>481</v>
+        <v>374</v>
       </c>
       <c r="P75" s="4" t="s">
-        <v>322</v>
+        <v>375</v>
       </c>
       <c r="Q75" s="3" t="s">
         <v>231</v>
@@ -6421,10 +6421,10 @@
         <v>100</v>
       </c>
       <c r="O76" s="4" t="s">
-        <v>482</v>
+        <v>376</v>
       </c>
       <c r="P76" s="4" t="s">
-        <v>323</v>
+        <v>377</v>
       </c>
       <c r="Q76" s="3" t="s">
         <v>231</v>
@@ -6477,10 +6477,10 @@
         <v>100</v>
       </c>
       <c r="O77" s="4" t="s">
-        <v>483</v>
+        <v>378</v>
       </c>
       <c r="P77" s="4" t="s">
-        <v>324</v>
+        <v>379</v>
       </c>
       <c r="Q77" s="3" t="s">
         <v>231</v>
@@ -6533,10 +6533,10 @@
         <v>100</v>
       </c>
       <c r="O78" s="4" t="s">
-        <v>484</v>
+        <v>380</v>
       </c>
       <c r="P78" s="4" t="s">
-        <v>325</v>
+        <v>381</v>
       </c>
       <c r="Q78" s="3" t="s">
         <v>231</v>
@@ -6589,10 +6589,10 @@
         <v>100</v>
       </c>
       <c r="O79" s="4" t="s">
-        <v>485</v>
+        <v>382</v>
       </c>
       <c r="P79" s="4" t="s">
-        <v>326</v>
+        <v>383</v>
       </c>
       <c r="Q79" s="3" t="s">
         <v>231</v>
@@ -6645,10 +6645,10 @@
         <v>100</v>
       </c>
       <c r="O80" s="4" t="s">
-        <v>486</v>
+        <v>384</v>
       </c>
       <c r="P80" s="4" t="s">
-        <v>327</v>
+        <v>385</v>
       </c>
       <c r="Q80" s="3" t="s">
         <v>231</v>
@@ -6701,10 +6701,10 @@
         <v>100</v>
       </c>
       <c r="O81" s="4" t="s">
-        <v>487</v>
+        <v>386</v>
       </c>
       <c r="P81" s="4" t="s">
-        <v>328</v>
+        <v>387</v>
       </c>
       <c r="Q81" s="3" t="s">
         <v>231</v>
@@ -6757,10 +6757,10 @@
         <v>100</v>
       </c>
       <c r="O82" s="4" t="s">
-        <v>488</v>
+        <v>388</v>
       </c>
       <c r="P82" s="4" t="s">
-        <v>329</v>
+        <v>389</v>
       </c>
       <c r="Q82" s="3" t="s">
         <v>231</v>
@@ -6813,10 +6813,10 @@
         <v>100</v>
       </c>
       <c r="O83" s="4" t="s">
-        <v>489</v>
+        <v>390</v>
       </c>
       <c r="P83" s="4" t="s">
-        <v>330</v>
+        <v>391</v>
       </c>
       <c r="Q83" s="3" t="s">
         <v>231</v>
@@ -6869,10 +6869,10 @@
         <v>100</v>
       </c>
       <c r="O84" s="4" t="s">
-        <v>490</v>
+        <v>392</v>
       </c>
       <c r="P84" s="4" t="s">
-        <v>331</v>
+        <v>393</v>
       </c>
       <c r="Q84" s="3" t="s">
         <v>231</v>
@@ -6925,10 +6925,10 @@
         <v>100</v>
       </c>
       <c r="O85" s="4" t="s">
-        <v>491</v>
+        <v>394</v>
       </c>
       <c r="P85" s="4" t="s">
-        <v>332</v>
+        <v>395</v>
       </c>
       <c r="Q85" s="3" t="s">
         <v>231</v>
@@ -6981,10 +6981,10 @@
         <v>100</v>
       </c>
       <c r="O86" s="4" t="s">
-        <v>492</v>
+        <v>396</v>
       </c>
       <c r="P86" s="4" t="s">
-        <v>333</v>
+        <v>397</v>
       </c>
       <c r="Q86" s="3" t="s">
         <v>231</v>
@@ -7037,10 +7037,10 @@
         <v>100</v>
       </c>
       <c r="O87" s="4" t="s">
-        <v>493</v>
+        <v>398</v>
       </c>
       <c r="P87" s="4" t="s">
-        <v>334</v>
+        <v>399</v>
       </c>
       <c r="Q87" s="3" t="s">
         <v>231</v>
@@ -7093,10 +7093,10 @@
         <v>100</v>
       </c>
       <c r="O88" s="4" t="s">
-        <v>494</v>
+        <v>400</v>
       </c>
       <c r="P88" s="4" t="s">
-        <v>335</v>
+        <v>401</v>
       </c>
       <c r="Q88" s="3" t="s">
         <v>231</v>
@@ -7149,10 +7149,10 @@
         <v>100</v>
       </c>
       <c r="O89" s="4" t="s">
-        <v>495</v>
+        <v>402</v>
       </c>
       <c r="P89" s="4" t="s">
-        <v>336</v>
+        <v>403</v>
       </c>
       <c r="Q89" s="3" t="s">
         <v>231</v>
@@ -7205,10 +7205,10 @@
         <v>100</v>
       </c>
       <c r="O90" s="4" t="s">
-        <v>496</v>
+        <v>404</v>
       </c>
       <c r="P90" s="4" t="s">
-        <v>337</v>
+        <v>405</v>
       </c>
       <c r="Q90" s="3" t="s">
         <v>231</v>
@@ -7261,10 +7261,10 @@
         <v>100</v>
       </c>
       <c r="O91" s="4" t="s">
-        <v>497</v>
+        <v>406</v>
       </c>
       <c r="P91" s="4" t="s">
-        <v>338</v>
+        <v>407</v>
       </c>
       <c r="Q91" s="3" t="s">
         <v>231</v>
@@ -7317,10 +7317,10 @@
         <v>100</v>
       </c>
       <c r="O92" s="4" t="s">
-        <v>498</v>
+        <v>408</v>
       </c>
       <c r="P92" s="4" t="s">
-        <v>339</v>
+        <v>409</v>
       </c>
       <c r="Q92" s="3" t="s">
         <v>231</v>
@@ -7373,10 +7373,10 @@
         <v>100</v>
       </c>
       <c r="O93" s="4" t="s">
-        <v>499</v>
+        <v>410</v>
       </c>
       <c r="P93" s="4" t="s">
-        <v>340</v>
+        <v>411</v>
       </c>
       <c r="Q93" s="3" t="s">
         <v>231</v>
@@ -7429,10 +7429,10 @@
         <v>100</v>
       </c>
       <c r="O94" s="4" t="s">
-        <v>500</v>
+        <v>412</v>
       </c>
       <c r="P94" s="4" t="s">
-        <v>341</v>
+        <v>413</v>
       </c>
       <c r="Q94" s="3" t="s">
         <v>231</v>
@@ -7485,10 +7485,10 @@
         <v>100</v>
       </c>
       <c r="O95" s="4" t="s">
-        <v>501</v>
+        <v>414</v>
       </c>
       <c r="P95" s="4" t="s">
-        <v>342</v>
+        <v>415</v>
       </c>
       <c r="Q95" s="3" t="s">
         <v>231</v>
@@ -7541,10 +7541,10 @@
         <v>100</v>
       </c>
       <c r="O96" s="4" t="s">
-        <v>502</v>
+        <v>416</v>
       </c>
       <c r="P96" s="4" t="s">
-        <v>343</v>
+        <v>417</v>
       </c>
       <c r="Q96" s="3" t="s">
         <v>231</v>
@@ -7597,10 +7597,10 @@
         <v>100</v>
       </c>
       <c r="O97" s="4" t="s">
-        <v>503</v>
+        <v>418</v>
       </c>
       <c r="P97" s="4" t="s">
-        <v>344</v>
+        <v>419</v>
       </c>
       <c r="Q97" s="3" t="s">
         <v>231</v>
@@ -7653,10 +7653,10 @@
         <v>100</v>
       </c>
       <c r="O98" s="4" t="s">
-        <v>504</v>
+        <v>420</v>
       </c>
       <c r="P98" s="4" t="s">
-        <v>345</v>
+        <v>421</v>
       </c>
       <c r="Q98" s="3" t="s">
         <v>231</v>
@@ -7709,10 +7709,10 @@
         <v>100</v>
       </c>
       <c r="O99" s="4" t="s">
-        <v>505</v>
+        <v>422</v>
       </c>
       <c r="P99" s="4" t="s">
-        <v>346</v>
+        <v>423</v>
       </c>
       <c r="Q99" s="3" t="s">
         <v>231</v>
@@ -7765,10 +7765,10 @@
         <v>100</v>
       </c>
       <c r="O100" s="4" t="s">
-        <v>506</v>
+        <v>424</v>
       </c>
       <c r="P100" s="4" t="s">
-        <v>347</v>
+        <v>425</v>
       </c>
       <c r="Q100" s="3" t="s">
         <v>231</v>
@@ -7821,10 +7821,10 @@
         <v>100</v>
       </c>
       <c r="O101" s="4" t="s">
-        <v>507</v>
+        <v>426</v>
       </c>
       <c r="P101" s="4" t="s">
-        <v>348</v>
+        <v>427</v>
       </c>
       <c r="Q101" s="3" t="s">
         <v>231</v>
@@ -7877,10 +7877,10 @@
         <v>100</v>
       </c>
       <c r="O102" s="4" t="s">
-        <v>508</v>
+        <v>428</v>
       </c>
       <c r="P102" s="4" t="s">
-        <v>349</v>
+        <v>429</v>
       </c>
       <c r="Q102" s="3" t="s">
         <v>231</v>
@@ -7933,10 +7933,10 @@
         <v>100</v>
       </c>
       <c r="O103" s="4" t="s">
-        <v>509</v>
+        <v>430</v>
       </c>
       <c r="P103" s="4" t="s">
-        <v>350</v>
+        <v>431</v>
       </c>
       <c r="Q103" s="3" t="s">
         <v>231</v>
@@ -7989,10 +7989,10 @@
         <v>100</v>
       </c>
       <c r="O104" s="4" t="s">
-        <v>510</v>
+        <v>432</v>
       </c>
       <c r="P104" s="4" t="s">
-        <v>351</v>
+        <v>433</v>
       </c>
       <c r="Q104" s="3" t="s">
         <v>231</v>
@@ -8045,10 +8045,10 @@
         <v>100</v>
       </c>
       <c r="O105" s="4" t="s">
-        <v>511</v>
+        <v>434</v>
       </c>
       <c r="P105" s="4" t="s">
-        <v>352</v>
+        <v>435</v>
       </c>
       <c r="Q105" s="3" t="s">
         <v>231</v>
@@ -8101,10 +8101,10 @@
         <v>100</v>
       </c>
       <c r="O106" s="4" t="s">
-        <v>512</v>
+        <v>436</v>
       </c>
       <c r="P106" s="4" t="s">
-        <v>353</v>
+        <v>437</v>
       </c>
       <c r="Q106" s="3" t="s">
         <v>231</v>
@@ -8157,10 +8157,10 @@
         <v>100</v>
       </c>
       <c r="O107" s="4" t="s">
-        <v>513</v>
+        <v>438</v>
       </c>
       <c r="P107" s="4" t="s">
-        <v>354</v>
+        <v>439</v>
       </c>
       <c r="Q107" s="3" t="s">
         <v>231</v>
@@ -8213,10 +8213,10 @@
         <v>100</v>
       </c>
       <c r="O108" s="4" t="s">
-        <v>514</v>
+        <v>440</v>
       </c>
       <c r="P108" s="4" t="s">
-        <v>355</v>
+        <v>441</v>
       </c>
       <c r="Q108" s="3" t="s">
         <v>231</v>
@@ -8269,10 +8269,10 @@
         <v>100</v>
       </c>
       <c r="O109" s="4" t="s">
-        <v>515</v>
+        <v>442</v>
       </c>
       <c r="P109" s="4" t="s">
-        <v>356</v>
+        <v>443</v>
       </c>
       <c r="Q109" s="3" t="s">
         <v>231</v>
@@ -8325,10 +8325,10 @@
         <v>100</v>
       </c>
       <c r="O110" s="4" t="s">
-        <v>516</v>
+        <v>444</v>
       </c>
       <c r="P110" s="4" t="s">
-        <v>357</v>
+        <v>445</v>
       </c>
       <c r="Q110" s="3" t="s">
         <v>231</v>
@@ -8381,10 +8381,10 @@
         <v>100</v>
       </c>
       <c r="O111" s="4" t="s">
-        <v>517</v>
+        <v>446</v>
       </c>
       <c r="P111" s="4" t="s">
-        <v>358</v>
+        <v>447</v>
       </c>
       <c r="Q111" s="3" t="s">
         <v>231</v>
@@ -8437,10 +8437,10 @@
         <v>100</v>
       </c>
       <c r="O112" s="4" t="s">
-        <v>518</v>
+        <v>448</v>
       </c>
       <c r="P112" s="4" t="s">
-        <v>359</v>
+        <v>449</v>
       </c>
       <c r="Q112" s="3" t="s">
         <v>231</v>
@@ -8493,10 +8493,10 @@
         <v>100</v>
       </c>
       <c r="O113" s="4" t="s">
-        <v>519</v>
+        <v>450</v>
       </c>
       <c r="P113" s="4" t="s">
-        <v>360</v>
+        <v>451</v>
       </c>
       <c r="Q113" s="3" t="s">
         <v>231</v>
@@ -8549,10 +8549,10 @@
         <v>100</v>
       </c>
       <c r="O114" s="4" t="s">
-        <v>520</v>
+        <v>452</v>
       </c>
       <c r="P114" s="4" t="s">
-        <v>361</v>
+        <v>453</v>
       </c>
       <c r="Q114" s="3" t="s">
         <v>231</v>
@@ -8605,10 +8605,10 @@
         <v>100</v>
       </c>
       <c r="O115" s="4" t="s">
-        <v>521</v>
+        <v>454</v>
       </c>
       <c r="P115" s="4" t="s">
-        <v>362</v>
+        <v>455</v>
       </c>
       <c r="Q115" s="3" t="s">
         <v>231</v>
@@ -8661,10 +8661,10 @@
         <v>100</v>
       </c>
       <c r="O116" s="4" t="s">
-        <v>522</v>
+        <v>456</v>
       </c>
       <c r="P116" s="4" t="s">
-        <v>363</v>
+        <v>457</v>
       </c>
       <c r="Q116" s="3" t="s">
         <v>231</v>
@@ -8717,10 +8717,10 @@
         <v>100</v>
       </c>
       <c r="O117" s="4" t="s">
-        <v>523</v>
+        <v>458</v>
       </c>
       <c r="P117" s="4" t="s">
-        <v>364</v>
+        <v>459</v>
       </c>
       <c r="Q117" s="3" t="s">
         <v>231</v>
@@ -8773,10 +8773,10 @@
         <v>100</v>
       </c>
       <c r="O118" s="4" t="s">
-        <v>524</v>
+        <v>460</v>
       </c>
       <c r="P118" s="4" t="s">
-        <v>365</v>
+        <v>461</v>
       </c>
       <c r="Q118" s="3" t="s">
         <v>231</v>
@@ -8829,10 +8829,10 @@
         <v>100</v>
       </c>
       <c r="O119" s="4" t="s">
-        <v>525</v>
+        <v>462</v>
       </c>
       <c r="P119" s="4" t="s">
-        <v>366</v>
+        <v>463</v>
       </c>
       <c r="Q119" s="3" t="s">
         <v>231</v>
@@ -8885,10 +8885,10 @@
         <v>100</v>
       </c>
       <c r="O120" s="4" t="s">
-        <v>526</v>
+        <v>464</v>
       </c>
       <c r="P120" s="4" t="s">
-        <v>367</v>
+        <v>465</v>
       </c>
       <c r="Q120" s="3" t="s">
         <v>231</v>
@@ -8941,10 +8941,10 @@
         <v>100</v>
       </c>
       <c r="O121" s="4" t="s">
-        <v>527</v>
+        <v>466</v>
       </c>
       <c r="P121" s="4" t="s">
-        <v>368</v>
+        <v>467</v>
       </c>
       <c r="Q121" s="3" t="s">
         <v>231</v>
@@ -8997,10 +8997,10 @@
         <v>100</v>
       </c>
       <c r="O122" s="4" t="s">
-        <v>528</v>
+        <v>468</v>
       </c>
       <c r="P122" s="4" t="s">
-        <v>369</v>
+        <v>469</v>
       </c>
       <c r="Q122" s="3" t="s">
         <v>231</v>
@@ -9053,10 +9053,10 @@
         <v>100</v>
       </c>
       <c r="O123" s="4" t="s">
-        <v>529</v>
+        <v>470</v>
       </c>
       <c r="P123" s="4" t="s">
-        <v>370</v>
+        <v>471</v>
       </c>
       <c r="Q123" s="3" t="s">
         <v>231</v>
@@ -9109,10 +9109,10 @@
         <v>100</v>
       </c>
       <c r="O124" s="4" t="s">
-        <v>530</v>
+        <v>472</v>
       </c>
       <c r="P124" s="4" t="s">
-        <v>371</v>
+        <v>473</v>
       </c>
       <c r="Q124" s="3" t="s">
         <v>231</v>
@@ -9165,10 +9165,10 @@
         <v>100</v>
       </c>
       <c r="O125" s="4" t="s">
-        <v>531</v>
+        <v>474</v>
       </c>
       <c r="P125" s="4" t="s">
-        <v>372</v>
+        <v>475</v>
       </c>
       <c r="Q125" s="3" t="s">
         <v>231</v>
@@ -9221,10 +9221,10 @@
         <v>100</v>
       </c>
       <c r="O126" s="4" t="s">
-        <v>532</v>
+        <v>476</v>
       </c>
       <c r="P126" s="4" t="s">
-        <v>373</v>
+        <v>477</v>
       </c>
       <c r="Q126" s="3" t="s">
         <v>231</v>
@@ -9277,10 +9277,10 @@
         <v>100</v>
       </c>
       <c r="O127" s="4" t="s">
-        <v>533</v>
+        <v>478</v>
       </c>
       <c r="P127" s="4" t="s">
-        <v>374</v>
+        <v>479</v>
       </c>
       <c r="Q127" s="3" t="s">
         <v>231</v>
@@ -9333,10 +9333,10 @@
         <v>100</v>
       </c>
       <c r="O128" s="4" t="s">
-        <v>534</v>
+        <v>480</v>
       </c>
       <c r="P128" s="4" t="s">
-        <v>375</v>
+        <v>481</v>
       </c>
       <c r="Q128" s="3" t="s">
         <v>231</v>
@@ -9389,10 +9389,10 @@
         <v>100</v>
       </c>
       <c r="O129" s="4" t="s">
-        <v>535</v>
+        <v>482</v>
       </c>
       <c r="P129" s="4" t="s">
-        <v>376</v>
+        <v>483</v>
       </c>
       <c r="Q129" s="3" t="s">
         <v>231</v>
@@ -9445,10 +9445,10 @@
         <v>100</v>
       </c>
       <c r="O130" s="4" t="s">
-        <v>536</v>
+        <v>484</v>
       </c>
       <c r="P130" s="4" t="s">
-        <v>377</v>
+        <v>485</v>
       </c>
       <c r="Q130" s="3" t="s">
         <v>231</v>
@@ -9501,10 +9501,10 @@
         <v>100</v>
       </c>
       <c r="O131" s="4" t="s">
-        <v>537</v>
+        <v>486</v>
       </c>
       <c r="P131" s="4" t="s">
-        <v>378</v>
+        <v>487</v>
       </c>
       <c r="Q131" s="3" t="s">
         <v>231</v>
@@ -9557,10 +9557,10 @@
         <v>100</v>
       </c>
       <c r="O132" s="4" t="s">
-        <v>538</v>
+        <v>488</v>
       </c>
       <c r="P132" s="4" t="s">
-        <v>379</v>
+        <v>489</v>
       </c>
       <c r="Q132" s="3" t="s">
         <v>231</v>
@@ -9613,10 +9613,10 @@
         <v>100</v>
       </c>
       <c r="O133" s="4" t="s">
-        <v>539</v>
+        <v>490</v>
       </c>
       <c r="P133" s="4" t="s">
-        <v>380</v>
+        <v>491</v>
       </c>
       <c r="Q133" s="3" t="s">
         <v>231</v>
@@ -9669,10 +9669,10 @@
         <v>100</v>
       </c>
       <c r="O134" s="4" t="s">
-        <v>540</v>
+        <v>492</v>
       </c>
       <c r="P134" s="4" t="s">
-        <v>381</v>
+        <v>493</v>
       </c>
       <c r="Q134" s="3" t="s">
         <v>231</v>
@@ -9725,10 +9725,10 @@
         <v>100</v>
       </c>
       <c r="O135" s="4" t="s">
-        <v>541</v>
+        <v>494</v>
       </c>
       <c r="P135" s="4" t="s">
-        <v>382</v>
+        <v>495</v>
       </c>
       <c r="Q135" s="3" t="s">
         <v>231</v>
@@ -9781,10 +9781,10 @@
         <v>100</v>
       </c>
       <c r="O136" s="4" t="s">
-        <v>542</v>
+        <v>496</v>
       </c>
       <c r="P136" s="4" t="s">
-        <v>383</v>
+        <v>497</v>
       </c>
       <c r="Q136" s="3" t="s">
         <v>231</v>
@@ -9837,10 +9837,10 @@
         <v>100</v>
       </c>
       <c r="O137" s="4" t="s">
-        <v>543</v>
+        <v>498</v>
       </c>
       <c r="P137" s="4" t="s">
-        <v>384</v>
+        <v>499</v>
       </c>
       <c r="Q137" s="3" t="s">
         <v>231</v>
@@ -9893,10 +9893,10 @@
         <v>100</v>
       </c>
       <c r="O138" s="4" t="s">
-        <v>544</v>
+        <v>500</v>
       </c>
       <c r="P138" s="4" t="s">
-        <v>385</v>
+        <v>501</v>
       </c>
       <c r="Q138" s="3" t="s">
         <v>231</v>
@@ -9949,10 +9949,10 @@
         <v>100</v>
       </c>
       <c r="O139" s="4" t="s">
-        <v>545</v>
+        <v>502</v>
       </c>
       <c r="P139" s="4" t="s">
-        <v>386</v>
+        <v>503</v>
       </c>
       <c r="Q139" s="3" t="s">
         <v>231</v>
@@ -10005,10 +10005,10 @@
         <v>100</v>
       </c>
       <c r="O140" s="4" t="s">
-        <v>546</v>
+        <v>504</v>
       </c>
       <c r="P140" s="4" t="s">
-        <v>387</v>
+        <v>505</v>
       </c>
       <c r="Q140" s="3" t="s">
         <v>231</v>
@@ -10061,10 +10061,10 @@
         <v>100</v>
       </c>
       <c r="O141" s="4" t="s">
-        <v>547</v>
+        <v>506</v>
       </c>
       <c r="P141" s="4" t="s">
-        <v>388</v>
+        <v>507</v>
       </c>
       <c r="Q141" s="3" t="s">
         <v>231</v>
@@ -10117,10 +10117,10 @@
         <v>100</v>
       </c>
       <c r="O142" s="4" t="s">
-        <v>548</v>
+        <v>508</v>
       </c>
       <c r="P142" s="4" t="s">
-        <v>389</v>
+        <v>509</v>
       </c>
       <c r="Q142" s="3" t="s">
         <v>231</v>
@@ -10173,10 +10173,10 @@
         <v>100</v>
       </c>
       <c r="O143" s="4" t="s">
-        <v>549</v>
+        <v>510</v>
       </c>
       <c r="P143" s="4" t="s">
-        <v>390</v>
+        <v>511</v>
       </c>
       <c r="Q143" s="3" t="s">
         <v>231</v>
@@ -10229,10 +10229,10 @@
         <v>100</v>
       </c>
       <c r="O144" s="4" t="s">
-        <v>550</v>
+        <v>512</v>
       </c>
       <c r="P144" s="4" t="s">
-        <v>391</v>
+        <v>513</v>
       </c>
       <c r="Q144" s="3" t="s">
         <v>231</v>
@@ -10285,10 +10285,10 @@
         <v>100</v>
       </c>
       <c r="O145" s="4" t="s">
-        <v>551</v>
+        <v>514</v>
       </c>
       <c r="P145" s="4" t="s">
-        <v>392</v>
+        <v>515</v>
       </c>
       <c r="Q145" s="3" t="s">
         <v>231</v>
@@ -10341,10 +10341,10 @@
         <v>100</v>
       </c>
       <c r="O146" s="4" t="s">
-        <v>552</v>
+        <v>516</v>
       </c>
       <c r="P146" s="4" t="s">
-        <v>393</v>
+        <v>517</v>
       </c>
       <c r="Q146" s="3" t="s">
         <v>231</v>
@@ -10397,10 +10397,10 @@
         <v>100</v>
       </c>
       <c r="O147" s="4" t="s">
-        <v>553</v>
+        <v>518</v>
       </c>
       <c r="P147" s="4" t="s">
-        <v>394</v>
+        <v>519</v>
       </c>
       <c r="Q147" s="3" t="s">
         <v>231</v>
@@ -10453,10 +10453,10 @@
         <v>100</v>
       </c>
       <c r="O148" s="4" t="s">
-        <v>554</v>
+        <v>520</v>
       </c>
       <c r="P148" s="4" t="s">
-        <v>395</v>
+        <v>521</v>
       </c>
       <c r="Q148" s="3" t="s">
         <v>231</v>
@@ -10509,10 +10509,10 @@
         <v>100</v>
       </c>
       <c r="O149" s="4" t="s">
-        <v>555</v>
+        <v>522</v>
       </c>
       <c r="P149" s="4" t="s">
-        <v>396</v>
+        <v>523</v>
       </c>
       <c r="Q149" s="3" t="s">
         <v>231</v>
@@ -10565,10 +10565,10 @@
         <v>100</v>
       </c>
       <c r="O150" s="4" t="s">
-        <v>556</v>
+        <v>524</v>
       </c>
       <c r="P150" s="4" t="s">
-        <v>397</v>
+        <v>525</v>
       </c>
       <c r="Q150" s="3" t="s">
         <v>231</v>
@@ -10621,10 +10621,10 @@
         <v>100</v>
       </c>
       <c r="O151" s="4" t="s">
-        <v>557</v>
+        <v>526</v>
       </c>
       <c r="P151" s="4" t="s">
-        <v>398</v>
+        <v>527</v>
       </c>
       <c r="Q151" s="3" t="s">
         <v>231</v>
@@ -10677,10 +10677,10 @@
         <v>100</v>
       </c>
       <c r="O152" s="4" t="s">
-        <v>558</v>
+        <v>528</v>
       </c>
       <c r="P152" s="4" t="s">
-        <v>399</v>
+        <v>529</v>
       </c>
       <c r="Q152" s="3" t="s">
         <v>231</v>
@@ -10733,10 +10733,10 @@
         <v>100</v>
       </c>
       <c r="O153" s="4" t="s">
-        <v>559</v>
+        <v>530</v>
       </c>
       <c r="P153" s="4" t="s">
-        <v>400</v>
+        <v>531</v>
       </c>
       <c r="Q153" s="3" t="s">
         <v>231</v>
@@ -10789,10 +10789,10 @@
         <v>100</v>
       </c>
       <c r="O154" s="4" t="s">
-        <v>560</v>
+        <v>532</v>
       </c>
       <c r="P154" s="4" t="s">
-        <v>401</v>
+        <v>533</v>
       </c>
       <c r="Q154" s="3" t="s">
         <v>231</v>
@@ -10845,10 +10845,10 @@
         <v>100</v>
       </c>
       <c r="O155" s="4" t="s">
-        <v>561</v>
+        <v>534</v>
       </c>
       <c r="P155" s="4" t="s">
-        <v>402</v>
+        <v>535</v>
       </c>
       <c r="Q155" s="3" t="s">
         <v>231</v>
@@ -10901,10 +10901,10 @@
         <v>100</v>
       </c>
       <c r="O156" s="4" t="s">
-        <v>562</v>
+        <v>536</v>
       </c>
       <c r="P156" s="4" t="s">
-        <v>403</v>
+        <v>537</v>
       </c>
       <c r="Q156" s="3" t="s">
         <v>231</v>
@@ -10957,10 +10957,10 @@
         <v>100</v>
       </c>
       <c r="O157" s="4" t="s">
-        <v>563</v>
+        <v>538</v>
       </c>
       <c r="P157" s="4" t="s">
-        <v>404</v>
+        <v>539</v>
       </c>
       <c r="Q157" s="3" t="s">
         <v>231</v>
@@ -11013,10 +11013,10 @@
         <v>100</v>
       </c>
       <c r="O158" s="4" t="s">
-        <v>564</v>
+        <v>540</v>
       </c>
       <c r="P158" s="4" t="s">
-        <v>405</v>
+        <v>541</v>
       </c>
       <c r="Q158" s="3" t="s">
         <v>231</v>
@@ -11069,10 +11069,10 @@
         <v>100</v>
       </c>
       <c r="O159" s="4" t="s">
-        <v>565</v>
+        <v>542</v>
       </c>
       <c r="P159" s="4" t="s">
-        <v>406</v>
+        <v>543</v>
       </c>
       <c r="Q159" s="3" t="s">
         <v>231</v>
@@ -11125,10 +11125,10 @@
         <v>100</v>
       </c>
       <c r="O160" s="4" t="s">
-        <v>566</v>
+        <v>544</v>
       </c>
       <c r="P160" s="4" t="s">
-        <v>407</v>
+        <v>545</v>
       </c>
       <c r="Q160" s="3" t="s">
         <v>231</v>
@@ -11181,10 +11181,10 @@
         <v>100</v>
       </c>
       <c r="O161" s="4" t="s">
-        <v>567</v>
+        <v>546</v>
       </c>
       <c r="P161" s="4" t="s">
-        <v>408</v>
+        <v>547</v>
       </c>
       <c r="Q161" s="3" t="s">
         <v>231</v>
@@ -11237,10 +11237,10 @@
         <v>100</v>
       </c>
       <c r="O162" s="4" t="s">
-        <v>568</v>
+        <v>548</v>
       </c>
       <c r="P162" s="4" t="s">
-        <v>409</v>
+        <v>549</v>
       </c>
       <c r="Q162" s="3" t="s">
         <v>231</v>
@@ -11293,10 +11293,10 @@
         <v>100</v>
       </c>
       <c r="O163" s="4" t="s">
-        <v>569</v>
+        <v>550</v>
       </c>
       <c r="P163" s="4" t="s">
-        <v>410</v>
+        <v>551</v>
       </c>
       <c r="Q163" s="3" t="s">
         <v>231</v>
@@ -11349,10 +11349,10 @@
         <v>100</v>
       </c>
       <c r="O164" s="4" t="s">
-        <v>570</v>
+        <v>552</v>
       </c>
       <c r="P164" s="4" t="s">
-        <v>411</v>
+        <v>553</v>
       </c>
       <c r="Q164" s="3" t="s">
         <v>231</v>

--- a/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{164C4A0B-0007-4BDF-A11F-7160A77D52B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF824F71-72DF-42A7-9792-F38727F3B427}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -852,978 +852,978 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>110001:0_110002:0_110003:0_110004:0</t>
+    <t>120001:100_0:100</t>
+  </si>
+  <si>
+    <t>120001:101_0:101</t>
+  </si>
+  <si>
+    <t>130001:100_0:100</t>
+  </si>
+  <si>
+    <t>130001:101_0:101</t>
+  </si>
+  <si>
+    <t>140001:100_0:100</t>
+  </si>
+  <si>
+    <t>140001:101_0:101</t>
+  </si>
+  <si>
+    <t>150001:100_0:100</t>
+  </si>
+  <si>
+    <t>150001:101_0:101</t>
+  </si>
+  <si>
+    <t>160001:100_0:100</t>
+  </si>
+  <si>
+    <t>160001:101_0:101</t>
+  </si>
+  <si>
+    <t>170001:100_0:100</t>
+  </si>
+  <si>
+    <t>170001:101_0:101</t>
+  </si>
+  <si>
+    <t>180001:100_0:100</t>
+  </si>
+  <si>
+    <t>180001:101_0:101</t>
+  </si>
+  <si>
+    <t>190001:100_0:100</t>
+  </si>
+  <si>
+    <t>190001:101_0:101</t>
+  </si>
+  <si>
+    <t>200001:100_0:100</t>
+  </si>
+  <si>
+    <t>200001:101_0:101</t>
+  </si>
+  <si>
+    <t>210001:100_0:100</t>
+  </si>
+  <si>
+    <t>210001:101_0:101</t>
+  </si>
+  <si>
+    <t>220001:100_0:100</t>
+  </si>
+  <si>
+    <t>220001:101_0:101</t>
+  </si>
+  <si>
+    <t>230001:100_0:100</t>
+  </si>
+  <si>
+    <t>230001:101_0:101</t>
+  </si>
+  <si>
+    <t>240001:100_0:100</t>
+  </si>
+  <si>
+    <t>240001:101_0:101</t>
+  </si>
+  <si>
+    <t>250001:100_0:100</t>
+  </si>
+  <si>
+    <t>250001:101_0:101</t>
+  </si>
+  <si>
+    <t>260001:100_0:100</t>
+  </si>
+  <si>
+    <t>260001:101_0:101</t>
+  </si>
+  <si>
+    <t>270001:100_0:100</t>
+  </si>
+  <si>
+    <t>270001:101_0:101</t>
+  </si>
+  <si>
+    <t>280001:100_0:100</t>
+  </si>
+  <si>
+    <t>280001:101_0:101</t>
+  </si>
+  <si>
+    <t>290001:100_0:100</t>
+  </si>
+  <si>
+    <t>290001:101_0:101</t>
+  </si>
+  <si>
+    <t>300001:100_0:100</t>
+  </si>
+  <si>
+    <t>300001:101_0:101</t>
+  </si>
+  <si>
+    <t>310001:100_0:100</t>
+  </si>
+  <si>
+    <t>310001:101_0:101</t>
+  </si>
+  <si>
+    <t>320001:100_0:100</t>
+  </si>
+  <si>
+    <t>320001:101_0:101</t>
+  </si>
+  <si>
+    <t>330001:100_0:100</t>
+  </si>
+  <si>
+    <t>330001:101_0:101</t>
+  </si>
+  <si>
+    <t>340001:100_0:100</t>
+  </si>
+  <si>
+    <t>340001:101_0:101</t>
+  </si>
+  <si>
+    <t>350001:100_0:100</t>
+  </si>
+  <si>
+    <t>350001:101_0:101</t>
+  </si>
+  <si>
+    <t>360001:100_0:100</t>
+  </si>
+  <si>
+    <t>360001:101_0:101</t>
+  </si>
+  <si>
+    <t>370001:100_0:100</t>
+  </si>
+  <si>
+    <t>370001:101_0:101</t>
+  </si>
+  <si>
+    <t>380001:100_0:100</t>
+  </si>
+  <si>
+    <t>380001:101_0:101</t>
+  </si>
+  <si>
+    <t>390001:100_0:100</t>
+  </si>
+  <si>
+    <t>390001:101_0:101</t>
+  </si>
+  <si>
+    <t>400001:100_0:100</t>
+  </si>
+  <si>
+    <t>400001:101_0:101</t>
+  </si>
+  <si>
+    <t>410001:100_0:100</t>
+  </si>
+  <si>
+    <t>410001:101_0:101</t>
+  </si>
+  <si>
+    <t>420001:100_0:100</t>
+  </si>
+  <si>
+    <t>420001:101_0:101</t>
+  </si>
+  <si>
+    <t>430001:100_0:100</t>
+  </si>
+  <si>
+    <t>430001:101_0:101</t>
+  </si>
+  <si>
+    <t>440001:100_0:100</t>
+  </si>
+  <si>
+    <t>440001:101_0:101</t>
+  </si>
+  <si>
+    <t>450001:100_0:100</t>
+  </si>
+  <si>
+    <t>450001:101_0:101</t>
+  </si>
+  <si>
+    <t>460001:100_0:100</t>
+  </si>
+  <si>
+    <t>460001:101_0:101</t>
+  </si>
+  <si>
+    <t>470001:100_0:100</t>
+  </si>
+  <si>
+    <t>470001:101_0:101</t>
+  </si>
+  <si>
+    <t>480001:100_0:100</t>
+  </si>
+  <si>
+    <t>480001:101_0:101</t>
+  </si>
+  <si>
+    <t>490001:100_0:100</t>
+  </si>
+  <si>
+    <t>490001:101_0:101</t>
+  </si>
+  <si>
+    <t>500001:100_0:100</t>
+  </si>
+  <si>
+    <t>500001:101_0:101</t>
+  </si>
+  <si>
+    <t>510001:100_0:100</t>
+  </si>
+  <si>
+    <t>510001:101_0:101</t>
+  </si>
+  <si>
+    <t>520001:100_0:100</t>
+  </si>
+  <si>
+    <t>520001:101_0:101</t>
+  </si>
+  <si>
+    <t>530001:100_0:100</t>
+  </si>
+  <si>
+    <t>530001:101_0:101</t>
+  </si>
+  <si>
+    <t>540001:100_0:100</t>
+  </si>
+  <si>
+    <t>540001:101_0:101</t>
+  </si>
+  <si>
+    <t>550001:100_0:100</t>
+  </si>
+  <si>
+    <t>550001:101_0:101</t>
+  </si>
+  <si>
+    <t>560001:100_0:100</t>
+  </si>
+  <si>
+    <t>560001:101_0:101</t>
+  </si>
+  <si>
+    <t>570001:100_0:100</t>
+  </si>
+  <si>
+    <t>570001:101_0:101</t>
+  </si>
+  <si>
+    <t>580001:100_0:100</t>
+  </si>
+  <si>
+    <t>580001:101_0:101</t>
+  </si>
+  <si>
+    <t>590001:100_0:100</t>
+  </si>
+  <si>
+    <t>590001:101_0:101</t>
+  </si>
+  <si>
+    <t>600001:100_0:100</t>
+  </si>
+  <si>
+    <t>600001:101_0:101</t>
+  </si>
+  <si>
+    <t>610001:100_0:100</t>
+  </si>
+  <si>
+    <t>610001:101_0:101</t>
+  </si>
+  <si>
+    <t>620001:100_0:100</t>
+  </si>
+  <si>
+    <t>620001:101_0:101</t>
+  </si>
+  <si>
+    <t>630001:100_0:100</t>
+  </si>
+  <si>
+    <t>630001:101_0:101</t>
+  </si>
+  <si>
+    <t>640001:100_0:100</t>
+  </si>
+  <si>
+    <t>640001:101_0:101</t>
+  </si>
+  <si>
+    <t>650001:100_0:100</t>
+  </si>
+  <si>
+    <t>650001:101_0:101</t>
+  </si>
+  <si>
+    <t>660001:100_0:100</t>
+  </si>
+  <si>
+    <t>660001:101_0:101</t>
+  </si>
+  <si>
+    <t>670001:100_0:100</t>
+  </si>
+  <si>
+    <t>670001:101_0:101</t>
+  </si>
+  <si>
+    <t>680001:100_0:100</t>
+  </si>
+  <si>
+    <t>680001:101_0:101</t>
+  </si>
+  <si>
+    <t>690001:100_0:100</t>
+  </si>
+  <si>
+    <t>690001:101_0:101</t>
+  </si>
+  <si>
+    <t>700001:100_0:100</t>
+  </si>
+  <si>
+    <t>700001:101_0:101</t>
+  </si>
+  <si>
+    <t>710001:100_0:100</t>
+  </si>
+  <si>
+    <t>710001:101_0:101</t>
+  </si>
+  <si>
+    <t>720001:100_0:100</t>
+  </si>
+  <si>
+    <t>720001:101_0:101</t>
+  </si>
+  <si>
+    <t>730001:100_0:100</t>
+  </si>
+  <si>
+    <t>730001:101_0:101</t>
+  </si>
+  <si>
+    <t>740001:100_0:100</t>
+  </si>
+  <si>
+    <t>740001:101_0:101</t>
+  </si>
+  <si>
+    <t>750001:100_0:100</t>
+  </si>
+  <si>
+    <t>750001:101_0:101</t>
+  </si>
+  <si>
+    <t>760001:100_0:100</t>
+  </si>
+  <si>
+    <t>760001:101_0:101</t>
+  </si>
+  <si>
+    <t>770001:100_0:100</t>
+  </si>
+  <si>
+    <t>770001:101_0:101</t>
+  </si>
+  <si>
+    <t>780001:100_0:100</t>
+  </si>
+  <si>
+    <t>780001:101_0:101</t>
+  </si>
+  <si>
+    <t>790001:100_0:100</t>
+  </si>
+  <si>
+    <t>790001:101_0:101</t>
+  </si>
+  <si>
+    <t>800001:100_0:100</t>
+  </si>
+  <si>
+    <t>800001:101_0:101</t>
+  </si>
+  <si>
+    <t>810001:100_0:100</t>
+  </si>
+  <si>
+    <t>810001:101_0:101</t>
+  </si>
+  <si>
+    <t>820001:100_0:100</t>
+  </si>
+  <si>
+    <t>820001:101_0:101</t>
+  </si>
+  <si>
+    <t>830001:100_0:100</t>
+  </si>
+  <si>
+    <t>830001:101_0:101</t>
+  </si>
+  <si>
+    <t>840001:100_0:100</t>
+  </si>
+  <si>
+    <t>840001:101_0:101</t>
+  </si>
+  <si>
+    <t>850001:100_0:100</t>
+  </si>
+  <si>
+    <t>850001:101_0:101</t>
+  </si>
+  <si>
+    <t>860001:100_0:100</t>
+  </si>
+  <si>
+    <t>860001:101_0:101</t>
+  </si>
+  <si>
+    <t>870001:100_0:100</t>
+  </si>
+  <si>
+    <t>870001:101_0:101</t>
+  </si>
+  <si>
+    <t>880001:100_0:100</t>
+  </si>
+  <si>
+    <t>880001:101_0:101</t>
+  </si>
+  <si>
+    <t>890001:100_0:100</t>
+  </si>
+  <si>
+    <t>890001:101_0:101</t>
+  </si>
+  <si>
+    <t>900001:100_0:100</t>
+  </si>
+  <si>
+    <t>900001:101_0:101</t>
+  </si>
+  <si>
+    <t>910001:100_0:100</t>
+  </si>
+  <si>
+    <t>910001:101_0:101</t>
+  </si>
+  <si>
+    <t>920001:100_0:100</t>
+  </si>
+  <si>
+    <t>920001:101_0:101</t>
+  </si>
+  <si>
+    <t>930001:100_0:100</t>
+  </si>
+  <si>
+    <t>930001:101_0:101</t>
+  </si>
+  <si>
+    <t>940001:100_0:100</t>
+  </si>
+  <si>
+    <t>940001:101_0:101</t>
+  </si>
+  <si>
+    <t>950001:100_0:100</t>
+  </si>
+  <si>
+    <t>950001:101_0:101</t>
+  </si>
+  <si>
+    <t>960001:100_0:100</t>
+  </si>
+  <si>
+    <t>960001:101_0:101</t>
+  </si>
+  <si>
+    <t>970001:100_0:100</t>
+  </si>
+  <si>
+    <t>970001:101_0:101</t>
+  </si>
+  <si>
+    <t>980001:100_0:100</t>
+  </si>
+  <si>
+    <t>980001:101_0:101</t>
+  </si>
+  <si>
+    <t>990001:100_0:100</t>
+  </si>
+  <si>
+    <t>990001:101_0:101</t>
+  </si>
+  <si>
+    <t>1000001:100_0:100</t>
+  </si>
+  <si>
+    <t>1000001:101_0:101</t>
+  </si>
+  <si>
+    <t>1010001:100_0:100</t>
+  </si>
+  <si>
+    <t>1010001:101_0:101</t>
+  </si>
+  <si>
+    <t>1020001:100_0:100</t>
+  </si>
+  <si>
+    <t>1020001:101_0:101</t>
+  </si>
+  <si>
+    <t>1030001:100_0:100</t>
+  </si>
+  <si>
+    <t>1030001:101_0:101</t>
+  </si>
+  <si>
+    <t>1040001:100_0:100</t>
+  </si>
+  <si>
+    <t>1040001:101_0:101</t>
+  </si>
+  <si>
+    <t>1050001:100_0:100</t>
+  </si>
+  <si>
+    <t>1050001:101_0:101</t>
+  </si>
+  <si>
+    <t>1060001:100_0:100</t>
+  </si>
+  <si>
+    <t>1060001:101_0:101</t>
+  </si>
+  <si>
+    <t>1070001:100_0:100</t>
+  </si>
+  <si>
+    <t>1070001:101_0:101</t>
+  </si>
+  <si>
+    <t>1080001:100_0:100</t>
+  </si>
+  <si>
+    <t>1080001:101_0:101</t>
+  </si>
+  <si>
+    <t>1090001:100_0:100</t>
+  </si>
+  <si>
+    <t>1090001:101_0:101</t>
+  </si>
+  <si>
+    <t>1100001:100_0:100</t>
+  </si>
+  <si>
+    <t>1100001:101_0:101</t>
+  </si>
+  <si>
+    <t>1110001:100_0:100</t>
+  </si>
+  <si>
+    <t>1110001:101_0:101</t>
+  </si>
+  <si>
+    <t>1120001:100_0:100</t>
+  </si>
+  <si>
+    <t>1120001:101_0:101</t>
+  </si>
+  <si>
+    <t>1130001:100_0:100</t>
+  </si>
+  <si>
+    <t>1130001:101_0:101</t>
+  </si>
+  <si>
+    <t>1140001:100_0:100</t>
+  </si>
+  <si>
+    <t>1140001:101_0:101</t>
+  </si>
+  <si>
+    <t>1150001:100_0:100</t>
+  </si>
+  <si>
+    <t>1150001:101_0:101</t>
+  </si>
+  <si>
+    <t>1160001:100_0:100</t>
+  </si>
+  <si>
+    <t>1160001:101_0:101</t>
+  </si>
+  <si>
+    <t>1170001:100_0:100</t>
+  </si>
+  <si>
+    <t>1170001:101_0:101</t>
+  </si>
+  <si>
+    <t>1180001:100_0:100</t>
+  </si>
+  <si>
+    <t>1180001:101_0:101</t>
+  </si>
+  <si>
+    <t>1190001:100_0:100</t>
+  </si>
+  <si>
+    <t>1190001:101_0:101</t>
+  </si>
+  <si>
+    <t>1200001:100_0:100</t>
+  </si>
+  <si>
+    <t>1200001:101_0:101</t>
+  </si>
+  <si>
+    <t>1210001:100_0:100</t>
+  </si>
+  <si>
+    <t>1210001:101_0:101</t>
+  </si>
+  <si>
+    <t>1220001:100_0:100</t>
+  </si>
+  <si>
+    <t>1220001:101_0:101</t>
+  </si>
+  <si>
+    <t>1230001:100_0:100</t>
+  </si>
+  <si>
+    <t>1230001:101_0:101</t>
+  </si>
+  <si>
+    <t>1240001:100_0:100</t>
+  </si>
+  <si>
+    <t>1240001:101_0:101</t>
+  </si>
+  <si>
+    <t>1250001:100_0:100</t>
+  </si>
+  <si>
+    <t>1250001:101_0:101</t>
+  </si>
+  <si>
+    <t>1260001:100_0:100</t>
+  </si>
+  <si>
+    <t>1260001:101_0:101</t>
+  </si>
+  <si>
+    <t>1270001:100_0:100</t>
+  </si>
+  <si>
+    <t>1270001:101_0:101</t>
+  </si>
+  <si>
+    <t>1280001:100_0:100</t>
+  </si>
+  <si>
+    <t>1280001:101_0:101</t>
+  </si>
+  <si>
+    <t>1290001:100_0:100</t>
+  </si>
+  <si>
+    <t>1290001:101_0:101</t>
+  </si>
+  <si>
+    <t>1300001:100_0:100</t>
+  </si>
+  <si>
+    <t>1300001:101_0:101</t>
+  </si>
+  <si>
+    <t>1310001:100_0:100</t>
+  </si>
+  <si>
+    <t>1310001:101_0:101</t>
+  </si>
+  <si>
+    <t>1320001:100_0:100</t>
+  </si>
+  <si>
+    <t>1320001:101_0:101</t>
+  </si>
+  <si>
+    <t>1330001:100_0:100</t>
+  </si>
+  <si>
+    <t>1330001:101_0:101</t>
+  </si>
+  <si>
+    <t>1340001:100_0:100</t>
+  </si>
+  <si>
+    <t>1340001:101_0:101</t>
+  </si>
+  <si>
+    <t>1350001:100_0:100</t>
+  </si>
+  <si>
+    <t>1350001:101_0:101</t>
+  </si>
+  <si>
+    <t>1360001:100_0:100</t>
+  </si>
+  <si>
+    <t>1360001:101_0:101</t>
+  </si>
+  <si>
+    <t>1370001:100_0:100</t>
+  </si>
+  <si>
+    <t>1370001:101_0:101</t>
+  </si>
+  <si>
+    <t>1380001:100_0:100</t>
+  </si>
+  <si>
+    <t>1380001:101_0:101</t>
+  </si>
+  <si>
+    <t>1390001:100_0:100</t>
+  </si>
+  <si>
+    <t>1390001:101_0:101</t>
+  </si>
+  <si>
+    <t>1400001:100_0:100</t>
+  </si>
+  <si>
+    <t>1400001:101_0:101</t>
+  </si>
+  <si>
+    <t>1410001:100_0:100</t>
+  </si>
+  <si>
+    <t>1410001:101_0:101</t>
+  </si>
+  <si>
+    <t>1420001:100_0:100</t>
+  </si>
+  <si>
+    <t>1420001:101_0:101</t>
+  </si>
+  <si>
+    <t>1430001:100_0:100</t>
+  </si>
+  <si>
+    <t>1430001:101_0:101</t>
+  </si>
+  <si>
+    <t>1440001:100_0:100</t>
+  </si>
+  <si>
+    <t>1440001:101_0:101</t>
+  </si>
+  <si>
+    <t>1450001:100_0:100</t>
+  </si>
+  <si>
+    <t>1450001:101_0:101</t>
+  </si>
+  <si>
+    <t>1460001:100_0:100</t>
+  </si>
+  <si>
+    <t>1460001:101_0:101</t>
+  </si>
+  <si>
+    <t>1470001:100_0:100</t>
+  </si>
+  <si>
+    <t>1470001:101_0:101</t>
+  </si>
+  <si>
+    <t>1480001:100_0:100</t>
+  </si>
+  <si>
+    <t>1480001:101_0:101</t>
+  </si>
+  <si>
+    <t>1490001:100_0:100</t>
+  </si>
+  <si>
+    <t>1490001:101_0:101</t>
+  </si>
+  <si>
+    <t>1500001:100_0:100</t>
+  </si>
+  <si>
+    <t>1500001:101_0:101</t>
+  </si>
+  <si>
+    <t>1510001:100_0:100</t>
+  </si>
+  <si>
+    <t>1510001:101_0:101</t>
+  </si>
+  <si>
+    <t>1520001:100_0:100</t>
+  </si>
+  <si>
+    <t>1520001:101_0:101</t>
+  </si>
+  <si>
+    <t>1530001:100_0:100</t>
+  </si>
+  <si>
+    <t>1530001:101_0:101</t>
+  </si>
+  <si>
+    <t>1540001:100_0:100</t>
+  </si>
+  <si>
+    <t>1540001:101_0:101</t>
+  </si>
+  <si>
+    <t>1550001:100_0:100</t>
+  </si>
+  <si>
+    <t>1550001:101_0:101</t>
+  </si>
+  <si>
+    <t>1560001:100_0:100</t>
+  </si>
+  <si>
+    <t>1560001:101_0:101</t>
+  </si>
+  <si>
+    <t>1570001:100_0:100</t>
+  </si>
+  <si>
+    <t>1570001:101_0:101</t>
+  </si>
+  <si>
+    <t>1580001:100_0:100</t>
+  </si>
+  <si>
+    <t>1580001:101_0:101</t>
+  </si>
+  <si>
+    <t>1590001:100_0:100</t>
+  </si>
+  <si>
+    <t>1590001:101_0:101</t>
+  </si>
+  <si>
+    <t>1600001:100_0:100</t>
+  </si>
+  <si>
+    <t>1600001:101_0:101</t>
+  </si>
+  <si>
+    <t>10001:100_0:100</t>
+  </si>
+  <si>
+    <t>10001:101_0:101</t>
+  </si>
+  <si>
+    <t>20001:100_0:100</t>
+  </si>
+  <si>
+    <t>20001:101_0:101</t>
+  </si>
+  <si>
+    <t>30001:100_0:100</t>
+  </si>
+  <si>
+    <t>30001:101_0:101</t>
+  </si>
+  <si>
+    <t>40001:100_0:100</t>
+  </si>
+  <si>
+    <t>40001:101_0:101</t>
+  </si>
+  <si>
+    <t>50001:100_0:100</t>
+  </si>
+  <si>
+    <t>50001:101_0:101</t>
+  </si>
+  <si>
+    <t>60001:100_0:100</t>
+  </si>
+  <si>
+    <t>60001:101_0:101</t>
+  </si>
+  <si>
+    <t>70001:100_0:100</t>
+  </si>
+  <si>
+    <t>70001:101_0:101</t>
+  </si>
+  <si>
+    <t>80001:100_0:100</t>
+  </si>
+  <si>
+    <t>80001:101_0:101</t>
+  </si>
+  <si>
+    <t>90001:100_0:100</t>
+  </si>
+  <si>
+    <t>90001:101_0:101</t>
+  </si>
+  <si>
+    <t>100001:100_0:100</t>
+  </si>
+  <si>
+    <t>100001:101_0:101</t>
+  </si>
+  <si>
+    <t>110001:1101_110002:1101_110003:1101_110004:1101_110005:1101_0:1101</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>110001:300_110002:950_110003:2100_110004:3350</t>
+    <t>110001:101_110002:101_110003:101_110004:101_110005:101_0:101</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>110001:550_110002:1350_110003:2400_110004:3700</t>
+    <t>110001:0_110002:0_110003:0_110004:0_110005:0</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>110001:1101_110002:1101_110003:1101_110004:1101_0:1101</t>
+    <t>110001:300_110002:950_110003:2100_110004:3350_110005:3350</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>110001:101_110002:101_110003:101_110004:101_0:101</t>
+    <t>110001:550_110002:1350_110003:2400_110004:3700_110005:3700</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>120001:100_0:100</t>
-  </si>
-  <si>
-    <t>120001:101_0:101</t>
-  </si>
-  <si>
-    <t>130001:100_0:100</t>
-  </si>
-  <si>
-    <t>130001:101_0:101</t>
-  </si>
-  <si>
-    <t>140001:100_0:100</t>
-  </si>
-  <si>
-    <t>140001:101_0:101</t>
-  </si>
-  <si>
-    <t>150001:100_0:100</t>
-  </si>
-  <si>
-    <t>150001:101_0:101</t>
-  </si>
-  <si>
-    <t>160001:100_0:100</t>
-  </si>
-  <si>
-    <t>160001:101_0:101</t>
-  </si>
-  <si>
-    <t>170001:100_0:100</t>
-  </si>
-  <si>
-    <t>170001:101_0:101</t>
-  </si>
-  <si>
-    <t>180001:100_0:100</t>
-  </si>
-  <si>
-    <t>180001:101_0:101</t>
-  </si>
-  <si>
-    <t>190001:100_0:100</t>
-  </si>
-  <si>
-    <t>190001:101_0:101</t>
-  </si>
-  <si>
-    <t>200001:100_0:100</t>
-  </si>
-  <si>
-    <t>200001:101_0:101</t>
-  </si>
-  <si>
-    <t>210001:100_0:100</t>
-  </si>
-  <si>
-    <t>210001:101_0:101</t>
-  </si>
-  <si>
-    <t>220001:100_0:100</t>
-  </si>
-  <si>
-    <t>220001:101_0:101</t>
-  </si>
-  <si>
-    <t>230001:100_0:100</t>
-  </si>
-  <si>
-    <t>230001:101_0:101</t>
-  </si>
-  <si>
-    <t>240001:100_0:100</t>
-  </si>
-  <si>
-    <t>240001:101_0:101</t>
-  </si>
-  <si>
-    <t>250001:100_0:100</t>
-  </si>
-  <si>
-    <t>250001:101_0:101</t>
-  </si>
-  <si>
-    <t>260001:100_0:100</t>
-  </si>
-  <si>
-    <t>260001:101_0:101</t>
-  </si>
-  <si>
-    <t>270001:100_0:100</t>
-  </si>
-  <si>
-    <t>270001:101_0:101</t>
-  </si>
-  <si>
-    <t>280001:100_0:100</t>
-  </si>
-  <si>
-    <t>280001:101_0:101</t>
-  </si>
-  <si>
-    <t>290001:100_0:100</t>
-  </si>
-  <si>
-    <t>290001:101_0:101</t>
-  </si>
-  <si>
-    <t>300001:100_0:100</t>
-  </si>
-  <si>
-    <t>300001:101_0:101</t>
-  </si>
-  <si>
-    <t>310001:100_0:100</t>
-  </si>
-  <si>
-    <t>310001:101_0:101</t>
-  </si>
-  <si>
-    <t>320001:100_0:100</t>
-  </si>
-  <si>
-    <t>320001:101_0:101</t>
-  </si>
-  <si>
-    <t>330001:100_0:100</t>
-  </si>
-  <si>
-    <t>330001:101_0:101</t>
-  </si>
-  <si>
-    <t>340001:100_0:100</t>
-  </si>
-  <si>
-    <t>340001:101_0:101</t>
-  </si>
-  <si>
-    <t>350001:100_0:100</t>
-  </si>
-  <si>
-    <t>350001:101_0:101</t>
-  </si>
-  <si>
-    <t>360001:100_0:100</t>
-  </si>
-  <si>
-    <t>360001:101_0:101</t>
-  </si>
-  <si>
-    <t>370001:100_0:100</t>
-  </si>
-  <si>
-    <t>370001:101_0:101</t>
-  </si>
-  <si>
-    <t>380001:100_0:100</t>
-  </si>
-  <si>
-    <t>380001:101_0:101</t>
-  </si>
-  <si>
-    <t>390001:100_0:100</t>
-  </si>
-  <si>
-    <t>390001:101_0:101</t>
-  </si>
-  <si>
-    <t>400001:100_0:100</t>
-  </si>
-  <si>
-    <t>400001:101_0:101</t>
-  </si>
-  <si>
-    <t>410001:100_0:100</t>
-  </si>
-  <si>
-    <t>410001:101_0:101</t>
-  </si>
-  <si>
-    <t>420001:100_0:100</t>
-  </si>
-  <si>
-    <t>420001:101_0:101</t>
-  </si>
-  <si>
-    <t>430001:100_0:100</t>
-  </si>
-  <si>
-    <t>430001:101_0:101</t>
-  </si>
-  <si>
-    <t>440001:100_0:100</t>
-  </si>
-  <si>
-    <t>440001:101_0:101</t>
-  </si>
-  <si>
-    <t>450001:100_0:100</t>
-  </si>
-  <si>
-    <t>450001:101_0:101</t>
-  </si>
-  <si>
-    <t>460001:100_0:100</t>
-  </si>
-  <si>
-    <t>460001:101_0:101</t>
-  </si>
-  <si>
-    <t>470001:100_0:100</t>
-  </si>
-  <si>
-    <t>470001:101_0:101</t>
-  </si>
-  <si>
-    <t>480001:100_0:100</t>
-  </si>
-  <si>
-    <t>480001:101_0:101</t>
-  </si>
-  <si>
-    <t>490001:100_0:100</t>
-  </si>
-  <si>
-    <t>490001:101_0:101</t>
-  </si>
-  <si>
-    <t>500001:100_0:100</t>
-  </si>
-  <si>
-    <t>500001:101_0:101</t>
-  </si>
-  <si>
-    <t>510001:100_0:100</t>
-  </si>
-  <si>
-    <t>510001:101_0:101</t>
-  </si>
-  <si>
-    <t>520001:100_0:100</t>
-  </si>
-  <si>
-    <t>520001:101_0:101</t>
-  </si>
-  <si>
-    <t>530001:100_0:100</t>
-  </si>
-  <si>
-    <t>530001:101_0:101</t>
-  </si>
-  <si>
-    <t>540001:100_0:100</t>
-  </si>
-  <si>
-    <t>540001:101_0:101</t>
-  </si>
-  <si>
-    <t>550001:100_0:100</t>
-  </si>
-  <si>
-    <t>550001:101_0:101</t>
-  </si>
-  <si>
-    <t>560001:100_0:100</t>
-  </si>
-  <si>
-    <t>560001:101_0:101</t>
-  </si>
-  <si>
-    <t>570001:100_0:100</t>
-  </si>
-  <si>
-    <t>570001:101_0:101</t>
-  </si>
-  <si>
-    <t>580001:100_0:100</t>
-  </si>
-  <si>
-    <t>580001:101_0:101</t>
-  </si>
-  <si>
-    <t>590001:100_0:100</t>
-  </si>
-  <si>
-    <t>590001:101_0:101</t>
-  </si>
-  <si>
-    <t>600001:100_0:100</t>
-  </si>
-  <si>
-    <t>600001:101_0:101</t>
-  </si>
-  <si>
-    <t>610001:100_0:100</t>
-  </si>
-  <si>
-    <t>610001:101_0:101</t>
-  </si>
-  <si>
-    <t>620001:100_0:100</t>
-  </si>
-  <si>
-    <t>620001:101_0:101</t>
-  </si>
-  <si>
-    <t>630001:100_0:100</t>
-  </si>
-  <si>
-    <t>630001:101_0:101</t>
-  </si>
-  <si>
-    <t>640001:100_0:100</t>
-  </si>
-  <si>
-    <t>640001:101_0:101</t>
-  </si>
-  <si>
-    <t>650001:100_0:100</t>
-  </si>
-  <si>
-    <t>650001:101_0:101</t>
-  </si>
-  <si>
-    <t>660001:100_0:100</t>
-  </si>
-  <si>
-    <t>660001:101_0:101</t>
-  </si>
-  <si>
-    <t>670001:100_0:100</t>
-  </si>
-  <si>
-    <t>670001:101_0:101</t>
-  </si>
-  <si>
-    <t>680001:100_0:100</t>
-  </si>
-  <si>
-    <t>680001:101_0:101</t>
-  </si>
-  <si>
-    <t>690001:100_0:100</t>
-  </si>
-  <si>
-    <t>690001:101_0:101</t>
-  </si>
-  <si>
-    <t>700001:100_0:100</t>
-  </si>
-  <si>
-    <t>700001:101_0:101</t>
-  </si>
-  <si>
-    <t>710001:100_0:100</t>
-  </si>
-  <si>
-    <t>710001:101_0:101</t>
-  </si>
-  <si>
-    <t>720001:100_0:100</t>
-  </si>
-  <si>
-    <t>720001:101_0:101</t>
-  </si>
-  <si>
-    <t>730001:100_0:100</t>
-  </si>
-  <si>
-    <t>730001:101_0:101</t>
-  </si>
-  <si>
-    <t>740001:100_0:100</t>
-  </si>
-  <si>
-    <t>740001:101_0:101</t>
-  </si>
-  <si>
-    <t>750001:100_0:100</t>
-  </si>
-  <si>
-    <t>750001:101_0:101</t>
-  </si>
-  <si>
-    <t>760001:100_0:100</t>
-  </si>
-  <si>
-    <t>760001:101_0:101</t>
-  </si>
-  <si>
-    <t>770001:100_0:100</t>
-  </si>
-  <si>
-    <t>770001:101_0:101</t>
-  </si>
-  <si>
-    <t>780001:100_0:100</t>
-  </si>
-  <si>
-    <t>780001:101_0:101</t>
-  </si>
-  <si>
-    <t>790001:100_0:100</t>
-  </si>
-  <si>
-    <t>790001:101_0:101</t>
-  </si>
-  <si>
-    <t>800001:100_0:100</t>
-  </si>
-  <si>
-    <t>800001:101_0:101</t>
-  </si>
-  <si>
-    <t>810001:100_0:100</t>
-  </si>
-  <si>
-    <t>810001:101_0:101</t>
-  </si>
-  <si>
-    <t>820001:100_0:100</t>
-  </si>
-  <si>
-    <t>820001:101_0:101</t>
-  </si>
-  <si>
-    <t>830001:100_0:100</t>
-  </si>
-  <si>
-    <t>830001:101_0:101</t>
-  </si>
-  <si>
-    <t>840001:100_0:100</t>
-  </si>
-  <si>
-    <t>840001:101_0:101</t>
-  </si>
-  <si>
-    <t>850001:100_0:100</t>
-  </si>
-  <si>
-    <t>850001:101_0:101</t>
-  </si>
-  <si>
-    <t>860001:100_0:100</t>
-  </si>
-  <si>
-    <t>860001:101_0:101</t>
-  </si>
-  <si>
-    <t>870001:100_0:100</t>
-  </si>
-  <si>
-    <t>870001:101_0:101</t>
-  </si>
-  <si>
-    <t>880001:100_0:100</t>
-  </si>
-  <si>
-    <t>880001:101_0:101</t>
-  </si>
-  <si>
-    <t>890001:100_0:100</t>
-  </si>
-  <si>
-    <t>890001:101_0:101</t>
-  </si>
-  <si>
-    <t>900001:100_0:100</t>
-  </si>
-  <si>
-    <t>900001:101_0:101</t>
-  </si>
-  <si>
-    <t>910001:100_0:100</t>
-  </si>
-  <si>
-    <t>910001:101_0:101</t>
-  </si>
-  <si>
-    <t>920001:100_0:100</t>
-  </si>
-  <si>
-    <t>920001:101_0:101</t>
-  </si>
-  <si>
-    <t>930001:100_0:100</t>
-  </si>
-  <si>
-    <t>930001:101_0:101</t>
-  </si>
-  <si>
-    <t>940001:100_0:100</t>
-  </si>
-  <si>
-    <t>940001:101_0:101</t>
-  </si>
-  <si>
-    <t>950001:100_0:100</t>
-  </si>
-  <si>
-    <t>950001:101_0:101</t>
-  </si>
-  <si>
-    <t>960001:100_0:100</t>
-  </si>
-  <si>
-    <t>960001:101_0:101</t>
-  </si>
-  <si>
-    <t>970001:100_0:100</t>
-  </si>
-  <si>
-    <t>970001:101_0:101</t>
-  </si>
-  <si>
-    <t>980001:100_0:100</t>
-  </si>
-  <si>
-    <t>980001:101_0:101</t>
-  </si>
-  <si>
-    <t>990001:100_0:100</t>
-  </si>
-  <si>
-    <t>990001:101_0:101</t>
-  </si>
-  <si>
-    <t>1000001:100_0:100</t>
-  </si>
-  <si>
-    <t>1000001:101_0:101</t>
-  </si>
-  <si>
-    <t>1010001:100_0:100</t>
-  </si>
-  <si>
-    <t>1010001:101_0:101</t>
-  </si>
-  <si>
-    <t>1020001:100_0:100</t>
-  </si>
-  <si>
-    <t>1020001:101_0:101</t>
-  </si>
-  <si>
-    <t>1030001:100_0:100</t>
-  </si>
-  <si>
-    <t>1030001:101_0:101</t>
-  </si>
-  <si>
-    <t>1040001:100_0:100</t>
-  </si>
-  <si>
-    <t>1040001:101_0:101</t>
-  </si>
-  <si>
-    <t>1050001:100_0:100</t>
-  </si>
-  <si>
-    <t>1050001:101_0:101</t>
-  </si>
-  <si>
-    <t>1060001:100_0:100</t>
-  </si>
-  <si>
-    <t>1060001:101_0:101</t>
-  </si>
-  <si>
-    <t>1070001:100_0:100</t>
-  </si>
-  <si>
-    <t>1070001:101_0:101</t>
-  </si>
-  <si>
-    <t>1080001:100_0:100</t>
-  </si>
-  <si>
-    <t>1080001:101_0:101</t>
-  </si>
-  <si>
-    <t>1090001:100_0:100</t>
-  </si>
-  <si>
-    <t>1090001:101_0:101</t>
-  </si>
-  <si>
-    <t>1100001:100_0:100</t>
-  </si>
-  <si>
-    <t>1100001:101_0:101</t>
-  </si>
-  <si>
-    <t>1110001:100_0:100</t>
-  </si>
-  <si>
-    <t>1110001:101_0:101</t>
-  </si>
-  <si>
-    <t>1120001:100_0:100</t>
-  </si>
-  <si>
-    <t>1120001:101_0:101</t>
-  </si>
-  <si>
-    <t>1130001:100_0:100</t>
-  </si>
-  <si>
-    <t>1130001:101_0:101</t>
-  </si>
-  <si>
-    <t>1140001:100_0:100</t>
-  </si>
-  <si>
-    <t>1140001:101_0:101</t>
-  </si>
-  <si>
-    <t>1150001:100_0:100</t>
-  </si>
-  <si>
-    <t>1150001:101_0:101</t>
-  </si>
-  <si>
-    <t>1160001:100_0:100</t>
-  </si>
-  <si>
-    <t>1160001:101_0:101</t>
-  </si>
-  <si>
-    <t>1170001:100_0:100</t>
-  </si>
-  <si>
-    <t>1170001:101_0:101</t>
-  </si>
-  <si>
-    <t>1180001:100_0:100</t>
-  </si>
-  <si>
-    <t>1180001:101_0:101</t>
-  </si>
-  <si>
-    <t>1190001:100_0:100</t>
-  </si>
-  <si>
-    <t>1190001:101_0:101</t>
-  </si>
-  <si>
-    <t>1200001:100_0:100</t>
-  </si>
-  <si>
-    <t>1200001:101_0:101</t>
-  </si>
-  <si>
-    <t>1210001:100_0:100</t>
-  </si>
-  <si>
-    <t>1210001:101_0:101</t>
-  </si>
-  <si>
-    <t>1220001:100_0:100</t>
-  </si>
-  <si>
-    <t>1220001:101_0:101</t>
-  </si>
-  <si>
-    <t>1230001:100_0:100</t>
-  </si>
-  <si>
-    <t>1230001:101_0:101</t>
-  </si>
-  <si>
-    <t>1240001:100_0:100</t>
-  </si>
-  <si>
-    <t>1240001:101_0:101</t>
-  </si>
-  <si>
-    <t>1250001:100_0:100</t>
-  </si>
-  <si>
-    <t>1250001:101_0:101</t>
-  </si>
-  <si>
-    <t>1260001:100_0:100</t>
-  </si>
-  <si>
-    <t>1260001:101_0:101</t>
-  </si>
-  <si>
-    <t>1270001:100_0:100</t>
-  </si>
-  <si>
-    <t>1270001:101_0:101</t>
-  </si>
-  <si>
-    <t>1280001:100_0:100</t>
-  </si>
-  <si>
-    <t>1280001:101_0:101</t>
-  </si>
-  <si>
-    <t>1290001:100_0:100</t>
-  </si>
-  <si>
-    <t>1290001:101_0:101</t>
-  </si>
-  <si>
-    <t>1300001:100_0:100</t>
-  </si>
-  <si>
-    <t>1300001:101_0:101</t>
-  </si>
-  <si>
-    <t>1310001:100_0:100</t>
-  </si>
-  <si>
-    <t>1310001:101_0:101</t>
-  </si>
-  <si>
-    <t>1320001:100_0:100</t>
-  </si>
-  <si>
-    <t>1320001:101_0:101</t>
-  </si>
-  <si>
-    <t>1330001:100_0:100</t>
-  </si>
-  <si>
-    <t>1330001:101_0:101</t>
-  </si>
-  <si>
-    <t>1340001:100_0:100</t>
-  </si>
-  <si>
-    <t>1340001:101_0:101</t>
-  </si>
-  <si>
-    <t>1350001:100_0:100</t>
-  </si>
-  <si>
-    <t>1350001:101_0:101</t>
-  </si>
-  <si>
-    <t>1360001:100_0:100</t>
-  </si>
-  <si>
-    <t>1360001:101_0:101</t>
-  </si>
-  <si>
-    <t>1370001:100_0:100</t>
-  </si>
-  <si>
-    <t>1370001:101_0:101</t>
-  </si>
-  <si>
-    <t>1380001:100_0:100</t>
-  </si>
-  <si>
-    <t>1380001:101_0:101</t>
-  </si>
-  <si>
-    <t>1390001:100_0:100</t>
-  </si>
-  <si>
-    <t>1390001:101_0:101</t>
-  </si>
-  <si>
-    <t>1400001:100_0:100</t>
-  </si>
-  <si>
-    <t>1400001:101_0:101</t>
-  </si>
-  <si>
-    <t>1410001:100_0:100</t>
-  </si>
-  <si>
-    <t>1410001:101_0:101</t>
-  </si>
-  <si>
-    <t>1420001:100_0:100</t>
-  </si>
-  <si>
-    <t>1420001:101_0:101</t>
-  </si>
-  <si>
-    <t>1430001:100_0:100</t>
-  </si>
-  <si>
-    <t>1430001:101_0:101</t>
-  </si>
-  <si>
-    <t>1440001:100_0:100</t>
-  </si>
-  <si>
-    <t>1440001:101_0:101</t>
-  </si>
-  <si>
-    <t>1450001:100_0:100</t>
-  </si>
-  <si>
-    <t>1450001:101_0:101</t>
-  </si>
-  <si>
-    <t>1460001:100_0:100</t>
-  </si>
-  <si>
-    <t>1460001:101_0:101</t>
-  </si>
-  <si>
-    <t>1470001:100_0:100</t>
-  </si>
-  <si>
-    <t>1470001:101_0:101</t>
-  </si>
-  <si>
-    <t>1480001:100_0:100</t>
-  </si>
-  <si>
-    <t>1480001:101_0:101</t>
-  </si>
-  <si>
-    <t>1490001:100_0:100</t>
-  </si>
-  <si>
-    <t>1490001:101_0:101</t>
-  </si>
-  <si>
-    <t>1500001:100_0:100</t>
-  </si>
-  <si>
-    <t>1500001:101_0:101</t>
-  </si>
-  <si>
-    <t>1510001:100_0:100</t>
-  </si>
-  <si>
-    <t>1510001:101_0:101</t>
-  </si>
-  <si>
-    <t>1520001:100_0:100</t>
-  </si>
-  <si>
-    <t>1520001:101_0:101</t>
-  </si>
-  <si>
-    <t>1530001:100_0:100</t>
-  </si>
-  <si>
-    <t>1530001:101_0:101</t>
-  </si>
-  <si>
-    <t>1540001:100_0:100</t>
-  </si>
-  <si>
-    <t>1540001:101_0:101</t>
-  </si>
-  <si>
-    <t>1550001:100_0:100</t>
-  </si>
-  <si>
-    <t>1550001:101_0:101</t>
-  </si>
-  <si>
-    <t>1560001:100_0:100</t>
-  </si>
-  <si>
-    <t>1560001:101_0:101</t>
-  </si>
-  <si>
-    <t>1570001:100_0:100</t>
-  </si>
-  <si>
-    <t>1570001:101_0:101</t>
-  </si>
-  <si>
-    <t>1580001:100_0:100</t>
-  </si>
-  <si>
-    <t>1580001:101_0:101</t>
-  </si>
-  <si>
-    <t>1590001:100_0:100</t>
-  </si>
-  <si>
-    <t>1590001:101_0:101</t>
-  </si>
-  <si>
-    <t>1600001:100_0:100</t>
-  </si>
-  <si>
-    <t>1600001:101_0:101</t>
-  </si>
-  <si>
-    <t>10001:100_0:100</t>
-  </si>
-  <si>
-    <t>10001:101_0:101</t>
-  </si>
-  <si>
-    <t>20001:100_0:100</t>
-  </si>
-  <si>
-    <t>20001:101_0:101</t>
-  </si>
-  <si>
-    <t>30001:100_0:100</t>
-  </si>
-  <si>
-    <t>30001:101_0:101</t>
-  </si>
-  <si>
-    <t>40001:100_0:100</t>
-  </si>
-  <si>
-    <t>40001:101_0:101</t>
-  </si>
-  <si>
-    <t>50001:100_0:100</t>
-  </si>
-  <si>
-    <t>50001:101_0:101</t>
-  </si>
-  <si>
-    <t>60001:100_0:100</t>
-  </si>
-  <si>
-    <t>60001:101_0:101</t>
-  </si>
-  <si>
-    <t>70001:100_0:100</t>
-  </si>
-  <si>
-    <t>70001:101_0:101</t>
-  </si>
-  <si>
-    <t>80001:100_0:100</t>
-  </si>
-  <si>
-    <t>80001:101_0:101</t>
-  </si>
-  <si>
-    <t>90001:100_0:100</t>
-  </si>
-  <si>
-    <t>90001:101_0:101</t>
-  </si>
-  <si>
-    <t>100001:100_0:100</t>
-  </si>
-  <si>
-    <t>100001:101_0:101</t>
   </si>
 </sst>
 </file>
@@ -2427,10 +2427,10 @@
         <v>150</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>554</v>
+        <v>549</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="Q5" s="3" t="s">
         <v>231</v>
@@ -2492,10 +2492,10 @@
         <v>200</v>
       </c>
       <c r="O6" s="4" t="s">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="P6" s="4" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="Q6" s="3" t="s">
         <v>231</v>
@@ -2548,10 +2548,10 @@
         <v>300</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>558</v>
+        <v>553</v>
       </c>
       <c r="P7" s="4" t="s">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="Q7" s="3" t="s">
         <v>231</v>
@@ -2604,10 +2604,10 @@
         <v>400</v>
       </c>
       <c r="O8" s="4" t="s">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="P8" s="4" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="Q8" s="3" t="s">
         <v>231</v>
@@ -2660,10 +2660,10 @@
         <v>500</v>
       </c>
       <c r="O9" s="4" t="s">
-        <v>562</v>
+        <v>557</v>
       </c>
       <c r="P9" s="4" t="s">
-        <v>563</v>
+        <v>558</v>
       </c>
       <c r="Q9" s="3" t="s">
         <v>231</v>
@@ -2716,10 +2716,10 @@
         <v>600</v>
       </c>
       <c r="O10" s="4" t="s">
-        <v>564</v>
+        <v>559</v>
       </c>
       <c r="P10" s="4" t="s">
-        <v>565</v>
+        <v>560</v>
       </c>
       <c r="Q10" s="3" t="s">
         <v>231</v>
@@ -2772,10 +2772,10 @@
         <v>100</v>
       </c>
       <c r="O11" s="4" t="s">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="P11" s="4" t="s">
-        <v>567</v>
+        <v>562</v>
       </c>
       <c r="Q11" s="3" t="s">
         <v>231</v>
@@ -2828,10 +2828,10 @@
         <v>100</v>
       </c>
       <c r="O12" s="4" t="s">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="P12" s="4" t="s">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="Q12" s="3" t="s">
         <v>231</v>
@@ -2884,10 +2884,10 @@
         <v>100</v>
       </c>
       <c r="O13" s="4" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="P13" s="4" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="Q13" s="3" t="s">
         <v>231</v>
@@ -2940,10 +2940,10 @@
         <v>100</v>
       </c>
       <c r="O14" s="4" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="P14" s="4" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>231</v>
@@ -2996,10 +2996,10 @@
         <v>100</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>254</v>
+        <v>569</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>255</v>
+        <v>570</v>
       </c>
       <c r="Q15" s="3" t="s">
         <v>231</v>
@@ -3008,13 +3008,13 @@
         <v>0</v>
       </c>
       <c r="S15" s="1" t="s">
-        <v>251</v>
+        <v>571</v>
       </c>
       <c r="T15" s="1" t="s">
-        <v>252</v>
+        <v>572</v>
       </c>
       <c r="U15" s="1" t="s">
-        <v>253</v>
+        <v>573</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.15">
@@ -3061,10 +3061,10 @@
         <v>100</v>
       </c>
       <c r="O16" s="4" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="P16" s="4" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="Q16" s="3" t="s">
         <v>231</v>
@@ -3117,10 +3117,10 @@
         <v>100</v>
       </c>
       <c r="O17" s="4" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="P17" s="4" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="Q17" s="3" t="s">
         <v>231</v>
@@ -3173,10 +3173,10 @@
         <v>100</v>
       </c>
       <c r="O18" s="4" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="P18" s="4" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="Q18" s="3" t="s">
         <v>231</v>
@@ -3229,10 +3229,10 @@
         <v>100</v>
       </c>
       <c r="O19" s="4" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="P19" s="4" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="Q19" s="3" t="s">
         <v>231</v>
@@ -3285,10 +3285,10 @@
         <v>100</v>
       </c>
       <c r="O20" s="4" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="P20" s="4" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="Q20" s="3" t="s">
         <v>231</v>
@@ -3341,10 +3341,10 @@
         <v>100</v>
       </c>
       <c r="O21" s="4" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="P21" s="4" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="Q21" s="3" t="s">
         <v>231</v>
@@ -3397,10 +3397,10 @@
         <v>100</v>
       </c>
       <c r="O22" s="4" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="P22" s="4" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="Q22" s="3" t="s">
         <v>231</v>
@@ -3453,10 +3453,10 @@
         <v>100</v>
       </c>
       <c r="O23" s="4" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="P23" s="4" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="Q23" s="3" t="s">
         <v>231</v>
@@ -3509,10 +3509,10 @@
         <v>100</v>
       </c>
       <c r="O24" s="4" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="P24" s="4" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="Q24" s="3" t="s">
         <v>231</v>
@@ -3565,10 +3565,10 @@
         <v>100</v>
       </c>
       <c r="O25" s="4" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="P25" s="4" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="Q25" s="3" t="s">
         <v>231</v>
@@ -3621,10 +3621,10 @@
         <v>100</v>
       </c>
       <c r="O26" s="4" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="P26" s="4" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="Q26" s="3" t="s">
         <v>231</v>
@@ -3677,10 +3677,10 @@
         <v>100</v>
       </c>
       <c r="O27" s="4" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="P27" s="4" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="Q27" s="3" t="s">
         <v>231</v>
@@ -3733,10 +3733,10 @@
         <v>100</v>
       </c>
       <c r="O28" s="4" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="P28" s="4" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="Q28" s="3" t="s">
         <v>231</v>
@@ -3789,10 +3789,10 @@
         <v>100</v>
       </c>
       <c r="O29" s="4" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="P29" s="4" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="Q29" s="3" t="s">
         <v>231</v>
@@ -3845,10 +3845,10 @@
         <v>100</v>
       </c>
       <c r="O30" s="4" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="P30" s="4" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="Q30" s="3" t="s">
         <v>231</v>
@@ -3901,10 +3901,10 @@
         <v>100</v>
       </c>
       <c r="O31" s="4" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="P31" s="4" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="Q31" s="3" t="s">
         <v>231</v>
@@ -3957,10 +3957,10 @@
         <v>100</v>
       </c>
       <c r="O32" s="4" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="P32" s="4" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="Q32" s="3" t="s">
         <v>231</v>
@@ -4013,10 +4013,10 @@
         <v>100</v>
       </c>
       <c r="O33" s="4" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="P33" s="4" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="Q33" s="3" t="s">
         <v>231</v>
@@ -4069,10 +4069,10 @@
         <v>100</v>
       </c>
       <c r="O34" s="4" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="P34" s="4" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="Q34" s="3" t="s">
         <v>231</v>
@@ -4125,10 +4125,10 @@
         <v>100</v>
       </c>
       <c r="O35" s="4" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="P35" s="4" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="Q35" s="3" t="s">
         <v>231</v>
@@ -4181,10 +4181,10 @@
         <v>100</v>
       </c>
       <c r="O36" s="4" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="P36" s="4" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="Q36" s="3" t="s">
         <v>231</v>
@@ -4237,10 +4237,10 @@
         <v>100</v>
       </c>
       <c r="O37" s="4" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="P37" s="4" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="Q37" s="3" t="s">
         <v>231</v>
@@ -4293,10 +4293,10 @@
         <v>100</v>
       </c>
       <c r="O38" s="4" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="P38" s="4" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="Q38" s="3" t="s">
         <v>231</v>
@@ -4349,10 +4349,10 @@
         <v>100</v>
       </c>
       <c r="O39" s="4" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="P39" s="4" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="Q39" s="3" t="s">
         <v>231</v>
@@ -4405,10 +4405,10 @@
         <v>100</v>
       </c>
       <c r="O40" s="4" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="P40" s="4" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="Q40" s="3" t="s">
         <v>231</v>
@@ -4461,10 +4461,10 @@
         <v>100</v>
       </c>
       <c r="O41" s="4" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="P41" s="4" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="Q41" s="3" t="s">
         <v>231</v>
@@ -4517,10 +4517,10 @@
         <v>100</v>
       </c>
       <c r="O42" s="4" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="P42" s="4" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="Q42" s="3" t="s">
         <v>231</v>
@@ -4573,10 +4573,10 @@
         <v>100</v>
       </c>
       <c r="O43" s="4" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="P43" s="4" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="Q43" s="3" t="s">
         <v>231</v>
@@ -4629,10 +4629,10 @@
         <v>100</v>
       </c>
       <c r="O44" s="4" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="P44" s="4" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="Q44" s="3" t="s">
         <v>231</v>
@@ -4685,10 +4685,10 @@
         <v>100</v>
       </c>
       <c r="O45" s="4" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="P45" s="4" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="Q45" s="3" t="s">
         <v>231</v>
@@ -4741,10 +4741,10 @@
         <v>100</v>
       </c>
       <c r="O46" s="4" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="P46" s="4" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="Q46" s="3" t="s">
         <v>231</v>
@@ -4797,10 +4797,10 @@
         <v>100</v>
       </c>
       <c r="O47" s="4" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="P47" s="4" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="Q47" s="3" t="s">
         <v>231</v>
@@ -4853,10 +4853,10 @@
         <v>100</v>
       </c>
       <c r="O48" s="4" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="P48" s="4" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="Q48" s="3" t="s">
         <v>231</v>
@@ -4909,10 +4909,10 @@
         <v>100</v>
       </c>
       <c r="O49" s="4" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="P49" s="4" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="Q49" s="3" t="s">
         <v>231</v>
@@ -4965,10 +4965,10 @@
         <v>100</v>
       </c>
       <c r="O50" s="4" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="P50" s="4" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="Q50" s="3" t="s">
         <v>231</v>
@@ -5021,10 +5021,10 @@
         <v>100</v>
       </c>
       <c r="O51" s="4" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="P51" s="4" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="Q51" s="3" t="s">
         <v>231</v>
@@ -5077,10 +5077,10 @@
         <v>100</v>
       </c>
       <c r="O52" s="4" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="P52" s="4" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="Q52" s="3" t="s">
         <v>231</v>
@@ -5133,10 +5133,10 @@
         <v>100</v>
       </c>
       <c r="O53" s="4" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="P53" s="4" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="Q53" s="3" t="s">
         <v>231</v>
@@ -5189,10 +5189,10 @@
         <v>100</v>
       </c>
       <c r="O54" s="4" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="P54" s="4" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="Q54" s="3" t="s">
         <v>231</v>
@@ -5245,10 +5245,10 @@
         <v>100</v>
       </c>
       <c r="O55" s="4" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="P55" s="4" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="Q55" s="3" t="s">
         <v>231</v>
@@ -5301,10 +5301,10 @@
         <v>100</v>
       </c>
       <c r="O56" s="4" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="P56" s="4" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="Q56" s="3" t="s">
         <v>231</v>
@@ -5357,10 +5357,10 @@
         <v>100</v>
       </c>
       <c r="O57" s="4" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="P57" s="4" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="Q57" s="3" t="s">
         <v>231</v>
@@ -5413,10 +5413,10 @@
         <v>100</v>
       </c>
       <c r="O58" s="4" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="P58" s="4" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="Q58" s="3" t="s">
         <v>231</v>
@@ -5469,10 +5469,10 @@
         <v>100</v>
       </c>
       <c r="O59" s="4" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="P59" s="4" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="Q59" s="3" t="s">
         <v>231</v>
@@ -5525,10 +5525,10 @@
         <v>100</v>
       </c>
       <c r="O60" s="4" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="P60" s="4" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="Q60" s="3" t="s">
         <v>231</v>
@@ -5581,10 +5581,10 @@
         <v>100</v>
       </c>
       <c r="O61" s="4" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="P61" s="4" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="Q61" s="3" t="s">
         <v>231</v>
@@ -5637,10 +5637,10 @@
         <v>100</v>
       </c>
       <c r="O62" s="4" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="P62" s="4" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="Q62" s="3" t="s">
         <v>231</v>
@@ -5693,10 +5693,10 @@
         <v>100</v>
       </c>
       <c r="O63" s="4" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="P63" s="4" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="Q63" s="3" t="s">
         <v>231</v>
@@ -5749,10 +5749,10 @@
         <v>100</v>
       </c>
       <c r="O64" s="4" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="P64" s="4" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="Q64" s="3" t="s">
         <v>231</v>
@@ -5805,10 +5805,10 @@
         <v>100</v>
       </c>
       <c r="O65" s="4" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="P65" s="4" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="Q65" s="3" t="s">
         <v>231</v>
@@ -5861,10 +5861,10 @@
         <v>100</v>
       </c>
       <c r="O66" s="4" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="P66" s="4" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="Q66" s="3" t="s">
         <v>231</v>
@@ -5917,10 +5917,10 @@
         <v>100</v>
       </c>
       <c r="O67" s="4" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="P67" s="4" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="Q67" s="3" t="s">
         <v>231</v>
@@ -5973,10 +5973,10 @@
         <v>100</v>
       </c>
       <c r="O68" s="4" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="P68" s="4" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="Q68" s="3" t="s">
         <v>231</v>
@@ -6029,10 +6029,10 @@
         <v>100</v>
       </c>
       <c r="O69" s="4" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="P69" s="4" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="Q69" s="3" t="s">
         <v>231</v>
@@ -6085,10 +6085,10 @@
         <v>100</v>
       </c>
       <c r="O70" s="4" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="P70" s="4" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="Q70" s="3" t="s">
         <v>231</v>
@@ -6141,10 +6141,10 @@
         <v>100</v>
       </c>
       <c r="O71" s="4" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="P71" s="4" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="Q71" s="3" t="s">
         <v>231</v>
@@ -6197,10 +6197,10 @@
         <v>100</v>
       </c>
       <c r="O72" s="4" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="P72" s="4" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="Q72" s="3" t="s">
         <v>231</v>
@@ -6253,10 +6253,10 @@
         <v>100</v>
       </c>
       <c r="O73" s="4" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="P73" s="4" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="Q73" s="3" t="s">
         <v>231</v>
@@ -6309,10 +6309,10 @@
         <v>100</v>
       </c>
       <c r="O74" s="4" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="P74" s="4" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="Q74" s="3" t="s">
         <v>231</v>
@@ -6365,10 +6365,10 @@
         <v>100</v>
       </c>
       <c r="O75" s="4" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="P75" s="4" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="Q75" s="3" t="s">
         <v>231</v>
@@ -6421,10 +6421,10 @@
         <v>100</v>
       </c>
       <c r="O76" s="4" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="P76" s="4" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="Q76" s="3" t="s">
         <v>231</v>
@@ -6477,10 +6477,10 @@
         <v>100</v>
       </c>
       <c r="O77" s="4" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="P77" s="4" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="Q77" s="3" t="s">
         <v>231</v>
@@ -6533,10 +6533,10 @@
         <v>100</v>
       </c>
       <c r="O78" s="4" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="P78" s="4" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="Q78" s="3" t="s">
         <v>231</v>
@@ -6589,10 +6589,10 @@
         <v>100</v>
       </c>
       <c r="O79" s="4" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="P79" s="4" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="Q79" s="3" t="s">
         <v>231</v>
@@ -6645,10 +6645,10 @@
         <v>100</v>
       </c>
       <c r="O80" s="4" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P80" s="4" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="Q80" s="3" t="s">
         <v>231</v>
@@ -6701,10 +6701,10 @@
         <v>100</v>
       </c>
       <c r="O81" s="4" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="P81" s="4" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="Q81" s="3" t="s">
         <v>231</v>
@@ -6757,10 +6757,10 @@
         <v>100</v>
       </c>
       <c r="O82" s="4" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="P82" s="4" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="Q82" s="3" t="s">
         <v>231</v>
@@ -6813,10 +6813,10 @@
         <v>100</v>
       </c>
       <c r="O83" s="4" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="P83" s="4" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="Q83" s="3" t="s">
         <v>231</v>
@@ -6869,10 +6869,10 @@
         <v>100</v>
       </c>
       <c r="O84" s="4" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="P84" s="4" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="Q84" s="3" t="s">
         <v>231</v>
@@ -6925,10 +6925,10 @@
         <v>100</v>
       </c>
       <c r="O85" s="4" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="P85" s="4" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="Q85" s="3" t="s">
         <v>231</v>
@@ -6981,10 +6981,10 @@
         <v>100</v>
       </c>
       <c r="O86" s="4" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="P86" s="4" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="Q86" s="3" t="s">
         <v>231</v>
@@ -7037,10 +7037,10 @@
         <v>100</v>
       </c>
       <c r="O87" s="4" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="P87" s="4" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="Q87" s="3" t="s">
         <v>231</v>
@@ -7093,10 +7093,10 @@
         <v>100</v>
       </c>
       <c r="O88" s="4" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="P88" s="4" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="Q88" s="3" t="s">
         <v>231</v>
@@ -7149,10 +7149,10 @@
         <v>100</v>
       </c>
       <c r="O89" s="4" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="P89" s="4" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="Q89" s="3" t="s">
         <v>231</v>
@@ -7205,10 +7205,10 @@
         <v>100</v>
       </c>
       <c r="O90" s="4" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="P90" s="4" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="Q90" s="3" t="s">
         <v>231</v>
@@ -7261,10 +7261,10 @@
         <v>100</v>
       </c>
       <c r="O91" s="4" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="P91" s="4" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="Q91" s="3" t="s">
         <v>231</v>
@@ -7317,10 +7317,10 @@
         <v>100</v>
       </c>
       <c r="O92" s="4" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="P92" s="4" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="Q92" s="3" t="s">
         <v>231</v>
@@ -7373,10 +7373,10 @@
         <v>100</v>
       </c>
       <c r="O93" s="4" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="P93" s="4" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="Q93" s="3" t="s">
         <v>231</v>
@@ -7429,10 +7429,10 @@
         <v>100</v>
       </c>
       <c r="O94" s="4" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="P94" s="4" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="Q94" s="3" t="s">
         <v>231</v>
@@ -7485,10 +7485,10 @@
         <v>100</v>
       </c>
       <c r="O95" s="4" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="P95" s="4" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="Q95" s="3" t="s">
         <v>231</v>
@@ -7541,10 +7541,10 @@
         <v>100</v>
       </c>
       <c r="O96" s="4" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="P96" s="4" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="Q96" s="3" t="s">
         <v>231</v>
@@ -7597,10 +7597,10 @@
         <v>100</v>
       </c>
       <c r="O97" s="4" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="P97" s="4" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="Q97" s="3" t="s">
         <v>231</v>
@@ -7653,10 +7653,10 @@
         <v>100</v>
       </c>
       <c r="O98" s="4" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="P98" s="4" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="Q98" s="3" t="s">
         <v>231</v>
@@ -7709,10 +7709,10 @@
         <v>100</v>
       </c>
       <c r="O99" s="4" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="P99" s="4" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="Q99" s="3" t="s">
         <v>231</v>
@@ -7765,10 +7765,10 @@
         <v>100</v>
       </c>
       <c r="O100" s="4" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="P100" s="4" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="Q100" s="3" t="s">
         <v>231</v>
@@ -7821,10 +7821,10 @@
         <v>100</v>
       </c>
       <c r="O101" s="4" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="P101" s="4" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="Q101" s="3" t="s">
         <v>231</v>
@@ -7877,10 +7877,10 @@
         <v>100</v>
       </c>
       <c r="O102" s="4" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="P102" s="4" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="Q102" s="3" t="s">
         <v>231</v>
@@ -7933,10 +7933,10 @@
         <v>100</v>
       </c>
       <c r="O103" s="4" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="P103" s="4" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="Q103" s="3" t="s">
         <v>231</v>
@@ -7989,10 +7989,10 @@
         <v>100</v>
       </c>
       <c r="O104" s="4" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="P104" s="4" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="Q104" s="3" t="s">
         <v>231</v>
@@ -8045,10 +8045,10 @@
         <v>100</v>
       </c>
       <c r="O105" s="4" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="P105" s="4" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="Q105" s="3" t="s">
         <v>231</v>
@@ -8101,10 +8101,10 @@
         <v>100</v>
       </c>
       <c r="O106" s="4" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="P106" s="4" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="Q106" s="3" t="s">
         <v>231</v>
@@ -8157,10 +8157,10 @@
         <v>100</v>
       </c>
       <c r="O107" s="4" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="P107" s="4" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="Q107" s="3" t="s">
         <v>231</v>
@@ -8213,10 +8213,10 @@
         <v>100</v>
       </c>
       <c r="O108" s="4" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="P108" s="4" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="Q108" s="3" t="s">
         <v>231</v>
@@ -8269,10 +8269,10 @@
         <v>100</v>
       </c>
       <c r="O109" s="4" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="P109" s="4" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="Q109" s="3" t="s">
         <v>231</v>
@@ -8325,10 +8325,10 @@
         <v>100</v>
       </c>
       <c r="O110" s="4" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="P110" s="4" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="Q110" s="3" t="s">
         <v>231</v>
@@ -8381,10 +8381,10 @@
         <v>100</v>
       </c>
       <c r="O111" s="4" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="P111" s="4" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="Q111" s="3" t="s">
         <v>231</v>
@@ -8437,10 +8437,10 @@
         <v>100</v>
       </c>
       <c r="O112" s="4" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="P112" s="4" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="Q112" s="3" t="s">
         <v>231</v>
@@ -8493,10 +8493,10 @@
         <v>100</v>
       </c>
       <c r="O113" s="4" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="P113" s="4" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="Q113" s="3" t="s">
         <v>231</v>
@@ -8549,10 +8549,10 @@
         <v>100</v>
       </c>
       <c r="O114" s="4" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="P114" s="4" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="Q114" s="3" t="s">
         <v>231</v>
@@ -8605,10 +8605,10 @@
         <v>100</v>
       </c>
       <c r="O115" s="4" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="P115" s="4" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="Q115" s="3" t="s">
         <v>231</v>
@@ -8661,10 +8661,10 @@
         <v>100</v>
       </c>
       <c r="O116" s="4" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="P116" s="4" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="Q116" s="3" t="s">
         <v>231</v>
@@ -8717,10 +8717,10 @@
         <v>100</v>
       </c>
       <c r="O117" s="4" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="P117" s="4" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="Q117" s="3" t="s">
         <v>231</v>
@@ -8773,10 +8773,10 @@
         <v>100</v>
       </c>
       <c r="O118" s="4" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="P118" s="4" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="Q118" s="3" t="s">
         <v>231</v>
@@ -8829,10 +8829,10 @@
         <v>100</v>
       </c>
       <c r="O119" s="4" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="P119" s="4" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="Q119" s="3" t="s">
         <v>231</v>
@@ -8885,10 +8885,10 @@
         <v>100</v>
       </c>
       <c r="O120" s="4" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="P120" s="4" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="Q120" s="3" t="s">
         <v>231</v>
@@ -8941,10 +8941,10 @@
         <v>100</v>
       </c>
       <c r="O121" s="4" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="P121" s="4" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="Q121" s="3" t="s">
         <v>231</v>
@@ -8997,10 +8997,10 @@
         <v>100</v>
       </c>
       <c r="O122" s="4" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="P122" s="4" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="Q122" s="3" t="s">
         <v>231</v>
@@ -9053,10 +9053,10 @@
         <v>100</v>
       </c>
       <c r="O123" s="4" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="P123" s="4" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="Q123" s="3" t="s">
         <v>231</v>
@@ -9109,10 +9109,10 @@
         <v>100</v>
       </c>
       <c r="O124" s="4" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="P124" s="4" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="Q124" s="3" t="s">
         <v>231</v>
@@ -9165,10 +9165,10 @@
         <v>100</v>
       </c>
       <c r="O125" s="4" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="P125" s="4" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="Q125" s="3" t="s">
         <v>231</v>
@@ -9221,10 +9221,10 @@
         <v>100</v>
       </c>
       <c r="O126" s="4" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="P126" s="4" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="Q126" s="3" t="s">
         <v>231</v>
@@ -9277,10 +9277,10 @@
         <v>100</v>
       </c>
       <c r="O127" s="4" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="P127" s="4" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="Q127" s="3" t="s">
         <v>231</v>
@@ -9333,10 +9333,10 @@
         <v>100</v>
       </c>
       <c r="O128" s="4" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="P128" s="4" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="Q128" s="3" t="s">
         <v>231</v>
@@ -9389,10 +9389,10 @@
         <v>100</v>
       </c>
       <c r="O129" s="4" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="P129" s="4" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="Q129" s="3" t="s">
         <v>231</v>
@@ -9445,10 +9445,10 @@
         <v>100</v>
       </c>
       <c r="O130" s="4" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="P130" s="4" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="Q130" s="3" t="s">
         <v>231</v>
@@ -9501,10 +9501,10 @@
         <v>100</v>
       </c>
       <c r="O131" s="4" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="P131" s="4" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="Q131" s="3" t="s">
         <v>231</v>
@@ -9557,10 +9557,10 @@
         <v>100</v>
       </c>
       <c r="O132" s="4" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="P132" s="4" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="Q132" s="3" t="s">
         <v>231</v>
@@ -9613,10 +9613,10 @@
         <v>100</v>
       </c>
       <c r="O133" s="4" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="P133" s="4" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="Q133" s="3" t="s">
         <v>231</v>
@@ -9669,10 +9669,10 @@
         <v>100</v>
       </c>
       <c r="O134" s="4" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="P134" s="4" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="Q134" s="3" t="s">
         <v>231</v>
@@ -9725,10 +9725,10 @@
         <v>100</v>
       </c>
       <c r="O135" s="4" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="P135" s="4" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="Q135" s="3" t="s">
         <v>231</v>
@@ -9781,10 +9781,10 @@
         <v>100</v>
       </c>
       <c r="O136" s="4" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="P136" s="4" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="Q136" s="3" t="s">
         <v>231</v>
@@ -9837,10 +9837,10 @@
         <v>100</v>
       </c>
       <c r="O137" s="4" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="P137" s="4" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="Q137" s="3" t="s">
         <v>231</v>
@@ -9893,10 +9893,10 @@
         <v>100</v>
       </c>
       <c r="O138" s="4" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="P138" s="4" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="Q138" s="3" t="s">
         <v>231</v>
@@ -9949,10 +9949,10 @@
         <v>100</v>
       </c>
       <c r="O139" s="4" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="P139" s="4" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="Q139" s="3" t="s">
         <v>231</v>
@@ -10005,10 +10005,10 @@
         <v>100</v>
       </c>
       <c r="O140" s="4" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="P140" s="4" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="Q140" s="3" t="s">
         <v>231</v>
@@ -10061,10 +10061,10 @@
         <v>100</v>
       </c>
       <c r="O141" s="4" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="P141" s="4" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="Q141" s="3" t="s">
         <v>231</v>
@@ -10117,10 +10117,10 @@
         <v>100</v>
       </c>
       <c r="O142" s="4" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="P142" s="4" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="Q142" s="3" t="s">
         <v>231</v>
@@ -10173,10 +10173,10 @@
         <v>100</v>
       </c>
       <c r="O143" s="4" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="P143" s="4" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="Q143" s="3" t="s">
         <v>231</v>
@@ -10229,10 +10229,10 @@
         <v>100</v>
       </c>
       <c r="O144" s="4" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="P144" s="4" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="Q144" s="3" t="s">
         <v>231</v>
@@ -10285,10 +10285,10 @@
         <v>100</v>
       </c>
       <c r="O145" s="4" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="P145" s="4" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="Q145" s="3" t="s">
         <v>231</v>
@@ -10341,10 +10341,10 @@
         <v>100</v>
       </c>
       <c r="O146" s="4" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="P146" s="4" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="Q146" s="3" t="s">
         <v>231</v>
@@ -10397,10 +10397,10 @@
         <v>100</v>
       </c>
       <c r="O147" s="4" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="P147" s="4" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="Q147" s="3" t="s">
         <v>231</v>
@@ -10453,10 +10453,10 @@
         <v>100</v>
       </c>
       <c r="O148" s="4" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="P148" s="4" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="Q148" s="3" t="s">
         <v>231</v>
@@ -10509,10 +10509,10 @@
         <v>100</v>
       </c>
       <c r="O149" s="4" t="s">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="P149" s="4" t="s">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="Q149" s="3" t="s">
         <v>231</v>
@@ -10565,10 +10565,10 @@
         <v>100</v>
       </c>
       <c r="O150" s="4" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="P150" s="4" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="Q150" s="3" t="s">
         <v>231</v>
@@ -10621,10 +10621,10 @@
         <v>100</v>
       </c>
       <c r="O151" s="4" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="P151" s="4" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="Q151" s="3" t="s">
         <v>231</v>
@@ -10677,10 +10677,10 @@
         <v>100</v>
       </c>
       <c r="O152" s="4" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="P152" s="4" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="Q152" s="3" t="s">
         <v>231</v>
@@ -10733,10 +10733,10 @@
         <v>100</v>
       </c>
       <c r="O153" s="4" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="P153" s="4" t="s">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="Q153" s="3" t="s">
         <v>231</v>
@@ -10789,10 +10789,10 @@
         <v>100</v>
       </c>
       <c r="O154" s="4" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="P154" s="4" t="s">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="Q154" s="3" t="s">
         <v>231</v>
@@ -10845,10 +10845,10 @@
         <v>100</v>
       </c>
       <c r="O155" s="4" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="P155" s="4" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="Q155" s="3" t="s">
         <v>231</v>
@@ -10901,10 +10901,10 @@
         <v>100</v>
       </c>
       <c r="O156" s="4" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="P156" s="4" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="Q156" s="3" t="s">
         <v>231</v>
@@ -10957,10 +10957,10 @@
         <v>100</v>
       </c>
       <c r="O157" s="4" t="s">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="P157" s="4" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="Q157" s="3" t="s">
         <v>231</v>
@@ -11013,10 +11013,10 @@
         <v>100</v>
       </c>
       <c r="O158" s="4" t="s">
-        <v>540</v>
+        <v>535</v>
       </c>
       <c r="P158" s="4" t="s">
-        <v>541</v>
+        <v>536</v>
       </c>
       <c r="Q158" s="3" t="s">
         <v>231</v>
@@ -11069,10 +11069,10 @@
         <v>100</v>
       </c>
       <c r="O159" s="4" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="P159" s="4" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="Q159" s="3" t="s">
         <v>231</v>
@@ -11125,10 +11125,10 @@
         <v>100</v>
       </c>
       <c r="O160" s="4" t="s">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="P160" s="4" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="Q160" s="3" t="s">
         <v>231</v>
@@ -11181,10 +11181,10 @@
         <v>100</v>
       </c>
       <c r="O161" s="4" t="s">
-        <v>546</v>
+        <v>541</v>
       </c>
       <c r="P161" s="4" t="s">
-        <v>547</v>
+        <v>542</v>
       </c>
       <c r="Q161" s="3" t="s">
         <v>231</v>
@@ -11237,10 +11237,10 @@
         <v>100</v>
       </c>
       <c r="O162" s="4" t="s">
-        <v>548</v>
+        <v>543</v>
       </c>
       <c r="P162" s="4" t="s">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="Q162" s="3" t="s">
         <v>231</v>
@@ -11293,10 +11293,10 @@
         <v>100</v>
       </c>
       <c r="O163" s="4" t="s">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="P163" s="4" t="s">
-        <v>551</v>
+        <v>546</v>
       </c>
       <c r="Q163" s="3" t="s">
         <v>231</v>
@@ -11349,10 +11349,10 @@
         <v>100</v>
       </c>
       <c r="O164" s="4" t="s">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="P164" s="4" t="s">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="Q164" s="3" t="s">
         <v>231</v>

--- a/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF824F71-72DF-42A7-9792-F38727F3B427}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3815FCD1-7045-4E72-B1D6-E63F1F659F48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1211" uniqueCount="574">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1212" uniqueCount="577">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -852,9 +852,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>120001:100_0:100</t>
-  </si>
-  <si>
     <t>120001:101_0:101</t>
   </si>
   <si>
@@ -1823,6 +1820,22 @@
   </si>
   <si>
     <t>110001:550_110002:1350_110003:2400_110004:3700_110005:3700</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>120001:1101_0:100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>120001:0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>120001:150</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>120001:240</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2427,10 +2440,10 @@
         <v>150</v>
       </c>
       <c r="O5" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="P5" s="1" t="s">
         <v>549</v>
-      </c>
-      <c r="P5" s="1" t="s">
-        <v>550</v>
       </c>
       <c r="Q5" s="3" t="s">
         <v>231</v>
@@ -2492,10 +2505,10 @@
         <v>200</v>
       </c>
       <c r="O6" s="4" t="s">
+        <v>550</v>
+      </c>
+      <c r="P6" s="4" t="s">
         <v>551</v>
-      </c>
-      <c r="P6" s="4" t="s">
-        <v>552</v>
       </c>
       <c r="Q6" s="3" t="s">
         <v>231</v>
@@ -2548,10 +2561,10 @@
         <v>300</v>
       </c>
       <c r="O7" s="4" t="s">
+        <v>552</v>
+      </c>
+      <c r="P7" s="4" t="s">
         <v>553</v>
-      </c>
-      <c r="P7" s="4" t="s">
-        <v>554</v>
       </c>
       <c r="Q7" s="3" t="s">
         <v>231</v>
@@ -2604,10 +2617,10 @@
         <v>400</v>
       </c>
       <c r="O8" s="4" t="s">
+        <v>554</v>
+      </c>
+      <c r="P8" s="4" t="s">
         <v>555</v>
-      </c>
-      <c r="P8" s="4" t="s">
-        <v>556</v>
       </c>
       <c r="Q8" s="3" t="s">
         <v>231</v>
@@ -2660,10 +2673,10 @@
         <v>500</v>
       </c>
       <c r="O9" s="4" t="s">
+        <v>556</v>
+      </c>
+      <c r="P9" s="4" t="s">
         <v>557</v>
-      </c>
-      <c r="P9" s="4" t="s">
-        <v>558</v>
       </c>
       <c r="Q9" s="3" t="s">
         <v>231</v>
@@ -2716,10 +2729,10 @@
         <v>600</v>
       </c>
       <c r="O10" s="4" t="s">
+        <v>558</v>
+      </c>
+      <c r="P10" s="4" t="s">
         <v>559</v>
-      </c>
-      <c r="P10" s="4" t="s">
-        <v>560</v>
       </c>
       <c r="Q10" s="3" t="s">
         <v>231</v>
@@ -2772,10 +2785,10 @@
         <v>100</v>
       </c>
       <c r="O11" s="4" t="s">
+        <v>560</v>
+      </c>
+      <c r="P11" s="4" t="s">
         <v>561</v>
-      </c>
-      <c r="P11" s="4" t="s">
-        <v>562</v>
       </c>
       <c r="Q11" s="3" t="s">
         <v>231</v>
@@ -2828,10 +2841,10 @@
         <v>100</v>
       </c>
       <c r="O12" s="4" t="s">
+        <v>562</v>
+      </c>
+      <c r="P12" s="4" t="s">
         <v>563</v>
-      </c>
-      <c r="P12" s="4" t="s">
-        <v>564</v>
       </c>
       <c r="Q12" s="3" t="s">
         <v>231</v>
@@ -2884,10 +2897,10 @@
         <v>100</v>
       </c>
       <c r="O13" s="4" t="s">
+        <v>564</v>
+      </c>
+      <c r="P13" s="4" t="s">
         <v>565</v>
-      </c>
-      <c r="P13" s="4" t="s">
-        <v>566</v>
       </c>
       <c r="Q13" s="3" t="s">
         <v>231</v>
@@ -2940,10 +2953,10 @@
         <v>100</v>
       </c>
       <c r="O14" s="4" t="s">
+        <v>566</v>
+      </c>
+      <c r="P14" s="4" t="s">
         <v>567</v>
-      </c>
-      <c r="P14" s="4" t="s">
-        <v>568</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>231</v>
@@ -2996,10 +3009,10 @@
         <v>100</v>
       </c>
       <c r="O15" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="P15" s="1" t="s">
         <v>569</v>
-      </c>
-      <c r="P15" s="1" t="s">
-        <v>570</v>
       </c>
       <c r="Q15" s="3" t="s">
         <v>231</v>
@@ -3008,13 +3021,13 @@
         <v>0</v>
       </c>
       <c r="S15" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="T15" s="1" t="s">
         <v>571</v>
       </c>
-      <c r="T15" s="1" t="s">
+      <c r="U15" s="1" t="s">
         <v>572</v>
-      </c>
-      <c r="U15" s="1" t="s">
-        <v>573</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.15">
@@ -3039,8 +3052,8 @@
       <c r="G16" s="1">
         <v>43400002</v>
       </c>
-      <c r="H16" s="1" t="s">
-        <v>202</v>
+      <c r="H16" s="1">
+        <v>0</v>
       </c>
       <c r="I16" s="1">
         <v>1</v>
@@ -3061,16 +3074,25 @@
         <v>100</v>
       </c>
       <c r="O16" s="4" t="s">
+        <v>573</v>
+      </c>
+      <c r="P16" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="P16" s="4" t="s">
-        <v>252</v>
-      </c>
       <c r="Q16" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="R16" s="1" t="s">
-        <v>239</v>
+      <c r="R16" s="1">
+        <v>0</v>
+      </c>
+      <c r="S16" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="T16" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="U16" s="1" t="s">
+        <v>576</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.15">
@@ -3117,10 +3139,10 @@
         <v>100</v>
       </c>
       <c r="O17" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="P17" s="4" t="s">
         <v>253</v>
-      </c>
-      <c r="P17" s="4" t="s">
-        <v>254</v>
       </c>
       <c r="Q17" s="3" t="s">
         <v>231</v>
@@ -3173,10 +3195,10 @@
         <v>100</v>
       </c>
       <c r="O18" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="P18" s="4" t="s">
         <v>255</v>
-      </c>
-      <c r="P18" s="4" t="s">
-        <v>256</v>
       </c>
       <c r="Q18" s="3" t="s">
         <v>231</v>
@@ -3229,10 +3251,10 @@
         <v>100</v>
       </c>
       <c r="O19" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="P19" s="4" t="s">
         <v>257</v>
-      </c>
-      <c r="P19" s="4" t="s">
-        <v>258</v>
       </c>
       <c r="Q19" s="3" t="s">
         <v>231</v>
@@ -3285,10 +3307,10 @@
         <v>100</v>
       </c>
       <c r="O20" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P20" s="4" t="s">
         <v>259</v>
-      </c>
-      <c r="P20" s="4" t="s">
-        <v>260</v>
       </c>
       <c r="Q20" s="3" t="s">
         <v>231</v>
@@ -3341,10 +3363,10 @@
         <v>100</v>
       </c>
       <c r="O21" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="P21" s="4" t="s">
         <v>261</v>
-      </c>
-      <c r="P21" s="4" t="s">
-        <v>262</v>
       </c>
       <c r="Q21" s="3" t="s">
         <v>231</v>
@@ -3397,10 +3419,10 @@
         <v>100</v>
       </c>
       <c r="O22" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="P22" s="4" t="s">
         <v>263</v>
-      </c>
-      <c r="P22" s="4" t="s">
-        <v>264</v>
       </c>
       <c r="Q22" s="3" t="s">
         <v>231</v>
@@ -3453,10 +3475,10 @@
         <v>100</v>
       </c>
       <c r="O23" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="P23" s="4" t="s">
         <v>265</v>
-      </c>
-      <c r="P23" s="4" t="s">
-        <v>266</v>
       </c>
       <c r="Q23" s="3" t="s">
         <v>231</v>
@@ -3509,10 +3531,10 @@
         <v>100</v>
       </c>
       <c r="O24" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="P24" s="4" t="s">
         <v>267</v>
-      </c>
-      <c r="P24" s="4" t="s">
-        <v>268</v>
       </c>
       <c r="Q24" s="3" t="s">
         <v>231</v>
@@ -3565,10 +3587,10 @@
         <v>100</v>
       </c>
       <c r="O25" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="P25" s="4" t="s">
         <v>269</v>
-      </c>
-      <c r="P25" s="4" t="s">
-        <v>270</v>
       </c>
       <c r="Q25" s="3" t="s">
         <v>231</v>
@@ -3621,10 +3643,10 @@
         <v>100</v>
       </c>
       <c r="O26" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="P26" s="4" t="s">
         <v>271</v>
-      </c>
-      <c r="P26" s="4" t="s">
-        <v>272</v>
       </c>
       <c r="Q26" s="3" t="s">
         <v>231</v>
@@ -3677,10 +3699,10 @@
         <v>100</v>
       </c>
       <c r="O27" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="P27" s="4" t="s">
         <v>273</v>
-      </c>
-      <c r="P27" s="4" t="s">
-        <v>274</v>
       </c>
       <c r="Q27" s="3" t="s">
         <v>231</v>
@@ -3733,10 +3755,10 @@
         <v>100</v>
       </c>
       <c r="O28" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="P28" s="4" t="s">
         <v>275</v>
-      </c>
-      <c r="P28" s="4" t="s">
-        <v>276</v>
       </c>
       <c r="Q28" s="3" t="s">
         <v>231</v>
@@ -3789,10 +3811,10 @@
         <v>100</v>
       </c>
       <c r="O29" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="P29" s="4" t="s">
         <v>277</v>
-      </c>
-      <c r="P29" s="4" t="s">
-        <v>278</v>
       </c>
       <c r="Q29" s="3" t="s">
         <v>231</v>
@@ -3845,10 +3867,10 @@
         <v>100</v>
       </c>
       <c r="O30" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="P30" s="4" t="s">
         <v>279</v>
-      </c>
-      <c r="P30" s="4" t="s">
-        <v>280</v>
       </c>
       <c r="Q30" s="3" t="s">
         <v>231</v>
@@ -3901,10 +3923,10 @@
         <v>100</v>
       </c>
       <c r="O31" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="P31" s="4" t="s">
         <v>281</v>
-      </c>
-      <c r="P31" s="4" t="s">
-        <v>282</v>
       </c>
       <c r="Q31" s="3" t="s">
         <v>231</v>
@@ -3957,10 +3979,10 @@
         <v>100</v>
       </c>
       <c r="O32" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="P32" s="4" t="s">
         <v>283</v>
-      </c>
-      <c r="P32" s="4" t="s">
-        <v>284</v>
       </c>
       <c r="Q32" s="3" t="s">
         <v>231</v>
@@ -4013,10 +4035,10 @@
         <v>100</v>
       </c>
       <c r="O33" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="P33" s="4" t="s">
         <v>285</v>
-      </c>
-      <c r="P33" s="4" t="s">
-        <v>286</v>
       </c>
       <c r="Q33" s="3" t="s">
         <v>231</v>
@@ -4069,10 +4091,10 @@
         <v>100</v>
       </c>
       <c r="O34" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="P34" s="4" t="s">
         <v>287</v>
-      </c>
-      <c r="P34" s="4" t="s">
-        <v>288</v>
       </c>
       <c r="Q34" s="3" t="s">
         <v>231</v>
@@ -4125,10 +4147,10 @@
         <v>100</v>
       </c>
       <c r="O35" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="P35" s="4" t="s">
         <v>289</v>
-      </c>
-      <c r="P35" s="4" t="s">
-        <v>290</v>
       </c>
       <c r="Q35" s="3" t="s">
         <v>231</v>
@@ -4181,10 +4203,10 @@
         <v>100</v>
       </c>
       <c r="O36" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="P36" s="4" t="s">
         <v>291</v>
-      </c>
-      <c r="P36" s="4" t="s">
-        <v>292</v>
       </c>
       <c r="Q36" s="3" t="s">
         <v>231</v>
@@ -4237,10 +4259,10 @@
         <v>100</v>
       </c>
       <c r="O37" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="P37" s="4" t="s">
         <v>293</v>
-      </c>
-      <c r="P37" s="4" t="s">
-        <v>294</v>
       </c>
       <c r="Q37" s="3" t="s">
         <v>231</v>
@@ -4293,10 +4315,10 @@
         <v>100</v>
       </c>
       <c r="O38" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="P38" s="4" t="s">
         <v>295</v>
-      </c>
-      <c r="P38" s="4" t="s">
-        <v>296</v>
       </c>
       <c r="Q38" s="3" t="s">
         <v>231</v>
@@ -4349,10 +4371,10 @@
         <v>100</v>
       </c>
       <c r="O39" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="P39" s="4" t="s">
         <v>297</v>
-      </c>
-      <c r="P39" s="4" t="s">
-        <v>298</v>
       </c>
       <c r="Q39" s="3" t="s">
         <v>231</v>
@@ -4405,10 +4427,10 @@
         <v>100</v>
       </c>
       <c r="O40" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="P40" s="4" t="s">
         <v>299</v>
-      </c>
-      <c r="P40" s="4" t="s">
-        <v>300</v>
       </c>
       <c r="Q40" s="3" t="s">
         <v>231</v>
@@ -4461,10 +4483,10 @@
         <v>100</v>
       </c>
       <c r="O41" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="P41" s="4" t="s">
         <v>301</v>
-      </c>
-      <c r="P41" s="4" t="s">
-        <v>302</v>
       </c>
       <c r="Q41" s="3" t="s">
         <v>231</v>
@@ -4517,10 +4539,10 @@
         <v>100</v>
       </c>
       <c r="O42" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="P42" s="4" t="s">
         <v>303</v>
-      </c>
-      <c r="P42" s="4" t="s">
-        <v>304</v>
       </c>
       <c r="Q42" s="3" t="s">
         <v>231</v>
@@ -4573,10 +4595,10 @@
         <v>100</v>
       </c>
       <c r="O43" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="P43" s="4" t="s">
         <v>305</v>
-      </c>
-      <c r="P43" s="4" t="s">
-        <v>306</v>
       </c>
       <c r="Q43" s="3" t="s">
         <v>231</v>
@@ -4629,10 +4651,10 @@
         <v>100</v>
       </c>
       <c r="O44" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="P44" s="4" t="s">
         <v>307</v>
-      </c>
-      <c r="P44" s="4" t="s">
-        <v>308</v>
       </c>
       <c r="Q44" s="3" t="s">
         <v>231</v>
@@ -4685,10 +4707,10 @@
         <v>100</v>
       </c>
       <c r="O45" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="P45" s="4" t="s">
         <v>309</v>
-      </c>
-      <c r="P45" s="4" t="s">
-        <v>310</v>
       </c>
       <c r="Q45" s="3" t="s">
         <v>231</v>
@@ -4741,10 +4763,10 @@
         <v>100</v>
       </c>
       <c r="O46" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="P46" s="4" t="s">
         <v>311</v>
-      </c>
-      <c r="P46" s="4" t="s">
-        <v>312</v>
       </c>
       <c r="Q46" s="3" t="s">
         <v>231</v>
@@ -4797,10 +4819,10 @@
         <v>100</v>
       </c>
       <c r="O47" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="P47" s="4" t="s">
         <v>313</v>
-      </c>
-      <c r="P47" s="4" t="s">
-        <v>314</v>
       </c>
       <c r="Q47" s="3" t="s">
         <v>231</v>
@@ -4853,10 +4875,10 @@
         <v>100</v>
       </c>
       <c r="O48" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="P48" s="4" t="s">
         <v>315</v>
-      </c>
-      <c r="P48" s="4" t="s">
-        <v>316</v>
       </c>
       <c r="Q48" s="3" t="s">
         <v>231</v>
@@ -4909,10 +4931,10 @@
         <v>100</v>
       </c>
       <c r="O49" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="P49" s="4" t="s">
         <v>317</v>
-      </c>
-      <c r="P49" s="4" t="s">
-        <v>318</v>
       </c>
       <c r="Q49" s="3" t="s">
         <v>231</v>
@@ -4965,10 +4987,10 @@
         <v>100</v>
       </c>
       <c r="O50" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="P50" s="4" t="s">
         <v>319</v>
-      </c>
-      <c r="P50" s="4" t="s">
-        <v>320</v>
       </c>
       <c r="Q50" s="3" t="s">
         <v>231</v>
@@ -5021,10 +5043,10 @@
         <v>100</v>
       </c>
       <c r="O51" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="P51" s="4" t="s">
         <v>321</v>
-      </c>
-      <c r="P51" s="4" t="s">
-        <v>322</v>
       </c>
       <c r="Q51" s="3" t="s">
         <v>231</v>
@@ -5077,10 +5099,10 @@
         <v>100</v>
       </c>
       <c r="O52" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="P52" s="4" t="s">
         <v>323</v>
-      </c>
-      <c r="P52" s="4" t="s">
-        <v>324</v>
       </c>
       <c r="Q52" s="3" t="s">
         <v>231</v>
@@ -5133,10 +5155,10 @@
         <v>100</v>
       </c>
       <c r="O53" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="P53" s="4" t="s">
         <v>325</v>
-      </c>
-      <c r="P53" s="4" t="s">
-        <v>326</v>
       </c>
       <c r="Q53" s="3" t="s">
         <v>231</v>
@@ -5189,10 +5211,10 @@
         <v>100</v>
       </c>
       <c r="O54" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="P54" s="4" t="s">
         <v>327</v>
-      </c>
-      <c r="P54" s="4" t="s">
-        <v>328</v>
       </c>
       <c r="Q54" s="3" t="s">
         <v>231</v>
@@ -5245,10 +5267,10 @@
         <v>100</v>
       </c>
       <c r="O55" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="P55" s="4" t="s">
         <v>329</v>
-      </c>
-      <c r="P55" s="4" t="s">
-        <v>330</v>
       </c>
       <c r="Q55" s="3" t="s">
         <v>231</v>
@@ -5301,10 +5323,10 @@
         <v>100</v>
       </c>
       <c r="O56" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="P56" s="4" t="s">
         <v>331</v>
-      </c>
-      <c r="P56" s="4" t="s">
-        <v>332</v>
       </c>
       <c r="Q56" s="3" t="s">
         <v>231</v>
@@ -5357,10 +5379,10 @@
         <v>100</v>
       </c>
       <c r="O57" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="P57" s="4" t="s">
         <v>333</v>
-      </c>
-      <c r="P57" s="4" t="s">
-        <v>334</v>
       </c>
       <c r="Q57" s="3" t="s">
         <v>231</v>
@@ -5413,10 +5435,10 @@
         <v>100</v>
       </c>
       <c r="O58" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="P58" s="4" t="s">
         <v>335</v>
-      </c>
-      <c r="P58" s="4" t="s">
-        <v>336</v>
       </c>
       <c r="Q58" s="3" t="s">
         <v>231</v>
@@ -5469,10 +5491,10 @@
         <v>100</v>
       </c>
       <c r="O59" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="P59" s="4" t="s">
         <v>337</v>
-      </c>
-      <c r="P59" s="4" t="s">
-        <v>338</v>
       </c>
       <c r="Q59" s="3" t="s">
         <v>231</v>
@@ -5525,10 +5547,10 @@
         <v>100</v>
       </c>
       <c r="O60" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="P60" s="4" t="s">
         <v>339</v>
-      </c>
-      <c r="P60" s="4" t="s">
-        <v>340</v>
       </c>
       <c r="Q60" s="3" t="s">
         <v>231</v>
@@ -5581,10 +5603,10 @@
         <v>100</v>
       </c>
       <c r="O61" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="P61" s="4" t="s">
         <v>341</v>
-      </c>
-      <c r="P61" s="4" t="s">
-        <v>342</v>
       </c>
       <c r="Q61" s="3" t="s">
         <v>231</v>
@@ -5637,10 +5659,10 @@
         <v>100</v>
       </c>
       <c r="O62" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="P62" s="4" t="s">
         <v>343</v>
-      </c>
-      <c r="P62" s="4" t="s">
-        <v>344</v>
       </c>
       <c r="Q62" s="3" t="s">
         <v>231</v>
@@ -5693,10 +5715,10 @@
         <v>100</v>
       </c>
       <c r="O63" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="P63" s="4" t="s">
         <v>345</v>
-      </c>
-      <c r="P63" s="4" t="s">
-        <v>346</v>
       </c>
       <c r="Q63" s="3" t="s">
         <v>231</v>
@@ -5749,10 +5771,10 @@
         <v>100</v>
       </c>
       <c r="O64" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="P64" s="4" t="s">
         <v>347</v>
-      </c>
-      <c r="P64" s="4" t="s">
-        <v>348</v>
       </c>
       <c r="Q64" s="3" t="s">
         <v>231</v>
@@ -5805,10 +5827,10 @@
         <v>100</v>
       </c>
       <c r="O65" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="P65" s="4" t="s">
         <v>349</v>
-      </c>
-      <c r="P65" s="4" t="s">
-        <v>350</v>
       </c>
       <c r="Q65" s="3" t="s">
         <v>231</v>
@@ -5861,10 +5883,10 @@
         <v>100</v>
       </c>
       <c r="O66" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="P66" s="4" t="s">
         <v>351</v>
-      </c>
-      <c r="P66" s="4" t="s">
-        <v>352</v>
       </c>
       <c r="Q66" s="3" t="s">
         <v>231</v>
@@ -5917,10 +5939,10 @@
         <v>100</v>
       </c>
       <c r="O67" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="P67" s="4" t="s">
         <v>353</v>
-      </c>
-      <c r="P67" s="4" t="s">
-        <v>354</v>
       </c>
       <c r="Q67" s="3" t="s">
         <v>231</v>
@@ -5973,10 +5995,10 @@
         <v>100</v>
       </c>
       <c r="O68" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="P68" s="4" t="s">
         <v>355</v>
-      </c>
-      <c r="P68" s="4" t="s">
-        <v>356</v>
       </c>
       <c r="Q68" s="3" t="s">
         <v>231</v>
@@ -6029,10 +6051,10 @@
         <v>100</v>
       </c>
       <c r="O69" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="P69" s="4" t="s">
         <v>357</v>
-      </c>
-      <c r="P69" s="4" t="s">
-        <v>358</v>
       </c>
       <c r="Q69" s="3" t="s">
         <v>231</v>
@@ -6085,10 +6107,10 @@
         <v>100</v>
       </c>
       <c r="O70" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="P70" s="4" t="s">
         <v>359</v>
-      </c>
-      <c r="P70" s="4" t="s">
-        <v>360</v>
       </c>
       <c r="Q70" s="3" t="s">
         <v>231</v>
@@ -6141,10 +6163,10 @@
         <v>100</v>
       </c>
       <c r="O71" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="P71" s="4" t="s">
         <v>361</v>
-      </c>
-      <c r="P71" s="4" t="s">
-        <v>362</v>
       </c>
       <c r="Q71" s="3" t="s">
         <v>231</v>
@@ -6197,10 +6219,10 @@
         <v>100</v>
       </c>
       <c r="O72" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="P72" s="4" t="s">
         <v>363</v>
-      </c>
-      <c r="P72" s="4" t="s">
-        <v>364</v>
       </c>
       <c r="Q72" s="3" t="s">
         <v>231</v>
@@ -6253,10 +6275,10 @@
         <v>100</v>
       </c>
       <c r="O73" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="P73" s="4" t="s">
         <v>365</v>
-      </c>
-      <c r="P73" s="4" t="s">
-        <v>366</v>
       </c>
       <c r="Q73" s="3" t="s">
         <v>231</v>
@@ -6309,10 +6331,10 @@
         <v>100</v>
       </c>
       <c r="O74" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="P74" s="4" t="s">
         <v>367</v>
-      </c>
-      <c r="P74" s="4" t="s">
-        <v>368</v>
       </c>
       <c r="Q74" s="3" t="s">
         <v>231</v>
@@ -6365,10 +6387,10 @@
         <v>100</v>
       </c>
       <c r="O75" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="P75" s="4" t="s">
         <v>369</v>
-      </c>
-      <c r="P75" s="4" t="s">
-        <v>370</v>
       </c>
       <c r="Q75" s="3" t="s">
         <v>231</v>
@@ -6421,10 +6443,10 @@
         <v>100</v>
       </c>
       <c r="O76" s="4" t="s">
+        <v>370</v>
+      </c>
+      <c r="P76" s="4" t="s">
         <v>371</v>
-      </c>
-      <c r="P76" s="4" t="s">
-        <v>372</v>
       </c>
       <c r="Q76" s="3" t="s">
         <v>231</v>
@@ -6477,10 +6499,10 @@
         <v>100</v>
       </c>
       <c r="O77" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="P77" s="4" t="s">
         <v>373</v>
-      </c>
-      <c r="P77" s="4" t="s">
-        <v>374</v>
       </c>
       <c r="Q77" s="3" t="s">
         <v>231</v>
@@ -6533,10 +6555,10 @@
         <v>100</v>
       </c>
       <c r="O78" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="P78" s="4" t="s">
         <v>375</v>
-      </c>
-      <c r="P78" s="4" t="s">
-        <v>376</v>
       </c>
       <c r="Q78" s="3" t="s">
         <v>231</v>
@@ -6589,10 +6611,10 @@
         <v>100</v>
       </c>
       <c r="O79" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="P79" s="4" t="s">
         <v>377</v>
-      </c>
-      <c r="P79" s="4" t="s">
-        <v>378</v>
       </c>
       <c r="Q79" s="3" t="s">
         <v>231</v>
@@ -6645,10 +6667,10 @@
         <v>100</v>
       </c>
       <c r="O80" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="P80" s="4" t="s">
         <v>379</v>
-      </c>
-      <c r="P80" s="4" t="s">
-        <v>380</v>
       </c>
       <c r="Q80" s="3" t="s">
         <v>231</v>
@@ -6701,10 +6723,10 @@
         <v>100</v>
       </c>
       <c r="O81" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="P81" s="4" t="s">
         <v>381</v>
-      </c>
-      <c r="P81" s="4" t="s">
-        <v>382</v>
       </c>
       <c r="Q81" s="3" t="s">
         <v>231</v>
@@ -6757,10 +6779,10 @@
         <v>100</v>
       </c>
       <c r="O82" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="P82" s="4" t="s">
         <v>383</v>
-      </c>
-      <c r="P82" s="4" t="s">
-        <v>384</v>
       </c>
       <c r="Q82" s="3" t="s">
         <v>231</v>
@@ -6813,10 +6835,10 @@
         <v>100</v>
       </c>
       <c r="O83" s="4" t="s">
+        <v>384</v>
+      </c>
+      <c r="P83" s="4" t="s">
         <v>385</v>
-      </c>
-      <c r="P83" s="4" t="s">
-        <v>386</v>
       </c>
       <c r="Q83" s="3" t="s">
         <v>231</v>
@@ -6869,10 +6891,10 @@
         <v>100</v>
       </c>
       <c r="O84" s="4" t="s">
+        <v>386</v>
+      </c>
+      <c r="P84" s="4" t="s">
         <v>387</v>
-      </c>
-      <c r="P84" s="4" t="s">
-        <v>388</v>
       </c>
       <c r="Q84" s="3" t="s">
         <v>231</v>
@@ -6925,10 +6947,10 @@
         <v>100</v>
       </c>
       <c r="O85" s="4" t="s">
+        <v>388</v>
+      </c>
+      <c r="P85" s="4" t="s">
         <v>389</v>
-      </c>
-      <c r="P85" s="4" t="s">
-        <v>390</v>
       </c>
       <c r="Q85" s="3" t="s">
         <v>231</v>
@@ -6981,10 +7003,10 @@
         <v>100</v>
       </c>
       <c r="O86" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="P86" s="4" t="s">
         <v>391</v>
-      </c>
-      <c r="P86" s="4" t="s">
-        <v>392</v>
       </c>
       <c r="Q86" s="3" t="s">
         <v>231</v>
@@ -7037,10 +7059,10 @@
         <v>100</v>
       </c>
       <c r="O87" s="4" t="s">
+        <v>392</v>
+      </c>
+      <c r="P87" s="4" t="s">
         <v>393</v>
-      </c>
-      <c r="P87" s="4" t="s">
-        <v>394</v>
       </c>
       <c r="Q87" s="3" t="s">
         <v>231</v>
@@ -7093,10 +7115,10 @@
         <v>100</v>
       </c>
       <c r="O88" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="P88" s="4" t="s">
         <v>395</v>
-      </c>
-      <c r="P88" s="4" t="s">
-        <v>396</v>
       </c>
       <c r="Q88" s="3" t="s">
         <v>231</v>
@@ -7149,10 +7171,10 @@
         <v>100</v>
       </c>
       <c r="O89" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="P89" s="4" t="s">
         <v>397</v>
-      </c>
-      <c r="P89" s="4" t="s">
-        <v>398</v>
       </c>
       <c r="Q89" s="3" t="s">
         <v>231</v>
@@ -7205,10 +7227,10 @@
         <v>100</v>
       </c>
       <c r="O90" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="P90" s="4" t="s">
         <v>399</v>
-      </c>
-      <c r="P90" s="4" t="s">
-        <v>400</v>
       </c>
       <c r="Q90" s="3" t="s">
         <v>231</v>
@@ -7261,10 +7283,10 @@
         <v>100</v>
       </c>
       <c r="O91" s="4" t="s">
+        <v>400</v>
+      </c>
+      <c r="P91" s="4" t="s">
         <v>401</v>
-      </c>
-      <c r="P91" s="4" t="s">
-        <v>402</v>
       </c>
       <c r="Q91" s="3" t="s">
         <v>231</v>
@@ -7317,10 +7339,10 @@
         <v>100</v>
       </c>
       <c r="O92" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="P92" s="4" t="s">
         <v>403</v>
-      </c>
-      <c r="P92" s="4" t="s">
-        <v>404</v>
       </c>
       <c r="Q92" s="3" t="s">
         <v>231</v>
@@ -7373,10 +7395,10 @@
         <v>100</v>
       </c>
       <c r="O93" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="P93" s="4" t="s">
         <v>405</v>
-      </c>
-      <c r="P93" s="4" t="s">
-        <v>406</v>
       </c>
       <c r="Q93" s="3" t="s">
         <v>231</v>
@@ -7429,10 +7451,10 @@
         <v>100</v>
       </c>
       <c r="O94" s="4" t="s">
+        <v>406</v>
+      </c>
+      <c r="P94" s="4" t="s">
         <v>407</v>
-      </c>
-      <c r="P94" s="4" t="s">
-        <v>408</v>
       </c>
       <c r="Q94" s="3" t="s">
         <v>231</v>
@@ -7485,10 +7507,10 @@
         <v>100</v>
       </c>
       <c r="O95" s="4" t="s">
+        <v>408</v>
+      </c>
+      <c r="P95" s="4" t="s">
         <v>409</v>
-      </c>
-      <c r="P95" s="4" t="s">
-        <v>410</v>
       </c>
       <c r="Q95" s="3" t="s">
         <v>231</v>
@@ -7541,10 +7563,10 @@
         <v>100</v>
       </c>
       <c r="O96" s="4" t="s">
+        <v>410</v>
+      </c>
+      <c r="P96" s="4" t="s">
         <v>411</v>
-      </c>
-      <c r="P96" s="4" t="s">
-        <v>412</v>
       </c>
       <c r="Q96" s="3" t="s">
         <v>231</v>
@@ -7597,10 +7619,10 @@
         <v>100</v>
       </c>
       <c r="O97" s="4" t="s">
+        <v>412</v>
+      </c>
+      <c r="P97" s="4" t="s">
         <v>413</v>
-      </c>
-      <c r="P97" s="4" t="s">
-        <v>414</v>
       </c>
       <c r="Q97" s="3" t="s">
         <v>231</v>
@@ -7653,10 +7675,10 @@
         <v>100</v>
       </c>
       <c r="O98" s="4" t="s">
+        <v>414</v>
+      </c>
+      <c r="P98" s="4" t="s">
         <v>415</v>
-      </c>
-      <c r="P98" s="4" t="s">
-        <v>416</v>
       </c>
       <c r="Q98" s="3" t="s">
         <v>231</v>
@@ -7709,10 +7731,10 @@
         <v>100</v>
       </c>
       <c r="O99" s="4" t="s">
+        <v>416</v>
+      </c>
+      <c r="P99" s="4" t="s">
         <v>417</v>
-      </c>
-      <c r="P99" s="4" t="s">
-        <v>418</v>
       </c>
       <c r="Q99" s="3" t="s">
         <v>231</v>
@@ -7765,10 +7787,10 @@
         <v>100</v>
       </c>
       <c r="O100" s="4" t="s">
+        <v>418</v>
+      </c>
+      <c r="P100" s="4" t="s">
         <v>419</v>
-      </c>
-      <c r="P100" s="4" t="s">
-        <v>420</v>
       </c>
       <c r="Q100" s="3" t="s">
         <v>231</v>
@@ -7821,10 +7843,10 @@
         <v>100</v>
       </c>
       <c r="O101" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="P101" s="4" t="s">
         <v>421</v>
-      </c>
-      <c r="P101" s="4" t="s">
-        <v>422</v>
       </c>
       <c r="Q101" s="3" t="s">
         <v>231</v>
@@ -7877,10 +7899,10 @@
         <v>100</v>
       </c>
       <c r="O102" s="4" t="s">
+        <v>422</v>
+      </c>
+      <c r="P102" s="4" t="s">
         <v>423</v>
-      </c>
-      <c r="P102" s="4" t="s">
-        <v>424</v>
       </c>
       <c r="Q102" s="3" t="s">
         <v>231</v>
@@ -7933,10 +7955,10 @@
         <v>100</v>
       </c>
       <c r="O103" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="P103" s="4" t="s">
         <v>425</v>
-      </c>
-      <c r="P103" s="4" t="s">
-        <v>426</v>
       </c>
       <c r="Q103" s="3" t="s">
         <v>231</v>
@@ -7989,10 +8011,10 @@
         <v>100</v>
       </c>
       <c r="O104" s="4" t="s">
+        <v>426</v>
+      </c>
+      <c r="P104" s="4" t="s">
         <v>427</v>
-      </c>
-      <c r="P104" s="4" t="s">
-        <v>428</v>
       </c>
       <c r="Q104" s="3" t="s">
         <v>231</v>
@@ -8045,10 +8067,10 @@
         <v>100</v>
       </c>
       <c r="O105" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="P105" s="4" t="s">
         <v>429</v>
-      </c>
-      <c r="P105" s="4" t="s">
-        <v>430</v>
       </c>
       <c r="Q105" s="3" t="s">
         <v>231</v>
@@ -8101,10 +8123,10 @@
         <v>100</v>
       </c>
       <c r="O106" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="P106" s="4" t="s">
         <v>431</v>
-      </c>
-      <c r="P106" s="4" t="s">
-        <v>432</v>
       </c>
       <c r="Q106" s="3" t="s">
         <v>231</v>
@@ -8157,10 +8179,10 @@
         <v>100</v>
       </c>
       <c r="O107" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="P107" s="4" t="s">
         <v>433</v>
-      </c>
-      <c r="P107" s="4" t="s">
-        <v>434</v>
       </c>
       <c r="Q107" s="3" t="s">
         <v>231</v>
@@ -8213,10 +8235,10 @@
         <v>100</v>
       </c>
       <c r="O108" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="P108" s="4" t="s">
         <v>435</v>
-      </c>
-      <c r="P108" s="4" t="s">
-        <v>436</v>
       </c>
       <c r="Q108" s="3" t="s">
         <v>231</v>
@@ -8269,10 +8291,10 @@
         <v>100</v>
       </c>
       <c r="O109" s="4" t="s">
+        <v>436</v>
+      </c>
+      <c r="P109" s="4" t="s">
         <v>437</v>
-      </c>
-      <c r="P109" s="4" t="s">
-        <v>438</v>
       </c>
       <c r="Q109" s="3" t="s">
         <v>231</v>
@@ -8325,10 +8347,10 @@
         <v>100</v>
       </c>
       <c r="O110" s="4" t="s">
+        <v>438</v>
+      </c>
+      <c r="P110" s="4" t="s">
         <v>439</v>
-      </c>
-      <c r="P110" s="4" t="s">
-        <v>440</v>
       </c>
       <c r="Q110" s="3" t="s">
         <v>231</v>
@@ -8381,10 +8403,10 @@
         <v>100</v>
       </c>
       <c r="O111" s="4" t="s">
+        <v>440</v>
+      </c>
+      <c r="P111" s="4" t="s">
         <v>441</v>
-      </c>
-      <c r="P111" s="4" t="s">
-        <v>442</v>
       </c>
       <c r="Q111" s="3" t="s">
         <v>231</v>
@@ -8437,10 +8459,10 @@
         <v>100</v>
       </c>
       <c r="O112" s="4" t="s">
+        <v>442</v>
+      </c>
+      <c r="P112" s="4" t="s">
         <v>443</v>
-      </c>
-      <c r="P112" s="4" t="s">
-        <v>444</v>
       </c>
       <c r="Q112" s="3" t="s">
         <v>231</v>
@@ -8493,10 +8515,10 @@
         <v>100</v>
       </c>
       <c r="O113" s="4" t="s">
+        <v>444</v>
+      </c>
+      <c r="P113" s="4" t="s">
         <v>445</v>
-      </c>
-      <c r="P113" s="4" t="s">
-        <v>446</v>
       </c>
       <c r="Q113" s="3" t="s">
         <v>231</v>
@@ -8549,10 +8571,10 @@
         <v>100</v>
       </c>
       <c r="O114" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="P114" s="4" t="s">
         <v>447</v>
-      </c>
-      <c r="P114" s="4" t="s">
-        <v>448</v>
       </c>
       <c r="Q114" s="3" t="s">
         <v>231</v>
@@ -8605,10 +8627,10 @@
         <v>100</v>
       </c>
       <c r="O115" s="4" t="s">
+        <v>448</v>
+      </c>
+      <c r="P115" s="4" t="s">
         <v>449</v>
-      </c>
-      <c r="P115" s="4" t="s">
-        <v>450</v>
       </c>
       <c r="Q115" s="3" t="s">
         <v>231</v>
@@ -8661,10 +8683,10 @@
         <v>100</v>
       </c>
       <c r="O116" s="4" t="s">
+        <v>450</v>
+      </c>
+      <c r="P116" s="4" t="s">
         <v>451</v>
-      </c>
-      <c r="P116" s="4" t="s">
-        <v>452</v>
       </c>
       <c r="Q116" s="3" t="s">
         <v>231</v>
@@ -8717,10 +8739,10 @@
         <v>100</v>
       </c>
       <c r="O117" s="4" t="s">
+        <v>452</v>
+      </c>
+      <c r="P117" s="4" t="s">
         <v>453</v>
-      </c>
-      <c r="P117" s="4" t="s">
-        <v>454</v>
       </c>
       <c r="Q117" s="3" t="s">
         <v>231</v>
@@ -8773,10 +8795,10 @@
         <v>100</v>
       </c>
       <c r="O118" s="4" t="s">
+        <v>454</v>
+      </c>
+      <c r="P118" s="4" t="s">
         <v>455</v>
-      </c>
-      <c r="P118" s="4" t="s">
-        <v>456</v>
       </c>
       <c r="Q118" s="3" t="s">
         <v>231</v>
@@ -8829,10 +8851,10 @@
         <v>100</v>
       </c>
       <c r="O119" s="4" t="s">
+        <v>456</v>
+      </c>
+      <c r="P119" s="4" t="s">
         <v>457</v>
-      </c>
-      <c r="P119" s="4" t="s">
-        <v>458</v>
       </c>
       <c r="Q119" s="3" t="s">
         <v>231</v>
@@ -8885,10 +8907,10 @@
         <v>100</v>
       </c>
       <c r="O120" s="4" t="s">
+        <v>458</v>
+      </c>
+      <c r="P120" s="4" t="s">
         <v>459</v>
-      </c>
-      <c r="P120" s="4" t="s">
-        <v>460</v>
       </c>
       <c r="Q120" s="3" t="s">
         <v>231</v>
@@ -8941,10 +8963,10 @@
         <v>100</v>
       </c>
       <c r="O121" s="4" t="s">
+        <v>460</v>
+      </c>
+      <c r="P121" s="4" t="s">
         <v>461</v>
-      </c>
-      <c r="P121" s="4" t="s">
-        <v>462</v>
       </c>
       <c r="Q121" s="3" t="s">
         <v>231</v>
@@ -8997,10 +9019,10 @@
         <v>100</v>
       </c>
       <c r="O122" s="4" t="s">
+        <v>462</v>
+      </c>
+      <c r="P122" s="4" t="s">
         <v>463</v>
-      </c>
-      <c r="P122" s="4" t="s">
-        <v>464</v>
       </c>
       <c r="Q122" s="3" t="s">
         <v>231</v>
@@ -9053,10 +9075,10 @@
         <v>100</v>
       </c>
       <c r="O123" s="4" t="s">
+        <v>464</v>
+      </c>
+      <c r="P123" s="4" t="s">
         <v>465</v>
-      </c>
-      <c r="P123" s="4" t="s">
-        <v>466</v>
       </c>
       <c r="Q123" s="3" t="s">
         <v>231</v>
@@ -9109,10 +9131,10 @@
         <v>100</v>
       </c>
       <c r="O124" s="4" t="s">
+        <v>466</v>
+      </c>
+      <c r="P124" s="4" t="s">
         <v>467</v>
-      </c>
-      <c r="P124" s="4" t="s">
-        <v>468</v>
       </c>
       <c r="Q124" s="3" t="s">
         <v>231</v>
@@ -9165,10 +9187,10 @@
         <v>100</v>
       </c>
       <c r="O125" s="4" t="s">
+        <v>468</v>
+      </c>
+      <c r="P125" s="4" t="s">
         <v>469</v>
-      </c>
-      <c r="P125" s="4" t="s">
-        <v>470</v>
       </c>
       <c r="Q125" s="3" t="s">
         <v>231</v>
@@ -9221,10 +9243,10 @@
         <v>100</v>
       </c>
       <c r="O126" s="4" t="s">
+        <v>470</v>
+      </c>
+      <c r="P126" s="4" t="s">
         <v>471</v>
-      </c>
-      <c r="P126" s="4" t="s">
-        <v>472</v>
       </c>
       <c r="Q126" s="3" t="s">
         <v>231</v>
@@ -9277,10 +9299,10 @@
         <v>100</v>
       </c>
       <c r="O127" s="4" t="s">
+        <v>472</v>
+      </c>
+      <c r="P127" s="4" t="s">
         <v>473</v>
-      </c>
-      <c r="P127" s="4" t="s">
-        <v>474</v>
       </c>
       <c r="Q127" s="3" t="s">
         <v>231</v>
@@ -9333,10 +9355,10 @@
         <v>100</v>
       </c>
       <c r="O128" s="4" t="s">
+        <v>474</v>
+      </c>
+      <c r="P128" s="4" t="s">
         <v>475</v>
-      </c>
-      <c r="P128" s="4" t="s">
-        <v>476</v>
       </c>
       <c r="Q128" s="3" t="s">
         <v>231</v>
@@ -9389,10 +9411,10 @@
         <v>100</v>
       </c>
       <c r="O129" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="P129" s="4" t="s">
         <v>477</v>
-      </c>
-      <c r="P129" s="4" t="s">
-        <v>478</v>
       </c>
       <c r="Q129" s="3" t="s">
         <v>231</v>
@@ -9445,10 +9467,10 @@
         <v>100</v>
       </c>
       <c r="O130" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="P130" s="4" t="s">
         <v>479</v>
-      </c>
-      <c r="P130" s="4" t="s">
-        <v>480</v>
       </c>
       <c r="Q130" s="3" t="s">
         <v>231</v>
@@ -9501,10 +9523,10 @@
         <v>100</v>
       </c>
       <c r="O131" s="4" t="s">
+        <v>480</v>
+      </c>
+      <c r="P131" s="4" t="s">
         <v>481</v>
-      </c>
-      <c r="P131" s="4" t="s">
-        <v>482</v>
       </c>
       <c r="Q131" s="3" t="s">
         <v>231</v>
@@ -9557,10 +9579,10 @@
         <v>100</v>
       </c>
       <c r="O132" s="4" t="s">
+        <v>482</v>
+      </c>
+      <c r="P132" s="4" t="s">
         <v>483</v>
-      </c>
-      <c r="P132" s="4" t="s">
-        <v>484</v>
       </c>
       <c r="Q132" s="3" t="s">
         <v>231</v>
@@ -9613,10 +9635,10 @@
         <v>100</v>
       </c>
       <c r="O133" s="4" t="s">
+        <v>484</v>
+      </c>
+      <c r="P133" s="4" t="s">
         <v>485</v>
-      </c>
-      <c r="P133" s="4" t="s">
-        <v>486</v>
       </c>
       <c r="Q133" s="3" t="s">
         <v>231</v>
@@ -9669,10 +9691,10 @@
         <v>100</v>
       </c>
       <c r="O134" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="P134" s="4" t="s">
         <v>487</v>
-      </c>
-      <c r="P134" s="4" t="s">
-        <v>488</v>
       </c>
       <c r="Q134" s="3" t="s">
         <v>231</v>
@@ -9725,10 +9747,10 @@
         <v>100</v>
       </c>
       <c r="O135" s="4" t="s">
+        <v>488</v>
+      </c>
+      <c r="P135" s="4" t="s">
         <v>489</v>
-      </c>
-      <c r="P135" s="4" t="s">
-        <v>490</v>
       </c>
       <c r="Q135" s="3" t="s">
         <v>231</v>
@@ -9781,10 +9803,10 @@
         <v>100</v>
       </c>
       <c r="O136" s="4" t="s">
+        <v>490</v>
+      </c>
+      <c r="P136" s="4" t="s">
         <v>491</v>
-      </c>
-      <c r="P136" s="4" t="s">
-        <v>492</v>
       </c>
       <c r="Q136" s="3" t="s">
         <v>231</v>
@@ -9837,10 +9859,10 @@
         <v>100</v>
       </c>
       <c r="O137" s="4" t="s">
+        <v>492</v>
+      </c>
+      <c r="P137" s="4" t="s">
         <v>493</v>
-      </c>
-      <c r="P137" s="4" t="s">
-        <v>494</v>
       </c>
       <c r="Q137" s="3" t="s">
         <v>231</v>
@@ -9893,10 +9915,10 @@
         <v>100</v>
       </c>
       <c r="O138" s="4" t="s">
+        <v>494</v>
+      </c>
+      <c r="P138" s="4" t="s">
         <v>495</v>
-      </c>
-      <c r="P138" s="4" t="s">
-        <v>496</v>
       </c>
       <c r="Q138" s="3" t="s">
         <v>231</v>
@@ -9949,10 +9971,10 @@
         <v>100</v>
       </c>
       <c r="O139" s="4" t="s">
+        <v>496</v>
+      </c>
+      <c r="P139" s="4" t="s">
         <v>497</v>
-      </c>
-      <c r="P139" s="4" t="s">
-        <v>498</v>
       </c>
       <c r="Q139" s="3" t="s">
         <v>231</v>
@@ -10005,10 +10027,10 @@
         <v>100</v>
       </c>
       <c r="O140" s="4" t="s">
+        <v>498</v>
+      </c>
+      <c r="P140" s="4" t="s">
         <v>499</v>
-      </c>
-      <c r="P140" s="4" t="s">
-        <v>500</v>
       </c>
       <c r="Q140" s="3" t="s">
         <v>231</v>
@@ -10061,10 +10083,10 @@
         <v>100</v>
       </c>
       <c r="O141" s="4" t="s">
+        <v>500</v>
+      </c>
+      <c r="P141" s="4" t="s">
         <v>501</v>
-      </c>
-      <c r="P141" s="4" t="s">
-        <v>502</v>
       </c>
       <c r="Q141" s="3" t="s">
         <v>231</v>
@@ -10117,10 +10139,10 @@
         <v>100</v>
       </c>
       <c r="O142" s="4" t="s">
+        <v>502</v>
+      </c>
+      <c r="P142" s="4" t="s">
         <v>503</v>
-      </c>
-      <c r="P142" s="4" t="s">
-        <v>504</v>
       </c>
       <c r="Q142" s="3" t="s">
         <v>231</v>
@@ -10173,10 +10195,10 @@
         <v>100</v>
       </c>
       <c r="O143" s="4" t="s">
+        <v>504</v>
+      </c>
+      <c r="P143" s="4" t="s">
         <v>505</v>
-      </c>
-      <c r="P143" s="4" t="s">
-        <v>506</v>
       </c>
       <c r="Q143" s="3" t="s">
         <v>231</v>
@@ -10229,10 +10251,10 @@
         <v>100</v>
       </c>
       <c r="O144" s="4" t="s">
+        <v>506</v>
+      </c>
+      <c r="P144" s="4" t="s">
         <v>507</v>
-      </c>
-      <c r="P144" s="4" t="s">
-        <v>508</v>
       </c>
       <c r="Q144" s="3" t="s">
         <v>231</v>
@@ -10285,10 +10307,10 @@
         <v>100</v>
       </c>
       <c r="O145" s="4" t="s">
+        <v>508</v>
+      </c>
+      <c r="P145" s="4" t="s">
         <v>509</v>
-      </c>
-      <c r="P145" s="4" t="s">
-        <v>510</v>
       </c>
       <c r="Q145" s="3" t="s">
         <v>231</v>
@@ -10341,10 +10363,10 @@
         <v>100</v>
       </c>
       <c r="O146" s="4" t="s">
+        <v>510</v>
+      </c>
+      <c r="P146" s="4" t="s">
         <v>511</v>
-      </c>
-      <c r="P146" s="4" t="s">
-        <v>512</v>
       </c>
       <c r="Q146" s="3" t="s">
         <v>231</v>
@@ -10397,10 +10419,10 @@
         <v>100</v>
       </c>
       <c r="O147" s="4" t="s">
+        <v>512</v>
+      </c>
+      <c r="P147" s="4" t="s">
         <v>513</v>
-      </c>
-      <c r="P147" s="4" t="s">
-        <v>514</v>
       </c>
       <c r="Q147" s="3" t="s">
         <v>231</v>
@@ -10453,10 +10475,10 @@
         <v>100</v>
       </c>
       <c r="O148" s="4" t="s">
+        <v>514</v>
+      </c>
+      <c r="P148" s="4" t="s">
         <v>515</v>
-      </c>
-      <c r="P148" s="4" t="s">
-        <v>516</v>
       </c>
       <c r="Q148" s="3" t="s">
         <v>231</v>
@@ -10509,10 +10531,10 @@
         <v>100</v>
       </c>
       <c r="O149" s="4" t="s">
+        <v>516</v>
+      </c>
+      <c r="P149" s="4" t="s">
         <v>517</v>
-      </c>
-      <c r="P149" s="4" t="s">
-        <v>518</v>
       </c>
       <c r="Q149" s="3" t="s">
         <v>231</v>
@@ -10565,10 +10587,10 @@
         <v>100</v>
       </c>
       <c r="O150" s="4" t="s">
+        <v>518</v>
+      </c>
+      <c r="P150" s="4" t="s">
         <v>519</v>
-      </c>
-      <c r="P150" s="4" t="s">
-        <v>520</v>
       </c>
       <c r="Q150" s="3" t="s">
         <v>231</v>
@@ -10621,10 +10643,10 @@
         <v>100</v>
       </c>
       <c r="O151" s="4" t="s">
+        <v>520</v>
+      </c>
+      <c r="P151" s="4" t="s">
         <v>521</v>
-      </c>
-      <c r="P151" s="4" t="s">
-        <v>522</v>
       </c>
       <c r="Q151" s="3" t="s">
         <v>231</v>
@@ -10677,10 +10699,10 @@
         <v>100</v>
       </c>
       <c r="O152" s="4" t="s">
+        <v>522</v>
+      </c>
+      <c r="P152" s="4" t="s">
         <v>523</v>
-      </c>
-      <c r="P152" s="4" t="s">
-        <v>524</v>
       </c>
       <c r="Q152" s="3" t="s">
         <v>231</v>
@@ -10733,10 +10755,10 @@
         <v>100</v>
       </c>
       <c r="O153" s="4" t="s">
+        <v>524</v>
+      </c>
+      <c r="P153" s="4" t="s">
         <v>525</v>
-      </c>
-      <c r="P153" s="4" t="s">
-        <v>526</v>
       </c>
       <c r="Q153" s="3" t="s">
         <v>231</v>
@@ -10789,10 +10811,10 @@
         <v>100</v>
       </c>
       <c r="O154" s="4" t="s">
+        <v>526</v>
+      </c>
+      <c r="P154" s="4" t="s">
         <v>527</v>
-      </c>
-      <c r="P154" s="4" t="s">
-        <v>528</v>
       </c>
       <c r="Q154" s="3" t="s">
         <v>231</v>
@@ -10845,10 +10867,10 @@
         <v>100</v>
       </c>
       <c r="O155" s="4" t="s">
+        <v>528</v>
+      </c>
+      <c r="P155" s="4" t="s">
         <v>529</v>
-      </c>
-      <c r="P155" s="4" t="s">
-        <v>530</v>
       </c>
       <c r="Q155" s="3" t="s">
         <v>231</v>
@@ -10901,10 +10923,10 @@
         <v>100</v>
       </c>
       <c r="O156" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="P156" s="4" t="s">
         <v>531</v>
-      </c>
-      <c r="P156" s="4" t="s">
-        <v>532</v>
       </c>
       <c r="Q156" s="3" t="s">
         <v>231</v>
@@ -10957,10 +10979,10 @@
         <v>100</v>
       </c>
       <c r="O157" s="4" t="s">
+        <v>532</v>
+      </c>
+      <c r="P157" s="4" t="s">
         <v>533</v>
-      </c>
-      <c r="P157" s="4" t="s">
-        <v>534</v>
       </c>
       <c r="Q157" s="3" t="s">
         <v>231</v>
@@ -11013,10 +11035,10 @@
         <v>100</v>
       </c>
       <c r="O158" s="4" t="s">
+        <v>534</v>
+      </c>
+      <c r="P158" s="4" t="s">
         <v>535</v>
-      </c>
-      <c r="P158" s="4" t="s">
-        <v>536</v>
       </c>
       <c r="Q158" s="3" t="s">
         <v>231</v>
@@ -11069,10 +11091,10 @@
         <v>100</v>
       </c>
       <c r="O159" s="4" t="s">
+        <v>536</v>
+      </c>
+      <c r="P159" s="4" t="s">
         <v>537</v>
-      </c>
-      <c r="P159" s="4" t="s">
-        <v>538</v>
       </c>
       <c r="Q159" s="3" t="s">
         <v>231</v>
@@ -11125,10 +11147,10 @@
         <v>100</v>
       </c>
       <c r="O160" s="4" t="s">
+        <v>538</v>
+      </c>
+      <c r="P160" s="4" t="s">
         <v>539</v>
-      </c>
-      <c r="P160" s="4" t="s">
-        <v>540</v>
       </c>
       <c r="Q160" s="3" t="s">
         <v>231</v>
@@ -11181,10 +11203,10 @@
         <v>100</v>
       </c>
       <c r="O161" s="4" t="s">
+        <v>540</v>
+      </c>
+      <c r="P161" s="4" t="s">
         <v>541</v>
-      </c>
-      <c r="P161" s="4" t="s">
-        <v>542</v>
       </c>
       <c r="Q161" s="3" t="s">
         <v>231</v>
@@ -11237,10 +11259,10 @@
         <v>100</v>
       </c>
       <c r="O162" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="P162" s="4" t="s">
         <v>543</v>
-      </c>
-      <c r="P162" s="4" t="s">
-        <v>544</v>
       </c>
       <c r="Q162" s="3" t="s">
         <v>231</v>
@@ -11293,10 +11315,10 @@
         <v>100</v>
       </c>
       <c r="O163" s="4" t="s">
+        <v>544</v>
+      </c>
+      <c r="P163" s="4" t="s">
         <v>545</v>
-      </c>
-      <c r="P163" s="4" t="s">
-        <v>546</v>
       </c>
       <c r="Q163" s="3" t="s">
         <v>231</v>
@@ -11349,10 +11371,10 @@
         <v>100</v>
       </c>
       <c r="O164" s="4" t="s">
+        <v>546</v>
+      </c>
+      <c r="P164" s="4" t="s">
         <v>547</v>
-      </c>
-      <c r="P164" s="4" t="s">
-        <v>548</v>
       </c>
       <c r="Q164" s="3" t="s">
         <v>231</v>

--- a/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3815FCD1-7045-4E72-B1D6-E63F1F659F48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FEC06B5-ACB7-4ED9-9494-53D68DAD9334}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -852,9 +852,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>120001:101_0:101</t>
-  </si>
-  <si>
     <t>130001:100_0:100</t>
   </si>
   <si>
@@ -1836,6 +1833,10 @@
   </si>
   <si>
     <t>120001:240</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>120001:102_0:102</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2440,10 +2441,10 @@
         <v>150</v>
       </c>
       <c r="O5" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="P5" s="1" t="s">
         <v>548</v>
-      </c>
-      <c r="P5" s="1" t="s">
-        <v>549</v>
       </c>
       <c r="Q5" s="3" t="s">
         <v>231</v>
@@ -2505,10 +2506,10 @@
         <v>200</v>
       </c>
       <c r="O6" s="4" t="s">
+        <v>549</v>
+      </c>
+      <c r="P6" s="4" t="s">
         <v>550</v>
-      </c>
-      <c r="P6" s="4" t="s">
-        <v>551</v>
       </c>
       <c r="Q6" s="3" t="s">
         <v>231</v>
@@ -2561,10 +2562,10 @@
         <v>300</v>
       </c>
       <c r="O7" s="4" t="s">
+        <v>551</v>
+      </c>
+      <c r="P7" s="4" t="s">
         <v>552</v>
-      </c>
-      <c r="P7" s="4" t="s">
-        <v>553</v>
       </c>
       <c r="Q7" s="3" t="s">
         <v>231</v>
@@ -2617,10 +2618,10 @@
         <v>400</v>
       </c>
       <c r="O8" s="4" t="s">
+        <v>553</v>
+      </c>
+      <c r="P8" s="4" t="s">
         <v>554</v>
-      </c>
-      <c r="P8" s="4" t="s">
-        <v>555</v>
       </c>
       <c r="Q8" s="3" t="s">
         <v>231</v>
@@ -2673,10 +2674,10 @@
         <v>500</v>
       </c>
       <c r="O9" s="4" t="s">
+        <v>555</v>
+      </c>
+      <c r="P9" s="4" t="s">
         <v>556</v>
-      </c>
-      <c r="P9" s="4" t="s">
-        <v>557</v>
       </c>
       <c r="Q9" s="3" t="s">
         <v>231</v>
@@ -2729,10 +2730,10 @@
         <v>600</v>
       </c>
       <c r="O10" s="4" t="s">
+        <v>557</v>
+      </c>
+      <c r="P10" s="4" t="s">
         <v>558</v>
-      </c>
-      <c r="P10" s="4" t="s">
-        <v>559</v>
       </c>
       <c r="Q10" s="3" t="s">
         <v>231</v>
@@ -2785,10 +2786,10 @@
         <v>100</v>
       </c>
       <c r="O11" s="4" t="s">
+        <v>559</v>
+      </c>
+      <c r="P11" s="4" t="s">
         <v>560</v>
-      </c>
-      <c r="P11" s="4" t="s">
-        <v>561</v>
       </c>
       <c r="Q11" s="3" t="s">
         <v>231</v>
@@ -2841,10 +2842,10 @@
         <v>100</v>
       </c>
       <c r="O12" s="4" t="s">
+        <v>561</v>
+      </c>
+      <c r="P12" s="4" t="s">
         <v>562</v>
-      </c>
-      <c r="P12" s="4" t="s">
-        <v>563</v>
       </c>
       <c r="Q12" s="3" t="s">
         <v>231</v>
@@ -2897,10 +2898,10 @@
         <v>100</v>
       </c>
       <c r="O13" s="4" t="s">
+        <v>563</v>
+      </c>
+      <c r="P13" s="4" t="s">
         <v>564</v>
-      </c>
-      <c r="P13" s="4" t="s">
-        <v>565</v>
       </c>
       <c r="Q13" s="3" t="s">
         <v>231</v>
@@ -2953,10 +2954,10 @@
         <v>100</v>
       </c>
       <c r="O14" s="4" t="s">
+        <v>565</v>
+      </c>
+      <c r="P14" s="4" t="s">
         <v>566</v>
-      </c>
-      <c r="P14" s="4" t="s">
-        <v>567</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>231</v>
@@ -3009,10 +3010,10 @@
         <v>100</v>
       </c>
       <c r="O15" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="P15" s="1" t="s">
         <v>568</v>
-      </c>
-      <c r="P15" s="1" t="s">
-        <v>569</v>
       </c>
       <c r="Q15" s="3" t="s">
         <v>231</v>
@@ -3021,13 +3022,13 @@
         <v>0</v>
       </c>
       <c r="S15" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="T15" s="1" t="s">
         <v>570</v>
       </c>
-      <c r="T15" s="1" t="s">
+      <c r="U15" s="1" t="s">
         <v>571</v>
-      </c>
-      <c r="U15" s="1" t="s">
-        <v>572</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.15">
@@ -3074,10 +3075,10 @@
         <v>100</v>
       </c>
       <c r="O16" s="4" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="P16" s="4" t="s">
-        <v>251</v>
+        <v>576</v>
       </c>
       <c r="Q16" s="3" t="s">
         <v>231</v>
@@ -3086,13 +3087,13 @@
         <v>0</v>
       </c>
       <c r="S16" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="T16" s="1" t="s">
         <v>574</v>
       </c>
-      <c r="T16" s="1" t="s">
+      <c r="U16" s="1" t="s">
         <v>575</v>
-      </c>
-      <c r="U16" s="1" t="s">
-        <v>576</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.15">
@@ -3139,10 +3140,10 @@
         <v>100</v>
       </c>
       <c r="O17" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="P17" s="4" t="s">
         <v>252</v>
-      </c>
-      <c r="P17" s="4" t="s">
-        <v>253</v>
       </c>
       <c r="Q17" s="3" t="s">
         <v>231</v>
@@ -3195,10 +3196,10 @@
         <v>100</v>
       </c>
       <c r="O18" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="P18" s="4" t="s">
         <v>254</v>
-      </c>
-      <c r="P18" s="4" t="s">
-        <v>255</v>
       </c>
       <c r="Q18" s="3" t="s">
         <v>231</v>
@@ -3251,10 +3252,10 @@
         <v>100</v>
       </c>
       <c r="O19" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="P19" s="4" t="s">
         <v>256</v>
-      </c>
-      <c r="P19" s="4" t="s">
-        <v>257</v>
       </c>
       <c r="Q19" s="3" t="s">
         <v>231</v>
@@ -3307,10 +3308,10 @@
         <v>100</v>
       </c>
       <c r="O20" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="P20" s="4" t="s">
         <v>258</v>
-      </c>
-      <c r="P20" s="4" t="s">
-        <v>259</v>
       </c>
       <c r="Q20" s="3" t="s">
         <v>231</v>
@@ -3363,10 +3364,10 @@
         <v>100</v>
       </c>
       <c r="O21" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="P21" s="4" t="s">
         <v>260</v>
-      </c>
-      <c r="P21" s="4" t="s">
-        <v>261</v>
       </c>
       <c r="Q21" s="3" t="s">
         <v>231</v>
@@ -3419,10 +3420,10 @@
         <v>100</v>
       </c>
       <c r="O22" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="P22" s="4" t="s">
         <v>262</v>
-      </c>
-      <c r="P22" s="4" t="s">
-        <v>263</v>
       </c>
       <c r="Q22" s="3" t="s">
         <v>231</v>
@@ -3475,10 +3476,10 @@
         <v>100</v>
       </c>
       <c r="O23" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="P23" s="4" t="s">
         <v>264</v>
-      </c>
-      <c r="P23" s="4" t="s">
-        <v>265</v>
       </c>
       <c r="Q23" s="3" t="s">
         <v>231</v>
@@ -3531,10 +3532,10 @@
         <v>100</v>
       </c>
       <c r="O24" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="P24" s="4" t="s">
         <v>266</v>
-      </c>
-      <c r="P24" s="4" t="s">
-        <v>267</v>
       </c>
       <c r="Q24" s="3" t="s">
         <v>231</v>
@@ -3587,10 +3588,10 @@
         <v>100</v>
       </c>
       <c r="O25" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="P25" s="4" t="s">
         <v>268</v>
-      </c>
-      <c r="P25" s="4" t="s">
-        <v>269</v>
       </c>
       <c r="Q25" s="3" t="s">
         <v>231</v>
@@ -3643,10 +3644,10 @@
         <v>100</v>
       </c>
       <c r="O26" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="P26" s="4" t="s">
         <v>270</v>
-      </c>
-      <c r="P26" s="4" t="s">
-        <v>271</v>
       </c>
       <c r="Q26" s="3" t="s">
         <v>231</v>
@@ -3699,10 +3700,10 @@
         <v>100</v>
       </c>
       <c r="O27" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="P27" s="4" t="s">
         <v>272</v>
-      </c>
-      <c r="P27" s="4" t="s">
-        <v>273</v>
       </c>
       <c r="Q27" s="3" t="s">
         <v>231</v>
@@ -3755,10 +3756,10 @@
         <v>100</v>
       </c>
       <c r="O28" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="P28" s="4" t="s">
         <v>274</v>
-      </c>
-      <c r="P28" s="4" t="s">
-        <v>275</v>
       </c>
       <c r="Q28" s="3" t="s">
         <v>231</v>
@@ -3811,10 +3812,10 @@
         <v>100</v>
       </c>
       <c r="O29" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="P29" s="4" t="s">
         <v>276</v>
-      </c>
-      <c r="P29" s="4" t="s">
-        <v>277</v>
       </c>
       <c r="Q29" s="3" t="s">
         <v>231</v>
@@ -3867,10 +3868,10 @@
         <v>100</v>
       </c>
       <c r="O30" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="P30" s="4" t="s">
         <v>278</v>
-      </c>
-      <c r="P30" s="4" t="s">
-        <v>279</v>
       </c>
       <c r="Q30" s="3" t="s">
         <v>231</v>
@@ -3923,10 +3924,10 @@
         <v>100</v>
       </c>
       <c r="O31" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="P31" s="4" t="s">
         <v>280</v>
-      </c>
-      <c r="P31" s="4" t="s">
-        <v>281</v>
       </c>
       <c r="Q31" s="3" t="s">
         <v>231</v>
@@ -3979,10 +3980,10 @@
         <v>100</v>
       </c>
       <c r="O32" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="P32" s="4" t="s">
         <v>282</v>
-      </c>
-      <c r="P32" s="4" t="s">
-        <v>283</v>
       </c>
       <c r="Q32" s="3" t="s">
         <v>231</v>
@@ -4035,10 +4036,10 @@
         <v>100</v>
       </c>
       <c r="O33" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="P33" s="4" t="s">
         <v>284</v>
-      </c>
-      <c r="P33" s="4" t="s">
-        <v>285</v>
       </c>
       <c r="Q33" s="3" t="s">
         <v>231</v>
@@ -4091,10 +4092,10 @@
         <v>100</v>
       </c>
       <c r="O34" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="P34" s="4" t="s">
         <v>286</v>
-      </c>
-      <c r="P34" s="4" t="s">
-        <v>287</v>
       </c>
       <c r="Q34" s="3" t="s">
         <v>231</v>
@@ -4147,10 +4148,10 @@
         <v>100</v>
       </c>
       <c r="O35" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="P35" s="4" t="s">
         <v>288</v>
-      </c>
-      <c r="P35" s="4" t="s">
-        <v>289</v>
       </c>
       <c r="Q35" s="3" t="s">
         <v>231</v>
@@ -4203,10 +4204,10 @@
         <v>100</v>
       </c>
       <c r="O36" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="P36" s="4" t="s">
         <v>290</v>
-      </c>
-      <c r="P36" s="4" t="s">
-        <v>291</v>
       </c>
       <c r="Q36" s="3" t="s">
         <v>231</v>
@@ -4259,10 +4260,10 @@
         <v>100</v>
       </c>
       <c r="O37" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="P37" s="4" t="s">
         <v>292</v>
-      </c>
-      <c r="P37" s="4" t="s">
-        <v>293</v>
       </c>
       <c r="Q37" s="3" t="s">
         <v>231</v>
@@ -4315,10 +4316,10 @@
         <v>100</v>
       </c>
       <c r="O38" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="P38" s="4" t="s">
         <v>294</v>
-      </c>
-      <c r="P38" s="4" t="s">
-        <v>295</v>
       </c>
       <c r="Q38" s="3" t="s">
         <v>231</v>
@@ -4371,10 +4372,10 @@
         <v>100</v>
       </c>
       <c r="O39" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="P39" s="4" t="s">
         <v>296</v>
-      </c>
-      <c r="P39" s="4" t="s">
-        <v>297</v>
       </c>
       <c r="Q39" s="3" t="s">
         <v>231</v>
@@ -4427,10 +4428,10 @@
         <v>100</v>
       </c>
       <c r="O40" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="P40" s="4" t="s">
         <v>298</v>
-      </c>
-      <c r="P40" s="4" t="s">
-        <v>299</v>
       </c>
       <c r="Q40" s="3" t="s">
         <v>231</v>
@@ -4483,10 +4484,10 @@
         <v>100</v>
       </c>
       <c r="O41" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="P41" s="4" t="s">
         <v>300</v>
-      </c>
-      <c r="P41" s="4" t="s">
-        <v>301</v>
       </c>
       <c r="Q41" s="3" t="s">
         <v>231</v>
@@ -4539,10 +4540,10 @@
         <v>100</v>
       </c>
       <c r="O42" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="P42" s="4" t="s">
         <v>302</v>
-      </c>
-      <c r="P42" s="4" t="s">
-        <v>303</v>
       </c>
       <c r="Q42" s="3" t="s">
         <v>231</v>
@@ -4595,10 +4596,10 @@
         <v>100</v>
       </c>
       <c r="O43" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="P43" s="4" t="s">
         <v>304</v>
-      </c>
-      <c r="P43" s="4" t="s">
-        <v>305</v>
       </c>
       <c r="Q43" s="3" t="s">
         <v>231</v>
@@ -4651,10 +4652,10 @@
         <v>100</v>
       </c>
       <c r="O44" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="P44" s="4" t="s">
         <v>306</v>
-      </c>
-      <c r="P44" s="4" t="s">
-        <v>307</v>
       </c>
       <c r="Q44" s="3" t="s">
         <v>231</v>
@@ -4707,10 +4708,10 @@
         <v>100</v>
       </c>
       <c r="O45" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="P45" s="4" t="s">
         <v>308</v>
-      </c>
-      <c r="P45" s="4" t="s">
-        <v>309</v>
       </c>
       <c r="Q45" s="3" t="s">
         <v>231</v>
@@ -4763,10 +4764,10 @@
         <v>100</v>
       </c>
       <c r="O46" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="P46" s="4" t="s">
         <v>310</v>
-      </c>
-      <c r="P46" s="4" t="s">
-        <v>311</v>
       </c>
       <c r="Q46" s="3" t="s">
         <v>231</v>
@@ -4819,10 +4820,10 @@
         <v>100</v>
       </c>
       <c r="O47" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="P47" s="4" t="s">
         <v>312</v>
-      </c>
-      <c r="P47" s="4" t="s">
-        <v>313</v>
       </c>
       <c r="Q47" s="3" t="s">
         <v>231</v>
@@ -4875,10 +4876,10 @@
         <v>100</v>
       </c>
       <c r="O48" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="P48" s="4" t="s">
         <v>314</v>
-      </c>
-      <c r="P48" s="4" t="s">
-        <v>315</v>
       </c>
       <c r="Q48" s="3" t="s">
         <v>231</v>
@@ -4931,10 +4932,10 @@
         <v>100</v>
       </c>
       <c r="O49" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="P49" s="4" t="s">
         <v>316</v>
-      </c>
-      <c r="P49" s="4" t="s">
-        <v>317</v>
       </c>
       <c r="Q49" s="3" t="s">
         <v>231</v>
@@ -4987,10 +4988,10 @@
         <v>100</v>
       </c>
       <c r="O50" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="P50" s="4" t="s">
         <v>318</v>
-      </c>
-      <c r="P50" s="4" t="s">
-        <v>319</v>
       </c>
       <c r="Q50" s="3" t="s">
         <v>231</v>
@@ -5043,10 +5044,10 @@
         <v>100</v>
       </c>
       <c r="O51" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="P51" s="4" t="s">
         <v>320</v>
-      </c>
-      <c r="P51" s="4" t="s">
-        <v>321</v>
       </c>
       <c r="Q51" s="3" t="s">
         <v>231</v>
@@ -5099,10 +5100,10 @@
         <v>100</v>
       </c>
       <c r="O52" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="P52" s="4" t="s">
         <v>322</v>
-      </c>
-      <c r="P52" s="4" t="s">
-        <v>323</v>
       </c>
       <c r="Q52" s="3" t="s">
         <v>231</v>
@@ -5155,10 +5156,10 @@
         <v>100</v>
       </c>
       <c r="O53" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="P53" s="4" t="s">
         <v>324</v>
-      </c>
-      <c r="P53" s="4" t="s">
-        <v>325</v>
       </c>
       <c r="Q53" s="3" t="s">
         <v>231</v>
@@ -5211,10 +5212,10 @@
         <v>100</v>
       </c>
       <c r="O54" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="P54" s="4" t="s">
         <v>326</v>
-      </c>
-      <c r="P54" s="4" t="s">
-        <v>327</v>
       </c>
       <c r="Q54" s="3" t="s">
         <v>231</v>
@@ -5267,10 +5268,10 @@
         <v>100</v>
       </c>
       <c r="O55" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="P55" s="4" t="s">
         <v>328</v>
-      </c>
-      <c r="P55" s="4" t="s">
-        <v>329</v>
       </c>
       <c r="Q55" s="3" t="s">
         <v>231</v>
@@ -5323,10 +5324,10 @@
         <v>100</v>
       </c>
       <c r="O56" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="P56" s="4" t="s">
         <v>330</v>
-      </c>
-      <c r="P56" s="4" t="s">
-        <v>331</v>
       </c>
       <c r="Q56" s="3" t="s">
         <v>231</v>
@@ -5379,10 +5380,10 @@
         <v>100</v>
       </c>
       <c r="O57" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="P57" s="4" t="s">
         <v>332</v>
-      </c>
-      <c r="P57" s="4" t="s">
-        <v>333</v>
       </c>
       <c r="Q57" s="3" t="s">
         <v>231</v>
@@ -5435,10 +5436,10 @@
         <v>100</v>
       </c>
       <c r="O58" s="4" t="s">
+        <v>333</v>
+      </c>
+      <c r="P58" s="4" t="s">
         <v>334</v>
-      </c>
-      <c r="P58" s="4" t="s">
-        <v>335</v>
       </c>
       <c r="Q58" s="3" t="s">
         <v>231</v>
@@ -5491,10 +5492,10 @@
         <v>100</v>
       </c>
       <c r="O59" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="P59" s="4" t="s">
         <v>336</v>
-      </c>
-      <c r="P59" s="4" t="s">
-        <v>337</v>
       </c>
       <c r="Q59" s="3" t="s">
         <v>231</v>
@@ -5547,10 +5548,10 @@
         <v>100</v>
       </c>
       <c r="O60" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="P60" s="4" t="s">
         <v>338</v>
-      </c>
-      <c r="P60" s="4" t="s">
-        <v>339</v>
       </c>
       <c r="Q60" s="3" t="s">
         <v>231</v>
@@ -5603,10 +5604,10 @@
         <v>100</v>
       </c>
       <c r="O61" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="P61" s="4" t="s">
         <v>340</v>
-      </c>
-      <c r="P61" s="4" t="s">
-        <v>341</v>
       </c>
       <c r="Q61" s="3" t="s">
         <v>231</v>
@@ -5659,10 +5660,10 @@
         <v>100</v>
       </c>
       <c r="O62" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="P62" s="4" t="s">
         <v>342</v>
-      </c>
-      <c r="P62" s="4" t="s">
-        <v>343</v>
       </c>
       <c r="Q62" s="3" t="s">
         <v>231</v>
@@ -5715,10 +5716,10 @@
         <v>100</v>
       </c>
       <c r="O63" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="P63" s="4" t="s">
         <v>344</v>
-      </c>
-      <c r="P63" s="4" t="s">
-        <v>345</v>
       </c>
       <c r="Q63" s="3" t="s">
         <v>231</v>
@@ -5771,10 +5772,10 @@
         <v>100</v>
       </c>
       <c r="O64" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="P64" s="4" t="s">
         <v>346</v>
-      </c>
-      <c r="P64" s="4" t="s">
-        <v>347</v>
       </c>
       <c r="Q64" s="3" t="s">
         <v>231</v>
@@ -5827,10 +5828,10 @@
         <v>100</v>
       </c>
       <c r="O65" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="P65" s="4" t="s">
         <v>348</v>
-      </c>
-      <c r="P65" s="4" t="s">
-        <v>349</v>
       </c>
       <c r="Q65" s="3" t="s">
         <v>231</v>
@@ -5883,10 +5884,10 @@
         <v>100</v>
       </c>
       <c r="O66" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="P66" s="4" t="s">
         <v>350</v>
-      </c>
-      <c r="P66" s="4" t="s">
-        <v>351</v>
       </c>
       <c r="Q66" s="3" t="s">
         <v>231</v>
@@ -5939,10 +5940,10 @@
         <v>100</v>
       </c>
       <c r="O67" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="P67" s="4" t="s">
         <v>352</v>
-      </c>
-      <c r="P67" s="4" t="s">
-        <v>353</v>
       </c>
       <c r="Q67" s="3" t="s">
         <v>231</v>
@@ -5995,10 +5996,10 @@
         <v>100</v>
       </c>
       <c r="O68" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="P68" s="4" t="s">
         <v>354</v>
-      </c>
-      <c r="P68" s="4" t="s">
-        <v>355</v>
       </c>
       <c r="Q68" s="3" t="s">
         <v>231</v>
@@ -6051,10 +6052,10 @@
         <v>100</v>
       </c>
       <c r="O69" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="P69" s="4" t="s">
         <v>356</v>
-      </c>
-      <c r="P69" s="4" t="s">
-        <v>357</v>
       </c>
       <c r="Q69" s="3" t="s">
         <v>231</v>
@@ -6107,10 +6108,10 @@
         <v>100</v>
       </c>
       <c r="O70" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="P70" s="4" t="s">
         <v>358</v>
-      </c>
-      <c r="P70" s="4" t="s">
-        <v>359</v>
       </c>
       <c r="Q70" s="3" t="s">
         <v>231</v>
@@ -6163,10 +6164,10 @@
         <v>100</v>
       </c>
       <c r="O71" s="4" t="s">
+        <v>359</v>
+      </c>
+      <c r="P71" s="4" t="s">
         <v>360</v>
-      </c>
-      <c r="P71" s="4" t="s">
-        <v>361</v>
       </c>
       <c r="Q71" s="3" t="s">
         <v>231</v>
@@ -6219,10 +6220,10 @@
         <v>100</v>
       </c>
       <c r="O72" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="P72" s="4" t="s">
         <v>362</v>
-      </c>
-      <c r="P72" s="4" t="s">
-        <v>363</v>
       </c>
       <c r="Q72" s="3" t="s">
         <v>231</v>
@@ -6275,10 +6276,10 @@
         <v>100</v>
       </c>
       <c r="O73" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="P73" s="4" t="s">
         <v>364</v>
-      </c>
-      <c r="P73" s="4" t="s">
-        <v>365</v>
       </c>
       <c r="Q73" s="3" t="s">
         <v>231</v>
@@ -6331,10 +6332,10 @@
         <v>100</v>
       </c>
       <c r="O74" s="4" t="s">
+        <v>365</v>
+      </c>
+      <c r="P74" s="4" t="s">
         <v>366</v>
-      </c>
-      <c r="P74" s="4" t="s">
-        <v>367</v>
       </c>
       <c r="Q74" s="3" t="s">
         <v>231</v>
@@ -6387,10 +6388,10 @@
         <v>100</v>
       </c>
       <c r="O75" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="P75" s="4" t="s">
         <v>368</v>
-      </c>
-      <c r="P75" s="4" t="s">
-        <v>369</v>
       </c>
       <c r="Q75" s="3" t="s">
         <v>231</v>
@@ -6443,10 +6444,10 @@
         <v>100</v>
       </c>
       <c r="O76" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="P76" s="4" t="s">
         <v>370</v>
-      </c>
-      <c r="P76" s="4" t="s">
-        <v>371</v>
       </c>
       <c r="Q76" s="3" t="s">
         <v>231</v>
@@ -6499,10 +6500,10 @@
         <v>100</v>
       </c>
       <c r="O77" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="P77" s="4" t="s">
         <v>372</v>
-      </c>
-      <c r="P77" s="4" t="s">
-        <v>373</v>
       </c>
       <c r="Q77" s="3" t="s">
         <v>231</v>
@@ -6555,10 +6556,10 @@
         <v>100</v>
       </c>
       <c r="O78" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="P78" s="4" t="s">
         <v>374</v>
-      </c>
-      <c r="P78" s="4" t="s">
-        <v>375</v>
       </c>
       <c r="Q78" s="3" t="s">
         <v>231</v>
@@ -6611,10 +6612,10 @@
         <v>100</v>
       </c>
       <c r="O79" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="P79" s="4" t="s">
         <v>376</v>
-      </c>
-      <c r="P79" s="4" t="s">
-        <v>377</v>
       </c>
       <c r="Q79" s="3" t="s">
         <v>231</v>
@@ -6667,10 +6668,10 @@
         <v>100</v>
       </c>
       <c r="O80" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="P80" s="4" t="s">
         <v>378</v>
-      </c>
-      <c r="P80" s="4" t="s">
-        <v>379</v>
       </c>
       <c r="Q80" s="3" t="s">
         <v>231</v>
@@ -6723,10 +6724,10 @@
         <v>100</v>
       </c>
       <c r="O81" s="4" t="s">
+        <v>379</v>
+      </c>
+      <c r="P81" s="4" t="s">
         <v>380</v>
-      </c>
-      <c r="P81" s="4" t="s">
-        <v>381</v>
       </c>
       <c r="Q81" s="3" t="s">
         <v>231</v>
@@ -6779,10 +6780,10 @@
         <v>100</v>
       </c>
       <c r="O82" s="4" t="s">
+        <v>381</v>
+      </c>
+      <c r="P82" s="4" t="s">
         <v>382</v>
-      </c>
-      <c r="P82" s="4" t="s">
-        <v>383</v>
       </c>
       <c r="Q82" s="3" t="s">
         <v>231</v>
@@ -6835,10 +6836,10 @@
         <v>100</v>
       </c>
       <c r="O83" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="P83" s="4" t="s">
         <v>384</v>
-      </c>
-      <c r="P83" s="4" t="s">
-        <v>385</v>
       </c>
       <c r="Q83" s="3" t="s">
         <v>231</v>
@@ -6891,10 +6892,10 @@
         <v>100</v>
       </c>
       <c r="O84" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="P84" s="4" t="s">
         <v>386</v>
-      </c>
-      <c r="P84" s="4" t="s">
-        <v>387</v>
       </c>
       <c r="Q84" s="3" t="s">
         <v>231</v>
@@ -6947,10 +6948,10 @@
         <v>100</v>
       </c>
       <c r="O85" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="P85" s="4" t="s">
         <v>388</v>
-      </c>
-      <c r="P85" s="4" t="s">
-        <v>389</v>
       </c>
       <c r="Q85" s="3" t="s">
         <v>231</v>
@@ -7003,10 +7004,10 @@
         <v>100</v>
       </c>
       <c r="O86" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="P86" s="4" t="s">
         <v>390</v>
-      </c>
-      <c r="P86" s="4" t="s">
-        <v>391</v>
       </c>
       <c r="Q86" s="3" t="s">
         <v>231</v>
@@ -7059,10 +7060,10 @@
         <v>100</v>
       </c>
       <c r="O87" s="4" t="s">
+        <v>391</v>
+      </c>
+      <c r="P87" s="4" t="s">
         <v>392</v>
-      </c>
-      <c r="P87" s="4" t="s">
-        <v>393</v>
       </c>
       <c r="Q87" s="3" t="s">
         <v>231</v>
@@ -7115,10 +7116,10 @@
         <v>100</v>
       </c>
       <c r="O88" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="P88" s="4" t="s">
         <v>394</v>
-      </c>
-      <c r="P88" s="4" t="s">
-        <v>395</v>
       </c>
       <c r="Q88" s="3" t="s">
         <v>231</v>
@@ -7171,10 +7172,10 @@
         <v>100</v>
       </c>
       <c r="O89" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="P89" s="4" t="s">
         <v>396</v>
-      </c>
-      <c r="P89" s="4" t="s">
-        <v>397</v>
       </c>
       <c r="Q89" s="3" t="s">
         <v>231</v>
@@ -7227,10 +7228,10 @@
         <v>100</v>
       </c>
       <c r="O90" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="P90" s="4" t="s">
         <v>398</v>
-      </c>
-      <c r="P90" s="4" t="s">
-        <v>399</v>
       </c>
       <c r="Q90" s="3" t="s">
         <v>231</v>
@@ -7283,10 +7284,10 @@
         <v>100</v>
       </c>
       <c r="O91" s="4" t="s">
+        <v>399</v>
+      </c>
+      <c r="P91" s="4" t="s">
         <v>400</v>
-      </c>
-      <c r="P91" s="4" t="s">
-        <v>401</v>
       </c>
       <c r="Q91" s="3" t="s">
         <v>231</v>
@@ -7339,10 +7340,10 @@
         <v>100</v>
       </c>
       <c r="O92" s="4" t="s">
+        <v>401</v>
+      </c>
+      <c r="P92" s="4" t="s">
         <v>402</v>
-      </c>
-      <c r="P92" s="4" t="s">
-        <v>403</v>
       </c>
       <c r="Q92" s="3" t="s">
         <v>231</v>
@@ -7395,10 +7396,10 @@
         <v>100</v>
       </c>
       <c r="O93" s="4" t="s">
+        <v>403</v>
+      </c>
+      <c r="P93" s="4" t="s">
         <v>404</v>
-      </c>
-      <c r="P93" s="4" t="s">
-        <v>405</v>
       </c>
       <c r="Q93" s="3" t="s">
         <v>231</v>
@@ -7451,10 +7452,10 @@
         <v>100</v>
       </c>
       <c r="O94" s="4" t="s">
+        <v>405</v>
+      </c>
+      <c r="P94" s="4" t="s">
         <v>406</v>
-      </c>
-      <c r="P94" s="4" t="s">
-        <v>407</v>
       </c>
       <c r="Q94" s="3" t="s">
         <v>231</v>
@@ -7507,10 +7508,10 @@
         <v>100</v>
       </c>
       <c r="O95" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="P95" s="4" t="s">
         <v>408</v>
-      </c>
-      <c r="P95" s="4" t="s">
-        <v>409</v>
       </c>
       <c r="Q95" s="3" t="s">
         <v>231</v>
@@ -7563,10 +7564,10 @@
         <v>100</v>
       </c>
       <c r="O96" s="4" t="s">
+        <v>409</v>
+      </c>
+      <c r="P96" s="4" t="s">
         <v>410</v>
-      </c>
-      <c r="P96" s="4" t="s">
-        <v>411</v>
       </c>
       <c r="Q96" s="3" t="s">
         <v>231</v>
@@ -7619,10 +7620,10 @@
         <v>100</v>
       </c>
       <c r="O97" s="4" t="s">
+        <v>411</v>
+      </c>
+      <c r="P97" s="4" t="s">
         <v>412</v>
-      </c>
-      <c r="P97" s="4" t="s">
-        <v>413</v>
       </c>
       <c r="Q97" s="3" t="s">
         <v>231</v>
@@ -7675,10 +7676,10 @@
         <v>100</v>
       </c>
       <c r="O98" s="4" t="s">
+        <v>413</v>
+      </c>
+      <c r="P98" s="4" t="s">
         <v>414</v>
-      </c>
-      <c r="P98" s="4" t="s">
-        <v>415</v>
       </c>
       <c r="Q98" s="3" t="s">
         <v>231</v>
@@ -7731,10 +7732,10 @@
         <v>100</v>
       </c>
       <c r="O99" s="4" t="s">
+        <v>415</v>
+      </c>
+      <c r="P99" s="4" t="s">
         <v>416</v>
-      </c>
-      <c r="P99" s="4" t="s">
-        <v>417</v>
       </c>
       <c r="Q99" s="3" t="s">
         <v>231</v>
@@ -7787,10 +7788,10 @@
         <v>100</v>
       </c>
       <c r="O100" s="4" t="s">
+        <v>417</v>
+      </c>
+      <c r="P100" s="4" t="s">
         <v>418</v>
-      </c>
-      <c r="P100" s="4" t="s">
-        <v>419</v>
       </c>
       <c r="Q100" s="3" t="s">
         <v>231</v>
@@ -7843,10 +7844,10 @@
         <v>100</v>
       </c>
       <c r="O101" s="4" t="s">
+        <v>419</v>
+      </c>
+      <c r="P101" s="4" t="s">
         <v>420</v>
-      </c>
-      <c r="P101" s="4" t="s">
-        <v>421</v>
       </c>
       <c r="Q101" s="3" t="s">
         <v>231</v>
@@ -7899,10 +7900,10 @@
         <v>100</v>
       </c>
       <c r="O102" s="4" t="s">
+        <v>421</v>
+      </c>
+      <c r="P102" s="4" t="s">
         <v>422</v>
-      </c>
-      <c r="P102" s="4" t="s">
-        <v>423</v>
       </c>
       <c r="Q102" s="3" t="s">
         <v>231</v>
@@ -7955,10 +7956,10 @@
         <v>100</v>
       </c>
       <c r="O103" s="4" t="s">
+        <v>423</v>
+      </c>
+      <c r="P103" s="4" t="s">
         <v>424</v>
-      </c>
-      <c r="P103" s="4" t="s">
-        <v>425</v>
       </c>
       <c r="Q103" s="3" t="s">
         <v>231</v>
@@ -8011,10 +8012,10 @@
         <v>100</v>
       </c>
       <c r="O104" s="4" t="s">
+        <v>425</v>
+      </c>
+      <c r="P104" s="4" t="s">
         <v>426</v>
-      </c>
-      <c r="P104" s="4" t="s">
-        <v>427</v>
       </c>
       <c r="Q104" s="3" t="s">
         <v>231</v>
@@ -8067,10 +8068,10 @@
         <v>100</v>
       </c>
       <c r="O105" s="4" t="s">
+        <v>427</v>
+      </c>
+      <c r="P105" s="4" t="s">
         <v>428</v>
-      </c>
-      <c r="P105" s="4" t="s">
-        <v>429</v>
       </c>
       <c r="Q105" s="3" t="s">
         <v>231</v>
@@ -8123,10 +8124,10 @@
         <v>100</v>
       </c>
       <c r="O106" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="P106" s="4" t="s">
         <v>430</v>
-      </c>
-      <c r="P106" s="4" t="s">
-        <v>431</v>
       </c>
       <c r="Q106" s="3" t="s">
         <v>231</v>
@@ -8179,10 +8180,10 @@
         <v>100</v>
       </c>
       <c r="O107" s="4" t="s">
+        <v>431</v>
+      </c>
+      <c r="P107" s="4" t="s">
         <v>432</v>
-      </c>
-      <c r="P107" s="4" t="s">
-        <v>433</v>
       </c>
       <c r="Q107" s="3" t="s">
         <v>231</v>
@@ -8235,10 +8236,10 @@
         <v>100</v>
       </c>
       <c r="O108" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="P108" s="4" t="s">
         <v>434</v>
-      </c>
-      <c r="P108" s="4" t="s">
-        <v>435</v>
       </c>
       <c r="Q108" s="3" t="s">
         <v>231</v>
@@ -8291,10 +8292,10 @@
         <v>100</v>
       </c>
       <c r="O109" s="4" t="s">
+        <v>435</v>
+      </c>
+      <c r="P109" s="4" t="s">
         <v>436</v>
-      </c>
-      <c r="P109" s="4" t="s">
-        <v>437</v>
       </c>
       <c r="Q109" s="3" t="s">
         <v>231</v>
@@ -8347,10 +8348,10 @@
         <v>100</v>
       </c>
       <c r="O110" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="P110" s="4" t="s">
         <v>438</v>
-      </c>
-      <c r="P110" s="4" t="s">
-        <v>439</v>
       </c>
       <c r="Q110" s="3" t="s">
         <v>231</v>
@@ -8403,10 +8404,10 @@
         <v>100</v>
       </c>
       <c r="O111" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="P111" s="4" t="s">
         <v>440</v>
-      </c>
-      <c r="P111" s="4" t="s">
-        <v>441</v>
       </c>
       <c r="Q111" s="3" t="s">
         <v>231</v>
@@ -8459,10 +8460,10 @@
         <v>100</v>
       </c>
       <c r="O112" s="4" t="s">
+        <v>441</v>
+      </c>
+      <c r="P112" s="4" t="s">
         <v>442</v>
-      </c>
-      <c r="P112" s="4" t="s">
-        <v>443</v>
       </c>
       <c r="Q112" s="3" t="s">
         <v>231</v>
@@ -8515,10 +8516,10 @@
         <v>100</v>
       </c>
       <c r="O113" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="P113" s="4" t="s">
         <v>444</v>
-      </c>
-      <c r="P113" s="4" t="s">
-        <v>445</v>
       </c>
       <c r="Q113" s="3" t="s">
         <v>231</v>
@@ -8571,10 +8572,10 @@
         <v>100</v>
       </c>
       <c r="O114" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="P114" s="4" t="s">
         <v>446</v>
-      </c>
-      <c r="P114" s="4" t="s">
-        <v>447</v>
       </c>
       <c r="Q114" s="3" t="s">
         <v>231</v>
@@ -8627,10 +8628,10 @@
         <v>100</v>
       </c>
       <c r="O115" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="P115" s="4" t="s">
         <v>448</v>
-      </c>
-      <c r="P115" s="4" t="s">
-        <v>449</v>
       </c>
       <c r="Q115" s="3" t="s">
         <v>231</v>
@@ -8683,10 +8684,10 @@
         <v>100</v>
       </c>
       <c r="O116" s="4" t="s">
+        <v>449</v>
+      </c>
+      <c r="P116" s="4" t="s">
         <v>450</v>
-      </c>
-      <c r="P116" s="4" t="s">
-        <v>451</v>
       </c>
       <c r="Q116" s="3" t="s">
         <v>231</v>
@@ -8739,10 +8740,10 @@
         <v>100</v>
       </c>
       <c r="O117" s="4" t="s">
+        <v>451</v>
+      </c>
+      <c r="P117" s="4" t="s">
         <v>452</v>
-      </c>
-      <c r="P117" s="4" t="s">
-        <v>453</v>
       </c>
       <c r="Q117" s="3" t="s">
         <v>231</v>
@@ -8795,10 +8796,10 @@
         <v>100</v>
       </c>
       <c r="O118" s="4" t="s">
+        <v>453</v>
+      </c>
+      <c r="P118" s="4" t="s">
         <v>454</v>
-      </c>
-      <c r="P118" s="4" t="s">
-        <v>455</v>
       </c>
       <c r="Q118" s="3" t="s">
         <v>231</v>
@@ -8851,10 +8852,10 @@
         <v>100</v>
       </c>
       <c r="O119" s="4" t="s">
+        <v>455</v>
+      </c>
+      <c r="P119" s="4" t="s">
         <v>456</v>
-      </c>
-      <c r="P119" s="4" t="s">
-        <v>457</v>
       </c>
       <c r="Q119" s="3" t="s">
         <v>231</v>
@@ -8907,10 +8908,10 @@
         <v>100</v>
       </c>
       <c r="O120" s="4" t="s">
+        <v>457</v>
+      </c>
+      <c r="P120" s="4" t="s">
         <v>458</v>
-      </c>
-      <c r="P120" s="4" t="s">
-        <v>459</v>
       </c>
       <c r="Q120" s="3" t="s">
         <v>231</v>
@@ -8963,10 +8964,10 @@
         <v>100</v>
       </c>
       <c r="O121" s="4" t="s">
+        <v>459</v>
+      </c>
+      <c r="P121" s="4" t="s">
         <v>460</v>
-      </c>
-      <c r="P121" s="4" t="s">
-        <v>461</v>
       </c>
       <c r="Q121" s="3" t="s">
         <v>231</v>
@@ -9019,10 +9020,10 @@
         <v>100</v>
       </c>
       <c r="O122" s="4" t="s">
+        <v>461</v>
+      </c>
+      <c r="P122" s="4" t="s">
         <v>462</v>
-      </c>
-      <c r="P122" s="4" t="s">
-        <v>463</v>
       </c>
       <c r="Q122" s="3" t="s">
         <v>231</v>
@@ -9075,10 +9076,10 @@
         <v>100</v>
       </c>
       <c r="O123" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="P123" s="4" t="s">
         <v>464</v>
-      </c>
-      <c r="P123" s="4" t="s">
-        <v>465</v>
       </c>
       <c r="Q123" s="3" t="s">
         <v>231</v>
@@ -9131,10 +9132,10 @@
         <v>100</v>
       </c>
       <c r="O124" s="4" t="s">
+        <v>465</v>
+      </c>
+      <c r="P124" s="4" t="s">
         <v>466</v>
-      </c>
-      <c r="P124" s="4" t="s">
-        <v>467</v>
       </c>
       <c r="Q124" s="3" t="s">
         <v>231</v>
@@ -9187,10 +9188,10 @@
         <v>100</v>
       </c>
       <c r="O125" s="4" t="s">
+        <v>467</v>
+      </c>
+      <c r="P125" s="4" t="s">
         <v>468</v>
-      </c>
-      <c r="P125" s="4" t="s">
-        <v>469</v>
       </c>
       <c r="Q125" s="3" t="s">
         <v>231</v>
@@ -9243,10 +9244,10 @@
         <v>100</v>
       </c>
       <c r="O126" s="4" t="s">
+        <v>469</v>
+      </c>
+      <c r="P126" s="4" t="s">
         <v>470</v>
-      </c>
-      <c r="P126" s="4" t="s">
-        <v>471</v>
       </c>
       <c r="Q126" s="3" t="s">
         <v>231</v>
@@ -9299,10 +9300,10 @@
         <v>100</v>
       </c>
       <c r="O127" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="P127" s="4" t="s">
         <v>472</v>
-      </c>
-      <c r="P127" s="4" t="s">
-        <v>473</v>
       </c>
       <c r="Q127" s="3" t="s">
         <v>231</v>
@@ -9355,10 +9356,10 @@
         <v>100</v>
       </c>
       <c r="O128" s="4" t="s">
+        <v>473</v>
+      </c>
+      <c r="P128" s="4" t="s">
         <v>474</v>
-      </c>
-      <c r="P128" s="4" t="s">
-        <v>475</v>
       </c>
       <c r="Q128" s="3" t="s">
         <v>231</v>
@@ -9411,10 +9412,10 @@
         <v>100</v>
       </c>
       <c r="O129" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="P129" s="4" t="s">
         <v>476</v>
-      </c>
-      <c r="P129" s="4" t="s">
-        <v>477</v>
       </c>
       <c r="Q129" s="3" t="s">
         <v>231</v>
@@ -9467,10 +9468,10 @@
         <v>100</v>
       </c>
       <c r="O130" s="4" t="s">
+        <v>477</v>
+      </c>
+      <c r="P130" s="4" t="s">
         <v>478</v>
-      </c>
-      <c r="P130" s="4" t="s">
-        <v>479</v>
       </c>
       <c r="Q130" s="3" t="s">
         <v>231</v>
@@ -9523,10 +9524,10 @@
         <v>100</v>
       </c>
       <c r="O131" s="4" t="s">
+        <v>479</v>
+      </c>
+      <c r="P131" s="4" t="s">
         <v>480</v>
-      </c>
-      <c r="P131" s="4" t="s">
-        <v>481</v>
       </c>
       <c r="Q131" s="3" t="s">
         <v>231</v>
@@ -9579,10 +9580,10 @@
         <v>100</v>
       </c>
       <c r="O132" s="4" t="s">
+        <v>481</v>
+      </c>
+      <c r="P132" s="4" t="s">
         <v>482</v>
-      </c>
-      <c r="P132" s="4" t="s">
-        <v>483</v>
       </c>
       <c r="Q132" s="3" t="s">
         <v>231</v>
@@ -9635,10 +9636,10 @@
         <v>100</v>
       </c>
       <c r="O133" s="4" t="s">
+        <v>483</v>
+      </c>
+      <c r="P133" s="4" t="s">
         <v>484</v>
-      </c>
-      <c r="P133" s="4" t="s">
-        <v>485</v>
       </c>
       <c r="Q133" s="3" t="s">
         <v>231</v>
@@ -9691,10 +9692,10 @@
         <v>100</v>
       </c>
       <c r="O134" s="4" t="s">
+        <v>485</v>
+      </c>
+      <c r="P134" s="4" t="s">
         <v>486</v>
-      </c>
-      <c r="P134" s="4" t="s">
-        <v>487</v>
       </c>
       <c r="Q134" s="3" t="s">
         <v>231</v>
@@ -9747,10 +9748,10 @@
         <v>100</v>
       </c>
       <c r="O135" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="P135" s="4" t="s">
         <v>488</v>
-      </c>
-      <c r="P135" s="4" t="s">
-        <v>489</v>
       </c>
       <c r="Q135" s="3" t="s">
         <v>231</v>
@@ -9803,10 +9804,10 @@
         <v>100</v>
       </c>
       <c r="O136" s="4" t="s">
+        <v>489</v>
+      </c>
+      <c r="P136" s="4" t="s">
         <v>490</v>
-      </c>
-      <c r="P136" s="4" t="s">
-        <v>491</v>
       </c>
       <c r="Q136" s="3" t="s">
         <v>231</v>
@@ -9859,10 +9860,10 @@
         <v>100</v>
       </c>
       <c r="O137" s="4" t="s">
+        <v>491</v>
+      </c>
+      <c r="P137" s="4" t="s">
         <v>492</v>
-      </c>
-      <c r="P137" s="4" t="s">
-        <v>493</v>
       </c>
       <c r="Q137" s="3" t="s">
         <v>231</v>
@@ -9915,10 +9916,10 @@
         <v>100</v>
       </c>
       <c r="O138" s="4" t="s">
+        <v>493</v>
+      </c>
+      <c r="P138" s="4" t="s">
         <v>494</v>
-      </c>
-      <c r="P138" s="4" t="s">
-        <v>495</v>
       </c>
       <c r="Q138" s="3" t="s">
         <v>231</v>
@@ -9971,10 +9972,10 @@
         <v>100</v>
       </c>
       <c r="O139" s="4" t="s">
+        <v>495</v>
+      </c>
+      <c r="P139" s="4" t="s">
         <v>496</v>
-      </c>
-      <c r="P139" s="4" t="s">
-        <v>497</v>
       </c>
       <c r="Q139" s="3" t="s">
         <v>231</v>
@@ -10027,10 +10028,10 @@
         <v>100</v>
       </c>
       <c r="O140" s="4" t="s">
+        <v>497</v>
+      </c>
+      <c r="P140" s="4" t="s">
         <v>498</v>
-      </c>
-      <c r="P140" s="4" t="s">
-        <v>499</v>
       </c>
       <c r="Q140" s="3" t="s">
         <v>231</v>
@@ -10083,10 +10084,10 @@
         <v>100</v>
       </c>
       <c r="O141" s="4" t="s">
+        <v>499</v>
+      </c>
+      <c r="P141" s="4" t="s">
         <v>500</v>
-      </c>
-      <c r="P141" s="4" t="s">
-        <v>501</v>
       </c>
       <c r="Q141" s="3" t="s">
         <v>231</v>
@@ -10139,10 +10140,10 @@
         <v>100</v>
       </c>
       <c r="O142" s="4" t="s">
+        <v>501</v>
+      </c>
+      <c r="P142" s="4" t="s">
         <v>502</v>
-      </c>
-      <c r="P142" s="4" t="s">
-        <v>503</v>
       </c>
       <c r="Q142" s="3" t="s">
         <v>231</v>
@@ -10195,10 +10196,10 @@
         <v>100</v>
       </c>
       <c r="O143" s="4" t="s">
+        <v>503</v>
+      </c>
+      <c r="P143" s="4" t="s">
         <v>504</v>
-      </c>
-      <c r="P143" s="4" t="s">
-        <v>505</v>
       </c>
       <c r="Q143" s="3" t="s">
         <v>231</v>
@@ -10251,10 +10252,10 @@
         <v>100</v>
       </c>
       <c r="O144" s="4" t="s">
+        <v>505</v>
+      </c>
+      <c r="P144" s="4" t="s">
         <v>506</v>
-      </c>
-      <c r="P144" s="4" t="s">
-        <v>507</v>
       </c>
       <c r="Q144" s="3" t="s">
         <v>231</v>
@@ -10307,10 +10308,10 @@
         <v>100</v>
       </c>
       <c r="O145" s="4" t="s">
+        <v>507</v>
+      </c>
+      <c r="P145" s="4" t="s">
         <v>508</v>
-      </c>
-      <c r="P145" s="4" t="s">
-        <v>509</v>
       </c>
       <c r="Q145" s="3" t="s">
         <v>231</v>
@@ -10363,10 +10364,10 @@
         <v>100</v>
       </c>
       <c r="O146" s="4" t="s">
+        <v>509</v>
+      </c>
+      <c r="P146" s="4" t="s">
         <v>510</v>
-      </c>
-      <c r="P146" s="4" t="s">
-        <v>511</v>
       </c>
       <c r="Q146" s="3" t="s">
         <v>231</v>
@@ -10419,10 +10420,10 @@
         <v>100</v>
       </c>
       <c r="O147" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="P147" s="4" t="s">
         <v>512</v>
-      </c>
-      <c r="P147" s="4" t="s">
-        <v>513</v>
       </c>
       <c r="Q147" s="3" t="s">
         <v>231</v>
@@ -10475,10 +10476,10 @@
         <v>100</v>
       </c>
       <c r="O148" s="4" t="s">
+        <v>513</v>
+      </c>
+      <c r="P148" s="4" t="s">
         <v>514</v>
-      </c>
-      <c r="P148" s="4" t="s">
-        <v>515</v>
       </c>
       <c r="Q148" s="3" t="s">
         <v>231</v>
@@ -10531,10 +10532,10 @@
         <v>100</v>
       </c>
       <c r="O149" s="4" t="s">
+        <v>515</v>
+      </c>
+      <c r="P149" s="4" t="s">
         <v>516</v>
-      </c>
-      <c r="P149" s="4" t="s">
-        <v>517</v>
       </c>
       <c r="Q149" s="3" t="s">
         <v>231</v>
@@ -10587,10 +10588,10 @@
         <v>100</v>
       </c>
       <c r="O150" s="4" t="s">
+        <v>517</v>
+      </c>
+      <c r="P150" s="4" t="s">
         <v>518</v>
-      </c>
-      <c r="P150" s="4" t="s">
-        <v>519</v>
       </c>
       <c r="Q150" s="3" t="s">
         <v>231</v>
@@ -10643,10 +10644,10 @@
         <v>100</v>
       </c>
       <c r="O151" s="4" t="s">
+        <v>519</v>
+      </c>
+      <c r="P151" s="4" t="s">
         <v>520</v>
-      </c>
-      <c r="P151" s="4" t="s">
-        <v>521</v>
       </c>
       <c r="Q151" s="3" t="s">
         <v>231</v>
@@ -10699,10 +10700,10 @@
         <v>100</v>
       </c>
       <c r="O152" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="P152" s="4" t="s">
         <v>522</v>
-      </c>
-      <c r="P152" s="4" t="s">
-        <v>523</v>
       </c>
       <c r="Q152" s="3" t="s">
         <v>231</v>
@@ -10755,10 +10756,10 @@
         <v>100</v>
       </c>
       <c r="O153" s="4" t="s">
+        <v>523</v>
+      </c>
+      <c r="P153" s="4" t="s">
         <v>524</v>
-      </c>
-      <c r="P153" s="4" t="s">
-        <v>525</v>
       </c>
       <c r="Q153" s="3" t="s">
         <v>231</v>
@@ -10811,10 +10812,10 @@
         <v>100</v>
       </c>
       <c r="O154" s="4" t="s">
+        <v>525</v>
+      </c>
+      <c r="P154" s="4" t="s">
         <v>526</v>
-      </c>
-      <c r="P154" s="4" t="s">
-        <v>527</v>
       </c>
       <c r="Q154" s="3" t="s">
         <v>231</v>
@@ -10867,10 +10868,10 @@
         <v>100</v>
       </c>
       <c r="O155" s="4" t="s">
+        <v>527</v>
+      </c>
+      <c r="P155" s="4" t="s">
         <v>528</v>
-      </c>
-      <c r="P155" s="4" t="s">
-        <v>529</v>
       </c>
       <c r="Q155" s="3" t="s">
         <v>231</v>
@@ -10923,10 +10924,10 @@
         <v>100</v>
       </c>
       <c r="O156" s="4" t="s">
+        <v>529</v>
+      </c>
+      <c r="P156" s="4" t="s">
         <v>530</v>
-      </c>
-      <c r="P156" s="4" t="s">
-        <v>531</v>
       </c>
       <c r="Q156" s="3" t="s">
         <v>231</v>
@@ -10979,10 +10980,10 @@
         <v>100</v>
       </c>
       <c r="O157" s="4" t="s">
+        <v>531</v>
+      </c>
+      <c r="P157" s="4" t="s">
         <v>532</v>
-      </c>
-      <c r="P157" s="4" t="s">
-        <v>533</v>
       </c>
       <c r="Q157" s="3" t="s">
         <v>231</v>
@@ -11035,10 +11036,10 @@
         <v>100</v>
       </c>
       <c r="O158" s="4" t="s">
+        <v>533</v>
+      </c>
+      <c r="P158" s="4" t="s">
         <v>534</v>
-      </c>
-      <c r="P158" s="4" t="s">
-        <v>535</v>
       </c>
       <c r="Q158" s="3" t="s">
         <v>231</v>
@@ -11091,10 +11092,10 @@
         <v>100</v>
       </c>
       <c r="O159" s="4" t="s">
+        <v>535</v>
+      </c>
+      <c r="P159" s="4" t="s">
         <v>536</v>
-      </c>
-      <c r="P159" s="4" t="s">
-        <v>537</v>
       </c>
       <c r="Q159" s="3" t="s">
         <v>231</v>
@@ -11147,10 +11148,10 @@
         <v>100</v>
       </c>
       <c r="O160" s="4" t="s">
+        <v>537</v>
+      </c>
+      <c r="P160" s="4" t="s">
         <v>538</v>
-      </c>
-      <c r="P160" s="4" t="s">
-        <v>539</v>
       </c>
       <c r="Q160" s="3" t="s">
         <v>231</v>
@@ -11203,10 +11204,10 @@
         <v>100</v>
       </c>
       <c r="O161" s="4" t="s">
+        <v>539</v>
+      </c>
+      <c r="P161" s="4" t="s">
         <v>540</v>
-      </c>
-      <c r="P161" s="4" t="s">
-        <v>541</v>
       </c>
       <c r="Q161" s="3" t="s">
         <v>231</v>
@@ -11259,10 +11260,10 @@
         <v>100</v>
       </c>
       <c r="O162" s="4" t="s">
+        <v>541</v>
+      </c>
+      <c r="P162" s="4" t="s">
         <v>542</v>
-      </c>
-      <c r="P162" s="4" t="s">
-        <v>543</v>
       </c>
       <c r="Q162" s="3" t="s">
         <v>231</v>
@@ -11315,10 +11316,10 @@
         <v>100</v>
       </c>
       <c r="O163" s="4" t="s">
+        <v>543</v>
+      </c>
+      <c r="P163" s="4" t="s">
         <v>544</v>
-      </c>
-      <c r="P163" s="4" t="s">
-        <v>545</v>
       </c>
       <c r="Q163" s="3" t="s">
         <v>231</v>
@@ -11371,10 +11372,10 @@
         <v>100</v>
       </c>
       <c r="O164" s="4" t="s">
+        <v>545</v>
+      </c>
+      <c r="P164" s="4" t="s">
         <v>546</v>
-      </c>
-      <c r="P164" s="4" t="s">
-        <v>547</v>
       </c>
       <c r="Q164" s="3" t="s">
         <v>231</v>

--- a/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FEC06B5-ACB7-4ED9-9494-53D68DAD9334}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBC8A19E-81F2-4B59-BBB2-8E6F6D21E231}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1212" uniqueCount="577">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2430" uniqueCount="612">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -840,10 +840,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>10001:160</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>10001:240</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1740,12 +1736,6 @@
     <t>1600001:101_0:101</t>
   </si>
   <si>
-    <t>10001:100_0:100</t>
-  </si>
-  <si>
-    <t>10001:101_0:101</t>
-  </si>
-  <si>
     <t>20001:100_0:100</t>
   </si>
   <si>
@@ -1838,6 +1828,123 @@
   <si>
     <t>120001:102_0:102</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10001:102_0:101</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10001:1101_0:100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10001:150</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20001:100</t>
+  </si>
+  <si>
+    <t>30001:100</t>
+  </si>
+  <si>
+    <t>40001:100</t>
+  </si>
+  <si>
+    <t>50001:100</t>
+  </si>
+  <si>
+    <t>60001:100</t>
+  </si>
+  <si>
+    <t>70001:100</t>
+  </si>
+  <si>
+    <t>80001:100</t>
+  </si>
+  <si>
+    <t>90001:100</t>
+  </si>
+  <si>
+    <t>100001:00</t>
+  </si>
+  <si>
+    <t>130001:00</t>
+  </si>
+  <si>
+    <t>140001:00</t>
+  </si>
+  <si>
+    <t>150001:00</t>
+  </si>
+  <si>
+    <t>160001:00</t>
+  </si>
+  <si>
+    <t>170001:00</t>
+  </si>
+  <si>
+    <t>180001:00</t>
+  </si>
+  <si>
+    <t>190001:00</t>
+  </si>
+  <si>
+    <t>200001:00</t>
+  </si>
+  <si>
+    <t>210001:00</t>
+  </si>
+  <si>
+    <t>220001:00</t>
+  </si>
+  <si>
+    <t>230001:00</t>
+  </si>
+  <si>
+    <t>240001:00</t>
+  </si>
+  <si>
+    <t>250001:00</t>
+  </si>
+  <si>
+    <t>260001:00</t>
+  </si>
+  <si>
+    <t>270001:00</t>
+  </si>
+  <si>
+    <t>280001:00</t>
+  </si>
+  <si>
+    <t>290001:00</t>
+  </si>
+  <si>
+    <t>300001:00</t>
+  </si>
+  <si>
+    <t>310001:00</t>
+  </si>
+  <si>
+    <t>320001:00</t>
+  </si>
+  <si>
+    <t>330001:00</t>
+  </si>
+  <si>
+    <t>340001:00</t>
+  </si>
+  <si>
+    <t>350001:00</t>
+  </si>
+  <si>
+    <t>360001:00</t>
+  </si>
+  <si>
+    <t>370001:00</t>
+  </si>
+  <si>
+    <t>380001:00</t>
   </si>
 </sst>
 </file>
@@ -2246,10 +2353,10 @@
         <v>220</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="Q2" s="1" t="s">
         <v>227</v>
@@ -2441,10 +2548,10 @@
         <v>150</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>547</v>
+        <v>575</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>548</v>
+        <v>574</v>
       </c>
       <c r="Q5" s="3" t="s">
         <v>231</v>
@@ -2456,10 +2563,10 @@
         <v>247</v>
       </c>
       <c r="T5" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="U5" s="1" t="s">
         <v>248</v>
-      </c>
-      <c r="U5" s="1" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.15">
@@ -2506,10 +2613,10 @@
         <v>200</v>
       </c>
       <c r="O6" s="4" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="P6" s="4" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="Q6" s="3" t="s">
         <v>231</v>
@@ -2562,10 +2669,10 @@
         <v>300</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="P7" s="4" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="Q7" s="3" t="s">
         <v>231</v>
@@ -2618,10 +2725,10 @@
         <v>400</v>
       </c>
       <c r="O8" s="4" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="P8" s="4" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="Q8" s="3" t="s">
         <v>231</v>
@@ -2674,10 +2781,10 @@
         <v>500</v>
       </c>
       <c r="O9" s="4" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="P9" s="4" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="Q9" s="3" t="s">
         <v>231</v>
@@ -2730,10 +2837,10 @@
         <v>600</v>
       </c>
       <c r="O10" s="4" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="P10" s="4" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="Q10" s="3" t="s">
         <v>231</v>
@@ -2786,10 +2893,10 @@
         <v>100</v>
       </c>
       <c r="O11" s="4" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P11" s="4" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="Q11" s="3" t="s">
         <v>231</v>
@@ -2842,10 +2949,10 @@
         <v>100</v>
       </c>
       <c r="O12" s="4" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="P12" s="4" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="Q12" s="3" t="s">
         <v>231</v>
@@ -2898,10 +3005,10 @@
         <v>100</v>
       </c>
       <c r="O13" s="4" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="P13" s="4" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="Q13" s="3" t="s">
         <v>231</v>
@@ -2954,10 +3061,10 @@
         <v>100</v>
       </c>
       <c r="O14" s="4" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="P14" s="4" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>231</v>
@@ -3010,10 +3117,10 @@
         <v>100</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="Q15" s="3" t="s">
         <v>231</v>
@@ -3022,13 +3129,13 @@
         <v>0</v>
       </c>
       <c r="S15" s="1" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="T15" s="1" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="U15" s="1" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.15">
@@ -3075,10 +3182,10 @@
         <v>100</v>
       </c>
       <c r="O16" s="4" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="P16" s="4" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="Q16" s="3" t="s">
         <v>231</v>
@@ -3087,13 +3194,13 @@
         <v>0</v>
       </c>
       <c r="S16" s="1" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="T16" s="1" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="U16" s="1" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.15">
@@ -3140,10 +3247,10 @@
         <v>100</v>
       </c>
       <c r="O17" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="P17" s="4" t="s">
         <v>251</v>
-      </c>
-      <c r="P17" s="4" t="s">
-        <v>252</v>
       </c>
       <c r="Q17" s="3" t="s">
         <v>231</v>
@@ -3196,10 +3303,10 @@
         <v>100</v>
       </c>
       <c r="O18" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="P18" s="4" t="s">
         <v>253</v>
-      </c>
-      <c r="P18" s="4" t="s">
-        <v>254</v>
       </c>
       <c r="Q18" s="3" t="s">
         <v>231</v>
@@ -3252,10 +3359,10 @@
         <v>100</v>
       </c>
       <c r="O19" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="P19" s="4" t="s">
         <v>255</v>
-      </c>
-      <c r="P19" s="4" t="s">
-        <v>256</v>
       </c>
       <c r="Q19" s="3" t="s">
         <v>231</v>
@@ -3308,10 +3415,10 @@
         <v>100</v>
       </c>
       <c r="O20" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="P20" s="4" t="s">
         <v>257</v>
-      </c>
-      <c r="P20" s="4" t="s">
-        <v>258</v>
       </c>
       <c r="Q20" s="3" t="s">
         <v>231</v>
@@ -3364,10 +3471,10 @@
         <v>100</v>
       </c>
       <c r="O21" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="P21" s="4" t="s">
         <v>259</v>
-      </c>
-      <c r="P21" s="4" t="s">
-        <v>260</v>
       </c>
       <c r="Q21" s="3" t="s">
         <v>231</v>
@@ -3420,10 +3527,10 @@
         <v>100</v>
       </c>
       <c r="O22" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="P22" s="4" t="s">
         <v>261</v>
-      </c>
-      <c r="P22" s="4" t="s">
-        <v>262</v>
       </c>
       <c r="Q22" s="3" t="s">
         <v>231</v>
@@ -3476,10 +3583,10 @@
         <v>100</v>
       </c>
       <c r="O23" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="P23" s="4" t="s">
         <v>263</v>
-      </c>
-      <c r="P23" s="4" t="s">
-        <v>264</v>
       </c>
       <c r="Q23" s="3" t="s">
         <v>231</v>
@@ -3532,10 +3639,10 @@
         <v>100</v>
       </c>
       <c r="O24" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="P24" s="4" t="s">
         <v>265</v>
-      </c>
-      <c r="P24" s="4" t="s">
-        <v>266</v>
       </c>
       <c r="Q24" s="3" t="s">
         <v>231</v>
@@ -3588,10 +3695,10 @@
         <v>100</v>
       </c>
       <c r="O25" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="P25" s="4" t="s">
         <v>267</v>
-      </c>
-      <c r="P25" s="4" t="s">
-        <v>268</v>
       </c>
       <c r="Q25" s="3" t="s">
         <v>231</v>
@@ -3644,10 +3751,10 @@
         <v>100</v>
       </c>
       <c r="O26" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="P26" s="4" t="s">
         <v>269</v>
-      </c>
-      <c r="P26" s="4" t="s">
-        <v>270</v>
       </c>
       <c r="Q26" s="3" t="s">
         <v>231</v>
@@ -3700,10 +3807,10 @@
         <v>100</v>
       </c>
       <c r="O27" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="P27" s="4" t="s">
         <v>271</v>
-      </c>
-      <c r="P27" s="4" t="s">
-        <v>272</v>
       </c>
       <c r="Q27" s="3" t="s">
         <v>231</v>
@@ -3756,10 +3863,10 @@
         <v>100</v>
       </c>
       <c r="O28" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="P28" s="4" t="s">
         <v>273</v>
-      </c>
-      <c r="P28" s="4" t="s">
-        <v>274</v>
       </c>
       <c r="Q28" s="3" t="s">
         <v>231</v>
@@ -3812,10 +3919,10 @@
         <v>100</v>
       </c>
       <c r="O29" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="P29" s="4" t="s">
         <v>275</v>
-      </c>
-      <c r="P29" s="4" t="s">
-        <v>276</v>
       </c>
       <c r="Q29" s="3" t="s">
         <v>231</v>
@@ -3868,10 +3975,10 @@
         <v>100</v>
       </c>
       <c r="O30" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="P30" s="4" t="s">
         <v>277</v>
-      </c>
-      <c r="P30" s="4" t="s">
-        <v>278</v>
       </c>
       <c r="Q30" s="3" t="s">
         <v>231</v>
@@ -3924,10 +4031,10 @@
         <v>100</v>
       </c>
       <c r="O31" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="P31" s="4" t="s">
         <v>279</v>
-      </c>
-      <c r="P31" s="4" t="s">
-        <v>280</v>
       </c>
       <c r="Q31" s="3" t="s">
         <v>231</v>
@@ -3980,10 +4087,10 @@
         <v>100</v>
       </c>
       <c r="O32" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="P32" s="4" t="s">
         <v>281</v>
-      </c>
-      <c r="P32" s="4" t="s">
-        <v>282</v>
       </c>
       <c r="Q32" s="3" t="s">
         <v>231</v>
@@ -4036,10 +4143,10 @@
         <v>100</v>
       </c>
       <c r="O33" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="P33" s="4" t="s">
         <v>283</v>
-      </c>
-      <c r="P33" s="4" t="s">
-        <v>284</v>
       </c>
       <c r="Q33" s="3" t="s">
         <v>231</v>
@@ -4092,10 +4199,10 @@
         <v>100</v>
       </c>
       <c r="O34" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="P34" s="4" t="s">
         <v>285</v>
-      </c>
-      <c r="P34" s="4" t="s">
-        <v>286</v>
       </c>
       <c r="Q34" s="3" t="s">
         <v>231</v>
@@ -4148,10 +4255,10 @@
         <v>100</v>
       </c>
       <c r="O35" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="P35" s="4" t="s">
         <v>287</v>
-      </c>
-      <c r="P35" s="4" t="s">
-        <v>288</v>
       </c>
       <c r="Q35" s="3" t="s">
         <v>231</v>
@@ -4204,10 +4311,10 @@
         <v>100</v>
       </c>
       <c r="O36" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="P36" s="4" t="s">
         <v>289</v>
-      </c>
-      <c r="P36" s="4" t="s">
-        <v>290</v>
       </c>
       <c r="Q36" s="3" t="s">
         <v>231</v>
@@ -4260,10 +4367,10 @@
         <v>100</v>
       </c>
       <c r="O37" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="P37" s="4" t="s">
         <v>291</v>
-      </c>
-      <c r="P37" s="4" t="s">
-        <v>292</v>
       </c>
       <c r="Q37" s="3" t="s">
         <v>231</v>
@@ -4316,10 +4423,10 @@
         <v>100</v>
       </c>
       <c r="O38" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="P38" s="4" t="s">
         <v>293</v>
-      </c>
-      <c r="P38" s="4" t="s">
-        <v>294</v>
       </c>
       <c r="Q38" s="3" t="s">
         <v>231</v>
@@ -4372,10 +4479,10 @@
         <v>100</v>
       </c>
       <c r="O39" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="P39" s="4" t="s">
         <v>295</v>
-      </c>
-      <c r="P39" s="4" t="s">
-        <v>296</v>
       </c>
       <c r="Q39" s="3" t="s">
         <v>231</v>
@@ -4428,10 +4535,10 @@
         <v>100</v>
       </c>
       <c r="O40" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="P40" s="4" t="s">
         <v>297</v>
-      </c>
-      <c r="P40" s="4" t="s">
-        <v>298</v>
       </c>
       <c r="Q40" s="3" t="s">
         <v>231</v>
@@ -4484,10 +4591,10 @@
         <v>100</v>
       </c>
       <c r="O41" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="P41" s="4" t="s">
         <v>299</v>
-      </c>
-      <c r="P41" s="4" t="s">
-        <v>300</v>
       </c>
       <c r="Q41" s="3" t="s">
         <v>231</v>
@@ -4540,10 +4647,10 @@
         <v>100</v>
       </c>
       <c r="O42" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="P42" s="4" t="s">
         <v>301</v>
-      </c>
-      <c r="P42" s="4" t="s">
-        <v>302</v>
       </c>
       <c r="Q42" s="3" t="s">
         <v>231</v>
@@ -4596,10 +4703,10 @@
         <v>100</v>
       </c>
       <c r="O43" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="P43" s="4" t="s">
         <v>303</v>
-      </c>
-      <c r="P43" s="4" t="s">
-        <v>304</v>
       </c>
       <c r="Q43" s="3" t="s">
         <v>231</v>
@@ -4652,10 +4759,10 @@
         <v>100</v>
       </c>
       <c r="O44" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="P44" s="4" t="s">
         <v>305</v>
-      </c>
-      <c r="P44" s="4" t="s">
-        <v>306</v>
       </c>
       <c r="Q44" s="3" t="s">
         <v>231</v>
@@ -4708,10 +4815,10 @@
         <v>100</v>
       </c>
       <c r="O45" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="P45" s="4" t="s">
         <v>307</v>
-      </c>
-      <c r="P45" s="4" t="s">
-        <v>308</v>
       </c>
       <c r="Q45" s="3" t="s">
         <v>231</v>
@@ -4764,10 +4871,10 @@
         <v>100</v>
       </c>
       <c r="O46" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="P46" s="4" t="s">
         <v>309</v>
-      </c>
-      <c r="P46" s="4" t="s">
-        <v>310</v>
       </c>
       <c r="Q46" s="3" t="s">
         <v>231</v>
@@ -4820,10 +4927,10 @@
         <v>100</v>
       </c>
       <c r="O47" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="P47" s="4" t="s">
         <v>311</v>
-      </c>
-      <c r="P47" s="4" t="s">
-        <v>312</v>
       </c>
       <c r="Q47" s="3" t="s">
         <v>231</v>
@@ -4876,10 +4983,10 @@
         <v>100</v>
       </c>
       <c r="O48" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="P48" s="4" t="s">
         <v>313</v>
-      </c>
-      <c r="P48" s="4" t="s">
-        <v>314</v>
       </c>
       <c r="Q48" s="3" t="s">
         <v>231</v>
@@ -4932,10 +5039,10 @@
         <v>100</v>
       </c>
       <c r="O49" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="P49" s="4" t="s">
         <v>315</v>
-      </c>
-      <c r="P49" s="4" t="s">
-        <v>316</v>
       </c>
       <c r="Q49" s="3" t="s">
         <v>231</v>
@@ -4988,10 +5095,10 @@
         <v>100</v>
       </c>
       <c r="O50" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="P50" s="4" t="s">
         <v>317</v>
-      </c>
-      <c r="P50" s="4" t="s">
-        <v>318</v>
       </c>
       <c r="Q50" s="3" t="s">
         <v>231</v>
@@ -5044,10 +5151,10 @@
         <v>100</v>
       </c>
       <c r="O51" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="P51" s="4" t="s">
         <v>319</v>
-      </c>
-      <c r="P51" s="4" t="s">
-        <v>320</v>
       </c>
       <c r="Q51" s="3" t="s">
         <v>231</v>
@@ -5100,10 +5207,10 @@
         <v>100</v>
       </c>
       <c r="O52" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="P52" s="4" t="s">
         <v>321</v>
-      </c>
-      <c r="P52" s="4" t="s">
-        <v>322</v>
       </c>
       <c r="Q52" s="3" t="s">
         <v>231</v>
@@ -5156,10 +5263,10 @@
         <v>100</v>
       </c>
       <c r="O53" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="P53" s="4" t="s">
         <v>323</v>
-      </c>
-      <c r="P53" s="4" t="s">
-        <v>324</v>
       </c>
       <c r="Q53" s="3" t="s">
         <v>231</v>
@@ -5212,10 +5319,10 @@
         <v>100</v>
       </c>
       <c r="O54" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="P54" s="4" t="s">
         <v>325</v>
-      </c>
-      <c r="P54" s="4" t="s">
-        <v>326</v>
       </c>
       <c r="Q54" s="3" t="s">
         <v>231</v>
@@ -5268,10 +5375,10 @@
         <v>100</v>
       </c>
       <c r="O55" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="P55" s="4" t="s">
         <v>327</v>
-      </c>
-      <c r="P55" s="4" t="s">
-        <v>328</v>
       </c>
       <c r="Q55" s="3" t="s">
         <v>231</v>
@@ -5324,10 +5431,10 @@
         <v>100</v>
       </c>
       <c r="O56" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="P56" s="4" t="s">
         <v>329</v>
-      </c>
-      <c r="P56" s="4" t="s">
-        <v>330</v>
       </c>
       <c r="Q56" s="3" t="s">
         <v>231</v>
@@ -5380,10 +5487,10 @@
         <v>100</v>
       </c>
       <c r="O57" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="P57" s="4" t="s">
         <v>331</v>
-      </c>
-      <c r="P57" s="4" t="s">
-        <v>332</v>
       </c>
       <c r="Q57" s="3" t="s">
         <v>231</v>
@@ -5436,10 +5543,10 @@
         <v>100</v>
       </c>
       <c r="O58" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="P58" s="4" t="s">
         <v>333</v>
-      </c>
-      <c r="P58" s="4" t="s">
-        <v>334</v>
       </c>
       <c r="Q58" s="3" t="s">
         <v>231</v>
@@ -5492,10 +5599,10 @@
         <v>100</v>
       </c>
       <c r="O59" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="P59" s="4" t="s">
         <v>335</v>
-      </c>
-      <c r="P59" s="4" t="s">
-        <v>336</v>
       </c>
       <c r="Q59" s="3" t="s">
         <v>231</v>
@@ -5548,10 +5655,10 @@
         <v>100</v>
       </c>
       <c r="O60" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="P60" s="4" t="s">
         <v>337</v>
-      </c>
-      <c r="P60" s="4" t="s">
-        <v>338</v>
       </c>
       <c r="Q60" s="3" t="s">
         <v>231</v>
@@ -5604,10 +5711,10 @@
         <v>100</v>
       </c>
       <c r="O61" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="P61" s="4" t="s">
         <v>339</v>
-      </c>
-      <c r="P61" s="4" t="s">
-        <v>340</v>
       </c>
       <c r="Q61" s="3" t="s">
         <v>231</v>
@@ -5660,10 +5767,10 @@
         <v>100</v>
       </c>
       <c r="O62" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="P62" s="4" t="s">
         <v>341</v>
-      </c>
-      <c r="P62" s="4" t="s">
-        <v>342</v>
       </c>
       <c r="Q62" s="3" t="s">
         <v>231</v>
@@ -5716,10 +5823,10 @@
         <v>100</v>
       </c>
       <c r="O63" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="P63" s="4" t="s">
         <v>343</v>
-      </c>
-      <c r="P63" s="4" t="s">
-        <v>344</v>
       </c>
       <c r="Q63" s="3" t="s">
         <v>231</v>
@@ -5772,10 +5879,10 @@
         <v>100</v>
       </c>
       <c r="O64" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="P64" s="4" t="s">
         <v>345</v>
-      </c>
-      <c r="P64" s="4" t="s">
-        <v>346</v>
       </c>
       <c r="Q64" s="3" t="s">
         <v>231</v>
@@ -5828,10 +5935,10 @@
         <v>100</v>
       </c>
       <c r="O65" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="P65" s="4" t="s">
         <v>347</v>
-      </c>
-      <c r="P65" s="4" t="s">
-        <v>348</v>
       </c>
       <c r="Q65" s="3" t="s">
         <v>231</v>
@@ -5884,10 +5991,10 @@
         <v>100</v>
       </c>
       <c r="O66" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="P66" s="4" t="s">
         <v>349</v>
-      </c>
-      <c r="P66" s="4" t="s">
-        <v>350</v>
       </c>
       <c r="Q66" s="3" t="s">
         <v>231</v>
@@ -5940,10 +6047,10 @@
         <v>100</v>
       </c>
       <c r="O67" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="P67" s="4" t="s">
         <v>351</v>
-      </c>
-      <c r="P67" s="4" t="s">
-        <v>352</v>
       </c>
       <c r="Q67" s="3" t="s">
         <v>231</v>
@@ -5996,10 +6103,10 @@
         <v>100</v>
       </c>
       <c r="O68" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="P68" s="4" t="s">
         <v>353</v>
-      </c>
-      <c r="P68" s="4" t="s">
-        <v>354</v>
       </c>
       <c r="Q68" s="3" t="s">
         <v>231</v>
@@ -6052,10 +6159,10 @@
         <v>100</v>
       </c>
       <c r="O69" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="P69" s="4" t="s">
         <v>355</v>
-      </c>
-      <c r="P69" s="4" t="s">
-        <v>356</v>
       </c>
       <c r="Q69" s="3" t="s">
         <v>231</v>
@@ -6108,10 +6215,10 @@
         <v>100</v>
       </c>
       <c r="O70" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="P70" s="4" t="s">
         <v>357</v>
-      </c>
-      <c r="P70" s="4" t="s">
-        <v>358</v>
       </c>
       <c r="Q70" s="3" t="s">
         <v>231</v>
@@ -6164,10 +6271,10 @@
         <v>100</v>
       </c>
       <c r="O71" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="P71" s="4" t="s">
         <v>359</v>
-      </c>
-      <c r="P71" s="4" t="s">
-        <v>360</v>
       </c>
       <c r="Q71" s="3" t="s">
         <v>231</v>
@@ -6220,10 +6327,10 @@
         <v>100</v>
       </c>
       <c r="O72" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="P72" s="4" t="s">
         <v>361</v>
-      </c>
-      <c r="P72" s="4" t="s">
-        <v>362</v>
       </c>
       <c r="Q72" s="3" t="s">
         <v>231</v>
@@ -6276,10 +6383,10 @@
         <v>100</v>
       </c>
       <c r="O73" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="P73" s="4" t="s">
         <v>363</v>
-      </c>
-      <c r="P73" s="4" t="s">
-        <v>364</v>
       </c>
       <c r="Q73" s="3" t="s">
         <v>231</v>
@@ -6332,10 +6439,10 @@
         <v>100</v>
       </c>
       <c r="O74" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="P74" s="4" t="s">
         <v>365</v>
-      </c>
-      <c r="P74" s="4" t="s">
-        <v>366</v>
       </c>
       <c r="Q74" s="3" t="s">
         <v>231</v>
@@ -6388,10 +6495,10 @@
         <v>100</v>
       </c>
       <c r="O75" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="P75" s="4" t="s">
         <v>367</v>
-      </c>
-      <c r="P75" s="4" t="s">
-        <v>368</v>
       </c>
       <c r="Q75" s="3" t="s">
         <v>231</v>
@@ -6444,10 +6551,10 @@
         <v>100</v>
       </c>
       <c r="O76" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="P76" s="4" t="s">
         <v>369</v>
-      </c>
-      <c r="P76" s="4" t="s">
-        <v>370</v>
       </c>
       <c r="Q76" s="3" t="s">
         <v>231</v>
@@ -6500,10 +6607,10 @@
         <v>100</v>
       </c>
       <c r="O77" s="4" t="s">
+        <v>370</v>
+      </c>
+      <c r="P77" s="4" t="s">
         <v>371</v>
-      </c>
-      <c r="P77" s="4" t="s">
-        <v>372</v>
       </c>
       <c r="Q77" s="3" t="s">
         <v>231</v>
@@ -6556,10 +6663,10 @@
         <v>100</v>
       </c>
       <c r="O78" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="P78" s="4" t="s">
         <v>373</v>
-      </c>
-      <c r="P78" s="4" t="s">
-        <v>374</v>
       </c>
       <c r="Q78" s="3" t="s">
         <v>231</v>
@@ -6612,10 +6719,10 @@
         <v>100</v>
       </c>
       <c r="O79" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="P79" s="4" t="s">
         <v>375</v>
-      </c>
-      <c r="P79" s="4" t="s">
-        <v>376</v>
       </c>
       <c r="Q79" s="3" t="s">
         <v>231</v>
@@ -6668,10 +6775,10 @@
         <v>100</v>
       </c>
       <c r="O80" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="P80" s="4" t="s">
         <v>377</v>
-      </c>
-      <c r="P80" s="4" t="s">
-        <v>378</v>
       </c>
       <c r="Q80" s="3" t="s">
         <v>231</v>
@@ -6724,10 +6831,10 @@
         <v>100</v>
       </c>
       <c r="O81" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="P81" s="4" t="s">
         <v>379</v>
-      </c>
-      <c r="P81" s="4" t="s">
-        <v>380</v>
       </c>
       <c r="Q81" s="3" t="s">
         <v>231</v>
@@ -6780,10 +6887,10 @@
         <v>100</v>
       </c>
       <c r="O82" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="P82" s="4" t="s">
         <v>381</v>
-      </c>
-      <c r="P82" s="4" t="s">
-        <v>382</v>
       </c>
       <c r="Q82" s="3" t="s">
         <v>231</v>
@@ -6836,10 +6943,10 @@
         <v>100</v>
       </c>
       <c r="O83" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="P83" s="4" t="s">
         <v>383</v>
-      </c>
-      <c r="P83" s="4" t="s">
-        <v>384</v>
       </c>
       <c r="Q83" s="3" t="s">
         <v>231</v>
@@ -6892,10 +6999,10 @@
         <v>100</v>
       </c>
       <c r="O84" s="4" t="s">
+        <v>384</v>
+      </c>
+      <c r="P84" s="4" t="s">
         <v>385</v>
-      </c>
-      <c r="P84" s="4" t="s">
-        <v>386</v>
       </c>
       <c r="Q84" s="3" t="s">
         <v>231</v>
@@ -6948,10 +7055,10 @@
         <v>100</v>
       </c>
       <c r="O85" s="4" t="s">
+        <v>386</v>
+      </c>
+      <c r="P85" s="4" t="s">
         <v>387</v>
-      </c>
-      <c r="P85" s="4" t="s">
-        <v>388</v>
       </c>
       <c r="Q85" s="3" t="s">
         <v>231</v>
@@ -7004,10 +7111,10 @@
         <v>100</v>
       </c>
       <c r="O86" s="4" t="s">
+        <v>388</v>
+      </c>
+      <c r="P86" s="4" t="s">
         <v>389</v>
-      </c>
-      <c r="P86" s="4" t="s">
-        <v>390</v>
       </c>
       <c r="Q86" s="3" t="s">
         <v>231</v>
@@ -7060,10 +7167,10 @@
         <v>100</v>
       </c>
       <c r="O87" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="P87" s="4" t="s">
         <v>391</v>
-      </c>
-      <c r="P87" s="4" t="s">
-        <v>392</v>
       </c>
       <c r="Q87" s="3" t="s">
         <v>231</v>
@@ -7116,10 +7223,10 @@
         <v>100</v>
       </c>
       <c r="O88" s="4" t="s">
+        <v>392</v>
+      </c>
+      <c r="P88" s="4" t="s">
         <v>393</v>
-      </c>
-      <c r="P88" s="4" t="s">
-        <v>394</v>
       </c>
       <c r="Q88" s="3" t="s">
         <v>231</v>
@@ -7172,10 +7279,10 @@
         <v>100</v>
       </c>
       <c r="O89" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="P89" s="4" t="s">
         <v>395</v>
-      </c>
-      <c r="P89" s="4" t="s">
-        <v>396</v>
       </c>
       <c r="Q89" s="3" t="s">
         <v>231</v>
@@ -7228,10 +7335,10 @@
         <v>100</v>
       </c>
       <c r="O90" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="P90" s="4" t="s">
         <v>397</v>
-      </c>
-      <c r="P90" s="4" t="s">
-        <v>398</v>
       </c>
       <c r="Q90" s="3" t="s">
         <v>231</v>
@@ -7284,10 +7391,10 @@
         <v>100</v>
       </c>
       <c r="O91" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="P91" s="4" t="s">
         <v>399</v>
-      </c>
-      <c r="P91" s="4" t="s">
-        <v>400</v>
       </c>
       <c r="Q91" s="3" t="s">
         <v>231</v>
@@ -7340,10 +7447,10 @@
         <v>100</v>
       </c>
       <c r="O92" s="4" t="s">
+        <v>400</v>
+      </c>
+      <c r="P92" s="4" t="s">
         <v>401</v>
-      </c>
-      <c r="P92" s="4" t="s">
-        <v>402</v>
       </c>
       <c r="Q92" s="3" t="s">
         <v>231</v>
@@ -7396,10 +7503,10 @@
         <v>100</v>
       </c>
       <c r="O93" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="P93" s="4" t="s">
         <v>403</v>
-      </c>
-      <c r="P93" s="4" t="s">
-        <v>404</v>
       </c>
       <c r="Q93" s="3" t="s">
         <v>231</v>
@@ -7452,10 +7559,10 @@
         <v>100</v>
       </c>
       <c r="O94" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="P94" s="4" t="s">
         <v>405</v>
-      </c>
-      <c r="P94" s="4" t="s">
-        <v>406</v>
       </c>
       <c r="Q94" s="3" t="s">
         <v>231</v>
@@ -7508,10 +7615,10 @@
         <v>100</v>
       </c>
       <c r="O95" s="4" t="s">
+        <v>406</v>
+      </c>
+      <c r="P95" s="4" t="s">
         <v>407</v>
-      </c>
-      <c r="P95" s="4" t="s">
-        <v>408</v>
       </c>
       <c r="Q95" s="3" t="s">
         <v>231</v>
@@ -7564,10 +7671,10 @@
         <v>100</v>
       </c>
       <c r="O96" s="4" t="s">
+        <v>408</v>
+      </c>
+      <c r="P96" s="4" t="s">
         <v>409</v>
-      </c>
-      <c r="P96" s="4" t="s">
-        <v>410</v>
       </c>
       <c r="Q96" s="3" t="s">
         <v>231</v>
@@ -7620,10 +7727,10 @@
         <v>100</v>
       </c>
       <c r="O97" s="4" t="s">
+        <v>410</v>
+      </c>
+      <c r="P97" s="4" t="s">
         <v>411</v>
-      </c>
-      <c r="P97" s="4" t="s">
-        <v>412</v>
       </c>
       <c r="Q97" s="3" t="s">
         <v>231</v>
@@ -7676,10 +7783,10 @@
         <v>100</v>
       </c>
       <c r="O98" s="4" t="s">
+        <v>412</v>
+      </c>
+      <c r="P98" s="4" t="s">
         <v>413</v>
-      </c>
-      <c r="P98" s="4" t="s">
-        <v>414</v>
       </c>
       <c r="Q98" s="3" t="s">
         <v>231</v>
@@ -7732,10 +7839,10 @@
         <v>100</v>
       </c>
       <c r="O99" s="4" t="s">
+        <v>414</v>
+      </c>
+      <c r="P99" s="4" t="s">
         <v>415</v>
-      </c>
-      <c r="P99" s="4" t="s">
-        <v>416</v>
       </c>
       <c r="Q99" s="3" t="s">
         <v>231</v>
@@ -7788,10 +7895,10 @@
         <v>100</v>
       </c>
       <c r="O100" s="4" t="s">
+        <v>416</v>
+      </c>
+      <c r="P100" s="4" t="s">
         <v>417</v>
-      </c>
-      <c r="P100" s="4" t="s">
-        <v>418</v>
       </c>
       <c r="Q100" s="3" t="s">
         <v>231</v>
@@ -7844,10 +7951,10 @@
         <v>100</v>
       </c>
       <c r="O101" s="4" t="s">
+        <v>418</v>
+      </c>
+      <c r="P101" s="4" t="s">
         <v>419</v>
-      </c>
-      <c r="P101" s="4" t="s">
-        <v>420</v>
       </c>
       <c r="Q101" s="3" t="s">
         <v>231</v>
@@ -7900,10 +8007,10 @@
         <v>100</v>
       </c>
       <c r="O102" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="P102" s="4" t="s">
         <v>421</v>
-      </c>
-      <c r="P102" s="4" t="s">
-        <v>422</v>
       </c>
       <c r="Q102" s="3" t="s">
         <v>231</v>
@@ -7956,10 +8063,10 @@
         <v>100</v>
       </c>
       <c r="O103" s="4" t="s">
+        <v>422</v>
+      </c>
+      <c r="P103" s="4" t="s">
         <v>423</v>
-      </c>
-      <c r="P103" s="4" t="s">
-        <v>424</v>
       </c>
       <c r="Q103" s="3" t="s">
         <v>231</v>
@@ -8012,10 +8119,10 @@
         <v>100</v>
       </c>
       <c r="O104" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="P104" s="4" t="s">
         <v>425</v>
-      </c>
-      <c r="P104" s="4" t="s">
-        <v>426</v>
       </c>
       <c r="Q104" s="3" t="s">
         <v>231</v>
@@ -8068,10 +8175,10 @@
         <v>100</v>
       </c>
       <c r="O105" s="4" t="s">
+        <v>426</v>
+      </c>
+      <c r="P105" s="4" t="s">
         <v>427</v>
-      </c>
-      <c r="P105" s="4" t="s">
-        <v>428</v>
       </c>
       <c r="Q105" s="3" t="s">
         <v>231</v>
@@ -8124,10 +8231,10 @@
         <v>100</v>
       </c>
       <c r="O106" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="P106" s="4" t="s">
         <v>429</v>
-      </c>
-      <c r="P106" s="4" t="s">
-        <v>430</v>
       </c>
       <c r="Q106" s="3" t="s">
         <v>231</v>
@@ -8180,10 +8287,10 @@
         <v>100</v>
       </c>
       <c r="O107" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="P107" s="4" t="s">
         <v>431</v>
-      </c>
-      <c r="P107" s="4" t="s">
-        <v>432</v>
       </c>
       <c r="Q107" s="3" t="s">
         <v>231</v>
@@ -8236,10 +8343,10 @@
         <v>100</v>
       </c>
       <c r="O108" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="P108" s="4" t="s">
         <v>433</v>
-      </c>
-      <c r="P108" s="4" t="s">
-        <v>434</v>
       </c>
       <c r="Q108" s="3" t="s">
         <v>231</v>
@@ -8292,10 +8399,10 @@
         <v>100</v>
       </c>
       <c r="O109" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="P109" s="4" t="s">
         <v>435</v>
-      </c>
-      <c r="P109" s="4" t="s">
-        <v>436</v>
       </c>
       <c r="Q109" s="3" t="s">
         <v>231</v>
@@ -8348,10 +8455,10 @@
         <v>100</v>
       </c>
       <c r="O110" s="4" t="s">
+        <v>436</v>
+      </c>
+      <c r="P110" s="4" t="s">
         <v>437</v>
-      </c>
-      <c r="P110" s="4" t="s">
-        <v>438</v>
       </c>
       <c r="Q110" s="3" t="s">
         <v>231</v>
@@ -8404,10 +8511,10 @@
         <v>100</v>
       </c>
       <c r="O111" s="4" t="s">
+        <v>438</v>
+      </c>
+      <c r="P111" s="4" t="s">
         <v>439</v>
-      </c>
-      <c r="P111" s="4" t="s">
-        <v>440</v>
       </c>
       <c r="Q111" s="3" t="s">
         <v>231</v>
@@ -8460,10 +8567,10 @@
         <v>100</v>
       </c>
       <c r="O112" s="4" t="s">
+        <v>440</v>
+      </c>
+      <c r="P112" s="4" t="s">
         <v>441</v>
-      </c>
-      <c r="P112" s="4" t="s">
-        <v>442</v>
       </c>
       <c r="Q112" s="3" t="s">
         <v>231</v>
@@ -8516,10 +8623,10 @@
         <v>100</v>
       </c>
       <c r="O113" s="4" t="s">
+        <v>442</v>
+      </c>
+      <c r="P113" s="4" t="s">
         <v>443</v>
-      </c>
-      <c r="P113" s="4" t="s">
-        <v>444</v>
       </c>
       <c r="Q113" s="3" t="s">
         <v>231</v>
@@ -8572,10 +8679,10 @@
         <v>100</v>
       </c>
       <c r="O114" s="4" t="s">
+        <v>444</v>
+      </c>
+      <c r="P114" s="4" t="s">
         <v>445</v>
-      </c>
-      <c r="P114" s="4" t="s">
-        <v>446</v>
       </c>
       <c r="Q114" s="3" t="s">
         <v>231</v>
@@ -8628,10 +8735,10 @@
         <v>100</v>
       </c>
       <c r="O115" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="P115" s="4" t="s">
         <v>447</v>
-      </c>
-      <c r="P115" s="4" t="s">
-        <v>448</v>
       </c>
       <c r="Q115" s="3" t="s">
         <v>231</v>
@@ -8684,10 +8791,10 @@
         <v>100</v>
       </c>
       <c r="O116" s="4" t="s">
+        <v>448</v>
+      </c>
+      <c r="P116" s="4" t="s">
         <v>449</v>
-      </c>
-      <c r="P116" s="4" t="s">
-        <v>450</v>
       </c>
       <c r="Q116" s="3" t="s">
         <v>231</v>
@@ -8740,10 +8847,10 @@
         <v>100</v>
       </c>
       <c r="O117" s="4" t="s">
+        <v>450</v>
+      </c>
+      <c r="P117" s="4" t="s">
         <v>451</v>
-      </c>
-      <c r="P117" s="4" t="s">
-        <v>452</v>
       </c>
       <c r="Q117" s="3" t="s">
         <v>231</v>
@@ -8796,10 +8903,10 @@
         <v>100</v>
       </c>
       <c r="O118" s="4" t="s">
+        <v>452</v>
+      </c>
+      <c r="P118" s="4" t="s">
         <v>453</v>
-      </c>
-      <c r="P118" s="4" t="s">
-        <v>454</v>
       </c>
       <c r="Q118" s="3" t="s">
         <v>231</v>
@@ -8852,10 +8959,10 @@
         <v>100</v>
       </c>
       <c r="O119" s="4" t="s">
+        <v>454</v>
+      </c>
+      <c r="P119" s="4" t="s">
         <v>455</v>
-      </c>
-      <c r="P119" s="4" t="s">
-        <v>456</v>
       </c>
       <c r="Q119" s="3" t="s">
         <v>231</v>
@@ -8908,10 +9015,10 @@
         <v>100</v>
       </c>
       <c r="O120" s="4" t="s">
+        <v>456</v>
+      </c>
+      <c r="P120" s="4" t="s">
         <v>457</v>
-      </c>
-      <c r="P120" s="4" t="s">
-        <v>458</v>
       </c>
       <c r="Q120" s="3" t="s">
         <v>231</v>
@@ -8964,10 +9071,10 @@
         <v>100</v>
       </c>
       <c r="O121" s="4" t="s">
+        <v>458</v>
+      </c>
+      <c r="P121" s="4" t="s">
         <v>459</v>
-      </c>
-      <c r="P121" s="4" t="s">
-        <v>460</v>
       </c>
       <c r="Q121" s="3" t="s">
         <v>231</v>
@@ -9020,10 +9127,10 @@
         <v>100</v>
       </c>
       <c r="O122" s="4" t="s">
+        <v>460</v>
+      </c>
+      <c r="P122" s="4" t="s">
         <v>461</v>
-      </c>
-      <c r="P122" s="4" t="s">
-        <v>462</v>
       </c>
       <c r="Q122" s="3" t="s">
         <v>231</v>
@@ -9076,10 +9183,10 @@
         <v>100</v>
       </c>
       <c r="O123" s="4" t="s">
+        <v>462</v>
+      </c>
+      <c r="P123" s="4" t="s">
         <v>463</v>
-      </c>
-      <c r="P123" s="4" t="s">
-        <v>464</v>
       </c>
       <c r="Q123" s="3" t="s">
         <v>231</v>
@@ -9132,10 +9239,10 @@
         <v>100</v>
       </c>
       <c r="O124" s="4" t="s">
+        <v>464</v>
+      </c>
+      <c r="P124" s="4" t="s">
         <v>465</v>
-      </c>
-      <c r="P124" s="4" t="s">
-        <v>466</v>
       </c>
       <c r="Q124" s="3" t="s">
         <v>231</v>
@@ -9188,10 +9295,10 @@
         <v>100</v>
       </c>
       <c r="O125" s="4" t="s">
+        <v>466</v>
+      </c>
+      <c r="P125" s="4" t="s">
         <v>467</v>
-      </c>
-      <c r="P125" s="4" t="s">
-        <v>468</v>
       </c>
       <c r="Q125" s="3" t="s">
         <v>231</v>
@@ -9244,10 +9351,10 @@
         <v>100</v>
       </c>
       <c r="O126" s="4" t="s">
+        <v>468</v>
+      </c>
+      <c r="P126" s="4" t="s">
         <v>469</v>
-      </c>
-      <c r="P126" s="4" t="s">
-        <v>470</v>
       </c>
       <c r="Q126" s="3" t="s">
         <v>231</v>
@@ -9300,10 +9407,10 @@
         <v>100</v>
       </c>
       <c r="O127" s="4" t="s">
+        <v>470</v>
+      </c>
+      <c r="P127" s="4" t="s">
         <v>471</v>
-      </c>
-      <c r="P127" s="4" t="s">
-        <v>472</v>
       </c>
       <c r="Q127" s="3" t="s">
         <v>231</v>
@@ -9356,10 +9463,10 @@
         <v>100</v>
       </c>
       <c r="O128" s="4" t="s">
+        <v>472</v>
+      </c>
+      <c r="P128" s="4" t="s">
         <v>473</v>
-      </c>
-      <c r="P128" s="4" t="s">
-        <v>474</v>
       </c>
       <c r="Q128" s="3" t="s">
         <v>231</v>
@@ -9412,10 +9519,10 @@
         <v>100</v>
       </c>
       <c r="O129" s="4" t="s">
+        <v>474</v>
+      </c>
+      <c r="P129" s="4" t="s">
         <v>475</v>
-      </c>
-      <c r="P129" s="4" t="s">
-        <v>476</v>
       </c>
       <c r="Q129" s="3" t="s">
         <v>231</v>
@@ -9468,10 +9575,10 @@
         <v>100</v>
       </c>
       <c r="O130" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="P130" s="4" t="s">
         <v>477</v>
-      </c>
-      <c r="P130" s="4" t="s">
-        <v>478</v>
       </c>
       <c r="Q130" s="3" t="s">
         <v>231</v>
@@ -9524,10 +9631,10 @@
         <v>100</v>
       </c>
       <c r="O131" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="P131" s="4" t="s">
         <v>479</v>
-      </c>
-      <c r="P131" s="4" t="s">
-        <v>480</v>
       </c>
       <c r="Q131" s="3" t="s">
         <v>231</v>
@@ -9580,10 +9687,10 @@
         <v>100</v>
       </c>
       <c r="O132" s="4" t="s">
+        <v>480</v>
+      </c>
+      <c r="P132" s="4" t="s">
         <v>481</v>
-      </c>
-      <c r="P132" s="4" t="s">
-        <v>482</v>
       </c>
       <c r="Q132" s="3" t="s">
         <v>231</v>
@@ -9636,10 +9743,10 @@
         <v>100</v>
       </c>
       <c r="O133" s="4" t="s">
+        <v>482</v>
+      </c>
+      <c r="P133" s="4" t="s">
         <v>483</v>
-      </c>
-      <c r="P133" s="4" t="s">
-        <v>484</v>
       </c>
       <c r="Q133" s="3" t="s">
         <v>231</v>
@@ -9692,10 +9799,10 @@
         <v>100</v>
       </c>
       <c r="O134" s="4" t="s">
+        <v>484</v>
+      </c>
+      <c r="P134" s="4" t="s">
         <v>485</v>
-      </c>
-      <c r="P134" s="4" t="s">
-        <v>486</v>
       </c>
       <c r="Q134" s="3" t="s">
         <v>231</v>
@@ -9748,10 +9855,10 @@
         <v>100</v>
       </c>
       <c r="O135" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="P135" s="4" t="s">
         <v>487</v>
-      </c>
-      <c r="P135" s="4" t="s">
-        <v>488</v>
       </c>
       <c r="Q135" s="3" t="s">
         <v>231</v>
@@ -9804,10 +9911,10 @@
         <v>100</v>
       </c>
       <c r="O136" s="4" t="s">
+        <v>488</v>
+      </c>
+      <c r="P136" s="4" t="s">
         <v>489</v>
-      </c>
-      <c r="P136" s="4" t="s">
-        <v>490</v>
       </c>
       <c r="Q136" s="3" t="s">
         <v>231</v>
@@ -9860,10 +9967,10 @@
         <v>100</v>
       </c>
       <c r="O137" s="4" t="s">
+        <v>490</v>
+      </c>
+      <c r="P137" s="4" t="s">
         <v>491</v>
-      </c>
-      <c r="P137" s="4" t="s">
-        <v>492</v>
       </c>
       <c r="Q137" s="3" t="s">
         <v>231</v>
@@ -9916,10 +10023,10 @@
         <v>100</v>
       </c>
       <c r="O138" s="4" t="s">
+        <v>492</v>
+      </c>
+      <c r="P138" s="4" t="s">
         <v>493</v>
-      </c>
-      <c r="P138" s="4" t="s">
-        <v>494</v>
       </c>
       <c r="Q138" s="3" t="s">
         <v>231</v>
@@ -9972,10 +10079,10 @@
         <v>100</v>
       </c>
       <c r="O139" s="4" t="s">
+        <v>494</v>
+      </c>
+      <c r="P139" s="4" t="s">
         <v>495</v>
-      </c>
-      <c r="P139" s="4" t="s">
-        <v>496</v>
       </c>
       <c r="Q139" s="3" t="s">
         <v>231</v>
@@ -10028,10 +10135,10 @@
         <v>100</v>
       </c>
       <c r="O140" s="4" t="s">
+        <v>496</v>
+      </c>
+      <c r="P140" s="4" t="s">
         <v>497</v>
-      </c>
-      <c r="P140" s="4" t="s">
-        <v>498</v>
       </c>
       <c r="Q140" s="3" t="s">
         <v>231</v>
@@ -10084,10 +10191,10 @@
         <v>100</v>
       </c>
       <c r="O141" s="4" t="s">
+        <v>498</v>
+      </c>
+      <c r="P141" s="4" t="s">
         <v>499</v>
-      </c>
-      <c r="P141" s="4" t="s">
-        <v>500</v>
       </c>
       <c r="Q141" s="3" t="s">
         <v>231</v>
@@ -10140,10 +10247,10 @@
         <v>100</v>
       </c>
       <c r="O142" s="4" t="s">
+        <v>500</v>
+      </c>
+      <c r="P142" s="4" t="s">
         <v>501</v>
-      </c>
-      <c r="P142" s="4" t="s">
-        <v>502</v>
       </c>
       <c r="Q142" s="3" t="s">
         <v>231</v>
@@ -10196,10 +10303,10 @@
         <v>100</v>
       </c>
       <c r="O143" s="4" t="s">
+        <v>502</v>
+      </c>
+      <c r="P143" s="4" t="s">
         <v>503</v>
-      </c>
-      <c r="P143" s="4" t="s">
-        <v>504</v>
       </c>
       <c r="Q143" s="3" t="s">
         <v>231</v>
@@ -10252,10 +10359,10 @@
         <v>100</v>
       </c>
       <c r="O144" s="4" t="s">
+        <v>504</v>
+      </c>
+      <c r="P144" s="4" t="s">
         <v>505</v>
-      </c>
-      <c r="P144" s="4" t="s">
-        <v>506</v>
       </c>
       <c r="Q144" s="3" t="s">
         <v>231</v>
@@ -10308,10 +10415,10 @@
         <v>100</v>
       </c>
       <c r="O145" s="4" t="s">
+        <v>506</v>
+      </c>
+      <c r="P145" s="4" t="s">
         <v>507</v>
-      </c>
-      <c r="P145" s="4" t="s">
-        <v>508</v>
       </c>
       <c r="Q145" s="3" t="s">
         <v>231</v>
@@ -10364,10 +10471,10 @@
         <v>100</v>
       </c>
       <c r="O146" s="4" t="s">
+        <v>508</v>
+      </c>
+      <c r="P146" s="4" t="s">
         <v>509</v>
-      </c>
-      <c r="P146" s="4" t="s">
-        <v>510</v>
       </c>
       <c r="Q146" s="3" t="s">
         <v>231</v>
@@ -10420,10 +10527,10 @@
         <v>100</v>
       </c>
       <c r="O147" s="4" t="s">
+        <v>510</v>
+      </c>
+      <c r="P147" s="4" t="s">
         <v>511</v>
-      </c>
-      <c r="P147" s="4" t="s">
-        <v>512</v>
       </c>
       <c r="Q147" s="3" t="s">
         <v>231</v>
@@ -10476,10 +10583,10 @@
         <v>100</v>
       </c>
       <c r="O148" s="4" t="s">
+        <v>512</v>
+      </c>
+      <c r="P148" s="4" t="s">
         <v>513</v>
-      </c>
-      <c r="P148" s="4" t="s">
-        <v>514</v>
       </c>
       <c r="Q148" s="3" t="s">
         <v>231</v>
@@ -10532,10 +10639,10 @@
         <v>100</v>
       </c>
       <c r="O149" s="4" t="s">
+        <v>514</v>
+      </c>
+      <c r="P149" s="4" t="s">
         <v>515</v>
-      </c>
-      <c r="P149" s="4" t="s">
-        <v>516</v>
       </c>
       <c r="Q149" s="3" t="s">
         <v>231</v>
@@ -10588,10 +10695,10 @@
         <v>100</v>
       </c>
       <c r="O150" s="4" t="s">
+        <v>516</v>
+      </c>
+      <c r="P150" s="4" t="s">
         <v>517</v>
-      </c>
-      <c r="P150" s="4" t="s">
-        <v>518</v>
       </c>
       <c r="Q150" s="3" t="s">
         <v>231</v>
@@ -10644,10 +10751,10 @@
         <v>100</v>
       </c>
       <c r="O151" s="4" t="s">
+        <v>518</v>
+      </c>
+      <c r="P151" s="4" t="s">
         <v>519</v>
-      </c>
-      <c r="P151" s="4" t="s">
-        <v>520</v>
       </c>
       <c r="Q151" s="3" t="s">
         <v>231</v>
@@ -10700,10 +10807,10 @@
         <v>100</v>
       </c>
       <c r="O152" s="4" t="s">
+        <v>520</v>
+      </c>
+      <c r="P152" s="4" t="s">
         <v>521</v>
-      </c>
-      <c r="P152" s="4" t="s">
-        <v>522</v>
       </c>
       <c r="Q152" s="3" t="s">
         <v>231</v>
@@ -10756,10 +10863,10 @@
         <v>100</v>
       </c>
       <c r="O153" s="4" t="s">
+        <v>522</v>
+      </c>
+      <c r="P153" s="4" t="s">
         <v>523</v>
-      </c>
-      <c r="P153" s="4" t="s">
-        <v>524</v>
       </c>
       <c r="Q153" s="3" t="s">
         <v>231</v>
@@ -10812,10 +10919,10 @@
         <v>100</v>
       </c>
       <c r="O154" s="4" t="s">
+        <v>524</v>
+      </c>
+      <c r="P154" s="4" t="s">
         <v>525</v>
-      </c>
-      <c r="P154" s="4" t="s">
-        <v>526</v>
       </c>
       <c r="Q154" s="3" t="s">
         <v>231</v>
@@ -10868,10 +10975,10 @@
         <v>100</v>
       </c>
       <c r="O155" s="4" t="s">
+        <v>526</v>
+      </c>
+      <c r="P155" s="4" t="s">
         <v>527</v>
-      </c>
-      <c r="P155" s="4" t="s">
-        <v>528</v>
       </c>
       <c r="Q155" s="3" t="s">
         <v>231</v>
@@ -10924,10 +11031,10 @@
         <v>100</v>
       </c>
       <c r="O156" s="4" t="s">
+        <v>528</v>
+      </c>
+      <c r="P156" s="4" t="s">
         <v>529</v>
-      </c>
-      <c r="P156" s="4" t="s">
-        <v>530</v>
       </c>
       <c r="Q156" s="3" t="s">
         <v>231</v>
@@ -10980,10 +11087,10 @@
         <v>100</v>
       </c>
       <c r="O157" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="P157" s="4" t="s">
         <v>531</v>
-      </c>
-      <c r="P157" s="4" t="s">
-        <v>532</v>
       </c>
       <c r="Q157" s="3" t="s">
         <v>231</v>
@@ -11036,10 +11143,10 @@
         <v>100</v>
       </c>
       <c r="O158" s="4" t="s">
+        <v>532</v>
+      </c>
+      <c r="P158" s="4" t="s">
         <v>533</v>
-      </c>
-      <c r="P158" s="4" t="s">
-        <v>534</v>
       </c>
       <c r="Q158" s="3" t="s">
         <v>231</v>
@@ -11092,10 +11199,10 @@
         <v>100</v>
       </c>
       <c r="O159" s="4" t="s">
+        <v>534</v>
+      </c>
+      <c r="P159" s="4" t="s">
         <v>535</v>
-      </c>
-      <c r="P159" s="4" t="s">
-        <v>536</v>
       </c>
       <c r="Q159" s="3" t="s">
         <v>231</v>
@@ -11148,10 +11255,10 @@
         <v>100</v>
       </c>
       <c r="O160" s="4" t="s">
+        <v>536</v>
+      </c>
+      <c r="P160" s="4" t="s">
         <v>537</v>
-      </c>
-      <c r="P160" s="4" t="s">
-        <v>538</v>
       </c>
       <c r="Q160" s="3" t="s">
         <v>231</v>
@@ -11204,10 +11311,10 @@
         <v>100</v>
       </c>
       <c r="O161" s="4" t="s">
+        <v>538</v>
+      </c>
+      <c r="P161" s="4" t="s">
         <v>539</v>
-      </c>
-      <c r="P161" s="4" t="s">
-        <v>540</v>
       </c>
       <c r="Q161" s="3" t="s">
         <v>231</v>
@@ -11260,10 +11367,10 @@
         <v>100</v>
       </c>
       <c r="O162" s="4" t="s">
+        <v>540</v>
+      </c>
+      <c r="P162" s="4" t="s">
         <v>541</v>
-      </c>
-      <c r="P162" s="4" t="s">
-        <v>542</v>
       </c>
       <c r="Q162" s="3" t="s">
         <v>231</v>
@@ -11316,10 +11423,10 @@
         <v>100</v>
       </c>
       <c r="O163" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="P163" s="4" t="s">
         <v>543</v>
-      </c>
-      <c r="P163" s="4" t="s">
-        <v>544</v>
       </c>
       <c r="Q163" s="3" t="s">
         <v>231</v>
@@ -11372,10 +11479,10 @@
         <v>100</v>
       </c>
       <c r="O164" s="4" t="s">
+        <v>544</v>
+      </c>
+      <c r="P164" s="4" t="s">
         <v>545</v>
-      </c>
-      <c r="P164" s="4" t="s">
-        <v>546</v>
       </c>
       <c r="Q164" s="3" t="s">
         <v>231</v>

--- a/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBC8A19E-81F2-4B59-BBB2-8E6F6D21E231}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48C184B5-CAD9-4F78-9ABB-57D9945EDC97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_barries_v8" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2430" uniqueCount="612">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1212" uniqueCount="577">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1818,14 +1818,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>120001:150</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>120001:240</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>120001:102_0:102</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1842,109 +1834,12 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>20001:100</t>
-  </si>
-  <si>
-    <t>30001:100</t>
-  </si>
-  <si>
-    <t>40001:100</t>
-  </si>
-  <si>
-    <t>50001:100</t>
-  </si>
-  <si>
-    <t>60001:100</t>
-  </si>
-  <si>
-    <t>70001:100</t>
-  </si>
-  <si>
-    <t>80001:100</t>
-  </si>
-  <si>
-    <t>90001:100</t>
-  </si>
-  <si>
-    <t>100001:00</t>
-  </si>
-  <si>
-    <t>130001:00</t>
-  </si>
-  <si>
-    <t>140001:00</t>
-  </si>
-  <si>
-    <t>150001:00</t>
-  </si>
-  <si>
-    <t>160001:00</t>
-  </si>
-  <si>
-    <t>170001:00</t>
-  </si>
-  <si>
-    <t>180001:00</t>
-  </si>
-  <si>
-    <t>190001:00</t>
-  </si>
-  <si>
-    <t>200001:00</t>
-  </si>
-  <si>
-    <t>210001:00</t>
-  </si>
-  <si>
-    <t>220001:00</t>
-  </si>
-  <si>
-    <t>230001:00</t>
-  </si>
-  <si>
-    <t>240001:00</t>
-  </si>
-  <si>
-    <t>250001:00</t>
-  </si>
-  <si>
-    <t>260001:00</t>
-  </si>
-  <si>
-    <t>270001:00</t>
-  </si>
-  <si>
-    <t>280001:00</t>
-  </si>
-  <si>
-    <t>290001:00</t>
-  </si>
-  <si>
-    <t>300001:00</t>
-  </si>
-  <si>
-    <t>310001:00</t>
-  </si>
-  <si>
-    <t>320001:00</t>
-  </si>
-  <si>
-    <t>330001:00</t>
-  </si>
-  <si>
-    <t>340001:00</t>
-  </si>
-  <si>
-    <t>350001:00</t>
-  </si>
-  <si>
-    <t>360001:00</t>
-  </si>
-  <si>
-    <t>370001:00</t>
-  </si>
-  <si>
-    <t>380001:00</t>
+    <t>120001:125</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>120001:200</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2548,10 +2443,10 @@
         <v>150</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="Q5" s="3" t="s">
         <v>231</v>
@@ -2563,7 +2458,7 @@
         <v>247</v>
       </c>
       <c r="T5" s="1" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="U5" s="1" t="s">
         <v>248</v>
@@ -3185,7 +3080,7 @@
         <v>569</v>
       </c>
       <c r="P16" s="4" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="Q16" s="3" t="s">
         <v>231</v>
@@ -3197,10 +3092,10 @@
         <v>570</v>
       </c>
       <c r="T16" s="1" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="U16" s="1" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.15">

--- a/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48C184B5-CAD9-4F78-9ABB-57D9945EDC97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55750D1A-8E91-4761-A797-054EBEFFD855}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1834,11 +1834,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>120001:125</t>
+    <t>120001:110</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>120001:200</t>
+    <t>120001:180</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>

--- a/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55750D1A-8E91-4761-A797-054EBEFFD855}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9601086F-28BF-4172-80B0-70D543D654F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1838,7 +1838,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>120001:180</t>
+    <t>120001:195</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>

--- a/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9601086F-28BF-4172-80B0-70D543D654F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{709ED253-6E92-42A5-A8A0-757967BF46D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_barries_v8" sheetId="1" r:id="rId1"/>
@@ -3139,7 +3139,7 @@
         <v>215</v>
       </c>
       <c r="N17" s="1">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="O17" s="4" t="s">
         <v>250</v>

--- a/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{709ED253-6E92-42A5-A8A0-757967BF46D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BBFD88C-12F9-4573-8874-6C34A8ECE7D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1838,7 +1838,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>120001:195</t>
+    <t>120001:150</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>

--- a/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BBFD88C-12F9-4573-8874-6C34A8ECE7D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E287B96-CD75-4FBE-BFFC-D1D7B887AAFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1834,11 +1834,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>120001:110</t>
+    <t>120001:10000</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>120001:150</t>
+    <t>120001:20000</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>

--- a/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E287B96-CD75-4FBE-BFFC-D1D7B887AAFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F8BA6A0-3D10-488E-A487-F309B35A2719}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1212" uniqueCount="577">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1217" uniqueCount="581">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1839,6 +1839,22 @@
   </si>
   <si>
     <t>120001:20000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>monster _max_num</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>区域刷怪数量上限</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10001:8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>120001:20</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2176,7 +2192,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:U164"/>
+  <dimension ref="A1:V164"/>
   <sheetFormatPr defaultColWidth="7.125" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.5" style="1" bestFit="1" customWidth="1"/>
@@ -2196,15 +2212,16 @@
     <col min="17" max="17" width="19.375" style="1" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="21.5" style="1" bestFit="1" customWidth="1"/>
     <col min="19" max="21" width="30.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="7.125" style="1"/>
+    <col min="22" max="22" width="19.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="7.125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -2268,8 +2285,11 @@
       <c r="U2" s="1" t="s">
         <v>246</v>
       </c>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="V2" s="1" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -2333,8 +2353,11 @@
       <c r="U3" s="1" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="V3" s="1" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -2398,8 +2421,11 @@
       <c r="U4" s="1" t="s">
         <v>242</v>
       </c>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="V4" s="1" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.15">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -2463,8 +2489,11 @@
       <c r="U5" s="1" t="s">
         <v>248</v>
       </c>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="V5" s="1" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.15">
       <c r="A6" s="1">
         <v>2</v>
       </c>
@@ -2520,7 +2549,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.15">
       <c r="A7" s="1">
         <v>3</v>
       </c>
@@ -2576,7 +2605,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.15">
       <c r="A8" s="1">
         <v>4</v>
       </c>
@@ -2632,7 +2661,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.15">
       <c r="A9" s="1">
         <v>5</v>
       </c>
@@ -2688,7 +2717,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.15">
       <c r="A10" s="1">
         <v>6</v>
       </c>
@@ -2744,7 +2773,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.15">
       <c r="A11" s="1">
         <v>7</v>
       </c>
@@ -2800,7 +2829,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.15">
       <c r="A12" s="1">
         <v>8</v>
       </c>
@@ -2856,7 +2885,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.15">
       <c r="A13" s="1">
         <v>9</v>
       </c>
@@ -2912,7 +2941,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="14" spans="1:21" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:22" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="1">
         <v>10</v>
       </c>
@@ -2968,7 +2997,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.15">
       <c r="A15" s="1">
         <v>11</v>
       </c>
@@ -3033,7 +3062,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.15">
       <c r="A16" s="1">
         <v>12</v>
       </c>
@@ -3096,6 +3125,9 @@
       </c>
       <c r="U16" s="1" t="s">
         <v>576</v>
+      </c>
+      <c r="V16" s="1" t="s">
+        <v>580</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.15">

--- a/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F8BA6A0-3D10-488E-A487-F309B35A2719}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C02EE51-CB07-42FA-8B63-FD67887E3C7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1842,10 +1842,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>monster _max_num</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>区域刷怪数量上限</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1855,6 +1851,10 @@
   </si>
   <si>
     <t>120001:20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>monster_max_num</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2354,7 +2354,7 @@
         <v>245</v>
       </c>
       <c r="V3" s="1" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.15">
@@ -2422,7 +2422,7 @@
         <v>242</v>
       </c>
       <c r="V4" s="1" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.15">
@@ -2490,7 +2490,7 @@
         <v>248</v>
       </c>
       <c r="V5" s="1" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.15">
@@ -3127,7 +3127,7 @@
         <v>576</v>
       </c>
       <c r="V16" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.15">

--- a/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4314ED86-D6F1-4D74-88E1-0D999F277398}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6DCF909-D463-41B1-BA48-4B3E5A5DF0DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1217" uniqueCount="581">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1221" uniqueCount="584">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1856,6 +1856,17 @@
   <si>
     <t>120001:35</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>box_ids</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>宝箱列表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>110001,110002,110003,110004,110005,110006,110007,110008,110009,110011</t>
   </si>
 </sst>
 </file>
@@ -1905,12 +1916,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="20" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2192,7 +2206,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:V164"/>
+  <dimension ref="A1:W164"/>
   <sheetFormatPr defaultColWidth="7.125" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.5" style="1" bestFit="1" customWidth="1"/>
@@ -2213,15 +2227,16 @@
     <col min="18" max="18" width="21.5" style="1" bestFit="1" customWidth="1"/>
     <col min="19" max="21" width="30.75" style="1" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="19.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="7.125" style="1"/>
+    <col min="23" max="23" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="7.125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -2288,8 +2303,11 @@
       <c r="V2" s="1" t="s">
         <v>249</v>
       </c>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.15">
+      <c r="W2" s="1" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -2356,8 +2374,11 @@
       <c r="V3" s="1" t="s">
         <v>579</v>
       </c>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.15">
+      <c r="W3" s="5" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -2424,8 +2445,11 @@
       <c r="V4" s="1" t="s">
         <v>577</v>
       </c>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.15">
+      <c r="W4" s="1" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -2492,8 +2516,11 @@
       <c r="V5" s="1" t="s">
         <v>578</v>
       </c>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.15">
+      <c r="W5" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A6" s="1">
         <v>2</v>
       </c>
@@ -2548,8 +2575,11 @@
       <c r="R6" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.15">
+      <c r="W6" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A7" s="1">
         <v>3</v>
       </c>
@@ -2604,8 +2634,11 @@
       <c r="R7" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.15">
+      <c r="W7" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A8" s="1">
         <v>4</v>
       </c>
@@ -2660,8 +2693,11 @@
       <c r="R8" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.15">
+      <c r="W8" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A9" s="1">
         <v>5</v>
       </c>
@@ -2716,8 +2752,11 @@
       <c r="R9" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.15">
+      <c r="W9" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A10" s="1">
         <v>6</v>
       </c>
@@ -2772,8 +2811,11 @@
       <c r="R10" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.15">
+      <c r="W10" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A11" s="1">
         <v>7</v>
       </c>
@@ -2828,8 +2870,11 @@
       <c r="R11" s="1">
         <v>101</v>
       </c>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.15">
+      <c r="W11" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A12" s="1">
         <v>8</v>
       </c>
@@ -2884,8 +2929,11 @@
       <c r="R12" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.15">
+      <c r="W12" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A13" s="1">
         <v>9</v>
       </c>
@@ -2940,8 +2988,11 @@
       <c r="R13" s="1">
         <v>101</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W13" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="1">
         <v>10</v>
       </c>
@@ -2996,8 +3047,11 @@
       <c r="R14" s="1">
         <v>101</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.15">
+      <c r="W14" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A15" s="1">
         <v>11</v>
       </c>
@@ -3061,8 +3115,11 @@
       <c r="U15" s="1" t="s">
         <v>568</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.15">
+      <c r="W15" s="1" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A16" s="1">
         <v>12</v>
       </c>
@@ -3129,8 +3186,11 @@
       <c r="V16" s="1" t="s">
         <v>580</v>
       </c>
-    </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W16" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A17" s="1">
         <v>13</v>
       </c>
@@ -3185,8 +3245,11 @@
       <c r="R17" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W17" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A18" s="1">
         <v>14</v>
       </c>
@@ -3241,8 +3304,11 @@
       <c r="R18" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W18" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A19" s="1">
         <v>15</v>
       </c>
@@ -3297,8 +3363,11 @@
       <c r="R19" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W19" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A20" s="1">
         <v>16</v>
       </c>
@@ -3353,8 +3422,11 @@
       <c r="R20" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W20" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A21" s="1">
         <v>17</v>
       </c>
@@ -3409,8 +3481,11 @@
       <c r="R21" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W21" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A22" s="1">
         <v>18</v>
       </c>
@@ -3465,8 +3540,11 @@
       <c r="R22" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W22" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A23" s="1">
         <v>19</v>
       </c>
@@ -3521,8 +3599,11 @@
       <c r="R23" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W23" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A24" s="1">
         <v>20</v>
       </c>
@@ -3577,8 +3658,11 @@
       <c r="R24" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W24" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A25" s="1">
         <v>21</v>
       </c>
@@ -3633,8 +3717,11 @@
       <c r="R25" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W25" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A26" s="1">
         <v>22</v>
       </c>
@@ -3689,8 +3776,11 @@
       <c r="R26" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W26" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A27" s="1">
         <v>23</v>
       </c>
@@ -3745,8 +3835,11 @@
       <c r="R27" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W27" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A28" s="1">
         <v>24</v>
       </c>
@@ -3801,8 +3894,11 @@
       <c r="R28" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W28" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A29" s="1">
         <v>25</v>
       </c>
@@ -3857,8 +3953,11 @@
       <c r="R29" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W29" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A30" s="1">
         <v>26</v>
       </c>
@@ -3913,8 +4012,11 @@
       <c r="R30" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W30" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A31" s="1">
         <v>27</v>
       </c>
@@ -3969,8 +4071,11 @@
       <c r="R31" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W31" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A32" s="1">
         <v>28</v>
       </c>
@@ -4025,8 +4130,11 @@
       <c r="R32" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W32" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A33" s="1">
         <v>29</v>
       </c>
@@ -4081,8 +4189,11 @@
       <c r="R33" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W33" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A34" s="1">
         <v>30</v>
       </c>
@@ -4137,8 +4248,11 @@
       <c r="R34" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W34" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A35" s="1">
         <v>31</v>
       </c>
@@ -4193,8 +4307,11 @@
       <c r="R35" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W35" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A36" s="1">
         <v>32</v>
       </c>
@@ -4249,8 +4366,11 @@
       <c r="R36" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W36" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A37" s="1">
         <v>33</v>
       </c>
@@ -4305,8 +4425,11 @@
       <c r="R37" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W37" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A38" s="1">
         <v>34</v>
       </c>
@@ -4361,8 +4484,11 @@
       <c r="R38" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W38" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A39" s="1">
         <v>35</v>
       </c>
@@ -4417,8 +4543,11 @@
       <c r="R39" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W39" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A40" s="1">
         <v>36</v>
       </c>
@@ -4473,8 +4602,11 @@
       <c r="R40" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W40" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A41" s="1">
         <v>37</v>
       </c>
@@ -4529,8 +4661,11 @@
       <c r="R41" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W41" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A42" s="1">
         <v>38</v>
       </c>
@@ -4585,8 +4720,11 @@
       <c r="R42" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W42" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A43" s="1">
         <v>39</v>
       </c>
@@ -4641,8 +4779,11 @@
       <c r="R43" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W43" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A44" s="1">
         <v>40</v>
       </c>
@@ -4697,8 +4838,11 @@
       <c r="R44" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W44" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A45" s="1">
         <v>41</v>
       </c>
@@ -4753,8 +4897,11 @@
       <c r="R45" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W45" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A46" s="1">
         <v>42</v>
       </c>
@@ -4809,8 +4956,11 @@
       <c r="R46" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W46" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A47" s="1">
         <v>43</v>
       </c>
@@ -4865,8 +5015,11 @@
       <c r="R47" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W47" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A48" s="1">
         <v>44</v>
       </c>
@@ -4921,8 +5074,11 @@
       <c r="R48" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W48" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A49" s="1">
         <v>45</v>
       </c>
@@ -4977,8 +5133,11 @@
       <c r="R49" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W49" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A50" s="1">
         <v>46</v>
       </c>
@@ -5033,8 +5192,11 @@
       <c r="R50" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W50" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A51" s="1">
         <v>47</v>
       </c>
@@ -5089,8 +5251,11 @@
       <c r="R51" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W51" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A52" s="1">
         <v>48</v>
       </c>
@@ -5145,8 +5310,11 @@
       <c r="R52" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W52" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A53" s="1">
         <v>49</v>
       </c>
@@ -5201,8 +5369,11 @@
       <c r="R53" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W53" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A54" s="1">
         <v>50</v>
       </c>
@@ -5257,8 +5428,11 @@
       <c r="R54" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W54" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A55" s="1">
         <v>51</v>
       </c>
@@ -5313,8 +5487,11 @@
       <c r="R55" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W55" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A56" s="1">
         <v>52</v>
       </c>
@@ -5369,8 +5546,11 @@
       <c r="R56" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W56" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A57" s="1">
         <v>53</v>
       </c>
@@ -5425,8 +5605,11 @@
       <c r="R57" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W57" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A58" s="1">
         <v>54</v>
       </c>
@@ -5481,8 +5664,11 @@
       <c r="R58" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W58" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A59" s="1">
         <v>55</v>
       </c>
@@ -5537,8 +5723,11 @@
       <c r="R59" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W59" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A60" s="1">
         <v>56</v>
       </c>
@@ -5593,8 +5782,11 @@
       <c r="R60" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W60" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A61" s="1">
         <v>57</v>
       </c>
@@ -5649,8 +5841,11 @@
       <c r="R61" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W61" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A62" s="1">
         <v>58</v>
       </c>
@@ -5705,8 +5900,11 @@
       <c r="R62" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W62" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A63" s="1">
         <v>59</v>
       </c>
@@ -5761,8 +5959,11 @@
       <c r="R63" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W63" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A64" s="1">
         <v>60</v>
       </c>
@@ -5817,8 +6018,11 @@
       <c r="R64" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="65" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W64" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A65" s="1">
         <v>61</v>
       </c>
@@ -5873,8 +6077,11 @@
       <c r="R65" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="66" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W65" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A66" s="1">
         <v>62</v>
       </c>
@@ -5929,8 +6136,11 @@
       <c r="R66" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="67" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W66" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A67" s="1">
         <v>63</v>
       </c>
@@ -5985,8 +6195,11 @@
       <c r="R67" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="68" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W67" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A68" s="1">
         <v>64</v>
       </c>
@@ -6041,8 +6254,11 @@
       <c r="R68" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="69" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W68" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A69" s="1">
         <v>65</v>
       </c>
@@ -6097,8 +6313,11 @@
       <c r="R69" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="70" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W69" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A70" s="1">
         <v>66</v>
       </c>
@@ -6153,8 +6372,11 @@
       <c r="R70" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="71" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W70" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A71" s="1">
         <v>67</v>
       </c>
@@ -6209,8 +6431,11 @@
       <c r="R71" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="72" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W71" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A72" s="1">
         <v>68</v>
       </c>
@@ -6265,8 +6490,11 @@
       <c r="R72" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="73" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W72" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A73" s="1">
         <v>69</v>
       </c>
@@ -6321,8 +6549,11 @@
       <c r="R73" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="74" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W73" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A74" s="1">
         <v>70</v>
       </c>
@@ -6377,8 +6608,11 @@
       <c r="R74" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="75" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W74" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A75" s="1">
         <v>71</v>
       </c>
@@ -6433,8 +6667,11 @@
       <c r="R75" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="76" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W75" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A76" s="1">
         <v>72</v>
       </c>
@@ -6489,8 +6726,11 @@
       <c r="R76" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="77" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W76" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A77" s="1">
         <v>73</v>
       </c>
@@ -6545,8 +6785,11 @@
       <c r="R77" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="78" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W77" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A78" s="1">
         <v>74</v>
       </c>
@@ -6601,8 +6844,11 @@
       <c r="R78" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="79" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W78" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A79" s="1">
         <v>75</v>
       </c>
@@ -6657,8 +6903,11 @@
       <c r="R79" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="80" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W79" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A80" s="1">
         <v>76</v>
       </c>
@@ -6713,8 +6962,11 @@
       <c r="R80" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="81" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W80" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A81" s="1">
         <v>77</v>
       </c>
@@ -6769,8 +7021,11 @@
       <c r="R81" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="82" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W81" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A82" s="1">
         <v>78</v>
       </c>
@@ -6825,8 +7080,11 @@
       <c r="R82" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="83" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W82" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A83" s="1">
         <v>79</v>
       </c>
@@ -6881,8 +7139,11 @@
       <c r="R83" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="84" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W83" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A84" s="1">
         <v>80</v>
       </c>
@@ -6937,8 +7198,11 @@
       <c r="R84" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="85" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W84" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A85" s="1">
         <v>81</v>
       </c>
@@ -6993,8 +7257,11 @@
       <c r="R85" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="86" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W85" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A86" s="1">
         <v>82</v>
       </c>
@@ -7049,8 +7316,11 @@
       <c r="R86" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="87" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W86" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A87" s="1">
         <v>83</v>
       </c>
@@ -7105,8 +7375,11 @@
       <c r="R87" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="88" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W87" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A88" s="1">
         <v>84</v>
       </c>
@@ -7161,8 +7434,11 @@
       <c r="R88" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="89" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W88" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A89" s="1">
         <v>85</v>
       </c>
@@ -7217,8 +7493,11 @@
       <c r="R89" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="90" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W89" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A90" s="1">
         <v>86</v>
       </c>
@@ -7273,8 +7552,11 @@
       <c r="R90" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="91" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W90" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A91" s="1">
         <v>87</v>
       </c>
@@ -7329,8 +7611,11 @@
       <c r="R91" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="92" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W91" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A92" s="1">
         <v>88</v>
       </c>
@@ -7385,8 +7670,11 @@
       <c r="R92" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="93" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W92" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A93" s="1">
         <v>89</v>
       </c>
@@ -7441,8 +7729,11 @@
       <c r="R93" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="94" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W93" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A94" s="1">
         <v>90</v>
       </c>
@@ -7497,8 +7788,11 @@
       <c r="R94" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="95" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W94" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A95" s="1">
         <v>91</v>
       </c>
@@ -7553,8 +7847,11 @@
       <c r="R95" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="96" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W95" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A96" s="1">
         <v>92</v>
       </c>
@@ -7609,8 +7906,11 @@
       <c r="R96" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="97" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W96" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A97" s="1">
         <v>93</v>
       </c>
@@ -7665,8 +7965,11 @@
       <c r="R97" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="98" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W97" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A98" s="1">
         <v>94</v>
       </c>
@@ -7721,8 +8024,11 @@
       <c r="R98" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="99" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W98" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A99" s="1">
         <v>95</v>
       </c>
@@ -7777,8 +8083,11 @@
       <c r="R99" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="100" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W99" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A100" s="1">
         <v>96</v>
       </c>
@@ -7833,8 +8142,11 @@
       <c r="R100" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="101" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W100" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A101" s="1">
         <v>97</v>
       </c>
@@ -7889,8 +8201,11 @@
       <c r="R101" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="102" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W101" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A102" s="1">
         <v>98</v>
       </c>
@@ -7945,8 +8260,11 @@
       <c r="R102" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="103" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W102" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A103" s="1">
         <v>99</v>
       </c>
@@ -8001,8 +8319,11 @@
       <c r="R103" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="104" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W103" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A104" s="1">
         <v>100</v>
       </c>
@@ -8057,8 +8378,11 @@
       <c r="R104" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="105" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W104" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A105" s="1">
         <v>101</v>
       </c>
@@ -8113,8 +8437,11 @@
       <c r="R105" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="106" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W105" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A106" s="1">
         <v>102</v>
       </c>
@@ -8169,8 +8496,11 @@
       <c r="R106" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="107" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W106" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A107" s="1">
         <v>103</v>
       </c>
@@ -8225,8 +8555,11 @@
       <c r="R107" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="108" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W107" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A108" s="1">
         <v>104</v>
       </c>
@@ -8281,8 +8614,11 @@
       <c r="R108" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="109" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W108" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A109" s="1">
         <v>105</v>
       </c>
@@ -8337,8 +8673,11 @@
       <c r="R109" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="110" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W109" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A110" s="1">
         <v>106</v>
       </c>
@@ -8393,8 +8732,11 @@
       <c r="R110" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="111" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W110" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A111" s="1">
         <v>107</v>
       </c>
@@ -8449,8 +8791,11 @@
       <c r="R111" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="112" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W111" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A112" s="1">
         <v>108</v>
       </c>
@@ -8505,8 +8850,11 @@
       <c r="R112" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="113" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W112" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A113" s="1">
         <v>109</v>
       </c>
@@ -8561,8 +8909,11 @@
       <c r="R113" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="114" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W113" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A114" s="1">
         <v>110</v>
       </c>
@@ -8617,8 +8968,11 @@
       <c r="R114" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="115" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W114" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A115" s="1">
         <v>111</v>
       </c>
@@ -8673,8 +9027,11 @@
       <c r="R115" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="116" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W115" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A116" s="1">
         <v>112</v>
       </c>
@@ -8729,8 +9086,11 @@
       <c r="R116" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="117" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W116" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A117" s="1">
         <v>113</v>
       </c>
@@ -8785,8 +9145,11 @@
       <c r="R117" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="118" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W117" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A118" s="1">
         <v>114</v>
       </c>
@@ -8841,8 +9204,11 @@
       <c r="R118" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="119" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W118" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A119" s="1">
         <v>115</v>
       </c>
@@ -8897,8 +9263,11 @@
       <c r="R119" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="120" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W119" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A120" s="1">
         <v>116</v>
       </c>
@@ -8953,8 +9322,11 @@
       <c r="R120" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="121" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W120" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A121" s="1">
         <v>117</v>
       </c>
@@ -9009,8 +9381,11 @@
       <c r="R121" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="122" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W121" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A122" s="1">
         <v>118</v>
       </c>
@@ -9065,8 +9440,11 @@
       <c r="R122" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="123" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W122" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A123" s="1">
         <v>119</v>
       </c>
@@ -9121,8 +9499,11 @@
       <c r="R123" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="124" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W123" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A124" s="1">
         <v>120</v>
       </c>
@@ -9177,8 +9558,11 @@
       <c r="R124" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="125" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W124" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A125" s="1">
         <v>121</v>
       </c>
@@ -9233,8 +9617,11 @@
       <c r="R125" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="126" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W125" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A126" s="1">
         <v>122</v>
       </c>
@@ -9289,8 +9676,11 @@
       <c r="R126" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="127" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W126" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A127" s="1">
         <v>123</v>
       </c>
@@ -9345,8 +9735,11 @@
       <c r="R127" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="128" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W127" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A128" s="1">
         <v>124</v>
       </c>
@@ -9401,8 +9794,11 @@
       <c r="R128" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="129" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W128" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A129" s="1">
         <v>125</v>
       </c>
@@ -9457,8 +9853,11 @@
       <c r="R129" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="130" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W129" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A130" s="1">
         <v>126</v>
       </c>
@@ -9513,8 +9912,11 @@
       <c r="R130" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="131" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W130" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A131" s="1">
         <v>127</v>
       </c>
@@ -9569,8 +9971,11 @@
       <c r="R131" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="132" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W131" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A132" s="1">
         <v>128</v>
       </c>
@@ -9625,8 +10030,11 @@
       <c r="R132" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="133" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W132" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A133" s="1">
         <v>129</v>
       </c>
@@ -9681,8 +10089,11 @@
       <c r="R133" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="134" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W133" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A134" s="1">
         <v>130</v>
       </c>
@@ -9737,8 +10148,11 @@
       <c r="R134" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="135" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W134" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A135" s="1">
         <v>131</v>
       </c>
@@ -9793,8 +10207,11 @@
       <c r="R135" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="136" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W135" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A136" s="1">
         <v>132</v>
       </c>
@@ -9849,8 +10266,11 @@
       <c r="R136" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="137" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W136" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A137" s="1">
         <v>133</v>
       </c>
@@ -9905,8 +10325,11 @@
       <c r="R137" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="138" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W137" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A138" s="1">
         <v>134</v>
       </c>
@@ -9961,8 +10384,11 @@
       <c r="R138" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="139" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W138" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A139" s="1">
         <v>135</v>
       </c>
@@ -10017,8 +10443,11 @@
       <c r="R139" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="140" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W139" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A140" s="1">
         <v>136</v>
       </c>
@@ -10073,8 +10502,11 @@
       <c r="R140" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="141" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W140" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A141" s="1">
         <v>137</v>
       </c>
@@ -10129,8 +10561,11 @@
       <c r="R141" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="142" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W141" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A142" s="1">
         <v>138</v>
       </c>
@@ -10185,8 +10620,11 @@
       <c r="R142" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="143" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W142" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A143" s="1">
         <v>139</v>
       </c>
@@ -10241,8 +10679,11 @@
       <c r="R143" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="144" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W143" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A144" s="1">
         <v>140</v>
       </c>
@@ -10297,8 +10738,11 @@
       <c r="R144" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="145" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W144" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A145" s="1">
         <v>141</v>
       </c>
@@ -10353,8 +10797,11 @@
       <c r="R145" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="146" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W145" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A146" s="1">
         <v>142</v>
       </c>
@@ -10409,8 +10856,11 @@
       <c r="R146" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="147" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W146" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A147" s="1">
         <v>143</v>
       </c>
@@ -10465,8 +10915,11 @@
       <c r="R147" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="148" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W147" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A148" s="1">
         <v>144</v>
       </c>
@@ -10521,8 +10974,11 @@
       <c r="R148" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="149" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W148" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A149" s="1">
         <v>145</v>
       </c>
@@ -10577,8 +11033,11 @@
       <c r="R149" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="150" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W149" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A150" s="1">
         <v>146</v>
       </c>
@@ -10633,8 +11092,11 @@
       <c r="R150" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="151" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W150" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A151" s="1">
         <v>147</v>
       </c>
@@ -10689,8 +11151,11 @@
       <c r="R151" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="152" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W151" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A152" s="1">
         <v>148</v>
       </c>
@@ -10745,8 +11210,11 @@
       <c r="R152" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="153" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W152" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A153" s="1">
         <v>149</v>
       </c>
@@ -10801,8 +11269,11 @@
       <c r="R153" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="154" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W153" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A154" s="1">
         <v>150</v>
       </c>
@@ -10857,8 +11328,11 @@
       <c r="R154" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="155" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W154" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A155" s="1">
         <v>151</v>
       </c>
@@ -10913,8 +11387,11 @@
       <c r="R155" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="156" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W155" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A156" s="1">
         <v>152</v>
       </c>
@@ -10969,8 +11446,11 @@
       <c r="R156" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="157" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W156" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A157" s="1">
         <v>153</v>
       </c>
@@ -11025,8 +11505,11 @@
       <c r="R157" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="158" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W157" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A158" s="1">
         <v>154</v>
       </c>
@@ -11081,8 +11564,11 @@
       <c r="R158" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="159" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W158" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A159" s="1">
         <v>155</v>
       </c>
@@ -11137,8 +11623,11 @@
       <c r="R159" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="160" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W159" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A160" s="1">
         <v>156</v>
       </c>
@@ -11193,8 +11682,11 @@
       <c r="R160" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="161" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W160" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A161" s="1">
         <v>157</v>
       </c>
@@ -11249,8 +11741,11 @@
       <c r="R161" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="162" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W161" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A162" s="1">
         <v>158</v>
       </c>
@@ -11305,8 +11800,11 @@
       <c r="R162" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="163" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W162" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A163" s="1">
         <v>159</v>
       </c>
@@ -11361,8 +11859,11 @@
       <c r="R163" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="164" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="W163" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A164" s="1">
         <v>160</v>
       </c>
@@ -11416,11 +11917,15 @@
       </c>
       <c r="R164" s="1" t="s">
         <v>239</v>
+      </c>
+      <c r="W164" s="1">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6DCF909-D463-41B1-BA48-4B3E5A5DF0DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB3AA3E1-3D0B-41E0-B5A3-5C5A664B579D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1221" uniqueCount="584">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1224" uniqueCount="588">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -896,12 +896,6 @@
     <t>200001:101_0:101</t>
   </si>
   <si>
-    <t>210001:100_0:100</t>
-  </si>
-  <si>
-    <t>210001:101_0:101</t>
-  </si>
-  <si>
     <t>220001:100_0:100</t>
   </si>
   <si>
@@ -1867,6 +1861,26 @@
   </si>
   <si>
     <t>110001,110002,110003,110004,110005,110006,110007,110008,110009,110011</t>
+  </si>
+  <si>
+    <t>210001:1101_0:100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>210001:102_0:102</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>210001:0</t>
+  </si>
+  <si>
+    <t>210001:10000</t>
+  </si>
+  <si>
+    <t>210001:20000</t>
+  </si>
+  <si>
+    <t>210001:35</t>
   </si>
 </sst>
 </file>
@@ -2372,10 +2386,10 @@
         <v>245</v>
       </c>
       <c r="V3" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="W3" s="5" t="s">
         <v>579</v>
-      </c>
-      <c r="W3" s="5" t="s">
-        <v>581</v>
       </c>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.15">
@@ -2443,10 +2457,10 @@
         <v>242</v>
       </c>
       <c r="V4" s="1" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="W4" s="1" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.15">
@@ -2493,10 +2507,10 @@
         <v>150</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="Q5" s="3" t="s">
         <v>231</v>
@@ -2508,13 +2522,13 @@
         <v>247</v>
       </c>
       <c r="T5" s="1" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="U5" s="1" t="s">
         <v>248</v>
       </c>
       <c r="V5" s="1" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="W5" s="1">
         <v>0</v>
@@ -2564,10 +2578,10 @@
         <v>200</v>
       </c>
       <c r="O6" s="4" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="P6" s="4" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="Q6" s="3" t="s">
         <v>231</v>
@@ -2623,10 +2637,10 @@
         <v>300</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="P7" s="4" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="Q7" s="3" t="s">
         <v>231</v>
@@ -2682,10 +2696,10 @@
         <v>400</v>
       </c>
       <c r="O8" s="4" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="P8" s="4" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="Q8" s="3" t="s">
         <v>231</v>
@@ -2741,10 +2755,10 @@
         <v>500</v>
       </c>
       <c r="O9" s="4" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="P9" s="4" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="Q9" s="3" t="s">
         <v>231</v>
@@ -2800,10 +2814,10 @@
         <v>600</v>
       </c>
       <c r="O10" s="4" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="P10" s="4" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="Q10" s="3" t="s">
         <v>231</v>
@@ -2859,10 +2873,10 @@
         <v>100</v>
       </c>
       <c r="O11" s="4" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="P11" s="4" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="Q11" s="3" t="s">
         <v>231</v>
@@ -2918,10 +2932,10 @@
         <v>100</v>
       </c>
       <c r="O12" s="4" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="P12" s="4" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="Q12" s="3" t="s">
         <v>231</v>
@@ -2977,10 +2991,10 @@
         <v>100</v>
       </c>
       <c r="O13" s="4" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="P13" s="4" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="Q13" s="3" t="s">
         <v>231</v>
@@ -3036,10 +3050,10 @@
         <v>100</v>
       </c>
       <c r="O14" s="4" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="P14" s="4" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>231</v>
@@ -3095,28 +3109,28 @@
         <v>100</v>
       </c>
       <c r="O15" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="P15" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="Q15" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="R15" s="1">
+        <v>0</v>
+      </c>
+      <c r="S15" s="1" t="s">
         <v>564</v>
       </c>
-      <c r="P15" s="1" t="s">
+      <c r="T15" s="1" t="s">
         <v>565</v>
       </c>
-      <c r="Q15" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="R15" s="1">
-        <v>0</v>
-      </c>
-      <c r="S15" s="1" t="s">
+      <c r="U15" s="1" t="s">
         <v>566</v>
       </c>
-      <c r="T15" s="1" t="s">
-        <v>567</v>
-      </c>
-      <c r="U15" s="1" t="s">
-        <v>568</v>
-      </c>
       <c r="W15" s="1" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.15">
@@ -3163,11 +3177,11 @@
         <v>100</v>
       </c>
       <c r="O16" s="4" t="s">
+        <v>567</v>
+      </c>
+      <c r="P16" s="4" t="s">
         <v>569</v>
       </c>
-      <c r="P16" s="4" t="s">
-        <v>571</v>
-      </c>
       <c r="Q16" s="3" t="s">
         <v>231</v>
       </c>
@@ -3175,16 +3189,16 @@
         <v>0</v>
       </c>
       <c r="S16" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="T16" s="1" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="U16" s="1" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="V16" s="1" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="W16" s="1">
         <v>0</v>
@@ -3706,16 +3720,28 @@
         <v>100</v>
       </c>
       <c r="O25" s="4" t="s">
-        <v>266</v>
+        <v>582</v>
       </c>
       <c r="P25" s="4" t="s">
-        <v>267</v>
+        <v>583</v>
       </c>
       <c r="Q25" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="R25" s="1" t="s">
-        <v>239</v>
+      <c r="R25" s="1">
+        <v>0</v>
+      </c>
+      <c r="S25" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="T25" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="U25" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="V25" s="1" t="s">
+        <v>587</v>
       </c>
       <c r="W25" s="1">
         <v>0</v>
@@ -3765,10 +3791,10 @@
         <v>100</v>
       </c>
       <c r="O26" s="4" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="P26" s="4" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="Q26" s="3" t="s">
         <v>231</v>
@@ -3824,10 +3850,10 @@
         <v>100</v>
       </c>
       <c r="O27" s="4" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="P27" s="4" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="Q27" s="3" t="s">
         <v>231</v>
@@ -3883,10 +3909,10 @@
         <v>100</v>
       </c>
       <c r="O28" s="4" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="P28" s="4" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="Q28" s="3" t="s">
         <v>231</v>
@@ -3942,10 +3968,10 @@
         <v>100</v>
       </c>
       <c r="O29" s="4" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="P29" s="4" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="Q29" s="3" t="s">
         <v>231</v>
@@ -4001,10 +4027,10 @@
         <v>100</v>
       </c>
       <c r="O30" s="4" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="P30" s="4" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="Q30" s="3" t="s">
         <v>231</v>
@@ -4060,10 +4086,10 @@
         <v>100</v>
       </c>
       <c r="O31" s="4" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="P31" s="4" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="Q31" s="3" t="s">
         <v>231</v>
@@ -4119,10 +4145,10 @@
         <v>100</v>
       </c>
       <c r="O32" s="4" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="P32" s="4" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="Q32" s="3" t="s">
         <v>231</v>
@@ -4178,10 +4204,10 @@
         <v>100</v>
       </c>
       <c r="O33" s="4" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="P33" s="4" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="Q33" s="3" t="s">
         <v>231</v>
@@ -4237,10 +4263,10 @@
         <v>100</v>
       </c>
       <c r="O34" s="4" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="P34" s="4" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="Q34" s="3" t="s">
         <v>231</v>
@@ -4296,10 +4322,10 @@
         <v>100</v>
       </c>
       <c r="O35" s="4" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="P35" s="4" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="Q35" s="3" t="s">
         <v>231</v>
@@ -4355,10 +4381,10 @@
         <v>100</v>
       </c>
       <c r="O36" s="4" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="P36" s="4" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="Q36" s="3" t="s">
         <v>231</v>
@@ -4414,10 +4440,10 @@
         <v>100</v>
       </c>
       <c r="O37" s="4" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="P37" s="4" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="Q37" s="3" t="s">
         <v>231</v>
@@ -4473,10 +4499,10 @@
         <v>100</v>
       </c>
       <c r="O38" s="4" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="P38" s="4" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="Q38" s="3" t="s">
         <v>231</v>
@@ -4532,10 +4558,10 @@
         <v>100</v>
       </c>
       <c r="O39" s="4" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="P39" s="4" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="Q39" s="3" t="s">
         <v>231</v>
@@ -4591,10 +4617,10 @@
         <v>100</v>
       </c>
       <c r="O40" s="4" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="P40" s="4" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="Q40" s="3" t="s">
         <v>231</v>
@@ -4650,10 +4676,10 @@
         <v>100</v>
       </c>
       <c r="O41" s="4" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="P41" s="4" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="Q41" s="3" t="s">
         <v>231</v>
@@ -4709,10 +4735,10 @@
         <v>100</v>
       </c>
       <c r="O42" s="4" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="P42" s="4" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="Q42" s="3" t="s">
         <v>231</v>
@@ -4768,10 +4794,10 @@
         <v>100</v>
       </c>
       <c r="O43" s="4" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="P43" s="4" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="Q43" s="3" t="s">
         <v>231</v>
@@ -4827,10 +4853,10 @@
         <v>100</v>
       </c>
       <c r="O44" s="4" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="P44" s="4" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="Q44" s="3" t="s">
         <v>231</v>
@@ -4886,10 +4912,10 @@
         <v>100</v>
       </c>
       <c r="O45" s="4" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="P45" s="4" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="Q45" s="3" t="s">
         <v>231</v>
@@ -4945,10 +4971,10 @@
         <v>100</v>
       </c>
       <c r="O46" s="4" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="P46" s="4" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="Q46" s="3" t="s">
         <v>231</v>
@@ -5004,10 +5030,10 @@
         <v>100</v>
       </c>
       <c r="O47" s="4" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="P47" s="4" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="Q47" s="3" t="s">
         <v>231</v>
@@ -5063,10 +5089,10 @@
         <v>100</v>
       </c>
       <c r="O48" s="4" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="P48" s="4" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="Q48" s="3" t="s">
         <v>231</v>
@@ -5122,10 +5148,10 @@
         <v>100</v>
       </c>
       <c r="O49" s="4" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="P49" s="4" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="Q49" s="3" t="s">
         <v>231</v>
@@ -5181,10 +5207,10 @@
         <v>100</v>
       </c>
       <c r="O50" s="4" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="P50" s="4" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="Q50" s="3" t="s">
         <v>231</v>
@@ -5240,10 +5266,10 @@
         <v>100</v>
       </c>
       <c r="O51" s="4" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="P51" s="4" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="Q51" s="3" t="s">
         <v>231</v>
@@ -5299,10 +5325,10 @@
         <v>100</v>
       </c>
       <c r="O52" s="4" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="P52" s="4" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="Q52" s="3" t="s">
         <v>231</v>
@@ -5358,10 +5384,10 @@
         <v>100</v>
       </c>
       <c r="O53" s="4" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="P53" s="4" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="Q53" s="3" t="s">
         <v>231</v>
@@ -5417,10 +5443,10 @@
         <v>100</v>
       </c>
       <c r="O54" s="4" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="P54" s="4" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="Q54" s="3" t="s">
         <v>231</v>
@@ -5476,10 +5502,10 @@
         <v>100</v>
       </c>
       <c r="O55" s="4" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="P55" s="4" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="Q55" s="3" t="s">
         <v>231</v>
@@ -5535,10 +5561,10 @@
         <v>100</v>
       </c>
       <c r="O56" s="4" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="P56" s="4" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="Q56" s="3" t="s">
         <v>231</v>
@@ -5594,10 +5620,10 @@
         <v>100</v>
       </c>
       <c r="O57" s="4" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="P57" s="4" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="Q57" s="3" t="s">
         <v>231</v>
@@ -5653,10 +5679,10 @@
         <v>100</v>
       </c>
       <c r="O58" s="4" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="P58" s="4" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="Q58" s="3" t="s">
         <v>231</v>
@@ -5712,10 +5738,10 @@
         <v>100</v>
       </c>
       <c r="O59" s="4" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="P59" s="4" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="Q59" s="3" t="s">
         <v>231</v>
@@ -5771,10 +5797,10 @@
         <v>100</v>
       </c>
       <c r="O60" s="4" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="P60" s="4" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="Q60" s="3" t="s">
         <v>231</v>
@@ -5830,10 +5856,10 @@
         <v>100</v>
       </c>
       <c r="O61" s="4" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="P61" s="4" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="Q61" s="3" t="s">
         <v>231</v>
@@ -5889,10 +5915,10 @@
         <v>100</v>
       </c>
       <c r="O62" s="4" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="P62" s="4" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="Q62" s="3" t="s">
         <v>231</v>
@@ -5948,10 +5974,10 @@
         <v>100</v>
       </c>
       <c r="O63" s="4" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="P63" s="4" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="Q63" s="3" t="s">
         <v>231</v>
@@ -6007,10 +6033,10 @@
         <v>100</v>
       </c>
       <c r="O64" s="4" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="P64" s="4" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="Q64" s="3" t="s">
         <v>231</v>
@@ -6066,10 +6092,10 @@
         <v>100</v>
       </c>
       <c r="O65" s="4" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="P65" s="4" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="Q65" s="3" t="s">
         <v>231</v>
@@ -6125,10 +6151,10 @@
         <v>100</v>
       </c>
       <c r="O66" s="4" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="P66" s="4" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="Q66" s="3" t="s">
         <v>231</v>
@@ -6184,10 +6210,10 @@
         <v>100</v>
       </c>
       <c r="O67" s="4" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="P67" s="4" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="Q67" s="3" t="s">
         <v>231</v>
@@ -6243,10 +6269,10 @@
         <v>100</v>
       </c>
       <c r="O68" s="4" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="P68" s="4" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="Q68" s="3" t="s">
         <v>231</v>
@@ -6302,10 +6328,10 @@
         <v>100</v>
       </c>
       <c r="O69" s="4" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="P69" s="4" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="Q69" s="3" t="s">
         <v>231</v>
@@ -6361,10 +6387,10 @@
         <v>100</v>
       </c>
       <c r="O70" s="4" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="P70" s="4" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="Q70" s="3" t="s">
         <v>231</v>
@@ -6420,10 +6446,10 @@
         <v>100</v>
       </c>
       <c r="O71" s="4" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="P71" s="4" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="Q71" s="3" t="s">
         <v>231</v>
@@ -6479,10 +6505,10 @@
         <v>100</v>
       </c>
       <c r="O72" s="4" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="P72" s="4" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="Q72" s="3" t="s">
         <v>231</v>
@@ -6538,10 +6564,10 @@
         <v>100</v>
       </c>
       <c r="O73" s="4" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="P73" s="4" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="Q73" s="3" t="s">
         <v>231</v>
@@ -6597,10 +6623,10 @@
         <v>100</v>
       </c>
       <c r="O74" s="4" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="P74" s="4" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="Q74" s="3" t="s">
         <v>231</v>
@@ -6656,10 +6682,10 @@
         <v>100</v>
       </c>
       <c r="O75" s="4" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="P75" s="4" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="Q75" s="3" t="s">
         <v>231</v>
@@ -6715,10 +6741,10 @@
         <v>100</v>
       </c>
       <c r="O76" s="4" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="P76" s="4" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="Q76" s="3" t="s">
         <v>231</v>
@@ -6774,10 +6800,10 @@
         <v>100</v>
       </c>
       <c r="O77" s="4" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="P77" s="4" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="Q77" s="3" t="s">
         <v>231</v>
@@ -6833,10 +6859,10 @@
         <v>100</v>
       </c>
       <c r="O78" s="4" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="P78" s="4" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="Q78" s="3" t="s">
         <v>231</v>
@@ -6892,10 +6918,10 @@
         <v>100</v>
       </c>
       <c r="O79" s="4" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="P79" s="4" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="Q79" s="3" t="s">
         <v>231</v>
@@ -6951,10 +6977,10 @@
         <v>100</v>
       </c>
       <c r="O80" s="4" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="P80" s="4" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="Q80" s="3" t="s">
         <v>231</v>
@@ -7010,10 +7036,10 @@
         <v>100</v>
       </c>
       <c r="O81" s="4" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="P81" s="4" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="Q81" s="3" t="s">
         <v>231</v>
@@ -7069,10 +7095,10 @@
         <v>100</v>
       </c>
       <c r="O82" s="4" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="P82" s="4" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="Q82" s="3" t="s">
         <v>231</v>
@@ -7128,10 +7154,10 @@
         <v>100</v>
       </c>
       <c r="O83" s="4" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="P83" s="4" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="Q83" s="3" t="s">
         <v>231</v>
@@ -7187,10 +7213,10 @@
         <v>100</v>
       </c>
       <c r="O84" s="4" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="P84" s="4" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="Q84" s="3" t="s">
         <v>231</v>
@@ -7246,10 +7272,10 @@
         <v>100</v>
       </c>
       <c r="O85" s="4" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="P85" s="4" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="Q85" s="3" t="s">
         <v>231</v>
@@ -7305,10 +7331,10 @@
         <v>100</v>
       </c>
       <c r="O86" s="4" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="P86" s="4" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="Q86" s="3" t="s">
         <v>231</v>
@@ -7364,10 +7390,10 @@
         <v>100</v>
       </c>
       <c r="O87" s="4" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="P87" s="4" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="Q87" s="3" t="s">
         <v>231</v>
@@ -7423,10 +7449,10 @@
         <v>100</v>
       </c>
       <c r="O88" s="4" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="P88" s="4" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="Q88" s="3" t="s">
         <v>231</v>
@@ -7482,10 +7508,10 @@
         <v>100</v>
       </c>
       <c r="O89" s="4" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="P89" s="4" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="Q89" s="3" t="s">
         <v>231</v>
@@ -7541,10 +7567,10 @@
         <v>100</v>
       </c>
       <c r="O90" s="4" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="P90" s="4" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="Q90" s="3" t="s">
         <v>231</v>
@@ -7600,10 +7626,10 @@
         <v>100</v>
       </c>
       <c r="O91" s="4" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="P91" s="4" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="Q91" s="3" t="s">
         <v>231</v>
@@ -7659,10 +7685,10 @@
         <v>100</v>
       </c>
       <c r="O92" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="P92" s="4" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="Q92" s="3" t="s">
         <v>231</v>
@@ -7718,10 +7744,10 @@
         <v>100</v>
       </c>
       <c r="O93" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="P93" s="4" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="Q93" s="3" t="s">
         <v>231</v>
@@ -7777,10 +7803,10 @@
         <v>100</v>
       </c>
       <c r="O94" s="4" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="P94" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="Q94" s="3" t="s">
         <v>231</v>
@@ -7836,10 +7862,10 @@
         <v>100</v>
       </c>
       <c r="O95" s="4" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="P95" s="4" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="Q95" s="3" t="s">
         <v>231</v>
@@ -7895,10 +7921,10 @@
         <v>100</v>
       </c>
       <c r="O96" s="4" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="P96" s="4" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="Q96" s="3" t="s">
         <v>231</v>
@@ -7954,10 +7980,10 @@
         <v>100</v>
       </c>
       <c r="O97" s="4" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="P97" s="4" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="Q97" s="3" t="s">
         <v>231</v>
@@ -8013,10 +8039,10 @@
         <v>100</v>
       </c>
       <c r="O98" s="4" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="P98" s="4" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="Q98" s="3" t="s">
         <v>231</v>
@@ -8072,10 +8098,10 @@
         <v>100</v>
       </c>
       <c r="O99" s="4" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="P99" s="4" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="Q99" s="3" t="s">
         <v>231</v>
@@ -8131,10 +8157,10 @@
         <v>100</v>
       </c>
       <c r="O100" s="4" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="P100" s="4" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="Q100" s="3" t="s">
         <v>231</v>
@@ -8190,10 +8216,10 @@
         <v>100</v>
       </c>
       <c r="O101" s="4" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="P101" s="4" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="Q101" s="3" t="s">
         <v>231</v>
@@ -8249,10 +8275,10 @@
         <v>100</v>
       </c>
       <c r="O102" s="4" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="P102" s="4" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="Q102" s="3" t="s">
         <v>231</v>
@@ -8308,10 +8334,10 @@
         <v>100</v>
       </c>
       <c r="O103" s="4" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="P103" s="4" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="Q103" s="3" t="s">
         <v>231</v>
@@ -8367,10 +8393,10 @@
         <v>100</v>
       </c>
       <c r="O104" s="4" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="P104" s="4" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="Q104" s="3" t="s">
         <v>231</v>
@@ -8426,10 +8452,10 @@
         <v>100</v>
       </c>
       <c r="O105" s="4" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="P105" s="4" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="Q105" s="3" t="s">
         <v>231</v>
@@ -8485,10 +8511,10 @@
         <v>100</v>
       </c>
       <c r="O106" s="4" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="P106" s="4" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="Q106" s="3" t="s">
         <v>231</v>
@@ -8544,10 +8570,10 @@
         <v>100</v>
       </c>
       <c r="O107" s="4" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="P107" s="4" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="Q107" s="3" t="s">
         <v>231</v>
@@ -8603,10 +8629,10 @@
         <v>100</v>
       </c>
       <c r="O108" s="4" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="P108" s="4" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="Q108" s="3" t="s">
         <v>231</v>
@@ -8662,10 +8688,10 @@
         <v>100</v>
       </c>
       <c r="O109" s="4" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="P109" s="4" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="Q109" s="3" t="s">
         <v>231</v>
@@ -8721,10 +8747,10 @@
         <v>100</v>
       </c>
       <c r="O110" s="4" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="P110" s="4" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="Q110" s="3" t="s">
         <v>231</v>
@@ -8780,10 +8806,10 @@
         <v>100</v>
       </c>
       <c r="O111" s="4" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="P111" s="4" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="Q111" s="3" t="s">
         <v>231</v>
@@ -8839,10 +8865,10 @@
         <v>100</v>
       </c>
       <c r="O112" s="4" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="P112" s="4" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="Q112" s="3" t="s">
         <v>231</v>
@@ -8898,10 +8924,10 @@
         <v>100</v>
       </c>
       <c r="O113" s="4" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="P113" s="4" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="Q113" s="3" t="s">
         <v>231</v>
@@ -8957,10 +8983,10 @@
         <v>100</v>
       </c>
       <c r="O114" s="4" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="P114" s="4" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="Q114" s="3" t="s">
         <v>231</v>
@@ -9016,10 +9042,10 @@
         <v>100</v>
       </c>
       <c r="O115" s="4" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="P115" s="4" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="Q115" s="3" t="s">
         <v>231</v>
@@ -9075,10 +9101,10 @@
         <v>100</v>
       </c>
       <c r="O116" s="4" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="P116" s="4" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="Q116" s="3" t="s">
         <v>231</v>
@@ -9134,10 +9160,10 @@
         <v>100</v>
       </c>
       <c r="O117" s="4" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="P117" s="4" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="Q117" s="3" t="s">
         <v>231</v>
@@ -9193,10 +9219,10 @@
         <v>100</v>
       </c>
       <c r="O118" s="4" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="P118" s="4" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="Q118" s="3" t="s">
         <v>231</v>
@@ -9252,10 +9278,10 @@
         <v>100</v>
       </c>
       <c r="O119" s="4" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="P119" s="4" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="Q119" s="3" t="s">
         <v>231</v>
@@ -9311,10 +9337,10 @@
         <v>100</v>
       </c>
       <c r="O120" s="4" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="P120" s="4" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="Q120" s="3" t="s">
         <v>231</v>
@@ -9370,10 +9396,10 @@
         <v>100</v>
       </c>
       <c r="O121" s="4" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="P121" s="4" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="Q121" s="3" t="s">
         <v>231</v>
@@ -9429,10 +9455,10 @@
         <v>100</v>
       </c>
       <c r="O122" s="4" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="P122" s="4" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q122" s="3" t="s">
         <v>231</v>
@@ -9488,10 +9514,10 @@
         <v>100</v>
       </c>
       <c r="O123" s="4" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="P123" s="4" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="Q123" s="3" t="s">
         <v>231</v>
@@ -9547,10 +9573,10 @@
         <v>100</v>
       </c>
       <c r="O124" s="4" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="P124" s="4" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="Q124" s="3" t="s">
         <v>231</v>
@@ -9606,10 +9632,10 @@
         <v>100</v>
       </c>
       <c r="O125" s="4" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="P125" s="4" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="Q125" s="3" t="s">
         <v>231</v>
@@ -9665,10 +9691,10 @@
         <v>100</v>
       </c>
       <c r="O126" s="4" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="P126" s="4" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="Q126" s="3" t="s">
         <v>231</v>
@@ -9724,10 +9750,10 @@
         <v>100</v>
       </c>
       <c r="O127" s="4" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="P127" s="4" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="Q127" s="3" t="s">
         <v>231</v>
@@ -9783,10 +9809,10 @@
         <v>100</v>
       </c>
       <c r="O128" s="4" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="P128" s="4" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="Q128" s="3" t="s">
         <v>231</v>
@@ -9842,10 +9868,10 @@
         <v>100</v>
       </c>
       <c r="O129" s="4" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="P129" s="4" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="Q129" s="3" t="s">
         <v>231</v>
@@ -9901,10 +9927,10 @@
         <v>100</v>
       </c>
       <c r="O130" s="4" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="P130" s="4" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="Q130" s="3" t="s">
         <v>231</v>
@@ -9960,10 +9986,10 @@
         <v>100</v>
       </c>
       <c r="O131" s="4" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="P131" s="4" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="Q131" s="3" t="s">
         <v>231</v>
@@ -10019,10 +10045,10 @@
         <v>100</v>
       </c>
       <c r="O132" s="4" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="P132" s="4" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="Q132" s="3" t="s">
         <v>231</v>
@@ -10078,10 +10104,10 @@
         <v>100</v>
       </c>
       <c r="O133" s="4" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="P133" s="4" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="Q133" s="3" t="s">
         <v>231</v>
@@ -10137,10 +10163,10 @@
         <v>100</v>
       </c>
       <c r="O134" s="4" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="P134" s="4" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="Q134" s="3" t="s">
         <v>231</v>
@@ -10196,10 +10222,10 @@
         <v>100</v>
       </c>
       <c r="O135" s="4" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="P135" s="4" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="Q135" s="3" t="s">
         <v>231</v>
@@ -10255,10 +10281,10 @@
         <v>100</v>
       </c>
       <c r="O136" s="4" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="P136" s="4" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="Q136" s="3" t="s">
         <v>231</v>
@@ -10314,10 +10340,10 @@
         <v>100</v>
       </c>
       <c r="O137" s="4" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="P137" s="4" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="Q137" s="3" t="s">
         <v>231</v>
@@ -10373,10 +10399,10 @@
         <v>100</v>
       </c>
       <c r="O138" s="4" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="P138" s="4" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="Q138" s="3" t="s">
         <v>231</v>
@@ -10432,10 +10458,10 @@
         <v>100</v>
       </c>
       <c r="O139" s="4" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="P139" s="4" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="Q139" s="3" t="s">
         <v>231</v>
@@ -10491,10 +10517,10 @@
         <v>100</v>
       </c>
       <c r="O140" s="4" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="P140" s="4" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="Q140" s="3" t="s">
         <v>231</v>
@@ -10550,10 +10576,10 @@
         <v>100</v>
       </c>
       <c r="O141" s="4" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="P141" s="4" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="Q141" s="3" t="s">
         <v>231</v>
@@ -10609,10 +10635,10 @@
         <v>100</v>
       </c>
       <c r="O142" s="4" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="P142" s="4" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="Q142" s="3" t="s">
         <v>231</v>
@@ -10668,10 +10694,10 @@
         <v>100</v>
       </c>
       <c r="O143" s="4" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="P143" s="4" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="Q143" s="3" t="s">
         <v>231</v>
@@ -10727,10 +10753,10 @@
         <v>100</v>
       </c>
       <c r="O144" s="4" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="P144" s="4" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="Q144" s="3" t="s">
         <v>231</v>
@@ -10786,10 +10812,10 @@
         <v>100</v>
       </c>
       <c r="O145" s="4" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="P145" s="4" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="Q145" s="3" t="s">
         <v>231</v>
@@ -10845,10 +10871,10 @@
         <v>100</v>
       </c>
       <c r="O146" s="4" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="P146" s="4" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="Q146" s="3" t="s">
         <v>231</v>
@@ -10904,10 +10930,10 @@
         <v>100</v>
       </c>
       <c r="O147" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="P147" s="4" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="Q147" s="3" t="s">
         <v>231</v>
@@ -10963,10 +10989,10 @@
         <v>100</v>
       </c>
       <c r="O148" s="4" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="P148" s="4" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="Q148" s="3" t="s">
         <v>231</v>
@@ -11022,10 +11048,10 @@
         <v>100</v>
       </c>
       <c r="O149" s="4" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="P149" s="4" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="Q149" s="3" t="s">
         <v>231</v>
@@ -11081,10 +11107,10 @@
         <v>100</v>
       </c>
       <c r="O150" s="4" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="P150" s="4" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="Q150" s="3" t="s">
         <v>231</v>
@@ -11140,10 +11166,10 @@
         <v>100</v>
       </c>
       <c r="O151" s="4" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="P151" s="4" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="Q151" s="3" t="s">
         <v>231</v>
@@ -11199,10 +11225,10 @@
         <v>100</v>
       </c>
       <c r="O152" s="4" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="P152" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="Q152" s="3" t="s">
         <v>231</v>
@@ -11258,10 +11284,10 @@
         <v>100</v>
       </c>
       <c r="O153" s="4" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="P153" s="4" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="Q153" s="3" t="s">
         <v>231</v>
@@ -11317,10 +11343,10 @@
         <v>100</v>
       </c>
       <c r="O154" s="4" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="P154" s="4" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="Q154" s="3" t="s">
         <v>231</v>
@@ -11376,10 +11402,10 @@
         <v>100</v>
       </c>
       <c r="O155" s="4" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="P155" s="4" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="Q155" s="3" t="s">
         <v>231</v>
@@ -11435,10 +11461,10 @@
         <v>100</v>
       </c>
       <c r="O156" s="4" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="P156" s="4" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="Q156" s="3" t="s">
         <v>231</v>
@@ -11494,10 +11520,10 @@
         <v>100</v>
       </c>
       <c r="O157" s="4" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="P157" s="4" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="Q157" s="3" t="s">
         <v>231</v>
@@ -11553,10 +11579,10 @@
         <v>100</v>
       </c>
       <c r="O158" s="4" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="P158" s="4" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="Q158" s="3" t="s">
         <v>231</v>
@@ -11612,10 +11638,10 @@
         <v>100</v>
       </c>
       <c r="O159" s="4" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="P159" s="4" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="Q159" s="3" t="s">
         <v>231</v>
@@ -11671,10 +11697,10 @@
         <v>100</v>
       </c>
       <c r="O160" s="4" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="P160" s="4" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="Q160" s="3" t="s">
         <v>231</v>
@@ -11730,10 +11756,10 @@
         <v>100</v>
       </c>
       <c r="O161" s="4" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="P161" s="4" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="Q161" s="3" t="s">
         <v>231</v>
@@ -11789,10 +11815,10 @@
         <v>100</v>
       </c>
       <c r="O162" s="4" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="P162" s="4" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="Q162" s="3" t="s">
         <v>231</v>
@@ -11848,10 +11874,10 @@
         <v>100</v>
       </c>
       <c r="O163" s="4" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="P163" s="4" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="Q163" s="3" t="s">
         <v>231</v>
@@ -11907,10 +11933,10 @@
         <v>100</v>
       </c>
       <c r="O164" s="4" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="P164" s="4" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="Q164" s="3" t="s">
         <v>231</v>

--- a/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB3AA3E1-3D0B-41E0-B5A3-5C5A664B579D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA5FED47-1894-4340-9D88-454DB683F98A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_barries_v8" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1224" uniqueCount="588">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1387" uniqueCount="593">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1739,9 +1739,6 @@
     <t>30001:100_0:100</t>
   </si>
   <si>
-    <t>30001:101_0:101</t>
-  </si>
-  <si>
     <t>40001:100_0:100</t>
   </si>
   <si>
@@ -1881,6 +1878,30 @@
   </si>
   <si>
     <t>210001:35</t>
+  </si>
+  <si>
+    <t>30001:101_0:101</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0:0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>300002:100_300003:1000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MAP&lt;INT:INT&gt;_C</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>region_kongfu</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>区域标准通关值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2220,7 +2241,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:W164"/>
+  <dimension ref="A1:X164"/>
   <sheetFormatPr defaultColWidth="7.125" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.5" style="1" bestFit="1" customWidth="1"/>
@@ -2242,15 +2263,16 @@
     <col min="19" max="21" width="30.75" style="1" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="19.375" style="1" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="7.125" style="1"/>
+    <col min="24" max="24" width="18.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="7.125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -2320,8 +2342,11 @@
       <c r="W2" s="1" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X2" s="1" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -2386,13 +2411,16 @@
         <v>245</v>
       </c>
       <c r="V3" s="1" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="W3" s="5" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.15">
+        <v>578</v>
+      </c>
+      <c r="X3" s="1" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -2457,13 +2485,16 @@
         <v>242</v>
       </c>
       <c r="V4" s="1" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="W4" s="1" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.15">
+        <v>579</v>
+      </c>
+      <c r="X4" s="1" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -2507,10 +2538,10 @@
         <v>150</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="Q5" s="3" t="s">
         <v>231</v>
@@ -2522,19 +2553,22 @@
         <v>247</v>
       </c>
       <c r="T5" s="1" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="U5" s="1" t="s">
         <v>248</v>
       </c>
       <c r="V5" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="W5" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X5" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A6" s="1">
         <v>2</v>
       </c>
@@ -2592,8 +2626,11 @@
       <c r="W6" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X6" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A7" s="1">
         <v>3</v>
       </c>
@@ -2640,7 +2677,7 @@
         <v>546</v>
       </c>
       <c r="P7" s="4" t="s">
-        <v>547</v>
+        <v>587</v>
       </c>
       <c r="Q7" s="3" t="s">
         <v>231</v>
@@ -2651,8 +2688,11 @@
       <c r="W7" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X7" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A8" s="1">
         <v>4</v>
       </c>
@@ -2696,10 +2736,10 @@
         <v>400</v>
       </c>
       <c r="O8" s="4" t="s">
+        <v>547</v>
+      </c>
+      <c r="P8" s="4" t="s">
         <v>548</v>
-      </c>
-      <c r="P8" s="4" t="s">
-        <v>549</v>
       </c>
       <c r="Q8" s="3" t="s">
         <v>231</v>
@@ -2710,8 +2750,11 @@
       <c r="W8" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X8" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A9" s="1">
         <v>5</v>
       </c>
@@ -2755,10 +2798,10 @@
         <v>500</v>
       </c>
       <c r="O9" s="4" t="s">
+        <v>549</v>
+      </c>
+      <c r="P9" s="4" t="s">
         <v>550</v>
-      </c>
-      <c r="P9" s="4" t="s">
-        <v>551</v>
       </c>
       <c r="Q9" s="3" t="s">
         <v>231</v>
@@ -2769,8 +2812,11 @@
       <c r="W9" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X9" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A10" s="1">
         <v>6</v>
       </c>
@@ -2814,10 +2860,10 @@
         <v>600</v>
       </c>
       <c r="O10" s="4" t="s">
+        <v>551</v>
+      </c>
+      <c r="P10" s="4" t="s">
         <v>552</v>
-      </c>
-      <c r="P10" s="4" t="s">
-        <v>553</v>
       </c>
       <c r="Q10" s="3" t="s">
         <v>231</v>
@@ -2828,8 +2874,11 @@
       <c r="W10" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X10" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A11" s="1">
         <v>7</v>
       </c>
@@ -2873,10 +2922,10 @@
         <v>100</v>
       </c>
       <c r="O11" s="4" t="s">
+        <v>553</v>
+      </c>
+      <c r="P11" s="4" t="s">
         <v>554</v>
-      </c>
-      <c r="P11" s="4" t="s">
-        <v>555</v>
       </c>
       <c r="Q11" s="3" t="s">
         <v>231</v>
@@ -2887,8 +2936,11 @@
       <c r="W11" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X11" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A12" s="1">
         <v>8</v>
       </c>
@@ -2932,10 +2984,10 @@
         <v>100</v>
       </c>
       <c r="O12" s="4" t="s">
+        <v>555</v>
+      </c>
+      <c r="P12" s="4" t="s">
         <v>556</v>
-      </c>
-      <c r="P12" s="4" t="s">
-        <v>557</v>
       </c>
       <c r="Q12" s="3" t="s">
         <v>231</v>
@@ -2946,8 +2998,11 @@
       <c r="W12" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X12" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A13" s="1">
         <v>9</v>
       </c>
@@ -2991,10 +3046,10 @@
         <v>100</v>
       </c>
       <c r="O13" s="4" t="s">
+        <v>557</v>
+      </c>
+      <c r="P13" s="4" t="s">
         <v>558</v>
-      </c>
-      <c r="P13" s="4" t="s">
-        <v>559</v>
       </c>
       <c r="Q13" s="3" t="s">
         <v>231</v>
@@ -3005,8 +3060,11 @@
       <c r="W13" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X13" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="1">
         <v>10</v>
       </c>
@@ -3050,10 +3108,10 @@
         <v>100</v>
       </c>
       <c r="O14" s="4" t="s">
+        <v>559</v>
+      </c>
+      <c r="P14" s="4" t="s">
         <v>560</v>
-      </c>
-      <c r="P14" s="4" t="s">
-        <v>561</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>231</v>
@@ -3064,8 +3122,11 @@
       <c r="W14" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X14" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A15" s="1">
         <v>11</v>
       </c>
@@ -3109,31 +3170,34 @@
         <v>100</v>
       </c>
       <c r="O15" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="P15" s="1" t="s">
         <v>562</v>
       </c>
-      <c r="P15" s="1" t="s">
+      <c r="Q15" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="R15" s="1">
+        <v>0</v>
+      </c>
+      <c r="S15" s="1" t="s">
         <v>563</v>
       </c>
-      <c r="Q15" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="R15" s="1">
-        <v>0</v>
-      </c>
-      <c r="S15" s="1" t="s">
+      <c r="T15" s="1" t="s">
         <v>564</v>
       </c>
-      <c r="T15" s="1" t="s">
+      <c r="U15" s="1" t="s">
         <v>565</v>
       </c>
-      <c r="U15" s="1" t="s">
-        <v>566</v>
-      </c>
       <c r="W15" s="1" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.15">
+        <v>580</v>
+      </c>
+      <c r="X15" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A16" s="1">
         <v>12</v>
       </c>
@@ -3177,34 +3241,37 @@
         <v>100</v>
       </c>
       <c r="O16" s="4" t="s">
+        <v>566</v>
+      </c>
+      <c r="P16" s="4" t="s">
+        <v>568</v>
+      </c>
+      <c r="Q16" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="R16" s="1">
+        <v>0</v>
+      </c>
+      <c r="S16" s="1" t="s">
         <v>567</v>
       </c>
-      <c r="P16" s="4" t="s">
-        <v>569</v>
-      </c>
-      <c r="Q16" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="R16" s="1">
-        <v>0</v>
-      </c>
-      <c r="S16" s="1" t="s">
-        <v>568</v>
-      </c>
       <c r="T16" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="U16" s="1" t="s">
         <v>573</v>
       </c>
-      <c r="U16" s="1" t="s">
-        <v>574</v>
-      </c>
       <c r="V16" s="1" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="W16" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X16" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="17" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A17" s="1">
         <v>13</v>
       </c>
@@ -3262,8 +3329,11 @@
       <c r="W17" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X17" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="18" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A18" s="1">
         <v>14</v>
       </c>
@@ -3321,8 +3391,11 @@
       <c r="W18" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X18" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="19" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A19" s="1">
         <v>15</v>
       </c>
@@ -3380,8 +3453,11 @@
       <c r="W19" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X19" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="20" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A20" s="1">
         <v>16</v>
       </c>
@@ -3439,8 +3515,11 @@
       <c r="W20" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X20" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="21" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A21" s="1">
         <v>17</v>
       </c>
@@ -3498,8 +3577,11 @@
       <c r="W21" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X21" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="22" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A22" s="1">
         <v>18</v>
       </c>
@@ -3557,8 +3639,11 @@
       <c r="W22" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X22" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="23" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A23" s="1">
         <v>19</v>
       </c>
@@ -3616,8 +3701,11 @@
       <c r="W23" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X23" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="24" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A24" s="1">
         <v>20</v>
       </c>
@@ -3675,8 +3763,11 @@
       <c r="W24" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X24" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="25" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A25" s="1">
         <v>21</v>
       </c>
@@ -3720,34 +3811,37 @@
         <v>100</v>
       </c>
       <c r="O25" s="4" t="s">
+        <v>581</v>
+      </c>
+      <c r="P25" s="4" t="s">
         <v>582</v>
       </c>
-      <c r="P25" s="4" t="s">
+      <c r="Q25" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="R25" s="1">
+        <v>0</v>
+      </c>
+      <c r="S25" s="1" t="s">
         <v>583</v>
       </c>
-      <c r="Q25" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="R25" s="1">
-        <v>0</v>
-      </c>
-      <c r="S25" s="1" t="s">
+      <c r="T25" s="1" t="s">
         <v>584</v>
       </c>
-      <c r="T25" s="1" t="s">
+      <c r="U25" s="1" t="s">
         <v>585</v>
       </c>
-      <c r="U25" s="1" t="s">
+      <c r="V25" s="1" t="s">
         <v>586</v>
       </c>
-      <c r="V25" s="1" t="s">
-        <v>587</v>
-      </c>
       <c r="W25" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X25" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="26" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A26" s="1">
         <v>22</v>
       </c>
@@ -3805,8 +3899,11 @@
       <c r="W26" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X26" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="27" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A27" s="1">
         <v>23</v>
       </c>
@@ -3864,8 +3961,11 @@
       <c r="W27" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X27" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="28" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A28" s="1">
         <v>24</v>
       </c>
@@ -3923,8 +4023,11 @@
       <c r="W28" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X28" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="29" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A29" s="1">
         <v>25</v>
       </c>
@@ -3982,8 +4085,11 @@
       <c r="W29" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X29" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="30" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A30" s="1">
         <v>26</v>
       </c>
@@ -4041,8 +4147,11 @@
       <c r="W30" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X30" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="31" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A31" s="1">
         <v>27</v>
       </c>
@@ -4100,8 +4209,11 @@
       <c r="W31" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X31" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="32" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A32" s="1">
         <v>28</v>
       </c>
@@ -4159,8 +4271,11 @@
       <c r="W32" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X32" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="33" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A33" s="1">
         <v>29</v>
       </c>
@@ -4218,8 +4333,11 @@
       <c r="W33" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X33" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="34" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A34" s="1">
         <v>30</v>
       </c>
@@ -4277,8 +4395,11 @@
       <c r="W34" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X34" s="3" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="35" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A35" s="1">
         <v>31</v>
       </c>
@@ -4336,8 +4457,11 @@
       <c r="W35" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X35" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="36" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A36" s="1">
         <v>32</v>
       </c>
@@ -4395,8 +4519,11 @@
       <c r="W36" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X36" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="37" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A37" s="1">
         <v>33</v>
       </c>
@@ -4454,8 +4581,11 @@
       <c r="W37" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="38" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X37" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="38" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A38" s="1">
         <v>34</v>
       </c>
@@ -4513,8 +4643,11 @@
       <c r="W38" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="39" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X38" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="39" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A39" s="1">
         <v>35</v>
       </c>
@@ -4572,8 +4705,11 @@
       <c r="W39" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="40" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X39" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="40" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A40" s="1">
         <v>36</v>
       </c>
@@ -4631,8 +4767,11 @@
       <c r="W40" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X40" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="41" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A41" s="1">
         <v>37</v>
       </c>
@@ -4690,8 +4829,11 @@
       <c r="W41" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X41" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="42" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A42" s="1">
         <v>38</v>
       </c>
@@ -4749,8 +4891,11 @@
       <c r="W42" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X42" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="43" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A43" s="1">
         <v>39</v>
       </c>
@@ -4808,8 +4953,11 @@
       <c r="W43" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X43" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="44" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A44" s="1">
         <v>40</v>
       </c>
@@ -4867,8 +5015,11 @@
       <c r="W44" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X44" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="45" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A45" s="1">
         <v>41</v>
       </c>
@@ -4926,8 +5077,11 @@
       <c r="W45" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X45" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="46" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A46" s="1">
         <v>42</v>
       </c>
@@ -4985,8 +5139,11 @@
       <c r="W46" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X46" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="47" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A47" s="1">
         <v>43</v>
       </c>
@@ -5044,8 +5201,11 @@
       <c r="W47" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X47" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="48" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A48" s="1">
         <v>44</v>
       </c>
@@ -5103,8 +5263,11 @@
       <c r="W48" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X48" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="49" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A49" s="1">
         <v>45</v>
       </c>
@@ -5162,8 +5325,11 @@
       <c r="W49" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X49" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="50" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A50" s="1">
         <v>46</v>
       </c>
@@ -5221,8 +5387,11 @@
       <c r="W50" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X50" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="51" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A51" s="1">
         <v>47</v>
       </c>
@@ -5280,8 +5449,11 @@
       <c r="W51" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X51" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="52" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A52" s="1">
         <v>48</v>
       </c>
@@ -5339,8 +5511,11 @@
       <c r="W52" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X52" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="53" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A53" s="1">
         <v>49</v>
       </c>
@@ -5398,8 +5573,11 @@
       <c r="W53" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X53" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="54" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A54" s="1">
         <v>50</v>
       </c>
@@ -5457,8 +5635,11 @@
       <c r="W54" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X54" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="55" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A55" s="1">
         <v>51</v>
       </c>
@@ -5516,8 +5697,11 @@
       <c r="W55" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="56" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X55" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="56" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A56" s="1">
         <v>52</v>
       </c>
@@ -5575,8 +5759,11 @@
       <c r="W56" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="57" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X56" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="57" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A57" s="1">
         <v>53</v>
       </c>
@@ -5634,8 +5821,11 @@
       <c r="W57" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X57" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="58" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A58" s="1">
         <v>54</v>
       </c>
@@ -5693,8 +5883,11 @@
       <c r="W58" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X58" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="59" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A59" s="1">
         <v>55</v>
       </c>
@@ -5752,8 +5945,11 @@
       <c r="W59" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X59" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="60" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A60" s="1">
         <v>56</v>
       </c>
@@ -5811,8 +6007,11 @@
       <c r="W60" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X60" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="61" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A61" s="1">
         <v>57</v>
       </c>
@@ -5870,8 +6069,11 @@
       <c r="W61" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X61" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="62" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A62" s="1">
         <v>58</v>
       </c>
@@ -5929,8 +6131,11 @@
       <c r="W62" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X62" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="63" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A63" s="1">
         <v>59</v>
       </c>
@@ -5988,8 +6193,11 @@
       <c r="W63" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X63" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="64" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A64" s="1">
         <v>60</v>
       </c>
@@ -6047,8 +6255,11 @@
       <c r="W64" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X64" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="65" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A65" s="1">
         <v>61</v>
       </c>
@@ -6106,8 +6317,11 @@
       <c r="W65" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X65" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="66" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A66" s="1">
         <v>62</v>
       </c>
@@ -6165,8 +6379,11 @@
       <c r="W66" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X66" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="67" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A67" s="1">
         <v>63</v>
       </c>
@@ -6224,8 +6441,11 @@
       <c r="W67" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="68" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X67" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="68" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A68" s="1">
         <v>64</v>
       </c>
@@ -6283,8 +6503,11 @@
       <c r="W68" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X68" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="69" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A69" s="1">
         <v>65</v>
       </c>
@@ -6342,8 +6565,11 @@
       <c r="W69" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X69" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="70" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A70" s="1">
         <v>66</v>
       </c>
@@ -6401,8 +6627,11 @@
       <c r="W70" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X70" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="71" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A71" s="1">
         <v>67</v>
       </c>
@@ -6460,8 +6689,11 @@
       <c r="W71" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X71" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="72" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A72" s="1">
         <v>68</v>
       </c>
@@ -6519,8 +6751,11 @@
       <c r="W72" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X72" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="73" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A73" s="1">
         <v>69</v>
       </c>
@@ -6578,8 +6813,11 @@
       <c r="W73" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X73" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="74" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A74" s="1">
         <v>70</v>
       </c>
@@ -6637,8 +6875,11 @@
       <c r="W74" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X74" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="75" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A75" s="1">
         <v>71</v>
       </c>
@@ -6696,8 +6937,11 @@
       <c r="W75" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X75" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="76" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A76" s="1">
         <v>72</v>
       </c>
@@ -6755,8 +6999,11 @@
       <c r="W76" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X76" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="77" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A77" s="1">
         <v>73</v>
       </c>
@@ -6814,8 +7061,11 @@
       <c r="W77" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="78" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X77" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="78" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A78" s="1">
         <v>74</v>
       </c>
@@ -6873,8 +7123,11 @@
       <c r="W78" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X78" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="79" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A79" s="1">
         <v>75</v>
       </c>
@@ -6932,8 +7185,11 @@
       <c r="W79" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="80" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X79" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="80" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A80" s="1">
         <v>76</v>
       </c>
@@ -6991,8 +7247,11 @@
       <c r="W80" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="81" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X80" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="81" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A81" s="1">
         <v>77</v>
       </c>
@@ -7050,8 +7309,11 @@
       <c r="W81" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X81" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="82" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A82" s="1">
         <v>78</v>
       </c>
@@ -7109,8 +7371,11 @@
       <c r="W82" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="83" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X82" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="83" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A83" s="1">
         <v>79</v>
       </c>
@@ -7168,8 +7433,11 @@
       <c r="W83" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X83" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="84" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A84" s="1">
         <v>80</v>
       </c>
@@ -7227,8 +7495,11 @@
       <c r="W84" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X84" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="85" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A85" s="1">
         <v>81</v>
       </c>
@@ -7286,8 +7557,11 @@
       <c r="W85" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X85" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="86" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A86" s="1">
         <v>82</v>
       </c>
@@ -7345,8 +7619,11 @@
       <c r="W86" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X86" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="87" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A87" s="1">
         <v>83</v>
       </c>
@@ -7404,8 +7681,11 @@
       <c r="W87" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X87" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="88" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A88" s="1">
         <v>84</v>
       </c>
@@ -7463,8 +7743,11 @@
       <c r="W88" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X88" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="89" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A89" s="1">
         <v>85</v>
       </c>
@@ -7522,8 +7805,11 @@
       <c r="W89" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X89" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="90" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A90" s="1">
         <v>86</v>
       </c>
@@ -7581,8 +7867,11 @@
       <c r="W90" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="91" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X90" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="91" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A91" s="1">
         <v>87</v>
       </c>
@@ -7640,8 +7929,11 @@
       <c r="W91" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X91" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="92" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A92" s="1">
         <v>88</v>
       </c>
@@ -7699,8 +7991,11 @@
       <c r="W92" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X92" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="93" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A93" s="1">
         <v>89</v>
       </c>
@@ -7758,8 +8053,11 @@
       <c r="W93" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X93" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="94" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A94" s="1">
         <v>90</v>
       </c>
@@ -7817,8 +8115,11 @@
       <c r="W94" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X94" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="95" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A95" s="1">
         <v>91</v>
       </c>
@@ -7876,8 +8177,11 @@
       <c r="W95" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="96" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X95" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="96" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A96" s="1">
         <v>92</v>
       </c>
@@ -7935,8 +8239,11 @@
       <c r="W96" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X96" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="97" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A97" s="1">
         <v>93</v>
       </c>
@@ -7994,8 +8301,11 @@
       <c r="W97" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X97" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="98" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A98" s="1">
         <v>94</v>
       </c>
@@ -8053,8 +8363,11 @@
       <c r="W98" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X98" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="99" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A99" s="1">
         <v>95</v>
       </c>
@@ -8112,8 +8425,11 @@
       <c r="W99" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X99" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="100" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A100" s="1">
         <v>96</v>
       </c>
@@ -8171,8 +8487,11 @@
       <c r="W100" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X100" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="101" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A101" s="1">
         <v>97</v>
       </c>
@@ -8230,8 +8549,11 @@
       <c r="W101" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X101" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="102" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A102" s="1">
         <v>98</v>
       </c>
@@ -8289,8 +8611,11 @@
       <c r="W102" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="103" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X102" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="103" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A103" s="1">
         <v>99</v>
       </c>
@@ -8348,8 +8673,11 @@
       <c r="W103" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="104" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X103" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="104" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A104" s="1">
         <v>100</v>
       </c>
@@ -8407,8 +8735,11 @@
       <c r="W104" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="105" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X104" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="105" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A105" s="1">
         <v>101</v>
       </c>
@@ -8466,8 +8797,11 @@
       <c r="W105" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="106" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X105" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="106" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A106" s="1">
         <v>102</v>
       </c>
@@ -8525,8 +8859,11 @@
       <c r="W106" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="107" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X106" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="107" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A107" s="1">
         <v>103</v>
       </c>
@@ -8584,8 +8921,11 @@
       <c r="W107" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="108" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X107" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="108" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A108" s="1">
         <v>104</v>
       </c>
@@ -8643,8 +8983,11 @@
       <c r="W108" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="109" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X108" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="109" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A109" s="1">
         <v>105</v>
       </c>
@@ -8702,8 +9045,11 @@
       <c r="W109" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="110" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X109" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="110" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A110" s="1">
         <v>106</v>
       </c>
@@ -8761,8 +9107,11 @@
       <c r="W110" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="111" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X110" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="111" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A111" s="1">
         <v>107</v>
       </c>
@@ -8820,8 +9169,11 @@
       <c r="W111" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="112" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X111" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="112" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A112" s="1">
         <v>108</v>
       </c>
@@ -8879,8 +9231,11 @@
       <c r="W112" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="113" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X112" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="113" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A113" s="1">
         <v>109</v>
       </c>
@@ -8938,8 +9293,11 @@
       <c r="W113" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="114" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X113" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="114" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A114" s="1">
         <v>110</v>
       </c>
@@ -8997,8 +9355,11 @@
       <c r="W114" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="115" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X114" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="115" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A115" s="1">
         <v>111</v>
       </c>
@@ -9056,8 +9417,11 @@
       <c r="W115" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="116" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X115" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="116" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A116" s="1">
         <v>112</v>
       </c>
@@ -9115,8 +9479,11 @@
       <c r="W116" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="117" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X116" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="117" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A117" s="1">
         <v>113</v>
       </c>
@@ -9174,8 +9541,11 @@
       <c r="W117" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="118" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X117" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="118" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A118" s="1">
         <v>114</v>
       </c>
@@ -9233,8 +9603,11 @@
       <c r="W118" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="119" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X118" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="119" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A119" s="1">
         <v>115</v>
       </c>
@@ -9292,8 +9665,11 @@
       <c r="W119" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="120" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X119" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="120" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A120" s="1">
         <v>116</v>
       </c>
@@ -9351,8 +9727,11 @@
       <c r="W120" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="121" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X120" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="121" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A121" s="1">
         <v>117</v>
       </c>
@@ -9410,8 +9789,11 @@
       <c r="W121" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="122" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X121" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="122" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A122" s="1">
         <v>118</v>
       </c>
@@ -9469,8 +9851,11 @@
       <c r="W122" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="123" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X122" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="123" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A123" s="1">
         <v>119</v>
       </c>
@@ -9528,8 +9913,11 @@
       <c r="W123" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="124" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X123" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="124" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A124" s="1">
         <v>120</v>
       </c>
@@ -9587,8 +9975,11 @@
       <c r="W124" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="125" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X124" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="125" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A125" s="1">
         <v>121</v>
       </c>
@@ -9646,8 +10037,11 @@
       <c r="W125" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="126" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X125" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="126" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A126" s="1">
         <v>122</v>
       </c>
@@ -9705,8 +10099,11 @@
       <c r="W126" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="127" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X126" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="127" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A127" s="1">
         <v>123</v>
       </c>
@@ -9764,8 +10161,11 @@
       <c r="W127" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="128" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X127" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="128" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A128" s="1">
         <v>124</v>
       </c>
@@ -9823,8 +10223,11 @@
       <c r="W128" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="129" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X128" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="129" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A129" s="1">
         <v>125</v>
       </c>
@@ -9882,8 +10285,11 @@
       <c r="W129" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="130" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X129" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="130" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A130" s="1">
         <v>126</v>
       </c>
@@ -9941,8 +10347,11 @@
       <c r="W130" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="131" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X130" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="131" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A131" s="1">
         <v>127</v>
       </c>
@@ -10000,8 +10409,11 @@
       <c r="W131" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="132" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X131" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="132" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A132" s="1">
         <v>128</v>
       </c>
@@ -10059,8 +10471,11 @@
       <c r="W132" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="133" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X132" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="133" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A133" s="1">
         <v>129</v>
       </c>
@@ -10118,8 +10533,11 @@
       <c r="W133" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="134" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X133" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="134" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A134" s="1">
         <v>130</v>
       </c>
@@ -10177,8 +10595,11 @@
       <c r="W134" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="135" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X134" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="135" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A135" s="1">
         <v>131</v>
       </c>
@@ -10236,8 +10657,11 @@
       <c r="W135" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="136" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X135" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="136" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A136" s="1">
         <v>132</v>
       </c>
@@ -10295,8 +10719,11 @@
       <c r="W136" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="137" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X136" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="137" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A137" s="1">
         <v>133</v>
       </c>
@@ -10354,8 +10781,11 @@
       <c r="W137" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="138" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X137" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="138" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A138" s="1">
         <v>134</v>
       </c>
@@ -10413,8 +10843,11 @@
       <c r="W138" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="139" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X138" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="139" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A139" s="1">
         <v>135</v>
       </c>
@@ -10472,8 +10905,11 @@
       <c r="W139" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="140" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X139" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="140" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A140" s="1">
         <v>136</v>
       </c>
@@ -10531,8 +10967,11 @@
       <c r="W140" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="141" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X140" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="141" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A141" s="1">
         <v>137</v>
       </c>
@@ -10590,8 +11029,11 @@
       <c r="W141" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="142" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X141" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="142" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A142" s="1">
         <v>138</v>
       </c>
@@ -10649,8 +11091,11 @@
       <c r="W142" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="143" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X142" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="143" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A143" s="1">
         <v>139</v>
       </c>
@@ -10708,8 +11153,11 @@
       <c r="W143" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="144" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X143" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="144" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A144" s="1">
         <v>140</v>
       </c>
@@ -10767,8 +11215,11 @@
       <c r="W144" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="145" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X144" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="145" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A145" s="1">
         <v>141</v>
       </c>
@@ -10826,8 +11277,11 @@
       <c r="W145" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="146" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X145" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="146" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A146" s="1">
         <v>142</v>
       </c>
@@ -10885,8 +11339,11 @@
       <c r="W146" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="147" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X146" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="147" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A147" s="1">
         <v>143</v>
       </c>
@@ -10944,8 +11401,11 @@
       <c r="W147" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="148" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X147" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="148" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A148" s="1">
         <v>144</v>
       </c>
@@ -11003,8 +11463,11 @@
       <c r="W148" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="149" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X148" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="149" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A149" s="1">
         <v>145</v>
       </c>
@@ -11062,8 +11525,11 @@
       <c r="W149" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="150" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X149" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="150" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A150" s="1">
         <v>146</v>
       </c>
@@ -11121,8 +11587,11 @@
       <c r="W150" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="151" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X150" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="151" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A151" s="1">
         <v>147</v>
       </c>
@@ -11180,8 +11649,11 @@
       <c r="W151" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="152" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X151" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="152" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A152" s="1">
         <v>148</v>
       </c>
@@ -11239,8 +11711,11 @@
       <c r="W152" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="153" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X152" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="153" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A153" s="1">
         <v>149</v>
       </c>
@@ -11298,8 +11773,11 @@
       <c r="W153" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="154" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X153" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="154" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A154" s="1">
         <v>150</v>
       </c>
@@ -11357,8 +11835,11 @@
       <c r="W154" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="155" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X154" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="155" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A155" s="1">
         <v>151</v>
       </c>
@@ -11416,8 +11897,11 @@
       <c r="W155" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="156" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X155" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="156" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A156" s="1">
         <v>152</v>
       </c>
@@ -11475,8 +11959,11 @@
       <c r="W156" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="157" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X156" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="157" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A157" s="1">
         <v>153</v>
       </c>
@@ -11534,8 +12021,11 @@
       <c r="W157" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="158" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X157" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="158" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A158" s="1">
         <v>154</v>
       </c>
@@ -11593,8 +12083,11 @@
       <c r="W158" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="159" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X158" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="159" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A159" s="1">
         <v>155</v>
       </c>
@@ -11652,8 +12145,11 @@
       <c r="W159" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="160" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X159" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="160" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A160" s="1">
         <v>156</v>
       </c>
@@ -11711,8 +12207,11 @@
       <c r="W160" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="161" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X160" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="161" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A161" s="1">
         <v>157</v>
       </c>
@@ -11770,8 +12269,11 @@
       <c r="W161" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="162" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X161" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="162" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A162" s="1">
         <v>158</v>
       </c>
@@ -11829,8 +12331,11 @@
       <c r="W162" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="163" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X162" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="163" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A163" s="1">
         <v>159</v>
       </c>
@@ -11888,8 +12393,11 @@
       <c r="W163" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="164" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="X163" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="164" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A164" s="1">
         <v>160</v>
       </c>
@@ -11946,6 +12454,9 @@
       </c>
       <c r="W164" s="1">
         <v>0</v>
+      </c>
+      <c r="X164" s="3" t="s">
+        <v>588</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA5FED47-1894-4340-9D88-454DB683F98A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5B545A2-2BBA-4B02-898A-66C73494217D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_barries_v8" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1387" uniqueCount="593">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1390" uniqueCount="598">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -944,12 +944,6 @@
     <t>290001:101_0:101</t>
   </si>
   <si>
-    <t>300001:100_0:100</t>
-  </si>
-  <si>
-    <t>300001:101_0:101</t>
-  </si>
-  <si>
     <t>310001:100_0:100</t>
   </si>
   <si>
@@ -1888,10 +1882,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>300002:100_300003:1000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>MAP&lt;INT:INT&gt;_C</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1901,6 +1891,37 @@
   </si>
   <si>
     <t>区域标准通关值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>300001,300002,300003,300004,300005,300006,300007,300008,300009,300011,300012,300013</t>
+  </si>
+  <si>
+    <t>300001:30_300002:600</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>300001:102_0:102</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>300001:1101_0:100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>310001:0_310002:0_310003:0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>310001:10000_310002:10000_310003:10000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>310001:20000_310002:20000_310003:20000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>310001:35_310002:40_310003:50</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2343,7 +2364,7 @@
         <v>205</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.15">
@@ -2411,13 +2432,13 @@
         <v>245</v>
       </c>
       <c r="V3" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="W3" s="5" t="s">
         <v>576</v>
       </c>
-      <c r="W3" s="5" t="s">
-        <v>578</v>
-      </c>
       <c r="X3" s="1" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.15">
@@ -2485,13 +2506,13 @@
         <v>242</v>
       </c>
       <c r="V4" s="1" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="W4" s="1" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="X4" s="1" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.15">
@@ -2538,10 +2559,10 @@
         <v>150</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="Q5" s="3" t="s">
         <v>231</v>
@@ -2553,19 +2574,19 @@
         <v>247</v>
       </c>
       <c r="T5" s="1" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="U5" s="1" t="s">
         <v>248</v>
       </c>
       <c r="V5" s="1" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="W5" s="1">
         <v>0</v>
       </c>
       <c r="X5" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.15">
@@ -2612,10 +2633,10 @@
         <v>200</v>
       </c>
       <c r="O6" s="4" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="P6" s="4" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="Q6" s="3" t="s">
         <v>231</v>
@@ -2627,7 +2648,7 @@
         <v>0</v>
       </c>
       <c r="X6" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.15">
@@ -2674,10 +2695,10 @@
         <v>300</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="P7" s="4" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="Q7" s="3" t="s">
         <v>231</v>
@@ -2689,7 +2710,7 @@
         <v>0</v>
       </c>
       <c r="X7" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.15">
@@ -2736,10 +2757,10 @@
         <v>400</v>
       </c>
       <c r="O8" s="4" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="P8" s="4" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="Q8" s="3" t="s">
         <v>231</v>
@@ -2751,7 +2772,7 @@
         <v>0</v>
       </c>
       <c r="X8" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.15">
@@ -2798,10 +2819,10 @@
         <v>500</v>
       </c>
       <c r="O9" s="4" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="P9" s="4" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="Q9" s="3" t="s">
         <v>231</v>
@@ -2813,7 +2834,7 @@
         <v>0</v>
       </c>
       <c r="X9" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.15">
@@ -2860,10 +2881,10 @@
         <v>600</v>
       </c>
       <c r="O10" s="4" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="P10" s="4" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="Q10" s="3" t="s">
         <v>231</v>
@@ -2875,7 +2896,7 @@
         <v>0</v>
       </c>
       <c r="X10" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.15">
@@ -2922,10 +2943,10 @@
         <v>100</v>
       </c>
       <c r="O11" s="4" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="P11" s="4" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="Q11" s="3" t="s">
         <v>231</v>
@@ -2937,7 +2958,7 @@
         <v>0</v>
       </c>
       <c r="X11" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.15">
@@ -2984,10 +3005,10 @@
         <v>100</v>
       </c>
       <c r="O12" s="4" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="P12" s="4" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="Q12" s="3" t="s">
         <v>231</v>
@@ -2999,7 +3020,7 @@
         <v>0</v>
       </c>
       <c r="X12" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.15">
@@ -3046,10 +3067,10 @@
         <v>100</v>
       </c>
       <c r="O13" s="4" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="P13" s="4" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Q13" s="3" t="s">
         <v>231</v>
@@ -3061,7 +3082,7 @@
         <v>0</v>
       </c>
       <c r="X13" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="14" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -3108,10 +3129,10 @@
         <v>100</v>
       </c>
       <c r="O14" s="4" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="P14" s="4" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>231</v>
@@ -3123,7 +3144,7 @@
         <v>0</v>
       </c>
       <c r="X14" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.15">
@@ -3170,31 +3191,31 @@
         <v>100</v>
       </c>
       <c r="O15" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="P15" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="Q15" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="R15" s="1">
+        <v>0</v>
+      </c>
+      <c r="S15" s="1" t="s">
         <v>561</v>
       </c>
-      <c r="P15" s="1" t="s">
+      <c r="T15" s="1" t="s">
         <v>562</v>
       </c>
-      <c r="Q15" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="R15" s="1">
-        <v>0</v>
-      </c>
-      <c r="S15" s="1" t="s">
+      <c r="U15" s="1" t="s">
         <v>563</v>
       </c>
-      <c r="T15" s="1" t="s">
-        <v>564</v>
-      </c>
-      <c r="U15" s="1" t="s">
-        <v>565</v>
-      </c>
       <c r="W15" s="1" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="X15" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.15">
@@ -3241,11 +3262,11 @@
         <v>100</v>
       </c>
       <c r="O16" s="4" t="s">
+        <v>564</v>
+      </c>
+      <c r="P16" s="4" t="s">
         <v>566</v>
       </c>
-      <c r="P16" s="4" t="s">
-        <v>568</v>
-      </c>
       <c r="Q16" s="3" t="s">
         <v>231</v>
       </c>
@@ -3253,22 +3274,22 @@
         <v>0</v>
       </c>
       <c r="S16" s="1" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="T16" s="1" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="U16" s="1" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="V16" s="1" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="W16" s="1">
         <v>0</v>
       </c>
       <c r="X16" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="17" spans="1:24" x14ac:dyDescent="0.15">
@@ -3330,7 +3351,7 @@
         <v>0</v>
       </c>
       <c r="X17" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="18" spans="1:24" x14ac:dyDescent="0.15">
@@ -3392,7 +3413,7 @@
         <v>0</v>
       </c>
       <c r="X18" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.15">
@@ -3454,7 +3475,7 @@
         <v>0</v>
       </c>
       <c r="X19" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="20" spans="1:24" x14ac:dyDescent="0.15">
@@ -3516,7 +3537,7 @@
         <v>0</v>
       </c>
       <c r="X20" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.15">
@@ -3578,7 +3599,7 @@
         <v>0</v>
       </c>
       <c r="X21" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.15">
@@ -3640,7 +3661,7 @@
         <v>0</v>
       </c>
       <c r="X22" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="23" spans="1:24" x14ac:dyDescent="0.15">
@@ -3702,7 +3723,7 @@
         <v>0</v>
       </c>
       <c r="X23" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="24" spans="1:24" x14ac:dyDescent="0.15">
@@ -3764,7 +3785,7 @@
         <v>0</v>
       </c>
       <c r="X24" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="25" spans="1:24" x14ac:dyDescent="0.15">
@@ -3811,34 +3832,34 @@
         <v>100</v>
       </c>
       <c r="O25" s="4" t="s">
+        <v>579</v>
+      </c>
+      <c r="P25" s="4" t="s">
+        <v>580</v>
+      </c>
+      <c r="Q25" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="R25" s="1">
+        <v>0</v>
+      </c>
+      <c r="S25" s="1" t="s">
         <v>581</v>
       </c>
-      <c r="P25" s="4" t="s">
+      <c r="T25" s="1" t="s">
         <v>582</v>
       </c>
-      <c r="Q25" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="R25" s="1">
-        <v>0</v>
-      </c>
-      <c r="S25" s="1" t="s">
+      <c r="U25" s="1" t="s">
         <v>583</v>
       </c>
-      <c r="T25" s="1" t="s">
+      <c r="V25" s="1" t="s">
         <v>584</v>
       </c>
-      <c r="U25" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="V25" s="1" t="s">
-        <v>586</v>
-      </c>
       <c r="W25" s="1">
         <v>0</v>
       </c>
       <c r="X25" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="26" spans="1:24" x14ac:dyDescent="0.15">
@@ -3900,7 +3921,7 @@
         <v>0</v>
       </c>
       <c r="X26" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="27" spans="1:24" x14ac:dyDescent="0.15">
@@ -3962,7 +3983,7 @@
         <v>0</v>
       </c>
       <c r="X27" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="28" spans="1:24" x14ac:dyDescent="0.15">
@@ -4024,7 +4045,7 @@
         <v>0</v>
       </c>
       <c r="X28" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="29" spans="1:24" x14ac:dyDescent="0.15">
@@ -4086,7 +4107,7 @@
         <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="30" spans="1:24" x14ac:dyDescent="0.15">
@@ -4148,7 +4169,7 @@
         <v>0</v>
       </c>
       <c r="X30" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="31" spans="1:24" x14ac:dyDescent="0.15">
@@ -4210,7 +4231,7 @@
         <v>0</v>
       </c>
       <c r="X31" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="32" spans="1:24" x14ac:dyDescent="0.15">
@@ -4272,7 +4293,7 @@
         <v>0</v>
       </c>
       <c r="X32" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="33" spans="1:24" x14ac:dyDescent="0.15">
@@ -4334,7 +4355,7 @@
         <v>0</v>
       </c>
       <c r="X33" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="34" spans="1:24" x14ac:dyDescent="0.15">
@@ -4359,8 +4380,8 @@
       <c r="G34" s="1">
         <v>43400002</v>
       </c>
-      <c r="H34" s="1" t="s">
-        <v>202</v>
+      <c r="H34" s="1">
+        <v>0</v>
       </c>
       <c r="I34" s="1">
         <v>1</v>
@@ -4378,25 +4399,37 @@
         <v>215</v>
       </c>
       <c r="N34" s="1">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="O34" s="4" t="s">
-        <v>282</v>
+        <v>593</v>
       </c>
       <c r="P34" s="4" t="s">
-        <v>283</v>
+        <v>592</v>
       </c>
       <c r="Q34" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="R34" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="W34" s="1">
-        <v>0</v>
+      <c r="R34" s="1">
+        <v>0</v>
+      </c>
+      <c r="S34" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="T34" s="1" t="s">
+        <v>595</v>
+      </c>
+      <c r="U34" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="V34" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="W34" s="1" t="s">
+        <v>590</v>
       </c>
       <c r="X34" s="3" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="35" spans="1:24" x14ac:dyDescent="0.15">
@@ -4443,10 +4476,10 @@
         <v>100</v>
       </c>
       <c r="O35" s="4" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="P35" s="4" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="Q35" s="3" t="s">
         <v>231</v>
@@ -4458,7 +4491,7 @@
         <v>0</v>
       </c>
       <c r="X35" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="36" spans="1:24" x14ac:dyDescent="0.15">
@@ -4505,10 +4538,10 @@
         <v>100</v>
       </c>
       <c r="O36" s="4" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="P36" s="4" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="Q36" s="3" t="s">
         <v>231</v>
@@ -4520,7 +4553,7 @@
         <v>0</v>
       </c>
       <c r="X36" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="37" spans="1:24" x14ac:dyDescent="0.15">
@@ -4567,10 +4600,10 @@
         <v>100</v>
       </c>
       <c r="O37" s="4" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="P37" s="4" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="Q37" s="3" t="s">
         <v>231</v>
@@ -4582,7 +4615,7 @@
         <v>0</v>
       </c>
       <c r="X37" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="38" spans="1:24" x14ac:dyDescent="0.15">
@@ -4629,10 +4662,10 @@
         <v>100</v>
       </c>
       <c r="O38" s="4" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="P38" s="4" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="Q38" s="3" t="s">
         <v>231</v>
@@ -4644,7 +4677,7 @@
         <v>0</v>
       </c>
       <c r="X38" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="39" spans="1:24" x14ac:dyDescent="0.15">
@@ -4691,10 +4724,10 @@
         <v>100</v>
       </c>
       <c r="O39" s="4" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="P39" s="4" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="Q39" s="3" t="s">
         <v>231</v>
@@ -4706,7 +4739,7 @@
         <v>0</v>
       </c>
       <c r="X39" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="40" spans="1:24" x14ac:dyDescent="0.15">
@@ -4753,10 +4786,10 @@
         <v>100</v>
       </c>
       <c r="O40" s="4" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="P40" s="4" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="Q40" s="3" t="s">
         <v>231</v>
@@ -4768,7 +4801,7 @@
         <v>0</v>
       </c>
       <c r="X40" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="41" spans="1:24" x14ac:dyDescent="0.15">
@@ -4815,10 +4848,10 @@
         <v>100</v>
       </c>
       <c r="O41" s="4" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="P41" s="4" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="Q41" s="3" t="s">
         <v>231</v>
@@ -4830,7 +4863,7 @@
         <v>0</v>
       </c>
       <c r="X41" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="42" spans="1:24" x14ac:dyDescent="0.15">
@@ -4877,10 +4910,10 @@
         <v>100</v>
       </c>
       <c r="O42" s="4" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="P42" s="4" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="Q42" s="3" t="s">
         <v>231</v>
@@ -4892,7 +4925,7 @@
         <v>0</v>
       </c>
       <c r="X42" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="43" spans="1:24" x14ac:dyDescent="0.15">
@@ -4939,10 +4972,10 @@
         <v>100</v>
       </c>
       <c r="O43" s="4" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="P43" s="4" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="Q43" s="3" t="s">
         <v>231</v>
@@ -4954,7 +4987,7 @@
         <v>0</v>
       </c>
       <c r="X43" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="44" spans="1:24" x14ac:dyDescent="0.15">
@@ -5001,10 +5034,10 @@
         <v>100</v>
       </c>
       <c r="O44" s="4" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="P44" s="4" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="Q44" s="3" t="s">
         <v>231</v>
@@ -5016,7 +5049,7 @@
         <v>0</v>
       </c>
       <c r="X44" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="45" spans="1:24" x14ac:dyDescent="0.15">
@@ -5063,10 +5096,10 @@
         <v>100</v>
       </c>
       <c r="O45" s="4" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="P45" s="4" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="Q45" s="3" t="s">
         <v>231</v>
@@ -5078,7 +5111,7 @@
         <v>0</v>
       </c>
       <c r="X45" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="46" spans="1:24" x14ac:dyDescent="0.15">
@@ -5125,10 +5158,10 @@
         <v>100</v>
       </c>
       <c r="O46" s="4" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="P46" s="4" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="Q46" s="3" t="s">
         <v>231</v>
@@ -5140,7 +5173,7 @@
         <v>0</v>
       </c>
       <c r="X46" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="47" spans="1:24" x14ac:dyDescent="0.15">
@@ -5187,10 +5220,10 @@
         <v>100</v>
       </c>
       <c r="O47" s="4" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="P47" s="4" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="Q47" s="3" t="s">
         <v>231</v>
@@ -5202,7 +5235,7 @@
         <v>0</v>
       </c>
       <c r="X47" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="48" spans="1:24" x14ac:dyDescent="0.15">
@@ -5249,10 +5282,10 @@
         <v>100</v>
       </c>
       <c r="O48" s="4" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="P48" s="4" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="Q48" s="3" t="s">
         <v>231</v>
@@ -5264,7 +5297,7 @@
         <v>0</v>
       </c>
       <c r="X48" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="49" spans="1:24" x14ac:dyDescent="0.15">
@@ -5311,10 +5344,10 @@
         <v>100</v>
       </c>
       <c r="O49" s="4" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="P49" s="4" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="Q49" s="3" t="s">
         <v>231</v>
@@ -5326,7 +5359,7 @@
         <v>0</v>
       </c>
       <c r="X49" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="50" spans="1:24" x14ac:dyDescent="0.15">
@@ -5373,10 +5406,10 @@
         <v>100</v>
       </c>
       <c r="O50" s="4" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="P50" s="4" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="Q50" s="3" t="s">
         <v>231</v>
@@ -5388,7 +5421,7 @@
         <v>0</v>
       </c>
       <c r="X50" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="51" spans="1:24" x14ac:dyDescent="0.15">
@@ -5435,10 +5468,10 @@
         <v>100</v>
       </c>
       <c r="O51" s="4" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="P51" s="4" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="Q51" s="3" t="s">
         <v>231</v>
@@ -5450,7 +5483,7 @@
         <v>0</v>
       </c>
       <c r="X51" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="52" spans="1:24" x14ac:dyDescent="0.15">
@@ -5497,10 +5530,10 @@
         <v>100</v>
       </c>
       <c r="O52" s="4" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="P52" s="4" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="Q52" s="3" t="s">
         <v>231</v>
@@ -5512,7 +5545,7 @@
         <v>0</v>
       </c>
       <c r="X52" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="53" spans="1:24" x14ac:dyDescent="0.15">
@@ -5559,10 +5592,10 @@
         <v>100</v>
       </c>
       <c r="O53" s="4" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="P53" s="4" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="Q53" s="3" t="s">
         <v>231</v>
@@ -5574,7 +5607,7 @@
         <v>0</v>
       </c>
       <c r="X53" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="54" spans="1:24" x14ac:dyDescent="0.15">
@@ -5621,10 +5654,10 @@
         <v>100</v>
       </c>
       <c r="O54" s="4" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="P54" s="4" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="Q54" s="3" t="s">
         <v>231</v>
@@ -5636,7 +5669,7 @@
         <v>0</v>
       </c>
       <c r="X54" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="55" spans="1:24" x14ac:dyDescent="0.15">
@@ -5683,10 +5716,10 @@
         <v>100</v>
       </c>
       <c r="O55" s="4" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="P55" s="4" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="Q55" s="3" t="s">
         <v>231</v>
@@ -5698,7 +5731,7 @@
         <v>0</v>
       </c>
       <c r="X55" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="56" spans="1:24" x14ac:dyDescent="0.15">
@@ -5745,10 +5778,10 @@
         <v>100</v>
       </c>
       <c r="O56" s="4" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="P56" s="4" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="Q56" s="3" t="s">
         <v>231</v>
@@ -5760,7 +5793,7 @@
         <v>0</v>
       </c>
       <c r="X56" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="57" spans="1:24" x14ac:dyDescent="0.15">
@@ -5807,10 +5840,10 @@
         <v>100</v>
       </c>
       <c r="O57" s="4" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="P57" s="4" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="Q57" s="3" t="s">
         <v>231</v>
@@ -5822,7 +5855,7 @@
         <v>0</v>
       </c>
       <c r="X57" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="58" spans="1:24" x14ac:dyDescent="0.15">
@@ -5869,10 +5902,10 @@
         <v>100</v>
       </c>
       <c r="O58" s="4" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="P58" s="4" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="Q58" s="3" t="s">
         <v>231</v>
@@ -5884,7 +5917,7 @@
         <v>0</v>
       </c>
       <c r="X58" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="59" spans="1:24" x14ac:dyDescent="0.15">
@@ -5931,10 +5964,10 @@
         <v>100</v>
       </c>
       <c r="O59" s="4" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="P59" s="4" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="Q59" s="3" t="s">
         <v>231</v>
@@ -5946,7 +5979,7 @@
         <v>0</v>
       </c>
       <c r="X59" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="60" spans="1:24" x14ac:dyDescent="0.15">
@@ -5993,10 +6026,10 @@
         <v>100</v>
       </c>
       <c r="O60" s="4" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="P60" s="4" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="Q60" s="3" t="s">
         <v>231</v>
@@ -6008,7 +6041,7 @@
         <v>0</v>
       </c>
       <c r="X60" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="61" spans="1:24" x14ac:dyDescent="0.15">
@@ -6055,10 +6088,10 @@
         <v>100</v>
       </c>
       <c r="O61" s="4" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="P61" s="4" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="Q61" s="3" t="s">
         <v>231</v>
@@ -6070,7 +6103,7 @@
         <v>0</v>
       </c>
       <c r="X61" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="62" spans="1:24" x14ac:dyDescent="0.15">
@@ -6117,10 +6150,10 @@
         <v>100</v>
       </c>
       <c r="O62" s="4" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="P62" s="4" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="Q62" s="3" t="s">
         <v>231</v>
@@ -6132,7 +6165,7 @@
         <v>0</v>
       </c>
       <c r="X62" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.15">
@@ -6179,10 +6212,10 @@
         <v>100</v>
       </c>
       <c r="O63" s="4" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="P63" s="4" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="Q63" s="3" t="s">
         <v>231</v>
@@ -6194,7 +6227,7 @@
         <v>0</v>
       </c>
       <c r="X63" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.15">
@@ -6241,10 +6274,10 @@
         <v>100</v>
       </c>
       <c r="O64" s="4" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="P64" s="4" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="Q64" s="3" t="s">
         <v>231</v>
@@ -6256,7 +6289,7 @@
         <v>0</v>
       </c>
       <c r="X64" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="65" spans="1:24" x14ac:dyDescent="0.15">
@@ -6303,10 +6336,10 @@
         <v>100</v>
       </c>
       <c r="O65" s="4" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="P65" s="4" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="Q65" s="3" t="s">
         <v>231</v>
@@ -6318,7 +6351,7 @@
         <v>0</v>
       </c>
       <c r="X65" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="66" spans="1:24" x14ac:dyDescent="0.15">
@@ -6365,10 +6398,10 @@
         <v>100</v>
       </c>
       <c r="O66" s="4" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="P66" s="4" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="Q66" s="3" t="s">
         <v>231</v>
@@ -6380,7 +6413,7 @@
         <v>0</v>
       </c>
       <c r="X66" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="67" spans="1:24" x14ac:dyDescent="0.15">
@@ -6427,10 +6460,10 @@
         <v>100</v>
       </c>
       <c r="O67" s="4" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="P67" s="4" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="Q67" s="3" t="s">
         <v>231</v>
@@ -6442,7 +6475,7 @@
         <v>0</v>
       </c>
       <c r="X67" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="68" spans="1:24" x14ac:dyDescent="0.15">
@@ -6489,10 +6522,10 @@
         <v>100</v>
       </c>
       <c r="O68" s="4" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="P68" s="4" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="Q68" s="3" t="s">
         <v>231</v>
@@ -6504,7 +6537,7 @@
         <v>0</v>
       </c>
       <c r="X68" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="69" spans="1:24" x14ac:dyDescent="0.15">
@@ -6551,10 +6584,10 @@
         <v>100</v>
       </c>
       <c r="O69" s="4" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="P69" s="4" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="Q69" s="3" t="s">
         <v>231</v>
@@ -6566,7 +6599,7 @@
         <v>0</v>
       </c>
       <c r="X69" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="70" spans="1:24" x14ac:dyDescent="0.15">
@@ -6613,10 +6646,10 @@
         <v>100</v>
       </c>
       <c r="O70" s="4" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="P70" s="4" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="Q70" s="3" t="s">
         <v>231</v>
@@ -6628,7 +6661,7 @@
         <v>0</v>
       </c>
       <c r="X70" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="71" spans="1:24" x14ac:dyDescent="0.15">
@@ -6675,10 +6708,10 @@
         <v>100</v>
       </c>
       <c r="O71" s="4" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="P71" s="4" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="Q71" s="3" t="s">
         <v>231</v>
@@ -6690,7 +6723,7 @@
         <v>0</v>
       </c>
       <c r="X71" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="72" spans="1:24" x14ac:dyDescent="0.15">
@@ -6737,10 +6770,10 @@
         <v>100</v>
       </c>
       <c r="O72" s="4" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="P72" s="4" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="Q72" s="3" t="s">
         <v>231</v>
@@ -6752,7 +6785,7 @@
         <v>0</v>
       </c>
       <c r="X72" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="73" spans="1:24" x14ac:dyDescent="0.15">
@@ -6799,10 +6832,10 @@
         <v>100</v>
       </c>
       <c r="O73" s="4" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="P73" s="4" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="Q73" s="3" t="s">
         <v>231</v>
@@ -6814,7 +6847,7 @@
         <v>0</v>
       </c>
       <c r="X73" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="74" spans="1:24" x14ac:dyDescent="0.15">
@@ -6861,10 +6894,10 @@
         <v>100</v>
       </c>
       <c r="O74" s="4" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="P74" s="4" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="Q74" s="3" t="s">
         <v>231</v>
@@ -6876,7 +6909,7 @@
         <v>0</v>
       </c>
       <c r="X74" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="75" spans="1:24" x14ac:dyDescent="0.15">
@@ -6923,10 +6956,10 @@
         <v>100</v>
       </c>
       <c r="O75" s="4" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="P75" s="4" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="Q75" s="3" t="s">
         <v>231</v>
@@ -6938,7 +6971,7 @@
         <v>0</v>
       </c>
       <c r="X75" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="76" spans="1:24" x14ac:dyDescent="0.15">
@@ -6985,10 +7018,10 @@
         <v>100</v>
       </c>
       <c r="O76" s="4" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="P76" s="4" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="Q76" s="3" t="s">
         <v>231</v>
@@ -7000,7 +7033,7 @@
         <v>0</v>
       </c>
       <c r="X76" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="77" spans="1:24" x14ac:dyDescent="0.15">
@@ -7047,10 +7080,10 @@
         <v>100</v>
       </c>
       <c r="O77" s="4" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="P77" s="4" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="Q77" s="3" t="s">
         <v>231</v>
@@ -7062,7 +7095,7 @@
         <v>0</v>
       </c>
       <c r="X77" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="78" spans="1:24" x14ac:dyDescent="0.15">
@@ -7109,10 +7142,10 @@
         <v>100</v>
       </c>
       <c r="O78" s="4" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="P78" s="4" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="Q78" s="3" t="s">
         <v>231</v>
@@ -7124,7 +7157,7 @@
         <v>0</v>
       </c>
       <c r="X78" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="79" spans="1:24" x14ac:dyDescent="0.15">
@@ -7171,10 +7204,10 @@
         <v>100</v>
       </c>
       <c r="O79" s="4" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="P79" s="4" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="Q79" s="3" t="s">
         <v>231</v>
@@ -7186,7 +7219,7 @@
         <v>0</v>
       </c>
       <c r="X79" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="80" spans="1:24" x14ac:dyDescent="0.15">
@@ -7233,10 +7266,10 @@
         <v>100</v>
       </c>
       <c r="O80" s="4" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="P80" s="4" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="Q80" s="3" t="s">
         <v>231</v>
@@ -7248,7 +7281,7 @@
         <v>0</v>
       </c>
       <c r="X80" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="81" spans="1:24" x14ac:dyDescent="0.15">
@@ -7295,10 +7328,10 @@
         <v>100</v>
       </c>
       <c r="O81" s="4" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="P81" s="4" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="Q81" s="3" t="s">
         <v>231</v>
@@ -7310,7 +7343,7 @@
         <v>0</v>
       </c>
       <c r="X81" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="82" spans="1:24" x14ac:dyDescent="0.15">
@@ -7357,10 +7390,10 @@
         <v>100</v>
       </c>
       <c r="O82" s="4" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="P82" s="4" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="Q82" s="3" t="s">
         <v>231</v>
@@ -7372,7 +7405,7 @@
         <v>0</v>
       </c>
       <c r="X82" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="83" spans="1:24" x14ac:dyDescent="0.15">
@@ -7419,10 +7452,10 @@
         <v>100</v>
       </c>
       <c r="O83" s="4" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="P83" s="4" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="Q83" s="3" t="s">
         <v>231</v>
@@ -7434,7 +7467,7 @@
         <v>0</v>
       </c>
       <c r="X83" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="84" spans="1:24" x14ac:dyDescent="0.15">
@@ -7481,10 +7514,10 @@
         <v>100</v>
       </c>
       <c r="O84" s="4" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="P84" s="4" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="Q84" s="3" t="s">
         <v>231</v>
@@ -7496,7 +7529,7 @@
         <v>0</v>
       </c>
       <c r="X84" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="85" spans="1:24" x14ac:dyDescent="0.15">
@@ -7543,10 +7576,10 @@
         <v>100</v>
       </c>
       <c r="O85" s="4" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="P85" s="4" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="Q85" s="3" t="s">
         <v>231</v>
@@ -7558,7 +7591,7 @@
         <v>0</v>
       </c>
       <c r="X85" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="86" spans="1:24" x14ac:dyDescent="0.15">
@@ -7605,10 +7638,10 @@
         <v>100</v>
       </c>
       <c r="O86" s="4" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="P86" s="4" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="Q86" s="3" t="s">
         <v>231</v>
@@ -7620,7 +7653,7 @@
         <v>0</v>
       </c>
       <c r="X86" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="87" spans="1:24" x14ac:dyDescent="0.15">
@@ -7667,10 +7700,10 @@
         <v>100</v>
       </c>
       <c r="O87" s="4" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="P87" s="4" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="Q87" s="3" t="s">
         <v>231</v>
@@ -7682,7 +7715,7 @@
         <v>0</v>
       </c>
       <c r="X87" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="88" spans="1:24" x14ac:dyDescent="0.15">
@@ -7729,10 +7762,10 @@
         <v>100</v>
       </c>
       <c r="O88" s="4" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="P88" s="4" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="Q88" s="3" t="s">
         <v>231</v>
@@ -7744,7 +7777,7 @@
         <v>0</v>
       </c>
       <c r="X88" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="89" spans="1:24" x14ac:dyDescent="0.15">
@@ -7791,10 +7824,10 @@
         <v>100</v>
       </c>
       <c r="O89" s="4" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="P89" s="4" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="Q89" s="3" t="s">
         <v>231</v>
@@ -7806,7 +7839,7 @@
         <v>0</v>
       </c>
       <c r="X89" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="90" spans="1:24" x14ac:dyDescent="0.15">
@@ -7853,10 +7886,10 @@
         <v>100</v>
       </c>
       <c r="O90" s="4" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="P90" s="4" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="Q90" s="3" t="s">
         <v>231</v>
@@ -7868,7 +7901,7 @@
         <v>0</v>
       </c>
       <c r="X90" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="91" spans="1:24" x14ac:dyDescent="0.15">
@@ -7915,10 +7948,10 @@
         <v>100</v>
       </c>
       <c r="O91" s="4" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="P91" s="4" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="Q91" s="3" t="s">
         <v>231</v>
@@ -7930,7 +7963,7 @@
         <v>0</v>
       </c>
       <c r="X91" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="92" spans="1:24" x14ac:dyDescent="0.15">
@@ -7977,10 +8010,10 @@
         <v>100</v>
       </c>
       <c r="O92" s="4" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="P92" s="4" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="Q92" s="3" t="s">
         <v>231</v>
@@ -7992,7 +8025,7 @@
         <v>0</v>
       </c>
       <c r="X92" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="93" spans="1:24" x14ac:dyDescent="0.15">
@@ -8039,10 +8072,10 @@
         <v>100</v>
       </c>
       <c r="O93" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="P93" s="4" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="Q93" s="3" t="s">
         <v>231</v>
@@ -8054,7 +8087,7 @@
         <v>0</v>
       </c>
       <c r="X93" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="94" spans="1:24" x14ac:dyDescent="0.15">
@@ -8101,10 +8134,10 @@
         <v>100</v>
       </c>
       <c r="O94" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="P94" s="4" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="Q94" s="3" t="s">
         <v>231</v>
@@ -8116,7 +8149,7 @@
         <v>0</v>
       </c>
       <c r="X94" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="95" spans="1:24" x14ac:dyDescent="0.15">
@@ -8163,10 +8196,10 @@
         <v>100</v>
       </c>
       <c r="O95" s="4" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="P95" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="Q95" s="3" t="s">
         <v>231</v>
@@ -8178,7 +8211,7 @@
         <v>0</v>
       </c>
       <c r="X95" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="96" spans="1:24" x14ac:dyDescent="0.15">
@@ -8225,10 +8258,10 @@
         <v>100</v>
       </c>
       <c r="O96" s="4" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="P96" s="4" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="Q96" s="3" t="s">
         <v>231</v>
@@ -8240,7 +8273,7 @@
         <v>0</v>
       </c>
       <c r="X96" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="97" spans="1:24" x14ac:dyDescent="0.15">
@@ -8287,10 +8320,10 @@
         <v>100</v>
       </c>
       <c r="O97" s="4" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="P97" s="4" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="Q97" s="3" t="s">
         <v>231</v>
@@ -8302,7 +8335,7 @@
         <v>0</v>
       </c>
       <c r="X97" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="98" spans="1:24" x14ac:dyDescent="0.15">
@@ -8349,10 +8382,10 @@
         <v>100</v>
       </c>
       <c r="O98" s="4" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="P98" s="4" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="Q98" s="3" t="s">
         <v>231</v>
@@ -8364,7 +8397,7 @@
         <v>0</v>
       </c>
       <c r="X98" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="99" spans="1:24" x14ac:dyDescent="0.15">
@@ -8411,10 +8444,10 @@
         <v>100</v>
       </c>
       <c r="O99" s="4" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="P99" s="4" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="Q99" s="3" t="s">
         <v>231</v>
@@ -8426,7 +8459,7 @@
         <v>0</v>
       </c>
       <c r="X99" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="100" spans="1:24" x14ac:dyDescent="0.15">
@@ -8473,10 +8506,10 @@
         <v>100</v>
       </c>
       <c r="O100" s="4" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="P100" s="4" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="Q100" s="3" t="s">
         <v>231</v>
@@ -8488,7 +8521,7 @@
         <v>0</v>
       </c>
       <c r="X100" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="101" spans="1:24" x14ac:dyDescent="0.15">
@@ -8535,10 +8568,10 @@
         <v>100</v>
       </c>
       <c r="O101" s="4" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="P101" s="4" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="Q101" s="3" t="s">
         <v>231</v>
@@ -8550,7 +8583,7 @@
         <v>0</v>
       </c>
       <c r="X101" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="102" spans="1:24" x14ac:dyDescent="0.15">
@@ -8597,10 +8630,10 @@
         <v>100</v>
       </c>
       <c r="O102" s="4" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="P102" s="4" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="Q102" s="3" t="s">
         <v>231</v>
@@ -8612,7 +8645,7 @@
         <v>0</v>
       </c>
       <c r="X102" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="103" spans="1:24" x14ac:dyDescent="0.15">
@@ -8659,10 +8692,10 @@
         <v>100</v>
       </c>
       <c r="O103" s="4" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="P103" s="4" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="Q103" s="3" t="s">
         <v>231</v>
@@ -8674,7 +8707,7 @@
         <v>0</v>
       </c>
       <c r="X103" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="104" spans="1:24" x14ac:dyDescent="0.15">
@@ -8721,10 +8754,10 @@
         <v>100</v>
       </c>
       <c r="O104" s="4" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="P104" s="4" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="Q104" s="3" t="s">
         <v>231</v>
@@ -8736,7 +8769,7 @@
         <v>0</v>
       </c>
       <c r="X104" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="105" spans="1:24" x14ac:dyDescent="0.15">
@@ -8783,10 +8816,10 @@
         <v>100</v>
       </c>
       <c r="O105" s="4" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="P105" s="4" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="Q105" s="3" t="s">
         <v>231</v>
@@ -8798,7 +8831,7 @@
         <v>0</v>
       </c>
       <c r="X105" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="106" spans="1:24" x14ac:dyDescent="0.15">
@@ -8845,10 +8878,10 @@
         <v>100</v>
       </c>
       <c r="O106" s="4" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="P106" s="4" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="Q106" s="3" t="s">
         <v>231</v>
@@ -8860,7 +8893,7 @@
         <v>0</v>
       </c>
       <c r="X106" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="107" spans="1:24" x14ac:dyDescent="0.15">
@@ -8907,10 +8940,10 @@
         <v>100</v>
       </c>
       <c r="O107" s="4" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="P107" s="4" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="Q107" s="3" t="s">
         <v>231</v>
@@ -8922,7 +8955,7 @@
         <v>0</v>
       </c>
       <c r="X107" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="108" spans="1:24" x14ac:dyDescent="0.15">
@@ -8969,10 +9002,10 @@
         <v>100</v>
       </c>
       <c r="O108" s="4" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="P108" s="4" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="Q108" s="3" t="s">
         <v>231</v>
@@ -8984,7 +9017,7 @@
         <v>0</v>
       </c>
       <c r="X108" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="109" spans="1:24" x14ac:dyDescent="0.15">
@@ -9031,10 +9064,10 @@
         <v>100</v>
       </c>
       <c r="O109" s="4" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="P109" s="4" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="Q109" s="3" t="s">
         <v>231</v>
@@ -9046,7 +9079,7 @@
         <v>0</v>
       </c>
       <c r="X109" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="110" spans="1:24" x14ac:dyDescent="0.15">
@@ -9093,10 +9126,10 @@
         <v>100</v>
       </c>
       <c r="O110" s="4" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="P110" s="4" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="Q110" s="3" t="s">
         <v>231</v>
@@ -9108,7 +9141,7 @@
         <v>0</v>
       </c>
       <c r="X110" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="111" spans="1:24" x14ac:dyDescent="0.15">
@@ -9155,10 +9188,10 @@
         <v>100</v>
       </c>
       <c r="O111" s="4" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="P111" s="4" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="Q111" s="3" t="s">
         <v>231</v>
@@ -9170,7 +9203,7 @@
         <v>0</v>
       </c>
       <c r="X111" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="112" spans="1:24" x14ac:dyDescent="0.15">
@@ -9217,10 +9250,10 @@
         <v>100</v>
       </c>
       <c r="O112" s="4" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="P112" s="4" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="Q112" s="3" t="s">
         <v>231</v>
@@ -9232,7 +9265,7 @@
         <v>0</v>
       </c>
       <c r="X112" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="113" spans="1:24" x14ac:dyDescent="0.15">
@@ -9279,10 +9312,10 @@
         <v>100</v>
       </c>
       <c r="O113" s="4" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="P113" s="4" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="Q113" s="3" t="s">
         <v>231</v>
@@ -9294,7 +9327,7 @@
         <v>0</v>
       </c>
       <c r="X113" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="114" spans="1:24" x14ac:dyDescent="0.15">
@@ -9341,10 +9374,10 @@
         <v>100</v>
       </c>
       <c r="O114" s="4" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="P114" s="4" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="Q114" s="3" t="s">
         <v>231</v>
@@ -9356,7 +9389,7 @@
         <v>0</v>
       </c>
       <c r="X114" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="115" spans="1:24" x14ac:dyDescent="0.15">
@@ -9403,10 +9436,10 @@
         <v>100</v>
       </c>
       <c r="O115" s="4" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="P115" s="4" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="Q115" s="3" t="s">
         <v>231</v>
@@ -9418,7 +9451,7 @@
         <v>0</v>
       </c>
       <c r="X115" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="116" spans="1:24" x14ac:dyDescent="0.15">
@@ -9465,10 +9498,10 @@
         <v>100</v>
       </c>
       <c r="O116" s="4" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="P116" s="4" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="Q116" s="3" t="s">
         <v>231</v>
@@ -9480,7 +9513,7 @@
         <v>0</v>
       </c>
       <c r="X116" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="117" spans="1:24" x14ac:dyDescent="0.15">
@@ -9527,10 +9560,10 @@
         <v>100</v>
       </c>
       <c r="O117" s="4" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="P117" s="4" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="Q117" s="3" t="s">
         <v>231</v>
@@ -9542,7 +9575,7 @@
         <v>0</v>
       </c>
       <c r="X117" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="118" spans="1:24" x14ac:dyDescent="0.15">
@@ -9589,10 +9622,10 @@
         <v>100</v>
       </c>
       <c r="O118" s="4" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="P118" s="4" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="Q118" s="3" t="s">
         <v>231</v>
@@ -9604,7 +9637,7 @@
         <v>0</v>
       </c>
       <c r="X118" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="119" spans="1:24" x14ac:dyDescent="0.15">
@@ -9651,10 +9684,10 @@
         <v>100</v>
       </c>
       <c r="O119" s="4" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="P119" s="4" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="Q119" s="3" t="s">
         <v>231</v>
@@ -9666,7 +9699,7 @@
         <v>0</v>
       </c>
       <c r="X119" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="120" spans="1:24" x14ac:dyDescent="0.15">
@@ -9713,10 +9746,10 @@
         <v>100</v>
       </c>
       <c r="O120" s="4" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="P120" s="4" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="Q120" s="3" t="s">
         <v>231</v>
@@ -9728,7 +9761,7 @@
         <v>0</v>
       </c>
       <c r="X120" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="121" spans="1:24" x14ac:dyDescent="0.15">
@@ -9775,10 +9808,10 @@
         <v>100</v>
       </c>
       <c r="O121" s="4" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="P121" s="4" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="Q121" s="3" t="s">
         <v>231</v>
@@ -9790,7 +9823,7 @@
         <v>0</v>
       </c>
       <c r="X121" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="122" spans="1:24" x14ac:dyDescent="0.15">
@@ -9837,10 +9870,10 @@
         <v>100</v>
       </c>
       <c r="O122" s="4" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="P122" s="4" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="Q122" s="3" t="s">
         <v>231</v>
@@ -9852,7 +9885,7 @@
         <v>0</v>
       </c>
       <c r="X122" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="123" spans="1:24" x14ac:dyDescent="0.15">
@@ -9899,10 +9932,10 @@
         <v>100</v>
       </c>
       <c r="O123" s="4" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="P123" s="4" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q123" s="3" t="s">
         <v>231</v>
@@ -9914,7 +9947,7 @@
         <v>0</v>
       </c>
       <c r="X123" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="124" spans="1:24" x14ac:dyDescent="0.15">
@@ -9961,10 +9994,10 @@
         <v>100</v>
       </c>
       <c r="O124" s="4" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="P124" s="4" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="Q124" s="3" t="s">
         <v>231</v>
@@ -9976,7 +10009,7 @@
         <v>0</v>
       </c>
       <c r="X124" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="125" spans="1:24" x14ac:dyDescent="0.15">
@@ -10023,10 +10056,10 @@
         <v>100</v>
       </c>
       <c r="O125" s="4" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="P125" s="4" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="Q125" s="3" t="s">
         <v>231</v>
@@ -10038,7 +10071,7 @@
         <v>0</v>
       </c>
       <c r="X125" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="126" spans="1:24" x14ac:dyDescent="0.15">
@@ -10085,10 +10118,10 @@
         <v>100</v>
       </c>
       <c r="O126" s="4" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="P126" s="4" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="Q126" s="3" t="s">
         <v>231</v>
@@ -10100,7 +10133,7 @@
         <v>0</v>
       </c>
       <c r="X126" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="127" spans="1:24" x14ac:dyDescent="0.15">
@@ -10147,10 +10180,10 @@
         <v>100</v>
       </c>
       <c r="O127" s="4" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="P127" s="4" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="Q127" s="3" t="s">
         <v>231</v>
@@ -10162,7 +10195,7 @@
         <v>0</v>
       </c>
       <c r="X127" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="128" spans="1:24" x14ac:dyDescent="0.15">
@@ -10209,10 +10242,10 @@
         <v>100</v>
       </c>
       <c r="O128" s="4" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="P128" s="4" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="Q128" s="3" t="s">
         <v>231</v>
@@ -10224,7 +10257,7 @@
         <v>0</v>
       </c>
       <c r="X128" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="129" spans="1:24" x14ac:dyDescent="0.15">
@@ -10271,10 +10304,10 @@
         <v>100</v>
       </c>
       <c r="O129" s="4" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="P129" s="4" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="Q129" s="3" t="s">
         <v>231</v>
@@ -10286,7 +10319,7 @@
         <v>0</v>
       </c>
       <c r="X129" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="130" spans="1:24" x14ac:dyDescent="0.15">
@@ -10333,10 +10366,10 @@
         <v>100</v>
       </c>
       <c r="O130" s="4" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="P130" s="4" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="Q130" s="3" t="s">
         <v>231</v>
@@ -10348,7 +10381,7 @@
         <v>0</v>
       </c>
       <c r="X130" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="131" spans="1:24" x14ac:dyDescent="0.15">
@@ -10395,10 +10428,10 @@
         <v>100</v>
       </c>
       <c r="O131" s="4" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="P131" s="4" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="Q131" s="3" t="s">
         <v>231</v>
@@ -10410,7 +10443,7 @@
         <v>0</v>
       </c>
       <c r="X131" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="132" spans="1:24" x14ac:dyDescent="0.15">
@@ -10457,10 +10490,10 @@
         <v>100</v>
       </c>
       <c r="O132" s="4" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="P132" s="4" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="Q132" s="3" t="s">
         <v>231</v>
@@ -10472,7 +10505,7 @@
         <v>0</v>
       </c>
       <c r="X132" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="133" spans="1:24" x14ac:dyDescent="0.15">
@@ -10519,10 +10552,10 @@
         <v>100</v>
       </c>
       <c r="O133" s="4" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="P133" s="4" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="Q133" s="3" t="s">
         <v>231</v>
@@ -10534,7 +10567,7 @@
         <v>0</v>
       </c>
       <c r="X133" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="134" spans="1:24" x14ac:dyDescent="0.15">
@@ -10581,10 +10614,10 @@
         <v>100</v>
       </c>
       <c r="O134" s="4" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="P134" s="4" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="Q134" s="3" t="s">
         <v>231</v>
@@ -10596,7 +10629,7 @@
         <v>0</v>
       </c>
       <c r="X134" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="135" spans="1:24" x14ac:dyDescent="0.15">
@@ -10643,10 +10676,10 @@
         <v>100</v>
       </c>
       <c r="O135" s="4" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="P135" s="4" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="Q135" s="3" t="s">
         <v>231</v>
@@ -10658,7 +10691,7 @@
         <v>0</v>
       </c>
       <c r="X135" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="136" spans="1:24" x14ac:dyDescent="0.15">
@@ -10705,10 +10738,10 @@
         <v>100</v>
       </c>
       <c r="O136" s="4" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="P136" s="4" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="Q136" s="3" t="s">
         <v>231</v>
@@ -10720,7 +10753,7 @@
         <v>0</v>
       </c>
       <c r="X136" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="137" spans="1:24" x14ac:dyDescent="0.15">
@@ -10767,10 +10800,10 @@
         <v>100</v>
       </c>
       <c r="O137" s="4" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="P137" s="4" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="Q137" s="3" t="s">
         <v>231</v>
@@ -10782,7 +10815,7 @@
         <v>0</v>
       </c>
       <c r="X137" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="138" spans="1:24" x14ac:dyDescent="0.15">
@@ -10829,10 +10862,10 @@
         <v>100</v>
       </c>
       <c r="O138" s="4" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="P138" s="4" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="Q138" s="3" t="s">
         <v>231</v>
@@ -10844,7 +10877,7 @@
         <v>0</v>
       </c>
       <c r="X138" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="139" spans="1:24" x14ac:dyDescent="0.15">
@@ -10891,10 +10924,10 @@
         <v>100</v>
       </c>
       <c r="O139" s="4" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="P139" s="4" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="Q139" s="3" t="s">
         <v>231</v>
@@ -10906,7 +10939,7 @@
         <v>0</v>
       </c>
       <c r="X139" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="140" spans="1:24" x14ac:dyDescent="0.15">
@@ -10953,10 +10986,10 @@
         <v>100</v>
       </c>
       <c r="O140" s="4" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="P140" s="4" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="Q140" s="3" t="s">
         <v>231</v>
@@ -10968,7 +11001,7 @@
         <v>0</v>
       </c>
       <c r="X140" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="141" spans="1:24" x14ac:dyDescent="0.15">
@@ -11015,10 +11048,10 @@
         <v>100</v>
       </c>
       <c r="O141" s="4" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="P141" s="4" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="Q141" s="3" t="s">
         <v>231</v>
@@ -11030,7 +11063,7 @@
         <v>0</v>
       </c>
       <c r="X141" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="142" spans="1:24" x14ac:dyDescent="0.15">
@@ -11077,10 +11110,10 @@
         <v>100</v>
       </c>
       <c r="O142" s="4" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="P142" s="4" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="Q142" s="3" t="s">
         <v>231</v>
@@ -11092,7 +11125,7 @@
         <v>0</v>
       </c>
       <c r="X142" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="143" spans="1:24" x14ac:dyDescent="0.15">
@@ -11139,10 +11172,10 @@
         <v>100</v>
       </c>
       <c r="O143" s="4" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="P143" s="4" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="Q143" s="3" t="s">
         <v>231</v>
@@ -11154,7 +11187,7 @@
         <v>0</v>
       </c>
       <c r="X143" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="144" spans="1:24" x14ac:dyDescent="0.15">
@@ -11201,10 +11234,10 @@
         <v>100</v>
       </c>
       <c r="O144" s="4" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="P144" s="4" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="Q144" s="3" t="s">
         <v>231</v>
@@ -11216,7 +11249,7 @@
         <v>0</v>
       </c>
       <c r="X144" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="145" spans="1:24" x14ac:dyDescent="0.15">
@@ -11263,10 +11296,10 @@
         <v>100</v>
       </c>
       <c r="O145" s="4" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="P145" s="4" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="Q145" s="3" t="s">
         <v>231</v>
@@ -11278,7 +11311,7 @@
         <v>0</v>
       </c>
       <c r="X145" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="146" spans="1:24" x14ac:dyDescent="0.15">
@@ -11325,10 +11358,10 @@
         <v>100</v>
       </c>
       <c r="O146" s="4" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="P146" s="4" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="Q146" s="3" t="s">
         <v>231</v>
@@ -11340,7 +11373,7 @@
         <v>0</v>
       </c>
       <c r="X146" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="147" spans="1:24" x14ac:dyDescent="0.15">
@@ -11387,10 +11420,10 @@
         <v>100</v>
       </c>
       <c r="O147" s="4" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="P147" s="4" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="Q147" s="3" t="s">
         <v>231</v>
@@ -11402,7 +11435,7 @@
         <v>0</v>
       </c>
       <c r="X147" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="148" spans="1:24" x14ac:dyDescent="0.15">
@@ -11449,10 +11482,10 @@
         <v>100</v>
       </c>
       <c r="O148" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="P148" s="4" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="Q148" s="3" t="s">
         <v>231</v>
@@ -11464,7 +11497,7 @@
         <v>0</v>
       </c>
       <c r="X148" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="149" spans="1:24" x14ac:dyDescent="0.15">
@@ -11511,10 +11544,10 @@
         <v>100</v>
       </c>
       <c r="O149" s="4" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="P149" s="4" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="Q149" s="3" t="s">
         <v>231</v>
@@ -11526,7 +11559,7 @@
         <v>0</v>
       </c>
       <c r="X149" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="150" spans="1:24" x14ac:dyDescent="0.15">
@@ -11573,10 +11606,10 @@
         <v>100</v>
       </c>
       <c r="O150" s="4" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="P150" s="4" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="Q150" s="3" t="s">
         <v>231</v>
@@ -11588,7 +11621,7 @@
         <v>0</v>
       </c>
       <c r="X150" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="151" spans="1:24" x14ac:dyDescent="0.15">
@@ -11635,10 +11668,10 @@
         <v>100</v>
       </c>
       <c r="O151" s="4" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="P151" s="4" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="Q151" s="3" t="s">
         <v>231</v>
@@ -11650,7 +11683,7 @@
         <v>0</v>
       </c>
       <c r="X151" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="152" spans="1:24" x14ac:dyDescent="0.15">
@@ -11697,10 +11730,10 @@
         <v>100</v>
       </c>
       <c r="O152" s="4" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="P152" s="4" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="Q152" s="3" t="s">
         <v>231</v>
@@ -11712,7 +11745,7 @@
         <v>0</v>
       </c>
       <c r="X152" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="153" spans="1:24" x14ac:dyDescent="0.15">
@@ -11759,10 +11792,10 @@
         <v>100</v>
       </c>
       <c r="O153" s="4" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="P153" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="Q153" s="3" t="s">
         <v>231</v>
@@ -11774,7 +11807,7 @@
         <v>0</v>
       </c>
       <c r="X153" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="154" spans="1:24" x14ac:dyDescent="0.15">
@@ -11821,10 +11854,10 @@
         <v>100</v>
       </c>
       <c r="O154" s="4" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="P154" s="4" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="Q154" s="3" t="s">
         <v>231</v>
@@ -11836,7 +11869,7 @@
         <v>0</v>
       </c>
       <c r="X154" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="155" spans="1:24" x14ac:dyDescent="0.15">
@@ -11883,10 +11916,10 @@
         <v>100</v>
       </c>
       <c r="O155" s="4" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="P155" s="4" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="Q155" s="3" t="s">
         <v>231</v>
@@ -11898,7 +11931,7 @@
         <v>0</v>
       </c>
       <c r="X155" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="156" spans="1:24" x14ac:dyDescent="0.15">
@@ -11945,10 +11978,10 @@
         <v>100</v>
       </c>
       <c r="O156" s="4" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="P156" s="4" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="Q156" s="3" t="s">
         <v>231</v>
@@ -11960,7 +11993,7 @@
         <v>0</v>
       </c>
       <c r="X156" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="157" spans="1:24" x14ac:dyDescent="0.15">
@@ -12007,10 +12040,10 @@
         <v>100</v>
       </c>
       <c r="O157" s="4" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="P157" s="4" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="Q157" s="3" t="s">
         <v>231</v>
@@ -12022,7 +12055,7 @@
         <v>0</v>
       </c>
       <c r="X157" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="158" spans="1:24" x14ac:dyDescent="0.15">
@@ -12069,10 +12102,10 @@
         <v>100</v>
       </c>
       <c r="O158" s="4" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="P158" s="4" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="Q158" s="3" t="s">
         <v>231</v>
@@ -12084,7 +12117,7 @@
         <v>0</v>
       </c>
       <c r="X158" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="159" spans="1:24" x14ac:dyDescent="0.15">
@@ -12131,10 +12164,10 @@
         <v>100</v>
       </c>
       <c r="O159" s="4" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="P159" s="4" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="Q159" s="3" t="s">
         <v>231</v>
@@ -12146,7 +12179,7 @@
         <v>0</v>
       </c>
       <c r="X159" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="160" spans="1:24" x14ac:dyDescent="0.15">
@@ -12193,10 +12226,10 @@
         <v>100</v>
       </c>
       <c r="O160" s="4" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="P160" s="4" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="Q160" s="3" t="s">
         <v>231</v>
@@ -12208,7 +12241,7 @@
         <v>0</v>
       </c>
       <c r="X160" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="161" spans="1:24" x14ac:dyDescent="0.15">
@@ -12255,10 +12288,10 @@
         <v>100</v>
       </c>
       <c r="O161" s="4" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="P161" s="4" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="Q161" s="3" t="s">
         <v>231</v>
@@ -12270,7 +12303,7 @@
         <v>0</v>
       </c>
       <c r="X161" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="162" spans="1:24" x14ac:dyDescent="0.15">
@@ -12317,10 +12350,10 @@
         <v>100</v>
       </c>
       <c r="O162" s="4" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="P162" s="4" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="Q162" s="3" t="s">
         <v>231</v>
@@ -12332,7 +12365,7 @@
         <v>0</v>
       </c>
       <c r="X162" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="163" spans="1:24" x14ac:dyDescent="0.15">
@@ -12379,10 +12412,10 @@
         <v>100</v>
       </c>
       <c r="O163" s="4" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="P163" s="4" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="Q163" s="3" t="s">
         <v>231</v>
@@ -12394,7 +12427,7 @@
         <v>0</v>
       </c>
       <c r="X163" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="164" spans="1:24" x14ac:dyDescent="0.15">
@@ -12441,10 +12474,10 @@
         <v>100</v>
       </c>
       <c r="O164" s="4" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="P164" s="4" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="Q164" s="3" t="s">
         <v>231</v>
@@ -12456,7 +12489,7 @@
         <v>0</v>
       </c>
       <c r="X164" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5B545A2-2BBA-4B02-898A-66C73494217D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{253F3A9B-42AD-41A8-BC52-74C961028380}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1390" uniqueCount="598">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1553" uniqueCount="601">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1922,6 +1922,18 @@
   </si>
   <si>
     <t>310001:35_310002:40_310003:50</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>300001:8000_300002:8000_300003:8000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>刷怪范围半径</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>brush_monsters_range</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2262,7 +2274,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:X164"/>
+  <dimension ref="A1:Y164"/>
   <sheetFormatPr defaultColWidth="7.125" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.5" style="1" bestFit="1" customWidth="1"/>
@@ -2284,16 +2296,16 @@
     <col min="19" max="21" width="30.75" style="1" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="19.375" style="1" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="18.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="7.125" style="1"/>
+    <col min="24" max="25" width="18.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="7.125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -2366,8 +2378,11 @@
       <c r="X2" s="1" t="s">
         <v>587</v>
       </c>
-    </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y2" s="1" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -2440,8 +2455,11 @@
       <c r="X3" s="1" t="s">
         <v>588</v>
       </c>
-    </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y3" s="1" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -2514,8 +2532,11 @@
       <c r="X4" s="1" t="s">
         <v>589</v>
       </c>
-    </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y4" s="1" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -2588,8 +2609,11 @@
       <c r="X5" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y5" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A6" s="1">
         <v>2</v>
       </c>
@@ -2650,8 +2674,11 @@
       <c r="X6" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y6" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A7" s="1">
         <v>3</v>
       </c>
@@ -2712,8 +2739,11 @@
       <c r="X7" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y7" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A8" s="1">
         <v>4</v>
       </c>
@@ -2774,8 +2804,11 @@
       <c r="X8" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y8" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A9" s="1">
         <v>5</v>
       </c>
@@ -2836,8 +2869,11 @@
       <c r="X9" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y9" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A10" s="1">
         <v>6</v>
       </c>
@@ -2898,8 +2934,11 @@
       <c r="X10" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y10" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A11" s="1">
         <v>7</v>
       </c>
@@ -2960,8 +2999,11 @@
       <c r="X11" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y11" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A12" s="1">
         <v>8</v>
       </c>
@@ -3022,8 +3064,11 @@
       <c r="X12" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y12" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A13" s="1">
         <v>9</v>
       </c>
@@ -3084,8 +3129,11 @@
       <c r="X13" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Y13" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="1">
         <v>10</v>
       </c>
@@ -3146,8 +3194,11 @@
       <c r="X14" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y14" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A15" s="1">
         <v>11</v>
       </c>
@@ -3217,8 +3268,11 @@
       <c r="X15" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y15" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A16" s="1">
         <v>12</v>
       </c>
@@ -3291,8 +3345,11 @@
       <c r="X16" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y16" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A17" s="1">
         <v>13</v>
       </c>
@@ -3353,8 +3410,11 @@
       <c r="X17" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y17" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A18" s="1">
         <v>14</v>
       </c>
@@ -3415,8 +3475,11 @@
       <c r="X18" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y18" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A19" s="1">
         <v>15</v>
       </c>
@@ -3477,8 +3540,11 @@
       <c r="X19" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y19" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A20" s="1">
         <v>16</v>
       </c>
@@ -3539,8 +3605,11 @@
       <c r="X20" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y20" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A21" s="1">
         <v>17</v>
       </c>
@@ -3601,8 +3670,11 @@
       <c r="X21" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y21" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A22" s="1">
         <v>18</v>
       </c>
@@ -3663,8 +3735,11 @@
       <c r="X22" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y22" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A23" s="1">
         <v>19</v>
       </c>
@@ -3725,8 +3800,11 @@
       <c r="X23" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y23" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A24" s="1">
         <v>20</v>
       </c>
@@ -3787,8 +3865,11 @@
       <c r="X24" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y24" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A25" s="1">
         <v>21</v>
       </c>
@@ -3861,8 +3942,11 @@
       <c r="X25" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y25" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A26" s="1">
         <v>22</v>
       </c>
@@ -3923,8 +4007,11 @@
       <c r="X26" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y26" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="27" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A27" s="1">
         <v>23</v>
       </c>
@@ -3985,8 +4072,11 @@
       <c r="X27" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y27" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="28" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A28" s="1">
         <v>24</v>
       </c>
@@ -4047,8 +4137,11 @@
       <c r="X28" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y28" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A29" s="1">
         <v>25</v>
       </c>
@@ -4109,8 +4202,11 @@
       <c r="X29" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y29" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="30" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A30" s="1">
         <v>26</v>
       </c>
@@ -4171,8 +4267,11 @@
       <c r="X30" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y30" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="31" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A31" s="1">
         <v>27</v>
       </c>
@@ -4233,8 +4332,11 @@
       <c r="X31" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y31" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="32" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A32" s="1">
         <v>28</v>
       </c>
@@ -4295,8 +4397,11 @@
       <c r="X32" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y32" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="33" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A33" s="1">
         <v>29</v>
       </c>
@@ -4357,8 +4462,11 @@
       <c r="X33" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="34" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y33" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="34" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A34" s="1">
         <v>30</v>
       </c>
@@ -4431,8 +4539,11 @@
       <c r="X34" s="3" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="35" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y34" s="3" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="35" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A35" s="1">
         <v>31</v>
       </c>
@@ -4493,8 +4604,11 @@
       <c r="X35" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="36" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y35" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="36" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A36" s="1">
         <v>32</v>
       </c>
@@ -4555,8 +4669,11 @@
       <c r="X36" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="37" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y36" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="37" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A37" s="1">
         <v>33</v>
       </c>
@@ -4617,8 +4734,11 @@
       <c r="X37" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="38" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y37" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="38" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A38" s="1">
         <v>34</v>
       </c>
@@ -4679,8 +4799,11 @@
       <c r="X38" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="39" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y38" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="39" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A39" s="1">
         <v>35</v>
       </c>
@@ -4741,8 +4864,11 @@
       <c r="X39" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="40" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y39" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="40" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A40" s="1">
         <v>36</v>
       </c>
@@ -4803,8 +4929,11 @@
       <c r="X40" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="41" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y40" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="41" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A41" s="1">
         <v>37</v>
       </c>
@@ -4865,8 +4994,11 @@
       <c r="X41" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="42" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y41" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="42" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A42" s="1">
         <v>38</v>
       </c>
@@ -4927,8 +5059,11 @@
       <c r="X42" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="43" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y42" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="43" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A43" s="1">
         <v>39</v>
       </c>
@@ -4989,8 +5124,11 @@
       <c r="X43" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="44" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y43" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="44" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A44" s="1">
         <v>40</v>
       </c>
@@ -5051,8 +5189,11 @@
       <c r="X44" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="45" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y44" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="45" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A45" s="1">
         <v>41</v>
       </c>
@@ -5113,8 +5254,11 @@
       <c r="X45" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="46" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y45" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="46" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A46" s="1">
         <v>42</v>
       </c>
@@ -5175,8 +5319,11 @@
       <c r="X46" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="47" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y46" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="47" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A47" s="1">
         <v>43</v>
       </c>
@@ -5237,8 +5384,11 @@
       <c r="X47" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="48" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y47" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="48" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A48" s="1">
         <v>44</v>
       </c>
@@ -5299,8 +5449,11 @@
       <c r="X48" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="49" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y48" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="49" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A49" s="1">
         <v>45</v>
       </c>
@@ -5361,8 +5514,11 @@
       <c r="X49" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="50" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y49" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="50" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A50" s="1">
         <v>46</v>
       </c>
@@ -5423,8 +5579,11 @@
       <c r="X50" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="51" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y50" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="51" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A51" s="1">
         <v>47</v>
       </c>
@@ -5485,8 +5644,11 @@
       <c r="X51" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="52" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y51" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="52" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A52" s="1">
         <v>48</v>
       </c>
@@ -5547,8 +5709,11 @@
       <c r="X52" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="53" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y52" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="53" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A53" s="1">
         <v>49</v>
       </c>
@@ -5609,8 +5774,11 @@
       <c r="X53" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="54" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y53" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="54" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A54" s="1">
         <v>50</v>
       </c>
@@ -5671,8 +5839,11 @@
       <c r="X54" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="55" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y54" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="55" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A55" s="1">
         <v>51</v>
       </c>
@@ -5733,8 +5904,11 @@
       <c r="X55" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="56" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y55" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="56" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A56" s="1">
         <v>52</v>
       </c>
@@ -5795,8 +5969,11 @@
       <c r="X56" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="57" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y56" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="57" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A57" s="1">
         <v>53</v>
       </c>
@@ -5857,8 +6034,11 @@
       <c r="X57" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="58" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y57" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="58" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A58" s="1">
         <v>54</v>
       </c>
@@ -5919,8 +6099,11 @@
       <c r="X58" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="59" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y58" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="59" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A59" s="1">
         <v>55</v>
       </c>
@@ -5981,8 +6164,11 @@
       <c r="X59" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="60" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y59" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="60" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A60" s="1">
         <v>56</v>
       </c>
@@ -6043,8 +6229,11 @@
       <c r="X60" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="61" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y60" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="61" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A61" s="1">
         <v>57</v>
       </c>
@@ -6105,8 +6294,11 @@
       <c r="X61" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="62" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y61" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="62" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A62" s="1">
         <v>58</v>
       </c>
@@ -6167,8 +6359,11 @@
       <c r="X62" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="63" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y62" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="63" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A63" s="1">
         <v>59</v>
       </c>
@@ -6229,8 +6424,11 @@
       <c r="X63" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="64" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y63" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="64" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A64" s="1">
         <v>60</v>
       </c>
@@ -6291,8 +6489,11 @@
       <c r="X64" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="65" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y64" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="65" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A65" s="1">
         <v>61</v>
       </c>
@@ -6353,8 +6554,11 @@
       <c r="X65" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="66" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y65" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="66" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A66" s="1">
         <v>62</v>
       </c>
@@ -6415,8 +6619,11 @@
       <c r="X66" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="67" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y66" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="67" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A67" s="1">
         <v>63</v>
       </c>
@@ -6477,8 +6684,11 @@
       <c r="X67" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="68" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y67" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="68" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A68" s="1">
         <v>64</v>
       </c>
@@ -6539,8 +6749,11 @@
       <c r="X68" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="69" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y68" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="69" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A69" s="1">
         <v>65</v>
       </c>
@@ -6601,8 +6814,11 @@
       <c r="X69" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="70" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y69" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="70" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A70" s="1">
         <v>66</v>
       </c>
@@ -6663,8 +6879,11 @@
       <c r="X70" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="71" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y70" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="71" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A71" s="1">
         <v>67</v>
       </c>
@@ -6725,8 +6944,11 @@
       <c r="X71" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="72" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y71" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="72" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A72" s="1">
         <v>68</v>
       </c>
@@ -6787,8 +7009,11 @@
       <c r="X72" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="73" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y72" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="73" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A73" s="1">
         <v>69</v>
       </c>
@@ -6849,8 +7074,11 @@
       <c r="X73" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="74" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y73" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="74" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A74" s="1">
         <v>70</v>
       </c>
@@ -6911,8 +7139,11 @@
       <c r="X74" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="75" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y74" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="75" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A75" s="1">
         <v>71</v>
       </c>
@@ -6973,8 +7204,11 @@
       <c r="X75" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="76" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y75" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="76" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A76" s="1">
         <v>72</v>
       </c>
@@ -7035,8 +7269,11 @@
       <c r="X76" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="77" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y76" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="77" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A77" s="1">
         <v>73</v>
       </c>
@@ -7097,8 +7334,11 @@
       <c r="X77" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="78" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y77" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="78" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A78" s="1">
         <v>74</v>
       </c>
@@ -7159,8 +7399,11 @@
       <c r="X78" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="79" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y78" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="79" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A79" s="1">
         <v>75</v>
       </c>
@@ -7221,8 +7464,11 @@
       <c r="X79" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="80" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y79" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="80" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A80" s="1">
         <v>76</v>
       </c>
@@ -7283,8 +7529,11 @@
       <c r="X80" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="81" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y80" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="81" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A81" s="1">
         <v>77</v>
       </c>
@@ -7345,8 +7594,11 @@
       <c r="X81" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="82" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y81" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="82" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A82" s="1">
         <v>78</v>
       </c>
@@ -7407,8 +7659,11 @@
       <c r="X82" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="83" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y82" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="83" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A83" s="1">
         <v>79</v>
       </c>
@@ -7469,8 +7724,11 @@
       <c r="X83" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="84" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y83" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="84" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A84" s="1">
         <v>80</v>
       </c>
@@ -7531,8 +7789,11 @@
       <c r="X84" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="85" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y84" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="85" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A85" s="1">
         <v>81</v>
       </c>
@@ -7593,8 +7854,11 @@
       <c r="X85" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="86" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y85" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="86" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A86" s="1">
         <v>82</v>
       </c>
@@ -7655,8 +7919,11 @@
       <c r="X86" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="87" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y86" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="87" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A87" s="1">
         <v>83</v>
       </c>
@@ -7717,8 +7984,11 @@
       <c r="X87" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="88" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y87" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="88" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A88" s="1">
         <v>84</v>
       </c>
@@ -7779,8 +8049,11 @@
       <c r="X88" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="89" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y88" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="89" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A89" s="1">
         <v>85</v>
       </c>
@@ -7841,8 +8114,11 @@
       <c r="X89" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="90" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y89" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="90" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A90" s="1">
         <v>86</v>
       </c>
@@ -7903,8 +8179,11 @@
       <c r="X90" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="91" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y90" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="91" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A91" s="1">
         <v>87</v>
       </c>
@@ -7965,8 +8244,11 @@
       <c r="X91" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="92" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y91" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="92" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A92" s="1">
         <v>88</v>
       </c>
@@ -8027,8 +8309,11 @@
       <c r="X92" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="93" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y92" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="93" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A93" s="1">
         <v>89</v>
       </c>
@@ -8089,8 +8374,11 @@
       <c r="X93" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="94" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y93" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="94" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A94" s="1">
         <v>90</v>
       </c>
@@ -8151,8 +8439,11 @@
       <c r="X94" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="95" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y94" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="95" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A95" s="1">
         <v>91</v>
       </c>
@@ -8213,8 +8504,11 @@
       <c r="X95" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="96" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y95" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="96" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A96" s="1">
         <v>92</v>
       </c>
@@ -8275,8 +8569,11 @@
       <c r="X96" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="97" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y96" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="97" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A97" s="1">
         <v>93</v>
       </c>
@@ -8337,8 +8634,11 @@
       <c r="X97" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="98" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y97" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="98" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A98" s="1">
         <v>94</v>
       </c>
@@ -8399,8 +8699,11 @@
       <c r="X98" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="99" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y98" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="99" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A99" s="1">
         <v>95</v>
       </c>
@@ -8461,8 +8764,11 @@
       <c r="X99" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="100" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y99" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="100" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A100" s="1">
         <v>96</v>
       </c>
@@ -8523,8 +8829,11 @@
       <c r="X100" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="101" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y100" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="101" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A101" s="1">
         <v>97</v>
       </c>
@@ -8585,8 +8894,11 @@
       <c r="X101" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="102" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y101" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="102" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A102" s="1">
         <v>98</v>
       </c>
@@ -8647,8 +8959,11 @@
       <c r="X102" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="103" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y102" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="103" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A103" s="1">
         <v>99</v>
       </c>
@@ -8709,8 +9024,11 @@
       <c r="X103" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="104" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y103" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="104" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A104" s="1">
         <v>100</v>
       </c>
@@ -8771,8 +9089,11 @@
       <c r="X104" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="105" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y104" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="105" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A105" s="1">
         <v>101</v>
       </c>
@@ -8833,8 +9154,11 @@
       <c r="X105" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="106" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y105" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="106" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A106" s="1">
         <v>102</v>
       </c>
@@ -8895,8 +9219,11 @@
       <c r="X106" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="107" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y106" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="107" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A107" s="1">
         <v>103</v>
       </c>
@@ -8957,8 +9284,11 @@
       <c r="X107" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="108" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y107" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="108" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A108" s="1">
         <v>104</v>
       </c>
@@ -9019,8 +9349,11 @@
       <c r="X108" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="109" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y108" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="109" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A109" s="1">
         <v>105</v>
       </c>
@@ -9081,8 +9414,11 @@
       <c r="X109" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="110" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y109" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="110" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A110" s="1">
         <v>106</v>
       </c>
@@ -9143,8 +9479,11 @@
       <c r="X110" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="111" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y110" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="111" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A111" s="1">
         <v>107</v>
       </c>
@@ -9205,8 +9544,11 @@
       <c r="X111" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="112" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y111" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="112" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A112" s="1">
         <v>108</v>
       </c>
@@ -9267,8 +9609,11 @@
       <c r="X112" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="113" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y112" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="113" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A113" s="1">
         <v>109</v>
       </c>
@@ -9329,8 +9674,11 @@
       <c r="X113" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="114" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y113" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="114" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A114" s="1">
         <v>110</v>
       </c>
@@ -9391,8 +9739,11 @@
       <c r="X114" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="115" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y114" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="115" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A115" s="1">
         <v>111</v>
       </c>
@@ -9453,8 +9804,11 @@
       <c r="X115" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="116" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y115" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="116" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A116" s="1">
         <v>112</v>
       </c>
@@ -9515,8 +9869,11 @@
       <c r="X116" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="117" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y116" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="117" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A117" s="1">
         <v>113</v>
       </c>
@@ -9577,8 +9934,11 @@
       <c r="X117" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="118" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y117" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="118" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A118" s="1">
         <v>114</v>
       </c>
@@ -9639,8 +9999,11 @@
       <c r="X118" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="119" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y118" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="119" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A119" s="1">
         <v>115</v>
       </c>
@@ -9701,8 +10064,11 @@
       <c r="X119" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="120" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y119" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="120" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A120" s="1">
         <v>116</v>
       </c>
@@ -9763,8 +10129,11 @@
       <c r="X120" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="121" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y120" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="121" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A121" s="1">
         <v>117</v>
       </c>
@@ -9825,8 +10194,11 @@
       <c r="X121" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="122" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y121" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="122" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A122" s="1">
         <v>118</v>
       </c>
@@ -9887,8 +10259,11 @@
       <c r="X122" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="123" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y122" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="123" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A123" s="1">
         <v>119</v>
       </c>
@@ -9949,8 +10324,11 @@
       <c r="X123" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="124" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y123" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="124" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A124" s="1">
         <v>120</v>
       </c>
@@ -10011,8 +10389,11 @@
       <c r="X124" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="125" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y124" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="125" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A125" s="1">
         <v>121</v>
       </c>
@@ -10073,8 +10454,11 @@
       <c r="X125" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="126" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y125" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="126" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A126" s="1">
         <v>122</v>
       </c>
@@ -10135,8 +10519,11 @@
       <c r="X126" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="127" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y126" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="127" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A127" s="1">
         <v>123</v>
       </c>
@@ -10197,8 +10584,11 @@
       <c r="X127" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="128" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y127" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="128" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A128" s="1">
         <v>124</v>
       </c>
@@ -10259,8 +10649,11 @@
       <c r="X128" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="129" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y128" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="129" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A129" s="1">
         <v>125</v>
       </c>
@@ -10321,8 +10714,11 @@
       <c r="X129" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="130" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y129" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="130" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A130" s="1">
         <v>126</v>
       </c>
@@ -10383,8 +10779,11 @@
       <c r="X130" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="131" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y130" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="131" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A131" s="1">
         <v>127</v>
       </c>
@@ -10445,8 +10844,11 @@
       <c r="X131" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="132" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y131" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="132" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A132" s="1">
         <v>128</v>
       </c>
@@ -10507,8 +10909,11 @@
       <c r="X132" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="133" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y132" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="133" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A133" s="1">
         <v>129</v>
       </c>
@@ -10569,8 +10974,11 @@
       <c r="X133" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="134" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y133" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="134" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A134" s="1">
         <v>130</v>
       </c>
@@ -10631,8 +11039,11 @@
       <c r="X134" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="135" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y134" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="135" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A135" s="1">
         <v>131</v>
       </c>
@@ -10693,8 +11104,11 @@
       <c r="X135" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="136" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y135" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="136" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A136" s="1">
         <v>132</v>
       </c>
@@ -10755,8 +11169,11 @@
       <c r="X136" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="137" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y136" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="137" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A137" s="1">
         <v>133</v>
       </c>
@@ -10817,8 +11234,11 @@
       <c r="X137" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="138" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y137" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="138" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A138" s="1">
         <v>134</v>
       </c>
@@ -10879,8 +11299,11 @@
       <c r="X138" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="139" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y138" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="139" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A139" s="1">
         <v>135</v>
       </c>
@@ -10941,8 +11364,11 @@
       <c r="X139" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="140" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y139" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="140" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A140" s="1">
         <v>136</v>
       </c>
@@ -11003,8 +11429,11 @@
       <c r="X140" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="141" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y140" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="141" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A141" s="1">
         <v>137</v>
       </c>
@@ -11065,8 +11494,11 @@
       <c r="X141" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="142" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y141" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="142" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A142" s="1">
         <v>138</v>
       </c>
@@ -11127,8 +11559,11 @@
       <c r="X142" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="143" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y142" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="143" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A143" s="1">
         <v>139</v>
       </c>
@@ -11189,8 +11624,11 @@
       <c r="X143" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="144" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y143" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="144" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A144" s="1">
         <v>140</v>
       </c>
@@ -11251,8 +11689,11 @@
       <c r="X144" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="145" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y144" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="145" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A145" s="1">
         <v>141</v>
       </c>
@@ -11313,8 +11754,11 @@
       <c r="X145" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="146" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y145" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="146" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A146" s="1">
         <v>142</v>
       </c>
@@ -11375,8 +11819,11 @@
       <c r="X146" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="147" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y146" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="147" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A147" s="1">
         <v>143</v>
       </c>
@@ -11437,8 +11884,11 @@
       <c r="X147" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="148" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y147" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="148" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A148" s="1">
         <v>144</v>
       </c>
@@ -11499,8 +11949,11 @@
       <c r="X148" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="149" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y148" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="149" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A149" s="1">
         <v>145</v>
       </c>
@@ -11561,8 +12014,11 @@
       <c r="X149" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="150" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y149" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="150" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A150" s="1">
         <v>146</v>
       </c>
@@ -11623,8 +12079,11 @@
       <c r="X150" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="151" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y150" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="151" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A151" s="1">
         <v>147</v>
       </c>
@@ -11685,8 +12144,11 @@
       <c r="X151" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="152" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y151" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="152" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A152" s="1">
         <v>148</v>
       </c>
@@ -11747,8 +12209,11 @@
       <c r="X152" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="153" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y152" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="153" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A153" s="1">
         <v>149</v>
       </c>
@@ -11809,8 +12274,11 @@
       <c r="X153" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="154" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y153" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="154" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A154" s="1">
         <v>150</v>
       </c>
@@ -11871,8 +12339,11 @@
       <c r="X154" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="155" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y154" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="155" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A155" s="1">
         <v>151</v>
       </c>
@@ -11933,8 +12404,11 @@
       <c r="X155" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="156" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y155" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="156" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A156" s="1">
         <v>152</v>
       </c>
@@ -11995,8 +12469,11 @@
       <c r="X156" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="157" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y156" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="157" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A157" s="1">
         <v>153</v>
       </c>
@@ -12057,8 +12534,11 @@
       <c r="X157" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="158" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y157" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="158" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A158" s="1">
         <v>154</v>
       </c>
@@ -12119,8 +12599,11 @@
       <c r="X158" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="159" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y158" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="159" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A159" s="1">
         <v>155</v>
       </c>
@@ -12181,8 +12664,11 @@
       <c r="X159" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="160" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y159" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="160" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A160" s="1">
         <v>156</v>
       </c>
@@ -12243,8 +12729,11 @@
       <c r="X160" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="161" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y160" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="161" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A161" s="1">
         <v>157</v>
       </c>
@@ -12305,8 +12794,11 @@
       <c r="X161" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="162" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y161" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="162" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A162" s="1">
         <v>158</v>
       </c>
@@ -12367,8 +12859,11 @@
       <c r="X162" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="163" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y162" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="163" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A163" s="1">
         <v>159</v>
       </c>
@@ -12429,8 +12924,11 @@
       <c r="X163" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="164" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="Y163" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="164" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A164" s="1">
         <v>160</v>
       </c>
@@ -12489,6 +12987,9 @@
         <v>0</v>
       </c>
       <c r="X164" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="Y164" s="3" t="s">
         <v>586</v>
       </c>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{253F3A9B-42AD-41A8-BC52-74C961028380}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F22CFB71-C57C-4A8C-83CB-7A097C60FE06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1905,10 +1905,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>300001:1101_0:100</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>310001:0_310002:0_310003:0</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1934,6 +1930,10 @@
   </si>
   <si>
     <t>brush_monsters_range</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>300001:1102_0:100</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2456,7 +2456,7 @@
         <v>588</v>
       </c>
       <c r="Y3" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.15">
@@ -2533,7 +2533,7 @@
         <v>589</v>
       </c>
       <c r="Y4" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.15">
@@ -4510,7 +4510,7 @@
         <v>1</v>
       </c>
       <c r="O34" s="4" t="s">
-        <v>593</v>
+        <v>600</v>
       </c>
       <c r="P34" s="4" t="s">
         <v>592</v>
@@ -4522,16 +4522,16 @@
         <v>0</v>
       </c>
       <c r="S34" s="1" t="s">
+        <v>593</v>
+      </c>
+      <c r="T34" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="T34" s="1" t="s">
+      <c r="U34" s="1" t="s">
         <v>595</v>
       </c>
-      <c r="U34" s="1" t="s">
+      <c r="V34" s="1" t="s">
         <v>596</v>
-      </c>
-      <c r="V34" s="1" t="s">
-        <v>597</v>
       </c>
       <c r="W34" s="1" t="s">
         <v>590</v>
@@ -4540,7 +4540,7 @@
         <v>591</v>
       </c>
       <c r="Y34" s="3" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="35" spans="1:25" x14ac:dyDescent="0.15">

--- a/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F22CFB71-C57C-4A8C-83CB-7A097C60FE06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E13CE62E-4D7A-4CEF-B205-F4B512CCEB16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1553" uniqueCount="601">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1553" uniqueCount="602">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1934,6 +1934,10 @@
   </si>
   <si>
     <t>300001:1102_0:100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>120001:8000</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3345,8 +3349,8 @@
       <c r="X16" s="3" t="s">
         <v>586</v>
       </c>
-      <c r="Y16" s="3" t="s">
-        <v>586</v>
+      <c r="Y16" s="1" t="s">
+        <v>601</v>
       </c>
     </row>
     <row r="17" spans="1:25" x14ac:dyDescent="0.15">

--- a/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E13CE62E-4D7A-4CEF-B205-F4B512CCEB16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7FC18E9-6184-449C-ADCA-A8197318AEAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1901,10 +1901,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>300001:102_0:102</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>310001:0_310002:0_310003:0</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1933,11 +1929,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>300001:1102_0:100</t>
+    <t>120001:8000</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>120001:8000</t>
+    <t>300001:102_300002:102_300003:102_0:102</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>300001:1102_300002:1102_300003:1102_0:100</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2460,7 +2460,7 @@
         <v>588</v>
       </c>
       <c r="Y3" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.15">
@@ -2537,7 +2537,7 @@
         <v>589</v>
       </c>
       <c r="Y4" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.15">
@@ -3350,7 +3350,7 @@
         <v>586</v>
       </c>
       <c r="Y16" s="1" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="17" spans="1:25" x14ac:dyDescent="0.15">
@@ -4514,10 +4514,10 @@
         <v>1</v>
       </c>
       <c r="O34" s="4" t="s">
+        <v>601</v>
+      </c>
+      <c r="P34" s="4" t="s">
         <v>600</v>
-      </c>
-      <c r="P34" s="4" t="s">
-        <v>592</v>
       </c>
       <c r="Q34" s="3" t="s">
         <v>231</v>
@@ -4526,16 +4526,16 @@
         <v>0</v>
       </c>
       <c r="S34" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="T34" s="1" t="s">
         <v>593</v>
       </c>
-      <c r="T34" s="1" t="s">
+      <c r="U34" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="U34" s="1" t="s">
+      <c r="V34" s="1" t="s">
         <v>595</v>
-      </c>
-      <c r="V34" s="1" t="s">
-        <v>596</v>
       </c>
       <c r="W34" s="1" t="s">
         <v>590</v>
@@ -4544,7 +4544,7 @@
         <v>591</v>
       </c>
       <c r="Y34" s="3" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="35" spans="1:25" x14ac:dyDescent="0.15">

--- a/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7FC18E9-6184-449C-ADCA-A8197318AEAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D00765AC-C268-4BEA-8A5A-1FF161A1D9E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1901,22 +1901,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>310001:0_310002:0_310003:0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>310001:10000_310002:10000_310003:10000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>310001:20000_310002:20000_310003:20000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>310001:35_310002:40_310003:50</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>300001:8000_300002:8000_300003:8000</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1938,6 +1922,22 @@
   </si>
   <si>
     <t>300001:1102_300002:1102_300003:1102_0:100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>300001:0_300002:0_300003:0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>300001:10000_300002:10000_300003:10000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>300001:20000_300002:20000_300003:20000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>300001:35_300002:40_300003:50</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2460,7 +2460,7 @@
         <v>588</v>
       </c>
       <c r="Y3" s="1" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.15">
@@ -2537,7 +2537,7 @@
         <v>589</v>
       </c>
       <c r="Y4" s="1" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.15">
@@ -3350,7 +3350,7 @@
         <v>586</v>
       </c>
       <c r="Y16" s="1" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
     </row>
     <row r="17" spans="1:25" x14ac:dyDescent="0.15">
@@ -4514,10 +4514,10 @@
         <v>1</v>
       </c>
       <c r="O34" s="4" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="P34" s="4" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="Q34" s="3" t="s">
         <v>231</v>
@@ -4526,16 +4526,16 @@
         <v>0</v>
       </c>
       <c r="S34" s="1" t="s">
-        <v>592</v>
+        <v>598</v>
       </c>
       <c r="T34" s="1" t="s">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="U34" s="1" t="s">
-        <v>594</v>
+        <v>600</v>
       </c>
       <c r="V34" s="1" t="s">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="W34" s="1" t="s">
         <v>590</v>
@@ -4544,7 +4544,7 @@
         <v>591</v>
       </c>
       <c r="Y34" s="3" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
     </row>
     <row r="35" spans="1:25" x14ac:dyDescent="0.15">

--- a/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D00765AC-C268-4BEA-8A5A-1FF161A1D9E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7A7D7D7-E3E2-417A-B93A-858DC42883AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1901,10 +1901,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>300001:8000_300002:8000_300003:8000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>刷怪范围半径</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1938,6 +1934,10 @@
   </si>
   <si>
     <t>300001:35_300002:40_300003:50</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>300001:12000_300002:12000_300003:12000</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2460,7 +2460,7 @@
         <v>588</v>
       </c>
       <c r="Y3" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.15">
@@ -2537,7 +2537,7 @@
         <v>589</v>
       </c>
       <c r="Y4" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.15">
@@ -3350,7 +3350,7 @@
         <v>586</v>
       </c>
       <c r="Y16" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="17" spans="1:25" x14ac:dyDescent="0.15">
@@ -4514,10 +4514,10 @@
         <v>1</v>
       </c>
       <c r="O34" s="4" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="P34" s="4" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="Q34" s="3" t="s">
         <v>231</v>
@@ -4526,16 +4526,16 @@
         <v>0</v>
       </c>
       <c r="S34" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="T34" s="1" t="s">
         <v>598</v>
       </c>
-      <c r="T34" s="1" t="s">
+      <c r="U34" s="1" t="s">
         <v>599</v>
       </c>
-      <c r="U34" s="1" t="s">
+      <c r="V34" s="1" t="s">
         <v>600</v>
-      </c>
-      <c r="V34" s="1" t="s">
-        <v>601</v>
       </c>
       <c r="W34" s="1" t="s">
         <v>590</v>
@@ -4544,7 +4544,7 @@
         <v>591</v>
       </c>
       <c r="Y34" s="3" t="s">
-        <v>592</v>
+        <v>601</v>
       </c>
     </row>
     <row r="35" spans="1:25" x14ac:dyDescent="0.15">

--- a/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7A7D7D7-E3E2-417A-B93A-858DC42883AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DF15445-2D77-44A1-9990-F1D896158CD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1553" uniqueCount="602">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1556" uniqueCount="608">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -944,12 +944,6 @@
     <t>290001:101_0:101</t>
   </si>
   <si>
-    <t>310001:100_0:100</t>
-  </si>
-  <si>
-    <t>310001:101_0:101</t>
-  </si>
-  <si>
     <t>320001:100_0:100</t>
   </si>
   <si>
@@ -1939,6 +1933,36 @@
   <si>
     <t>300001:12000_300002:12000_300003:12000</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>310001:1102_0:100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>310001:102_0:101</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>310001:12000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>310001:30_310002:600</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>310001:35_310002:40_310003:50</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>310001:0_310002:0_310003:0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>310001:10000_310002:10000_310003:10000</t>
+  </si>
+  <si>
+    <t>310001:20000_310002:20000_310003:20000</t>
   </si>
 </sst>
 </file>
@@ -2380,10 +2404,10 @@
         <v>205</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.15">
@@ -2451,16 +2475,16 @@
         <v>245</v>
       </c>
       <c r="V3" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="W3" s="5" t="s">
         <v>574</v>
       </c>
-      <c r="W3" s="5" t="s">
-        <v>576</v>
-      </c>
       <c r="X3" s="1" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="Y3" s="1" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.15">
@@ -2528,16 +2552,16 @@
         <v>242</v>
       </c>
       <c r="V4" s="1" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="W4" s="1" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="X4" s="1" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="Y4" s="1" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.15">
@@ -2584,10 +2608,10 @@
         <v>150</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="Q5" s="3" t="s">
         <v>231</v>
@@ -2599,22 +2623,22 @@
         <v>247</v>
       </c>
       <c r="T5" s="1" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="U5" s="1" t="s">
         <v>248</v>
       </c>
       <c r="V5" s="1" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="W5" s="1">
         <v>0</v>
       </c>
       <c r="X5" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y5" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.15">
@@ -2661,10 +2685,10 @@
         <v>200</v>
       </c>
       <c r="O6" s="4" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="P6" s="4" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="Q6" s="3" t="s">
         <v>231</v>
@@ -2676,10 +2700,10 @@
         <v>0</v>
       </c>
       <c r="X6" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y6" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.15">
@@ -2726,10 +2750,10 @@
         <v>300</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="P7" s="4" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="Q7" s="3" t="s">
         <v>231</v>
@@ -2741,10 +2765,10 @@
         <v>0</v>
       </c>
       <c r="X7" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y7" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.15">
@@ -2791,10 +2815,10 @@
         <v>400</v>
       </c>
       <c r="O8" s="4" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="P8" s="4" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="Q8" s="3" t="s">
         <v>231</v>
@@ -2806,10 +2830,10 @@
         <v>0</v>
       </c>
       <c r="X8" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y8" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.15">
@@ -2856,10 +2880,10 @@
         <v>500</v>
       </c>
       <c r="O9" s="4" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="P9" s="4" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="Q9" s="3" t="s">
         <v>231</v>
@@ -2871,10 +2895,10 @@
         <v>0</v>
       </c>
       <c r="X9" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y9" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.15">
@@ -2921,10 +2945,10 @@
         <v>600</v>
       </c>
       <c r="O10" s="4" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="P10" s="4" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="Q10" s="3" t="s">
         <v>231</v>
@@ -2936,10 +2960,10 @@
         <v>0</v>
       </c>
       <c r="X10" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y10" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.15">
@@ -2986,10 +3010,10 @@
         <v>100</v>
       </c>
       <c r="O11" s="4" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="P11" s="4" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="Q11" s="3" t="s">
         <v>231</v>
@@ -3001,10 +3025,10 @@
         <v>0</v>
       </c>
       <c r="X11" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y11" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.15">
@@ -3051,10 +3075,10 @@
         <v>100</v>
       </c>
       <c r="O12" s="4" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="P12" s="4" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="Q12" s="3" t="s">
         <v>231</v>
@@ -3066,10 +3090,10 @@
         <v>0</v>
       </c>
       <c r="X12" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y12" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.15">
@@ -3116,10 +3140,10 @@
         <v>100</v>
       </c>
       <c r="O13" s="4" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="P13" s="4" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="Q13" s="3" t="s">
         <v>231</v>
@@ -3131,10 +3155,10 @@
         <v>0</v>
       </c>
       <c r="X13" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y13" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="14" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -3181,10 +3205,10 @@
         <v>100</v>
       </c>
       <c r="O14" s="4" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="P14" s="4" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>231</v>
@@ -3196,10 +3220,10 @@
         <v>0</v>
       </c>
       <c r="X14" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y14" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.15">
@@ -3246,10 +3270,10 @@
         <v>100</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="Q15" s="3" t="s">
         <v>231</v>
@@ -3258,22 +3282,22 @@
         <v>0</v>
       </c>
       <c r="S15" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="T15" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="U15" s="1" t="s">
         <v>561</v>
       </c>
-      <c r="T15" s="1" t="s">
-        <v>562</v>
-      </c>
-      <c r="U15" s="1" t="s">
-        <v>563</v>
-      </c>
       <c r="W15" s="1" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="X15" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y15" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.15">
@@ -3320,10 +3344,10 @@
         <v>100</v>
       </c>
       <c r="O16" s="4" t="s">
+        <v>562</v>
+      </c>
+      <c r="P16" s="4" t="s">
         <v>564</v>
-      </c>
-      <c r="P16" s="4" t="s">
-        <v>566</v>
       </c>
       <c r="Q16" s="3" t="s">
         <v>231</v>
@@ -3332,25 +3356,25 @@
         <v>0</v>
       </c>
       <c r="S16" s="1" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="T16" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="U16" s="1" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="V16" s="1" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="W16" s="1">
         <v>0</v>
       </c>
       <c r="X16" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y16" s="1" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
     </row>
     <row r="17" spans="1:25" x14ac:dyDescent="0.15">
@@ -3412,10 +3436,10 @@
         <v>0</v>
       </c>
       <c r="X17" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y17" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="18" spans="1:25" x14ac:dyDescent="0.15">
@@ -3477,10 +3501,10 @@
         <v>0</v>
       </c>
       <c r="X18" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y18" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="19" spans="1:25" x14ac:dyDescent="0.15">
@@ -3542,10 +3566,10 @@
         <v>0</v>
       </c>
       <c r="X19" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y19" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="20" spans="1:25" x14ac:dyDescent="0.15">
@@ -3607,10 +3631,10 @@
         <v>0</v>
       </c>
       <c r="X20" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y20" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="21" spans="1:25" x14ac:dyDescent="0.15">
@@ -3672,10 +3696,10 @@
         <v>0</v>
       </c>
       <c r="X21" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y21" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="22" spans="1:25" x14ac:dyDescent="0.15">
@@ -3737,10 +3761,10 @@
         <v>0</v>
       </c>
       <c r="X22" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y22" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="23" spans="1:25" x14ac:dyDescent="0.15">
@@ -3802,10 +3826,10 @@
         <v>0</v>
       </c>
       <c r="X23" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y23" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="24" spans="1:25" x14ac:dyDescent="0.15">
@@ -3867,10 +3891,10 @@
         <v>0</v>
       </c>
       <c r="X24" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y24" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="25" spans="1:25" x14ac:dyDescent="0.15">
@@ -3917,10 +3941,10 @@
         <v>100</v>
       </c>
       <c r="O25" s="4" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="P25" s="4" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="Q25" s="3" t="s">
         <v>231</v>
@@ -3929,25 +3953,25 @@
         <v>0</v>
       </c>
       <c r="S25" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="T25" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="U25" s="1" t="s">
         <v>581</v>
       </c>
-      <c r="T25" s="1" t="s">
+      <c r="V25" s="1" t="s">
         <v>582</v>
       </c>
-      <c r="U25" s="1" t="s">
-        <v>583</v>
-      </c>
-      <c r="V25" s="1" t="s">
-        <v>584</v>
-      </c>
       <c r="W25" s="1">
         <v>0</v>
       </c>
       <c r="X25" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y25" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="26" spans="1:25" x14ac:dyDescent="0.15">
@@ -4009,10 +4033,10 @@
         <v>0</v>
       </c>
       <c r="X26" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y26" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="27" spans="1:25" x14ac:dyDescent="0.15">
@@ -4074,10 +4098,10 @@
         <v>0</v>
       </c>
       <c r="X27" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y27" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="28" spans="1:25" x14ac:dyDescent="0.15">
@@ -4139,10 +4163,10 @@
         <v>0</v>
       </c>
       <c r="X28" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y28" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="29" spans="1:25" x14ac:dyDescent="0.15">
@@ -4204,10 +4228,10 @@
         <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y29" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="30" spans="1:25" x14ac:dyDescent="0.15">
@@ -4269,10 +4293,10 @@
         <v>0</v>
       </c>
       <c r="X30" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y30" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="31" spans="1:25" x14ac:dyDescent="0.15">
@@ -4334,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="X31" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y31" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="32" spans="1:25" x14ac:dyDescent="0.15">
@@ -4399,10 +4423,10 @@
         <v>0</v>
       </c>
       <c r="X32" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y32" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="33" spans="1:25" x14ac:dyDescent="0.15">
@@ -4464,10 +4488,10 @@
         <v>0</v>
       </c>
       <c r="X33" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y33" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="34" spans="1:25" x14ac:dyDescent="0.15">
@@ -4514,10 +4538,10 @@
         <v>1</v>
       </c>
       <c r="O34" s="4" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="P34" s="4" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="Q34" s="3" t="s">
         <v>231</v>
@@ -4526,25 +4550,25 @@
         <v>0</v>
       </c>
       <c r="S34" s="1" t="s">
+        <v>595</v>
+      </c>
+      <c r="T34" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="U34" s="1" t="s">
         <v>597</v>
       </c>
-      <c r="T34" s="1" t="s">
+      <c r="V34" s="1" t="s">
         <v>598</v>
       </c>
-      <c r="U34" s="1" t="s">
+      <c r="W34" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="X34" s="3" t="s">
+        <v>589</v>
+      </c>
+      <c r="Y34" s="3" t="s">
         <v>599</v>
-      </c>
-      <c r="V34" s="1" t="s">
-        <v>600</v>
-      </c>
-      <c r="W34" s="1" t="s">
-        <v>590</v>
-      </c>
-      <c r="X34" s="3" t="s">
-        <v>591</v>
-      </c>
-      <c r="Y34" s="3" t="s">
-        <v>601</v>
       </c>
     </row>
     <row r="35" spans="1:25" x14ac:dyDescent="0.15">
@@ -4569,8 +4593,8 @@
       <c r="G35" s="1">
         <v>43400002</v>
       </c>
-      <c r="H35" s="1" t="s">
-        <v>202</v>
+      <c r="H35" s="1">
+        <v>0</v>
       </c>
       <c r="I35" s="1">
         <v>1</v>
@@ -4588,28 +4612,40 @@
         <v>215</v>
       </c>
       <c r="N35" s="1">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="O35" s="4" t="s">
-        <v>282</v>
+        <v>600</v>
       </c>
       <c r="P35" s="4" t="s">
-        <v>283</v>
+        <v>601</v>
       </c>
       <c r="Q35" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="R35" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="W35" s="1">
-        <v>0</v>
+      <c r="R35" s="1">
+        <v>0</v>
+      </c>
+      <c r="S35" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="T35" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="U35" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="V35" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="W35" s="1" t="s">
+        <v>588</v>
       </c>
       <c r="X35" s="3" t="s">
-        <v>586</v>
+        <v>603</v>
       </c>
       <c r="Y35" s="3" t="s">
-        <v>586</v>
+        <v>602</v>
       </c>
     </row>
     <row r="36" spans="1:25" x14ac:dyDescent="0.15">
@@ -4656,10 +4692,10 @@
         <v>100</v>
       </c>
       <c r="O36" s="4" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="P36" s="4" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="Q36" s="3" t="s">
         <v>231</v>
@@ -4671,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="X36" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y36" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="37" spans="1:25" x14ac:dyDescent="0.15">
@@ -4721,10 +4757,10 @@
         <v>100</v>
       </c>
       <c r="O37" s="4" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="P37" s="4" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="Q37" s="3" t="s">
         <v>231</v>
@@ -4736,10 +4772,10 @@
         <v>0</v>
       </c>
       <c r="X37" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y37" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="38" spans="1:25" x14ac:dyDescent="0.15">
@@ -4786,10 +4822,10 @@
         <v>100</v>
       </c>
       <c r="O38" s="4" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="P38" s="4" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="Q38" s="3" t="s">
         <v>231</v>
@@ -4801,10 +4837,10 @@
         <v>0</v>
       </c>
       <c r="X38" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y38" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="39" spans="1:25" x14ac:dyDescent="0.15">
@@ -4851,10 +4887,10 @@
         <v>100</v>
       </c>
       <c r="O39" s="4" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="P39" s="4" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="Q39" s="3" t="s">
         <v>231</v>
@@ -4866,10 +4902,10 @@
         <v>0</v>
       </c>
       <c r="X39" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y39" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="40" spans="1:25" x14ac:dyDescent="0.15">
@@ -4916,10 +4952,10 @@
         <v>100</v>
       </c>
       <c r="O40" s="4" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="P40" s="4" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="Q40" s="3" t="s">
         <v>231</v>
@@ -4931,10 +4967,10 @@
         <v>0</v>
       </c>
       <c r="X40" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y40" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="41" spans="1:25" x14ac:dyDescent="0.15">
@@ -4981,10 +5017,10 @@
         <v>100</v>
       </c>
       <c r="O41" s="4" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="P41" s="4" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="Q41" s="3" t="s">
         <v>231</v>
@@ -4996,10 +5032,10 @@
         <v>0</v>
       </c>
       <c r="X41" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y41" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="42" spans="1:25" x14ac:dyDescent="0.15">
@@ -5046,10 +5082,10 @@
         <v>100</v>
       </c>
       <c r="O42" s="4" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="P42" s="4" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="Q42" s="3" t="s">
         <v>231</v>
@@ -5061,10 +5097,10 @@
         <v>0</v>
       </c>
       <c r="X42" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y42" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="43" spans="1:25" x14ac:dyDescent="0.15">
@@ -5111,10 +5147,10 @@
         <v>100</v>
       </c>
       <c r="O43" s="4" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="P43" s="4" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="Q43" s="3" t="s">
         <v>231</v>
@@ -5126,10 +5162,10 @@
         <v>0</v>
       </c>
       <c r="X43" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y43" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="44" spans="1:25" x14ac:dyDescent="0.15">
@@ -5176,10 +5212,10 @@
         <v>100</v>
       </c>
       <c r="O44" s="4" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="P44" s="4" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="Q44" s="3" t="s">
         <v>231</v>
@@ -5191,10 +5227,10 @@
         <v>0</v>
       </c>
       <c r="X44" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y44" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="45" spans="1:25" x14ac:dyDescent="0.15">
@@ -5241,10 +5277,10 @@
         <v>100</v>
       </c>
       <c r="O45" s="4" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="P45" s="4" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="Q45" s="3" t="s">
         <v>231</v>
@@ -5256,10 +5292,10 @@
         <v>0</v>
       </c>
       <c r="X45" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y45" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="46" spans="1:25" x14ac:dyDescent="0.15">
@@ -5306,10 +5342,10 @@
         <v>100</v>
       </c>
       <c r="O46" s="4" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="P46" s="4" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="Q46" s="3" t="s">
         <v>231</v>
@@ -5321,10 +5357,10 @@
         <v>0</v>
       </c>
       <c r="X46" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y46" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="47" spans="1:25" x14ac:dyDescent="0.15">
@@ -5371,10 +5407,10 @@
         <v>100</v>
       </c>
       <c r="O47" s="4" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="P47" s="4" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="Q47" s="3" t="s">
         <v>231</v>
@@ -5386,10 +5422,10 @@
         <v>0</v>
       </c>
       <c r="X47" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y47" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="48" spans="1:25" x14ac:dyDescent="0.15">
@@ -5436,10 +5472,10 @@
         <v>100</v>
       </c>
       <c r="O48" s="4" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="P48" s="4" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="Q48" s="3" t="s">
         <v>231</v>
@@ -5451,10 +5487,10 @@
         <v>0</v>
       </c>
       <c r="X48" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y48" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="49" spans="1:25" x14ac:dyDescent="0.15">
@@ -5501,10 +5537,10 @@
         <v>100</v>
       </c>
       <c r="O49" s="4" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="P49" s="4" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="Q49" s="3" t="s">
         <v>231</v>
@@ -5516,10 +5552,10 @@
         <v>0</v>
       </c>
       <c r="X49" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y49" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="50" spans="1:25" x14ac:dyDescent="0.15">
@@ -5566,10 +5602,10 @@
         <v>100</v>
       </c>
       <c r="O50" s="4" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="P50" s="4" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="Q50" s="3" t="s">
         <v>231</v>
@@ -5581,10 +5617,10 @@
         <v>0</v>
       </c>
       <c r="X50" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y50" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="51" spans="1:25" x14ac:dyDescent="0.15">
@@ -5631,10 +5667,10 @@
         <v>100</v>
       </c>
       <c r="O51" s="4" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="P51" s="4" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="Q51" s="3" t="s">
         <v>231</v>
@@ -5646,10 +5682,10 @@
         <v>0</v>
       </c>
       <c r="X51" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y51" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="52" spans="1:25" x14ac:dyDescent="0.15">
@@ -5696,10 +5732,10 @@
         <v>100</v>
       </c>
       <c r="O52" s="4" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="P52" s="4" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="Q52" s="3" t="s">
         <v>231</v>
@@ -5711,10 +5747,10 @@
         <v>0</v>
       </c>
       <c r="X52" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y52" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="53" spans="1:25" x14ac:dyDescent="0.15">
@@ -5761,10 +5797,10 @@
         <v>100</v>
       </c>
       <c r="O53" s="4" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="P53" s="4" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="Q53" s="3" t="s">
         <v>231</v>
@@ -5776,10 +5812,10 @@
         <v>0</v>
       </c>
       <c r="X53" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y53" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="54" spans="1:25" x14ac:dyDescent="0.15">
@@ -5826,10 +5862,10 @@
         <v>100</v>
       </c>
       <c r="O54" s="4" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="P54" s="4" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="Q54" s="3" t="s">
         <v>231</v>
@@ -5841,10 +5877,10 @@
         <v>0</v>
       </c>
       <c r="X54" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y54" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="55" spans="1:25" x14ac:dyDescent="0.15">
@@ -5891,10 +5927,10 @@
         <v>100</v>
       </c>
       <c r="O55" s="4" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="P55" s="4" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="Q55" s="3" t="s">
         <v>231</v>
@@ -5906,10 +5942,10 @@
         <v>0</v>
       </c>
       <c r="X55" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y55" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="56" spans="1:25" x14ac:dyDescent="0.15">
@@ -5956,10 +5992,10 @@
         <v>100</v>
       </c>
       <c r="O56" s="4" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="P56" s="4" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="Q56" s="3" t="s">
         <v>231</v>
@@ -5971,10 +6007,10 @@
         <v>0</v>
       </c>
       <c r="X56" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y56" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="57" spans="1:25" x14ac:dyDescent="0.15">
@@ -6021,10 +6057,10 @@
         <v>100</v>
       </c>
       <c r="O57" s="4" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="P57" s="4" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="Q57" s="3" t="s">
         <v>231</v>
@@ -6036,10 +6072,10 @@
         <v>0</v>
       </c>
       <c r="X57" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y57" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="58" spans="1:25" x14ac:dyDescent="0.15">
@@ -6086,10 +6122,10 @@
         <v>100</v>
       </c>
       <c r="O58" s="4" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="P58" s="4" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="Q58" s="3" t="s">
         <v>231</v>
@@ -6101,10 +6137,10 @@
         <v>0</v>
       </c>
       <c r="X58" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y58" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="59" spans="1:25" x14ac:dyDescent="0.15">
@@ -6151,10 +6187,10 @@
         <v>100</v>
       </c>
       <c r="O59" s="4" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="P59" s="4" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="Q59" s="3" t="s">
         <v>231</v>
@@ -6166,10 +6202,10 @@
         <v>0</v>
       </c>
       <c r="X59" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y59" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="60" spans="1:25" x14ac:dyDescent="0.15">
@@ -6216,10 +6252,10 @@
         <v>100</v>
       </c>
       <c r="O60" s="4" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="P60" s="4" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="Q60" s="3" t="s">
         <v>231</v>
@@ -6231,10 +6267,10 @@
         <v>0</v>
       </c>
       <c r="X60" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y60" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="61" spans="1:25" x14ac:dyDescent="0.15">
@@ -6281,10 +6317,10 @@
         <v>100</v>
       </c>
       <c r="O61" s="4" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="P61" s="4" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="Q61" s="3" t="s">
         <v>231</v>
@@ -6296,10 +6332,10 @@
         <v>0</v>
       </c>
       <c r="X61" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y61" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="62" spans="1:25" x14ac:dyDescent="0.15">
@@ -6346,10 +6382,10 @@
         <v>100</v>
       </c>
       <c r="O62" s="4" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="P62" s="4" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="Q62" s="3" t="s">
         <v>231</v>
@@ -6361,10 +6397,10 @@
         <v>0</v>
       </c>
       <c r="X62" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y62" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="63" spans="1:25" x14ac:dyDescent="0.15">
@@ -6411,10 +6447,10 @@
         <v>100</v>
       </c>
       <c r="O63" s="4" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="P63" s="4" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="Q63" s="3" t="s">
         <v>231</v>
@@ -6426,10 +6462,10 @@
         <v>0</v>
       </c>
       <c r="X63" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y63" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="64" spans="1:25" x14ac:dyDescent="0.15">
@@ -6476,10 +6512,10 @@
         <v>100</v>
       </c>
       <c r="O64" s="4" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="P64" s="4" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="Q64" s="3" t="s">
         <v>231</v>
@@ -6491,10 +6527,10 @@
         <v>0</v>
       </c>
       <c r="X64" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y64" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="65" spans="1:25" x14ac:dyDescent="0.15">
@@ -6541,10 +6577,10 @@
         <v>100</v>
       </c>
       <c r="O65" s="4" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="P65" s="4" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="Q65" s="3" t="s">
         <v>231</v>
@@ -6556,10 +6592,10 @@
         <v>0</v>
       </c>
       <c r="X65" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y65" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="66" spans="1:25" x14ac:dyDescent="0.15">
@@ -6606,10 +6642,10 @@
         <v>100</v>
       </c>
       <c r="O66" s="4" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="P66" s="4" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="Q66" s="3" t="s">
         <v>231</v>
@@ -6621,10 +6657,10 @@
         <v>0</v>
       </c>
       <c r="X66" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y66" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="67" spans="1:25" x14ac:dyDescent="0.15">
@@ -6671,10 +6707,10 @@
         <v>100</v>
       </c>
       <c r="O67" s="4" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="P67" s="4" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="Q67" s="3" t="s">
         <v>231</v>
@@ -6686,10 +6722,10 @@
         <v>0</v>
       </c>
       <c r="X67" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y67" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="68" spans="1:25" x14ac:dyDescent="0.15">
@@ -6736,10 +6772,10 @@
         <v>100</v>
       </c>
       <c r="O68" s="4" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="P68" s="4" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="Q68" s="3" t="s">
         <v>231</v>
@@ -6751,10 +6787,10 @@
         <v>0</v>
       </c>
       <c r="X68" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y68" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="69" spans="1:25" x14ac:dyDescent="0.15">
@@ -6801,10 +6837,10 @@
         <v>100</v>
       </c>
       <c r="O69" s="4" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="P69" s="4" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="Q69" s="3" t="s">
         <v>231</v>
@@ -6816,10 +6852,10 @@
         <v>0</v>
       </c>
       <c r="X69" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y69" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="70" spans="1:25" x14ac:dyDescent="0.15">
@@ -6866,10 +6902,10 @@
         <v>100</v>
       </c>
       <c r="O70" s="4" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="P70" s="4" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="Q70" s="3" t="s">
         <v>231</v>
@@ -6881,10 +6917,10 @@
         <v>0</v>
       </c>
       <c r="X70" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y70" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="71" spans="1:25" x14ac:dyDescent="0.15">
@@ -6931,10 +6967,10 @@
         <v>100</v>
       </c>
       <c r="O71" s="4" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="P71" s="4" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="Q71" s="3" t="s">
         <v>231</v>
@@ -6946,10 +6982,10 @@
         <v>0</v>
       </c>
       <c r="X71" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y71" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="72" spans="1:25" x14ac:dyDescent="0.15">
@@ -6996,10 +7032,10 @@
         <v>100</v>
       </c>
       <c r="O72" s="4" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="P72" s="4" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="Q72" s="3" t="s">
         <v>231</v>
@@ -7011,10 +7047,10 @@
         <v>0</v>
       </c>
       <c r="X72" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y72" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="73" spans="1:25" x14ac:dyDescent="0.15">
@@ -7061,10 +7097,10 @@
         <v>100</v>
       </c>
       <c r="O73" s="4" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="P73" s="4" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="Q73" s="3" t="s">
         <v>231</v>
@@ -7076,10 +7112,10 @@
         <v>0</v>
       </c>
       <c r="X73" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y73" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="74" spans="1:25" x14ac:dyDescent="0.15">
@@ -7126,10 +7162,10 @@
         <v>100</v>
       </c>
       <c r="O74" s="4" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="P74" s="4" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="Q74" s="3" t="s">
         <v>231</v>
@@ -7141,10 +7177,10 @@
         <v>0</v>
       </c>
       <c r="X74" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y74" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="75" spans="1:25" x14ac:dyDescent="0.15">
@@ -7191,10 +7227,10 @@
         <v>100</v>
       </c>
       <c r="O75" s="4" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="P75" s="4" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="Q75" s="3" t="s">
         <v>231</v>
@@ -7206,10 +7242,10 @@
         <v>0</v>
       </c>
       <c r="X75" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y75" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="76" spans="1:25" x14ac:dyDescent="0.15">
@@ -7256,10 +7292,10 @@
         <v>100</v>
       </c>
       <c r="O76" s="4" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="P76" s="4" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="Q76" s="3" t="s">
         <v>231</v>
@@ -7271,10 +7307,10 @@
         <v>0</v>
       </c>
       <c r="X76" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y76" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="77" spans="1:25" x14ac:dyDescent="0.15">
@@ -7321,10 +7357,10 @@
         <v>100</v>
       </c>
       <c r="O77" s="4" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="P77" s="4" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="Q77" s="3" t="s">
         <v>231</v>
@@ -7336,10 +7372,10 @@
         <v>0</v>
       </c>
       <c r="X77" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y77" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="78" spans="1:25" x14ac:dyDescent="0.15">
@@ -7386,10 +7422,10 @@
         <v>100</v>
       </c>
       <c r="O78" s="4" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="P78" s="4" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="Q78" s="3" t="s">
         <v>231</v>
@@ -7401,10 +7437,10 @@
         <v>0</v>
       </c>
       <c r="X78" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y78" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="79" spans="1:25" x14ac:dyDescent="0.15">
@@ -7451,10 +7487,10 @@
         <v>100</v>
       </c>
       <c r="O79" s="4" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="P79" s="4" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="Q79" s="3" t="s">
         <v>231</v>
@@ -7466,10 +7502,10 @@
         <v>0</v>
       </c>
       <c r="X79" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y79" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="80" spans="1:25" x14ac:dyDescent="0.15">
@@ -7516,10 +7552,10 @@
         <v>100</v>
       </c>
       <c r="O80" s="4" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="P80" s="4" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="Q80" s="3" t="s">
         <v>231</v>
@@ -7531,10 +7567,10 @@
         <v>0</v>
       </c>
       <c r="X80" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y80" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="81" spans="1:25" x14ac:dyDescent="0.15">
@@ -7581,10 +7617,10 @@
         <v>100</v>
       </c>
       <c r="O81" s="4" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="P81" s="4" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="Q81" s="3" t="s">
         <v>231</v>
@@ -7596,10 +7632,10 @@
         <v>0</v>
       </c>
       <c r="X81" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y81" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="82" spans="1:25" x14ac:dyDescent="0.15">
@@ -7646,10 +7682,10 @@
         <v>100</v>
       </c>
       <c r="O82" s="4" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="P82" s="4" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="Q82" s="3" t="s">
         <v>231</v>
@@ -7661,10 +7697,10 @@
         <v>0</v>
       </c>
       <c r="X82" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y82" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="83" spans="1:25" x14ac:dyDescent="0.15">
@@ -7711,10 +7747,10 @@
         <v>100</v>
       </c>
       <c r="O83" s="4" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="P83" s="4" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="Q83" s="3" t="s">
         <v>231</v>
@@ -7726,10 +7762,10 @@
         <v>0</v>
       </c>
       <c r="X83" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y83" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="84" spans="1:25" x14ac:dyDescent="0.15">
@@ -7776,10 +7812,10 @@
         <v>100</v>
       </c>
       <c r="O84" s="4" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="P84" s="4" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="Q84" s="3" t="s">
         <v>231</v>
@@ -7791,10 +7827,10 @@
         <v>0</v>
       </c>
       <c r="X84" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y84" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="85" spans="1:25" x14ac:dyDescent="0.15">
@@ -7841,10 +7877,10 @@
         <v>100</v>
       </c>
       <c r="O85" s="4" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="P85" s="4" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="Q85" s="3" t="s">
         <v>231</v>
@@ -7856,10 +7892,10 @@
         <v>0</v>
       </c>
       <c r="X85" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y85" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="86" spans="1:25" x14ac:dyDescent="0.15">
@@ -7906,10 +7942,10 @@
         <v>100</v>
       </c>
       <c r="O86" s="4" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="P86" s="4" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="Q86" s="3" t="s">
         <v>231</v>
@@ -7921,10 +7957,10 @@
         <v>0</v>
       </c>
       <c r="X86" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y86" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="87" spans="1:25" x14ac:dyDescent="0.15">
@@ -7971,10 +8007,10 @@
         <v>100</v>
       </c>
       <c r="O87" s="4" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="P87" s="4" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="Q87" s="3" t="s">
         <v>231</v>
@@ -7986,10 +8022,10 @@
         <v>0</v>
       </c>
       <c r="X87" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y87" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="88" spans="1:25" x14ac:dyDescent="0.15">
@@ -8036,10 +8072,10 @@
         <v>100</v>
       </c>
       <c r="O88" s="4" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="P88" s="4" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="Q88" s="3" t="s">
         <v>231</v>
@@ -8051,10 +8087,10 @@
         <v>0</v>
       </c>
       <c r="X88" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y88" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="89" spans="1:25" x14ac:dyDescent="0.15">
@@ -8101,10 +8137,10 @@
         <v>100</v>
       </c>
       <c r="O89" s="4" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="P89" s="4" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="Q89" s="3" t="s">
         <v>231</v>
@@ -8116,10 +8152,10 @@
         <v>0</v>
       </c>
       <c r="X89" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y89" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="90" spans="1:25" x14ac:dyDescent="0.15">
@@ -8166,10 +8202,10 @@
         <v>100</v>
       </c>
       <c r="O90" s="4" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="P90" s="4" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="Q90" s="3" t="s">
         <v>231</v>
@@ -8181,10 +8217,10 @@
         <v>0</v>
       </c>
       <c r="X90" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y90" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="91" spans="1:25" x14ac:dyDescent="0.15">
@@ -8231,10 +8267,10 @@
         <v>100</v>
       </c>
       <c r="O91" s="4" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="P91" s="4" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="Q91" s="3" t="s">
         <v>231</v>
@@ -8246,10 +8282,10 @@
         <v>0</v>
       </c>
       <c r="X91" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y91" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="92" spans="1:25" x14ac:dyDescent="0.15">
@@ -8296,10 +8332,10 @@
         <v>100</v>
       </c>
       <c r="O92" s="4" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="P92" s="4" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="Q92" s="3" t="s">
         <v>231</v>
@@ -8311,10 +8347,10 @@
         <v>0</v>
       </c>
       <c r="X92" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y92" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="93" spans="1:25" x14ac:dyDescent="0.15">
@@ -8361,10 +8397,10 @@
         <v>100</v>
       </c>
       <c r="O93" s="4" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="P93" s="4" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="Q93" s="3" t="s">
         <v>231</v>
@@ -8376,10 +8412,10 @@
         <v>0</v>
       </c>
       <c r="X93" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y93" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="94" spans="1:25" x14ac:dyDescent="0.15">
@@ -8426,10 +8462,10 @@
         <v>100</v>
       </c>
       <c r="O94" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="P94" s="4" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="Q94" s="3" t="s">
         <v>231</v>
@@ -8441,10 +8477,10 @@
         <v>0</v>
       </c>
       <c r="X94" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y94" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="95" spans="1:25" x14ac:dyDescent="0.15">
@@ -8491,10 +8527,10 @@
         <v>100</v>
       </c>
       <c r="O95" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="P95" s="4" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="Q95" s="3" t="s">
         <v>231</v>
@@ -8506,10 +8542,10 @@
         <v>0</v>
       </c>
       <c r="X95" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y95" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="96" spans="1:25" x14ac:dyDescent="0.15">
@@ -8556,10 +8592,10 @@
         <v>100</v>
       </c>
       <c r="O96" s="4" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="P96" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="Q96" s="3" t="s">
         <v>231</v>
@@ -8571,10 +8607,10 @@
         <v>0</v>
       </c>
       <c r="X96" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y96" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="97" spans="1:25" x14ac:dyDescent="0.15">
@@ -8621,10 +8657,10 @@
         <v>100</v>
       </c>
       <c r="O97" s="4" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="P97" s="4" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="Q97" s="3" t="s">
         <v>231</v>
@@ -8636,10 +8672,10 @@
         <v>0</v>
       </c>
       <c r="X97" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y97" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="98" spans="1:25" x14ac:dyDescent="0.15">
@@ -8686,10 +8722,10 @@
         <v>100</v>
       </c>
       <c r="O98" s="4" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="P98" s="4" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="Q98" s="3" t="s">
         <v>231</v>
@@ -8701,10 +8737,10 @@
         <v>0</v>
       </c>
       <c r="X98" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y98" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="99" spans="1:25" x14ac:dyDescent="0.15">
@@ -8751,10 +8787,10 @@
         <v>100</v>
       </c>
       <c r="O99" s="4" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="P99" s="4" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="Q99" s="3" t="s">
         <v>231</v>
@@ -8766,10 +8802,10 @@
         <v>0</v>
       </c>
       <c r="X99" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y99" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="100" spans="1:25" x14ac:dyDescent="0.15">
@@ -8816,10 +8852,10 @@
         <v>100</v>
       </c>
       <c r="O100" s="4" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="P100" s="4" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="Q100" s="3" t="s">
         <v>231</v>
@@ -8831,10 +8867,10 @@
         <v>0</v>
       </c>
       <c r="X100" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y100" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="101" spans="1:25" x14ac:dyDescent="0.15">
@@ -8881,10 +8917,10 @@
         <v>100</v>
       </c>
       <c r="O101" s="4" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="P101" s="4" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="Q101" s="3" t="s">
         <v>231</v>
@@ -8896,10 +8932,10 @@
         <v>0</v>
       </c>
       <c r="X101" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y101" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="102" spans="1:25" x14ac:dyDescent="0.15">
@@ -8946,10 +8982,10 @@
         <v>100</v>
       </c>
       <c r="O102" s="4" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="P102" s="4" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="Q102" s="3" t="s">
         <v>231</v>
@@ -8961,10 +8997,10 @@
         <v>0</v>
       </c>
       <c r="X102" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y102" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="103" spans="1:25" x14ac:dyDescent="0.15">
@@ -9011,10 +9047,10 @@
         <v>100</v>
       </c>
       <c r="O103" s="4" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="P103" s="4" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="Q103" s="3" t="s">
         <v>231</v>
@@ -9026,10 +9062,10 @@
         <v>0</v>
       </c>
       <c r="X103" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y103" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="104" spans="1:25" x14ac:dyDescent="0.15">
@@ -9076,10 +9112,10 @@
         <v>100</v>
       </c>
       <c r="O104" s="4" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="P104" s="4" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="Q104" s="3" t="s">
         <v>231</v>
@@ -9091,10 +9127,10 @@
         <v>0</v>
       </c>
       <c r="X104" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y104" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="105" spans="1:25" x14ac:dyDescent="0.15">
@@ -9141,10 +9177,10 @@
         <v>100</v>
       </c>
       <c r="O105" s="4" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="P105" s="4" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="Q105" s="3" t="s">
         <v>231</v>
@@ -9156,10 +9192,10 @@
         <v>0</v>
       </c>
       <c r="X105" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y105" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="106" spans="1:25" x14ac:dyDescent="0.15">
@@ -9206,10 +9242,10 @@
         <v>100</v>
       </c>
       <c r="O106" s="4" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="P106" s="4" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="Q106" s="3" t="s">
         <v>231</v>
@@ -9221,10 +9257,10 @@
         <v>0</v>
       </c>
       <c r="X106" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y106" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="107" spans="1:25" x14ac:dyDescent="0.15">
@@ -9271,10 +9307,10 @@
         <v>100</v>
       </c>
       <c r="O107" s="4" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="P107" s="4" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="Q107" s="3" t="s">
         <v>231</v>
@@ -9286,10 +9322,10 @@
         <v>0</v>
       </c>
       <c r="X107" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y107" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="108" spans="1:25" x14ac:dyDescent="0.15">
@@ -9336,10 +9372,10 @@
         <v>100</v>
       </c>
       <c r="O108" s="4" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="P108" s="4" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="Q108" s="3" t="s">
         <v>231</v>
@@ -9351,10 +9387,10 @@
         <v>0</v>
       </c>
       <c r="X108" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y108" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="109" spans="1:25" x14ac:dyDescent="0.15">
@@ -9401,10 +9437,10 @@
         <v>100</v>
       </c>
       <c r="O109" s="4" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="P109" s="4" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="Q109" s="3" t="s">
         <v>231</v>
@@ -9416,10 +9452,10 @@
         <v>0</v>
       </c>
       <c r="X109" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y109" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="110" spans="1:25" x14ac:dyDescent="0.15">
@@ -9466,10 +9502,10 @@
         <v>100</v>
       </c>
       <c r="O110" s="4" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="P110" s="4" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="Q110" s="3" t="s">
         <v>231</v>
@@ -9481,10 +9517,10 @@
         <v>0</v>
       </c>
       <c r="X110" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y110" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="111" spans="1:25" x14ac:dyDescent="0.15">
@@ -9531,10 +9567,10 @@
         <v>100</v>
       </c>
       <c r="O111" s="4" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="P111" s="4" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="Q111" s="3" t="s">
         <v>231</v>
@@ -9546,10 +9582,10 @@
         <v>0</v>
       </c>
       <c r="X111" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y111" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="112" spans="1:25" x14ac:dyDescent="0.15">
@@ -9596,10 +9632,10 @@
         <v>100</v>
       </c>
       <c r="O112" s="4" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="P112" s="4" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="Q112" s="3" t="s">
         <v>231</v>
@@ -9611,10 +9647,10 @@
         <v>0</v>
       </c>
       <c r="X112" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y112" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="113" spans="1:25" x14ac:dyDescent="0.15">
@@ -9661,10 +9697,10 @@
         <v>100</v>
       </c>
       <c r="O113" s="4" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="P113" s="4" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="Q113" s="3" t="s">
         <v>231</v>
@@ -9676,10 +9712,10 @@
         <v>0</v>
       </c>
       <c r="X113" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y113" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="114" spans="1:25" x14ac:dyDescent="0.15">
@@ -9726,10 +9762,10 @@
         <v>100</v>
       </c>
       <c r="O114" s="4" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="P114" s="4" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="Q114" s="3" t="s">
         <v>231</v>
@@ -9741,10 +9777,10 @@
         <v>0</v>
       </c>
       <c r="X114" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y114" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="115" spans="1:25" x14ac:dyDescent="0.15">
@@ -9791,10 +9827,10 @@
         <v>100</v>
       </c>
       <c r="O115" s="4" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="P115" s="4" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="Q115" s="3" t="s">
         <v>231</v>
@@ -9806,10 +9842,10 @@
         <v>0</v>
       </c>
       <c r="X115" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y115" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="116" spans="1:25" x14ac:dyDescent="0.15">
@@ -9856,10 +9892,10 @@
         <v>100</v>
       </c>
       <c r="O116" s="4" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="P116" s="4" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="Q116" s="3" t="s">
         <v>231</v>
@@ -9871,10 +9907,10 @@
         <v>0</v>
       </c>
       <c r="X116" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y116" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="117" spans="1:25" x14ac:dyDescent="0.15">
@@ -9921,10 +9957,10 @@
         <v>100</v>
       </c>
       <c r="O117" s="4" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="P117" s="4" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="Q117" s="3" t="s">
         <v>231</v>
@@ -9936,10 +9972,10 @@
         <v>0</v>
       </c>
       <c r="X117" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y117" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="118" spans="1:25" x14ac:dyDescent="0.15">
@@ -9986,10 +10022,10 @@
         <v>100</v>
       </c>
       <c r="O118" s="4" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="P118" s="4" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="Q118" s="3" t="s">
         <v>231</v>
@@ -10001,10 +10037,10 @@
         <v>0</v>
       </c>
       <c r="X118" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y118" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="119" spans="1:25" x14ac:dyDescent="0.15">
@@ -10051,10 +10087,10 @@
         <v>100</v>
       </c>
       <c r="O119" s="4" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="P119" s="4" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="Q119" s="3" t="s">
         <v>231</v>
@@ -10066,10 +10102,10 @@
         <v>0</v>
       </c>
       <c r="X119" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y119" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="120" spans="1:25" x14ac:dyDescent="0.15">
@@ -10116,10 +10152,10 @@
         <v>100</v>
       </c>
       <c r="O120" s="4" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="P120" s="4" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="Q120" s="3" t="s">
         <v>231</v>
@@ -10131,10 +10167,10 @@
         <v>0</v>
       </c>
       <c r="X120" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y120" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="121" spans="1:25" x14ac:dyDescent="0.15">
@@ -10181,10 +10217,10 @@
         <v>100</v>
       </c>
       <c r="O121" s="4" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="P121" s="4" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="Q121" s="3" t="s">
         <v>231</v>
@@ -10196,10 +10232,10 @@
         <v>0</v>
       </c>
       <c r="X121" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y121" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="122" spans="1:25" x14ac:dyDescent="0.15">
@@ -10246,10 +10282,10 @@
         <v>100</v>
       </c>
       <c r="O122" s="4" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="P122" s="4" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="Q122" s="3" t="s">
         <v>231</v>
@@ -10261,10 +10297,10 @@
         <v>0</v>
       </c>
       <c r="X122" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y122" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="123" spans="1:25" x14ac:dyDescent="0.15">
@@ -10311,10 +10347,10 @@
         <v>100</v>
       </c>
       <c r="O123" s="4" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="P123" s="4" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="Q123" s="3" t="s">
         <v>231</v>
@@ -10326,10 +10362,10 @@
         <v>0</v>
       </c>
       <c r="X123" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y123" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="124" spans="1:25" x14ac:dyDescent="0.15">
@@ -10376,10 +10412,10 @@
         <v>100</v>
       </c>
       <c r="O124" s="4" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="P124" s="4" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q124" s="3" t="s">
         <v>231</v>
@@ -10391,10 +10427,10 @@
         <v>0</v>
       </c>
       <c r="X124" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y124" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="125" spans="1:25" x14ac:dyDescent="0.15">
@@ -10441,10 +10477,10 @@
         <v>100</v>
       </c>
       <c r="O125" s="4" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="P125" s="4" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="Q125" s="3" t="s">
         <v>231</v>
@@ -10456,10 +10492,10 @@
         <v>0</v>
       </c>
       <c r="X125" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y125" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="126" spans="1:25" x14ac:dyDescent="0.15">
@@ -10506,10 +10542,10 @@
         <v>100</v>
       </c>
       <c r="O126" s="4" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="P126" s="4" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="Q126" s="3" t="s">
         <v>231</v>
@@ -10521,10 +10557,10 @@
         <v>0</v>
       </c>
       <c r="X126" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y126" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="127" spans="1:25" x14ac:dyDescent="0.15">
@@ -10571,10 +10607,10 @@
         <v>100</v>
       </c>
       <c r="O127" s="4" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="P127" s="4" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="Q127" s="3" t="s">
         <v>231</v>
@@ -10586,10 +10622,10 @@
         <v>0</v>
       </c>
       <c r="X127" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y127" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="128" spans="1:25" x14ac:dyDescent="0.15">
@@ -10636,10 +10672,10 @@
         <v>100</v>
       </c>
       <c r="O128" s="4" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="P128" s="4" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="Q128" s="3" t="s">
         <v>231</v>
@@ -10651,10 +10687,10 @@
         <v>0</v>
       </c>
       <c r="X128" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y128" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="129" spans="1:25" x14ac:dyDescent="0.15">
@@ -10701,10 +10737,10 @@
         <v>100</v>
       </c>
       <c r="O129" s="4" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="P129" s="4" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="Q129" s="3" t="s">
         <v>231</v>
@@ -10716,10 +10752,10 @@
         <v>0</v>
       </c>
       <c r="X129" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y129" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="130" spans="1:25" x14ac:dyDescent="0.15">
@@ -10766,10 +10802,10 @@
         <v>100</v>
       </c>
       <c r="O130" s="4" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="P130" s="4" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="Q130" s="3" t="s">
         <v>231</v>
@@ -10781,10 +10817,10 @@
         <v>0</v>
       </c>
       <c r="X130" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y130" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="131" spans="1:25" x14ac:dyDescent="0.15">
@@ -10831,10 +10867,10 @@
         <v>100</v>
       </c>
       <c r="O131" s="4" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="P131" s="4" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="Q131" s="3" t="s">
         <v>231</v>
@@ -10846,10 +10882,10 @@
         <v>0</v>
       </c>
       <c r="X131" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y131" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="132" spans="1:25" x14ac:dyDescent="0.15">
@@ -10896,10 +10932,10 @@
         <v>100</v>
       </c>
       <c r="O132" s="4" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="P132" s="4" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="Q132" s="3" t="s">
         <v>231</v>
@@ -10911,10 +10947,10 @@
         <v>0</v>
       </c>
       <c r="X132" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y132" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="133" spans="1:25" x14ac:dyDescent="0.15">
@@ -10961,10 +10997,10 @@
         <v>100</v>
       </c>
       <c r="O133" s="4" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="P133" s="4" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="Q133" s="3" t="s">
         <v>231</v>
@@ -10976,10 +11012,10 @@
         <v>0</v>
       </c>
       <c r="X133" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y133" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="134" spans="1:25" x14ac:dyDescent="0.15">
@@ -11026,10 +11062,10 @@
         <v>100</v>
       </c>
       <c r="O134" s="4" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="P134" s="4" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="Q134" s="3" t="s">
         <v>231</v>
@@ -11041,10 +11077,10 @@
         <v>0</v>
       </c>
       <c r="X134" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y134" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="135" spans="1:25" x14ac:dyDescent="0.15">
@@ -11091,10 +11127,10 @@
         <v>100</v>
       </c>
       <c r="O135" s="4" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="P135" s="4" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="Q135" s="3" t="s">
         <v>231</v>
@@ -11106,10 +11142,10 @@
         <v>0</v>
       </c>
       <c r="X135" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y135" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="136" spans="1:25" x14ac:dyDescent="0.15">
@@ -11156,10 +11192,10 @@
         <v>100</v>
       </c>
       <c r="O136" s="4" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="P136" s="4" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="Q136" s="3" t="s">
         <v>231</v>
@@ -11171,10 +11207,10 @@
         <v>0</v>
       </c>
       <c r="X136" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y136" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="137" spans="1:25" x14ac:dyDescent="0.15">
@@ -11221,10 +11257,10 @@
         <v>100</v>
       </c>
       <c r="O137" s="4" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="P137" s="4" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="Q137" s="3" t="s">
         <v>231</v>
@@ -11236,10 +11272,10 @@
         <v>0</v>
       </c>
       <c r="X137" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y137" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="138" spans="1:25" x14ac:dyDescent="0.15">
@@ -11286,10 +11322,10 @@
         <v>100</v>
       </c>
       <c r="O138" s="4" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="P138" s="4" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="Q138" s="3" t="s">
         <v>231</v>
@@ -11301,10 +11337,10 @@
         <v>0</v>
       </c>
       <c r="X138" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y138" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="139" spans="1:25" x14ac:dyDescent="0.15">
@@ -11351,10 +11387,10 @@
         <v>100</v>
       </c>
       <c r="O139" s="4" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="P139" s="4" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="Q139" s="3" t="s">
         <v>231</v>
@@ -11366,10 +11402,10 @@
         <v>0</v>
       </c>
       <c r="X139" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y139" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="140" spans="1:25" x14ac:dyDescent="0.15">
@@ -11416,10 +11452,10 @@
         <v>100</v>
       </c>
       <c r="O140" s="4" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="P140" s="4" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="Q140" s="3" t="s">
         <v>231</v>
@@ -11431,10 +11467,10 @@
         <v>0</v>
       </c>
       <c r="X140" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y140" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="141" spans="1:25" x14ac:dyDescent="0.15">
@@ -11481,10 +11517,10 @@
         <v>100</v>
       </c>
       <c r="O141" s="4" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="P141" s="4" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="Q141" s="3" t="s">
         <v>231</v>
@@ -11496,10 +11532,10 @@
         <v>0</v>
       </c>
       <c r="X141" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y141" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="142" spans="1:25" x14ac:dyDescent="0.15">
@@ -11546,10 +11582,10 @@
         <v>100</v>
       </c>
       <c r="O142" s="4" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="P142" s="4" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="Q142" s="3" t="s">
         <v>231</v>
@@ -11561,10 +11597,10 @@
         <v>0</v>
       </c>
       <c r="X142" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y142" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="143" spans="1:25" x14ac:dyDescent="0.15">
@@ -11611,10 +11647,10 @@
         <v>100</v>
       </c>
       <c r="O143" s="4" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="P143" s="4" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="Q143" s="3" t="s">
         <v>231</v>
@@ -11626,10 +11662,10 @@
         <v>0</v>
       </c>
       <c r="X143" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y143" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="144" spans="1:25" x14ac:dyDescent="0.15">
@@ -11676,10 +11712,10 @@
         <v>100</v>
       </c>
       <c r="O144" s="4" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="P144" s="4" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="Q144" s="3" t="s">
         <v>231</v>
@@ -11691,10 +11727,10 @@
         <v>0</v>
       </c>
       <c r="X144" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y144" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="145" spans="1:25" x14ac:dyDescent="0.15">
@@ -11741,10 +11777,10 @@
         <v>100</v>
       </c>
       <c r="O145" s="4" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="P145" s="4" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="Q145" s="3" t="s">
         <v>231</v>
@@ -11756,10 +11792,10 @@
         <v>0</v>
       </c>
       <c r="X145" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y145" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="146" spans="1:25" x14ac:dyDescent="0.15">
@@ -11806,10 +11842,10 @@
         <v>100</v>
       </c>
       <c r="O146" s="4" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="P146" s="4" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="Q146" s="3" t="s">
         <v>231</v>
@@ -11821,10 +11857,10 @@
         <v>0</v>
       </c>
       <c r="X146" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y146" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="147" spans="1:25" x14ac:dyDescent="0.15">
@@ -11871,10 +11907,10 @@
         <v>100</v>
       </c>
       <c r="O147" s="4" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="P147" s="4" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="Q147" s="3" t="s">
         <v>231</v>
@@ -11886,10 +11922,10 @@
         <v>0</v>
       </c>
       <c r="X147" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y147" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="148" spans="1:25" x14ac:dyDescent="0.15">
@@ -11936,10 +11972,10 @@
         <v>100</v>
       </c>
       <c r="O148" s="4" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="P148" s="4" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="Q148" s="3" t="s">
         <v>231</v>
@@ -11951,10 +11987,10 @@
         <v>0</v>
       </c>
       <c r="X148" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y148" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="149" spans="1:25" x14ac:dyDescent="0.15">
@@ -12001,10 +12037,10 @@
         <v>100</v>
       </c>
       <c r="O149" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="P149" s="4" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="Q149" s="3" t="s">
         <v>231</v>
@@ -12016,10 +12052,10 @@
         <v>0</v>
       </c>
       <c r="X149" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y149" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="150" spans="1:25" x14ac:dyDescent="0.15">
@@ -12066,10 +12102,10 @@
         <v>100</v>
       </c>
       <c r="O150" s="4" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="P150" s="4" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="Q150" s="3" t="s">
         <v>231</v>
@@ -12081,10 +12117,10 @@
         <v>0</v>
       </c>
       <c r="X150" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y150" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="151" spans="1:25" x14ac:dyDescent="0.15">
@@ -12131,10 +12167,10 @@
         <v>100</v>
       </c>
       <c r="O151" s="4" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="P151" s="4" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="Q151" s="3" t="s">
         <v>231</v>
@@ -12146,10 +12182,10 @@
         <v>0</v>
       </c>
       <c r="X151" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y151" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="152" spans="1:25" x14ac:dyDescent="0.15">
@@ -12196,10 +12232,10 @@
         <v>100</v>
       </c>
       <c r="O152" s="4" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="P152" s="4" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="Q152" s="3" t="s">
         <v>231</v>
@@ -12211,10 +12247,10 @@
         <v>0</v>
       </c>
       <c r="X152" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y152" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="153" spans="1:25" x14ac:dyDescent="0.15">
@@ -12261,10 +12297,10 @@
         <v>100</v>
       </c>
       <c r="O153" s="4" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="P153" s="4" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="Q153" s="3" t="s">
         <v>231</v>
@@ -12276,10 +12312,10 @@
         <v>0</v>
       </c>
       <c r="X153" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y153" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="154" spans="1:25" x14ac:dyDescent="0.15">
@@ -12326,10 +12362,10 @@
         <v>100</v>
       </c>
       <c r="O154" s="4" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="P154" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="Q154" s="3" t="s">
         <v>231</v>
@@ -12341,10 +12377,10 @@
         <v>0</v>
       </c>
       <c r="X154" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y154" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="155" spans="1:25" x14ac:dyDescent="0.15">
@@ -12391,10 +12427,10 @@
         <v>100</v>
       </c>
       <c r="O155" s="4" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="P155" s="4" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="Q155" s="3" t="s">
         <v>231</v>
@@ -12406,10 +12442,10 @@
         <v>0</v>
       </c>
       <c r="X155" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y155" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="156" spans="1:25" x14ac:dyDescent="0.15">
@@ -12456,10 +12492,10 @@
         <v>100</v>
       </c>
       <c r="O156" s="4" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="P156" s="4" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="Q156" s="3" t="s">
         <v>231</v>
@@ -12471,10 +12507,10 @@
         <v>0</v>
       </c>
       <c r="X156" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y156" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="157" spans="1:25" x14ac:dyDescent="0.15">
@@ -12521,10 +12557,10 @@
         <v>100</v>
       </c>
       <c r="O157" s="4" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="P157" s="4" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="Q157" s="3" t="s">
         <v>231</v>
@@ -12536,10 +12572,10 @@
         <v>0</v>
       </c>
       <c r="X157" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y157" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="158" spans="1:25" x14ac:dyDescent="0.15">
@@ -12586,10 +12622,10 @@
         <v>100</v>
       </c>
       <c r="O158" s="4" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="P158" s="4" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="Q158" s="3" t="s">
         <v>231</v>
@@ -12601,10 +12637,10 @@
         <v>0</v>
       </c>
       <c r="X158" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y158" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="159" spans="1:25" x14ac:dyDescent="0.15">
@@ -12651,10 +12687,10 @@
         <v>100</v>
       </c>
       <c r="O159" s="4" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="P159" s="4" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="Q159" s="3" t="s">
         <v>231</v>
@@ -12666,10 +12702,10 @@
         <v>0</v>
       </c>
       <c r="X159" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y159" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="160" spans="1:25" x14ac:dyDescent="0.15">
@@ -12716,10 +12752,10 @@
         <v>100</v>
       </c>
       <c r="O160" s="4" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="P160" s="4" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="Q160" s="3" t="s">
         <v>231</v>
@@ -12731,10 +12767,10 @@
         <v>0</v>
       </c>
       <c r="X160" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y160" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="161" spans="1:25" x14ac:dyDescent="0.15">
@@ -12781,10 +12817,10 @@
         <v>100</v>
       </c>
       <c r="O161" s="4" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="P161" s="4" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="Q161" s="3" t="s">
         <v>231</v>
@@ -12796,10 +12832,10 @@
         <v>0</v>
       </c>
       <c r="X161" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y161" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="162" spans="1:25" x14ac:dyDescent="0.15">
@@ -12846,10 +12882,10 @@
         <v>100</v>
       </c>
       <c r="O162" s="4" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="P162" s="4" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="Q162" s="3" t="s">
         <v>231</v>
@@ -12861,10 +12897,10 @@
         <v>0</v>
       </c>
       <c r="X162" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y162" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="163" spans="1:25" x14ac:dyDescent="0.15">
@@ -12911,10 +12947,10 @@
         <v>100</v>
       </c>
       <c r="O163" s="4" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="P163" s="4" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="Q163" s="3" t="s">
         <v>231</v>
@@ -12926,10 +12962,10 @@
         <v>0</v>
       </c>
       <c r="X163" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y163" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="164" spans="1:25" x14ac:dyDescent="0.15">
@@ -12976,10 +13012,10 @@
         <v>100</v>
       </c>
       <c r="O164" s="4" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="P164" s="4" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="Q164" s="3" t="s">
         <v>231</v>
@@ -12991,10 +13027,10 @@
         <v>0</v>
       </c>
       <c r="X164" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y164" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DF15445-2D77-44A1-9990-F1D896158CD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFBA51C9-AC2F-4B49-A52C-788F37650148}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1935,18 +1935,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>310001:1102_0:100</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>310001:102_0:101</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>310001:12000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>310001:30_310002:600</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1963,6 +1951,18 @@
   </si>
   <si>
     <t>310001:20000_310002:20000_310003:20000</t>
+  </si>
+  <si>
+    <t>310001:12000_310002:12000_310003:12000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>310001:1102_310002:1102_310003:1102_0:100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>310001:102_310003:102_310003:102_0:101</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -4615,10 +4615,10 @@
         <v>1</v>
       </c>
       <c r="O35" s="4" t="s">
-        <v>600</v>
+        <v>606</v>
       </c>
       <c r="P35" s="4" t="s">
-        <v>601</v>
+        <v>607</v>
       </c>
       <c r="Q35" s="3" t="s">
         <v>231</v>
@@ -4627,25 +4627,25 @@
         <v>0</v>
       </c>
       <c r="S35" s="1" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="T35" s="1" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="U35" s="1" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="V35" s="1" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="W35" s="1" t="s">
         <v>588</v>
       </c>
       <c r="X35" s="3" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="Y35" s="3" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
     </row>
     <row r="36" spans="1:25" x14ac:dyDescent="0.15">

--- a/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFBA51C9-AC2F-4B49-A52C-788F37650148}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21EA32EC-BB45-43B5-973D-90D6EFDA1EEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_barries_v8" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1556" uniqueCount="608">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1556" uniqueCount="609">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1935,34 +1935,31 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>310001:30_310002:600</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>310001:35_310002:40_310003:50</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>310001:0_310002:0_310003:0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>310001:10000_310002:10000_310003:10000</t>
-  </si>
-  <si>
-    <t>310001:20000_310002:20000_310003:20000</t>
-  </si>
-  <si>
-    <t>310001:12000_310002:12000_310003:12000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>310001:1102_310002:1102_310003:1102_0:100</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>310001:102_310003:102_310003:102_0:101</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>300001:1102_300002:1102_300003:1102_0:100</t>
+  </si>
+  <si>
+    <t>300001:102_300003:102_300003:102_0:101</t>
+  </si>
+  <si>
+    <t>46200001,46800001,46900001,42761001,42761002,42761003,42761004,42761005,42761006,42761007,42761008,42761009,42761010,42761011,42761012,42761013,42761014,42761015,42761016,42761017,42761018,42761019,42761020,42761021,42761022,42761023,42761024,42761025,42761026,42761027,42761028,42761029,42761030,42761031,42761032,42761033,42761034,42761035,42761036,42761037,42761038,42761039,42761040,42761041,42761042,42761043,42761044,42761045,42761046,42761047,42761048,42761049,42761050,42761051,42761052,42761053,42761054,42761055,42761056,42761057,42761058,42761059,42761060,42761061,42761062,42761063,42761064,42761065,42761066,42761067,42761068,42761069,42761070,42761071,42761072,42761073,42761074,42761075,42761076,42761077,42761078,42761079,42761080,42761081,42761082,42761083,42761084,42761085,42761086,42761087,42761088,42761089,42761090,42761091,42761092,42761093,42761094,42761095,42761096,42761097,42761098,42761099,42761100,42761101,42761102,42761103,42761104,42761105,42761106,42761107,42761108,42761109,42761110,42761111,42761112,42761113,42761114,42761115,42761116,42761117,42761118,42761119,42761120,42761121,42761122,42761123,42761124,42761125,42761126,42761127,42761128,42761129,42761130,42761131,42761132,42761133,42761134,42761135,42761136,42761137,42761138,42761139,42761140,42761141,42761142,42761143,42761144,42761145,42761146,42761147,42761148,42761149,42761150,42761151,42761152,42761153,42761154,42761155,42761156,42761157,42761158,42761159,42761160,42662001,42662002,42662003,42662004,42662005,42662006,42662007,42662008,42662009,42662010,42662011,42662012,42662013,42662014,42662015,42662016,42662017,42662018,42662019,42662020,42662021,42662022,42662023,42662024,42662025,42662026,42662027,42662028,42662029,42662030,42662031,42662032,42662033,42662034,42662035,42662036,42662037,42662038,42662039,42662040,42662041,42662042,42662043,42662044,42662045,42662046,42662047,42662048,42662049,42662050,42662051,42662052,42662053,42662054,42662055,42662056,42662057,42662058,42662059,42662060,42662061,42662062,42662063,42662064,42662065,42662066,42662067,42662068,42662069,42662070,42662071,42662072,42662073,42662074,42662075,42662076,42662077,42662078,42662079,42662080,42662081,42662082,42662083,42662084,42662085,42662086,42662087,42662088,42662089,42662090,42662091,42662092,42662093,42662094,42662095,42662096,42662097,42662098,42662099,42662100,42662101,42662102,42662103,42662104,42662105,42662106,42662107,42662108,42662109,42662110,42662111,42662112,42662113,42662114,42662115,42662116,42662117,42662118,42662119,42662120,42662121,42662122,42662123,42662124,42662125,42662126,42662127,42662128,42662129,42662130,42662131,42662132,42662133,42662134,42662135,42662136,42662137,42662138,42662139,42662140,42662141,42662142,42662143,42662144,42662145,42662146,42662147,42662148,42662149,42662150,42662151,42662152,42662153,42662154,42662155,42662156,42662157,42662158,42662159,42662160,42663001,42663002,42663003,42663004,42663005,42663006,42663007,42663008,42663009,42663010,42663011,42663012,42663013,42663014,42663015,42663016,42663017,42663018,42663019,42663020,42663021,42663022,42663023,42663024,42663025,42663026,42663027,42663028,42663029,42663030,42663031,42663032,42663033,42663034,42663035,42663036,42663037,42663038,42663039,42663040,42663041,42663042,42663043,42663044,42663045,42663046,42663047,42663048,42663049,42663050,42663051,42663052,42663053,42663054,42663055,42663056,42663057,42663058,42663059,42663060,42663061,42663062,42663063,42663064,42663065,42663066,42663067,42663068,42663069,42663070,42663071,42663072,42663073,42663074,42663075,42663076,42663077,42663078,42663079,42663080,42663081,42663082,42663083,42663084,42663085,42663086,42663087,42663088,42663089,42663090,42663091,42663092,42663093,42663094,42663095,42663096,42663097,42663098,42663099,42663000,42663101,42663102,42663103,42663104,42663105,42663106,42663107,42663108,42663109,42663110,42663111,42663112,42663113,42663114,42663115,42663116,42663117,42663118,42663119,42663120,42663121,42663122,42663123,42663124,42663125,42663126,42663127,42663128,42663129,42663130,42663131,42663132,42663133,42663134,42663135,42663136,42663137,42663138,42663139,42663140,42663141,42663142,42663143,42663144,42663145,42663146,42663147,42663148,42663149,42663150,42663151,42663152,42663153,42663154,42663155,42663156,42663157,42663158,42663159,42663160,42666001,42666002,42666003,42666004,42666005,42666006,42666007,42666008,42666009,42666010,42666011,42666012,42666013,42666014,42666015,42666016,42666017,42666018,42666019,42666020,42666021,42666022,42666023,42666024,42666025,42666026,42666027,42666028,42666029,42666030,42666031,42666032,42666033,42666034,42666035,42666036,42666037,42666038,42666039,42666040,42666041,42666042,42666043,42666044,42666045,42666046,42666047,42666048,42666049,42666050,42666051,42666052,42666053,42666054,42666055,42666056,42666057,42666058,42666059,42666060,42666061,42666062,42666063,42666064,42666065,42666066,42666067,42666068,42666069,42666070,42666071,42666072,42666073,42666074,42666075,42666076,42666077,42666078,42666079,42666080,42666081,42666082,42666083,42666084,42666085,42666086,42666087,42666088,42666089,42666090,42666091,42666092,42666093,42666094,42666095,42666096,42666097,42666098,42666099,42666100,42666101,42666102,42666103,42666104,42666105,42666106,42666107,42666108,42666109,42666110,42666111,42666112,42666113,42666114,42666115,42666116,42666117,42666118,42666119,42666120,42666121,42666122,42666123,42666124,42666125,42666126,42666127,42666128,42666129,42666130,42666131,42666132,42666133,42666134,42666135,42666136,42666137,42666138,42666139,42666140,42666141,42666142,42666143,42666144,42666145,42666146,42666147,42666148,42666149,42666150,42666151,42666152,42666153,42666154,42666155,42666156,42666157,42666158,42666159,42666160,42664001,42664002,42664003,42664004,42664005,42664006,42664007,42664008,42664009,42664010,42664011,42664012,42664013,42664014,42664015,42664016,42664017,42664018,42664019,42664020,42664021,42664022,42664023,42664024,42664025,42664026,42664027,42664028,42664029,42664030,42664031,42664032,42664033,42664034,42664035,42664036,42664037,42664038,42664039,42664040,42664041,42664042,42664043,42664044,42664045,42664046,42664047,42664048,42664049,42664050,42664051,42664052,42664053,42664054,42664055,42664056,42664057,42664058,42664059,42664060,42664061,42664062,42664063,42664064,42664065,42664066,42664067,42664068,42664069,42664070,42664071,42664072,42664073,42664074,42664075,42664076,42664077,42664078,42664079,42664080,42664081,42664082,42664083,42664084,42664085,42664086,42664087,42664088,42664089,42664090,42664091,42664092,42664093,42664094,42664095,42664096,42664097,42664098,42664099,42664100,42664101,42664102,42664103,42664104,42664105,42664106,42664107,42664108,42664109,42664110,42664111,42664112,42664113,42664114,42664115,42664116,42664117,42664118,42664119,42664120,42664121,42664122,42664123,42664124,42664125,42664126,42664127,42664128,42664129,42664130,42664131,42664132,42664133,42664134,42664135,42664136,42664137,42664138,42664139,42664140,42664141,42664142,42664143,42664144,42664145,42664146,42664147,42664148,42664149,42664150,42664151,42664152,42664153,42664154,42664155,42664156,42664157,42664158,42664159,42664160,42665001,42665002,42665003,42665004,42665005,42665006,42665007,42665008,42665009,42665010,42665011,42665012,42665013,42665014,42665015,42665016,42665017,42665018,42665019,42665020,42665021,42665022,42665023,42665024,42665025,42665026,42665027,42665028,42665029,42665030,42665031,42665032,42665033,42665034,42665035,42665036,42665037,42665038,42665039,42665040,42665041,42665042,42665043,42665044,42665045,42665046,42665047,42665048,42665049,42665050,42665051,42665052,42665053,42665054,42665055,42665056,42665057,42665058,42665059,42665060,42665061,42665062,42665063,42665064,42665065,42665066,42665067,42665068,42665069,42665070,42665071,42665072,42665073,42665074,42665075,42665076,42665077,42665078,42665079,42665080,42665081,42665082,42665083,42665084,42665085,42665086,42665087,42665088,42665089,42665090,42665091,42665092,42665093,42665094,42665095,42665096,42665097,42665098,42665099,42665100,42665101,42665102,42665103,42665104,42665105,42665106,42665107,42665108,42665109,42665110,42665111,42665112,42665113,42665114,42665115,42665116,42665117,42665118,42665119,42665120,42665121,42665122,42665123,42665124,42665125,42665126,42665127,42665128,42665129,42665130,42665131,42665132,42665133,42665134,42665135,42665136,42665137,42665138,42665139,42665140,42665141,42665142,42665143,42665144,42665145,42665146,42665147,42665148,42665149,42665150,42665151,42665152,42665153,42665154,42665155,42665156,42665157,42665158,42665159,42665160,42667001,42667002,42667003,42667004,42667005,42667006,42667007,42667008,42667009,42667010,42667011,42667012,42667013,42667014,42667015,42667016,42667017,42667018,42667019,42667020,42667021,42667022,42667023,42667024,42667025,42667026,42667027,42667028,42667029,42667030,42667031,42667032,42667033,42667034,42667035,42667036,42667037,42667038,42667039,42667040,42667041,42667042,42667043,42667044,42667045,42667046,42667047,42667048,42667049,42667050,42667051,42667052,42667053,42667054,42667055,42667056,42667057,42667058,42667059,42667060,42667061,42667062,42667063,42667064,42667065,42667066,42667067,42667068,42667069,42667070,42667071,42667072,42667073,42667074,42667075,42667076,42667077,42667078,42667079,42667080,42667081,42667082,42667083,42667084,42667085,42667086,42667087,42667088,42667089,42667090,42667091,42667092,42667093,42667094,42667095,42667096,42667097,42667098,42667099,42667100,42667101,42667102,42667103,42667104,42667105,42667106,42667107,42667108,42667109,42667110,42667111,42667112,42667113,42667114,42667115,42667116,42667117,42667118,42667119,42667120,42667121,42667122,42667123,42667124,42667125,42667126,42667127,42667128,42667129,42667130,42667131,42667132,42667133,42667134,42667135,42667136,42667137,42667138,42667139,42667140,42667141,42667142,42667143,42667144,42667145,42667146,42667147,42667148,42667149,42667150,42667151,42667152,42667153,42667154,42667155,42667156,42667157,42667158,42667159,42667160,42668001,42668002,42668003,42668004,42668005,42668006,42668007,42668008,42668009,42668010,42668011,42668012,42668013,42668014,42668015,42668016,42668017,42668018,42668019,42668020,42668021,42668022,42668023,42668024,42668025,42668026,42668027,42668028,42668029,42668030,42668031,42668032,42668033,42668034,42668035,42668036,42668037,42668038,42668039,42668040,42668041,42668042,42668043,42668044,42668045,42668046,42668047,42668048,42668049,42668050,42668051,42668052,42668053,42668054,42668055,42668056,42668057,42668058,42668059,42668060,42668061,42668062,42668063,42668064,42668065,42668066,42668067,42668068,42668069,42668070,42668071,42668072,42668073,42668074,42668075,42668076,42668077,42668078,42668079,42668080,42668081,42668082,42668083,42668084,42668085,42668086,42668087,42668088,42668089,42668090,42668091,42668092,42668093,42668094,42668095,42668096,42668097,42668098,42668099,42668100,42668101,42668102,42668103,42668104,42668105,42668106,42668107,42668108,42668109,42668110,42668111,42668112,42668113,42668114,42668115,42668116,42668117,42668118,42668119,42668120,42668121,42668122,42668123,42668124,42668125,42668126,42668127,42668128,42668129,42668130,42668131,42668132,42668133,42668134,42668135,42668136,42668137,42668138,42668139,42668140,42668141,42668142,42668143,42668144,42668145,42668146,42668147,42668148,42668149,42668150,42668151,42668152,42668153,42668154,42668155,42668156,42668157,42668158,42668159,42668160,42781001,42781002,42781003,42781004,42781005,42781006,42781007,42781008,42781009,42781010,42781011,42781012,42781013,42781014,42781015,42781016,42781017,42781018,42781019,42781020,42781021,42781022,42781023,42781024,42781025,42781026,42781027,42781028,42781029,42781030,42781031,42781032,42781033,42781034,42781035,42781036,42781037,42781038,42781039,42781040,42781041,42781042,42781043,42781044,42781045,42781046,42781047,42781048,42781049,42781050,42781051,42781052,42781053,42781054,42781055,42781056,42781057,42781058,42781059,42781060,42781061,42781062,42781063,42781064,42781065,42781066,42781067,42781068,42781069,42781070,42781071,42781072,42781073,42781074,42781075,42781076,42781077,42781078,42781079,42781080,42781081,42781082,42781083,42781084,42781085,42781086,42781087,42781088,42781089,42781090,42781091,42781092,42781093,42781094,42781095,42781096,42781097,42781098,42781099,42781100,42781101,42781102,42781103,42781104,42781105,42781106,42781107,42781108,42781109,42781110,42781111,42781112,42781113,42781114,42781115,42781116,42781117,42781118,42781119,42781120,42781121,42781122,42781123,42781124,42781125,42781126,42781127,42781128,42781129,42781130,42781131,42781132,42781133,42781134,42781135,42781136,42781137,42781138,42781139,42781140,42781141,42781142,42781143,42781144,42781145,42781146,42781147,42781148,42781149,42781150,42781151,42781152,42781153,42781154,42781155,42781156,42781157,42781158,42781159,42781160,42682001,42682002,42682003,42682004,42682005,42682006,42682007,42682008,42682009,42682010,42682011,42682012,42682013,42682014,42682015,42682016,42682017,42682018,42682019,42682020,42682021,42682022,42682023,42682024,42682025,42682026,42682027,42682028,42682029,42682030,42682031,42682032,42682033,42682034,42682035,42682036,42682037,42682038,42682039,42682040,42682041,42682042,42682043,42682044,42682045,42682046,42682047,42682048,42682049,42682050,42682051,42682052,42682053,42682054,42682055,42682056,42682057,42682058,42682059,42682060,42682061,42682062,42682063,42682064,42682065,42682066,42682067,42682068,42682069,42682070,42682071,42682072,42682073,42682074,42682075,42682076,42682077,42682078,42682079,42682080,42682081,42682082,42682083,42682084,42682085,42682086,42682087,42682088,42682089,42682090,42682091,42682092,42682093,42682094,42682095,42682096,42682097,42682098,42682099,42682100,42682101,42682102,42682103,42682104,42682105,42682106,42682107,42682108,42682109,42682110,42682111,42682112,42682113,42682114,42682115,42682116,42682117,42682118,42682119,42682120,42682121,42682122,42682123,42682124,42682125,42682126,42682127,42682128,42682129,42682130,42682131,42682132,42682133,42682134,42682135,42682136,42682137,42682138,42682139,42682140,42682141,42682142,42682143,42682144,42682145,42682146,42682147,42682148,42682149,42682150,42682151,42682152,42682153,42682154,42682155,42682156,42682157,42682158,42682159,42682160,42683001,42683002,42683003,42683004,42683005,42683006,42683007,42683008,42683009,42683010,42683011,42683012,42683013,42683014,42683015,42683016,42683017,42683018,42683019,42683020,42683021,42683022,42683023,42683024,42683025,42683026,42683027,42683028,42683029,42683030,42683031,42683032,42683033,42683034,42683035,42683036,42683037,42683038,42683039,42683040,42683041,42683042,42683043,42683044,42683045,42683046,42683047,42683048,42683049,42683050,42683051,42683052,42683053,42683054,42683055,42683056,42683057,42683058,42683059,42683060,42683061,42683062,42683063,42683064,42683065,42683066,42683067,42683068,42683069,42683070,42683071,42683072,42683073,42683074,42683075,42683076,42683077,42683078,42683079,42683080,42683081,42683082,42683083,42683084,42683085,42683086,42683087,42683088,42683089,42683090,42683091,42683092,42683093,42683094,42683095,42683096,42683097,42683098,42683099,42683000,42683101,42683102,42683103,42683104,42683105,42683106,42683107,42683108,42683109,42683110,42683111,42683112,42683113,42683114,42683115,42683116,42683117,42683118,42683119,42683120,42683121,42683122,42683123,42683124,42683125,42683126,42683127,42683128,42683129,42683130,42683131,42683132,42683133,42683134,42683135,42683136,42683137,42683138,42683139,42683140,42683141,42683142,42683143,42683144,42683145,42683146,42683147,42683148,42683149,42683150,42683151,42683152,42683153,42683154,42683155,42683156,42683157,42683158,42683159,42683160,42686001,42686002,42686003,42686004,42686005,42686006,42686007,42686008,42686009,42686010,42686011,42686012,42686013,42686014,42686015,42686016,42686017,42686018,42686019,42686020,42686021,42686022,42686023,42686024,42686025,42686026,42686027,42686028,42686029,42686030,42686031,42686032,42686033,42686034,42686035,42686036,42686037,42686038,42686039,42686040,42686041,42686042,42686043,42686044,42686045,42686046,42686047,42686048,42686049,42686050,42686051,42686052,42686053,42686054,42686055,42686056,42686057,42686058,42686059,42686060,42686061,42686062,42686063,42686064,42686065,42686066,42686067,42686068,42686069,42686070,42686071,42686072,42686073,42686074,42686075,42686076,42686077,42686078,42686079,42686080,42686081,42686082,42686083,42686084,42686085,42686086,42686087,42686088,42686089,42686090,42686091,42686092,42686093,42686094,42686095,42686096,42686097,42686098,42686099,42686100,42686101,42686102,42686103,42686104,42686105,42686106,42686107,42686108,42686109,42686110,42686111,42686112,42686113,42686114,42686115,42686116,42686117,42686118,42686119,42686120,42686121,42686122,42686123,42686124,42686125,42686126,42686127,42686128,42686129,42686130,42686131,42686132,42686133,42686134,42686135,42686136,42686137,42686138,42686139,42686140,42686141,42686142,42686143,42686144,42686145,42686146,42686147,42686148,42686149,42686150,42686151,42686152,42686153,42686154,42686155,42686156,42686157,42686158,42686159,42686160,42684001,42684002,42684003,42684004,42684005,42684006,42684007,42684008,42684009,42684010,42684011,42684012,42684013,42684014,42684015,42684016,42684017,42684018,42684019,42684020,42684021,42684022,42684023,42684024,42684025,42684026,42684027,42684028,42684029,42684030,42684031,42684032,42684033,42684034,42684035,42684036,42684037,42684038,42684039,42684040,42684041,42684042,42684043,42684044,42684045,42684046,42684047,42684048,42684049,42684050,42684051,42684052,42684053,42684054,42684055,42684056,42684057,42684058,42684059,42684060,42684061,42684062,42684063,42684064,42684065,42684066,42684067,42684068,42684069,42684070,42684071,42684072,42684073,42684074,42684075,42684076,42684077,42684078,42684079,42684080,42684081,42684082,42684083,42684084,42684085,42684086,42684087,42684088,42684089,42684090,42684091,42684092,42684093,42684094,42684095,42684096,42684097,42684098,42684099,42684100,42684101,42684102,42684103,42684104,42684105,42684106,42684107,42684108,42684109,42684110,42684111,42684112,42684113,42684114,42684115,42684116,42684117,42684118,42684119,42684120,42684121,42684122,42684123,42684124,42684125,42684126,42684127,42684128,42684129,42684130,42684131,42684132,42684133,42684134,42684135,42684136,42684137,42684138,42684139,42684140,42684141,42684142,42684143,42684144,42684145,42684146,42684147,42684148,42684149,42684150,42684151,42684152,42684153,42684154,42684155,42684156,42684157,42684158,42684159,42684160,42685001,42685002,42685003,42685004,42685005,42685006,42685007,42685008,42685009,42685010,42685011,42685012,42685013,42685014,42685015,42685016,42685017,42685018,42685019,42685020,42685021,42685022,42685023,42685024,42685025,42685026,42685027,42685028,42685029,42685030,42685031,42685032,42685033,42685034,42685035,42685036,42685037,42685038,42685039,42685040,42685041,42685042,42685043,42685044,42685045,42685046,42685047,42685048,42685049,42685050,42685051,42685052,42685053,42685054,42685055,42685056,42685057,42685058,42685059,42685060,42685061,42685062,42685063,42685064,42685065,42685066,42685067,42685068,42685069,42685070,42685071,42685072,42685073,42685074,42685075,42685076,42685077,42685078,42685079,42685080,42685081,42685082,42685083,42685084,42685085,42685086,42685087,42685088,42685089,42685090,42685091,42685092,42685093,42685094,42685095,42685096,42685097,42685098,42685099,42685100,42685101,42685102,42685103,42685104,42685105,42685106,42685107,42685108,42685109,42685110,42685111,42685112,42685113,42685114,42685115,42685116,42685117,42685118,42685119,42685120,42685121,42685122,42685123,42685124,42685125,42685126,42685127,42685128,42685129,42685130,42685131,42685132,42685133,42685134,42685135,42685136,42685137,42685138,42685139,42685140,42685141,42685142,42685143,42685144,42685145,42685146,42685147,42685148,42685149,42685150,42685151,42685152,42685153,42685154,42685155,42685156,42685157,42685158,42685159,42685160,42687001,42687002,42687003,42687004,42687005,42687006,42687007,42687008,42687009,42687010,42687011,42687012,42687013,42687014,42687015,42687016,42687017,42687018,42687019,42687020,42687021,42687022,42687023,42687024,42687025,42687026,42687027,42687028,42687029,42687030,42687031,42687032,42687033,42687034,42687035,42687036,42687037,42687038,42687039,42687040,42687041,42687042,42687043,42687044,42687045,42687046,42687047,42687048,42687049,42687050,42687051,42687052,42687053,42687054,42687055,42687056,42687057,42687058,42687059,42687060,42687061,42687062,42687063,42687064,42687065,42687066,42687067,42687068,42687069,42687070,42687071,42687072,42687073,42687074,42687075,42687076,42687077,42687078,42687079,42687080,42687081,42687082,42687083,42687084,42687085,42687086,42687087,42687088,42687089,42687090,42687091,42687092,42687093,42687094,42687095,42687096,42687097,42687098,42687099,42687100,42687101,42687102,42687103,42687104,42687105,42687106,42687107,42687108,42687109,42687110,42687111,42687112,42687113,42687114,42687115,42687116,42687117,42687118,42687119,42687120,42687121,42687122,42687123,42687124,42687125,42687126,42687127,42687128,42687129,42687130,42687131,42687132,42687133,42687134,42687135,42687136,42687137,42687138,42687139,42687140,42687141,42687142,42687143,42687144,42687145,42687146,42687147,42687148,42687149,42687150,42687151,42687152,42687153,42687154,42687155,42687156,42687157,42687158,42687159,42687160,42688001,42688002,42688003,42688004,42688005,42688006,42688007,42688008,42688009,42688010,42688011,42688012,42688013,42688014,42688015,42688016,42688017,42688018,42688019,42688020,42688021,42688022,42688023,42688024,42688025,42688026,42688027,42688028,42688029,42688030,42688031,42688032,42688033,42688034,42688035,42688036,42688037,42688038,42688039,42688040,42688041,42688042,42688043,42688044,42688045,42688046,42688047,42688048,42688049,42688050,42688051,42688052,42688053,42688054,42688055,42688056,42688057,42688058,42688059,42688060,42688061,42688062,42688063,42688064,42688065,42688066,42688067,42688068,42688069,42688070,42688071,42688072,42688073,42688074,42688075,42688076,42688077,42688078,42688079,42688080,42688081,42688082,42688083,42688084,42688085,42688086,42688087,42688088,42688089,42688090,42688091,42688092,42688093,42688094,42688095,42688096,42688097,42688098,42688099,42688100,42688101,42688102,42688103,42688104,42688105,42688106,42688107,42688108,42688109,42688110,42688111,42688112,42688113,42688114,42688115,42688116,42688117,42688118,42688119,42688120,42688121,42688122,42688123,42688124,42688125,42688126,42688127,42688128,42688129,42688130,42688131,42688132,42688133,42688134,42688135,42688136,42688137,42688138,42688139,42688140,42688141,42688142,42688143,42688144,42688145,42688146,42688147,42688148,42688149,42688150,42688151,42688152,42688153,42688154,42688155,42688156,42688157,42688158,42688159,42688160</t>
+  </si>
+  <si>
+    <t>300001:0_300002:0_300003:0</t>
+  </si>
+  <si>
+    <t>300001:10000_300002:10000_300003:10000</t>
+  </si>
+  <si>
+    <t>300001:20000_300002:20000_300003:20000</t>
+  </si>
+  <si>
+    <t>300001:35_300002:40_300003:50</t>
+  </si>
+  <si>
+    <t>300001:30_300002:600</t>
+  </si>
+  <si>
+    <t>300001:12000_300002:12000_300003:12000</t>
   </si>
 </sst>
 </file>
@@ -4615,37 +4612,37 @@
         <v>1</v>
       </c>
       <c r="O35" s="4" t="s">
+        <v>600</v>
+      </c>
+      <c r="P35" s="4" t="s">
+        <v>601</v>
+      </c>
+      <c r="Q35" s="3" t="s">
+        <v>602</v>
+      </c>
+      <c r="R35" s="1">
+        <v>0</v>
+      </c>
+      <c r="S35" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="T35" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="U35" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="V35" s="1" t="s">
         <v>606</v>
-      </c>
-      <c r="P35" s="4" t="s">
-        <v>607</v>
-      </c>
-      <c r="Q35" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="R35" s="1">
-        <v>0</v>
-      </c>
-      <c r="S35" s="1" t="s">
-        <v>602</v>
-      </c>
-      <c r="T35" s="1" t="s">
-        <v>603</v>
-      </c>
-      <c r="U35" s="1" t="s">
-        <v>604</v>
-      </c>
-      <c r="V35" s="1" t="s">
-        <v>601</v>
       </c>
       <c r="W35" s="1" t="s">
         <v>588</v>
       </c>
       <c r="X35" s="3" t="s">
-        <v>600</v>
+        <v>607</v>
       </c>
       <c r="Y35" s="3" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
     </row>
     <row r="36" spans="1:25" x14ac:dyDescent="0.15">

--- a/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21EA32EC-BB45-43B5-973D-90D6EFDA1EEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42B384AE-0119-4069-9446-61815DF5E3D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1556" uniqueCount="609">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1559" uniqueCount="607">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -942,12 +942,6 @@
   </si>
   <si>
     <t>290001:101_0:101</t>
-  </si>
-  <si>
-    <t>320001:100_0:100</t>
-  </si>
-  <si>
-    <t>320001:101_0:101</t>
   </si>
   <si>
     <t>330001:100_0:100</t>
@@ -2401,10 +2395,10 @@
         <v>205</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.15">
@@ -2472,16 +2466,16 @@
         <v>245</v>
       </c>
       <c r="V3" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="W3" s="5" t="s">
         <v>572</v>
       </c>
-      <c r="W3" s="5" t="s">
-        <v>574</v>
-      </c>
       <c r="X3" s="1" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Y3" s="1" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.15">
@@ -2549,16 +2543,16 @@
         <v>242</v>
       </c>
       <c r="V4" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="W4" s="1" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="X4" s="1" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="Y4" s="1" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.15">
@@ -2605,10 +2599,10 @@
         <v>150</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="Q5" s="3" t="s">
         <v>231</v>
@@ -2620,22 +2614,22 @@
         <v>247</v>
       </c>
       <c r="T5" s="1" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="U5" s="1" t="s">
         <v>248</v>
       </c>
       <c r="V5" s="1" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="W5" s="1">
         <v>0</v>
       </c>
       <c r="X5" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y5" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.15">
@@ -2682,10 +2676,10 @@
         <v>200</v>
       </c>
       <c r="O6" s="4" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="P6" s="4" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="Q6" s="3" t="s">
         <v>231</v>
@@ -2697,10 +2691,10 @@
         <v>0</v>
       </c>
       <c r="X6" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y6" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.15">
@@ -2747,10 +2741,10 @@
         <v>300</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="P7" s="4" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="Q7" s="3" t="s">
         <v>231</v>
@@ -2762,10 +2756,10 @@
         <v>0</v>
       </c>
       <c r="X7" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y7" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.15">
@@ -2812,10 +2806,10 @@
         <v>400</v>
       </c>
       <c r="O8" s="4" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="P8" s="4" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="Q8" s="3" t="s">
         <v>231</v>
@@ -2827,10 +2821,10 @@
         <v>0</v>
       </c>
       <c r="X8" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y8" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.15">
@@ -2877,10 +2871,10 @@
         <v>500</v>
       </c>
       <c r="O9" s="4" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="P9" s="4" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="Q9" s="3" t="s">
         <v>231</v>
@@ -2892,10 +2886,10 @@
         <v>0</v>
       </c>
       <c r="X9" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y9" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.15">
@@ -2942,10 +2936,10 @@
         <v>600</v>
       </c>
       <c r="O10" s="4" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="P10" s="4" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="Q10" s="3" t="s">
         <v>231</v>
@@ -2957,10 +2951,10 @@
         <v>0</v>
       </c>
       <c r="X10" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y10" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.15">
@@ -3007,10 +3001,10 @@
         <v>100</v>
       </c>
       <c r="O11" s="4" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="P11" s="4" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="Q11" s="3" t="s">
         <v>231</v>
@@ -3022,10 +3016,10 @@
         <v>0</v>
       </c>
       <c r="X11" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y11" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.15">
@@ -3072,10 +3066,10 @@
         <v>100</v>
       </c>
       <c r="O12" s="4" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="P12" s="4" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="Q12" s="3" t="s">
         <v>231</v>
@@ -3087,10 +3081,10 @@
         <v>0</v>
       </c>
       <c r="X12" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y12" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.15">
@@ -3137,10 +3131,10 @@
         <v>100</v>
       </c>
       <c r="O13" s="4" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="P13" s="4" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="Q13" s="3" t="s">
         <v>231</v>
@@ -3152,10 +3146,10 @@
         <v>0</v>
       </c>
       <c r="X13" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y13" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="14" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -3202,10 +3196,10 @@
         <v>100</v>
       </c>
       <c r="O14" s="4" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="P14" s="4" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>231</v>
@@ -3217,10 +3211,10 @@
         <v>0</v>
       </c>
       <c r="X14" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y14" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.15">
@@ -3267,10 +3261,10 @@
         <v>100</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Q15" s="3" t="s">
         <v>231</v>
@@ -3279,22 +3273,22 @@
         <v>0</v>
       </c>
       <c r="S15" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="T15" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="U15" s="1" t="s">
         <v>559</v>
       </c>
-      <c r="T15" s="1" t="s">
-        <v>560</v>
-      </c>
-      <c r="U15" s="1" t="s">
-        <v>561</v>
-      </c>
       <c r="W15" s="1" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="X15" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y15" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.15">
@@ -3341,10 +3335,10 @@
         <v>100</v>
       </c>
       <c r="O16" s="4" t="s">
+        <v>560</v>
+      </c>
+      <c r="P16" s="4" t="s">
         <v>562</v>
-      </c>
-      <c r="P16" s="4" t="s">
-        <v>564</v>
       </c>
       <c r="Q16" s="3" t="s">
         <v>231</v>
@@ -3353,25 +3347,25 @@
         <v>0</v>
       </c>
       <c r="S16" s="1" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="T16" s="1" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="U16" s="1" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="V16" s="1" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="W16" s="1">
         <v>0</v>
       </c>
       <c r="X16" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y16" s="1" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
     </row>
     <row r="17" spans="1:25" x14ac:dyDescent="0.15">
@@ -3433,10 +3427,10 @@
         <v>0</v>
       </c>
       <c r="X17" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y17" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="18" spans="1:25" x14ac:dyDescent="0.15">
@@ -3498,10 +3492,10 @@
         <v>0</v>
       </c>
       <c r="X18" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y18" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="19" spans="1:25" x14ac:dyDescent="0.15">
@@ -3563,10 +3557,10 @@
         <v>0</v>
       </c>
       <c r="X19" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y19" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="20" spans="1:25" x14ac:dyDescent="0.15">
@@ -3628,10 +3622,10 @@
         <v>0</v>
       </c>
       <c r="X20" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y20" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="21" spans="1:25" x14ac:dyDescent="0.15">
@@ -3693,10 +3687,10 @@
         <v>0</v>
       </c>
       <c r="X21" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y21" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="22" spans="1:25" x14ac:dyDescent="0.15">
@@ -3758,10 +3752,10 @@
         <v>0</v>
       </c>
       <c r="X22" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y22" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="23" spans="1:25" x14ac:dyDescent="0.15">
@@ -3823,10 +3817,10 @@
         <v>0</v>
       </c>
       <c r="X23" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y23" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="24" spans="1:25" x14ac:dyDescent="0.15">
@@ -3888,10 +3882,10 @@
         <v>0</v>
       </c>
       <c r="X24" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y24" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="25" spans="1:25" x14ac:dyDescent="0.15">
@@ -3938,10 +3932,10 @@
         <v>100</v>
       </c>
       <c r="O25" s="4" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="P25" s="4" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="Q25" s="3" t="s">
         <v>231</v>
@@ -3950,25 +3944,25 @@
         <v>0</v>
       </c>
       <c r="S25" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="T25" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="U25" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="T25" s="1" t="s">
+      <c r="V25" s="1" t="s">
         <v>580</v>
       </c>
-      <c r="U25" s="1" t="s">
-        <v>581</v>
-      </c>
-      <c r="V25" s="1" t="s">
-        <v>582</v>
-      </c>
       <c r="W25" s="1">
         <v>0</v>
       </c>
       <c r="X25" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y25" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="26" spans="1:25" x14ac:dyDescent="0.15">
@@ -4030,10 +4024,10 @@
         <v>0</v>
       </c>
       <c r="X26" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y26" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="27" spans="1:25" x14ac:dyDescent="0.15">
@@ -4095,10 +4089,10 @@
         <v>0</v>
       </c>
       <c r="X27" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y27" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="28" spans="1:25" x14ac:dyDescent="0.15">
@@ -4160,10 +4154,10 @@
         <v>0</v>
       </c>
       <c r="X28" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y28" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="29" spans="1:25" x14ac:dyDescent="0.15">
@@ -4225,10 +4219,10 @@
         <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y29" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="30" spans="1:25" x14ac:dyDescent="0.15">
@@ -4290,10 +4284,10 @@
         <v>0</v>
       </c>
       <c r="X30" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y30" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="31" spans="1:25" x14ac:dyDescent="0.15">
@@ -4355,10 +4349,10 @@
         <v>0</v>
       </c>
       <c r="X31" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y31" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="32" spans="1:25" x14ac:dyDescent="0.15">
@@ -4420,10 +4414,10 @@
         <v>0</v>
       </c>
       <c r="X32" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y32" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="33" spans="1:25" x14ac:dyDescent="0.15">
@@ -4485,10 +4479,10 @@
         <v>0</v>
       </c>
       <c r="X33" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y33" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="34" spans="1:25" x14ac:dyDescent="0.15">
@@ -4535,10 +4529,10 @@
         <v>1</v>
       </c>
       <c r="O34" s="4" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="P34" s="4" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="Q34" s="3" t="s">
         <v>231</v>
@@ -4547,25 +4541,25 @@
         <v>0</v>
       </c>
       <c r="S34" s="1" t="s">
+        <v>593</v>
+      </c>
+      <c r="T34" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="U34" s="1" t="s">
         <v>595</v>
       </c>
-      <c r="T34" s="1" t="s">
+      <c r="V34" s="1" t="s">
         <v>596</v>
       </c>
-      <c r="U34" s="1" t="s">
+      <c r="W34" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="X34" s="3" t="s">
+        <v>587</v>
+      </c>
+      <c r="Y34" s="3" t="s">
         <v>597</v>
-      </c>
-      <c r="V34" s="1" t="s">
-        <v>598</v>
-      </c>
-      <c r="W34" s="1" t="s">
-        <v>588</v>
-      </c>
-      <c r="X34" s="3" t="s">
-        <v>589</v>
-      </c>
-      <c r="Y34" s="3" t="s">
-        <v>599</v>
       </c>
     </row>
     <row r="35" spans="1:25" x14ac:dyDescent="0.15">
@@ -4612,37 +4606,37 @@
         <v>1</v>
       </c>
       <c r="O35" s="4" t="s">
+        <v>598</v>
+      </c>
+      <c r="P35" s="4" t="s">
+        <v>599</v>
+      </c>
+      <c r="Q35" s="3" t="s">
         <v>600</v>
       </c>
-      <c r="P35" s="4" t="s">
+      <c r="R35" s="1">
+        <v>0</v>
+      </c>
+      <c r="S35" s="1" t="s">
         <v>601</v>
       </c>
-      <c r="Q35" s="3" t="s">
+      <c r="T35" s="1" t="s">
         <v>602</v>
       </c>
-      <c r="R35" s="1">
-        <v>0</v>
-      </c>
-      <c r="S35" s="1" t="s">
+      <c r="U35" s="1" t="s">
         <v>603</v>
       </c>
-      <c r="T35" s="1" t="s">
+      <c r="V35" s="1" t="s">
         <v>604</v>
       </c>
-      <c r="U35" s="1" t="s">
+      <c r="W35" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="X35" s="3" t="s">
         <v>605</v>
       </c>
-      <c r="V35" s="1" t="s">
+      <c r="Y35" s="3" t="s">
         <v>606</v>
-      </c>
-      <c r="W35" s="1" t="s">
-        <v>588</v>
-      </c>
-      <c r="X35" s="3" t="s">
-        <v>607</v>
-      </c>
-      <c r="Y35" s="3" t="s">
-        <v>608</v>
       </c>
     </row>
     <row r="36" spans="1:25" x14ac:dyDescent="0.15">
@@ -4667,8 +4661,8 @@
       <c r="G36" s="1">
         <v>43400002</v>
       </c>
-      <c r="H36" s="1" t="s">
-        <v>202</v>
+      <c r="H36" s="1">
+        <v>0</v>
       </c>
       <c r="I36" s="1">
         <v>1</v>
@@ -4686,28 +4680,40 @@
         <v>215</v>
       </c>
       <c r="N36" s="1">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="O36" s="4" t="s">
-        <v>282</v>
+        <v>598</v>
       </c>
       <c r="P36" s="4" t="s">
-        <v>283</v>
+        <v>599</v>
       </c>
       <c r="Q36" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="R36" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="W36" s="1">
-        <v>0</v>
+      <c r="R36" s="1">
+        <v>0</v>
+      </c>
+      <c r="S36" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="T36" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="U36" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="V36" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="W36" s="1" t="s">
+        <v>586</v>
       </c>
       <c r="X36" s="3" t="s">
-        <v>584</v>
+        <v>605</v>
       </c>
       <c r="Y36" s="3" t="s">
-        <v>584</v>
+        <v>606</v>
       </c>
     </row>
     <row r="37" spans="1:25" x14ac:dyDescent="0.15">
@@ -4754,10 +4760,10 @@
         <v>100</v>
       </c>
       <c r="O37" s="4" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="P37" s="4" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="Q37" s="3" t="s">
         <v>231</v>
@@ -4769,10 +4775,10 @@
         <v>0</v>
       </c>
       <c r="X37" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y37" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="38" spans="1:25" x14ac:dyDescent="0.15">
@@ -4819,10 +4825,10 @@
         <v>100</v>
       </c>
       <c r="O38" s="4" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="P38" s="4" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="Q38" s="3" t="s">
         <v>231</v>
@@ -4834,10 +4840,10 @@
         <v>0</v>
       </c>
       <c r="X38" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y38" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="39" spans="1:25" x14ac:dyDescent="0.15">
@@ -4884,10 +4890,10 @@
         <v>100</v>
       </c>
       <c r="O39" s="4" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="P39" s="4" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="Q39" s="3" t="s">
         <v>231</v>
@@ -4899,10 +4905,10 @@
         <v>0</v>
       </c>
       <c r="X39" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y39" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="40" spans="1:25" x14ac:dyDescent="0.15">
@@ -4949,10 +4955,10 @@
         <v>100</v>
       </c>
       <c r="O40" s="4" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="P40" s="4" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="Q40" s="3" t="s">
         <v>231</v>
@@ -4964,10 +4970,10 @@
         <v>0</v>
       </c>
       <c r="X40" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y40" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="41" spans="1:25" x14ac:dyDescent="0.15">
@@ -5014,10 +5020,10 @@
         <v>100</v>
       </c>
       <c r="O41" s="4" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="P41" s="4" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="Q41" s="3" t="s">
         <v>231</v>
@@ -5029,10 +5035,10 @@
         <v>0</v>
       </c>
       <c r="X41" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y41" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="42" spans="1:25" x14ac:dyDescent="0.15">
@@ -5079,10 +5085,10 @@
         <v>100</v>
       </c>
       <c r="O42" s="4" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="P42" s="4" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="Q42" s="3" t="s">
         <v>231</v>
@@ -5094,10 +5100,10 @@
         <v>0</v>
       </c>
       <c r="X42" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y42" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="43" spans="1:25" x14ac:dyDescent="0.15">
@@ -5144,10 +5150,10 @@
         <v>100</v>
       </c>
       <c r="O43" s="4" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="P43" s="4" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="Q43" s="3" t="s">
         <v>231</v>
@@ -5159,10 +5165,10 @@
         <v>0</v>
       </c>
       <c r="X43" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y43" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="44" spans="1:25" x14ac:dyDescent="0.15">
@@ -5209,10 +5215,10 @@
         <v>100</v>
       </c>
       <c r="O44" s="4" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="P44" s="4" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="Q44" s="3" t="s">
         <v>231</v>
@@ -5224,10 +5230,10 @@
         <v>0</v>
       </c>
       <c r="X44" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y44" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="45" spans="1:25" x14ac:dyDescent="0.15">
@@ -5274,10 +5280,10 @@
         <v>100</v>
       </c>
       <c r="O45" s="4" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="P45" s="4" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="Q45" s="3" t="s">
         <v>231</v>
@@ -5289,10 +5295,10 @@
         <v>0</v>
       </c>
       <c r="X45" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y45" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="46" spans="1:25" x14ac:dyDescent="0.15">
@@ -5339,10 +5345,10 @@
         <v>100</v>
       </c>
       <c r="O46" s="4" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="P46" s="4" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="Q46" s="3" t="s">
         <v>231</v>
@@ -5354,10 +5360,10 @@
         <v>0</v>
       </c>
       <c r="X46" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y46" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="47" spans="1:25" x14ac:dyDescent="0.15">
@@ -5404,10 +5410,10 @@
         <v>100</v>
       </c>
       <c r="O47" s="4" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="P47" s="4" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="Q47" s="3" t="s">
         <v>231</v>
@@ -5419,10 +5425,10 @@
         <v>0</v>
       </c>
       <c r="X47" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y47" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="48" spans="1:25" x14ac:dyDescent="0.15">
@@ -5469,10 +5475,10 @@
         <v>100</v>
       </c>
       <c r="O48" s="4" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="P48" s="4" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="Q48" s="3" t="s">
         <v>231</v>
@@ -5484,10 +5490,10 @@
         <v>0</v>
       </c>
       <c r="X48" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y48" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="49" spans="1:25" x14ac:dyDescent="0.15">
@@ -5534,10 +5540,10 @@
         <v>100</v>
       </c>
       <c r="O49" s="4" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="P49" s="4" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="Q49" s="3" t="s">
         <v>231</v>
@@ -5549,10 +5555,10 @@
         <v>0</v>
       </c>
       <c r="X49" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y49" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="50" spans="1:25" x14ac:dyDescent="0.15">
@@ -5599,10 +5605,10 @@
         <v>100</v>
       </c>
       <c r="O50" s="4" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="P50" s="4" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="Q50" s="3" t="s">
         <v>231</v>
@@ -5614,10 +5620,10 @@
         <v>0</v>
       </c>
       <c r="X50" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y50" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="51" spans="1:25" x14ac:dyDescent="0.15">
@@ -5664,10 +5670,10 @@
         <v>100</v>
       </c>
       <c r="O51" s="4" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="P51" s="4" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="Q51" s="3" t="s">
         <v>231</v>
@@ -5679,10 +5685,10 @@
         <v>0</v>
       </c>
       <c r="X51" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y51" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="52" spans="1:25" x14ac:dyDescent="0.15">
@@ -5729,10 +5735,10 @@
         <v>100</v>
       </c>
       <c r="O52" s="4" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="P52" s="4" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="Q52" s="3" t="s">
         <v>231</v>
@@ -5744,10 +5750,10 @@
         <v>0</v>
       </c>
       <c r="X52" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y52" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="53" spans="1:25" x14ac:dyDescent="0.15">
@@ -5794,10 +5800,10 @@
         <v>100</v>
       </c>
       <c r="O53" s="4" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="P53" s="4" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="Q53" s="3" t="s">
         <v>231</v>
@@ -5809,10 +5815,10 @@
         <v>0</v>
       </c>
       <c r="X53" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y53" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="54" spans="1:25" x14ac:dyDescent="0.15">
@@ -5859,10 +5865,10 @@
         <v>100</v>
       </c>
       <c r="O54" s="4" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="P54" s="4" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="Q54" s="3" t="s">
         <v>231</v>
@@ -5874,10 +5880,10 @@
         <v>0</v>
       </c>
       <c r="X54" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y54" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="55" spans="1:25" x14ac:dyDescent="0.15">
@@ -5924,10 +5930,10 @@
         <v>100</v>
       </c>
       <c r="O55" s="4" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="P55" s="4" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="Q55" s="3" t="s">
         <v>231</v>
@@ -5939,10 +5945,10 @@
         <v>0</v>
       </c>
       <c r="X55" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y55" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="56" spans="1:25" x14ac:dyDescent="0.15">
@@ -5989,10 +5995,10 @@
         <v>100</v>
       </c>
       <c r="O56" s="4" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="P56" s="4" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="Q56" s="3" t="s">
         <v>231</v>
@@ -6004,10 +6010,10 @@
         <v>0</v>
       </c>
       <c r="X56" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y56" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="57" spans="1:25" x14ac:dyDescent="0.15">
@@ -6054,10 +6060,10 @@
         <v>100</v>
       </c>
       <c r="O57" s="4" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="P57" s="4" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="Q57" s="3" t="s">
         <v>231</v>
@@ -6069,10 +6075,10 @@
         <v>0</v>
       </c>
       <c r="X57" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y57" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="58" spans="1:25" x14ac:dyDescent="0.15">
@@ -6119,10 +6125,10 @@
         <v>100</v>
       </c>
       <c r="O58" s="4" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="P58" s="4" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="Q58" s="3" t="s">
         <v>231</v>
@@ -6134,10 +6140,10 @@
         <v>0</v>
       </c>
       <c r="X58" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y58" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="59" spans="1:25" x14ac:dyDescent="0.15">
@@ -6184,10 +6190,10 @@
         <v>100</v>
       </c>
       <c r="O59" s="4" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="P59" s="4" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="Q59" s="3" t="s">
         <v>231</v>
@@ -6199,10 +6205,10 @@
         <v>0</v>
       </c>
       <c r="X59" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y59" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="60" spans="1:25" x14ac:dyDescent="0.15">
@@ -6249,10 +6255,10 @@
         <v>100</v>
       </c>
       <c r="O60" s="4" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="P60" s="4" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="Q60" s="3" t="s">
         <v>231</v>
@@ -6264,10 +6270,10 @@
         <v>0</v>
       </c>
       <c r="X60" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y60" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="61" spans="1:25" x14ac:dyDescent="0.15">
@@ -6314,10 +6320,10 @@
         <v>100</v>
       </c>
       <c r="O61" s="4" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="P61" s="4" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="Q61" s="3" t="s">
         <v>231</v>
@@ -6329,10 +6335,10 @@
         <v>0</v>
       </c>
       <c r="X61" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y61" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="62" spans="1:25" x14ac:dyDescent="0.15">
@@ -6379,10 +6385,10 @@
         <v>100</v>
       </c>
       <c r="O62" s="4" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="P62" s="4" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="Q62" s="3" t="s">
         <v>231</v>
@@ -6394,10 +6400,10 @@
         <v>0</v>
       </c>
       <c r="X62" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y62" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="63" spans="1:25" x14ac:dyDescent="0.15">
@@ -6444,10 +6450,10 @@
         <v>100</v>
       </c>
       <c r="O63" s="4" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="P63" s="4" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="Q63" s="3" t="s">
         <v>231</v>
@@ -6459,10 +6465,10 @@
         <v>0</v>
       </c>
       <c r="X63" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y63" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="64" spans="1:25" x14ac:dyDescent="0.15">
@@ -6509,10 +6515,10 @@
         <v>100</v>
       </c>
       <c r="O64" s="4" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="P64" s="4" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="Q64" s="3" t="s">
         <v>231</v>
@@ -6524,10 +6530,10 @@
         <v>0</v>
       </c>
       <c r="X64" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y64" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="65" spans="1:25" x14ac:dyDescent="0.15">
@@ -6574,10 +6580,10 @@
         <v>100</v>
       </c>
       <c r="O65" s="4" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="P65" s="4" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="Q65" s="3" t="s">
         <v>231</v>
@@ -6589,10 +6595,10 @@
         <v>0</v>
       </c>
       <c r="X65" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y65" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="66" spans="1:25" x14ac:dyDescent="0.15">
@@ -6639,10 +6645,10 @@
         <v>100</v>
       </c>
       <c r="O66" s="4" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="P66" s="4" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="Q66" s="3" t="s">
         <v>231</v>
@@ -6654,10 +6660,10 @@
         <v>0</v>
       </c>
       <c r="X66" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y66" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="67" spans="1:25" x14ac:dyDescent="0.15">
@@ -6704,10 +6710,10 @@
         <v>100</v>
       </c>
       <c r="O67" s="4" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="P67" s="4" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="Q67" s="3" t="s">
         <v>231</v>
@@ -6719,10 +6725,10 @@
         <v>0</v>
       </c>
       <c r="X67" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y67" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="68" spans="1:25" x14ac:dyDescent="0.15">
@@ -6769,10 +6775,10 @@
         <v>100</v>
       </c>
       <c r="O68" s="4" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="P68" s="4" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="Q68" s="3" t="s">
         <v>231</v>
@@ -6784,10 +6790,10 @@
         <v>0</v>
       </c>
       <c r="X68" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y68" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="69" spans="1:25" x14ac:dyDescent="0.15">
@@ -6834,10 +6840,10 @@
         <v>100</v>
       </c>
       <c r="O69" s="4" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="P69" s="4" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="Q69" s="3" t="s">
         <v>231</v>
@@ -6849,10 +6855,10 @@
         <v>0</v>
       </c>
       <c r="X69" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y69" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="70" spans="1:25" x14ac:dyDescent="0.15">
@@ -6899,10 +6905,10 @@
         <v>100</v>
       </c>
       <c r="O70" s="4" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="P70" s="4" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="Q70" s="3" t="s">
         <v>231</v>
@@ -6914,10 +6920,10 @@
         <v>0</v>
       </c>
       <c r="X70" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y70" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="71" spans="1:25" x14ac:dyDescent="0.15">
@@ -6964,10 +6970,10 @@
         <v>100</v>
       </c>
       <c r="O71" s="4" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="P71" s="4" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="Q71" s="3" t="s">
         <v>231</v>
@@ -6979,10 +6985,10 @@
         <v>0</v>
       </c>
       <c r="X71" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y71" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="72" spans="1:25" x14ac:dyDescent="0.15">
@@ -7029,10 +7035,10 @@
         <v>100</v>
       </c>
       <c r="O72" s="4" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="P72" s="4" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="Q72" s="3" t="s">
         <v>231</v>
@@ -7044,10 +7050,10 @@
         <v>0</v>
       </c>
       <c r="X72" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y72" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="73" spans="1:25" x14ac:dyDescent="0.15">
@@ -7094,10 +7100,10 @@
         <v>100</v>
       </c>
       <c r="O73" s="4" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="P73" s="4" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="Q73" s="3" t="s">
         <v>231</v>
@@ -7109,10 +7115,10 @@
         <v>0</v>
       </c>
       <c r="X73" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y73" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="74" spans="1:25" x14ac:dyDescent="0.15">
@@ -7159,10 +7165,10 @@
         <v>100</v>
       </c>
       <c r="O74" s="4" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="P74" s="4" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="Q74" s="3" t="s">
         <v>231</v>
@@ -7174,10 +7180,10 @@
         <v>0</v>
       </c>
       <c r="X74" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y74" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="75" spans="1:25" x14ac:dyDescent="0.15">
@@ -7224,10 +7230,10 @@
         <v>100</v>
       </c>
       <c r="O75" s="4" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="P75" s="4" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="Q75" s="3" t="s">
         <v>231</v>
@@ -7239,10 +7245,10 @@
         <v>0</v>
       </c>
       <c r="X75" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y75" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="76" spans="1:25" x14ac:dyDescent="0.15">
@@ -7289,10 +7295,10 @@
         <v>100</v>
       </c>
       <c r="O76" s="4" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="P76" s="4" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="Q76" s="3" t="s">
         <v>231</v>
@@ -7304,10 +7310,10 @@
         <v>0</v>
       </c>
       <c r="X76" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y76" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="77" spans="1:25" x14ac:dyDescent="0.15">
@@ -7354,10 +7360,10 @@
         <v>100</v>
       </c>
       <c r="O77" s="4" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="P77" s="4" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="Q77" s="3" t="s">
         <v>231</v>
@@ -7369,10 +7375,10 @@
         <v>0</v>
       </c>
       <c r="X77" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y77" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="78" spans="1:25" x14ac:dyDescent="0.15">
@@ -7419,10 +7425,10 @@
         <v>100</v>
       </c>
       <c r="O78" s="4" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="P78" s="4" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="Q78" s="3" t="s">
         <v>231</v>
@@ -7434,10 +7440,10 @@
         <v>0</v>
       </c>
       <c r="X78" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y78" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="79" spans="1:25" x14ac:dyDescent="0.15">
@@ -7484,10 +7490,10 @@
         <v>100</v>
       </c>
       <c r="O79" s="4" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="P79" s="4" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="Q79" s="3" t="s">
         <v>231</v>
@@ -7499,10 +7505,10 @@
         <v>0</v>
       </c>
       <c r="X79" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y79" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="80" spans="1:25" x14ac:dyDescent="0.15">
@@ -7549,10 +7555,10 @@
         <v>100</v>
       </c>
       <c r="O80" s="4" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="P80" s="4" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="Q80" s="3" t="s">
         <v>231</v>
@@ -7564,10 +7570,10 @@
         <v>0</v>
       </c>
       <c r="X80" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y80" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="81" spans="1:25" x14ac:dyDescent="0.15">
@@ -7614,10 +7620,10 @@
         <v>100</v>
       </c>
       <c r="O81" s="4" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="P81" s="4" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="Q81" s="3" t="s">
         <v>231</v>
@@ -7629,10 +7635,10 @@
         <v>0</v>
       </c>
       <c r="X81" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y81" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="82" spans="1:25" x14ac:dyDescent="0.15">
@@ -7679,10 +7685,10 @@
         <v>100</v>
       </c>
       <c r="O82" s="4" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="P82" s="4" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="Q82" s="3" t="s">
         <v>231</v>
@@ -7694,10 +7700,10 @@
         <v>0</v>
       </c>
       <c r="X82" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y82" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="83" spans="1:25" x14ac:dyDescent="0.15">
@@ -7744,10 +7750,10 @@
         <v>100</v>
       </c>
       <c r="O83" s="4" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="P83" s="4" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="Q83" s="3" t="s">
         <v>231</v>
@@ -7759,10 +7765,10 @@
         <v>0</v>
       </c>
       <c r="X83" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y83" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="84" spans="1:25" x14ac:dyDescent="0.15">
@@ -7809,10 +7815,10 @@
         <v>100</v>
       </c>
       <c r="O84" s="4" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="P84" s="4" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="Q84" s="3" t="s">
         <v>231</v>
@@ -7824,10 +7830,10 @@
         <v>0</v>
       </c>
       <c r="X84" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y84" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="85" spans="1:25" x14ac:dyDescent="0.15">
@@ -7874,10 +7880,10 @@
         <v>100</v>
       </c>
       <c r="O85" s="4" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="P85" s="4" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="Q85" s="3" t="s">
         <v>231</v>
@@ -7889,10 +7895,10 @@
         <v>0</v>
       </c>
       <c r="X85" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y85" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="86" spans="1:25" x14ac:dyDescent="0.15">
@@ -7939,10 +7945,10 @@
         <v>100</v>
       </c>
       <c r="O86" s="4" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="P86" s="4" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="Q86" s="3" t="s">
         <v>231</v>
@@ -7954,10 +7960,10 @@
         <v>0</v>
       </c>
       <c r="X86" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y86" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="87" spans="1:25" x14ac:dyDescent="0.15">
@@ -8004,10 +8010,10 @@
         <v>100</v>
       </c>
       <c r="O87" s="4" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="P87" s="4" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="Q87" s="3" t="s">
         <v>231</v>
@@ -8019,10 +8025,10 @@
         <v>0</v>
       </c>
       <c r="X87" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y87" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="88" spans="1:25" x14ac:dyDescent="0.15">
@@ -8069,10 +8075,10 @@
         <v>100</v>
       </c>
       <c r="O88" s="4" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="P88" s="4" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="Q88" s="3" t="s">
         <v>231</v>
@@ -8084,10 +8090,10 @@
         <v>0</v>
       </c>
       <c r="X88" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y88" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="89" spans="1:25" x14ac:dyDescent="0.15">
@@ -8134,10 +8140,10 @@
         <v>100</v>
       </c>
       <c r="O89" s="4" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="P89" s="4" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="Q89" s="3" t="s">
         <v>231</v>
@@ -8149,10 +8155,10 @@
         <v>0</v>
       </c>
       <c r="X89" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y89" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="90" spans="1:25" x14ac:dyDescent="0.15">
@@ -8199,10 +8205,10 @@
         <v>100</v>
       </c>
       <c r="O90" s="4" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="P90" s="4" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="Q90" s="3" t="s">
         <v>231</v>
@@ -8214,10 +8220,10 @@
         <v>0</v>
       </c>
       <c r="X90" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y90" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="91" spans="1:25" x14ac:dyDescent="0.15">
@@ -8264,10 +8270,10 @@
         <v>100</v>
       </c>
       <c r="O91" s="4" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="P91" s="4" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="Q91" s="3" t="s">
         <v>231</v>
@@ -8279,10 +8285,10 @@
         <v>0</v>
       </c>
       <c r="X91" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y91" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="92" spans="1:25" x14ac:dyDescent="0.15">
@@ -8329,10 +8335,10 @@
         <v>100</v>
       </c>
       <c r="O92" s="4" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="P92" s="4" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="Q92" s="3" t="s">
         <v>231</v>
@@ -8344,10 +8350,10 @@
         <v>0</v>
       </c>
       <c r="X92" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y92" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="93" spans="1:25" x14ac:dyDescent="0.15">
@@ -8394,10 +8400,10 @@
         <v>100</v>
       </c>
       <c r="O93" s="4" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="P93" s="4" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="Q93" s="3" t="s">
         <v>231</v>
@@ -8409,10 +8415,10 @@
         <v>0</v>
       </c>
       <c r="X93" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y93" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="94" spans="1:25" x14ac:dyDescent="0.15">
@@ -8459,10 +8465,10 @@
         <v>100</v>
       </c>
       <c r="O94" s="4" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="P94" s="4" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="Q94" s="3" t="s">
         <v>231</v>
@@ -8474,10 +8480,10 @@
         <v>0</v>
       </c>
       <c r="X94" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y94" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="95" spans="1:25" x14ac:dyDescent="0.15">
@@ -8524,10 +8530,10 @@
         <v>100</v>
       </c>
       <c r="O95" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="P95" s="4" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="Q95" s="3" t="s">
         <v>231</v>
@@ -8539,10 +8545,10 @@
         <v>0</v>
       </c>
       <c r="X95" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y95" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="96" spans="1:25" x14ac:dyDescent="0.15">
@@ -8589,10 +8595,10 @@
         <v>100</v>
       </c>
       <c r="O96" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="P96" s="4" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="Q96" s="3" t="s">
         <v>231</v>
@@ -8604,10 +8610,10 @@
         <v>0</v>
       </c>
       <c r="X96" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y96" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="97" spans="1:25" x14ac:dyDescent="0.15">
@@ -8654,10 +8660,10 @@
         <v>100</v>
       </c>
       <c r="O97" s="4" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="P97" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="Q97" s="3" t="s">
         <v>231</v>
@@ -8669,10 +8675,10 @@
         <v>0</v>
       </c>
       <c r="X97" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y97" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="98" spans="1:25" x14ac:dyDescent="0.15">
@@ -8719,10 +8725,10 @@
         <v>100</v>
       </c>
       <c r="O98" s="4" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="P98" s="4" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="Q98" s="3" t="s">
         <v>231</v>
@@ -8734,10 +8740,10 @@
         <v>0</v>
       </c>
       <c r="X98" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y98" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="99" spans="1:25" x14ac:dyDescent="0.15">
@@ -8784,10 +8790,10 @@
         <v>100</v>
       </c>
       <c r="O99" s="4" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="P99" s="4" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="Q99" s="3" t="s">
         <v>231</v>
@@ -8799,10 +8805,10 @@
         <v>0</v>
       </c>
       <c r="X99" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y99" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="100" spans="1:25" x14ac:dyDescent="0.15">
@@ -8849,10 +8855,10 @@
         <v>100</v>
       </c>
       <c r="O100" s="4" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="P100" s="4" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="Q100" s="3" t="s">
         <v>231</v>
@@ -8864,10 +8870,10 @@
         <v>0</v>
       </c>
       <c r="X100" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y100" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="101" spans="1:25" x14ac:dyDescent="0.15">
@@ -8914,10 +8920,10 @@
         <v>100</v>
       </c>
       <c r="O101" s="4" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="P101" s="4" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="Q101" s="3" t="s">
         <v>231</v>
@@ -8929,10 +8935,10 @@
         <v>0</v>
       </c>
       <c r="X101" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y101" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="102" spans="1:25" x14ac:dyDescent="0.15">
@@ -8979,10 +8985,10 @@
         <v>100</v>
       </c>
       <c r="O102" s="4" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="P102" s="4" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="Q102" s="3" t="s">
         <v>231</v>
@@ -8994,10 +9000,10 @@
         <v>0</v>
       </c>
       <c r="X102" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y102" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="103" spans="1:25" x14ac:dyDescent="0.15">
@@ -9044,10 +9050,10 @@
         <v>100</v>
       </c>
       <c r="O103" s="4" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="P103" s="4" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="Q103" s="3" t="s">
         <v>231</v>
@@ -9059,10 +9065,10 @@
         <v>0</v>
       </c>
       <c r="X103" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y103" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="104" spans="1:25" x14ac:dyDescent="0.15">
@@ -9109,10 +9115,10 @@
         <v>100</v>
       </c>
       <c r="O104" s="4" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="P104" s="4" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="Q104" s="3" t="s">
         <v>231</v>
@@ -9124,10 +9130,10 @@
         <v>0</v>
       </c>
       <c r="X104" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y104" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="105" spans="1:25" x14ac:dyDescent="0.15">
@@ -9174,10 +9180,10 @@
         <v>100</v>
       </c>
       <c r="O105" s="4" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="P105" s="4" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="Q105" s="3" t="s">
         <v>231</v>
@@ -9189,10 +9195,10 @@
         <v>0</v>
       </c>
       <c r="X105" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y105" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="106" spans="1:25" x14ac:dyDescent="0.15">
@@ -9239,10 +9245,10 @@
         <v>100</v>
       </c>
       <c r="O106" s="4" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="P106" s="4" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="Q106" s="3" t="s">
         <v>231</v>
@@ -9254,10 +9260,10 @@
         <v>0</v>
       </c>
       <c r="X106" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y106" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="107" spans="1:25" x14ac:dyDescent="0.15">
@@ -9304,10 +9310,10 @@
         <v>100</v>
       </c>
       <c r="O107" s="4" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="P107" s="4" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="Q107" s="3" t="s">
         <v>231</v>
@@ -9319,10 +9325,10 @@
         <v>0</v>
       </c>
       <c r="X107" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y107" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="108" spans="1:25" x14ac:dyDescent="0.15">
@@ -9369,10 +9375,10 @@
         <v>100</v>
       </c>
       <c r="O108" s="4" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="P108" s="4" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="Q108" s="3" t="s">
         <v>231</v>
@@ -9384,10 +9390,10 @@
         <v>0</v>
       </c>
       <c r="X108" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y108" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="109" spans="1:25" x14ac:dyDescent="0.15">
@@ -9434,10 +9440,10 @@
         <v>100</v>
       </c>
       <c r="O109" s="4" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="P109" s="4" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="Q109" s="3" t="s">
         <v>231</v>
@@ -9449,10 +9455,10 @@
         <v>0</v>
       </c>
       <c r="X109" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y109" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="110" spans="1:25" x14ac:dyDescent="0.15">
@@ -9499,10 +9505,10 @@
         <v>100</v>
       </c>
       <c r="O110" s="4" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="P110" s="4" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="Q110" s="3" t="s">
         <v>231</v>
@@ -9514,10 +9520,10 @@
         <v>0</v>
       </c>
       <c r="X110" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y110" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="111" spans="1:25" x14ac:dyDescent="0.15">
@@ -9564,10 +9570,10 @@
         <v>100</v>
       </c>
       <c r="O111" s="4" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="P111" s="4" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="Q111" s="3" t="s">
         <v>231</v>
@@ -9579,10 +9585,10 @@
         <v>0</v>
       </c>
       <c r="X111" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y111" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="112" spans="1:25" x14ac:dyDescent="0.15">
@@ -9629,10 +9635,10 @@
         <v>100</v>
       </c>
       <c r="O112" s="4" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="P112" s="4" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="Q112" s="3" t="s">
         <v>231</v>
@@ -9644,10 +9650,10 @@
         <v>0</v>
       </c>
       <c r="X112" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y112" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="113" spans="1:25" x14ac:dyDescent="0.15">
@@ -9694,10 +9700,10 @@
         <v>100</v>
       </c>
       <c r="O113" s="4" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="P113" s="4" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="Q113" s="3" t="s">
         <v>231</v>
@@ -9709,10 +9715,10 @@
         <v>0</v>
       </c>
       <c r="X113" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y113" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="114" spans="1:25" x14ac:dyDescent="0.15">
@@ -9759,10 +9765,10 @@
         <v>100</v>
       </c>
       <c r="O114" s="4" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="P114" s="4" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="Q114" s="3" t="s">
         <v>231</v>
@@ -9774,10 +9780,10 @@
         <v>0</v>
       </c>
       <c r="X114" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y114" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="115" spans="1:25" x14ac:dyDescent="0.15">
@@ -9824,10 +9830,10 @@
         <v>100</v>
       </c>
       <c r="O115" s="4" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="P115" s="4" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="Q115" s="3" t="s">
         <v>231</v>
@@ -9839,10 +9845,10 @@
         <v>0</v>
       </c>
       <c r="X115" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y115" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="116" spans="1:25" x14ac:dyDescent="0.15">
@@ -9889,10 +9895,10 @@
         <v>100</v>
       </c>
       <c r="O116" s="4" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="P116" s="4" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="Q116" s="3" t="s">
         <v>231</v>
@@ -9904,10 +9910,10 @@
         <v>0</v>
       </c>
       <c r="X116" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y116" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="117" spans="1:25" x14ac:dyDescent="0.15">
@@ -9954,10 +9960,10 @@
         <v>100</v>
       </c>
       <c r="O117" s="4" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="P117" s="4" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="Q117" s="3" t="s">
         <v>231</v>
@@ -9969,10 +9975,10 @@
         <v>0</v>
       </c>
       <c r="X117" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y117" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="118" spans="1:25" x14ac:dyDescent="0.15">
@@ -10019,10 +10025,10 @@
         <v>100</v>
       </c>
       <c r="O118" s="4" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="P118" s="4" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="Q118" s="3" t="s">
         <v>231</v>
@@ -10034,10 +10040,10 @@
         <v>0</v>
       </c>
       <c r="X118" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y118" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="119" spans="1:25" x14ac:dyDescent="0.15">
@@ -10084,10 +10090,10 @@
         <v>100</v>
       </c>
       <c r="O119" s="4" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="P119" s="4" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="Q119" s="3" t="s">
         <v>231</v>
@@ -10099,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="X119" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y119" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="120" spans="1:25" x14ac:dyDescent="0.15">
@@ -10149,10 +10155,10 @@
         <v>100</v>
       </c>
       <c r="O120" s="4" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="P120" s="4" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="Q120" s="3" t="s">
         <v>231</v>
@@ -10164,10 +10170,10 @@
         <v>0</v>
       </c>
       <c r="X120" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y120" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="121" spans="1:25" x14ac:dyDescent="0.15">
@@ -10214,10 +10220,10 @@
         <v>100</v>
       </c>
       <c r="O121" s="4" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="P121" s="4" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="Q121" s="3" t="s">
         <v>231</v>
@@ -10229,10 +10235,10 @@
         <v>0</v>
       </c>
       <c r="X121" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y121" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="122" spans="1:25" x14ac:dyDescent="0.15">
@@ -10279,10 +10285,10 @@
         <v>100</v>
       </c>
       <c r="O122" s="4" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="P122" s="4" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="Q122" s="3" t="s">
         <v>231</v>
@@ -10294,10 +10300,10 @@
         <v>0</v>
       </c>
       <c r="X122" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y122" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="123" spans="1:25" x14ac:dyDescent="0.15">
@@ -10344,10 +10350,10 @@
         <v>100</v>
       </c>
       <c r="O123" s="4" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="P123" s="4" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="Q123" s="3" t="s">
         <v>231</v>
@@ -10359,10 +10365,10 @@
         <v>0</v>
       </c>
       <c r="X123" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y123" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="124" spans="1:25" x14ac:dyDescent="0.15">
@@ -10409,10 +10415,10 @@
         <v>100</v>
       </c>
       <c r="O124" s="4" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="P124" s="4" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="Q124" s="3" t="s">
         <v>231</v>
@@ -10424,10 +10430,10 @@
         <v>0</v>
       </c>
       <c r="X124" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y124" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="125" spans="1:25" x14ac:dyDescent="0.15">
@@ -10474,10 +10480,10 @@
         <v>100</v>
       </c>
       <c r="O125" s="4" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="P125" s="4" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q125" s="3" t="s">
         <v>231</v>
@@ -10489,10 +10495,10 @@
         <v>0</v>
       </c>
       <c r="X125" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y125" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="126" spans="1:25" x14ac:dyDescent="0.15">
@@ -10539,10 +10545,10 @@
         <v>100</v>
       </c>
       <c r="O126" s="4" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="P126" s="4" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="Q126" s="3" t="s">
         <v>231</v>
@@ -10554,10 +10560,10 @@
         <v>0</v>
       </c>
       <c r="X126" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y126" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="127" spans="1:25" x14ac:dyDescent="0.15">
@@ -10604,10 +10610,10 @@
         <v>100</v>
       </c>
       <c r="O127" s="4" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="P127" s="4" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="Q127" s="3" t="s">
         <v>231</v>
@@ -10619,10 +10625,10 @@
         <v>0</v>
       </c>
       <c r="X127" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y127" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="128" spans="1:25" x14ac:dyDescent="0.15">
@@ -10669,10 +10675,10 @@
         <v>100</v>
       </c>
       <c r="O128" s="4" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="P128" s="4" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="Q128" s="3" t="s">
         <v>231</v>
@@ -10684,10 +10690,10 @@
         <v>0</v>
       </c>
       <c r="X128" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y128" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="129" spans="1:25" x14ac:dyDescent="0.15">
@@ -10734,10 +10740,10 @@
         <v>100</v>
       </c>
       <c r="O129" s="4" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="P129" s="4" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="Q129" s="3" t="s">
         <v>231</v>
@@ -10749,10 +10755,10 @@
         <v>0</v>
       </c>
       <c r="X129" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y129" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="130" spans="1:25" x14ac:dyDescent="0.15">
@@ -10799,10 +10805,10 @@
         <v>100</v>
       </c>
       <c r="O130" s="4" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="P130" s="4" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="Q130" s="3" t="s">
         <v>231</v>
@@ -10814,10 +10820,10 @@
         <v>0</v>
       </c>
       <c r="X130" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y130" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="131" spans="1:25" x14ac:dyDescent="0.15">
@@ -10864,10 +10870,10 @@
         <v>100</v>
       </c>
       <c r="O131" s="4" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="P131" s="4" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="Q131" s="3" t="s">
         <v>231</v>
@@ -10879,10 +10885,10 @@
         <v>0</v>
       </c>
       <c r="X131" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y131" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="132" spans="1:25" x14ac:dyDescent="0.15">
@@ -10929,10 +10935,10 @@
         <v>100</v>
       </c>
       <c r="O132" s="4" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="P132" s="4" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="Q132" s="3" t="s">
         <v>231</v>
@@ -10944,10 +10950,10 @@
         <v>0</v>
       </c>
       <c r="X132" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y132" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="133" spans="1:25" x14ac:dyDescent="0.15">
@@ -10994,10 +11000,10 @@
         <v>100</v>
       </c>
       <c r="O133" s="4" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="P133" s="4" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="Q133" s="3" t="s">
         <v>231</v>
@@ -11009,10 +11015,10 @@
         <v>0</v>
       </c>
       <c r="X133" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y133" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="134" spans="1:25" x14ac:dyDescent="0.15">
@@ -11059,10 +11065,10 @@
         <v>100</v>
       </c>
       <c r="O134" s="4" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="P134" s="4" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="Q134" s="3" t="s">
         <v>231</v>
@@ -11074,10 +11080,10 @@
         <v>0</v>
       </c>
       <c r="X134" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y134" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="135" spans="1:25" x14ac:dyDescent="0.15">
@@ -11124,10 +11130,10 @@
         <v>100</v>
       </c>
       <c r="O135" s="4" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="P135" s="4" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="Q135" s="3" t="s">
         <v>231</v>
@@ -11139,10 +11145,10 @@
         <v>0</v>
       </c>
       <c r="X135" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y135" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="136" spans="1:25" x14ac:dyDescent="0.15">
@@ -11189,10 +11195,10 @@
         <v>100</v>
       </c>
       <c r="O136" s="4" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="P136" s="4" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="Q136" s="3" t="s">
         <v>231</v>
@@ -11204,10 +11210,10 @@
         <v>0</v>
       </c>
       <c r="X136" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y136" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="137" spans="1:25" x14ac:dyDescent="0.15">
@@ -11254,10 +11260,10 @@
         <v>100</v>
       </c>
       <c r="O137" s="4" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="P137" s="4" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="Q137" s="3" t="s">
         <v>231</v>
@@ -11269,10 +11275,10 @@
         <v>0</v>
       </c>
       <c r="X137" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y137" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="138" spans="1:25" x14ac:dyDescent="0.15">
@@ -11319,10 +11325,10 @@
         <v>100</v>
       </c>
       <c r="O138" s="4" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="P138" s="4" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="Q138" s="3" t="s">
         <v>231</v>
@@ -11334,10 +11340,10 @@
         <v>0</v>
       </c>
       <c r="X138" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y138" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="139" spans="1:25" x14ac:dyDescent="0.15">
@@ -11384,10 +11390,10 @@
         <v>100</v>
       </c>
       <c r="O139" s="4" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="P139" s="4" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="Q139" s="3" t="s">
         <v>231</v>
@@ -11399,10 +11405,10 @@
         <v>0</v>
       </c>
       <c r="X139" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y139" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="140" spans="1:25" x14ac:dyDescent="0.15">
@@ -11449,10 +11455,10 @@
         <v>100</v>
       </c>
       <c r="O140" s="4" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="P140" s="4" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="Q140" s="3" t="s">
         <v>231</v>
@@ -11464,10 +11470,10 @@
         <v>0</v>
       </c>
       <c r="X140" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y140" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="141" spans="1:25" x14ac:dyDescent="0.15">
@@ -11514,10 +11520,10 @@
         <v>100</v>
       </c>
       <c r="O141" s="4" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="P141" s="4" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="Q141" s="3" t="s">
         <v>231</v>
@@ -11529,10 +11535,10 @@
         <v>0</v>
       </c>
       <c r="X141" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y141" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="142" spans="1:25" x14ac:dyDescent="0.15">
@@ -11579,10 +11585,10 @@
         <v>100</v>
       </c>
       <c r="O142" s="4" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="P142" s="4" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="Q142" s="3" t="s">
         <v>231</v>
@@ -11594,10 +11600,10 @@
         <v>0</v>
       </c>
       <c r="X142" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y142" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="143" spans="1:25" x14ac:dyDescent="0.15">
@@ -11644,10 +11650,10 @@
         <v>100</v>
       </c>
       <c r="O143" s="4" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="P143" s="4" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="Q143" s="3" t="s">
         <v>231</v>
@@ -11659,10 +11665,10 @@
         <v>0</v>
       </c>
       <c r="X143" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y143" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="144" spans="1:25" x14ac:dyDescent="0.15">
@@ -11709,10 +11715,10 @@
         <v>100</v>
       </c>
       <c r="O144" s="4" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="P144" s="4" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="Q144" s="3" t="s">
         <v>231</v>
@@ -11724,10 +11730,10 @@
         <v>0</v>
       </c>
       <c r="X144" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y144" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="145" spans="1:25" x14ac:dyDescent="0.15">
@@ -11774,10 +11780,10 @@
         <v>100</v>
       </c>
       <c r="O145" s="4" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="P145" s="4" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="Q145" s="3" t="s">
         <v>231</v>
@@ -11789,10 +11795,10 @@
         <v>0</v>
       </c>
       <c r="X145" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y145" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="146" spans="1:25" x14ac:dyDescent="0.15">
@@ -11839,10 +11845,10 @@
         <v>100</v>
       </c>
       <c r="O146" s="4" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="P146" s="4" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="Q146" s="3" t="s">
         <v>231</v>
@@ -11854,10 +11860,10 @@
         <v>0</v>
       </c>
       <c r="X146" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y146" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="147" spans="1:25" x14ac:dyDescent="0.15">
@@ -11904,10 +11910,10 @@
         <v>100</v>
       </c>
       <c r="O147" s="4" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="P147" s="4" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="Q147" s="3" t="s">
         <v>231</v>
@@ -11919,10 +11925,10 @@
         <v>0</v>
       </c>
       <c r="X147" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y147" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="148" spans="1:25" x14ac:dyDescent="0.15">
@@ -11969,10 +11975,10 @@
         <v>100</v>
       </c>
       <c r="O148" s="4" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="P148" s="4" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="Q148" s="3" t="s">
         <v>231</v>
@@ -11984,10 +11990,10 @@
         <v>0</v>
       </c>
       <c r="X148" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y148" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="149" spans="1:25" x14ac:dyDescent="0.15">
@@ -12034,10 +12040,10 @@
         <v>100</v>
       </c>
       <c r="O149" s="4" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="P149" s="4" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="Q149" s="3" t="s">
         <v>231</v>
@@ -12049,10 +12055,10 @@
         <v>0</v>
       </c>
       <c r="X149" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y149" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="150" spans="1:25" x14ac:dyDescent="0.15">
@@ -12099,10 +12105,10 @@
         <v>100</v>
       </c>
       <c r="O150" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="P150" s="4" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="Q150" s="3" t="s">
         <v>231</v>
@@ -12114,10 +12120,10 @@
         <v>0</v>
       </c>
       <c r="X150" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y150" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="151" spans="1:25" x14ac:dyDescent="0.15">
@@ -12164,10 +12170,10 @@
         <v>100</v>
       </c>
       <c r="O151" s="4" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="P151" s="4" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="Q151" s="3" t="s">
         <v>231</v>
@@ -12179,10 +12185,10 @@
         <v>0</v>
       </c>
       <c r="X151" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y151" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="152" spans="1:25" x14ac:dyDescent="0.15">
@@ -12229,10 +12235,10 @@
         <v>100</v>
       </c>
       <c r="O152" s="4" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="P152" s="4" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="Q152" s="3" t="s">
         <v>231</v>
@@ -12244,10 +12250,10 @@
         <v>0</v>
       </c>
       <c r="X152" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y152" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="153" spans="1:25" x14ac:dyDescent="0.15">
@@ -12294,10 +12300,10 @@
         <v>100</v>
       </c>
       <c r="O153" s="4" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="P153" s="4" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="Q153" s="3" t="s">
         <v>231</v>
@@ -12309,10 +12315,10 @@
         <v>0</v>
       </c>
       <c r="X153" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y153" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="154" spans="1:25" x14ac:dyDescent="0.15">
@@ -12359,10 +12365,10 @@
         <v>100</v>
       </c>
       <c r="O154" s="4" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="P154" s="4" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="Q154" s="3" t="s">
         <v>231</v>
@@ -12374,10 +12380,10 @@
         <v>0</v>
       </c>
       <c r="X154" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y154" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="155" spans="1:25" x14ac:dyDescent="0.15">
@@ -12424,10 +12430,10 @@
         <v>100</v>
       </c>
       <c r="O155" s="4" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="P155" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="Q155" s="3" t="s">
         <v>231</v>
@@ -12439,10 +12445,10 @@
         <v>0</v>
       </c>
       <c r="X155" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y155" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="156" spans="1:25" x14ac:dyDescent="0.15">
@@ -12489,10 +12495,10 @@
         <v>100</v>
       </c>
       <c r="O156" s="4" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="P156" s="4" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="Q156" s="3" t="s">
         <v>231</v>
@@ -12504,10 +12510,10 @@
         <v>0</v>
       </c>
       <c r="X156" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y156" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="157" spans="1:25" x14ac:dyDescent="0.15">
@@ -12554,10 +12560,10 @@
         <v>100</v>
       </c>
       <c r="O157" s="4" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="P157" s="4" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="Q157" s="3" t="s">
         <v>231</v>
@@ -12569,10 +12575,10 @@
         <v>0</v>
       </c>
       <c r="X157" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y157" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="158" spans="1:25" x14ac:dyDescent="0.15">
@@ -12619,10 +12625,10 @@
         <v>100</v>
       </c>
       <c r="O158" s="4" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="P158" s="4" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="Q158" s="3" t="s">
         <v>231</v>
@@ -12634,10 +12640,10 @@
         <v>0</v>
       </c>
       <c r="X158" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y158" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="159" spans="1:25" x14ac:dyDescent="0.15">
@@ -12684,10 +12690,10 @@
         <v>100</v>
       </c>
       <c r="O159" s="4" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="P159" s="4" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="Q159" s="3" t="s">
         <v>231</v>
@@ -12699,10 +12705,10 @@
         <v>0</v>
       </c>
       <c r="X159" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y159" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="160" spans="1:25" x14ac:dyDescent="0.15">
@@ -12749,10 +12755,10 @@
         <v>100</v>
       </c>
       <c r="O160" s="4" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="P160" s="4" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="Q160" s="3" t="s">
         <v>231</v>
@@ -12764,10 +12770,10 @@
         <v>0</v>
       </c>
       <c r="X160" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y160" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="161" spans="1:25" x14ac:dyDescent="0.15">
@@ -12814,10 +12820,10 @@
         <v>100</v>
       </c>
       <c r="O161" s="4" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="P161" s="4" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="Q161" s="3" t="s">
         <v>231</v>
@@ -12829,10 +12835,10 @@
         <v>0</v>
       </c>
       <c r="X161" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y161" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="162" spans="1:25" x14ac:dyDescent="0.15">
@@ -12879,10 +12885,10 @@
         <v>100</v>
       </c>
       <c r="O162" s="4" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="P162" s="4" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="Q162" s="3" t="s">
         <v>231</v>
@@ -12894,10 +12900,10 @@
         <v>0</v>
       </c>
       <c r="X162" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y162" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="163" spans="1:25" x14ac:dyDescent="0.15">
@@ -12944,10 +12950,10 @@
         <v>100</v>
       </c>
       <c r="O163" s="4" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="P163" s="4" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="Q163" s="3" t="s">
         <v>231</v>
@@ -12959,10 +12965,10 @@
         <v>0</v>
       </c>
       <c r="X163" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y163" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="164" spans="1:25" x14ac:dyDescent="0.15">
@@ -13009,10 +13015,10 @@
         <v>100</v>
       </c>
       <c r="O164" s="4" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="P164" s="4" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="Q164" s="3" t="s">
         <v>231</v>
@@ -13024,10 +13030,10 @@
         <v>0</v>
       </c>
       <c r="X164" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Y164" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42B384AE-0119-4069-9446-61815DF5E3D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDBD88C3-AC85-418B-AB09-2BA1610B3272}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_barries_v8" sheetId="1" r:id="rId1"/>
@@ -1932,9 +1932,6 @@
     <t>300001:1102_300002:1102_300003:1102_0:100</t>
   </si>
   <si>
-    <t>300001:102_300003:102_300003:102_0:101</t>
-  </si>
-  <si>
     <t>46200001,46800001,46900001,42761001,42761002,42761003,42761004,42761005,42761006,42761007,42761008,42761009,42761010,42761011,42761012,42761013,42761014,42761015,42761016,42761017,42761018,42761019,42761020,42761021,42761022,42761023,42761024,42761025,42761026,42761027,42761028,42761029,42761030,42761031,42761032,42761033,42761034,42761035,42761036,42761037,42761038,42761039,42761040,42761041,42761042,42761043,42761044,42761045,42761046,42761047,42761048,42761049,42761050,42761051,42761052,42761053,42761054,42761055,42761056,42761057,42761058,42761059,42761060,42761061,42761062,42761063,42761064,42761065,42761066,42761067,42761068,42761069,42761070,42761071,42761072,42761073,42761074,42761075,42761076,42761077,42761078,42761079,42761080,42761081,42761082,42761083,42761084,42761085,42761086,42761087,42761088,42761089,42761090,42761091,42761092,42761093,42761094,42761095,42761096,42761097,42761098,42761099,42761100,42761101,42761102,42761103,42761104,42761105,42761106,42761107,42761108,42761109,42761110,42761111,42761112,42761113,42761114,42761115,42761116,42761117,42761118,42761119,42761120,42761121,42761122,42761123,42761124,42761125,42761126,42761127,42761128,42761129,42761130,42761131,42761132,42761133,42761134,42761135,42761136,42761137,42761138,42761139,42761140,42761141,42761142,42761143,42761144,42761145,42761146,42761147,42761148,42761149,42761150,42761151,42761152,42761153,42761154,42761155,42761156,42761157,42761158,42761159,42761160,42662001,42662002,42662003,42662004,42662005,42662006,42662007,42662008,42662009,42662010,42662011,42662012,42662013,42662014,42662015,42662016,42662017,42662018,42662019,42662020,42662021,42662022,42662023,42662024,42662025,42662026,42662027,42662028,42662029,42662030,42662031,42662032,42662033,42662034,42662035,42662036,42662037,42662038,42662039,42662040,42662041,42662042,42662043,42662044,42662045,42662046,42662047,42662048,42662049,42662050,42662051,42662052,42662053,42662054,42662055,42662056,42662057,42662058,42662059,42662060,42662061,42662062,42662063,42662064,42662065,42662066,42662067,42662068,42662069,42662070,42662071,42662072,42662073,42662074,42662075,42662076,42662077,42662078,42662079,42662080,42662081,42662082,42662083,42662084,42662085,42662086,42662087,42662088,42662089,42662090,42662091,42662092,42662093,42662094,42662095,42662096,42662097,42662098,42662099,42662100,42662101,42662102,42662103,42662104,42662105,42662106,42662107,42662108,42662109,42662110,42662111,42662112,42662113,42662114,42662115,42662116,42662117,42662118,42662119,42662120,42662121,42662122,42662123,42662124,42662125,42662126,42662127,42662128,42662129,42662130,42662131,42662132,42662133,42662134,42662135,42662136,42662137,42662138,42662139,42662140,42662141,42662142,42662143,42662144,42662145,42662146,42662147,42662148,42662149,42662150,42662151,42662152,42662153,42662154,42662155,42662156,42662157,42662158,42662159,42662160,42663001,42663002,42663003,42663004,42663005,42663006,42663007,42663008,42663009,42663010,42663011,42663012,42663013,42663014,42663015,42663016,42663017,42663018,42663019,42663020,42663021,42663022,42663023,42663024,42663025,42663026,42663027,42663028,42663029,42663030,42663031,42663032,42663033,42663034,42663035,42663036,42663037,42663038,42663039,42663040,42663041,42663042,42663043,42663044,42663045,42663046,42663047,42663048,42663049,42663050,42663051,42663052,42663053,42663054,42663055,42663056,42663057,42663058,42663059,42663060,42663061,42663062,42663063,42663064,42663065,42663066,42663067,42663068,42663069,42663070,42663071,42663072,42663073,42663074,42663075,42663076,42663077,42663078,42663079,42663080,42663081,42663082,42663083,42663084,42663085,42663086,42663087,42663088,42663089,42663090,42663091,42663092,42663093,42663094,42663095,42663096,42663097,42663098,42663099,42663000,42663101,42663102,42663103,42663104,42663105,42663106,42663107,42663108,42663109,42663110,42663111,42663112,42663113,42663114,42663115,42663116,42663117,42663118,42663119,42663120,42663121,42663122,42663123,42663124,42663125,42663126,42663127,42663128,42663129,42663130,42663131,42663132,42663133,42663134,42663135,42663136,42663137,42663138,42663139,42663140,42663141,42663142,42663143,42663144,42663145,42663146,42663147,42663148,42663149,42663150,42663151,42663152,42663153,42663154,42663155,42663156,42663157,42663158,42663159,42663160,42666001,42666002,42666003,42666004,42666005,42666006,42666007,42666008,42666009,42666010,42666011,42666012,42666013,42666014,42666015,42666016,42666017,42666018,42666019,42666020,42666021,42666022,42666023,42666024,42666025,42666026,42666027,42666028,42666029,42666030,42666031,42666032,42666033,42666034,42666035,42666036,42666037,42666038,42666039,42666040,42666041,42666042,42666043,42666044,42666045,42666046,42666047,42666048,42666049,42666050,42666051,42666052,42666053,42666054,42666055,42666056,42666057,42666058,42666059,42666060,42666061,42666062,42666063,42666064,42666065,42666066,42666067,42666068,42666069,42666070,42666071,42666072,42666073,42666074,42666075,42666076,42666077,42666078,42666079,42666080,42666081,42666082,42666083,42666084,42666085,42666086,42666087,42666088,42666089,42666090,42666091,42666092,42666093,42666094,42666095,42666096,42666097,42666098,42666099,42666100,42666101,42666102,42666103,42666104,42666105,42666106,42666107,42666108,42666109,42666110,42666111,42666112,42666113,42666114,42666115,42666116,42666117,42666118,42666119,42666120,42666121,42666122,42666123,42666124,42666125,42666126,42666127,42666128,42666129,42666130,42666131,42666132,42666133,42666134,42666135,42666136,42666137,42666138,42666139,42666140,42666141,42666142,42666143,42666144,42666145,42666146,42666147,42666148,42666149,42666150,42666151,42666152,42666153,42666154,42666155,42666156,42666157,42666158,42666159,42666160,42664001,42664002,42664003,42664004,42664005,42664006,42664007,42664008,42664009,42664010,42664011,42664012,42664013,42664014,42664015,42664016,42664017,42664018,42664019,42664020,42664021,42664022,42664023,42664024,42664025,42664026,42664027,42664028,42664029,42664030,42664031,42664032,42664033,42664034,42664035,42664036,42664037,42664038,42664039,42664040,42664041,42664042,42664043,42664044,42664045,42664046,42664047,42664048,42664049,42664050,42664051,42664052,42664053,42664054,42664055,42664056,42664057,42664058,42664059,42664060,42664061,42664062,42664063,42664064,42664065,42664066,42664067,42664068,42664069,42664070,42664071,42664072,42664073,42664074,42664075,42664076,42664077,42664078,42664079,42664080,42664081,42664082,42664083,42664084,42664085,42664086,42664087,42664088,42664089,42664090,42664091,42664092,42664093,42664094,42664095,42664096,42664097,42664098,42664099,42664100,42664101,42664102,42664103,42664104,42664105,42664106,42664107,42664108,42664109,42664110,42664111,42664112,42664113,42664114,42664115,42664116,42664117,42664118,42664119,42664120,42664121,42664122,42664123,42664124,42664125,42664126,42664127,42664128,42664129,42664130,42664131,42664132,42664133,42664134,42664135,42664136,42664137,42664138,42664139,42664140,42664141,42664142,42664143,42664144,42664145,42664146,42664147,42664148,42664149,42664150,42664151,42664152,42664153,42664154,42664155,42664156,42664157,42664158,42664159,42664160,42665001,42665002,42665003,42665004,42665005,42665006,42665007,42665008,42665009,42665010,42665011,42665012,42665013,42665014,42665015,42665016,42665017,42665018,42665019,42665020,42665021,42665022,42665023,42665024,42665025,42665026,42665027,42665028,42665029,42665030,42665031,42665032,42665033,42665034,42665035,42665036,42665037,42665038,42665039,42665040,42665041,42665042,42665043,42665044,42665045,42665046,42665047,42665048,42665049,42665050,42665051,42665052,42665053,42665054,42665055,42665056,42665057,42665058,42665059,42665060,42665061,42665062,42665063,42665064,42665065,42665066,42665067,42665068,42665069,42665070,42665071,42665072,42665073,42665074,42665075,42665076,42665077,42665078,42665079,42665080,42665081,42665082,42665083,42665084,42665085,42665086,42665087,42665088,42665089,42665090,42665091,42665092,42665093,42665094,42665095,42665096,42665097,42665098,42665099,42665100,42665101,42665102,42665103,42665104,42665105,42665106,42665107,42665108,42665109,42665110,42665111,42665112,42665113,42665114,42665115,42665116,42665117,42665118,42665119,42665120,42665121,42665122,42665123,42665124,42665125,42665126,42665127,42665128,42665129,42665130,42665131,42665132,42665133,42665134,42665135,42665136,42665137,42665138,42665139,42665140,42665141,42665142,42665143,42665144,42665145,42665146,42665147,42665148,42665149,42665150,42665151,42665152,42665153,42665154,42665155,42665156,42665157,42665158,42665159,42665160,42667001,42667002,42667003,42667004,42667005,42667006,42667007,42667008,42667009,42667010,42667011,42667012,42667013,42667014,42667015,42667016,42667017,42667018,42667019,42667020,42667021,42667022,42667023,42667024,42667025,42667026,42667027,42667028,42667029,42667030,42667031,42667032,42667033,42667034,42667035,42667036,42667037,42667038,42667039,42667040,42667041,42667042,42667043,42667044,42667045,42667046,42667047,42667048,42667049,42667050,42667051,42667052,42667053,42667054,42667055,42667056,42667057,42667058,42667059,42667060,42667061,42667062,42667063,42667064,42667065,42667066,42667067,42667068,42667069,42667070,42667071,42667072,42667073,42667074,42667075,42667076,42667077,42667078,42667079,42667080,42667081,42667082,42667083,42667084,42667085,42667086,42667087,42667088,42667089,42667090,42667091,42667092,42667093,42667094,42667095,42667096,42667097,42667098,42667099,42667100,42667101,42667102,42667103,42667104,42667105,42667106,42667107,42667108,42667109,42667110,42667111,42667112,42667113,42667114,42667115,42667116,42667117,42667118,42667119,42667120,42667121,42667122,42667123,42667124,42667125,42667126,42667127,42667128,42667129,42667130,42667131,42667132,42667133,42667134,42667135,42667136,42667137,42667138,42667139,42667140,42667141,42667142,42667143,42667144,42667145,42667146,42667147,42667148,42667149,42667150,42667151,42667152,42667153,42667154,42667155,42667156,42667157,42667158,42667159,42667160,42668001,42668002,42668003,42668004,42668005,42668006,42668007,42668008,42668009,42668010,42668011,42668012,42668013,42668014,42668015,42668016,42668017,42668018,42668019,42668020,42668021,42668022,42668023,42668024,42668025,42668026,42668027,42668028,42668029,42668030,42668031,42668032,42668033,42668034,42668035,42668036,42668037,42668038,42668039,42668040,42668041,42668042,42668043,42668044,42668045,42668046,42668047,42668048,42668049,42668050,42668051,42668052,42668053,42668054,42668055,42668056,42668057,42668058,42668059,42668060,42668061,42668062,42668063,42668064,42668065,42668066,42668067,42668068,42668069,42668070,42668071,42668072,42668073,42668074,42668075,42668076,42668077,42668078,42668079,42668080,42668081,42668082,42668083,42668084,42668085,42668086,42668087,42668088,42668089,42668090,42668091,42668092,42668093,42668094,42668095,42668096,42668097,42668098,42668099,42668100,42668101,42668102,42668103,42668104,42668105,42668106,42668107,42668108,42668109,42668110,42668111,42668112,42668113,42668114,42668115,42668116,42668117,42668118,42668119,42668120,42668121,42668122,42668123,42668124,42668125,42668126,42668127,42668128,42668129,42668130,42668131,42668132,42668133,42668134,42668135,42668136,42668137,42668138,42668139,42668140,42668141,42668142,42668143,42668144,42668145,42668146,42668147,42668148,42668149,42668150,42668151,42668152,42668153,42668154,42668155,42668156,42668157,42668158,42668159,42668160,42781001,42781002,42781003,42781004,42781005,42781006,42781007,42781008,42781009,42781010,42781011,42781012,42781013,42781014,42781015,42781016,42781017,42781018,42781019,42781020,42781021,42781022,42781023,42781024,42781025,42781026,42781027,42781028,42781029,42781030,42781031,42781032,42781033,42781034,42781035,42781036,42781037,42781038,42781039,42781040,42781041,42781042,42781043,42781044,42781045,42781046,42781047,42781048,42781049,42781050,42781051,42781052,42781053,42781054,42781055,42781056,42781057,42781058,42781059,42781060,42781061,42781062,42781063,42781064,42781065,42781066,42781067,42781068,42781069,42781070,42781071,42781072,42781073,42781074,42781075,42781076,42781077,42781078,42781079,42781080,42781081,42781082,42781083,42781084,42781085,42781086,42781087,42781088,42781089,42781090,42781091,42781092,42781093,42781094,42781095,42781096,42781097,42781098,42781099,42781100,42781101,42781102,42781103,42781104,42781105,42781106,42781107,42781108,42781109,42781110,42781111,42781112,42781113,42781114,42781115,42781116,42781117,42781118,42781119,42781120,42781121,42781122,42781123,42781124,42781125,42781126,42781127,42781128,42781129,42781130,42781131,42781132,42781133,42781134,42781135,42781136,42781137,42781138,42781139,42781140,42781141,42781142,42781143,42781144,42781145,42781146,42781147,42781148,42781149,42781150,42781151,42781152,42781153,42781154,42781155,42781156,42781157,42781158,42781159,42781160,42682001,42682002,42682003,42682004,42682005,42682006,42682007,42682008,42682009,42682010,42682011,42682012,42682013,42682014,42682015,42682016,42682017,42682018,42682019,42682020,42682021,42682022,42682023,42682024,42682025,42682026,42682027,42682028,42682029,42682030,42682031,42682032,42682033,42682034,42682035,42682036,42682037,42682038,42682039,42682040,42682041,42682042,42682043,42682044,42682045,42682046,42682047,42682048,42682049,42682050,42682051,42682052,42682053,42682054,42682055,42682056,42682057,42682058,42682059,42682060,42682061,42682062,42682063,42682064,42682065,42682066,42682067,42682068,42682069,42682070,42682071,42682072,42682073,42682074,42682075,42682076,42682077,42682078,42682079,42682080,42682081,42682082,42682083,42682084,42682085,42682086,42682087,42682088,42682089,42682090,42682091,42682092,42682093,42682094,42682095,42682096,42682097,42682098,42682099,42682100,42682101,42682102,42682103,42682104,42682105,42682106,42682107,42682108,42682109,42682110,42682111,42682112,42682113,42682114,42682115,42682116,42682117,42682118,42682119,42682120,42682121,42682122,42682123,42682124,42682125,42682126,42682127,42682128,42682129,42682130,42682131,42682132,42682133,42682134,42682135,42682136,42682137,42682138,42682139,42682140,42682141,42682142,42682143,42682144,42682145,42682146,42682147,42682148,42682149,42682150,42682151,42682152,42682153,42682154,42682155,42682156,42682157,42682158,42682159,42682160,42683001,42683002,42683003,42683004,42683005,42683006,42683007,42683008,42683009,42683010,42683011,42683012,42683013,42683014,42683015,42683016,42683017,42683018,42683019,42683020,42683021,42683022,42683023,42683024,42683025,42683026,42683027,42683028,42683029,42683030,42683031,42683032,42683033,42683034,42683035,42683036,42683037,42683038,42683039,42683040,42683041,42683042,42683043,42683044,42683045,42683046,42683047,42683048,42683049,42683050,42683051,42683052,42683053,42683054,42683055,42683056,42683057,42683058,42683059,42683060,42683061,42683062,42683063,42683064,42683065,42683066,42683067,42683068,42683069,42683070,42683071,42683072,42683073,42683074,42683075,42683076,42683077,42683078,42683079,42683080,42683081,42683082,42683083,42683084,42683085,42683086,42683087,42683088,42683089,42683090,42683091,42683092,42683093,42683094,42683095,42683096,42683097,42683098,42683099,42683000,42683101,42683102,42683103,42683104,42683105,42683106,42683107,42683108,42683109,42683110,42683111,42683112,42683113,42683114,42683115,42683116,42683117,42683118,42683119,42683120,42683121,42683122,42683123,42683124,42683125,42683126,42683127,42683128,42683129,42683130,42683131,42683132,42683133,42683134,42683135,42683136,42683137,42683138,42683139,42683140,42683141,42683142,42683143,42683144,42683145,42683146,42683147,42683148,42683149,42683150,42683151,42683152,42683153,42683154,42683155,42683156,42683157,42683158,42683159,42683160,42686001,42686002,42686003,42686004,42686005,42686006,42686007,42686008,42686009,42686010,42686011,42686012,42686013,42686014,42686015,42686016,42686017,42686018,42686019,42686020,42686021,42686022,42686023,42686024,42686025,42686026,42686027,42686028,42686029,42686030,42686031,42686032,42686033,42686034,42686035,42686036,42686037,42686038,42686039,42686040,42686041,42686042,42686043,42686044,42686045,42686046,42686047,42686048,42686049,42686050,42686051,42686052,42686053,42686054,42686055,42686056,42686057,42686058,42686059,42686060,42686061,42686062,42686063,42686064,42686065,42686066,42686067,42686068,42686069,42686070,42686071,42686072,42686073,42686074,42686075,42686076,42686077,42686078,42686079,42686080,42686081,42686082,42686083,42686084,42686085,42686086,42686087,42686088,42686089,42686090,42686091,42686092,42686093,42686094,42686095,42686096,42686097,42686098,42686099,42686100,42686101,42686102,42686103,42686104,42686105,42686106,42686107,42686108,42686109,42686110,42686111,42686112,42686113,42686114,42686115,42686116,42686117,42686118,42686119,42686120,42686121,42686122,42686123,42686124,42686125,42686126,42686127,42686128,42686129,42686130,42686131,42686132,42686133,42686134,42686135,42686136,42686137,42686138,42686139,42686140,42686141,42686142,42686143,42686144,42686145,42686146,42686147,42686148,42686149,42686150,42686151,42686152,42686153,42686154,42686155,42686156,42686157,42686158,42686159,42686160,42684001,42684002,42684003,42684004,42684005,42684006,42684007,42684008,42684009,42684010,42684011,42684012,42684013,42684014,42684015,42684016,42684017,42684018,42684019,42684020,42684021,42684022,42684023,42684024,42684025,42684026,42684027,42684028,42684029,42684030,42684031,42684032,42684033,42684034,42684035,42684036,42684037,42684038,42684039,42684040,42684041,42684042,42684043,42684044,42684045,42684046,42684047,42684048,42684049,42684050,42684051,42684052,42684053,42684054,42684055,42684056,42684057,42684058,42684059,42684060,42684061,42684062,42684063,42684064,42684065,42684066,42684067,42684068,42684069,42684070,42684071,42684072,42684073,42684074,42684075,42684076,42684077,42684078,42684079,42684080,42684081,42684082,42684083,42684084,42684085,42684086,42684087,42684088,42684089,42684090,42684091,42684092,42684093,42684094,42684095,42684096,42684097,42684098,42684099,42684100,42684101,42684102,42684103,42684104,42684105,42684106,42684107,42684108,42684109,42684110,42684111,42684112,42684113,42684114,42684115,42684116,42684117,42684118,42684119,42684120,42684121,42684122,42684123,42684124,42684125,42684126,42684127,42684128,42684129,42684130,42684131,42684132,42684133,42684134,42684135,42684136,42684137,42684138,42684139,42684140,42684141,42684142,42684143,42684144,42684145,42684146,42684147,42684148,42684149,42684150,42684151,42684152,42684153,42684154,42684155,42684156,42684157,42684158,42684159,42684160,42685001,42685002,42685003,42685004,42685005,42685006,42685007,42685008,42685009,42685010,42685011,42685012,42685013,42685014,42685015,42685016,42685017,42685018,42685019,42685020,42685021,42685022,42685023,42685024,42685025,42685026,42685027,42685028,42685029,42685030,42685031,42685032,42685033,42685034,42685035,42685036,42685037,42685038,42685039,42685040,42685041,42685042,42685043,42685044,42685045,42685046,42685047,42685048,42685049,42685050,42685051,42685052,42685053,42685054,42685055,42685056,42685057,42685058,42685059,42685060,42685061,42685062,42685063,42685064,42685065,42685066,42685067,42685068,42685069,42685070,42685071,42685072,42685073,42685074,42685075,42685076,42685077,42685078,42685079,42685080,42685081,42685082,42685083,42685084,42685085,42685086,42685087,42685088,42685089,42685090,42685091,42685092,42685093,42685094,42685095,42685096,42685097,42685098,42685099,42685100,42685101,42685102,42685103,42685104,42685105,42685106,42685107,42685108,42685109,42685110,42685111,42685112,42685113,42685114,42685115,42685116,42685117,42685118,42685119,42685120,42685121,42685122,42685123,42685124,42685125,42685126,42685127,42685128,42685129,42685130,42685131,42685132,42685133,42685134,42685135,42685136,42685137,42685138,42685139,42685140,42685141,42685142,42685143,42685144,42685145,42685146,42685147,42685148,42685149,42685150,42685151,42685152,42685153,42685154,42685155,42685156,42685157,42685158,42685159,42685160,42687001,42687002,42687003,42687004,42687005,42687006,42687007,42687008,42687009,42687010,42687011,42687012,42687013,42687014,42687015,42687016,42687017,42687018,42687019,42687020,42687021,42687022,42687023,42687024,42687025,42687026,42687027,42687028,42687029,42687030,42687031,42687032,42687033,42687034,42687035,42687036,42687037,42687038,42687039,42687040,42687041,42687042,42687043,42687044,42687045,42687046,42687047,42687048,42687049,42687050,42687051,42687052,42687053,42687054,42687055,42687056,42687057,42687058,42687059,42687060,42687061,42687062,42687063,42687064,42687065,42687066,42687067,42687068,42687069,42687070,42687071,42687072,42687073,42687074,42687075,42687076,42687077,42687078,42687079,42687080,42687081,42687082,42687083,42687084,42687085,42687086,42687087,42687088,42687089,42687090,42687091,42687092,42687093,42687094,42687095,42687096,42687097,42687098,42687099,42687100,42687101,42687102,42687103,42687104,42687105,42687106,42687107,42687108,42687109,42687110,42687111,42687112,42687113,42687114,42687115,42687116,42687117,42687118,42687119,42687120,42687121,42687122,42687123,42687124,42687125,42687126,42687127,42687128,42687129,42687130,42687131,42687132,42687133,42687134,42687135,42687136,42687137,42687138,42687139,42687140,42687141,42687142,42687143,42687144,42687145,42687146,42687147,42687148,42687149,42687150,42687151,42687152,42687153,42687154,42687155,42687156,42687157,42687158,42687159,42687160,42688001,42688002,42688003,42688004,42688005,42688006,42688007,42688008,42688009,42688010,42688011,42688012,42688013,42688014,42688015,42688016,42688017,42688018,42688019,42688020,42688021,42688022,42688023,42688024,42688025,42688026,42688027,42688028,42688029,42688030,42688031,42688032,42688033,42688034,42688035,42688036,42688037,42688038,42688039,42688040,42688041,42688042,42688043,42688044,42688045,42688046,42688047,42688048,42688049,42688050,42688051,42688052,42688053,42688054,42688055,42688056,42688057,42688058,42688059,42688060,42688061,42688062,42688063,42688064,42688065,42688066,42688067,42688068,42688069,42688070,42688071,42688072,42688073,42688074,42688075,42688076,42688077,42688078,42688079,42688080,42688081,42688082,42688083,42688084,42688085,42688086,42688087,42688088,42688089,42688090,42688091,42688092,42688093,42688094,42688095,42688096,42688097,42688098,42688099,42688100,42688101,42688102,42688103,42688104,42688105,42688106,42688107,42688108,42688109,42688110,42688111,42688112,42688113,42688114,42688115,42688116,42688117,42688118,42688119,42688120,42688121,42688122,42688123,42688124,42688125,42688126,42688127,42688128,42688129,42688130,42688131,42688132,42688133,42688134,42688135,42688136,42688137,42688138,42688139,42688140,42688141,42688142,42688143,42688144,42688145,42688146,42688147,42688148,42688149,42688150,42688151,42688152,42688153,42688154,42688155,42688156,42688157,42688158,42688159,42688160</t>
   </si>
   <si>
@@ -1954,6 +1951,10 @@
   </si>
   <si>
     <t>300001:12000_300002:12000_300003:12000</t>
+  </si>
+  <si>
+    <t>300001:102_300002:102_300003:102_0:101</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -4606,37 +4607,37 @@
         <v>1</v>
       </c>
       <c r="O35" s="4" t="s">
-        <v>598</v>
+        <v>592</v>
       </c>
       <c r="P35" s="4" t="s">
+        <v>606</v>
+      </c>
+      <c r="Q35" s="3" t="s">
         <v>599</v>
       </c>
-      <c r="Q35" s="3" t="s">
+      <c r="R35" s="1">
+        <v>0</v>
+      </c>
+      <c r="S35" s="1" t="s">
         <v>600</v>
       </c>
-      <c r="R35" s="1">
-        <v>0</v>
-      </c>
-      <c r="S35" s="1" t="s">
+      <c r="T35" s="1" t="s">
         <v>601</v>
       </c>
-      <c r="T35" s="1" t="s">
+      <c r="U35" s="1" t="s">
         <v>602</v>
       </c>
-      <c r="U35" s="1" t="s">
+      <c r="V35" s="1" t="s">
         <v>603</v>
-      </c>
-      <c r="V35" s="1" t="s">
-        <v>604</v>
       </c>
       <c r="W35" s="1" t="s">
         <v>586</v>
       </c>
       <c r="X35" s="3" t="s">
+        <v>604</v>
+      </c>
+      <c r="Y35" s="3" t="s">
         <v>605</v>
-      </c>
-      <c r="Y35" s="3" t="s">
-        <v>606</v>
       </c>
     </row>
     <row r="36" spans="1:25" x14ac:dyDescent="0.15">
@@ -4686,7 +4687,7 @@
         <v>598</v>
       </c>
       <c r="P36" s="4" t="s">
-        <v>599</v>
+        <v>606</v>
       </c>
       <c r="Q36" s="3" t="s">
         <v>231</v>
@@ -4695,25 +4696,25 @@
         <v>0</v>
       </c>
       <c r="S36" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="T36" s="1" t="s">
         <v>601</v>
       </c>
-      <c r="T36" s="1" t="s">
+      <c r="U36" s="1" t="s">
         <v>602</v>
       </c>
-      <c r="U36" s="1" t="s">
+      <c r="V36" s="1" t="s">
         <v>603</v>
-      </c>
-      <c r="V36" s="1" t="s">
-        <v>604</v>
       </c>
       <c r="W36" s="1" t="s">
         <v>586</v>
       </c>
       <c r="X36" s="3" t="s">
+        <v>604</v>
+      </c>
+      <c r="Y36" s="3" t="s">
         <v>605</v>
-      </c>
-      <c r="Y36" s="3" t="s">
-        <v>606</v>
       </c>
     </row>
     <row r="37" spans="1:25" x14ac:dyDescent="0.15">

--- a/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDBD88C3-AC85-418B-AB09-2BA1610B3272}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA9A08C9-D925-49D1-B57D-A5ED292F7AA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1559" uniqueCount="607">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1581" uniqueCount="650">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -784,18 +784,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>18,78,150,210,320,440,580</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>12,30,55,80,133,155,175,205,238</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>11,38,56</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>drop_id</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -840,10 +828,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>10001:240</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>MAP&lt;INT:INT&gt;_S_C</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1712,55 +1696,13 @@
     <t>1600001:101_0:101</t>
   </si>
   <si>
-    <t>20001:100_0:100</t>
-  </si>
-  <si>
-    <t>20001:101_0:101</t>
-  </si>
-  <si>
-    <t>30001:100_0:100</t>
-  </si>
-  <si>
-    <t>40001:100_0:100</t>
-  </si>
-  <si>
-    <t>40001:101_0:101</t>
-  </si>
-  <si>
-    <t>50001:100_0:100</t>
-  </si>
-  <si>
-    <t>50001:101_0:101</t>
-  </si>
-  <si>
-    <t>60001:100_0:100</t>
-  </si>
-  <si>
-    <t>60001:101_0:101</t>
-  </si>
-  <si>
-    <t>70001:100_0:100</t>
-  </si>
-  <si>
-    <t>70001:101_0:101</t>
-  </si>
-  <si>
     <t>80001:100_0:100</t>
   </si>
   <si>
-    <t>80001:101_0:101</t>
-  </si>
-  <si>
     <t>90001:100_0:100</t>
   </si>
   <si>
-    <t>90001:101_0:101</t>
-  </si>
-  <si>
     <t>100001:100_0:100</t>
-  </si>
-  <si>
-    <t>100001:101_0:101</t>
   </si>
   <si>
     <t>110001:1101_110002:1101_110003:1101_110004:1101_110005:1101_0:1101</t>
@@ -1795,18 +1737,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>10001:102_0:101</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10001:1101_0:100</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10001:150</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>120001:10000</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1819,10 +1749,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>10001:8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>monster_max_num</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1862,10 +1788,6 @@
     <t>210001:35</t>
   </si>
   <si>
-    <t>30001:101_0:101</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>0:0</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1955,6 +1877,229 @@
   <si>
     <t>300001:102_300002:102_300003:102_0:101</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10001:1_0:100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20001:2_0:100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>30001:3_0:100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>40001:4_0:100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>50001:5_50002:5_0:100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>60001:6_60002:6_0:100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>70001:7_70002:7_0:100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10001:102_0:102</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>30001:102_0:102</t>
+  </si>
+  <si>
+    <t>40001:102_0:102</t>
+  </si>
+  <si>
+    <t>80001:102_0:102</t>
+  </si>
+  <si>
+    <t>90001:102_0:102</t>
+  </si>
+  <si>
+    <t>100001:102_0:102</t>
+  </si>
+  <si>
+    <t>20001:102_0:102</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>70001:102_70002:102_0:102</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>60001:102_60002:102_0:102</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>50001:102_70002:102_0:102</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10001:99999999</t>
+  </si>
+  <si>
+    <t>10001:999999999</t>
+  </si>
+  <si>
+    <t>20001:0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>30001:0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>40001:0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>80001:0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>90001:0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>100001:0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>50001:0_50002:0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>60001:0_60002:0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>70001:0_70002:0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20001:99999999</t>
+  </si>
+  <si>
+    <t>30001:99999999</t>
+  </si>
+  <si>
+    <t>40001:99999999</t>
+  </si>
+  <si>
+    <t>50001:99999999_50002:99999999</t>
+  </si>
+  <si>
+    <t>60001:99999999_60002:99999999</t>
+  </si>
+  <si>
+    <t>70001:99999999_70002:99999999</t>
+  </si>
+  <si>
+    <t>80001:99999999</t>
+  </si>
+  <si>
+    <t>90001:99999999</t>
+  </si>
+  <si>
+    <t>100001:99999999</t>
+  </si>
+  <si>
+    <t>20001:999999999</t>
+  </si>
+  <si>
+    <t>30001:999999999</t>
+  </si>
+  <si>
+    <t>40001:999999999</t>
+  </si>
+  <si>
+    <t>50001:999999999_50002:999999999</t>
+  </si>
+  <si>
+    <t>60001:999999999_60002:999999999</t>
+  </si>
+  <si>
+    <t>70001:999999999_70002:999999999</t>
+  </si>
+  <si>
+    <t>80001:999999999</t>
+  </si>
+  <si>
+    <t>90001:999999999</t>
+  </si>
+  <si>
+    <t>100001:999999999</t>
+  </si>
+  <si>
+    <t>10001:40</t>
+  </si>
+  <si>
+    <t>20001:40</t>
+  </si>
+  <si>
+    <t>30001:40</t>
+  </si>
+  <si>
+    <t>40001:40</t>
+  </si>
+  <si>
+    <t>80001:40</t>
+  </si>
+  <si>
+    <t>90001:40</t>
+  </si>
+  <si>
+    <t>100001:40</t>
+  </si>
+  <si>
+    <t>50001:40_50002:50</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>60001:40_60002:50</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>70001:40_70002:50</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10001:10000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20001:10000</t>
+  </si>
+  <si>
+    <t>30001:10000</t>
+  </si>
+  <si>
+    <t>40001:10000</t>
+  </si>
+  <si>
+    <t>50001:10000_50002:10000</t>
+  </si>
+  <si>
+    <t>60001:10000_60002:10000</t>
+  </si>
+  <si>
+    <t>70001:10000_70002:10000</t>
+  </si>
+  <si>
+    <t>80001:10000</t>
+  </si>
+  <si>
+    <t>90001:10000</t>
+  </si>
+  <si>
+    <t>100001:10000</t>
   </si>
 </sst>
 </file>
@@ -2369,10 +2514,10 @@
         <v>220</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="Q2" s="1" t="s">
         <v>227</v>
@@ -2381,25 +2526,25 @@
         <v>205</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="W2" s="1" t="s">
         <v>205</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>583</v>
+        <v>560</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>583</v>
+        <v>560</v>
       </c>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.15">
@@ -2455,28 +2600,28 @@
         <v>225</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="S3" s="1" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="T3" s="1" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="U3" s="1" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="V3" s="1" t="s">
-        <v>570</v>
+        <v>548</v>
       </c>
       <c r="W3" s="5" t="s">
-        <v>572</v>
+        <v>550</v>
       </c>
       <c r="X3" s="1" t="s">
-        <v>584</v>
+        <v>561</v>
       </c>
       <c r="Y3" s="1" t="s">
-        <v>589</v>
+        <v>566</v>
       </c>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.15">
@@ -2532,28 +2677,28 @@
         <v>226</v>
       </c>
       <c r="R4" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="S4" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="T4" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="S4" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="T4" s="1" t="s">
-        <v>241</v>
-      </c>
       <c r="U4" s="1" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="V4" s="1" t="s">
-        <v>568</v>
+        <v>547</v>
       </c>
       <c r="W4" s="1" t="s">
-        <v>573</v>
+        <v>551</v>
       </c>
       <c r="X4" s="1" t="s">
-        <v>585</v>
+        <v>562</v>
       </c>
       <c r="Y4" s="1" t="s">
-        <v>588</v>
+        <v>565</v>
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.15">
@@ -2578,8 +2723,8 @@
       <c r="G5" s="1">
         <v>43400002</v>
       </c>
-      <c r="H5" s="1" t="s">
-        <v>236</v>
+      <c r="H5" s="1">
+        <v>0</v>
       </c>
       <c r="I5" s="1">
         <v>1</v>
@@ -2597,40 +2742,40 @@
         <v>215</v>
       </c>
       <c r="N5" s="1">
-        <v>150</v>
+        <v>1</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>564</v>
+        <v>584</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>563</v>
+        <v>591</v>
       </c>
       <c r="Q5" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="R5" s="1" t="s">
-        <v>239</v>
+      <c r="R5" s="1">
+        <v>0</v>
       </c>
       <c r="S5" s="1" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="T5" s="1" t="s">
-        <v>565</v>
+        <v>601</v>
       </c>
       <c r="U5" s="1" t="s">
-        <v>248</v>
+        <v>602</v>
       </c>
       <c r="V5" s="1" t="s">
-        <v>569</v>
+        <v>630</v>
       </c>
       <c r="W5" s="1">
         <v>0</v>
       </c>
       <c r="X5" s="3" t="s">
-        <v>582</v>
-      </c>
-      <c r="Y5" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
+      </c>
+      <c r="Y5" s="1" t="s">
+        <v>640</v>
       </c>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.15">
@@ -2655,8 +2800,8 @@
       <c r="G6" s="1">
         <v>43400002</v>
       </c>
-      <c r="H6" s="1" t="s">
-        <v>235</v>
+      <c r="H6" s="1">
+        <v>0</v>
       </c>
       <c r="I6" s="1">
         <v>1</v>
@@ -2674,28 +2819,40 @@
         <v>215</v>
       </c>
       <c r="N6" s="1">
-        <v>200</v>
+        <v>1</v>
       </c>
       <c r="O6" s="4" t="s">
-        <v>538</v>
+        <v>585</v>
       </c>
       <c r="P6" s="4" t="s">
-        <v>539</v>
+        <v>597</v>
       </c>
       <c r="Q6" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="R6" s="1" t="s">
-        <v>239</v>
+      <c r="R6" s="1">
+        <v>0</v>
+      </c>
+      <c r="S6" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="T6" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="U6" s="1" t="s">
+        <v>621</v>
+      </c>
+      <c r="V6" s="1" t="s">
+        <v>631</v>
       </c>
       <c r="W6" s="1">
         <v>0</v>
       </c>
       <c r="X6" s="3" t="s">
-        <v>582</v>
-      </c>
-      <c r="Y6" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
+      </c>
+      <c r="Y6" s="1" t="s">
+        <v>641</v>
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.15">
@@ -2720,8 +2877,8 @@
       <c r="G7" s="1">
         <v>43400002</v>
       </c>
-      <c r="H7" s="1" t="s">
-        <v>235</v>
+      <c r="H7" s="1">
+        <v>0</v>
       </c>
       <c r="I7" s="1">
         <v>1</v>
@@ -2739,28 +2896,40 @@
         <v>215</v>
       </c>
       <c r="N7" s="1">
-        <v>300</v>
+        <v>1</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>540</v>
+        <v>586</v>
       </c>
       <c r="P7" s="4" t="s">
-        <v>581</v>
+        <v>592</v>
       </c>
       <c r="Q7" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="R7" s="1" t="s">
-        <v>239</v>
+      <c r="R7" s="1">
+        <v>0</v>
+      </c>
+      <c r="S7" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="T7" s="1" t="s">
+        <v>613</v>
+      </c>
+      <c r="U7" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="V7" s="1" t="s">
+        <v>632</v>
       </c>
       <c r="W7" s="1">
         <v>0</v>
       </c>
       <c r="X7" s="3" t="s">
-        <v>582</v>
-      </c>
-      <c r="Y7" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
+      </c>
+      <c r="Y7" s="1" t="s">
+        <v>642</v>
       </c>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.15">
@@ -2785,8 +2954,8 @@
       <c r="G8" s="1">
         <v>43400002</v>
       </c>
-      <c r="H8" s="1" t="s">
-        <v>235</v>
+      <c r="H8" s="1">
+        <v>0</v>
       </c>
       <c r="I8" s="1">
         <v>1</v>
@@ -2804,28 +2973,40 @@
         <v>215</v>
       </c>
       <c r="N8" s="1">
-        <v>400</v>
+        <v>1</v>
       </c>
       <c r="O8" s="4" t="s">
-        <v>541</v>
+        <v>587</v>
       </c>
       <c r="P8" s="4" t="s">
-        <v>542</v>
+        <v>593</v>
       </c>
       <c r="Q8" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="R8" s="1" t="s">
-        <v>239</v>
+      <c r="R8" s="1">
+        <v>0</v>
+      </c>
+      <c r="S8" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="T8" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="U8" s="1" t="s">
+        <v>623</v>
+      </c>
+      <c r="V8" s="1" t="s">
+        <v>633</v>
       </c>
       <c r="W8" s="1">
         <v>0</v>
       </c>
       <c r="X8" s="3" t="s">
-        <v>582</v>
-      </c>
-      <c r="Y8" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
+      </c>
+      <c r="Y8" s="1" t="s">
+        <v>643</v>
       </c>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.15">
@@ -2850,8 +3031,8 @@
       <c r="G9" s="1">
         <v>43400002</v>
       </c>
-      <c r="H9" s="1" t="s">
-        <v>234</v>
+      <c r="H9" s="1">
+        <v>0</v>
       </c>
       <c r="I9" s="1">
         <v>1</v>
@@ -2869,28 +3050,40 @@
         <v>215</v>
       </c>
       <c r="N9" s="1">
-        <v>500</v>
+        <v>1</v>
       </c>
       <c r="O9" s="4" t="s">
-        <v>543</v>
+        <v>588</v>
       </c>
       <c r="P9" s="4" t="s">
-        <v>544</v>
+        <v>600</v>
       </c>
       <c r="Q9" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="R9" s="1" t="s">
-        <v>239</v>
+      <c r="R9" s="1">
+        <v>0</v>
+      </c>
+      <c r="S9" s="1" t="s">
+        <v>609</v>
+      </c>
+      <c r="T9" s="1" t="s">
+        <v>615</v>
+      </c>
+      <c r="U9" s="1" t="s">
+        <v>624</v>
+      </c>
+      <c r="V9" s="1" t="s">
+        <v>637</v>
       </c>
       <c r="W9" s="1">
         <v>0</v>
       </c>
       <c r="X9" s="3" t="s">
-        <v>582</v>
-      </c>
-      <c r="Y9" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
+      </c>
+      <c r="Y9" s="1" t="s">
+        <v>644</v>
       </c>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.15">
@@ -2915,8 +3108,8 @@
       <c r="G10" s="1">
         <v>43400002</v>
       </c>
-      <c r="H10" s="1" t="s">
-        <v>234</v>
+      <c r="H10" s="1">
+        <v>0</v>
       </c>
       <c r="I10" s="1">
         <v>1</v>
@@ -2934,28 +3127,40 @@
         <v>215</v>
       </c>
       <c r="N10" s="1">
-        <v>600</v>
+        <v>1</v>
       </c>
       <c r="O10" s="4" t="s">
-        <v>545</v>
+        <v>589</v>
       </c>
       <c r="P10" s="4" t="s">
-        <v>546</v>
+        <v>599</v>
       </c>
       <c r="Q10" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="R10" s="1" t="s">
-        <v>239</v>
+      <c r="R10" s="1">
+        <v>0</v>
+      </c>
+      <c r="S10" s="1" t="s">
+        <v>610</v>
+      </c>
+      <c r="T10" s="1" t="s">
+        <v>616</v>
+      </c>
+      <c r="U10" s="1" t="s">
+        <v>625</v>
+      </c>
+      <c r="V10" s="1" t="s">
+        <v>638</v>
       </c>
       <c r="W10" s="1">
         <v>0</v>
       </c>
       <c r="X10" s="3" t="s">
-        <v>582</v>
-      </c>
-      <c r="Y10" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
+      </c>
+      <c r="Y10" s="1" t="s">
+        <v>645</v>
       </c>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.15">
@@ -2999,28 +3204,40 @@
         <v>215</v>
       </c>
       <c r="N11" s="1">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="O11" s="4" t="s">
-        <v>547</v>
+        <v>590</v>
       </c>
       <c r="P11" s="4" t="s">
-        <v>548</v>
+        <v>598</v>
       </c>
       <c r="Q11" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R11" s="1">
-        <v>101</v>
+        <v>0</v>
+      </c>
+      <c r="S11" s="1" t="s">
+        <v>611</v>
+      </c>
+      <c r="T11" s="1" t="s">
+        <v>617</v>
+      </c>
+      <c r="U11" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="V11" s="1" t="s">
+        <v>639</v>
       </c>
       <c r="W11" s="1">
         <v>0</v>
       </c>
       <c r="X11" s="3" t="s">
-        <v>582</v>
-      </c>
-      <c r="Y11" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
+      </c>
+      <c r="Y11" s="1" t="s">
+        <v>646</v>
       </c>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.15">
@@ -3045,8 +3262,8 @@
       <c r="G12" s="1">
         <v>43400002</v>
       </c>
-      <c r="H12" s="1" t="s">
-        <v>202</v>
+      <c r="H12" s="1">
+        <v>0</v>
       </c>
       <c r="I12" s="1">
         <v>1</v>
@@ -3064,28 +3281,40 @@
         <v>215</v>
       </c>
       <c r="N12" s="1">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="O12" s="4" t="s">
-        <v>549</v>
+        <v>534</v>
       </c>
       <c r="P12" s="4" t="s">
-        <v>550</v>
+        <v>594</v>
       </c>
       <c r="Q12" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="R12" s="1" t="s">
-        <v>239</v>
+      <c r="R12" s="1">
+        <v>0</v>
+      </c>
+      <c r="S12" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="T12" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="U12" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="V12" s="1" t="s">
+        <v>634</v>
       </c>
       <c r="W12" s="1">
         <v>0</v>
       </c>
       <c r="X12" s="3" t="s">
-        <v>582</v>
-      </c>
-      <c r="Y12" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
+      </c>
+      <c r="Y12" s="1" t="s">
+        <v>647</v>
       </c>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.15">
@@ -3129,28 +3358,40 @@
         <v>215</v>
       </c>
       <c r="N13" s="1">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="O13" s="4" t="s">
-        <v>551</v>
+        <v>535</v>
       </c>
       <c r="P13" s="4" t="s">
-        <v>552</v>
+        <v>595</v>
       </c>
       <c r="Q13" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R13" s="1">
-        <v>101</v>
+        <v>0</v>
+      </c>
+      <c r="S13" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="T13" s="1" t="s">
+        <v>619</v>
+      </c>
+      <c r="U13" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="V13" s="1" t="s">
+        <v>635</v>
       </c>
       <c r="W13" s="1">
         <v>0</v>
       </c>
       <c r="X13" s="3" t="s">
-        <v>582</v>
-      </c>
-      <c r="Y13" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
+      </c>
+      <c r="Y13" s="1" t="s">
+        <v>648</v>
       </c>
     </row>
     <row r="14" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -3194,28 +3435,40 @@
         <v>215</v>
       </c>
       <c r="N14" s="1">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="O14" s="4" t="s">
-        <v>553</v>
+        <v>536</v>
       </c>
       <c r="P14" s="4" t="s">
-        <v>554</v>
+        <v>596</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R14" s="1">
-        <v>101</v>
+        <v>0</v>
+      </c>
+      <c r="S14" s="1" t="s">
+        <v>608</v>
+      </c>
+      <c r="T14" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="U14" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="V14" s="1" t="s">
+        <v>636</v>
       </c>
       <c r="W14" s="1">
         <v>0</v>
       </c>
       <c r="X14" s="3" t="s">
-        <v>582</v>
-      </c>
-      <c r="Y14" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
+      </c>
+      <c r="Y14" s="1" t="s">
+        <v>649</v>
       </c>
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.15">
@@ -3259,13 +3512,13 @@
         <v>215</v>
       </c>
       <c r="N15" s="1">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>555</v>
+        <v>537</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>556</v>
+        <v>538</v>
       </c>
       <c r="Q15" s="3" t="s">
         <v>231</v>
@@ -3274,22 +3527,22 @@
         <v>0</v>
       </c>
       <c r="S15" s="1" t="s">
-        <v>557</v>
+        <v>539</v>
       </c>
       <c r="T15" s="1" t="s">
-        <v>558</v>
+        <v>540</v>
       </c>
       <c r="U15" s="1" t="s">
-        <v>559</v>
+        <v>541</v>
       </c>
       <c r="W15" s="1" t="s">
-        <v>574</v>
+        <v>552</v>
       </c>
       <c r="X15" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y15" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.15">
@@ -3333,13 +3586,13 @@
         <v>215</v>
       </c>
       <c r="N16" s="1">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="O16" s="4" t="s">
-        <v>560</v>
+        <v>542</v>
       </c>
       <c r="P16" s="4" t="s">
-        <v>562</v>
+        <v>544</v>
       </c>
       <c r="Q16" s="3" t="s">
         <v>231</v>
@@ -3348,25 +3601,25 @@
         <v>0</v>
       </c>
       <c r="S16" s="1" t="s">
-        <v>561</v>
+        <v>543</v>
       </c>
       <c r="T16" s="1" t="s">
-        <v>566</v>
+        <v>545</v>
       </c>
       <c r="U16" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="V16" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="W16" s="1">
+        <v>0</v>
+      </c>
+      <c r="X16" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="Y16" s="1" t="s">
         <v>567</v>
-      </c>
-      <c r="V16" s="1" t="s">
-        <v>571</v>
-      </c>
-      <c r="W16" s="1">
-        <v>0</v>
-      </c>
-      <c r="X16" s="3" t="s">
-        <v>582</v>
-      </c>
-      <c r="Y16" s="1" t="s">
-        <v>590</v>
       </c>
     </row>
     <row r="17" spans="1:25" x14ac:dyDescent="0.15">
@@ -3413,25 +3666,25 @@
         <v>1</v>
       </c>
       <c r="O17" s="4" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="P17" s="4" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="Q17" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R17" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W17" s="1">
         <v>0</v>
       </c>
       <c r="X17" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y17" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="18" spans="1:25" x14ac:dyDescent="0.15">
@@ -3478,25 +3731,25 @@
         <v>100</v>
       </c>
       <c r="O18" s="4" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="P18" s="4" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="Q18" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R18" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W18" s="1">
         <v>0</v>
       </c>
       <c r="X18" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y18" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="19" spans="1:25" x14ac:dyDescent="0.15">
@@ -3543,25 +3796,25 @@
         <v>100</v>
       </c>
       <c r="O19" s="4" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="P19" s="4" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="Q19" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R19" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W19" s="1">
         <v>0</v>
       </c>
       <c r="X19" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y19" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="20" spans="1:25" x14ac:dyDescent="0.15">
@@ -3608,25 +3861,25 @@
         <v>100</v>
       </c>
       <c r="O20" s="4" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="P20" s="4" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="Q20" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R20" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W20" s="1">
         <v>0</v>
       </c>
       <c r="X20" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y20" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="21" spans="1:25" x14ac:dyDescent="0.15">
@@ -3673,25 +3926,25 @@
         <v>100</v>
       </c>
       <c r="O21" s="4" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="P21" s="4" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="Q21" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R21" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W21" s="1">
         <v>0</v>
       </c>
       <c r="X21" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y21" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="22" spans="1:25" x14ac:dyDescent="0.15">
@@ -3738,25 +3991,25 @@
         <v>100</v>
       </c>
       <c r="O22" s="4" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="P22" s="4" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="Q22" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R22" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W22" s="1">
         <v>0</v>
       </c>
       <c r="X22" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y22" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="23" spans="1:25" x14ac:dyDescent="0.15">
@@ -3803,25 +4056,25 @@
         <v>100</v>
       </c>
       <c r="O23" s="4" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="P23" s="4" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="Q23" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R23" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W23" s="1">
         <v>0</v>
       </c>
       <c r="X23" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y23" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="24" spans="1:25" x14ac:dyDescent="0.15">
@@ -3868,25 +4121,25 @@
         <v>100</v>
       </c>
       <c r="O24" s="4" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="P24" s="4" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="Q24" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R24" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W24" s="1">
         <v>0</v>
       </c>
       <c r="X24" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y24" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="25" spans="1:25" x14ac:dyDescent="0.15">
@@ -3933,10 +4186,10 @@
         <v>100</v>
       </c>
       <c r="O25" s="4" t="s">
-        <v>575</v>
+        <v>553</v>
       </c>
       <c r="P25" s="4" t="s">
-        <v>576</v>
+        <v>554</v>
       </c>
       <c r="Q25" s="3" t="s">
         <v>231</v>
@@ -3945,25 +4198,25 @@
         <v>0</v>
       </c>
       <c r="S25" s="1" t="s">
-        <v>577</v>
+        <v>555</v>
       </c>
       <c r="T25" s="1" t="s">
-        <v>578</v>
+        <v>556</v>
       </c>
       <c r="U25" s="1" t="s">
-        <v>579</v>
+        <v>557</v>
       </c>
       <c r="V25" s="1" t="s">
-        <v>580</v>
+        <v>558</v>
       </c>
       <c r="W25" s="1">
         <v>0</v>
       </c>
       <c r="X25" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y25" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="26" spans="1:25" x14ac:dyDescent="0.15">
@@ -4010,25 +4263,25 @@
         <v>100</v>
       </c>
       <c r="O26" s="4" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="P26" s="4" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="Q26" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R26" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W26" s="1">
         <v>0</v>
       </c>
       <c r="X26" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y26" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="27" spans="1:25" x14ac:dyDescent="0.15">
@@ -4075,25 +4328,25 @@
         <v>100</v>
       </c>
       <c r="O27" s="4" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="P27" s="4" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="Q27" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R27" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W27" s="1">
         <v>0</v>
       </c>
       <c r="X27" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y27" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="28" spans="1:25" x14ac:dyDescent="0.15">
@@ -4140,25 +4393,25 @@
         <v>100</v>
       </c>
       <c r="O28" s="4" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="P28" s="4" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="Q28" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R28" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W28" s="1">
         <v>0</v>
       </c>
       <c r="X28" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y28" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="29" spans="1:25" x14ac:dyDescent="0.15">
@@ -4205,25 +4458,25 @@
         <v>100</v>
       </c>
       <c r="O29" s="4" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="P29" s="4" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="Q29" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R29" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W29" s="1">
         <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y29" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="30" spans="1:25" x14ac:dyDescent="0.15">
@@ -4270,25 +4523,25 @@
         <v>100</v>
       </c>
       <c r="O30" s="4" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="P30" s="4" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="Q30" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R30" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W30" s="1">
         <v>0</v>
       </c>
       <c r="X30" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y30" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="31" spans="1:25" x14ac:dyDescent="0.15">
@@ -4335,25 +4588,25 @@
         <v>100</v>
       </c>
       <c r="O31" s="4" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="P31" s="4" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="Q31" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R31" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W31" s="1">
         <v>0</v>
       </c>
       <c r="X31" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y31" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="32" spans="1:25" x14ac:dyDescent="0.15">
@@ -4400,25 +4653,25 @@
         <v>100</v>
       </c>
       <c r="O32" s="4" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="P32" s="4" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="Q32" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R32" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W32" s="1">
         <v>0</v>
       </c>
       <c r="X32" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y32" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="33" spans="1:25" x14ac:dyDescent="0.15">
@@ -4465,25 +4718,25 @@
         <v>100</v>
       </c>
       <c r="O33" s="4" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="P33" s="4" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="Q33" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R33" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W33" s="1">
         <v>0</v>
       </c>
       <c r="X33" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y33" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="34" spans="1:25" x14ac:dyDescent="0.15">
@@ -4530,10 +4783,10 @@
         <v>1</v>
       </c>
       <c r="O34" s="4" t="s">
-        <v>592</v>
+        <v>569</v>
       </c>
       <c r="P34" s="4" t="s">
-        <v>591</v>
+        <v>568</v>
       </c>
       <c r="Q34" s="3" t="s">
         <v>231</v>
@@ -4542,25 +4795,25 @@
         <v>0</v>
       </c>
       <c r="S34" s="1" t="s">
-        <v>593</v>
+        <v>570</v>
       </c>
       <c r="T34" s="1" t="s">
-        <v>594</v>
+        <v>571</v>
       </c>
       <c r="U34" s="1" t="s">
-        <v>595</v>
+        <v>572</v>
       </c>
       <c r="V34" s="1" t="s">
-        <v>596</v>
+        <v>573</v>
       </c>
       <c r="W34" s="1" t="s">
-        <v>586</v>
+        <v>563</v>
       </c>
       <c r="X34" s="3" t="s">
-        <v>587</v>
+        <v>564</v>
       </c>
       <c r="Y34" s="3" t="s">
-        <v>597</v>
+        <v>574</v>
       </c>
     </row>
     <row r="35" spans="1:25" x14ac:dyDescent="0.15">
@@ -4607,37 +4860,37 @@
         <v>1</v>
       </c>
       <c r="O35" s="4" t="s">
-        <v>592</v>
+        <v>569</v>
       </c>
       <c r="P35" s="4" t="s">
-        <v>606</v>
+        <v>583</v>
       </c>
       <c r="Q35" s="3" t="s">
-        <v>599</v>
+        <v>576</v>
       </c>
       <c r="R35" s="1">
         <v>0</v>
       </c>
       <c r="S35" s="1" t="s">
-        <v>600</v>
+        <v>577</v>
       </c>
       <c r="T35" s="1" t="s">
-        <v>601</v>
+        <v>578</v>
       </c>
       <c r="U35" s="1" t="s">
-        <v>602</v>
+        <v>579</v>
       </c>
       <c r="V35" s="1" t="s">
-        <v>603</v>
+        <v>580</v>
       </c>
       <c r="W35" s="1" t="s">
-        <v>586</v>
+        <v>563</v>
       </c>
       <c r="X35" s="3" t="s">
-        <v>604</v>
+        <v>581</v>
       </c>
       <c r="Y35" s="3" t="s">
-        <v>605</v>
+        <v>582</v>
       </c>
     </row>
     <row r="36" spans="1:25" x14ac:dyDescent="0.15">
@@ -4684,10 +4937,10 @@
         <v>1</v>
       </c>
       <c r="O36" s="4" t="s">
-        <v>598</v>
+        <v>575</v>
       </c>
       <c r="P36" s="4" t="s">
-        <v>606</v>
+        <v>583</v>
       </c>
       <c r="Q36" s="3" t="s">
         <v>231</v>
@@ -4696,25 +4949,25 @@
         <v>0</v>
       </c>
       <c r="S36" s="1" t="s">
-        <v>600</v>
+        <v>577</v>
       </c>
       <c r="T36" s="1" t="s">
-        <v>601</v>
+        <v>578</v>
       </c>
       <c r="U36" s="1" t="s">
-        <v>602</v>
+        <v>579</v>
       </c>
       <c r="V36" s="1" t="s">
-        <v>603</v>
+        <v>580</v>
       </c>
       <c r="W36" s="1" t="s">
-        <v>586</v>
+        <v>563</v>
       </c>
       <c r="X36" s="3" t="s">
-        <v>604</v>
+        <v>581</v>
       </c>
       <c r="Y36" s="3" t="s">
-        <v>605</v>
+        <v>582</v>
       </c>
     </row>
     <row r="37" spans="1:25" x14ac:dyDescent="0.15">
@@ -4761,25 +5014,25 @@
         <v>100</v>
       </c>
       <c r="O37" s="4" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="P37" s="4" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="Q37" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R37" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W37" s="1">
         <v>0</v>
       </c>
       <c r="X37" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y37" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="38" spans="1:25" x14ac:dyDescent="0.15">
@@ -4826,25 +5079,25 @@
         <v>100</v>
       </c>
       <c r="O38" s="4" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="P38" s="4" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="Q38" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R38" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W38" s="1">
         <v>0</v>
       </c>
       <c r="X38" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y38" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="39" spans="1:25" x14ac:dyDescent="0.15">
@@ -4891,25 +5144,25 @@
         <v>100</v>
       </c>
       <c r="O39" s="4" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="P39" s="4" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="Q39" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R39" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W39" s="1">
         <v>0</v>
       </c>
       <c r="X39" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y39" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="40" spans="1:25" x14ac:dyDescent="0.15">
@@ -4956,25 +5209,25 @@
         <v>100</v>
       </c>
       <c r="O40" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="P40" s="4" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="Q40" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R40" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W40" s="1">
         <v>0</v>
       </c>
       <c r="X40" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y40" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="41" spans="1:25" x14ac:dyDescent="0.15">
@@ -5021,25 +5274,25 @@
         <v>100</v>
       </c>
       <c r="O41" s="4" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="P41" s="4" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="Q41" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R41" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W41" s="1">
         <v>0</v>
       </c>
       <c r="X41" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y41" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="42" spans="1:25" x14ac:dyDescent="0.15">
@@ -5086,25 +5339,25 @@
         <v>100</v>
       </c>
       <c r="O42" s="4" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="P42" s="4" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="Q42" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R42" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W42" s="1">
         <v>0</v>
       </c>
       <c r="X42" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y42" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="43" spans="1:25" x14ac:dyDescent="0.15">
@@ -5151,25 +5404,25 @@
         <v>100</v>
       </c>
       <c r="O43" s="4" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="P43" s="4" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="Q43" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R43" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W43" s="1">
         <v>0</v>
       </c>
       <c r="X43" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y43" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="44" spans="1:25" x14ac:dyDescent="0.15">
@@ -5216,25 +5469,25 @@
         <v>100</v>
       </c>
       <c r="O44" s="4" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="P44" s="4" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="Q44" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R44" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W44" s="1">
         <v>0</v>
       </c>
       <c r="X44" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y44" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="45" spans="1:25" x14ac:dyDescent="0.15">
@@ -5281,25 +5534,25 @@
         <v>100</v>
       </c>
       <c r="O45" s="4" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="P45" s="4" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="Q45" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R45" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W45" s="1">
         <v>0</v>
       </c>
       <c r="X45" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y45" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="46" spans="1:25" x14ac:dyDescent="0.15">
@@ -5346,25 +5599,25 @@
         <v>100</v>
       </c>
       <c r="O46" s="4" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="P46" s="4" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="Q46" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R46" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W46" s="1">
         <v>0</v>
       </c>
       <c r="X46" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y46" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="47" spans="1:25" x14ac:dyDescent="0.15">
@@ -5411,25 +5664,25 @@
         <v>100</v>
       </c>
       <c r="O47" s="4" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="P47" s="4" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="Q47" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R47" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W47" s="1">
         <v>0</v>
       </c>
       <c r="X47" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y47" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="48" spans="1:25" x14ac:dyDescent="0.15">
@@ -5476,25 +5729,25 @@
         <v>100</v>
       </c>
       <c r="O48" s="4" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="P48" s="4" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="Q48" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R48" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W48" s="1">
         <v>0</v>
       </c>
       <c r="X48" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y48" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="49" spans="1:25" x14ac:dyDescent="0.15">
@@ -5541,25 +5794,25 @@
         <v>100</v>
       </c>
       <c r="O49" s="4" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="P49" s="4" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="Q49" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R49" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W49" s="1">
         <v>0</v>
       </c>
       <c r="X49" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y49" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="50" spans="1:25" x14ac:dyDescent="0.15">
@@ -5606,25 +5859,25 @@
         <v>100</v>
       </c>
       <c r="O50" s="4" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="P50" s="4" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="Q50" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R50" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W50" s="1">
         <v>0</v>
       </c>
       <c r="X50" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y50" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="51" spans="1:25" x14ac:dyDescent="0.15">
@@ -5671,25 +5924,25 @@
         <v>100</v>
       </c>
       <c r="O51" s="4" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="P51" s="4" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="Q51" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R51" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W51" s="1">
         <v>0</v>
       </c>
       <c r="X51" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y51" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="52" spans="1:25" x14ac:dyDescent="0.15">
@@ -5736,25 +5989,25 @@
         <v>100</v>
       </c>
       <c r="O52" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="P52" s="4" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="Q52" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R52" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W52" s="1">
         <v>0</v>
       </c>
       <c r="X52" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y52" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="53" spans="1:25" x14ac:dyDescent="0.15">
@@ -5801,25 +6054,25 @@
         <v>100</v>
       </c>
       <c r="O53" s="4" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="P53" s="4" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="Q53" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R53" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W53" s="1">
         <v>0</v>
       </c>
       <c r="X53" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y53" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="54" spans="1:25" x14ac:dyDescent="0.15">
@@ -5866,25 +6119,25 @@
         <v>100</v>
       </c>
       <c r="O54" s="4" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="P54" s="4" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="Q54" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R54" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W54" s="1">
         <v>0</v>
       </c>
       <c r="X54" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y54" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="55" spans="1:25" x14ac:dyDescent="0.15">
@@ -5931,25 +6184,25 @@
         <v>100</v>
       </c>
       <c r="O55" s="4" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="P55" s="4" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="Q55" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R55" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W55" s="1">
         <v>0</v>
       </c>
       <c r="X55" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y55" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="56" spans="1:25" x14ac:dyDescent="0.15">
@@ -5996,25 +6249,25 @@
         <v>100</v>
       </c>
       <c r="O56" s="4" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="P56" s="4" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="Q56" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R56" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W56" s="1">
         <v>0</v>
       </c>
       <c r="X56" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y56" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="57" spans="1:25" x14ac:dyDescent="0.15">
@@ -6061,25 +6314,25 @@
         <v>100</v>
       </c>
       <c r="O57" s="4" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="P57" s="4" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="Q57" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R57" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W57" s="1">
         <v>0</v>
       </c>
       <c r="X57" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y57" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="58" spans="1:25" x14ac:dyDescent="0.15">
@@ -6126,25 +6379,25 @@
         <v>100</v>
       </c>
       <c r="O58" s="4" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="P58" s="4" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="Q58" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R58" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W58" s="1">
         <v>0</v>
       </c>
       <c r="X58" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y58" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="59" spans="1:25" x14ac:dyDescent="0.15">
@@ -6191,25 +6444,25 @@
         <v>100</v>
       </c>
       <c r="O59" s="4" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="P59" s="4" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="Q59" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R59" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W59" s="1">
         <v>0</v>
       </c>
       <c r="X59" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y59" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="60" spans="1:25" x14ac:dyDescent="0.15">
@@ -6256,25 +6509,25 @@
         <v>100</v>
       </c>
       <c r="O60" s="4" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="P60" s="4" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="Q60" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R60" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W60" s="1">
         <v>0</v>
       </c>
       <c r="X60" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y60" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="61" spans="1:25" x14ac:dyDescent="0.15">
@@ -6321,25 +6574,25 @@
         <v>100</v>
       </c>
       <c r="O61" s="4" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="P61" s="4" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="Q61" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R61" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W61" s="1">
         <v>0</v>
       </c>
       <c r="X61" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y61" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="62" spans="1:25" x14ac:dyDescent="0.15">
@@ -6386,25 +6639,25 @@
         <v>100</v>
       </c>
       <c r="O62" s="4" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="P62" s="4" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="Q62" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R62" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W62" s="1">
         <v>0</v>
       </c>
       <c r="X62" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y62" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="63" spans="1:25" x14ac:dyDescent="0.15">
@@ -6451,25 +6704,25 @@
         <v>100</v>
       </c>
       <c r="O63" s="4" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="P63" s="4" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="Q63" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R63" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W63" s="1">
         <v>0</v>
       </c>
       <c r="X63" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y63" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="64" spans="1:25" x14ac:dyDescent="0.15">
@@ -6516,25 +6769,25 @@
         <v>100</v>
       </c>
       <c r="O64" s="4" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="P64" s="4" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="Q64" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R64" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W64" s="1">
         <v>0</v>
       </c>
       <c r="X64" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y64" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="65" spans="1:25" x14ac:dyDescent="0.15">
@@ -6581,25 +6834,25 @@
         <v>100</v>
       </c>
       <c r="O65" s="4" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="P65" s="4" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="Q65" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R65" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W65" s="1">
         <v>0</v>
       </c>
       <c r="X65" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y65" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="66" spans="1:25" x14ac:dyDescent="0.15">
@@ -6646,25 +6899,25 @@
         <v>100</v>
       </c>
       <c r="O66" s="4" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="P66" s="4" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="Q66" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R66" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W66" s="1">
         <v>0</v>
       </c>
       <c r="X66" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y66" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="67" spans="1:25" x14ac:dyDescent="0.15">
@@ -6711,25 +6964,25 @@
         <v>100</v>
       </c>
       <c r="O67" s="4" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="P67" s="4" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="Q67" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R67" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W67" s="1">
         <v>0</v>
       </c>
       <c r="X67" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y67" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="68" spans="1:25" x14ac:dyDescent="0.15">
@@ -6776,25 +7029,25 @@
         <v>100</v>
       </c>
       <c r="O68" s="4" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="P68" s="4" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="Q68" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R68" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W68" s="1">
         <v>0</v>
       </c>
       <c r="X68" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y68" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="69" spans="1:25" x14ac:dyDescent="0.15">
@@ -6841,25 +7094,25 @@
         <v>100</v>
       </c>
       <c r="O69" s="4" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="P69" s="4" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="Q69" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R69" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W69" s="1">
         <v>0</v>
       </c>
       <c r="X69" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y69" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="70" spans="1:25" x14ac:dyDescent="0.15">
@@ -6906,25 +7159,25 @@
         <v>100</v>
       </c>
       <c r="O70" s="4" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="P70" s="4" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="Q70" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R70" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W70" s="1">
         <v>0</v>
       </c>
       <c r="X70" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y70" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="71" spans="1:25" x14ac:dyDescent="0.15">
@@ -6971,25 +7224,25 @@
         <v>100</v>
       </c>
       <c r="O71" s="4" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="P71" s="4" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="Q71" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R71" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W71" s="1">
         <v>0</v>
       </c>
       <c r="X71" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y71" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="72" spans="1:25" x14ac:dyDescent="0.15">
@@ -7036,25 +7289,25 @@
         <v>100</v>
       </c>
       <c r="O72" s="4" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="P72" s="4" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="Q72" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R72" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W72" s="1">
         <v>0</v>
       </c>
       <c r="X72" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y72" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="73" spans="1:25" x14ac:dyDescent="0.15">
@@ -7101,25 +7354,25 @@
         <v>100</v>
       </c>
       <c r="O73" s="4" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="P73" s="4" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="Q73" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R73" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W73" s="1">
         <v>0</v>
       </c>
       <c r="X73" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y73" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="74" spans="1:25" x14ac:dyDescent="0.15">
@@ -7166,25 +7419,25 @@
         <v>100</v>
       </c>
       <c r="O74" s="4" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="P74" s="4" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="Q74" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R74" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W74" s="1">
         <v>0</v>
       </c>
       <c r="X74" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y74" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="75" spans="1:25" x14ac:dyDescent="0.15">
@@ -7231,25 +7484,25 @@
         <v>100</v>
       </c>
       <c r="O75" s="4" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="P75" s="4" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="Q75" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R75" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W75" s="1">
         <v>0</v>
       </c>
       <c r="X75" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y75" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="76" spans="1:25" x14ac:dyDescent="0.15">
@@ -7296,25 +7549,25 @@
         <v>100</v>
       </c>
       <c r="O76" s="4" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="P76" s="4" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="Q76" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R76" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W76" s="1">
         <v>0</v>
       </c>
       <c r="X76" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y76" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="77" spans="1:25" x14ac:dyDescent="0.15">
@@ -7361,25 +7614,25 @@
         <v>100</v>
       </c>
       <c r="O77" s="4" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="P77" s="4" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="Q77" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R77" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W77" s="1">
         <v>0</v>
       </c>
       <c r="X77" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y77" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="78" spans="1:25" x14ac:dyDescent="0.15">
@@ -7426,25 +7679,25 @@
         <v>100</v>
       </c>
       <c r="O78" s="4" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="P78" s="4" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="Q78" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R78" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W78" s="1">
         <v>0</v>
       </c>
       <c r="X78" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y78" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="79" spans="1:25" x14ac:dyDescent="0.15">
@@ -7491,25 +7744,25 @@
         <v>100</v>
       </c>
       <c r="O79" s="4" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="P79" s="4" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="Q79" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R79" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W79" s="1">
         <v>0</v>
       </c>
       <c r="X79" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y79" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="80" spans="1:25" x14ac:dyDescent="0.15">
@@ -7556,25 +7809,25 @@
         <v>100</v>
       </c>
       <c r="O80" s="4" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="P80" s="4" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="Q80" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R80" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W80" s="1">
         <v>0</v>
       </c>
       <c r="X80" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y80" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="81" spans="1:25" x14ac:dyDescent="0.15">
@@ -7621,25 +7874,25 @@
         <v>100</v>
       </c>
       <c r="O81" s="4" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="P81" s="4" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="Q81" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R81" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W81" s="1">
         <v>0</v>
       </c>
       <c r="X81" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y81" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="82" spans="1:25" x14ac:dyDescent="0.15">
@@ -7686,25 +7939,25 @@
         <v>100</v>
       </c>
       <c r="O82" s="4" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="P82" s="4" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="Q82" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R82" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W82" s="1">
         <v>0</v>
       </c>
       <c r="X82" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y82" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="83" spans="1:25" x14ac:dyDescent="0.15">
@@ -7751,25 +8004,25 @@
         <v>100</v>
       </c>
       <c r="O83" s="4" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="P83" s="4" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="Q83" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R83" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W83" s="1">
         <v>0</v>
       </c>
       <c r="X83" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y83" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="84" spans="1:25" x14ac:dyDescent="0.15">
@@ -7816,25 +8069,25 @@
         <v>100</v>
       </c>
       <c r="O84" s="4" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="P84" s="4" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="Q84" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R84" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W84" s="1">
         <v>0</v>
       </c>
       <c r="X84" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y84" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="85" spans="1:25" x14ac:dyDescent="0.15">
@@ -7881,25 +8134,25 @@
         <v>100</v>
       </c>
       <c r="O85" s="4" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="P85" s="4" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="Q85" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R85" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W85" s="1">
         <v>0</v>
       </c>
       <c r="X85" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y85" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="86" spans="1:25" x14ac:dyDescent="0.15">
@@ -7946,25 +8199,25 @@
         <v>100</v>
       </c>
       <c r="O86" s="4" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="P86" s="4" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="Q86" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R86" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W86" s="1">
         <v>0</v>
       </c>
       <c r="X86" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y86" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="87" spans="1:25" x14ac:dyDescent="0.15">
@@ -8011,25 +8264,25 @@
         <v>100</v>
       </c>
       <c r="O87" s="4" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="P87" s="4" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="Q87" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R87" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W87" s="1">
         <v>0</v>
       </c>
       <c r="X87" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y87" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="88" spans="1:25" x14ac:dyDescent="0.15">
@@ -8076,25 +8329,25 @@
         <v>100</v>
       </c>
       <c r="O88" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="P88" s="4" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="Q88" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R88" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W88" s="1">
         <v>0</v>
       </c>
       <c r="X88" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y88" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="89" spans="1:25" x14ac:dyDescent="0.15">
@@ -8141,25 +8394,25 @@
         <v>100</v>
       </c>
       <c r="O89" s="4" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="P89" s="4" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="Q89" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R89" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W89" s="1">
         <v>0</v>
       </c>
       <c r="X89" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y89" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="90" spans="1:25" x14ac:dyDescent="0.15">
@@ -8206,25 +8459,25 @@
         <v>100</v>
       </c>
       <c r="O90" s="4" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="P90" s="4" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="Q90" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R90" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W90" s="1">
         <v>0</v>
       </c>
       <c r="X90" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y90" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="91" spans="1:25" x14ac:dyDescent="0.15">
@@ -8271,25 +8524,25 @@
         <v>100</v>
       </c>
       <c r="O91" s="4" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="P91" s="4" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="Q91" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R91" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W91" s="1">
         <v>0</v>
       </c>
       <c r="X91" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y91" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="92" spans="1:25" x14ac:dyDescent="0.15">
@@ -8336,25 +8589,25 @@
         <v>100</v>
       </c>
       <c r="O92" s="4" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="P92" s="4" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="Q92" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R92" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W92" s="1">
         <v>0</v>
       </c>
       <c r="X92" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y92" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="93" spans="1:25" x14ac:dyDescent="0.15">
@@ -8401,25 +8654,25 @@
         <v>100</v>
       </c>
       <c r="O93" s="4" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="P93" s="4" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="Q93" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R93" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W93" s="1">
         <v>0</v>
       </c>
       <c r="X93" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y93" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="94" spans="1:25" x14ac:dyDescent="0.15">
@@ -8466,25 +8719,25 @@
         <v>100</v>
       </c>
       <c r="O94" s="4" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="P94" s="4" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="Q94" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R94" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W94" s="1">
         <v>0</v>
       </c>
       <c r="X94" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y94" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="95" spans="1:25" x14ac:dyDescent="0.15">
@@ -8531,25 +8784,25 @@
         <v>100</v>
       </c>
       <c r="O95" s="4" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="P95" s="4" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="Q95" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R95" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W95" s="1">
         <v>0</v>
       </c>
       <c r="X95" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y95" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="96" spans="1:25" x14ac:dyDescent="0.15">
@@ -8596,25 +8849,25 @@
         <v>100</v>
       </c>
       <c r="O96" s="4" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="P96" s="4" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="Q96" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R96" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W96" s="1">
         <v>0</v>
       </c>
       <c r="X96" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y96" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="97" spans="1:25" x14ac:dyDescent="0.15">
@@ -8661,25 +8914,25 @@
         <v>100</v>
       </c>
       <c r="O97" s="4" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="P97" s="4" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="Q97" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R97" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W97" s="1">
         <v>0</v>
       </c>
       <c r="X97" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y97" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="98" spans="1:25" x14ac:dyDescent="0.15">
@@ -8726,25 +8979,25 @@
         <v>100</v>
       </c>
       <c r="O98" s="4" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="P98" s="4" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="Q98" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R98" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W98" s="1">
         <v>0</v>
       </c>
       <c r="X98" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y98" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="99" spans="1:25" x14ac:dyDescent="0.15">
@@ -8791,25 +9044,25 @@
         <v>100</v>
       </c>
       <c r="O99" s="4" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="P99" s="4" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="Q99" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R99" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W99" s="1">
         <v>0</v>
       </c>
       <c r="X99" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y99" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="100" spans="1:25" x14ac:dyDescent="0.15">
@@ -8856,25 +9109,25 @@
         <v>100</v>
       </c>
       <c r="O100" s="4" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="P100" s="4" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="Q100" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R100" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W100" s="1">
         <v>0</v>
       </c>
       <c r="X100" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y100" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="101" spans="1:25" x14ac:dyDescent="0.15">
@@ -8921,25 +9174,25 @@
         <v>100</v>
       </c>
       <c r="O101" s="4" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="P101" s="4" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="Q101" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R101" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W101" s="1">
         <v>0</v>
       </c>
       <c r="X101" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y101" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="102" spans="1:25" x14ac:dyDescent="0.15">
@@ -8986,25 +9239,25 @@
         <v>100</v>
       </c>
       <c r="O102" s="4" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="P102" s="4" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="Q102" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R102" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W102" s="1">
         <v>0</v>
       </c>
       <c r="X102" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y102" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="103" spans="1:25" x14ac:dyDescent="0.15">
@@ -9051,25 +9304,25 @@
         <v>100</v>
       </c>
       <c r="O103" s="4" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="P103" s="4" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="Q103" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R103" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W103" s="1">
         <v>0</v>
       </c>
       <c r="X103" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y103" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="104" spans="1:25" x14ac:dyDescent="0.15">
@@ -9116,25 +9369,25 @@
         <v>100</v>
       </c>
       <c r="O104" s="4" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="P104" s="4" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="Q104" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R104" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W104" s="1">
         <v>0</v>
       </c>
       <c r="X104" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y104" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="105" spans="1:25" x14ac:dyDescent="0.15">
@@ -9181,25 +9434,25 @@
         <v>100</v>
       </c>
       <c r="O105" s="4" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="P105" s="4" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="Q105" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R105" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W105" s="1">
         <v>0</v>
       </c>
       <c r="X105" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y105" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="106" spans="1:25" x14ac:dyDescent="0.15">
@@ -9246,25 +9499,25 @@
         <v>100</v>
       </c>
       <c r="O106" s="4" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="P106" s="4" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="Q106" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R106" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W106" s="1">
         <v>0</v>
       </c>
       <c r="X106" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y106" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="107" spans="1:25" x14ac:dyDescent="0.15">
@@ -9311,25 +9564,25 @@
         <v>100</v>
       </c>
       <c r="O107" s="4" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="P107" s="4" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="Q107" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R107" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W107" s="1">
         <v>0</v>
       </c>
       <c r="X107" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y107" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="108" spans="1:25" x14ac:dyDescent="0.15">
@@ -9376,25 +9629,25 @@
         <v>100</v>
       </c>
       <c r="O108" s="4" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="P108" s="4" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="Q108" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R108" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W108" s="1">
         <v>0</v>
       </c>
       <c r="X108" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y108" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="109" spans="1:25" x14ac:dyDescent="0.15">
@@ -9441,25 +9694,25 @@
         <v>100</v>
       </c>
       <c r="O109" s="4" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="P109" s="4" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="Q109" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R109" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W109" s="1">
         <v>0</v>
       </c>
       <c r="X109" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y109" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="110" spans="1:25" x14ac:dyDescent="0.15">
@@ -9506,25 +9759,25 @@
         <v>100</v>
       </c>
       <c r="O110" s="4" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="P110" s="4" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="Q110" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R110" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W110" s="1">
         <v>0</v>
       </c>
       <c r="X110" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y110" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="111" spans="1:25" x14ac:dyDescent="0.15">
@@ -9571,25 +9824,25 @@
         <v>100</v>
       </c>
       <c r="O111" s="4" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="P111" s="4" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="Q111" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R111" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W111" s="1">
         <v>0</v>
       </c>
       <c r="X111" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y111" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="112" spans="1:25" x14ac:dyDescent="0.15">
@@ -9636,25 +9889,25 @@
         <v>100</v>
       </c>
       <c r="O112" s="4" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="P112" s="4" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="Q112" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R112" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W112" s="1">
         <v>0</v>
       </c>
       <c r="X112" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y112" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="113" spans="1:25" x14ac:dyDescent="0.15">
@@ -9701,25 +9954,25 @@
         <v>100</v>
       </c>
       <c r="O113" s="4" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="P113" s="4" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="Q113" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R113" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W113" s="1">
         <v>0</v>
       </c>
       <c r="X113" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y113" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="114" spans="1:25" x14ac:dyDescent="0.15">
@@ -9766,25 +10019,25 @@
         <v>100</v>
       </c>
       <c r="O114" s="4" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="P114" s="4" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="Q114" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R114" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W114" s="1">
         <v>0</v>
       </c>
       <c r="X114" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y114" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="115" spans="1:25" x14ac:dyDescent="0.15">
@@ -9831,25 +10084,25 @@
         <v>100</v>
       </c>
       <c r="O115" s="4" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="P115" s="4" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="Q115" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R115" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W115" s="1">
         <v>0</v>
       </c>
       <c r="X115" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y115" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="116" spans="1:25" x14ac:dyDescent="0.15">
@@ -9896,25 +10149,25 @@
         <v>100</v>
       </c>
       <c r="O116" s="4" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="P116" s="4" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="Q116" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R116" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W116" s="1">
         <v>0</v>
       </c>
       <c r="X116" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y116" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="117" spans="1:25" x14ac:dyDescent="0.15">
@@ -9961,25 +10214,25 @@
         <v>100</v>
       </c>
       <c r="O117" s="4" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="P117" s="4" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="Q117" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R117" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W117" s="1">
         <v>0</v>
       </c>
       <c r="X117" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y117" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="118" spans="1:25" x14ac:dyDescent="0.15">
@@ -10026,25 +10279,25 @@
         <v>100</v>
       </c>
       <c r="O118" s="4" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="P118" s="4" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="Q118" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R118" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W118" s="1">
         <v>0</v>
       </c>
       <c r="X118" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y118" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="119" spans="1:25" x14ac:dyDescent="0.15">
@@ -10091,25 +10344,25 @@
         <v>100</v>
       </c>
       <c r="O119" s="4" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="P119" s="4" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="Q119" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R119" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W119" s="1">
         <v>0</v>
       </c>
       <c r="X119" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y119" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="120" spans="1:25" x14ac:dyDescent="0.15">
@@ -10156,25 +10409,25 @@
         <v>100</v>
       </c>
       <c r="O120" s="4" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="P120" s="4" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="Q120" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R120" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W120" s="1">
         <v>0</v>
       </c>
       <c r="X120" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y120" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="121" spans="1:25" x14ac:dyDescent="0.15">
@@ -10221,25 +10474,25 @@
         <v>100</v>
       </c>
       <c r="O121" s="4" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="P121" s="4" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="Q121" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R121" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W121" s="1">
         <v>0</v>
       </c>
       <c r="X121" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y121" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="122" spans="1:25" x14ac:dyDescent="0.15">
@@ -10286,25 +10539,25 @@
         <v>100</v>
       </c>
       <c r="O122" s="4" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="P122" s="4" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="Q122" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R122" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W122" s="1">
         <v>0</v>
       </c>
       <c r="X122" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y122" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="123" spans="1:25" x14ac:dyDescent="0.15">
@@ -10351,25 +10604,25 @@
         <v>100</v>
       </c>
       <c r="O123" s="4" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="P123" s="4" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="Q123" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R123" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W123" s="1">
         <v>0</v>
       </c>
       <c r="X123" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y123" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="124" spans="1:25" x14ac:dyDescent="0.15">
@@ -10416,25 +10669,25 @@
         <v>100</v>
       </c>
       <c r="O124" s="4" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="P124" s="4" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="Q124" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R124" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W124" s="1">
         <v>0</v>
       </c>
       <c r="X124" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y124" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="125" spans="1:25" x14ac:dyDescent="0.15">
@@ -10481,25 +10734,25 @@
         <v>100</v>
       </c>
       <c r="O125" s="4" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="P125" s="4" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="Q125" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R125" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W125" s="1">
         <v>0</v>
       </c>
       <c r="X125" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y125" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="126" spans="1:25" x14ac:dyDescent="0.15">
@@ -10546,25 +10799,25 @@
         <v>100</v>
       </c>
       <c r="O126" s="4" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="P126" s="4" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="Q126" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R126" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W126" s="1">
         <v>0</v>
       </c>
       <c r="X126" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y126" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="127" spans="1:25" x14ac:dyDescent="0.15">
@@ -10611,25 +10864,25 @@
         <v>100</v>
       </c>
       <c r="O127" s="4" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="P127" s="4" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="Q127" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R127" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W127" s="1">
         <v>0</v>
       </c>
       <c r="X127" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y127" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="128" spans="1:25" x14ac:dyDescent="0.15">
@@ -10676,25 +10929,25 @@
         <v>100</v>
       </c>
       <c r="O128" s="4" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="P128" s="4" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="Q128" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R128" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W128" s="1">
         <v>0</v>
       </c>
       <c r="X128" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y128" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="129" spans="1:25" x14ac:dyDescent="0.15">
@@ -10741,25 +10994,25 @@
         <v>100</v>
       </c>
       <c r="O129" s="4" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="P129" s="4" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="Q129" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R129" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W129" s="1">
         <v>0</v>
       </c>
       <c r="X129" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y129" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="130" spans="1:25" x14ac:dyDescent="0.15">
@@ -10806,25 +11059,25 @@
         <v>100</v>
       </c>
       <c r="O130" s="4" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="P130" s="4" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="Q130" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R130" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W130" s="1">
         <v>0</v>
       </c>
       <c r="X130" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y130" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="131" spans="1:25" x14ac:dyDescent="0.15">
@@ -10871,25 +11124,25 @@
         <v>100</v>
       </c>
       <c r="O131" s="4" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="P131" s="4" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="Q131" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R131" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W131" s="1">
         <v>0</v>
       </c>
       <c r="X131" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y131" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="132" spans="1:25" x14ac:dyDescent="0.15">
@@ -10936,25 +11189,25 @@
         <v>100</v>
       </c>
       <c r="O132" s="4" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="P132" s="4" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="Q132" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R132" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W132" s="1">
         <v>0</v>
       </c>
       <c r="X132" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y132" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="133" spans="1:25" x14ac:dyDescent="0.15">
@@ -11001,25 +11254,25 @@
         <v>100</v>
       </c>
       <c r="O133" s="4" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="P133" s="4" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="Q133" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R133" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W133" s="1">
         <v>0</v>
       </c>
       <c r="X133" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y133" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="134" spans="1:25" x14ac:dyDescent="0.15">
@@ -11066,25 +11319,25 @@
         <v>100</v>
       </c>
       <c r="O134" s="4" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="P134" s="4" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="Q134" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R134" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W134" s="1">
         <v>0</v>
       </c>
       <c r="X134" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y134" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="135" spans="1:25" x14ac:dyDescent="0.15">
@@ -11131,25 +11384,25 @@
         <v>100</v>
       </c>
       <c r="O135" s="4" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="P135" s="4" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="Q135" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R135" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W135" s="1">
         <v>0</v>
       </c>
       <c r="X135" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y135" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="136" spans="1:25" x14ac:dyDescent="0.15">
@@ -11196,25 +11449,25 @@
         <v>100</v>
       </c>
       <c r="O136" s="4" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="P136" s="4" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="Q136" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R136" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W136" s="1">
         <v>0</v>
       </c>
       <c r="X136" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y136" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="137" spans="1:25" x14ac:dyDescent="0.15">
@@ -11261,25 +11514,25 @@
         <v>100</v>
       </c>
       <c r="O137" s="4" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="P137" s="4" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="Q137" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R137" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W137" s="1">
         <v>0</v>
       </c>
       <c r="X137" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y137" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="138" spans="1:25" x14ac:dyDescent="0.15">
@@ -11326,25 +11579,25 @@
         <v>100</v>
       </c>
       <c r="O138" s="4" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="P138" s="4" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="Q138" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R138" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W138" s="1">
         <v>0</v>
       </c>
       <c r="X138" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y138" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="139" spans="1:25" x14ac:dyDescent="0.15">
@@ -11391,25 +11644,25 @@
         <v>100</v>
       </c>
       <c r="O139" s="4" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="P139" s="4" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="Q139" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R139" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W139" s="1">
         <v>0</v>
       </c>
       <c r="X139" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y139" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="140" spans="1:25" x14ac:dyDescent="0.15">
@@ -11456,25 +11709,25 @@
         <v>100</v>
       </c>
       <c r="O140" s="4" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="P140" s="4" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="Q140" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R140" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W140" s="1">
         <v>0</v>
       </c>
       <c r="X140" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y140" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="141" spans="1:25" x14ac:dyDescent="0.15">
@@ -11521,25 +11774,25 @@
         <v>100</v>
       </c>
       <c r="O141" s="4" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="P141" s="4" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="Q141" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R141" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W141" s="1">
         <v>0</v>
       </c>
       <c r="X141" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y141" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="142" spans="1:25" x14ac:dyDescent="0.15">
@@ -11586,25 +11839,25 @@
         <v>100</v>
       </c>
       <c r="O142" s="4" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="P142" s="4" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="Q142" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R142" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W142" s="1">
         <v>0</v>
       </c>
       <c r="X142" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y142" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="143" spans="1:25" x14ac:dyDescent="0.15">
@@ -11651,25 +11904,25 @@
         <v>100</v>
       </c>
       <c r="O143" s="4" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="P143" s="4" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="Q143" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R143" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W143" s="1">
         <v>0</v>
       </c>
       <c r="X143" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y143" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="144" spans="1:25" x14ac:dyDescent="0.15">
@@ -11716,25 +11969,25 @@
         <v>100</v>
       </c>
       <c r="O144" s="4" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="P144" s="4" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="Q144" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R144" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W144" s="1">
         <v>0</v>
       </c>
       <c r="X144" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y144" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="145" spans="1:25" x14ac:dyDescent="0.15">
@@ -11781,25 +12034,25 @@
         <v>100</v>
       </c>
       <c r="O145" s="4" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="P145" s="4" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="Q145" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R145" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W145" s="1">
         <v>0</v>
       </c>
       <c r="X145" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y145" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="146" spans="1:25" x14ac:dyDescent="0.15">
@@ -11846,25 +12099,25 @@
         <v>100</v>
       </c>
       <c r="O146" s="4" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="P146" s="4" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="Q146" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R146" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W146" s="1">
         <v>0</v>
       </c>
       <c r="X146" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y146" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="147" spans="1:25" x14ac:dyDescent="0.15">
@@ -11911,25 +12164,25 @@
         <v>100</v>
       </c>
       <c r="O147" s="4" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="P147" s="4" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="Q147" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R147" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W147" s="1">
         <v>0</v>
       </c>
       <c r="X147" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y147" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="148" spans="1:25" x14ac:dyDescent="0.15">
@@ -11976,25 +12229,25 @@
         <v>100</v>
       </c>
       <c r="O148" s="4" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="P148" s="4" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="Q148" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R148" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W148" s="1">
         <v>0</v>
       </c>
       <c r="X148" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y148" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="149" spans="1:25" x14ac:dyDescent="0.15">
@@ -12041,25 +12294,25 @@
         <v>100</v>
       </c>
       <c r="O149" s="4" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="P149" s="4" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="Q149" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R149" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W149" s="1">
         <v>0</v>
       </c>
       <c r="X149" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y149" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="150" spans="1:25" x14ac:dyDescent="0.15">
@@ -12106,25 +12359,25 @@
         <v>100</v>
       </c>
       <c r="O150" s="4" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="P150" s="4" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="Q150" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R150" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W150" s="1">
         <v>0</v>
       </c>
       <c r="X150" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y150" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="151" spans="1:25" x14ac:dyDescent="0.15">
@@ -12171,25 +12424,25 @@
         <v>100</v>
       </c>
       <c r="O151" s="4" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="P151" s="4" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="Q151" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R151" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W151" s="1">
         <v>0</v>
       </c>
       <c r="X151" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y151" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="152" spans="1:25" x14ac:dyDescent="0.15">
@@ -12236,25 +12489,25 @@
         <v>100</v>
       </c>
       <c r="O152" s="4" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="P152" s="4" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="Q152" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R152" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W152" s="1">
         <v>0</v>
       </c>
       <c r="X152" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y152" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="153" spans="1:25" x14ac:dyDescent="0.15">
@@ -12301,25 +12554,25 @@
         <v>100</v>
       </c>
       <c r="O153" s="4" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="P153" s="4" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="Q153" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R153" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W153" s="1">
         <v>0</v>
       </c>
       <c r="X153" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y153" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="154" spans="1:25" x14ac:dyDescent="0.15">
@@ -12366,25 +12619,25 @@
         <v>100</v>
       </c>
       <c r="O154" s="4" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="P154" s="4" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="Q154" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R154" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W154" s="1">
         <v>0</v>
       </c>
       <c r="X154" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y154" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="155" spans="1:25" x14ac:dyDescent="0.15">
@@ -12431,25 +12684,25 @@
         <v>100</v>
       </c>
       <c r="O155" s="4" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="P155" s="4" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="Q155" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R155" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W155" s="1">
         <v>0</v>
       </c>
       <c r="X155" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y155" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="156" spans="1:25" x14ac:dyDescent="0.15">
@@ -12496,25 +12749,25 @@
         <v>100</v>
       </c>
       <c r="O156" s="4" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="P156" s="4" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="Q156" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R156" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W156" s="1">
         <v>0</v>
       </c>
       <c r="X156" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y156" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="157" spans="1:25" x14ac:dyDescent="0.15">
@@ -12561,25 +12814,25 @@
         <v>100</v>
       </c>
       <c r="O157" s="4" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="P157" s="4" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="Q157" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R157" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W157" s="1">
         <v>0</v>
       </c>
       <c r="X157" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y157" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="158" spans="1:25" x14ac:dyDescent="0.15">
@@ -12626,25 +12879,25 @@
         <v>100</v>
       </c>
       <c r="O158" s="4" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="P158" s="4" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="Q158" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R158" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W158" s="1">
         <v>0</v>
       </c>
       <c r="X158" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y158" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="159" spans="1:25" x14ac:dyDescent="0.15">
@@ -12691,25 +12944,25 @@
         <v>100</v>
       </c>
       <c r="O159" s="4" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="P159" s="4" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="Q159" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R159" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W159" s="1">
         <v>0</v>
       </c>
       <c r="X159" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y159" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="160" spans="1:25" x14ac:dyDescent="0.15">
@@ -12756,25 +13009,25 @@
         <v>100</v>
       </c>
       <c r="O160" s="4" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="P160" s="4" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="Q160" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R160" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W160" s="1">
         <v>0</v>
       </c>
       <c r="X160" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y160" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="161" spans="1:25" x14ac:dyDescent="0.15">
@@ -12821,25 +13074,25 @@
         <v>100</v>
       </c>
       <c r="O161" s="4" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="P161" s="4" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="Q161" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R161" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W161" s="1">
         <v>0</v>
       </c>
       <c r="X161" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y161" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="162" spans="1:25" x14ac:dyDescent="0.15">
@@ -12886,25 +13139,25 @@
         <v>100</v>
       </c>
       <c r="O162" s="4" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="P162" s="4" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="Q162" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R162" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W162" s="1">
         <v>0</v>
       </c>
       <c r="X162" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y162" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="163" spans="1:25" x14ac:dyDescent="0.15">
@@ -12951,25 +13204,25 @@
         <v>100</v>
       </c>
       <c r="O163" s="4" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="P163" s="4" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="Q163" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R163" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W163" s="1">
         <v>0</v>
       </c>
       <c r="X163" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y163" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="164" spans="1:25" x14ac:dyDescent="0.15">
@@ -13016,25 +13269,25 @@
         <v>100</v>
       </c>
       <c r="O164" s="4" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="P164" s="4" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="Q164" s="3" t="s">
         <v>231</v>
       </c>
       <c r="R164" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W164" s="1">
         <v>0</v>
       </c>
       <c r="X164" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="Y164" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA9A08C9-D925-49D1-B57D-A5ED292F7AA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEA015FE-A0A6-4B8C-8802-2D4F3131AD66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_barries_v8" sheetId="1" r:id="rId1"/>
@@ -1733,10 +1733,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>120001:102_0:102</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>120001:10000</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2100,6 +2096,10 @@
   </si>
   <si>
     <t>100001:10000</t>
+  </si>
+  <si>
+    <t>120001:103_0:103</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2541,10 +2541,10 @@
         <v>205</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.15">
@@ -2612,16 +2612,16 @@
         <v>242</v>
       </c>
       <c r="V3" s="1" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="W3" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="X3" s="1" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="Y3" s="1" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.15">
@@ -2689,16 +2689,16 @@
         <v>239</v>
       </c>
       <c r="V4" s="1" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="W4" s="1" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="X4" s="1" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="Y4" s="1" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.15">
@@ -2745,10 +2745,10 @@
         <v>1</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="Q5" s="3" t="s">
         <v>231</v>
@@ -2760,22 +2760,22 @@
         <v>244</v>
       </c>
       <c r="T5" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="U5" s="1" t="s">
         <v>601</v>
       </c>
-      <c r="U5" s="1" t="s">
-        <v>602</v>
-      </c>
       <c r="V5" s="1" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="W5" s="1">
         <v>0</v>
       </c>
       <c r="X5" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y5" s="1" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.15">
@@ -2822,10 +2822,10 @@
         <v>1</v>
       </c>
       <c r="O6" s="4" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="P6" s="4" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="Q6" s="3" t="s">
         <v>231</v>
@@ -2834,25 +2834,25 @@
         <v>0</v>
       </c>
       <c r="S6" s="1" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="T6" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="U6" s="1" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="V6" s="1" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="W6" s="1">
         <v>0</v>
       </c>
       <c r="X6" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y6" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.15">
@@ -2899,10 +2899,10 @@
         <v>1</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="P7" s="4" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="Q7" s="3" t="s">
         <v>231</v>
@@ -2911,25 +2911,25 @@
         <v>0</v>
       </c>
       <c r="S7" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="T7" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="U7" s="1" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="V7" s="1" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="W7" s="1">
         <v>0</v>
       </c>
       <c r="X7" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y7" s="1" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.15">
@@ -2976,10 +2976,10 @@
         <v>1</v>
       </c>
       <c r="O8" s="4" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="P8" s="4" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="Q8" s="3" t="s">
         <v>231</v>
@@ -2988,25 +2988,25 @@
         <v>0</v>
       </c>
       <c r="S8" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="T8" s="1" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="U8" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="V8" s="1" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="W8" s="1">
         <v>0</v>
       </c>
       <c r="X8" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y8" s="1" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.15">
@@ -3053,10 +3053,10 @@
         <v>1</v>
       </c>
       <c r="O9" s="4" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="P9" s="4" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="Q9" s="3" t="s">
         <v>231</v>
@@ -3065,25 +3065,25 @@
         <v>0</v>
       </c>
       <c r="S9" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="T9" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="U9" s="1" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="V9" s="1" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="W9" s="1">
         <v>0</v>
       </c>
       <c r="X9" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y9" s="1" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.15">
@@ -3130,10 +3130,10 @@
         <v>1</v>
       </c>
       <c r="O10" s="4" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="P10" s="4" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="Q10" s="3" t="s">
         <v>231</v>
@@ -3142,25 +3142,25 @@
         <v>0</v>
       </c>
       <c r="S10" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="T10" s="1" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="U10" s="1" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="V10" s="1" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="W10" s="1">
         <v>0</v>
       </c>
       <c r="X10" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y10" s="1" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.15">
@@ -3207,10 +3207,10 @@
         <v>1</v>
       </c>
       <c r="O11" s="4" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="P11" s="4" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="Q11" s="3" t="s">
         <v>231</v>
@@ -3219,25 +3219,25 @@
         <v>0</v>
       </c>
       <c r="S11" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="T11" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="U11" s="1" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="V11" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="W11" s="1">
         <v>0</v>
       </c>
       <c r="X11" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y11" s="1" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.15">
@@ -3287,7 +3287,7 @@
         <v>534</v>
       </c>
       <c r="P12" s="4" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="Q12" s="3" t="s">
         <v>231</v>
@@ -3296,25 +3296,25 @@
         <v>0</v>
       </c>
       <c r="S12" s="1" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="T12" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="U12" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="V12" s="1" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="W12" s="1">
         <v>0</v>
       </c>
       <c r="X12" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y12" s="1" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.15">
@@ -3364,7 +3364,7 @@
         <v>535</v>
       </c>
       <c r="P13" s="4" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="Q13" s="3" t="s">
         <v>231</v>
@@ -3373,25 +3373,25 @@
         <v>0</v>
       </c>
       <c r="S13" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="T13" s="1" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="U13" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="V13" s="1" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="W13" s="1">
         <v>0</v>
       </c>
       <c r="X13" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y13" s="1" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
     </row>
     <row r="14" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -3441,7 +3441,7 @@
         <v>536</v>
       </c>
       <c r="P14" s="4" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>231</v>
@@ -3450,25 +3450,25 @@
         <v>0</v>
       </c>
       <c r="S14" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="T14" s="1" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="U14" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="V14" s="1" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="W14" s="1">
         <v>0</v>
       </c>
       <c r="X14" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y14" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.15">
@@ -3536,13 +3536,13 @@
         <v>541</v>
       </c>
       <c r="W15" s="1" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="X15" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y15" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.15">
@@ -3592,7 +3592,7 @@
         <v>542</v>
       </c>
       <c r="P16" s="4" t="s">
-        <v>544</v>
+        <v>649</v>
       </c>
       <c r="Q16" s="3" t="s">
         <v>231</v>
@@ -3604,22 +3604,22 @@
         <v>543</v>
       </c>
       <c r="T16" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="U16" s="1" t="s">
         <v>545</v>
       </c>
-      <c r="U16" s="1" t="s">
-        <v>546</v>
-      </c>
       <c r="V16" s="1" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="W16" s="1">
         <v>0</v>
       </c>
       <c r="X16" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y16" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="17" spans="1:25" x14ac:dyDescent="0.15">
@@ -3681,10 +3681,10 @@
         <v>0</v>
       </c>
       <c r="X17" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y17" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="18" spans="1:25" x14ac:dyDescent="0.15">
@@ -3746,10 +3746,10 @@
         <v>0</v>
       </c>
       <c r="X18" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y18" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="19" spans="1:25" x14ac:dyDescent="0.15">
@@ -3811,10 +3811,10 @@
         <v>0</v>
       </c>
       <c r="X19" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y19" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="20" spans="1:25" x14ac:dyDescent="0.15">
@@ -3876,10 +3876,10 @@
         <v>0</v>
       </c>
       <c r="X20" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y20" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="21" spans="1:25" x14ac:dyDescent="0.15">
@@ -3941,10 +3941,10 @@
         <v>0</v>
       </c>
       <c r="X21" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y21" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="22" spans="1:25" x14ac:dyDescent="0.15">
@@ -4006,10 +4006,10 @@
         <v>0</v>
       </c>
       <c r="X22" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y22" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="23" spans="1:25" x14ac:dyDescent="0.15">
@@ -4071,10 +4071,10 @@
         <v>0</v>
       </c>
       <c r="X23" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y23" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="24" spans="1:25" x14ac:dyDescent="0.15">
@@ -4136,10 +4136,10 @@
         <v>0</v>
       </c>
       <c r="X24" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y24" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="25" spans="1:25" x14ac:dyDescent="0.15">
@@ -4186,10 +4186,10 @@
         <v>100</v>
       </c>
       <c r="O25" s="4" t="s">
+        <v>552</v>
+      </c>
+      <c r="P25" s="4" t="s">
         <v>553</v>
-      </c>
-      <c r="P25" s="4" t="s">
-        <v>554</v>
       </c>
       <c r="Q25" s="3" t="s">
         <v>231</v>
@@ -4198,25 +4198,25 @@
         <v>0</v>
       </c>
       <c r="S25" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="T25" s="1" t="s">
         <v>555</v>
       </c>
-      <c r="T25" s="1" t="s">
+      <c r="U25" s="1" t="s">
         <v>556</v>
       </c>
-      <c r="U25" s="1" t="s">
+      <c r="V25" s="1" t="s">
         <v>557</v>
       </c>
-      <c r="V25" s="1" t="s">
-        <v>558</v>
-      </c>
       <c r="W25" s="1">
         <v>0</v>
       </c>
       <c r="X25" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y25" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="26" spans="1:25" x14ac:dyDescent="0.15">
@@ -4278,10 +4278,10 @@
         <v>0</v>
       </c>
       <c r="X26" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y26" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="27" spans="1:25" x14ac:dyDescent="0.15">
@@ -4343,10 +4343,10 @@
         <v>0</v>
       </c>
       <c r="X27" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y27" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="28" spans="1:25" x14ac:dyDescent="0.15">
@@ -4408,10 +4408,10 @@
         <v>0</v>
       </c>
       <c r="X28" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y28" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="29" spans="1:25" x14ac:dyDescent="0.15">
@@ -4473,10 +4473,10 @@
         <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y29" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="30" spans="1:25" x14ac:dyDescent="0.15">
@@ -4538,10 +4538,10 @@
         <v>0</v>
       </c>
       <c r="X30" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y30" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="31" spans="1:25" x14ac:dyDescent="0.15">
@@ -4603,10 +4603,10 @@
         <v>0</v>
       </c>
       <c r="X31" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y31" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="32" spans="1:25" x14ac:dyDescent="0.15">
@@ -4668,10 +4668,10 @@
         <v>0</v>
       </c>
       <c r="X32" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y32" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="33" spans="1:25" x14ac:dyDescent="0.15">
@@ -4733,10 +4733,10 @@
         <v>0</v>
       </c>
       <c r="X33" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y33" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="34" spans="1:25" x14ac:dyDescent="0.15">
@@ -4783,10 +4783,10 @@
         <v>1</v>
       </c>
       <c r="O34" s="4" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="P34" s="4" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="Q34" s="3" t="s">
         <v>231</v>
@@ -4795,25 +4795,25 @@
         <v>0</v>
       </c>
       <c r="S34" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="T34" s="1" t="s">
         <v>570</v>
       </c>
-      <c r="T34" s="1" t="s">
+      <c r="U34" s="1" t="s">
         <v>571</v>
       </c>
-      <c r="U34" s="1" t="s">
+      <c r="V34" s="1" t="s">
         <v>572</v>
       </c>
-      <c r="V34" s="1" t="s">
+      <c r="W34" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="X34" s="3" t="s">
+        <v>563</v>
+      </c>
+      <c r="Y34" s="3" t="s">
         <v>573</v>
-      </c>
-      <c r="W34" s="1" t="s">
-        <v>563</v>
-      </c>
-      <c r="X34" s="3" t="s">
-        <v>564</v>
-      </c>
-      <c r="Y34" s="3" t="s">
-        <v>574</v>
       </c>
     </row>
     <row r="35" spans="1:25" x14ac:dyDescent="0.15">
@@ -4860,37 +4860,37 @@
         <v>1</v>
       </c>
       <c r="O35" s="4" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="P35" s="4" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="Q35" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="R35" s="1">
+        <v>0</v>
+      </c>
+      <c r="S35" s="1" t="s">
         <v>576</v>
       </c>
-      <c r="R35" s="1">
-        <v>0</v>
-      </c>
-      <c r="S35" s="1" t="s">
+      <c r="T35" s="1" t="s">
         <v>577</v>
       </c>
-      <c r="T35" s="1" t="s">
+      <c r="U35" s="1" t="s">
         <v>578</v>
       </c>
-      <c r="U35" s="1" t="s">
+      <c r="V35" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="V35" s="1" t="s">
+      <c r="W35" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="X35" s="3" t="s">
         <v>580</v>
       </c>
-      <c r="W35" s="1" t="s">
-        <v>563</v>
-      </c>
-      <c r="X35" s="3" t="s">
+      <c r="Y35" s="3" t="s">
         <v>581</v>
-      </c>
-      <c r="Y35" s="3" t="s">
-        <v>582</v>
       </c>
     </row>
     <row r="36" spans="1:25" x14ac:dyDescent="0.15">
@@ -4937,10 +4937,10 @@
         <v>1</v>
       </c>
       <c r="O36" s="4" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="P36" s="4" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="Q36" s="3" t="s">
         <v>231</v>
@@ -4949,25 +4949,25 @@
         <v>0</v>
       </c>
       <c r="S36" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="T36" s="1" t="s">
         <v>577</v>
       </c>
-      <c r="T36" s="1" t="s">
+      <c r="U36" s="1" t="s">
         <v>578</v>
       </c>
-      <c r="U36" s="1" t="s">
+      <c r="V36" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="V36" s="1" t="s">
+      <c r="W36" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="X36" s="3" t="s">
         <v>580</v>
       </c>
-      <c r="W36" s="1" t="s">
-        <v>563</v>
-      </c>
-      <c r="X36" s="3" t="s">
+      <c r="Y36" s="3" t="s">
         <v>581</v>
-      </c>
-      <c r="Y36" s="3" t="s">
-        <v>582</v>
       </c>
     </row>
     <row r="37" spans="1:25" x14ac:dyDescent="0.15">
@@ -5029,10 +5029,10 @@
         <v>0</v>
       </c>
       <c r="X37" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y37" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="38" spans="1:25" x14ac:dyDescent="0.15">
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="X38" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y38" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="39" spans="1:25" x14ac:dyDescent="0.15">
@@ -5159,10 +5159,10 @@
         <v>0</v>
       </c>
       <c r="X39" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y39" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="40" spans="1:25" x14ac:dyDescent="0.15">
@@ -5224,10 +5224,10 @@
         <v>0</v>
       </c>
       <c r="X40" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y40" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="41" spans="1:25" x14ac:dyDescent="0.15">
@@ -5289,10 +5289,10 @@
         <v>0</v>
       </c>
       <c r="X41" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y41" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="42" spans="1:25" x14ac:dyDescent="0.15">
@@ -5354,10 +5354,10 @@
         <v>0</v>
       </c>
       <c r="X42" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y42" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="43" spans="1:25" x14ac:dyDescent="0.15">
@@ -5419,10 +5419,10 @@
         <v>0</v>
       </c>
       <c r="X43" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y43" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="44" spans="1:25" x14ac:dyDescent="0.15">
@@ -5484,10 +5484,10 @@
         <v>0</v>
       </c>
       <c r="X44" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y44" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="45" spans="1:25" x14ac:dyDescent="0.15">
@@ -5549,10 +5549,10 @@
         <v>0</v>
       </c>
       <c r="X45" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y45" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="46" spans="1:25" x14ac:dyDescent="0.15">
@@ -5614,10 +5614,10 @@
         <v>0</v>
       </c>
       <c r="X46" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y46" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="47" spans="1:25" x14ac:dyDescent="0.15">
@@ -5679,10 +5679,10 @@
         <v>0</v>
       </c>
       <c r="X47" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y47" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="48" spans="1:25" x14ac:dyDescent="0.15">
@@ -5744,10 +5744,10 @@
         <v>0</v>
       </c>
       <c r="X48" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y48" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="49" spans="1:25" x14ac:dyDescent="0.15">
@@ -5809,10 +5809,10 @@
         <v>0</v>
       </c>
       <c r="X49" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y49" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="50" spans="1:25" x14ac:dyDescent="0.15">
@@ -5874,10 +5874,10 @@
         <v>0</v>
       </c>
       <c r="X50" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y50" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="51" spans="1:25" x14ac:dyDescent="0.15">
@@ -5939,10 +5939,10 @@
         <v>0</v>
       </c>
       <c r="X51" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y51" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="52" spans="1:25" x14ac:dyDescent="0.15">
@@ -6004,10 +6004,10 @@
         <v>0</v>
       </c>
       <c r="X52" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y52" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="53" spans="1:25" x14ac:dyDescent="0.15">
@@ -6069,10 +6069,10 @@
         <v>0</v>
       </c>
       <c r="X53" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y53" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="54" spans="1:25" x14ac:dyDescent="0.15">
@@ -6134,10 +6134,10 @@
         <v>0</v>
       </c>
       <c r="X54" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y54" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="55" spans="1:25" x14ac:dyDescent="0.15">
@@ -6199,10 +6199,10 @@
         <v>0</v>
       </c>
       <c r="X55" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y55" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="56" spans="1:25" x14ac:dyDescent="0.15">
@@ -6264,10 +6264,10 @@
         <v>0</v>
       </c>
       <c r="X56" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y56" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="57" spans="1:25" x14ac:dyDescent="0.15">
@@ -6329,10 +6329,10 @@
         <v>0</v>
       </c>
       <c r="X57" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y57" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="58" spans="1:25" x14ac:dyDescent="0.15">
@@ -6394,10 +6394,10 @@
         <v>0</v>
       </c>
       <c r="X58" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y58" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="59" spans="1:25" x14ac:dyDescent="0.15">
@@ -6459,10 +6459,10 @@
         <v>0</v>
       </c>
       <c r="X59" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y59" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="60" spans="1:25" x14ac:dyDescent="0.15">
@@ -6524,10 +6524,10 @@
         <v>0</v>
       </c>
       <c r="X60" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y60" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="61" spans="1:25" x14ac:dyDescent="0.15">
@@ -6589,10 +6589,10 @@
         <v>0</v>
       </c>
       <c r="X61" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y61" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="62" spans="1:25" x14ac:dyDescent="0.15">
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="X62" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y62" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="63" spans="1:25" x14ac:dyDescent="0.15">
@@ -6719,10 +6719,10 @@
         <v>0</v>
       </c>
       <c r="X63" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y63" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="64" spans="1:25" x14ac:dyDescent="0.15">
@@ -6784,10 +6784,10 @@
         <v>0</v>
       </c>
       <c r="X64" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y64" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="65" spans="1:25" x14ac:dyDescent="0.15">
@@ -6849,10 +6849,10 @@
         <v>0</v>
       </c>
       <c r="X65" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y65" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="66" spans="1:25" x14ac:dyDescent="0.15">
@@ -6914,10 +6914,10 @@
         <v>0</v>
       </c>
       <c r="X66" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y66" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="67" spans="1:25" x14ac:dyDescent="0.15">
@@ -6979,10 +6979,10 @@
         <v>0</v>
       </c>
       <c r="X67" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y67" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="68" spans="1:25" x14ac:dyDescent="0.15">
@@ -7044,10 +7044,10 @@
         <v>0</v>
       </c>
       <c r="X68" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y68" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="69" spans="1:25" x14ac:dyDescent="0.15">
@@ -7109,10 +7109,10 @@
         <v>0</v>
       </c>
       <c r="X69" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y69" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="70" spans="1:25" x14ac:dyDescent="0.15">
@@ -7174,10 +7174,10 @@
         <v>0</v>
       </c>
       <c r="X70" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y70" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="71" spans="1:25" x14ac:dyDescent="0.15">
@@ -7239,10 +7239,10 @@
         <v>0</v>
       </c>
       <c r="X71" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y71" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="72" spans="1:25" x14ac:dyDescent="0.15">
@@ -7304,10 +7304,10 @@
         <v>0</v>
       </c>
       <c r="X72" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y72" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="73" spans="1:25" x14ac:dyDescent="0.15">
@@ -7369,10 +7369,10 @@
         <v>0</v>
       </c>
       <c r="X73" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y73" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="74" spans="1:25" x14ac:dyDescent="0.15">
@@ -7434,10 +7434,10 @@
         <v>0</v>
       </c>
       <c r="X74" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y74" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="75" spans="1:25" x14ac:dyDescent="0.15">
@@ -7499,10 +7499,10 @@
         <v>0</v>
       </c>
       <c r="X75" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y75" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="76" spans="1:25" x14ac:dyDescent="0.15">
@@ -7564,10 +7564,10 @@
         <v>0</v>
       </c>
       <c r="X76" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y76" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="77" spans="1:25" x14ac:dyDescent="0.15">
@@ -7629,10 +7629,10 @@
         <v>0</v>
       </c>
       <c r="X77" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y77" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="78" spans="1:25" x14ac:dyDescent="0.15">
@@ -7694,10 +7694,10 @@
         <v>0</v>
       </c>
       <c r="X78" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y78" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="79" spans="1:25" x14ac:dyDescent="0.15">
@@ -7759,10 +7759,10 @@
         <v>0</v>
       </c>
       <c r="X79" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y79" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="80" spans="1:25" x14ac:dyDescent="0.15">
@@ -7824,10 +7824,10 @@
         <v>0</v>
       </c>
       <c r="X80" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y80" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="81" spans="1:25" x14ac:dyDescent="0.15">
@@ -7889,10 +7889,10 @@
         <v>0</v>
       </c>
       <c r="X81" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y81" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="82" spans="1:25" x14ac:dyDescent="0.15">
@@ -7954,10 +7954,10 @@
         <v>0</v>
       </c>
       <c r="X82" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y82" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="83" spans="1:25" x14ac:dyDescent="0.15">
@@ -8019,10 +8019,10 @@
         <v>0</v>
       </c>
       <c r="X83" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y83" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="84" spans="1:25" x14ac:dyDescent="0.15">
@@ -8084,10 +8084,10 @@
         <v>0</v>
       </c>
       <c r="X84" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y84" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="85" spans="1:25" x14ac:dyDescent="0.15">
@@ -8149,10 +8149,10 @@
         <v>0</v>
       </c>
       <c r="X85" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y85" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="86" spans="1:25" x14ac:dyDescent="0.15">
@@ -8214,10 +8214,10 @@
         <v>0</v>
       </c>
       <c r="X86" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y86" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="87" spans="1:25" x14ac:dyDescent="0.15">
@@ -8279,10 +8279,10 @@
         <v>0</v>
       </c>
       <c r="X87" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y87" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="88" spans="1:25" x14ac:dyDescent="0.15">
@@ -8344,10 +8344,10 @@
         <v>0</v>
       </c>
       <c r="X88" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y88" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="89" spans="1:25" x14ac:dyDescent="0.15">
@@ -8409,10 +8409,10 @@
         <v>0</v>
       </c>
       <c r="X89" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y89" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="90" spans="1:25" x14ac:dyDescent="0.15">
@@ -8474,10 +8474,10 @@
         <v>0</v>
       </c>
       <c r="X90" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y90" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="91" spans="1:25" x14ac:dyDescent="0.15">
@@ -8539,10 +8539,10 @@
         <v>0</v>
       </c>
       <c r="X91" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y91" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="92" spans="1:25" x14ac:dyDescent="0.15">
@@ -8604,10 +8604,10 @@
         <v>0</v>
       </c>
       <c r="X92" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y92" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="93" spans="1:25" x14ac:dyDescent="0.15">
@@ -8669,10 +8669,10 @@
         <v>0</v>
       </c>
       <c r="X93" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y93" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="94" spans="1:25" x14ac:dyDescent="0.15">
@@ -8734,10 +8734,10 @@
         <v>0</v>
       </c>
       <c r="X94" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y94" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="95" spans="1:25" x14ac:dyDescent="0.15">
@@ -8799,10 +8799,10 @@
         <v>0</v>
       </c>
       <c r="X95" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y95" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="96" spans="1:25" x14ac:dyDescent="0.15">
@@ -8864,10 +8864,10 @@
         <v>0</v>
       </c>
       <c r="X96" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y96" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="97" spans="1:25" x14ac:dyDescent="0.15">
@@ -8929,10 +8929,10 @@
         <v>0</v>
       </c>
       <c r="X97" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y97" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="98" spans="1:25" x14ac:dyDescent="0.15">
@@ -8994,10 +8994,10 @@
         <v>0</v>
       </c>
       <c r="X98" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y98" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="99" spans="1:25" x14ac:dyDescent="0.15">
@@ -9059,10 +9059,10 @@
         <v>0</v>
       </c>
       <c r="X99" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y99" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="100" spans="1:25" x14ac:dyDescent="0.15">
@@ -9124,10 +9124,10 @@
         <v>0</v>
       </c>
       <c r="X100" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y100" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="101" spans="1:25" x14ac:dyDescent="0.15">
@@ -9189,10 +9189,10 @@
         <v>0</v>
       </c>
       <c r="X101" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y101" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="102" spans="1:25" x14ac:dyDescent="0.15">
@@ -9254,10 +9254,10 @@
         <v>0</v>
       </c>
       <c r="X102" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y102" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="103" spans="1:25" x14ac:dyDescent="0.15">
@@ -9319,10 +9319,10 @@
         <v>0</v>
       </c>
       <c r="X103" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y103" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="104" spans="1:25" x14ac:dyDescent="0.15">
@@ -9384,10 +9384,10 @@
         <v>0</v>
       </c>
       <c r="X104" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y104" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="105" spans="1:25" x14ac:dyDescent="0.15">
@@ -9449,10 +9449,10 @@
         <v>0</v>
       </c>
       <c r="X105" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y105" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="106" spans="1:25" x14ac:dyDescent="0.15">
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="X106" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y106" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="107" spans="1:25" x14ac:dyDescent="0.15">
@@ -9579,10 +9579,10 @@
         <v>0</v>
       </c>
       <c r="X107" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y107" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="108" spans="1:25" x14ac:dyDescent="0.15">
@@ -9644,10 +9644,10 @@
         <v>0</v>
       </c>
       <c r="X108" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y108" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="109" spans="1:25" x14ac:dyDescent="0.15">
@@ -9709,10 +9709,10 @@
         <v>0</v>
       </c>
       <c r="X109" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y109" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="110" spans="1:25" x14ac:dyDescent="0.15">
@@ -9774,10 +9774,10 @@
         <v>0</v>
       </c>
       <c r="X110" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y110" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="111" spans="1:25" x14ac:dyDescent="0.15">
@@ -9839,10 +9839,10 @@
         <v>0</v>
       </c>
       <c r="X111" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y111" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="112" spans="1:25" x14ac:dyDescent="0.15">
@@ -9904,10 +9904,10 @@
         <v>0</v>
       </c>
       <c r="X112" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y112" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="113" spans="1:25" x14ac:dyDescent="0.15">
@@ -9969,10 +9969,10 @@
         <v>0</v>
       </c>
       <c r="X113" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y113" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="114" spans="1:25" x14ac:dyDescent="0.15">
@@ -10034,10 +10034,10 @@
         <v>0</v>
       </c>
       <c r="X114" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y114" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="115" spans="1:25" x14ac:dyDescent="0.15">
@@ -10099,10 +10099,10 @@
         <v>0</v>
       </c>
       <c r="X115" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y115" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="116" spans="1:25" x14ac:dyDescent="0.15">
@@ -10164,10 +10164,10 @@
         <v>0</v>
       </c>
       <c r="X116" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y116" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="117" spans="1:25" x14ac:dyDescent="0.15">
@@ -10229,10 +10229,10 @@
         <v>0</v>
       </c>
       <c r="X117" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y117" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="118" spans="1:25" x14ac:dyDescent="0.15">
@@ -10294,10 +10294,10 @@
         <v>0</v>
       </c>
       <c r="X118" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y118" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="119" spans="1:25" x14ac:dyDescent="0.15">
@@ -10359,10 +10359,10 @@
         <v>0</v>
       </c>
       <c r="X119" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y119" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="120" spans="1:25" x14ac:dyDescent="0.15">
@@ -10424,10 +10424,10 @@
         <v>0</v>
       </c>
       <c r="X120" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y120" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="121" spans="1:25" x14ac:dyDescent="0.15">
@@ -10489,10 +10489,10 @@
         <v>0</v>
       </c>
       <c r="X121" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y121" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="122" spans="1:25" x14ac:dyDescent="0.15">
@@ -10554,10 +10554,10 @@
         <v>0</v>
       </c>
       <c r="X122" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y122" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="123" spans="1:25" x14ac:dyDescent="0.15">
@@ -10619,10 +10619,10 @@
         <v>0</v>
       </c>
       <c r="X123" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y123" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="124" spans="1:25" x14ac:dyDescent="0.15">
@@ -10684,10 +10684,10 @@
         <v>0</v>
       </c>
       <c r="X124" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y124" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="125" spans="1:25" x14ac:dyDescent="0.15">
@@ -10749,10 +10749,10 @@
         <v>0</v>
       </c>
       <c r="X125" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y125" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="126" spans="1:25" x14ac:dyDescent="0.15">
@@ -10814,10 +10814,10 @@
         <v>0</v>
       </c>
       <c r="X126" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y126" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="127" spans="1:25" x14ac:dyDescent="0.15">
@@ -10879,10 +10879,10 @@
         <v>0</v>
       </c>
       <c r="X127" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y127" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="128" spans="1:25" x14ac:dyDescent="0.15">
@@ -10944,10 +10944,10 @@
         <v>0</v>
       </c>
       <c r="X128" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y128" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="129" spans="1:25" x14ac:dyDescent="0.15">
@@ -11009,10 +11009,10 @@
         <v>0</v>
       </c>
       <c r="X129" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y129" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="130" spans="1:25" x14ac:dyDescent="0.15">
@@ -11074,10 +11074,10 @@
         <v>0</v>
       </c>
       <c r="X130" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y130" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="131" spans="1:25" x14ac:dyDescent="0.15">
@@ -11139,10 +11139,10 @@
         <v>0</v>
       </c>
       <c r="X131" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y131" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="132" spans="1:25" x14ac:dyDescent="0.15">
@@ -11204,10 +11204,10 @@
         <v>0</v>
       </c>
       <c r="X132" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y132" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="133" spans="1:25" x14ac:dyDescent="0.15">
@@ -11269,10 +11269,10 @@
         <v>0</v>
       </c>
       <c r="X133" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y133" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="134" spans="1:25" x14ac:dyDescent="0.15">
@@ -11334,10 +11334,10 @@
         <v>0</v>
       </c>
       <c r="X134" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y134" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="135" spans="1:25" x14ac:dyDescent="0.15">
@@ -11399,10 +11399,10 @@
         <v>0</v>
       </c>
       <c r="X135" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y135" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="136" spans="1:25" x14ac:dyDescent="0.15">
@@ -11464,10 +11464,10 @@
         <v>0</v>
       </c>
       <c r="X136" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y136" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="137" spans="1:25" x14ac:dyDescent="0.15">
@@ -11529,10 +11529,10 @@
         <v>0</v>
       </c>
       <c r="X137" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y137" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="138" spans="1:25" x14ac:dyDescent="0.15">
@@ -11594,10 +11594,10 @@
         <v>0</v>
       </c>
       <c r="X138" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y138" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="139" spans="1:25" x14ac:dyDescent="0.15">
@@ -11659,10 +11659,10 @@
         <v>0</v>
       </c>
       <c r="X139" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y139" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="140" spans="1:25" x14ac:dyDescent="0.15">
@@ -11724,10 +11724,10 @@
         <v>0</v>
       </c>
       <c r="X140" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y140" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="141" spans="1:25" x14ac:dyDescent="0.15">
@@ -11789,10 +11789,10 @@
         <v>0</v>
       </c>
       <c r="X141" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y141" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="142" spans="1:25" x14ac:dyDescent="0.15">
@@ -11854,10 +11854,10 @@
         <v>0</v>
       </c>
       <c r="X142" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y142" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="143" spans="1:25" x14ac:dyDescent="0.15">
@@ -11919,10 +11919,10 @@
         <v>0</v>
       </c>
       <c r="X143" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y143" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="144" spans="1:25" x14ac:dyDescent="0.15">
@@ -11984,10 +11984,10 @@
         <v>0</v>
       </c>
       <c r="X144" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y144" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="145" spans="1:25" x14ac:dyDescent="0.15">
@@ -12049,10 +12049,10 @@
         <v>0</v>
       </c>
       <c r="X145" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y145" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="146" spans="1:25" x14ac:dyDescent="0.15">
@@ -12114,10 +12114,10 @@
         <v>0</v>
       </c>
       <c r="X146" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y146" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="147" spans="1:25" x14ac:dyDescent="0.15">
@@ -12179,10 +12179,10 @@
         <v>0</v>
       </c>
       <c r="X147" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y147" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="148" spans="1:25" x14ac:dyDescent="0.15">
@@ -12244,10 +12244,10 @@
         <v>0</v>
       </c>
       <c r="X148" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y148" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="149" spans="1:25" x14ac:dyDescent="0.15">
@@ -12309,10 +12309,10 @@
         <v>0</v>
       </c>
       <c r="X149" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y149" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="150" spans="1:25" x14ac:dyDescent="0.15">
@@ -12374,10 +12374,10 @@
         <v>0</v>
       </c>
       <c r="X150" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y150" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="151" spans="1:25" x14ac:dyDescent="0.15">
@@ -12439,10 +12439,10 @@
         <v>0</v>
       </c>
       <c r="X151" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y151" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="152" spans="1:25" x14ac:dyDescent="0.15">
@@ -12504,10 +12504,10 @@
         <v>0</v>
       </c>
       <c r="X152" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y152" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="153" spans="1:25" x14ac:dyDescent="0.15">
@@ -12569,10 +12569,10 @@
         <v>0</v>
       </c>
       <c r="X153" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y153" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="154" spans="1:25" x14ac:dyDescent="0.15">
@@ -12634,10 +12634,10 @@
         <v>0</v>
       </c>
       <c r="X154" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y154" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="155" spans="1:25" x14ac:dyDescent="0.15">
@@ -12699,10 +12699,10 @@
         <v>0</v>
       </c>
       <c r="X155" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y155" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="156" spans="1:25" x14ac:dyDescent="0.15">
@@ -12764,10 +12764,10 @@
         <v>0</v>
       </c>
       <c r="X156" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y156" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="157" spans="1:25" x14ac:dyDescent="0.15">
@@ -12829,10 +12829,10 @@
         <v>0</v>
       </c>
       <c r="X157" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y157" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="158" spans="1:25" x14ac:dyDescent="0.15">
@@ -12894,10 +12894,10 @@
         <v>0</v>
       </c>
       <c r="X158" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y158" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="159" spans="1:25" x14ac:dyDescent="0.15">
@@ -12959,10 +12959,10 @@
         <v>0</v>
       </c>
       <c r="X159" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y159" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="160" spans="1:25" x14ac:dyDescent="0.15">
@@ -13024,10 +13024,10 @@
         <v>0</v>
       </c>
       <c r="X160" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y160" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="161" spans="1:25" x14ac:dyDescent="0.15">
@@ -13089,10 +13089,10 @@
         <v>0</v>
       </c>
       <c r="X161" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y161" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="162" spans="1:25" x14ac:dyDescent="0.15">
@@ -13154,10 +13154,10 @@
         <v>0</v>
       </c>
       <c r="X162" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y162" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="163" spans="1:25" x14ac:dyDescent="0.15">
@@ -13219,10 +13219,10 @@
         <v>0</v>
       </c>
       <c r="X163" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y163" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="164" spans="1:25" x14ac:dyDescent="0.15">
@@ -13284,10 +13284,10 @@
         <v>0</v>
       </c>
       <c r="X164" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y164" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEA015FE-A0A6-4B8C-8802-2D4F3131AD66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3BD5473-BD8E-4069-B30E-888DF6168831}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_barries_v8" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1581" uniqueCount="650">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1581" uniqueCount="655">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1956,18 +1956,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>80001:0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>90001:0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>100001:0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>50001:0_50002:0</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1998,15 +1986,6 @@
     <t>70001:99999999_70002:99999999</t>
   </si>
   <si>
-    <t>80001:99999999</t>
-  </si>
-  <si>
-    <t>90001:99999999</t>
-  </si>
-  <si>
-    <t>100001:99999999</t>
-  </si>
-  <si>
     <t>20001:999999999</t>
   </si>
   <si>
@@ -2025,15 +2004,6 @@
     <t>70001:999999999_70002:999999999</t>
   </si>
   <si>
-    <t>80001:999999999</t>
-  </si>
-  <si>
-    <t>90001:999999999</t>
-  </si>
-  <si>
-    <t>100001:999999999</t>
-  </si>
-  <si>
     <t>10001:40</t>
   </si>
   <si>
@@ -2044,15 +2014,6 @@
   </si>
   <si>
     <t>40001:40</t>
-  </si>
-  <si>
-    <t>80001:40</t>
-  </si>
-  <si>
-    <t>90001:40</t>
-  </si>
-  <si>
-    <t>100001:40</t>
   </si>
   <si>
     <t>50001:40_50002:50</t>
@@ -2099,6 +2060,74 @@
   </si>
   <si>
     <t>120001:103_0:103</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>80001:0_80002:0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>90001:0_90002:0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>100001:0_100002:0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>80001:99999999_80002:99999999</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>90001:99999999_90002:99999999</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>100001:99999999_100002:99999999</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>80001:999999999_80002:999999999</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>90001:999999999_90002:999999999</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>100001:999999999_90002:999999999</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>80001:40_80002:50</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>90001:40_90002:50</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>100001:40_100002:50</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>30001:16</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>70001:300_70002:6000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>100001:300_100002:6000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>90001:300_90002:6000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>80001:300_80002:6000</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2742,7 +2771,7 @@
         <v>215</v>
       </c>
       <c r="N5" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="O5" s="1" t="s">
         <v>583</v>
@@ -2766,7 +2795,7 @@
         <v>601</v>
       </c>
       <c r="V5" s="1" t="s">
-        <v>629</v>
+        <v>620</v>
       </c>
       <c r="W5" s="1">
         <v>0</v>
@@ -2775,7 +2804,7 @@
         <v>558</v>
       </c>
       <c r="Y5" s="1" t="s">
-        <v>639</v>
+        <v>627</v>
       </c>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.15">
@@ -2819,7 +2848,7 @@
         <v>215</v>
       </c>
       <c r="N6" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="O6" s="4" t="s">
         <v>584</v>
@@ -2837,13 +2866,13 @@
         <v>602</v>
       </c>
       <c r="T6" s="1" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="U6" s="1" t="s">
-        <v>620</v>
+        <v>614</v>
       </c>
       <c r="V6" s="1" t="s">
-        <v>630</v>
+        <v>621</v>
       </c>
       <c r="W6" s="1">
         <v>0</v>
@@ -2852,7 +2881,7 @@
         <v>558</v>
       </c>
       <c r="Y6" s="1" t="s">
-        <v>640</v>
+        <v>628</v>
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.15">
@@ -2896,7 +2925,7 @@
         <v>215</v>
       </c>
       <c r="N7" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="O7" s="4" t="s">
         <v>585</v>
@@ -2914,22 +2943,22 @@
         <v>603</v>
       </c>
       <c r="T7" s="1" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="U7" s="1" t="s">
-        <v>621</v>
+        <v>615</v>
       </c>
       <c r="V7" s="1" t="s">
-        <v>631</v>
+        <v>622</v>
       </c>
       <c r="W7" s="1">
         <v>0</v>
       </c>
       <c r="X7" s="3" t="s">
-        <v>558</v>
+        <v>650</v>
       </c>
       <c r="Y7" s="1" t="s">
-        <v>641</v>
+        <v>629</v>
       </c>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.15">
@@ -2973,7 +3002,7 @@
         <v>215</v>
       </c>
       <c r="N8" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="O8" s="4" t="s">
         <v>586</v>
@@ -2991,13 +3020,13 @@
         <v>604</v>
       </c>
       <c r="T8" s="1" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="U8" s="1" t="s">
-        <v>622</v>
+        <v>616</v>
       </c>
       <c r="V8" s="1" t="s">
-        <v>632</v>
+        <v>623</v>
       </c>
       <c r="W8" s="1">
         <v>0</v>
@@ -3006,7 +3035,7 @@
         <v>558</v>
       </c>
       <c r="Y8" s="1" t="s">
-        <v>642</v>
+        <v>630</v>
       </c>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.15">
@@ -3050,7 +3079,7 @@
         <v>215</v>
       </c>
       <c r="N9" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="O9" s="4" t="s">
         <v>587</v>
@@ -3065,16 +3094,16 @@
         <v>0</v>
       </c>
       <c r="S9" s="1" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="T9" s="1" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="U9" s="1" t="s">
-        <v>623</v>
+        <v>617</v>
       </c>
       <c r="V9" s="1" t="s">
-        <v>636</v>
+        <v>624</v>
       </c>
       <c r="W9" s="1">
         <v>0</v>
@@ -3083,7 +3112,7 @@
         <v>558</v>
       </c>
       <c r="Y9" s="1" t="s">
-        <v>643</v>
+        <v>631</v>
       </c>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.15">
@@ -3127,7 +3156,7 @@
         <v>215</v>
       </c>
       <c r="N10" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="O10" s="4" t="s">
         <v>588</v>
@@ -3142,16 +3171,16 @@
         <v>0</v>
       </c>
       <c r="S10" s="1" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="T10" s="1" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="U10" s="1" t="s">
-        <v>624</v>
+        <v>618</v>
       </c>
       <c r="V10" s="1" t="s">
-        <v>637</v>
+        <v>625</v>
       </c>
       <c r="W10" s="1">
         <v>0</v>
@@ -3160,7 +3189,7 @@
         <v>558</v>
       </c>
       <c r="Y10" s="1" t="s">
-        <v>644</v>
+        <v>632</v>
       </c>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.15">
@@ -3204,7 +3233,7 @@
         <v>215</v>
       </c>
       <c r="N11" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="O11" s="4" t="s">
         <v>589</v>
@@ -3219,25 +3248,25 @@
         <v>0</v>
       </c>
       <c r="S11" s="1" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="T11" s="1" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="U11" s="1" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="V11" s="1" t="s">
-        <v>638</v>
+        <v>626</v>
       </c>
       <c r="W11" s="1">
         <v>0</v>
       </c>
-      <c r="X11" s="3" t="s">
-        <v>558</v>
+      <c r="X11" s="1" t="s">
+        <v>651</v>
       </c>
       <c r="Y11" s="1" t="s">
-        <v>645</v>
+        <v>633</v>
       </c>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.15">
@@ -3281,7 +3310,7 @@
         <v>215</v>
       </c>
       <c r="N12" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="O12" s="4" t="s">
         <v>534</v>
@@ -3296,25 +3325,25 @@
         <v>0</v>
       </c>
       <c r="S12" s="1" t="s">
-        <v>605</v>
+        <v>638</v>
       </c>
       <c r="T12" s="1" t="s">
-        <v>617</v>
+        <v>641</v>
       </c>
       <c r="U12" s="1" t="s">
-        <v>626</v>
+        <v>644</v>
       </c>
       <c r="V12" s="1" t="s">
-        <v>633</v>
+        <v>647</v>
       </c>
       <c r="W12" s="1">
         <v>0</v>
       </c>
-      <c r="X12" s="3" t="s">
-        <v>558</v>
+      <c r="X12" s="1" t="s">
+        <v>654</v>
       </c>
       <c r="Y12" s="1" t="s">
-        <v>646</v>
+        <v>634</v>
       </c>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.15">
@@ -3358,7 +3387,7 @@
         <v>215</v>
       </c>
       <c r="N13" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="O13" s="4" t="s">
         <v>535</v>
@@ -3373,25 +3402,25 @@
         <v>0</v>
       </c>
       <c r="S13" s="1" t="s">
-        <v>606</v>
+        <v>639</v>
       </c>
       <c r="T13" s="1" t="s">
-        <v>618</v>
+        <v>642</v>
       </c>
       <c r="U13" s="1" t="s">
-        <v>627</v>
+        <v>645</v>
       </c>
       <c r="V13" s="1" t="s">
-        <v>634</v>
+        <v>648</v>
       </c>
       <c r="W13" s="1">
         <v>0</v>
       </c>
-      <c r="X13" s="3" t="s">
-        <v>558</v>
+      <c r="X13" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="Y13" s="1" t="s">
-        <v>647</v>
+        <v>635</v>
       </c>
     </row>
     <row r="14" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -3435,7 +3464,7 @@
         <v>215</v>
       </c>
       <c r="N14" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="O14" s="4" t="s">
         <v>536</v>
@@ -3450,25 +3479,25 @@
         <v>0</v>
       </c>
       <c r="S14" s="1" t="s">
-        <v>607</v>
+        <v>640</v>
       </c>
       <c r="T14" s="1" t="s">
-        <v>619</v>
+        <v>643</v>
       </c>
       <c r="U14" s="1" t="s">
-        <v>628</v>
+        <v>646</v>
       </c>
       <c r="V14" s="1" t="s">
-        <v>635</v>
+        <v>649</v>
       </c>
       <c r="W14" s="1">
         <v>0</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>558</v>
+      <c r="X14" s="1" t="s">
+        <v>652</v>
       </c>
       <c r="Y14" s="1" t="s">
-        <v>648</v>
+        <v>636</v>
       </c>
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.15">
@@ -3592,7 +3621,7 @@
         <v>542</v>
       </c>
       <c r="P16" s="4" t="s">
-        <v>649</v>
+        <v>637</v>
       </c>
       <c r="Q16" s="3" t="s">
         <v>231</v>

--- a/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3BD5473-BD8E-4069-B30E-888DF6168831}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D273BB9-3203-4945-9673-D784021953A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2115,19 +2115,19 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>70001:300_70002:6000</t>
+    <t>70001:300_70002:8000</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>100001:300_100002:6000</t>
+    <t>80001:300_80002:8000</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>90001:300_90002:6000</t>
+    <t>90001:300_90002:8000</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>80001:300_80002:6000</t>
+    <t>100001:300_100002:8000</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3340,7 +3340,7 @@
         <v>0</v>
       </c>
       <c r="X12" s="1" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="Y12" s="1" t="s">
         <v>634</v>
@@ -3494,7 +3494,7 @@
         <v>0</v>
       </c>
       <c r="X14" s="1" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="Y14" s="1" t="s">
         <v>636</v>

--- a/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D273BB9-3203-4945-9673-D784021953A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{302E9529-FC90-446A-89FC-02121D709279}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1581" uniqueCount="655">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1584" uniqueCount="657">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2128,6 +2128,14 @@
   </si>
   <si>
     <t>100001:300_100002:8000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>equ_drop</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>装备掉落id</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2468,7 +2476,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:Y164"/>
+  <dimension ref="A1:Z164"/>
   <sheetFormatPr defaultColWidth="7.125" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.5" style="1" bestFit="1" customWidth="1"/>
@@ -2491,15 +2499,16 @@
     <col min="22" max="22" width="19.375" style="1" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="15" style="1" bestFit="1" customWidth="1"/>
     <col min="24" max="25" width="18.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="7.125" style="1"/>
+    <col min="26" max="26" width="11.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="7.125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -2575,8 +2584,11 @@
       <c r="Y2" s="1" t="s">
         <v>559</v>
       </c>
-    </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z2" s="5" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -2652,8 +2664,11 @@
       <c r="Y3" s="1" t="s">
         <v>565</v>
       </c>
-    </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z3" s="5" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -2729,8 +2744,11 @@
       <c r="Y4" s="1" t="s">
         <v>564</v>
       </c>
-    </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z4" s="5" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -2806,8 +2824,11 @@
       <c r="Y5" s="1" t="s">
         <v>627</v>
       </c>
-    </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z5" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A6" s="1">
         <v>2</v>
       </c>
@@ -2883,8 +2904,11 @@
       <c r="Y6" s="1" t="s">
         <v>628</v>
       </c>
-    </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z6" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A7" s="1">
         <v>3</v>
       </c>
@@ -2960,8 +2984,11 @@
       <c r="Y7" s="1" t="s">
         <v>629</v>
       </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z7" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A8" s="1">
         <v>4</v>
       </c>
@@ -3037,8 +3064,11 @@
       <c r="Y8" s="1" t="s">
         <v>630</v>
       </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z8" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A9" s="1">
         <v>5</v>
       </c>
@@ -3114,8 +3144,11 @@
       <c r="Y9" s="1" t="s">
         <v>631</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z9" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A10" s="1">
         <v>6</v>
       </c>
@@ -3191,8 +3224,11 @@
       <c r="Y10" s="1" t="s">
         <v>632</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z10" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A11" s="1">
         <v>7</v>
       </c>
@@ -3268,8 +3304,11 @@
       <c r="Y11" s="1" t="s">
         <v>633</v>
       </c>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z11" s="5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A12" s="1">
         <v>8</v>
       </c>
@@ -3345,8 +3384,11 @@
       <c r="Y12" s="1" t="s">
         <v>634</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z12" s="5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A13" s="1">
         <v>9</v>
       </c>
@@ -3422,8 +3464,11 @@
       <c r="Y13" s="1" t="s">
         <v>635</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Z13" s="5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="1">
         <v>10</v>
       </c>
@@ -3499,8 +3544,11 @@
       <c r="Y14" s="1" t="s">
         <v>636</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z14" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A15" s="1">
         <v>11</v>
       </c>
@@ -3573,8 +3621,11 @@
       <c r="Y15" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z15" s="5">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A16" s="1">
         <v>12</v>
       </c>
@@ -3650,8 +3701,11 @@
       <c r="Y16" s="1" t="s">
         <v>566</v>
       </c>
-    </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z16" s="5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A17" s="1">
         <v>13</v>
       </c>
@@ -3715,8 +3769,11 @@
       <c r="Y17" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z17" s="5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A18" s="1">
         <v>14</v>
       </c>
@@ -3780,8 +3837,11 @@
       <c r="Y18" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z18" s="5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A19" s="1">
         <v>15</v>
       </c>
@@ -3845,8 +3905,11 @@
       <c r="Y19" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z19" s="5">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A20" s="1">
         <v>16</v>
       </c>
@@ -3910,8 +3973,11 @@
       <c r="Y20" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z20" s="5">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A21" s="1">
         <v>17</v>
       </c>
@@ -3975,8 +4041,11 @@
       <c r="Y21" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z21" s="5">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A22" s="1">
         <v>18</v>
       </c>
@@ -4040,8 +4109,11 @@
       <c r="Y22" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z22" s="5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A23" s="1">
         <v>19</v>
       </c>
@@ -4105,8 +4177,11 @@
       <c r="Y23" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z23" s="5">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="24" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A24" s="1">
         <v>20</v>
       </c>
@@ -4170,8 +4245,11 @@
       <c r="Y24" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z24" s="5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A25" s="1">
         <v>21</v>
       </c>
@@ -4247,8 +4325,11 @@
       <c r="Y25" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z25" s="5">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="26" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A26" s="1">
         <v>22</v>
       </c>
@@ -4312,8 +4393,11 @@
       <c r="Y26" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z26" s="5">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="27" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A27" s="1">
         <v>23</v>
       </c>
@@ -4377,8 +4461,11 @@
       <c r="Y27" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z27" s="5">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="28" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A28" s="1">
         <v>24</v>
       </c>
@@ -4442,8 +4529,11 @@
       <c r="Y28" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z28" s="5">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A29" s="1">
         <v>25</v>
       </c>
@@ -4507,8 +4597,11 @@
       <c r="Y29" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z29" s="5">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="30" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A30" s="1">
         <v>26</v>
       </c>
@@ -4572,8 +4665,11 @@
       <c r="Y30" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z30" s="5">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="31" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A31" s="1">
         <v>27</v>
       </c>
@@ -4637,8 +4733,11 @@
       <c r="Y31" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z31" s="5">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="32" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A32" s="1">
         <v>28</v>
       </c>
@@ -4702,8 +4801,11 @@
       <c r="Y32" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="33" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z32" s="5">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="33" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A33" s="1">
         <v>29</v>
       </c>
@@ -4767,8 +4869,11 @@
       <c r="Y33" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="34" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z33" s="5">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="34" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A34" s="1">
         <v>30</v>
       </c>
@@ -4844,8 +4949,11 @@
       <c r="Y34" s="3" t="s">
         <v>573</v>
       </c>
-    </row>
-    <row r="35" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z34" s="5">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="35" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A35" s="1">
         <v>31</v>
       </c>
@@ -4921,8 +5029,11 @@
       <c r="Y35" s="3" t="s">
         <v>581</v>
       </c>
-    </row>
-    <row r="36" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z35" s="5">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="36" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A36" s="1">
         <v>32</v>
       </c>
@@ -4998,8 +5109,11 @@
       <c r="Y36" s="3" t="s">
         <v>581</v>
       </c>
-    </row>
-    <row r="37" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z36" s="5">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="37" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A37" s="1">
         <v>33</v>
       </c>
@@ -5063,8 +5177,11 @@
       <c r="Y37" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="38" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z37" s="5">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="38" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A38" s="1">
         <v>34</v>
       </c>
@@ -5128,8 +5245,11 @@
       <c r="Y38" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="39" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z38" s="5">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="39" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A39" s="1">
         <v>35</v>
       </c>
@@ -5193,8 +5313,11 @@
       <c r="Y39" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="40" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z39" s="5">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="40" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A40" s="1">
         <v>36</v>
       </c>
@@ -5258,8 +5381,11 @@
       <c r="Y40" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="41" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z40" s="5">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="41" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A41" s="1">
         <v>37</v>
       </c>
@@ -5323,8 +5449,11 @@
       <c r="Y41" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="42" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z41" s="5">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="42" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A42" s="1">
         <v>38</v>
       </c>
@@ -5388,8 +5517,11 @@
       <c r="Y42" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="43" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z42" s="5">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="43" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A43" s="1">
         <v>39</v>
       </c>
@@ -5453,8 +5585,11 @@
       <c r="Y43" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="44" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z43" s="5">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="44" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A44" s="1">
         <v>40</v>
       </c>
@@ -5518,8 +5653,11 @@
       <c r="Y44" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="45" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z44" s="5">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="45" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A45" s="1">
         <v>41</v>
       </c>
@@ -5583,8 +5721,11 @@
       <c r="Y45" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="46" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z45" s="5">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="46" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A46" s="1">
         <v>42</v>
       </c>
@@ -5648,8 +5789,11 @@
       <c r="Y46" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="47" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z46" s="5">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="47" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A47" s="1">
         <v>43</v>
       </c>
@@ -5713,8 +5857,11 @@
       <c r="Y47" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="48" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z47" s="5">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="48" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A48" s="1">
         <v>44</v>
       </c>
@@ -5778,8 +5925,11 @@
       <c r="Y48" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="49" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z48" s="5">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="49" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A49" s="1">
         <v>45</v>
       </c>
@@ -5843,8 +5993,11 @@
       <c r="Y49" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="50" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z49" s="5">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="50" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A50" s="1">
         <v>46</v>
       </c>
@@ -5908,8 +6061,11 @@
       <c r="Y50" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="51" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z50" s="5">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="51" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A51" s="1">
         <v>47</v>
       </c>
@@ -5973,8 +6129,11 @@
       <c r="Y51" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="52" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z51" s="5">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="52" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A52" s="1">
         <v>48</v>
       </c>
@@ -6038,8 +6197,11 @@
       <c r="Y52" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="53" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z52" s="5">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="53" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A53" s="1">
         <v>49</v>
       </c>
@@ -6103,8 +6265,11 @@
       <c r="Y53" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="54" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z53" s="5">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="54" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A54" s="1">
         <v>50</v>
       </c>
@@ -6168,8 +6333,11 @@
       <c r="Y54" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="55" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z54" s="5">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="55" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A55" s="1">
         <v>51</v>
       </c>
@@ -6233,8 +6401,11 @@
       <c r="Y55" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="56" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z55" s="5">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="56" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A56" s="1">
         <v>52</v>
       </c>
@@ -6298,8 +6469,11 @@
       <c r="Y56" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="57" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z56" s="5">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="57" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A57" s="1">
         <v>53</v>
       </c>
@@ -6363,8 +6537,11 @@
       <c r="Y57" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="58" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z57" s="5">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="58" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A58" s="1">
         <v>54</v>
       </c>
@@ -6428,8 +6605,11 @@
       <c r="Y58" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="59" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z58" s="5">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="59" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A59" s="1">
         <v>55</v>
       </c>
@@ -6493,8 +6673,11 @@
       <c r="Y59" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="60" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z59" s="5">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="60" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A60" s="1">
         <v>56</v>
       </c>
@@ -6558,8 +6741,11 @@
       <c r="Y60" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="61" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z60" s="5">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="61" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A61" s="1">
         <v>57</v>
       </c>
@@ -6623,8 +6809,11 @@
       <c r="Y61" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="62" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z61" s="5">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="62" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A62" s="1">
         <v>58</v>
       </c>
@@ -6688,8 +6877,11 @@
       <c r="Y62" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="63" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z62" s="5">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="63" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A63" s="1">
         <v>59</v>
       </c>
@@ -6753,8 +6945,11 @@
       <c r="Y63" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="64" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z63" s="5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="64" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A64" s="1">
         <v>60</v>
       </c>
@@ -6818,8 +7013,11 @@
       <c r="Y64" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="65" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z64" s="5">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="65" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A65" s="1">
         <v>61</v>
       </c>
@@ -6883,8 +7081,11 @@
       <c r="Y65" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="66" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z65" s="5">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="66" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A66" s="1">
         <v>62</v>
       </c>
@@ -6948,8 +7149,11 @@
       <c r="Y66" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="67" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z66" s="5">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="67" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A67" s="1">
         <v>63</v>
       </c>
@@ -7013,8 +7217,11 @@
       <c r="Y67" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="68" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z67" s="5">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="68" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A68" s="1">
         <v>64</v>
       </c>
@@ -7078,8 +7285,11 @@
       <c r="Y68" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="69" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z68" s="5">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="69" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A69" s="1">
         <v>65</v>
       </c>
@@ -7143,8 +7353,11 @@
       <c r="Y69" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="70" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z69" s="5">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="70" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A70" s="1">
         <v>66</v>
       </c>
@@ -7208,8 +7421,11 @@
       <c r="Y70" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="71" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z70" s="5">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="71" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A71" s="1">
         <v>67</v>
       </c>
@@ -7273,8 +7489,11 @@
       <c r="Y71" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="72" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z71" s="5">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="72" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A72" s="1">
         <v>68</v>
       </c>
@@ -7338,8 +7557,11 @@
       <c r="Y72" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="73" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z72" s="5">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="73" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A73" s="1">
         <v>69</v>
       </c>
@@ -7403,8 +7625,11 @@
       <c r="Y73" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="74" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z73" s="5">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="74" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A74" s="1">
         <v>70</v>
       </c>
@@ -7468,8 +7693,11 @@
       <c r="Y74" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="75" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z74" s="5">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="75" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A75" s="1">
         <v>71</v>
       </c>
@@ -7533,8 +7761,11 @@
       <c r="Y75" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="76" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z75" s="5">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="76" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A76" s="1">
         <v>72</v>
       </c>
@@ -7598,8 +7829,11 @@
       <c r="Y76" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="77" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z76" s="5">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="77" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A77" s="1">
         <v>73</v>
       </c>
@@ -7663,8 +7897,11 @@
       <c r="Y77" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="78" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z77" s="5">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="78" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A78" s="1">
         <v>74</v>
       </c>
@@ -7728,8 +7965,11 @@
       <c r="Y78" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="79" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z78" s="5">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="79" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A79" s="1">
         <v>75</v>
       </c>
@@ -7793,8 +8033,11 @@
       <c r="Y79" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="80" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z79" s="5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="80" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A80" s="1">
         <v>76</v>
       </c>
@@ -7858,8 +8101,11 @@
       <c r="Y80" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="81" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z80" s="5">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="81" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A81" s="1">
         <v>77</v>
       </c>
@@ -7923,8 +8169,11 @@
       <c r="Y81" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="82" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z81" s="5">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="82" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A82" s="1">
         <v>78</v>
       </c>
@@ -7988,8 +8237,11 @@
       <c r="Y82" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="83" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z82" s="5">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="83" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A83" s="1">
         <v>79</v>
       </c>
@@ -8053,8 +8305,11 @@
       <c r="Y83" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="84" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z83" s="5">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="84" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A84" s="1">
         <v>80</v>
       </c>
@@ -8118,8 +8373,11 @@
       <c r="Y84" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="85" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z84" s="5">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="85" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A85" s="1">
         <v>81</v>
       </c>
@@ -8183,8 +8441,11 @@
       <c r="Y85" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="86" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z85" s="5">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="86" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A86" s="1">
         <v>82</v>
       </c>
@@ -8248,8 +8509,11 @@
       <c r="Y86" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="87" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z86" s="5">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="87" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A87" s="1">
         <v>83</v>
       </c>
@@ -8313,8 +8577,11 @@
       <c r="Y87" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="88" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z87" s="5">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="88" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A88" s="1">
         <v>84</v>
       </c>
@@ -8378,8 +8645,11 @@
       <c r="Y88" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="89" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z88" s="5">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="89" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A89" s="1">
         <v>85</v>
       </c>
@@ -8443,8 +8713,11 @@
       <c r="Y89" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="90" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z89" s="5">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="90" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A90" s="1">
         <v>86</v>
       </c>
@@ -8508,8 +8781,11 @@
       <c r="Y90" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="91" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z90" s="5">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="91" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A91" s="1">
         <v>87</v>
       </c>
@@ -8573,8 +8849,11 @@
       <c r="Y91" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="92" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z91" s="5">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="92" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A92" s="1">
         <v>88</v>
       </c>
@@ -8638,8 +8917,11 @@
       <c r="Y92" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="93" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z92" s="5">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="93" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A93" s="1">
         <v>89</v>
       </c>
@@ -8703,8 +8985,11 @@
       <c r="Y93" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="94" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z93" s="5">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="94" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A94" s="1">
         <v>90</v>
       </c>
@@ -8768,8 +9053,11 @@
       <c r="Y94" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="95" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z94" s="5">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="95" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A95" s="1">
         <v>91</v>
       </c>
@@ -8833,8 +9121,11 @@
       <c r="Y95" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="96" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z95" s="5">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="96" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A96" s="1">
         <v>92</v>
       </c>
@@ -8898,8 +9189,11 @@
       <c r="Y96" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="97" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z96" s="5">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="97" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A97" s="1">
         <v>93</v>
       </c>
@@ -8963,8 +9257,11 @@
       <c r="Y97" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="98" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z97" s="5">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="98" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A98" s="1">
         <v>94</v>
       </c>
@@ -9028,8 +9325,11 @@
       <c r="Y98" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="99" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z98" s="5">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="99" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A99" s="1">
         <v>95</v>
       </c>
@@ -9093,8 +9393,11 @@
       <c r="Y99" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="100" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z99" s="5">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="100" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A100" s="1">
         <v>96</v>
       </c>
@@ -9158,8 +9461,11 @@
       <c r="Y100" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="101" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z100" s="5">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="101" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A101" s="1">
         <v>97</v>
       </c>
@@ -9223,8 +9529,11 @@
       <c r="Y101" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="102" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z101" s="5">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="102" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A102" s="1">
         <v>98</v>
       </c>
@@ -9288,8 +9597,11 @@
       <c r="Y102" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="103" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z102" s="5">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="103" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A103" s="1">
         <v>99</v>
       </c>
@@ -9353,8 +9665,11 @@
       <c r="Y103" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="104" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z103" s="5">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="104" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A104" s="1">
         <v>100</v>
       </c>
@@ -9418,8 +9733,11 @@
       <c r="Y104" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="105" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z104" s="5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="105" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A105" s="1">
         <v>101</v>
       </c>
@@ -9483,8 +9801,11 @@
       <c r="Y105" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="106" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z105" s="5">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="106" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A106" s="1">
         <v>102</v>
       </c>
@@ -9548,8 +9869,11 @@
       <c r="Y106" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="107" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z106" s="5">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="107" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A107" s="1">
         <v>103</v>
       </c>
@@ -9613,8 +9937,11 @@
       <c r="Y107" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="108" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z107" s="5">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="108" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A108" s="1">
         <v>104</v>
       </c>
@@ -9678,8 +10005,11 @@
       <c r="Y108" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="109" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z108" s="5">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="109" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A109" s="1">
         <v>105</v>
       </c>
@@ -9743,8 +10073,11 @@
       <c r="Y109" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="110" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z109" s="5">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="110" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A110" s="1">
         <v>106</v>
       </c>
@@ -9808,8 +10141,11 @@
       <c r="Y110" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="111" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z110" s="5">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="111" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A111" s="1">
         <v>107</v>
       </c>
@@ -9873,8 +10209,11 @@
       <c r="Y111" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="112" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z111" s="5">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="112" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A112" s="1">
         <v>108</v>
       </c>
@@ -9938,8 +10277,11 @@
       <c r="Y112" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="113" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z112" s="5">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="113" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A113" s="1">
         <v>109</v>
       </c>
@@ -10003,8 +10345,11 @@
       <c r="Y113" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="114" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z113" s="5">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="114" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A114" s="1">
         <v>110</v>
       </c>
@@ -10068,8 +10413,11 @@
       <c r="Y114" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="115" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z114" s="5">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="115" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A115" s="1">
         <v>111</v>
       </c>
@@ -10133,8 +10481,11 @@
       <c r="Y115" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="116" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z115" s="5">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="116" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A116" s="1">
         <v>112</v>
       </c>
@@ -10198,8 +10549,11 @@
       <c r="Y116" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="117" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z116" s="5">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="117" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A117" s="1">
         <v>113</v>
       </c>
@@ -10263,8 +10617,11 @@
       <c r="Y117" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="118" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z117" s="5">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="118" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A118" s="1">
         <v>114</v>
       </c>
@@ -10328,8 +10685,11 @@
       <c r="Y118" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="119" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z118" s="5">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="119" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A119" s="1">
         <v>115</v>
       </c>
@@ -10393,8 +10753,11 @@
       <c r="Y119" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="120" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z119" s="5">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="120" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A120" s="1">
         <v>116</v>
       </c>
@@ -10458,8 +10821,11 @@
       <c r="Y120" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="121" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z120" s="5">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="121" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A121" s="1">
         <v>117</v>
       </c>
@@ -10523,8 +10889,11 @@
       <c r="Y121" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="122" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z121" s="5">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="122" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A122" s="1">
         <v>118</v>
       </c>
@@ -10588,8 +10957,11 @@
       <c r="Y122" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="123" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z122" s="5">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="123" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A123" s="1">
         <v>119</v>
       </c>
@@ -10653,8 +11025,11 @@
       <c r="Y123" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="124" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z123" s="5">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="124" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A124" s="1">
         <v>120</v>
       </c>
@@ -10718,8 +11093,11 @@
       <c r="Y124" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="125" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z124" s="5">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="125" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A125" s="1">
         <v>121</v>
       </c>
@@ -10783,8 +11161,11 @@
       <c r="Y125" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="126" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z125" s="5">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="126" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A126" s="1">
         <v>122</v>
       </c>
@@ -10848,8 +11229,11 @@
       <c r="Y126" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="127" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z126" s="5">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="127" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A127" s="1">
         <v>123</v>
       </c>
@@ -10913,8 +11297,11 @@
       <c r="Y127" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="128" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z127" s="5">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="128" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A128" s="1">
         <v>124</v>
       </c>
@@ -10978,8 +11365,11 @@
       <c r="Y128" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="129" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z128" s="5">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="129" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A129" s="1">
         <v>125</v>
       </c>
@@ -11043,8 +11433,11 @@
       <c r="Y129" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="130" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z129" s="5">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="130" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A130" s="1">
         <v>126</v>
       </c>
@@ -11108,8 +11501,11 @@
       <c r="Y130" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="131" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z130" s="5">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="131" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A131" s="1">
         <v>127</v>
       </c>
@@ -11173,8 +11569,11 @@
       <c r="Y131" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="132" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z131" s="5">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="132" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A132" s="1">
         <v>128</v>
       </c>
@@ -11238,8 +11637,11 @@
       <c r="Y132" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="133" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z132" s="5">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="133" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A133" s="1">
         <v>129</v>
       </c>
@@ -11303,8 +11705,11 @@
       <c r="Y133" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="134" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z133" s="5">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="134" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A134" s="1">
         <v>130</v>
       </c>
@@ -11368,8 +11773,11 @@
       <c r="Y134" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="135" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z134" s="5">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="135" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A135" s="1">
         <v>131</v>
       </c>
@@ -11433,8 +11841,11 @@
       <c r="Y135" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="136" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z135" s="5">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="136" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A136" s="1">
         <v>132</v>
       </c>
@@ -11498,8 +11909,11 @@
       <c r="Y136" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="137" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z136" s="5">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="137" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A137" s="1">
         <v>133</v>
       </c>
@@ -11563,8 +11977,11 @@
       <c r="Y137" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="138" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z137" s="5">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="138" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A138" s="1">
         <v>134</v>
       </c>
@@ -11628,8 +12045,11 @@
       <c r="Y138" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="139" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z138" s="5">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="139" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A139" s="1">
         <v>135</v>
       </c>
@@ -11693,8 +12113,11 @@
       <c r="Y139" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="140" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z139" s="5">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="140" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A140" s="1">
         <v>136</v>
       </c>
@@ -11758,8 +12181,11 @@
       <c r="Y140" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="141" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z140" s="5">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="141" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A141" s="1">
         <v>137</v>
       </c>
@@ -11823,8 +12249,11 @@
       <c r="Y141" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="142" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z141" s="5">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="142" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A142" s="1">
         <v>138</v>
       </c>
@@ -11888,8 +12317,11 @@
       <c r="Y142" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="143" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z142" s="5">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="143" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A143" s="1">
         <v>139</v>
       </c>
@@ -11953,8 +12385,11 @@
       <c r="Y143" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="144" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z143" s="5">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="144" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A144" s="1">
         <v>140</v>
       </c>
@@ -12018,8 +12453,11 @@
       <c r="Y144" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="145" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z144" s="5">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="145" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A145" s="1">
         <v>141</v>
       </c>
@@ -12083,8 +12521,11 @@
       <c r="Y145" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="146" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z145" s="5">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="146" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A146" s="1">
         <v>142</v>
       </c>
@@ -12148,8 +12589,11 @@
       <c r="Y146" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="147" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z146" s="5">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="147" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A147" s="1">
         <v>143</v>
       </c>
@@ -12213,8 +12657,11 @@
       <c r="Y147" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="148" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z147" s="5">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="148" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A148" s="1">
         <v>144</v>
       </c>
@@ -12278,8 +12725,11 @@
       <c r="Y148" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="149" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z148" s="5">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="149" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A149" s="1">
         <v>145</v>
       </c>
@@ -12343,8 +12793,11 @@
       <c r="Y149" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="150" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z149" s="5">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="150" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A150" s="1">
         <v>146</v>
       </c>
@@ -12408,8 +12861,11 @@
       <c r="Y150" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="151" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z150" s="5">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="151" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A151" s="1">
         <v>147</v>
       </c>
@@ -12473,8 +12929,11 @@
       <c r="Y151" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="152" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z151" s="5">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="152" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A152" s="1">
         <v>148</v>
       </c>
@@ -12538,8 +12997,11 @@
       <c r="Y152" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="153" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z152" s="5">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="153" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A153" s="1">
         <v>149</v>
       </c>
@@ -12603,8 +13065,11 @@
       <c r="Y153" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="154" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z153" s="5">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="154" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A154" s="1">
         <v>150</v>
       </c>
@@ -12668,8 +13133,11 @@
       <c r="Y154" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="155" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z154" s="5">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="155" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A155" s="1">
         <v>151</v>
       </c>
@@ -12733,8 +13201,11 @@
       <c r="Y155" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="156" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z155" s="5">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="156" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A156" s="1">
         <v>152</v>
       </c>
@@ -12798,8 +13269,11 @@
       <c r="Y156" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="157" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z156" s="5">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="157" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A157" s="1">
         <v>153</v>
       </c>
@@ -12863,8 +13337,11 @@
       <c r="Y157" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="158" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z157" s="5">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="158" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A158" s="1">
         <v>154</v>
       </c>
@@ -12928,8 +13405,11 @@
       <c r="Y158" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="159" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z158" s="5">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="159" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A159" s="1">
         <v>155</v>
       </c>
@@ -12993,8 +13473,11 @@
       <c r="Y159" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="160" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z159" s="5">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="160" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A160" s="1">
         <v>156</v>
       </c>
@@ -13058,8 +13541,11 @@
       <c r="Y160" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="161" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z160" s="5">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="161" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A161" s="1">
         <v>157</v>
       </c>
@@ -13123,8 +13609,11 @@
       <c r="Y161" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="162" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z161" s="5">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="162" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A162" s="1">
         <v>158</v>
       </c>
@@ -13188,8 +13677,11 @@
       <c r="Y162" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="163" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z162" s="5">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="163" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A163" s="1">
         <v>159</v>
       </c>
@@ -13253,8 +13745,11 @@
       <c r="Y163" s="3" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="164" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Z163" s="5">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="164" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A164" s="1">
         <v>160</v>
       </c>
@@ -13317,6 +13812,9 @@
       </c>
       <c r="Y164" s="3" t="s">
         <v>558</v>
+      </c>
+      <c r="Z164" s="5">
+        <v>160</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{302E9529-FC90-446A-89FC-02121D709279}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F0D8A37-B87B-4C75-999A-C78B9DEA599E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_barries_v8" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1584" uniqueCount="657">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1587" uniqueCount="659">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -880,9 +880,6 @@
     <t>200001:101_0:101</t>
   </si>
   <si>
-    <t>220001:100_0:100</t>
-  </si>
-  <si>
     <t>220001:101_0:101</t>
   </si>
   <si>
@@ -1768,10 +1765,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>210001:102_0:102</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>210001:0</t>
   </si>
   <si>
@@ -2136,6 +2129,22 @@
   </si>
   <si>
     <t>装备掉落id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>need_equip_score</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>掉落装备所需积分</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>210001:103_0:103</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>220001:1101_0:100</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2476,7 +2485,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:Z164"/>
+  <dimension ref="A1:AA164"/>
   <sheetFormatPr defaultColWidth="7.125" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.5" style="1" bestFit="1" customWidth="1"/>
@@ -2500,15 +2509,16 @@
     <col min="23" max="23" width="15" style="1" bestFit="1" customWidth="1"/>
     <col min="24" max="25" width="18.375" style="1" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="11.125" style="5" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="7.125" style="1"/>
+    <col min="27" max="27" width="16.75" style="5" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="7.125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -2579,16 +2589,19 @@
         <v>205</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="Z2" s="5" t="s">
         <v>220</v>
       </c>
-    </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA2" s="5" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -2653,22 +2666,25 @@
         <v>242</v>
       </c>
       <c r="V3" s="1" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="W3" s="5" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="X3" s="1" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="Y3" s="1" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="Z3" s="5" t="s">
+        <v>653</v>
+      </c>
+      <c r="AA3" t="s">
         <v>655</v>
       </c>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -2733,22 +2749,25 @@
         <v>239</v>
       </c>
       <c r="V4" s="1" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="W4" s="1" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="X4" s="1" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="Y4" s="1" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="Z4" s="5" t="s">
+        <v>654</v>
+      </c>
+      <c r="AA4" s="5" t="s">
         <v>656</v>
       </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -2792,10 +2811,10 @@
         <v>10</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="Q5" s="3" t="s">
         <v>231</v>
@@ -2807,28 +2826,31 @@
         <v>244</v>
       </c>
       <c r="T5" s="1" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="U5" s="1" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="V5" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="W5" s="1">
         <v>0</v>
       </c>
       <c r="X5" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y5" s="1" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="Z5" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA5" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A6" s="1">
         <v>2</v>
       </c>
@@ -2872,10 +2894,10 @@
         <v>10</v>
       </c>
       <c r="O6" s="4" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="P6" s="4" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="Q6" s="3" t="s">
         <v>231</v>
@@ -2884,31 +2906,34 @@
         <v>0</v>
       </c>
       <c r="S6" s="1" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="T6" s="1" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="U6" s="1" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="V6" s="1" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="W6" s="1">
         <v>0</v>
       </c>
       <c r="X6" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y6" s="1" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="Z6" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA6" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A7" s="1">
         <v>3</v>
       </c>
@@ -2952,10 +2977,10 @@
         <v>10</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="P7" s="4" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="Q7" s="3" t="s">
         <v>231</v>
@@ -2964,31 +2989,34 @@
         <v>0</v>
       </c>
       <c r="S7" s="1" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="T7" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="U7" s="1" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="V7" s="1" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="W7" s="1">
         <v>0</v>
       </c>
       <c r="X7" s="3" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="Y7" s="1" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="Z7" s="5">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA7" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A8" s="1">
         <v>4</v>
       </c>
@@ -3032,10 +3060,10 @@
         <v>10</v>
       </c>
       <c r="O8" s="4" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="P8" s="4" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="Q8" s="3" t="s">
         <v>231</v>
@@ -3044,31 +3072,34 @@
         <v>0</v>
       </c>
       <c r="S8" s="1" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="T8" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="U8" s="1" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="V8" s="1" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="W8" s="1">
         <v>0</v>
       </c>
       <c r="X8" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y8" s="1" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="Z8" s="5">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA8" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A9" s="1">
         <v>5</v>
       </c>
@@ -3112,10 +3143,10 @@
         <v>10</v>
       </c>
       <c r="O9" s="4" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="P9" s="4" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="Q9" s="3" t="s">
         <v>231</v>
@@ -3124,31 +3155,34 @@
         <v>0</v>
       </c>
       <c r="S9" s="1" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="T9" s="1" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="U9" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="V9" s="1" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="W9" s="1">
         <v>0</v>
       </c>
       <c r="X9" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y9" s="1" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="Z9" s="5">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA9" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A10" s="1">
         <v>6</v>
       </c>
@@ -3192,10 +3226,10 @@
         <v>10</v>
       </c>
       <c r="O10" s="4" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="P10" s="4" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="Q10" s="3" t="s">
         <v>231</v>
@@ -3204,31 +3238,34 @@
         <v>0</v>
       </c>
       <c r="S10" s="1" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="T10" s="1" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="U10" s="1" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="V10" s="1" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="W10" s="1">
         <v>0</v>
       </c>
       <c r="X10" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y10" s="1" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="Z10" s="5">
         <v>6</v>
       </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA10" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A11" s="1">
         <v>7</v>
       </c>
@@ -3272,10 +3309,10 @@
         <v>10</v>
       </c>
       <c r="O11" s="4" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="P11" s="4" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="Q11" s="3" t="s">
         <v>231</v>
@@ -3284,31 +3321,34 @@
         <v>0</v>
       </c>
       <c r="S11" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="T11" s="1" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="U11" s="1" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="V11" s="1" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="W11" s="1">
         <v>0</v>
       </c>
       <c r="X11" s="1" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="Y11" s="1" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="Z11" s="5">
         <v>7</v>
       </c>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA11" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A12" s="1">
         <v>8</v>
       </c>
@@ -3352,10 +3392,10 @@
         <v>10</v>
       </c>
       <c r="O12" s="4" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="P12" s="4" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="Q12" s="3" t="s">
         <v>231</v>
@@ -3364,31 +3404,34 @@
         <v>0</v>
       </c>
       <c r="S12" s="1" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="T12" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="U12" s="1" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="V12" s="1" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="W12" s="1">
         <v>0</v>
       </c>
       <c r="X12" s="1" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="Y12" s="1" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="Z12" s="5">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA12" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A13" s="1">
         <v>9</v>
       </c>
@@ -3432,10 +3475,10 @@
         <v>10</v>
       </c>
       <c r="O13" s="4" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="P13" s="4" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="Q13" s="3" t="s">
         <v>231</v>
@@ -3444,31 +3487,34 @@
         <v>0</v>
       </c>
       <c r="S13" s="1" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="T13" s="1" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="U13" s="1" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="V13" s="1" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="W13" s="1">
         <v>0</v>
       </c>
       <c r="X13" s="1" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="Y13" s="1" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="Z13" s="5">
         <v>9</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AA13" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="1">
         <v>10</v>
       </c>
@@ -3512,10 +3558,10 @@
         <v>10</v>
       </c>
       <c r="O14" s="4" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="P14" s="4" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>231</v>
@@ -3524,31 +3570,34 @@
         <v>0</v>
       </c>
       <c r="S14" s="1" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="T14" s="1" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="U14" s="1" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="V14" s="1" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="W14" s="1">
         <v>0</v>
       </c>
       <c r="X14" s="1" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="Y14" s="1" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="Z14" s="5">
         <v>10</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA14" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A15" s="1">
         <v>11</v>
       </c>
@@ -3592,10 +3641,10 @@
         <v>1</v>
       </c>
       <c r="O15" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="P15" s="1" t="s">
         <v>537</v>
-      </c>
-      <c r="P15" s="1" t="s">
-        <v>538</v>
       </c>
       <c r="Q15" s="3" t="s">
         <v>231</v>
@@ -3604,28 +3653,31 @@
         <v>0</v>
       </c>
       <c r="S15" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="T15" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="T15" s="1" t="s">
+      <c r="U15" s="1" t="s">
         <v>540</v>
       </c>
-      <c r="U15" s="1" t="s">
-        <v>541</v>
-      </c>
       <c r="W15" s="1" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="X15" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y15" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z15" s="5">
         <v>11</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA15" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A16" s="1">
         <v>12</v>
       </c>
@@ -3669,10 +3721,10 @@
         <v>1</v>
       </c>
       <c r="O16" s="4" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="P16" s="4" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="Q16" s="3" t="s">
         <v>231</v>
@@ -3681,31 +3733,34 @@
         <v>0</v>
       </c>
       <c r="S16" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="T16" s="1" t="s">
         <v>543</v>
       </c>
-      <c r="T16" s="1" t="s">
+      <c r="U16" s="1" t="s">
         <v>544</v>
       </c>
-      <c r="U16" s="1" t="s">
-        <v>545</v>
-      </c>
       <c r="V16" s="1" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="W16" s="1">
         <v>0</v>
       </c>
       <c r="X16" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y16" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="Z16" s="5">
         <v>12</v>
       </c>
-    </row>
-    <row r="17" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA16" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A17" s="1">
         <v>13</v>
       </c>
@@ -3764,16 +3819,19 @@
         <v>0</v>
       </c>
       <c r="X17" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y17" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z17" s="5">
         <v>13</v>
       </c>
-    </row>
-    <row r="18" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA17" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A18" s="1">
         <v>14</v>
       </c>
@@ -3832,16 +3890,19 @@
         <v>0</v>
       </c>
       <c r="X18" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y18" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z18" s="5">
         <v>14</v>
       </c>
-    </row>
-    <row r="19" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA18" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A19" s="1">
         <v>15</v>
       </c>
@@ -3900,16 +3961,19 @@
         <v>0</v>
       </c>
       <c r="X19" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y19" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z19" s="5">
         <v>15</v>
       </c>
-    </row>
-    <row r="20" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA19" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A20" s="1">
         <v>16</v>
       </c>
@@ -3968,16 +4032,19 @@
         <v>0</v>
       </c>
       <c r="X20" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y20" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z20" s="5">
         <v>16</v>
       </c>
-    </row>
-    <row r="21" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA20" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A21" s="1">
         <v>17</v>
       </c>
@@ -4036,16 +4103,19 @@
         <v>0</v>
       </c>
       <c r="X21" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y21" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z21" s="5">
         <v>17</v>
       </c>
-    </row>
-    <row r="22" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA21" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A22" s="1">
         <v>18</v>
       </c>
@@ -4104,16 +4174,19 @@
         <v>0</v>
       </c>
       <c r="X22" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y22" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z22" s="5">
         <v>18</v>
       </c>
-    </row>
-    <row r="23" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA22" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A23" s="1">
         <v>19</v>
       </c>
@@ -4172,16 +4245,19 @@
         <v>0</v>
       </c>
       <c r="X23" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y23" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z23" s="5">
         <v>19</v>
       </c>
-    </row>
-    <row r="24" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA23" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A24" s="1">
         <v>20</v>
       </c>
@@ -4240,16 +4316,19 @@
         <v>0</v>
       </c>
       <c r="X24" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y24" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z24" s="5">
         <v>20</v>
       </c>
-    </row>
-    <row r="25" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA24" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A25" s="1">
         <v>21</v>
       </c>
@@ -4293,10 +4372,10 @@
         <v>100</v>
       </c>
       <c r="O25" s="4" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="P25" s="4" t="s">
-        <v>553</v>
+        <v>657</v>
       </c>
       <c r="Q25" s="3" t="s">
         <v>231</v>
@@ -4305,31 +4384,34 @@
         <v>0</v>
       </c>
       <c r="S25" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="T25" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="U25" s="1" t="s">
         <v>554</v>
       </c>
-      <c r="T25" s="1" t="s">
+      <c r="V25" s="1" t="s">
         <v>555</v>
       </c>
-      <c r="U25" s="1" t="s">
-        <v>556</v>
-      </c>
-      <c r="V25" s="1" t="s">
-        <v>557</v>
-      </c>
       <c r="W25" s="1">
         <v>0</v>
       </c>
       <c r="X25" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y25" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z25" s="5">
         <v>21</v>
       </c>
-    </row>
-    <row r="26" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA25" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A26" s="1">
         <v>22</v>
       </c>
@@ -4373,10 +4455,10 @@
         <v>100</v>
       </c>
       <c r="O26" s="4" t="s">
+        <v>658</v>
+      </c>
+      <c r="P26" s="4" t="s">
         <v>262</v>
-      </c>
-      <c r="P26" s="4" t="s">
-        <v>263</v>
       </c>
       <c r="Q26" s="3" t="s">
         <v>231</v>
@@ -4388,16 +4470,19 @@
         <v>0</v>
       </c>
       <c r="X26" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y26" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z26" s="5">
         <v>22</v>
       </c>
-    </row>
-    <row r="27" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA26" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A27" s="1">
         <v>23</v>
       </c>
@@ -4441,10 +4526,10 @@
         <v>100</v>
       </c>
       <c r="O27" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="P27" s="4" t="s">
         <v>264</v>
-      </c>
-      <c r="P27" s="4" t="s">
-        <v>265</v>
       </c>
       <c r="Q27" s="3" t="s">
         <v>231</v>
@@ -4456,16 +4541,19 @@
         <v>0</v>
       </c>
       <c r="X27" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y27" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z27" s="5">
         <v>23</v>
       </c>
-    </row>
-    <row r="28" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA27" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A28" s="1">
         <v>24</v>
       </c>
@@ -4509,10 +4597,10 @@
         <v>100</v>
       </c>
       <c r="O28" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="P28" s="4" t="s">
         <v>266</v>
-      </c>
-      <c r="P28" s="4" t="s">
-        <v>267</v>
       </c>
       <c r="Q28" s="3" t="s">
         <v>231</v>
@@ -4524,16 +4612,19 @@
         <v>0</v>
       </c>
       <c r="X28" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y28" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z28" s="5">
         <v>24</v>
       </c>
-    </row>
-    <row r="29" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA28" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A29" s="1">
         <v>25</v>
       </c>
@@ -4577,10 +4668,10 @@
         <v>100</v>
       </c>
       <c r="O29" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="P29" s="4" t="s">
         <v>268</v>
-      </c>
-      <c r="P29" s="4" t="s">
-        <v>269</v>
       </c>
       <c r="Q29" s="3" t="s">
         <v>231</v>
@@ -4592,16 +4683,19 @@
         <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y29" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z29" s="5">
         <v>25</v>
       </c>
-    </row>
-    <row r="30" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA29" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A30" s="1">
         <v>26</v>
       </c>
@@ -4645,10 +4739,10 @@
         <v>100</v>
       </c>
       <c r="O30" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="P30" s="4" t="s">
         <v>270</v>
-      </c>
-      <c r="P30" s="4" t="s">
-        <v>271</v>
       </c>
       <c r="Q30" s="3" t="s">
         <v>231</v>
@@ -4660,16 +4754,19 @@
         <v>0</v>
       </c>
       <c r="X30" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y30" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z30" s="5">
         <v>26</v>
       </c>
-    </row>
-    <row r="31" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA30" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A31" s="1">
         <v>27</v>
       </c>
@@ -4713,10 +4810,10 @@
         <v>100</v>
       </c>
       <c r="O31" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="P31" s="4" t="s">
         <v>272</v>
-      </c>
-      <c r="P31" s="4" t="s">
-        <v>273</v>
       </c>
       <c r="Q31" s="3" t="s">
         <v>231</v>
@@ -4728,16 +4825,19 @@
         <v>0</v>
       </c>
       <c r="X31" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y31" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z31" s="5">
         <v>27</v>
       </c>
-    </row>
-    <row r="32" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA31" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A32" s="1">
         <v>28</v>
       </c>
@@ -4781,10 +4881,10 @@
         <v>100</v>
       </c>
       <c r="O32" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="P32" s="4" t="s">
         <v>274</v>
-      </c>
-      <c r="P32" s="4" t="s">
-        <v>275</v>
       </c>
       <c r="Q32" s="3" t="s">
         <v>231</v>
@@ -4796,16 +4896,19 @@
         <v>0</v>
       </c>
       <c r="X32" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y32" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z32" s="5">
         <v>28</v>
       </c>
-    </row>
-    <row r="33" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA32" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="33" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A33" s="1">
         <v>29</v>
       </c>
@@ -4849,10 +4952,10 @@
         <v>100</v>
       </c>
       <c r="O33" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="P33" s="4" t="s">
         <v>276</v>
-      </c>
-      <c r="P33" s="4" t="s">
-        <v>277</v>
       </c>
       <c r="Q33" s="3" t="s">
         <v>231</v>
@@ -4864,16 +4967,19 @@
         <v>0</v>
       </c>
       <c r="X33" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y33" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z33" s="5">
         <v>29</v>
       </c>
-    </row>
-    <row r="34" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA33" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="34" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A34" s="1">
         <v>30</v>
       </c>
@@ -4917,10 +5023,10 @@
         <v>1</v>
       </c>
       <c r="O34" s="4" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="P34" s="4" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="Q34" s="3" t="s">
         <v>231</v>
@@ -4929,31 +5035,34 @@
         <v>0</v>
       </c>
       <c r="S34" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="T34" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="U34" s="1" t="s">
         <v>569</v>
       </c>
-      <c r="T34" s="1" t="s">
+      <c r="V34" s="1" t="s">
         <v>570</v>
       </c>
-      <c r="U34" s="1" t="s">
+      <c r="W34" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="X34" s="3" t="s">
+        <v>561</v>
+      </c>
+      <c r="Y34" s="3" t="s">
         <v>571</v>
-      </c>
-      <c r="V34" s="1" t="s">
-        <v>572</v>
-      </c>
-      <c r="W34" s="1" t="s">
-        <v>562</v>
-      </c>
-      <c r="X34" s="3" t="s">
-        <v>563</v>
-      </c>
-      <c r="Y34" s="3" t="s">
-        <v>573</v>
       </c>
       <c r="Z34" s="5">
         <v>30</v>
       </c>
-    </row>
-    <row r="35" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA34" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="35" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A35" s="1">
         <v>31</v>
       </c>
@@ -4997,43 +5106,46 @@
         <v>1</v>
       </c>
       <c r="O35" s="4" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="P35" s="4" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="Q35" s="3" t="s">
+        <v>573</v>
+      </c>
+      <c r="R35" s="1">
+        <v>0</v>
+      </c>
+      <c r="S35" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="T35" s="1" t="s">
         <v>575</v>
       </c>
-      <c r="R35" s="1">
-        <v>0</v>
-      </c>
-      <c r="S35" s="1" t="s">
+      <c r="U35" s="1" t="s">
         <v>576</v>
       </c>
-      <c r="T35" s="1" t="s">
+      <c r="V35" s="1" t="s">
         <v>577</v>
       </c>
-      <c r="U35" s="1" t="s">
+      <c r="W35" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="X35" s="3" t="s">
         <v>578</v>
       </c>
-      <c r="V35" s="1" t="s">
+      <c r="Y35" s="3" t="s">
         <v>579</v>
-      </c>
-      <c r="W35" s="1" t="s">
-        <v>562</v>
-      </c>
-      <c r="X35" s="3" t="s">
-        <v>580</v>
-      </c>
-      <c r="Y35" s="3" t="s">
-        <v>581</v>
       </c>
       <c r="Z35" s="5">
         <v>31</v>
       </c>
-    </row>
-    <row r="36" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA35" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A36" s="1">
         <v>32</v>
       </c>
@@ -5077,10 +5189,10 @@
         <v>1</v>
       </c>
       <c r="O36" s="4" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="P36" s="4" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="Q36" s="3" t="s">
         <v>231</v>
@@ -5089,31 +5201,34 @@
         <v>0</v>
       </c>
       <c r="S36" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="T36" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="U36" s="1" t="s">
         <v>576</v>
       </c>
-      <c r="T36" s="1" t="s">
+      <c r="V36" s="1" t="s">
         <v>577</v>
       </c>
-      <c r="U36" s="1" t="s">
+      <c r="W36" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="X36" s="3" t="s">
         <v>578</v>
       </c>
-      <c r="V36" s="1" t="s">
+      <c r="Y36" s="3" t="s">
         <v>579</v>
-      </c>
-      <c r="W36" s="1" t="s">
-        <v>562</v>
-      </c>
-      <c r="X36" s="3" t="s">
-        <v>580</v>
-      </c>
-      <c r="Y36" s="3" t="s">
-        <v>581</v>
       </c>
       <c r="Z36" s="5">
         <v>32</v>
       </c>
-    </row>
-    <row r="37" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA36" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="37" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A37" s="1">
         <v>33</v>
       </c>
@@ -5157,10 +5272,10 @@
         <v>100</v>
       </c>
       <c r="O37" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="P37" s="4" t="s">
         <v>278</v>
-      </c>
-      <c r="P37" s="4" t="s">
-        <v>279</v>
       </c>
       <c r="Q37" s="3" t="s">
         <v>231</v>
@@ -5172,16 +5287,19 @@
         <v>0</v>
       </c>
       <c r="X37" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y37" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z37" s="5">
         <v>33</v>
       </c>
-    </row>
-    <row r="38" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA37" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="38" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A38" s="1">
         <v>34</v>
       </c>
@@ -5225,10 +5343,10 @@
         <v>100</v>
       </c>
       <c r="O38" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="P38" s="4" t="s">
         <v>280</v>
-      </c>
-      <c r="P38" s="4" t="s">
-        <v>281</v>
       </c>
       <c r="Q38" s="3" t="s">
         <v>231</v>
@@ -5240,16 +5358,19 @@
         <v>0</v>
       </c>
       <c r="X38" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y38" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z38" s="5">
         <v>34</v>
       </c>
-    </row>
-    <row r="39" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA38" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A39" s="1">
         <v>35</v>
       </c>
@@ -5293,10 +5414,10 @@
         <v>100</v>
       </c>
       <c r="O39" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="P39" s="4" t="s">
         <v>282</v>
-      </c>
-      <c r="P39" s="4" t="s">
-        <v>283</v>
       </c>
       <c r="Q39" s="3" t="s">
         <v>231</v>
@@ -5308,16 +5429,19 @@
         <v>0</v>
       </c>
       <c r="X39" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y39" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z39" s="5">
         <v>35</v>
       </c>
-    </row>
-    <row r="40" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA39" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="40" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A40" s="1">
         <v>36</v>
       </c>
@@ -5361,10 +5485,10 @@
         <v>100</v>
       </c>
       <c r="O40" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="P40" s="4" t="s">
         <v>284</v>
-      </c>
-      <c r="P40" s="4" t="s">
-        <v>285</v>
       </c>
       <c r="Q40" s="3" t="s">
         <v>231</v>
@@ -5376,16 +5500,19 @@
         <v>0</v>
       </c>
       <c r="X40" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y40" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z40" s="5">
         <v>36</v>
       </c>
-    </row>
-    <row r="41" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA40" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="41" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A41" s="1">
         <v>37</v>
       </c>
@@ -5429,10 +5556,10 @@
         <v>100</v>
       </c>
       <c r="O41" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="P41" s="4" t="s">
         <v>286</v>
-      </c>
-      <c r="P41" s="4" t="s">
-        <v>287</v>
       </c>
       <c r="Q41" s="3" t="s">
         <v>231</v>
@@ -5444,16 +5571,19 @@
         <v>0</v>
       </c>
       <c r="X41" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y41" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z41" s="5">
         <v>37</v>
       </c>
-    </row>
-    <row r="42" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA41" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="42" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A42" s="1">
         <v>38</v>
       </c>
@@ -5497,10 +5627,10 @@
         <v>100</v>
       </c>
       <c r="O42" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="P42" s="4" t="s">
         <v>288</v>
-      </c>
-      <c r="P42" s="4" t="s">
-        <v>289</v>
       </c>
       <c r="Q42" s="3" t="s">
         <v>231</v>
@@ -5512,16 +5642,19 @@
         <v>0</v>
       </c>
       <c r="X42" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y42" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z42" s="5">
         <v>38</v>
       </c>
-    </row>
-    <row r="43" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA42" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="43" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A43" s="1">
         <v>39</v>
       </c>
@@ -5565,10 +5698,10 @@
         <v>100</v>
       </c>
       <c r="O43" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="P43" s="4" t="s">
         <v>290</v>
-      </c>
-      <c r="P43" s="4" t="s">
-        <v>291</v>
       </c>
       <c r="Q43" s="3" t="s">
         <v>231</v>
@@ -5580,16 +5713,19 @@
         <v>0</v>
       </c>
       <c r="X43" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y43" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z43" s="5">
         <v>39</v>
       </c>
-    </row>
-    <row r="44" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA43" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="44" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A44" s="1">
         <v>40</v>
       </c>
@@ -5633,10 +5769,10 @@
         <v>100</v>
       </c>
       <c r="O44" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="P44" s="4" t="s">
         <v>292</v>
-      </c>
-      <c r="P44" s="4" t="s">
-        <v>293</v>
       </c>
       <c r="Q44" s="3" t="s">
         <v>231</v>
@@ -5648,16 +5784,19 @@
         <v>0</v>
       </c>
       <c r="X44" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y44" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z44" s="5">
         <v>40</v>
       </c>
-    </row>
-    <row r="45" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA44" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="45" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A45" s="1">
         <v>41</v>
       </c>
@@ -5701,10 +5840,10 @@
         <v>100</v>
       </c>
       <c r="O45" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="P45" s="4" t="s">
         <v>294</v>
-      </c>
-      <c r="P45" s="4" t="s">
-        <v>295</v>
       </c>
       <c r="Q45" s="3" t="s">
         <v>231</v>
@@ -5716,16 +5855,19 @@
         <v>0</v>
       </c>
       <c r="X45" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y45" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z45" s="5">
         <v>41</v>
       </c>
-    </row>
-    <row r="46" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA45" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="46" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A46" s="1">
         <v>42</v>
       </c>
@@ -5769,10 +5911,10 @@
         <v>100</v>
       </c>
       <c r="O46" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="P46" s="4" t="s">
         <v>296</v>
-      </c>
-      <c r="P46" s="4" t="s">
-        <v>297</v>
       </c>
       <c r="Q46" s="3" t="s">
         <v>231</v>
@@ -5784,16 +5926,19 @@
         <v>0</v>
       </c>
       <c r="X46" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y46" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z46" s="5">
         <v>42</v>
       </c>
-    </row>
-    <row r="47" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA46" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="47" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A47" s="1">
         <v>43</v>
       </c>
@@ -5837,10 +5982,10 @@
         <v>100</v>
       </c>
       <c r="O47" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="P47" s="4" t="s">
         <v>298</v>
-      </c>
-      <c r="P47" s="4" t="s">
-        <v>299</v>
       </c>
       <c r="Q47" s="3" t="s">
         <v>231</v>
@@ -5852,16 +5997,19 @@
         <v>0</v>
       </c>
       <c r="X47" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y47" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z47" s="5">
         <v>43</v>
       </c>
-    </row>
-    <row r="48" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA47" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="48" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A48" s="1">
         <v>44</v>
       </c>
@@ -5905,10 +6053,10 @@
         <v>100</v>
       </c>
       <c r="O48" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="P48" s="4" t="s">
         <v>300</v>
-      </c>
-      <c r="P48" s="4" t="s">
-        <v>301</v>
       </c>
       <c r="Q48" s="3" t="s">
         <v>231</v>
@@ -5920,16 +6068,19 @@
         <v>0</v>
       </c>
       <c r="X48" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y48" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z48" s="5">
         <v>44</v>
       </c>
-    </row>
-    <row r="49" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA48" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="49" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A49" s="1">
         <v>45</v>
       </c>
@@ -5973,10 +6124,10 @@
         <v>100</v>
       </c>
       <c r="O49" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="P49" s="4" t="s">
         <v>302</v>
-      </c>
-      <c r="P49" s="4" t="s">
-        <v>303</v>
       </c>
       <c r="Q49" s="3" t="s">
         <v>231</v>
@@ -5988,16 +6139,19 @@
         <v>0</v>
       </c>
       <c r="X49" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y49" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z49" s="5">
         <v>45</v>
       </c>
-    </row>
-    <row r="50" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA49" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="50" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A50" s="1">
         <v>46</v>
       </c>
@@ -6041,10 +6195,10 @@
         <v>100</v>
       </c>
       <c r="O50" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="P50" s="4" t="s">
         <v>304</v>
-      </c>
-      <c r="P50" s="4" t="s">
-        <v>305</v>
       </c>
       <c r="Q50" s="3" t="s">
         <v>231</v>
@@ -6056,16 +6210,19 @@
         <v>0</v>
       </c>
       <c r="X50" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y50" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z50" s="5">
         <v>46</v>
       </c>
-    </row>
-    <row r="51" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA50" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="51" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A51" s="1">
         <v>47</v>
       </c>
@@ -6109,10 +6266,10 @@
         <v>100</v>
       </c>
       <c r="O51" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="P51" s="4" t="s">
         <v>306</v>
-      </c>
-      <c r="P51" s="4" t="s">
-        <v>307</v>
       </c>
       <c r="Q51" s="3" t="s">
         <v>231</v>
@@ -6124,16 +6281,19 @@
         <v>0</v>
       </c>
       <c r="X51" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y51" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z51" s="5">
         <v>47</v>
       </c>
-    </row>
-    <row r="52" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA51" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="52" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A52" s="1">
         <v>48</v>
       </c>
@@ -6177,10 +6337,10 @@
         <v>100</v>
       </c>
       <c r="O52" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="P52" s="4" t="s">
         <v>308</v>
-      </c>
-      <c r="P52" s="4" t="s">
-        <v>309</v>
       </c>
       <c r="Q52" s="3" t="s">
         <v>231</v>
@@ -6192,16 +6352,19 @@
         <v>0</v>
       </c>
       <c r="X52" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y52" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z52" s="5">
         <v>48</v>
       </c>
-    </row>
-    <row r="53" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA52" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="53" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A53" s="1">
         <v>49</v>
       </c>
@@ -6245,10 +6408,10 @@
         <v>100</v>
       </c>
       <c r="O53" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="P53" s="4" t="s">
         <v>310</v>
-      </c>
-      <c r="P53" s="4" t="s">
-        <v>311</v>
       </c>
       <c r="Q53" s="3" t="s">
         <v>231</v>
@@ -6260,16 +6423,19 @@
         <v>0</v>
       </c>
       <c r="X53" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y53" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z53" s="5">
         <v>49</v>
       </c>
-    </row>
-    <row r="54" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA53" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="54" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A54" s="1">
         <v>50</v>
       </c>
@@ -6313,10 +6479,10 @@
         <v>100</v>
       </c>
       <c r="O54" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="P54" s="4" t="s">
         <v>312</v>
-      </c>
-      <c r="P54" s="4" t="s">
-        <v>313</v>
       </c>
       <c r="Q54" s="3" t="s">
         <v>231</v>
@@ -6328,16 +6494,19 @@
         <v>0</v>
       </c>
       <c r="X54" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y54" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z54" s="5">
         <v>50</v>
       </c>
-    </row>
-    <row r="55" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA54" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="55" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A55" s="1">
         <v>51</v>
       </c>
@@ -6381,10 +6550,10 @@
         <v>100</v>
       </c>
       <c r="O55" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="P55" s="4" t="s">
         <v>314</v>
-      </c>
-      <c r="P55" s="4" t="s">
-        <v>315</v>
       </c>
       <c r="Q55" s="3" t="s">
         <v>231</v>
@@ -6396,16 +6565,19 @@
         <v>0</v>
       </c>
       <c r="X55" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y55" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z55" s="5">
         <v>51</v>
       </c>
-    </row>
-    <row r="56" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA55" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="56" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A56" s="1">
         <v>52</v>
       </c>
@@ -6449,10 +6621,10 @@
         <v>100</v>
       </c>
       <c r="O56" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="P56" s="4" t="s">
         <v>316</v>
-      </c>
-      <c r="P56" s="4" t="s">
-        <v>317</v>
       </c>
       <c r="Q56" s="3" t="s">
         <v>231</v>
@@ -6464,16 +6636,19 @@
         <v>0</v>
       </c>
       <c r="X56" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y56" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z56" s="5">
         <v>52</v>
       </c>
-    </row>
-    <row r="57" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA56" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="57" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A57" s="1">
         <v>53</v>
       </c>
@@ -6517,10 +6692,10 @@
         <v>100</v>
       </c>
       <c r="O57" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="P57" s="4" t="s">
         <v>318</v>
-      </c>
-      <c r="P57" s="4" t="s">
-        <v>319</v>
       </c>
       <c r="Q57" s="3" t="s">
         <v>231</v>
@@ -6532,16 +6707,19 @@
         <v>0</v>
       </c>
       <c r="X57" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y57" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z57" s="5">
         <v>53</v>
       </c>
-    </row>
-    <row r="58" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA57" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="58" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A58" s="1">
         <v>54</v>
       </c>
@@ -6585,10 +6763,10 @@
         <v>100</v>
       </c>
       <c r="O58" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="P58" s="4" t="s">
         <v>320</v>
-      </c>
-      <c r="P58" s="4" t="s">
-        <v>321</v>
       </c>
       <c r="Q58" s="3" t="s">
         <v>231</v>
@@ -6600,16 +6778,19 @@
         <v>0</v>
       </c>
       <c r="X58" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y58" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z58" s="5">
         <v>54</v>
       </c>
-    </row>
-    <row r="59" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA58" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="59" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A59" s="1">
         <v>55</v>
       </c>
@@ -6653,10 +6834,10 @@
         <v>100</v>
       </c>
       <c r="O59" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="P59" s="4" t="s">
         <v>322</v>
-      </c>
-      <c r="P59" s="4" t="s">
-        <v>323</v>
       </c>
       <c r="Q59" s="3" t="s">
         <v>231</v>
@@ -6668,16 +6849,19 @@
         <v>0</v>
       </c>
       <c r="X59" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y59" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z59" s="5">
         <v>55</v>
       </c>
-    </row>
-    <row r="60" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA59" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="60" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A60" s="1">
         <v>56</v>
       </c>
@@ -6721,10 +6905,10 @@
         <v>100</v>
       </c>
       <c r="O60" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="P60" s="4" t="s">
         <v>324</v>
-      </c>
-      <c r="P60" s="4" t="s">
-        <v>325</v>
       </c>
       <c r="Q60" s="3" t="s">
         <v>231</v>
@@ -6736,16 +6920,19 @@
         <v>0</v>
       </c>
       <c r="X60" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y60" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z60" s="5">
         <v>56</v>
       </c>
-    </row>
-    <row r="61" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA60" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="61" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A61" s="1">
         <v>57</v>
       </c>
@@ -6789,10 +6976,10 @@
         <v>100</v>
       </c>
       <c r="O61" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="P61" s="4" t="s">
         <v>326</v>
-      </c>
-      <c r="P61" s="4" t="s">
-        <v>327</v>
       </c>
       <c r="Q61" s="3" t="s">
         <v>231</v>
@@ -6804,16 +6991,19 @@
         <v>0</v>
       </c>
       <c r="X61" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y61" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z61" s="5">
         <v>57</v>
       </c>
-    </row>
-    <row r="62" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA61" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="62" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A62" s="1">
         <v>58</v>
       </c>
@@ -6857,10 +7047,10 @@
         <v>100</v>
       </c>
       <c r="O62" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="P62" s="4" t="s">
         <v>328</v>
-      </c>
-      <c r="P62" s="4" t="s">
-        <v>329</v>
       </c>
       <c r="Q62" s="3" t="s">
         <v>231</v>
@@ -6872,16 +7062,19 @@
         <v>0</v>
       </c>
       <c r="X62" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y62" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z62" s="5">
         <v>58</v>
       </c>
-    </row>
-    <row r="63" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA62" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="63" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A63" s="1">
         <v>59</v>
       </c>
@@ -6925,10 +7118,10 @@
         <v>100</v>
       </c>
       <c r="O63" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="P63" s="4" t="s">
         <v>330</v>
-      </c>
-      <c r="P63" s="4" t="s">
-        <v>331</v>
       </c>
       <c r="Q63" s="3" t="s">
         <v>231</v>
@@ -6940,16 +7133,19 @@
         <v>0</v>
       </c>
       <c r="X63" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y63" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z63" s="5">
         <v>59</v>
       </c>
-    </row>
-    <row r="64" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA63" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="64" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A64" s="1">
         <v>60</v>
       </c>
@@ -6993,10 +7189,10 @@
         <v>100</v>
       </c>
       <c r="O64" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="P64" s="4" t="s">
         <v>332</v>
-      </c>
-      <c r="P64" s="4" t="s">
-        <v>333</v>
       </c>
       <c r="Q64" s="3" t="s">
         <v>231</v>
@@ -7008,16 +7204,19 @@
         <v>0</v>
       </c>
       <c r="X64" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y64" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z64" s="5">
         <v>60</v>
       </c>
-    </row>
-    <row r="65" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA64" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="65" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A65" s="1">
         <v>61</v>
       </c>
@@ -7061,10 +7260,10 @@
         <v>100</v>
       </c>
       <c r="O65" s="4" t="s">
+        <v>333</v>
+      </c>
+      <c r="P65" s="4" t="s">
         <v>334</v>
-      </c>
-      <c r="P65" s="4" t="s">
-        <v>335</v>
       </c>
       <c r="Q65" s="3" t="s">
         <v>231</v>
@@ -7076,16 +7275,19 @@
         <v>0</v>
       </c>
       <c r="X65" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y65" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z65" s="5">
         <v>61</v>
       </c>
-    </row>
-    <row r="66" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA65" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="66" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A66" s="1">
         <v>62</v>
       </c>
@@ -7129,10 +7331,10 @@
         <v>100</v>
       </c>
       <c r="O66" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="P66" s="4" t="s">
         <v>336</v>
-      </c>
-      <c r="P66" s="4" t="s">
-        <v>337</v>
       </c>
       <c r="Q66" s="3" t="s">
         <v>231</v>
@@ -7144,16 +7346,19 @@
         <v>0</v>
       </c>
       <c r="X66" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y66" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z66" s="5">
         <v>62</v>
       </c>
-    </row>
-    <row r="67" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA66" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="67" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A67" s="1">
         <v>63</v>
       </c>
@@ -7197,10 +7402,10 @@
         <v>100</v>
       </c>
       <c r="O67" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="P67" s="4" t="s">
         <v>338</v>
-      </c>
-      <c r="P67" s="4" t="s">
-        <v>339</v>
       </c>
       <c r="Q67" s="3" t="s">
         <v>231</v>
@@ -7212,16 +7417,19 @@
         <v>0</v>
       </c>
       <c r="X67" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y67" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z67" s="5">
         <v>63</v>
       </c>
-    </row>
-    <row r="68" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA67" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="68" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A68" s="1">
         <v>64</v>
       </c>
@@ -7265,10 +7473,10 @@
         <v>100</v>
       </c>
       <c r="O68" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="P68" s="4" t="s">
         <v>340</v>
-      </c>
-      <c r="P68" s="4" t="s">
-        <v>341</v>
       </c>
       <c r="Q68" s="3" t="s">
         <v>231</v>
@@ -7280,16 +7488,19 @@
         <v>0</v>
       </c>
       <c r="X68" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y68" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z68" s="5">
         <v>64</v>
       </c>
-    </row>
-    <row r="69" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA68" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="69" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A69" s="1">
         <v>65</v>
       </c>
@@ -7333,10 +7544,10 @@
         <v>100</v>
       </c>
       <c r="O69" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="P69" s="4" t="s">
         <v>342</v>
-      </c>
-      <c r="P69" s="4" t="s">
-        <v>343</v>
       </c>
       <c r="Q69" s="3" t="s">
         <v>231</v>
@@ -7348,16 +7559,19 @@
         <v>0</v>
       </c>
       <c r="X69" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y69" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z69" s="5">
         <v>65</v>
       </c>
-    </row>
-    <row r="70" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA69" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="70" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A70" s="1">
         <v>66</v>
       </c>
@@ -7401,10 +7615,10 @@
         <v>100</v>
       </c>
       <c r="O70" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="P70" s="4" t="s">
         <v>344</v>
-      </c>
-      <c r="P70" s="4" t="s">
-        <v>345</v>
       </c>
       <c r="Q70" s="3" t="s">
         <v>231</v>
@@ -7416,16 +7630,19 @@
         <v>0</v>
       </c>
       <c r="X70" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y70" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z70" s="5">
         <v>66</v>
       </c>
-    </row>
-    <row r="71" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA70" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="71" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A71" s="1">
         <v>67</v>
       </c>
@@ -7469,10 +7686,10 @@
         <v>100</v>
       </c>
       <c r="O71" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="P71" s="4" t="s">
         <v>346</v>
-      </c>
-      <c r="P71" s="4" t="s">
-        <v>347</v>
       </c>
       <c r="Q71" s="3" t="s">
         <v>231</v>
@@ -7484,16 +7701,19 @@
         <v>0</v>
       </c>
       <c r="X71" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y71" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z71" s="5">
         <v>67</v>
       </c>
-    </row>
-    <row r="72" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA71" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="72" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A72" s="1">
         <v>68</v>
       </c>
@@ -7537,10 +7757,10 @@
         <v>100</v>
       </c>
       <c r="O72" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="P72" s="4" t="s">
         <v>348</v>
-      </c>
-      <c r="P72" s="4" t="s">
-        <v>349</v>
       </c>
       <c r="Q72" s="3" t="s">
         <v>231</v>
@@ -7552,16 +7772,19 @@
         <v>0</v>
       </c>
       <c r="X72" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y72" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z72" s="5">
         <v>68</v>
       </c>
-    </row>
-    <row r="73" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA72" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="73" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A73" s="1">
         <v>69</v>
       </c>
@@ -7605,10 +7828,10 @@
         <v>100</v>
       </c>
       <c r="O73" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="P73" s="4" t="s">
         <v>350</v>
-      </c>
-      <c r="P73" s="4" t="s">
-        <v>351</v>
       </c>
       <c r="Q73" s="3" t="s">
         <v>231</v>
@@ -7620,16 +7843,19 @@
         <v>0</v>
       </c>
       <c r="X73" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y73" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z73" s="5">
         <v>69</v>
       </c>
-    </row>
-    <row r="74" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA73" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="74" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A74" s="1">
         <v>70</v>
       </c>
@@ -7673,10 +7899,10 @@
         <v>100</v>
       </c>
       <c r="O74" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="P74" s="4" t="s">
         <v>352</v>
-      </c>
-      <c r="P74" s="4" t="s">
-        <v>353</v>
       </c>
       <c r="Q74" s="3" t="s">
         <v>231</v>
@@ -7688,16 +7914,19 @@
         <v>0</v>
       </c>
       <c r="X74" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y74" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z74" s="5">
         <v>70</v>
       </c>
-    </row>
-    <row r="75" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA74" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="75" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A75" s="1">
         <v>71</v>
       </c>
@@ -7741,10 +7970,10 @@
         <v>100</v>
       </c>
       <c r="O75" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="P75" s="4" t="s">
         <v>354</v>
-      </c>
-      <c r="P75" s="4" t="s">
-        <v>355</v>
       </c>
       <c r="Q75" s="3" t="s">
         <v>231</v>
@@ -7756,16 +7985,19 @@
         <v>0</v>
       </c>
       <c r="X75" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y75" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z75" s="5">
         <v>71</v>
       </c>
-    </row>
-    <row r="76" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA75" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="76" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A76" s="1">
         <v>72</v>
       </c>
@@ -7809,10 +8041,10 @@
         <v>100</v>
       </c>
       <c r="O76" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="P76" s="4" t="s">
         <v>356</v>
-      </c>
-      <c r="P76" s="4" t="s">
-        <v>357</v>
       </c>
       <c r="Q76" s="3" t="s">
         <v>231</v>
@@ -7824,16 +8056,19 @@
         <v>0</v>
       </c>
       <c r="X76" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y76" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z76" s="5">
         <v>72</v>
       </c>
-    </row>
-    <row r="77" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA76" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="77" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A77" s="1">
         <v>73</v>
       </c>
@@ -7877,10 +8112,10 @@
         <v>100</v>
       </c>
       <c r="O77" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="P77" s="4" t="s">
         <v>358</v>
-      </c>
-      <c r="P77" s="4" t="s">
-        <v>359</v>
       </c>
       <c r="Q77" s="3" t="s">
         <v>231</v>
@@ -7892,16 +8127,19 @@
         <v>0</v>
       </c>
       <c r="X77" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y77" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z77" s="5">
         <v>73</v>
       </c>
-    </row>
-    <row r="78" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA77" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="78" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A78" s="1">
         <v>74</v>
       </c>
@@ -7945,10 +8183,10 @@
         <v>100</v>
       </c>
       <c r="O78" s="4" t="s">
+        <v>359</v>
+      </c>
+      <c r="P78" s="4" t="s">
         <v>360</v>
-      </c>
-      <c r="P78" s="4" t="s">
-        <v>361</v>
       </c>
       <c r="Q78" s="3" t="s">
         <v>231</v>
@@ -7960,16 +8198,19 @@
         <v>0</v>
       </c>
       <c r="X78" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y78" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z78" s="5">
         <v>74</v>
       </c>
-    </row>
-    <row r="79" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA78" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="79" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A79" s="1">
         <v>75</v>
       </c>
@@ -8013,10 +8254,10 @@
         <v>100</v>
       </c>
       <c r="O79" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="P79" s="4" t="s">
         <v>362</v>
-      </c>
-      <c r="P79" s="4" t="s">
-        <v>363</v>
       </c>
       <c r="Q79" s="3" t="s">
         <v>231</v>
@@ -8028,16 +8269,19 @@
         <v>0</v>
       </c>
       <c r="X79" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y79" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z79" s="5">
         <v>75</v>
       </c>
-    </row>
-    <row r="80" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA79" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="80" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A80" s="1">
         <v>76</v>
       </c>
@@ -8081,10 +8325,10 @@
         <v>100</v>
       </c>
       <c r="O80" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="P80" s="4" t="s">
         <v>364</v>
-      </c>
-      <c r="P80" s="4" t="s">
-        <v>365</v>
       </c>
       <c r="Q80" s="3" t="s">
         <v>231</v>
@@ -8096,16 +8340,19 @@
         <v>0</v>
       </c>
       <c r="X80" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y80" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z80" s="5">
         <v>76</v>
       </c>
-    </row>
-    <row r="81" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA80" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="81" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A81" s="1">
         <v>77</v>
       </c>
@@ -8149,10 +8396,10 @@
         <v>100</v>
       </c>
       <c r="O81" s="4" t="s">
+        <v>365</v>
+      </c>
+      <c r="P81" s="4" t="s">
         <v>366</v>
-      </c>
-      <c r="P81" s="4" t="s">
-        <v>367</v>
       </c>
       <c r="Q81" s="3" t="s">
         <v>231</v>
@@ -8164,16 +8411,19 @@
         <v>0</v>
       </c>
       <c r="X81" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y81" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z81" s="5">
         <v>77</v>
       </c>
-    </row>
-    <row r="82" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA81" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="82" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A82" s="1">
         <v>78</v>
       </c>
@@ -8217,10 +8467,10 @@
         <v>100</v>
       </c>
       <c r="O82" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="P82" s="4" t="s">
         <v>368</v>
-      </c>
-      <c r="P82" s="4" t="s">
-        <v>369</v>
       </c>
       <c r="Q82" s="3" t="s">
         <v>231</v>
@@ -8232,16 +8482,19 @@
         <v>0</v>
       </c>
       <c r="X82" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y82" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z82" s="5">
         <v>78</v>
       </c>
-    </row>
-    <row r="83" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA82" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="83" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A83" s="1">
         <v>79</v>
       </c>
@@ -8285,10 +8538,10 @@
         <v>100</v>
       </c>
       <c r="O83" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="P83" s="4" t="s">
         <v>370</v>
-      </c>
-      <c r="P83" s="4" t="s">
-        <v>371</v>
       </c>
       <c r="Q83" s="3" t="s">
         <v>231</v>
@@ -8300,16 +8553,19 @@
         <v>0</v>
       </c>
       <c r="X83" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y83" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z83" s="5">
         <v>79</v>
       </c>
-    </row>
-    <row r="84" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA83" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="84" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A84" s="1">
         <v>80</v>
       </c>
@@ -8353,10 +8609,10 @@
         <v>100</v>
       </c>
       <c r="O84" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="P84" s="4" t="s">
         <v>372</v>
-      </c>
-      <c r="P84" s="4" t="s">
-        <v>373</v>
       </c>
       <c r="Q84" s="3" t="s">
         <v>231</v>
@@ -8368,16 +8624,19 @@
         <v>0</v>
       </c>
       <c r="X84" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y84" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z84" s="5">
         <v>80</v>
       </c>
-    </row>
-    <row r="85" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA84" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="85" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A85" s="1">
         <v>81</v>
       </c>
@@ -8421,10 +8680,10 @@
         <v>100</v>
       </c>
       <c r="O85" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="P85" s="4" t="s">
         <v>374</v>
-      </c>
-      <c r="P85" s="4" t="s">
-        <v>375</v>
       </c>
       <c r="Q85" s="3" t="s">
         <v>231</v>
@@ -8436,16 +8695,19 @@
         <v>0</v>
       </c>
       <c r="X85" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y85" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z85" s="5">
         <v>81</v>
       </c>
-    </row>
-    <row r="86" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA85" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="86" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A86" s="1">
         <v>82</v>
       </c>
@@ -8489,10 +8751,10 @@
         <v>100</v>
       </c>
       <c r="O86" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="P86" s="4" t="s">
         <v>376</v>
-      </c>
-      <c r="P86" s="4" t="s">
-        <v>377</v>
       </c>
       <c r="Q86" s="3" t="s">
         <v>231</v>
@@ -8504,16 +8766,19 @@
         <v>0</v>
       </c>
       <c r="X86" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y86" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z86" s="5">
         <v>82</v>
       </c>
-    </row>
-    <row r="87" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA86" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="87" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A87" s="1">
         <v>83</v>
       </c>
@@ -8557,10 +8822,10 @@
         <v>100</v>
       </c>
       <c r="O87" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="P87" s="4" t="s">
         <v>378</v>
-      </c>
-      <c r="P87" s="4" t="s">
-        <v>379</v>
       </c>
       <c r="Q87" s="3" t="s">
         <v>231</v>
@@ -8572,16 +8837,19 @@
         <v>0</v>
       </c>
       <c r="X87" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y87" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z87" s="5">
         <v>83</v>
       </c>
-    </row>
-    <row r="88" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA87" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="88" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A88" s="1">
         <v>84</v>
       </c>
@@ -8625,10 +8893,10 @@
         <v>100</v>
       </c>
       <c r="O88" s="4" t="s">
+        <v>379</v>
+      </c>
+      <c r="P88" s="4" t="s">
         <v>380</v>
-      </c>
-      <c r="P88" s="4" t="s">
-        <v>381</v>
       </c>
       <c r="Q88" s="3" t="s">
         <v>231</v>
@@ -8640,16 +8908,19 @@
         <v>0</v>
       </c>
       <c r="X88" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y88" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z88" s="5">
         <v>84</v>
       </c>
-    </row>
-    <row r="89" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA88" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="89" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A89" s="1">
         <v>85</v>
       </c>
@@ -8693,10 +8964,10 @@
         <v>100</v>
       </c>
       <c r="O89" s="4" t="s">
+        <v>381</v>
+      </c>
+      <c r="P89" s="4" t="s">
         <v>382</v>
-      </c>
-      <c r="P89" s="4" t="s">
-        <v>383</v>
       </c>
       <c r="Q89" s="3" t="s">
         <v>231</v>
@@ -8708,16 +8979,19 @@
         <v>0</v>
       </c>
       <c r="X89" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y89" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z89" s="5">
         <v>85</v>
       </c>
-    </row>
-    <row r="90" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA89" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="90" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A90" s="1">
         <v>86</v>
       </c>
@@ -8761,10 +9035,10 @@
         <v>100</v>
       </c>
       <c r="O90" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="P90" s="4" t="s">
         <v>384</v>
-      </c>
-      <c r="P90" s="4" t="s">
-        <v>385</v>
       </c>
       <c r="Q90" s="3" t="s">
         <v>231</v>
@@ -8776,16 +9050,19 @@
         <v>0</v>
       </c>
       <c r="X90" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y90" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z90" s="5">
         <v>86</v>
       </c>
-    </row>
-    <row r="91" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA90" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="91" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A91" s="1">
         <v>87</v>
       </c>
@@ -8829,10 +9106,10 @@
         <v>100</v>
       </c>
       <c r="O91" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="P91" s="4" t="s">
         <v>386</v>
-      </c>
-      <c r="P91" s="4" t="s">
-        <v>387</v>
       </c>
       <c r="Q91" s="3" t="s">
         <v>231</v>
@@ -8844,16 +9121,19 @@
         <v>0</v>
       </c>
       <c r="X91" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y91" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z91" s="5">
         <v>87</v>
       </c>
-    </row>
-    <row r="92" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA91" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="92" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A92" s="1">
         <v>88</v>
       </c>
@@ -8897,10 +9177,10 @@
         <v>100</v>
       </c>
       <c r="O92" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="P92" s="4" t="s">
         <v>388</v>
-      </c>
-      <c r="P92" s="4" t="s">
-        <v>389</v>
       </c>
       <c r="Q92" s="3" t="s">
         <v>231</v>
@@ -8912,16 +9192,19 @@
         <v>0</v>
       </c>
       <c r="X92" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y92" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z92" s="5">
         <v>88</v>
       </c>
-    </row>
-    <row r="93" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA92" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="93" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A93" s="1">
         <v>89</v>
       </c>
@@ -8965,10 +9248,10 @@
         <v>100</v>
       </c>
       <c r="O93" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="P93" s="4" t="s">
         <v>390</v>
-      </c>
-      <c r="P93" s="4" t="s">
-        <v>391</v>
       </c>
       <c r="Q93" s="3" t="s">
         <v>231</v>
@@ -8980,16 +9263,19 @@
         <v>0</v>
       </c>
       <c r="X93" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y93" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z93" s="5">
         <v>89</v>
       </c>
-    </row>
-    <row r="94" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA93" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="94" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A94" s="1">
         <v>90</v>
       </c>
@@ -9033,10 +9319,10 @@
         <v>100</v>
       </c>
       <c r="O94" s="4" t="s">
+        <v>391</v>
+      </c>
+      <c r="P94" s="4" t="s">
         <v>392</v>
-      </c>
-      <c r="P94" s="4" t="s">
-        <v>393</v>
       </c>
       <c r="Q94" s="3" t="s">
         <v>231</v>
@@ -9048,16 +9334,19 @@
         <v>0</v>
       </c>
       <c r="X94" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y94" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z94" s="5">
         <v>90</v>
       </c>
-    </row>
-    <row r="95" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA94" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="95" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A95" s="1">
         <v>91</v>
       </c>
@@ -9101,10 +9390,10 @@
         <v>100</v>
       </c>
       <c r="O95" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="P95" s="4" t="s">
         <v>394</v>
-      </c>
-      <c r="P95" s="4" t="s">
-        <v>395</v>
       </c>
       <c r="Q95" s="3" t="s">
         <v>231</v>
@@ -9116,16 +9405,19 @@
         <v>0</v>
       </c>
       <c r="X95" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y95" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z95" s="5">
         <v>91</v>
       </c>
-    </row>
-    <row r="96" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA95" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="96" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A96" s="1">
         <v>92</v>
       </c>
@@ -9169,10 +9461,10 @@
         <v>100</v>
       </c>
       <c r="O96" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="P96" s="4" t="s">
         <v>396</v>
-      </c>
-      <c r="P96" s="4" t="s">
-        <v>397</v>
       </c>
       <c r="Q96" s="3" t="s">
         <v>231</v>
@@ -9184,16 +9476,19 @@
         <v>0</v>
       </c>
       <c r="X96" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y96" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z96" s="5">
         <v>92</v>
       </c>
-    </row>
-    <row r="97" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA96" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="97" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A97" s="1">
         <v>93</v>
       </c>
@@ -9237,10 +9532,10 @@
         <v>100</v>
       </c>
       <c r="O97" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="P97" s="4" t="s">
         <v>398</v>
-      </c>
-      <c r="P97" s="4" t="s">
-        <v>399</v>
       </c>
       <c r="Q97" s="3" t="s">
         <v>231</v>
@@ -9252,16 +9547,19 @@
         <v>0</v>
       </c>
       <c r="X97" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y97" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z97" s="5">
         <v>93</v>
       </c>
-    </row>
-    <row r="98" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA97" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="98" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A98" s="1">
         <v>94</v>
       </c>
@@ -9305,10 +9603,10 @@
         <v>100</v>
       </c>
       <c r="O98" s="4" t="s">
+        <v>399</v>
+      </c>
+      <c r="P98" s="4" t="s">
         <v>400</v>
-      </c>
-      <c r="P98" s="4" t="s">
-        <v>401</v>
       </c>
       <c r="Q98" s="3" t="s">
         <v>231</v>
@@ -9320,16 +9618,19 @@
         <v>0</v>
       </c>
       <c r="X98" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y98" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z98" s="5">
         <v>94</v>
       </c>
-    </row>
-    <row r="99" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA98" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="99" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A99" s="1">
         <v>95</v>
       </c>
@@ -9373,10 +9674,10 @@
         <v>100</v>
       </c>
       <c r="O99" s="4" t="s">
+        <v>401</v>
+      </c>
+      <c r="P99" s="4" t="s">
         <v>402</v>
-      </c>
-      <c r="P99" s="4" t="s">
-        <v>403</v>
       </c>
       <c r="Q99" s="3" t="s">
         <v>231</v>
@@ -9388,16 +9689,19 @@
         <v>0</v>
       </c>
       <c r="X99" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y99" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z99" s="5">
         <v>95</v>
       </c>
-    </row>
-    <row r="100" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA99" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="100" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A100" s="1">
         <v>96</v>
       </c>
@@ -9441,10 +9745,10 @@
         <v>100</v>
       </c>
       <c r="O100" s="4" t="s">
+        <v>403</v>
+      </c>
+      <c r="P100" s="4" t="s">
         <v>404</v>
-      </c>
-      <c r="P100" s="4" t="s">
-        <v>405</v>
       </c>
       <c r="Q100" s="3" t="s">
         <v>231</v>
@@ -9456,16 +9760,19 @@
         <v>0</v>
       </c>
       <c r="X100" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y100" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z100" s="5">
         <v>96</v>
       </c>
-    </row>
-    <row r="101" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA100" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="101" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A101" s="1">
         <v>97</v>
       </c>
@@ -9509,10 +9816,10 @@
         <v>100</v>
       </c>
       <c r="O101" s="4" t="s">
+        <v>405</v>
+      </c>
+      <c r="P101" s="4" t="s">
         <v>406</v>
-      </c>
-      <c r="P101" s="4" t="s">
-        <v>407</v>
       </c>
       <c r="Q101" s="3" t="s">
         <v>231</v>
@@ -9524,16 +9831,19 @@
         <v>0</v>
       </c>
       <c r="X101" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y101" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z101" s="5">
         <v>97</v>
       </c>
-    </row>
-    <row r="102" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA101" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="102" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A102" s="1">
         <v>98</v>
       </c>
@@ -9577,10 +9887,10 @@
         <v>100</v>
       </c>
       <c r="O102" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="P102" s="4" t="s">
         <v>408</v>
-      </c>
-      <c r="P102" s="4" t="s">
-        <v>409</v>
       </c>
       <c r="Q102" s="3" t="s">
         <v>231</v>
@@ -9592,16 +9902,19 @@
         <v>0</v>
       </c>
       <c r="X102" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y102" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z102" s="5">
         <v>98</v>
       </c>
-    </row>
-    <row r="103" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA102" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="103" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A103" s="1">
         <v>99</v>
       </c>
@@ -9645,10 +9958,10 @@
         <v>100</v>
       </c>
       <c r="O103" s="4" t="s">
+        <v>409</v>
+      </c>
+      <c r="P103" s="4" t="s">
         <v>410</v>
-      </c>
-      <c r="P103" s="4" t="s">
-        <v>411</v>
       </c>
       <c r="Q103" s="3" t="s">
         <v>231</v>
@@ -9660,16 +9973,19 @@
         <v>0</v>
       </c>
       <c r="X103" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y103" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z103" s="5">
         <v>99</v>
       </c>
-    </row>
-    <row r="104" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA103" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="104" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A104" s="1">
         <v>100</v>
       </c>
@@ -9713,10 +10029,10 @@
         <v>100</v>
       </c>
       <c r="O104" s="4" t="s">
+        <v>411</v>
+      </c>
+      <c r="P104" s="4" t="s">
         <v>412</v>
-      </c>
-      <c r="P104" s="4" t="s">
-        <v>413</v>
       </c>
       <c r="Q104" s="3" t="s">
         <v>231</v>
@@ -9728,16 +10044,19 @@
         <v>0</v>
       </c>
       <c r="X104" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y104" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z104" s="5">
         <v>100</v>
       </c>
-    </row>
-    <row r="105" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA104" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="105" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A105" s="1">
         <v>101</v>
       </c>
@@ -9781,10 +10100,10 @@
         <v>100</v>
       </c>
       <c r="O105" s="4" t="s">
+        <v>413</v>
+      </c>
+      <c r="P105" s="4" t="s">
         <v>414</v>
-      </c>
-      <c r="P105" s="4" t="s">
-        <v>415</v>
       </c>
       <c r="Q105" s="3" t="s">
         <v>231</v>
@@ -9796,16 +10115,19 @@
         <v>0</v>
       </c>
       <c r="X105" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y105" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z105" s="5">
         <v>101</v>
       </c>
-    </row>
-    <row r="106" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA105" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="106" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A106" s="1">
         <v>102</v>
       </c>
@@ -9849,10 +10171,10 @@
         <v>100</v>
       </c>
       <c r="O106" s="4" t="s">
+        <v>415</v>
+      </c>
+      <c r="P106" s="4" t="s">
         <v>416</v>
-      </c>
-      <c r="P106" s="4" t="s">
-        <v>417</v>
       </c>
       <c r="Q106" s="3" t="s">
         <v>231</v>
@@ -9864,16 +10186,19 @@
         <v>0</v>
       </c>
       <c r="X106" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y106" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z106" s="5">
         <v>102</v>
       </c>
-    </row>
-    <row r="107" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA106" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="107" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A107" s="1">
         <v>103</v>
       </c>
@@ -9917,10 +10242,10 @@
         <v>100</v>
       </c>
       <c r="O107" s="4" t="s">
+        <v>417</v>
+      </c>
+      <c r="P107" s="4" t="s">
         <v>418</v>
-      </c>
-      <c r="P107" s="4" t="s">
-        <v>419</v>
       </c>
       <c r="Q107" s="3" t="s">
         <v>231</v>
@@ -9932,16 +10257,19 @@
         <v>0</v>
       </c>
       <c r="X107" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y107" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z107" s="5">
         <v>103</v>
       </c>
-    </row>
-    <row r="108" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA107" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="108" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A108" s="1">
         <v>104</v>
       </c>
@@ -9985,10 +10313,10 @@
         <v>100</v>
       </c>
       <c r="O108" s="4" t="s">
+        <v>419</v>
+      </c>
+      <c r="P108" s="4" t="s">
         <v>420</v>
-      </c>
-      <c r="P108" s="4" t="s">
-        <v>421</v>
       </c>
       <c r="Q108" s="3" t="s">
         <v>231</v>
@@ -10000,16 +10328,19 @@
         <v>0</v>
       </c>
       <c r="X108" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y108" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z108" s="5">
         <v>104</v>
       </c>
-    </row>
-    <row r="109" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA108" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="109" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A109" s="1">
         <v>105</v>
       </c>
@@ -10053,10 +10384,10 @@
         <v>100</v>
       </c>
       <c r="O109" s="4" t="s">
+        <v>421</v>
+      </c>
+      <c r="P109" s="4" t="s">
         <v>422</v>
-      </c>
-      <c r="P109" s="4" t="s">
-        <v>423</v>
       </c>
       <c r="Q109" s="3" t="s">
         <v>231</v>
@@ -10068,16 +10399,19 @@
         <v>0</v>
       </c>
       <c r="X109" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y109" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z109" s="5">
         <v>105</v>
       </c>
-    </row>
-    <row r="110" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA109" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="110" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A110" s="1">
         <v>106</v>
       </c>
@@ -10121,10 +10455,10 @@
         <v>100</v>
       </c>
       <c r="O110" s="4" t="s">
+        <v>423</v>
+      </c>
+      <c r="P110" s="4" t="s">
         <v>424</v>
-      </c>
-      <c r="P110" s="4" t="s">
-        <v>425</v>
       </c>
       <c r="Q110" s="3" t="s">
         <v>231</v>
@@ -10136,16 +10470,19 @@
         <v>0</v>
       </c>
       <c r="X110" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y110" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z110" s="5">
         <v>106</v>
       </c>
-    </row>
-    <row r="111" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA110" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="111" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A111" s="1">
         <v>107</v>
       </c>
@@ -10189,10 +10526,10 @@
         <v>100</v>
       </c>
       <c r="O111" s="4" t="s">
+        <v>425</v>
+      </c>
+      <c r="P111" s="4" t="s">
         <v>426</v>
-      </c>
-      <c r="P111" s="4" t="s">
-        <v>427</v>
       </c>
       <c r="Q111" s="3" t="s">
         <v>231</v>
@@ -10204,16 +10541,19 @@
         <v>0</v>
       </c>
       <c r="X111" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y111" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z111" s="5">
         <v>107</v>
       </c>
-    </row>
-    <row r="112" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA111" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="112" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A112" s="1">
         <v>108</v>
       </c>
@@ -10257,10 +10597,10 @@
         <v>100</v>
       </c>
       <c r="O112" s="4" t="s">
+        <v>427</v>
+      </c>
+      <c r="P112" s="4" t="s">
         <v>428</v>
-      </c>
-      <c r="P112" s="4" t="s">
-        <v>429</v>
       </c>
       <c r="Q112" s="3" t="s">
         <v>231</v>
@@ -10272,16 +10612,19 @@
         <v>0</v>
       </c>
       <c r="X112" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y112" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z112" s="5">
         <v>108</v>
       </c>
-    </row>
-    <row r="113" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA112" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="113" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A113" s="1">
         <v>109</v>
       </c>
@@ -10325,10 +10668,10 @@
         <v>100</v>
       </c>
       <c r="O113" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="P113" s="4" t="s">
         <v>430</v>
-      </c>
-      <c r="P113" s="4" t="s">
-        <v>431</v>
       </c>
       <c r="Q113" s="3" t="s">
         <v>231</v>
@@ -10340,16 +10683,19 @@
         <v>0</v>
       </c>
       <c r="X113" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y113" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z113" s="5">
         <v>109</v>
       </c>
-    </row>
-    <row r="114" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA113" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="114" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A114" s="1">
         <v>110</v>
       </c>
@@ -10393,10 +10739,10 @@
         <v>100</v>
       </c>
       <c r="O114" s="4" t="s">
+        <v>431</v>
+      </c>
+      <c r="P114" s="4" t="s">
         <v>432</v>
-      </c>
-      <c r="P114" s="4" t="s">
-        <v>433</v>
       </c>
       <c r="Q114" s="3" t="s">
         <v>231</v>
@@ -10408,16 +10754,19 @@
         <v>0</v>
       </c>
       <c r="X114" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y114" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z114" s="5">
         <v>110</v>
       </c>
-    </row>
-    <row r="115" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA114" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="115" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A115" s="1">
         <v>111</v>
       </c>
@@ -10461,10 +10810,10 @@
         <v>100</v>
       </c>
       <c r="O115" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="P115" s="4" t="s">
         <v>434</v>
-      </c>
-      <c r="P115" s="4" t="s">
-        <v>435</v>
       </c>
       <c r="Q115" s="3" t="s">
         <v>231</v>
@@ -10476,16 +10825,19 @@
         <v>0</v>
       </c>
       <c r="X115" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y115" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z115" s="5">
         <v>111</v>
       </c>
-    </row>
-    <row r="116" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA115" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="116" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A116" s="1">
         <v>112</v>
       </c>
@@ -10529,10 +10881,10 @@
         <v>100</v>
       </c>
       <c r="O116" s="4" t="s">
+        <v>435</v>
+      </c>
+      <c r="P116" s="4" t="s">
         <v>436</v>
-      </c>
-      <c r="P116" s="4" t="s">
-        <v>437</v>
       </c>
       <c r="Q116" s="3" t="s">
         <v>231</v>
@@ -10544,16 +10896,19 @@
         <v>0</v>
       </c>
       <c r="X116" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y116" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z116" s="5">
         <v>112</v>
       </c>
-    </row>
-    <row r="117" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA116" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="117" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A117" s="1">
         <v>113</v>
       </c>
@@ -10597,10 +10952,10 @@
         <v>100</v>
       </c>
       <c r="O117" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="P117" s="4" t="s">
         <v>438</v>
-      </c>
-      <c r="P117" s="4" t="s">
-        <v>439</v>
       </c>
       <c r="Q117" s="3" t="s">
         <v>231</v>
@@ -10612,16 +10967,19 @@
         <v>0</v>
       </c>
       <c r="X117" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y117" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z117" s="5">
         <v>113</v>
       </c>
-    </row>
-    <row r="118" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA117" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="118" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A118" s="1">
         <v>114</v>
       </c>
@@ -10665,10 +11023,10 @@
         <v>100</v>
       </c>
       <c r="O118" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="P118" s="4" t="s">
         <v>440</v>
-      </c>
-      <c r="P118" s="4" t="s">
-        <v>441</v>
       </c>
       <c r="Q118" s="3" t="s">
         <v>231</v>
@@ -10680,16 +11038,19 @@
         <v>0</v>
       </c>
       <c r="X118" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y118" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z118" s="5">
         <v>114</v>
       </c>
-    </row>
-    <row r="119" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA118" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="119" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A119" s="1">
         <v>115</v>
       </c>
@@ -10733,10 +11094,10 @@
         <v>100</v>
       </c>
       <c r="O119" s="4" t="s">
+        <v>441</v>
+      </c>
+      <c r="P119" s="4" t="s">
         <v>442</v>
-      </c>
-      <c r="P119" s="4" t="s">
-        <v>443</v>
       </c>
       <c r="Q119" s="3" t="s">
         <v>231</v>
@@ -10748,16 +11109,19 @@
         <v>0</v>
       </c>
       <c r="X119" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y119" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z119" s="5">
         <v>115</v>
       </c>
-    </row>
-    <row r="120" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA119" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="120" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A120" s="1">
         <v>116</v>
       </c>
@@ -10801,10 +11165,10 @@
         <v>100</v>
       </c>
       <c r="O120" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="P120" s="4" t="s">
         <v>444</v>
-      </c>
-      <c r="P120" s="4" t="s">
-        <v>445</v>
       </c>
       <c r="Q120" s="3" t="s">
         <v>231</v>
@@ -10816,16 +11180,19 @@
         <v>0</v>
       </c>
       <c r="X120" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y120" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z120" s="5">
         <v>116</v>
       </c>
-    </row>
-    <row r="121" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="AA120" s="5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="121" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A121" s="1">
         <v>117</v>
       </c>
@@ -10869,10 +11236,10 @@
         <v>100</v>
       </c>
       <c r="O121" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="P121" s="4" t="s">
         <v>446</v>
-      </c>
-      <c r="P121" s="4" t="s">
-        <v>447</v>
       </c>
       <c r="Q121" s="3" t="s">
         <v>231</v>
@@ -10884,16 +11251,19 @@
         <v>0</v>
       </c>
       <c r="X121" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y121" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z121" s="